--- a/lot_recon.xlsx
+++ b/lot_recon.xlsx
@@ -16,11 +16,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Removed" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Appliance Parts'!$A$1:$O$38</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Appliance Parts'!$A$1:$O$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wolf New'!$A$1:$O$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wolf Used'!$A$1:$O$189</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Wolf Unclear'!$A$1:$O$43</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Removed'!$A$1:$O$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -581,7 +581,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Last updated: 2026-10-18 08:06 ET</t>
+          <t>Last updated: 2026-10-18 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -595,7 +595,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Active listings: 280 · Removed: 0</t>
+          <t>Active listings: 285 · Removed: 0</t>
         </is>
       </c>
     </row>
@@ -645,10 +645,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>83696</v>
+        <v>84696</v>
       </c>
       <c r="D8" t="n">
         <v>4</v>
@@ -712,13 +712,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -728,10 +728,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>900075.08</v>
+        <v>901075.08</v>
       </c>
     </row>
     <row r="15">
@@ -795,7 +795,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -810,7 +810,7 @@
         <v>1</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>4023.69</v>
@@ -960,7 +960,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -975,7 +975,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="6" t="n">
         <v>0</v>
@@ -1290,10 +1290,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D32" t="n">
         <v>0</v>
@@ -1308,49 +1308,82 @@
         <v>0</v>
       </c>
       <c r="H32" s="6" t="n">
-        <v>40000</v>
+        <v>41000</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2575</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="15" customHeight="1">
+          <t>2575–2629</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Unknown location</t>
+          <t>West / Other</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>75</v>
+        <v>2</v>
       </c>
       <c r="C33" t="n">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
         <v>0</v>
       </c>
-      <c r="D33" t="n">
-        <v>14</v>
-      </c>
       <c r="E33" t="n">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
       </c>
       <c r="G33" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="H33" s="6" t="n">
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>2307</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="15" customHeight="1">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Unknown location</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>75</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>14</v>
+      </c>
+      <c r="E34" t="n">
+        <v>61</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="6" t="n">
         <v>285195.89</v>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="9" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>Price $ (est.) = asking price or current high bid (+ stated shipping); items with no $ figure count as 0.</t>
         </is>
@@ -1367,7 +1400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O38"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2917,7 +2950,7 @@
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>▸ California  (1)</t>
+          <t>▸ California  (2)</t>
         </is>
       </c>
       <c r="B36" s="12" t="n"/>
@@ -2996,35 +3029,211 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="17" t="inlineStr">
+    <row r="38" outlineLevel="1">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>Coin-op Whirlpool washer &amp; dryer parts (late 80s–mid 90s) – OEM parts, 40+ coin boxes, consoles, 12 transmissions</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
+        <is>
+          <t>bulk lot</t>
+        </is>
+      </c>
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>Chico</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>2629</v>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>$1,000</t>
+        </is>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="J38" s="13" t="inlineStr"/>
+      <c r="K38" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L38" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M38" s="13" t="inlineStr"/>
+      <c r="N38" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O38" s="14" t="inlineStr">
+        <is>
+          <t>Retired laundry-route owner (35 yrs). Calls only, no shipping, pickup in Chico. No motors or pumps. Niche older coin-op parts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="17" t="inlineStr">
         <is>
           <t>Subtotal — California</t>
         </is>
       </c>
-      <c r="B38" s="17" t="inlineStr">
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>2 item(s)</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="n"/>
+      <c r="D39" s="18" t="n"/>
+      <c r="E39" s="18" t="n"/>
+      <c r="F39" s="18" t="n"/>
+      <c r="G39" s="18" t="n"/>
+      <c r="H39" s="19" t="n">
+        <v>41000</v>
+      </c>
+      <c r="I39" s="18" t="n"/>
+      <c r="J39" s="18" t="n"/>
+      <c r="K39" s="18" t="n"/>
+      <c r="L39" s="18" t="n"/>
+      <c r="M39" s="18" t="n"/>
+      <c r="N39" s="18" t="n"/>
+      <c r="O39" s="18" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t>▸ West / Other  (1)</t>
+        </is>
+      </c>
+      <c r="B40" s="12" t="n"/>
+      <c r="C40" s="12" t="n"/>
+      <c r="D40" s="12" t="n"/>
+      <c r="E40" s="12" t="n"/>
+      <c r="F40" s="12" t="n"/>
+      <c r="G40" s="12" t="n"/>
+      <c r="H40" s="12" t="n"/>
+      <c r="I40" s="12" t="n"/>
+      <c r="J40" s="12" t="n"/>
+      <c r="K40" s="12" t="n"/>
+      <c r="L40" s="12" t="n"/>
+      <c r="M40" s="12" t="n"/>
+      <c r="N40" s="12" t="n"/>
+      <c r="O40" s="12" t="n"/>
+    </row>
+    <row r="41" outlineLevel="1">
+      <c r="A41" s="13" t="inlineStr">
+        <is>
+          <t>West / Other</t>
+        </is>
+      </c>
+      <c r="B41" s="14" t="inlineStr">
+        <is>
+          <t>Storage locker filled with appliance parts – washer/dryer parts, heating elements, cords, rollers, belts, tools</t>
+        </is>
+      </c>
+      <c r="C41" s="13" t="inlineStr">
+        <is>
+          <t>bulk lot</t>
+        </is>
+      </c>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="E41" s="13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="F41" s="13" t="n">
+        <v>2307</v>
+      </c>
+      <c r="G41" s="13" t="inlineStr">
+        <is>
+          <t>Message for pricing</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="n"/>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J41" s="13" t="inlineStr"/>
+      <c r="K41" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L41" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M41" s="13" t="inlineStr"/>
+      <c r="N41" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O41" s="14" t="inlineStr">
+        <is>
+          <t>Seller is getting out of the appliance business; selling the whole locker (North Phoenix, Deer Valley Rd near 19th Ave). Delivery available per post. Separate from the Phoenix parts-store closing ad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — West / Other</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C38" s="18" t="n"/>
-      <c r="D38" s="18" t="n"/>
-      <c r="E38" s="18" t="n"/>
-      <c r="F38" s="18" t="n"/>
-      <c r="G38" s="18" t="n"/>
-      <c r="H38" s="19" t="n">
-        <v>40000</v>
-      </c>
-      <c r="I38" s="18" t="n"/>
-      <c r="J38" s="18" t="n"/>
-      <c r="K38" s="18" t="n"/>
-      <c r="L38" s="18" t="n"/>
-      <c r="M38" s="18" t="n"/>
-      <c r="N38" s="18" t="n"/>
-      <c r="O38" s="18" t="n"/>
+      <c r="C42" s="18" t="n"/>
+      <c r="D42" s="18" t="n"/>
+      <c r="E42" s="18" t="n"/>
+      <c r="F42" s="18" t="n"/>
+      <c r="G42" s="18" t="n"/>
+      <c r="H42" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="18" t="n"/>
+      <c r="J42" s="18" t="n"/>
+      <c r="K42" s="18" t="n"/>
+      <c r="L42" s="18" t="n"/>
+      <c r="M42" s="18" t="n"/>
+      <c r="N42" s="18" t="n"/>
+      <c r="O42" s="18" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O38"/>
+  <autoFilter ref="A1:O42"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId2"/>
@@ -3043,6 +3252,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18521,7 +18732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:O69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -18621,7 +18832,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>▸ Greater Boston / South Shore (&lt;50mi)  (4)</t>
+          <t>▸ Greater Boston / South Shore (&lt;50mi)  (5)</t>
         </is>
       </c>
       <c r="B2" s="12" t="n"/>
@@ -18836,17 +19047,17 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>Cannabis facility contents incl. commercial kitchen / stainless</t>
+          <t>Retirement bulk tool lot – 10 tools, sold together</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>facility contents</t>
+          <t>retirement</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Waltham</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -18855,23 +19066,23 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>Auction, 18% BP</t>
+          <t>$250 all</t>
         </is>
       </c>
       <c r="H6" s="15" t="n"/>
-      <c r="I6" s="13" t="inlineStr"/>
-      <c r="J6" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-03 10:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr"/>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>Paul E. Saperstein (PESCO)</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L6" s="13" t="inlineStr">
@@ -18887,120 +19098,120 @@
       </c>
       <c r="O6" s="14" t="inlineStr">
         <is>
+          <t>Small off-category FYI; seller says resell individually.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" outlineLevel="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Greater Boston / South Shore (&lt;50mi)</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Cannabis facility contents incl. commercial kitchen / stainless</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>facility contents</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Milford</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>Auction, 18% BP</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="n"/>
+      <c r="I7" s="13" t="inlineStr"/>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-03 10:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>Paul E. Saperstein (PESCO)</t>
+        </is>
+      </c>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M7" s="13" t="inlineStr"/>
+      <c r="N7" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O7" s="14" t="inlineStr">
+        <is>
           <t>Calendar page only (no event page yet). ~45 mi.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Greater Boston / South Shore (&lt;50mi)</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>4 item(s)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="n"/>
-      <c r="D7" s="18" t="n"/>
-      <c r="E7" s="18" t="n"/>
-      <c r="F7" s="18" t="n"/>
-      <c r="G7" s="18" t="n"/>
-      <c r="H7" s="19" t="n">
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>5 item(s)</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="n"/>
+      <c r="D8" s="18" t="n"/>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="18" t="n"/>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="18" t="n"/>
-      <c r="J7" s="18" t="n"/>
-      <c r="K7" s="18" t="n"/>
-      <c r="L7" s="18" t="n"/>
-      <c r="M7" s="18" t="n"/>
-      <c r="N7" s="18" t="n"/>
-      <c r="O7" s="18" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="I8" s="18" t="n"/>
+      <c r="J8" s="18" t="n"/>
+      <c r="K8" s="18" t="n"/>
+      <c r="L8" s="18" t="n"/>
+      <c r="M8" s="18" t="n"/>
+      <c r="N8" s="18" t="n"/>
+      <c r="O8" s="18" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>▸ North Shore / Merrimack Valley / S. NH  (2)</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n"/>
-      <c r="C8" s="12" t="n"/>
-      <c r="D8" s="12" t="n"/>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="12" t="n"/>
-      <c r="G8" s="12" t="n"/>
-      <c r="H8" s="12" t="n"/>
-      <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="12" t="n"/>
-      <c r="M8" s="12" t="n"/>
-      <c r="N8" s="12" t="n"/>
-      <c r="O8" s="12" t="n"/>
-    </row>
-    <row r="9" outlineLevel="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>North Shore / Merrimack Valley / S. NH</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>Commercial mechanical/plumbing/HVAC contractor inventory – multiple pallets of boxed stock, water heater, venting, diffusers</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>Merrimack</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>NH</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>62</v>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>$1 placeholder – make offer on everything</t>
-        </is>
-      </c>
-      <c r="H9" s="15" t="n"/>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="J9" s="13" t="inlineStr"/>
-      <c r="K9" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L9" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M9" s="13" t="inlineStr"/>
-      <c r="N9" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O9" s="14" t="inlineStr">
-        <is>
-          <t>Bulk buyers preferred.</t>
-        </is>
-      </c>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="12" t="n"/>
+      <c r="M9" s="12" t="n"/>
+      <c r="N9" s="12" t="n"/>
+      <c r="O9" s="12" t="n"/>
     </row>
     <row r="10" outlineLevel="1">
       <c r="A10" s="13" t="inlineStr">
@@ -19010,17 +19221,17 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating overstock/returns online auction – 183 lots (fixtures, furnaces, heaters, A/C)</t>
+          <t>Commercial mechanical/plumbing/HVAC contractor inventory – multiple pallets of boxed stock, water heater, venting, diffusers</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>Concord</t>
+          <t>Merrimack</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
@@ -19029,27 +19240,23 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>$1 placeholder – make offer on everything</t>
         </is>
       </c>
       <c r="H10" s="15" t="n"/>
       <c r="I10" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="J10" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-27 07:00 PM ET</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr"/>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Atlantic Auction Co.)</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L10" s="13" t="inlineStr">
@@ -19065,120 +19272,124 @@
       </c>
       <c r="O10" s="14" t="inlineStr">
         <is>
+          <t>Bulk buyers preferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" outlineLevel="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>North Shore / Merrimack Valley / S. NH</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Plumbing &amp; heating overstock/returns online auction – 183 lots (fixtures, furnaces, heaters, A/C)</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>auction</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Concord</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>84</v>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Online auction</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="n"/>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-27 07:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (Atlantic Auction Co.)</t>
+        </is>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M11" s="13" t="inlineStr"/>
+      <c r="N11" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O11" s="14" t="inlineStr">
+        <is>
           <t>Overstock sale, not a closing. Pickup Oct 29–30.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Subtotal — North Shore / Merrimack Valley / S. NH</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>2 item(s)</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n"/>
-      <c r="D11" s="18" t="n"/>
-      <c r="E11" s="18" t="n"/>
-      <c r="F11" s="18" t="n"/>
-      <c r="G11" s="18" t="n"/>
-      <c r="H11" s="19" t="n">
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="18" t="n"/>
-      <c r="J11" s="18" t="n"/>
-      <c r="K11" s="18" t="n"/>
-      <c r="L11" s="18" t="n"/>
-      <c r="M11" s="18" t="n"/>
-      <c r="N11" s="18" t="n"/>
-      <c r="O11" s="18" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="I12" s="18" t="n"/>
+      <c r="J12" s="18" t="n"/>
+      <c r="K12" s="18" t="n"/>
+      <c r="L12" s="18" t="n"/>
+      <c r="M12" s="18" t="n"/>
+      <c r="N12" s="18" t="n"/>
+      <c r="O12" s="18" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>▸ Central / Western MA  (3)</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
-      <c r="H12" s="12" t="n"/>
-      <c r="I12" s="12" t="n"/>
-      <c r="J12" s="12" t="n"/>
-      <c r="K12" s="12" t="n"/>
-      <c r="L12" s="12" t="n"/>
-      <c r="M12" s="12" t="n"/>
-      <c r="N12" s="12" t="n"/>
-      <c r="O12" s="12" t="n"/>
-    </row>
-    <row r="13" outlineLevel="1">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Central / Western MA</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>Gift/souvenir store closing (retirement) – all new stock</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>store closing</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>Thorndike</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>77</v>
-      </c>
-      <c r="G13" s="13" t="inlineStr">
-        <is>
-          <t>By appointment</t>
-        </is>
-      </c>
-      <c r="H13" s="15" t="n"/>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J13" s="13" t="inlineStr"/>
-      <c r="K13" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L13" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M13" s="13" t="inlineStr"/>
-      <c r="N13" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O13" s="14" t="inlineStr">
-        <is>
-          <t>Updated Oct 8. Off-category FYI.</t>
-        </is>
-      </c>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+      <c r="H13" s="12" t="n"/>
+      <c r="I13" s="12" t="n"/>
+      <c r="J13" s="12" t="n"/>
+      <c r="K13" s="12" t="n"/>
+      <c r="L13" s="12" t="n"/>
+      <c r="M13" s="12" t="n"/>
+      <c r="N13" s="12" t="n"/>
+      <c r="O13" s="12" t="n"/>
     </row>
     <row r="14" outlineLevel="1">
       <c r="A14" s="13" t="inlineStr">
@@ -19188,17 +19399,17 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>UNECO Manufacturing – owners retiring, machine-shop metrology &amp; tooling</t>
+          <t>Gift/souvenir store closing (retirement) – all new stock</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>retirement</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>Chicopee</t>
+          <t>Thorndike</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
@@ -19207,23 +19418,23 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>Online auction, 18% BP</t>
+          <t>By appointment</t>
         </is>
       </c>
       <c r="H14" s="15" t="n"/>
-      <c r="I14" s="13" t="inlineStr"/>
-      <c r="J14" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-04 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="J14" s="13" t="inlineStr"/>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>HiBid (DeCosmo Industrial)</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L14" s="13" t="inlineStr">
@@ -19239,7 +19450,7 @@
       </c>
       <c r="O14" s="14" t="inlineStr">
         <is>
-          <t>Niche tooling only. Bidding opens Oct 19.</t>
+          <t>Updated Oct 8. Off-category FYI.</t>
         </is>
       </c>
     </row>
@@ -19251,17 +19462,17 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>Restaurant closing, everything must go – kitchen equipment, stainless, smallwares</t>
+          <t>UNECO Manufacturing – owners retiring, machine-shop metrology &amp; tooling</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>retirement</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>Westfield</t>
+          <t>Chicopee</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
@@ -19270,23 +19481,23 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>Make offer</t>
+          <t>Online auction, 18% BP</t>
         </is>
       </c>
       <c r="H15" s="15" t="n"/>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="J15" s="13" t="inlineStr"/>
+      <c r="I15" s="13" t="inlineStr"/>
+      <c r="J15" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-04 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>HiBid (DeCosmo Industrial)</t>
         </is>
       </c>
       <c r="L15" s="13" t="inlineStr">
@@ -19302,120 +19513,120 @@
       </c>
       <c r="O15" s="14" t="inlineStr">
         <is>
+          <t>Niche tooling only. Bidding opens Oct 19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" outlineLevel="1">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Central / Western MA</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant closing, everything must go – kitchen equipment, stainless, smallwares</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>restaurant closing</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Westfield</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>99</v>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>Make offer</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="n"/>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="inlineStr"/>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L16" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M16" s="13" t="inlineStr"/>
+      <c r="N16" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O16" s="14" t="inlineStr">
+        <is>
           <t>Related separate post "Complete Restaurant Equipment Package" $3,500 OBO (maybe same restaurant): https://www.craigslist.org/view/d/westfield-complete-restaurant-equipment/9Y5KCdhhgSqEBYbD3wKqVd</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Central / Western MA</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>3 item(s)</t>
         </is>
       </c>
-      <c r="C16" s="18" t="n"/>
-      <c r="D16" s="18" t="n"/>
-      <c r="E16" s="18" t="n"/>
-      <c r="F16" s="18" t="n"/>
-      <c r="G16" s="18" t="n"/>
-      <c r="H16" s="19" t="n">
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="18" t="n"/>
+      <c r="E17" s="18" t="n"/>
+      <c r="F17" s="18" t="n"/>
+      <c r="G17" s="18" t="n"/>
+      <c r="H17" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="18" t="n"/>
-      <c r="J16" s="18" t="n"/>
-      <c r="K16" s="18" t="n"/>
-      <c r="L16" s="18" t="n"/>
-      <c r="M16" s="18" t="n"/>
-      <c r="N16" s="18" t="n"/>
-      <c r="O16" s="18" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>▸ Maine / VT / Northern NH  (4)</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="12" t="n"/>
-      <c r="J17" s="12" t="n"/>
-      <c r="K17" s="12" t="n"/>
-      <c r="L17" s="12" t="n"/>
-      <c r="M17" s="12" t="n"/>
-      <c r="N17" s="12" t="n"/>
-      <c r="O17" s="12" t="n"/>
-    </row>
-    <row r="18" outlineLevel="1">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>Maine / VT / Northern NH</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>Oola Bowls secured-party sale – restaurant equipment bought new 2024-25 (Electro Freeze, Scotsman, Atosa)</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>restaurant</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>Scarborough</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>ME</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="n">
-        <v>104</v>
-      </c>
-      <c r="G18" s="13" t="inlineStr">
-        <is>
-          <t>Online auction (freezers $80–150 when seen)</t>
-        </is>
-      </c>
-      <c r="H18" s="15" t="n"/>
-      <c r="I18" s="13" t="inlineStr"/>
-      <c r="J18" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-19 01:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K18" s="13" t="inlineStr">
-        <is>
-          <t>Keenan Auction / Proxibid</t>
-        </is>
-      </c>
-      <c r="L18" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M18" s="13" t="inlineStr"/>
-      <c r="N18" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O18" s="14" t="inlineStr">
-        <is>
-          <t>Pickup Oct 21 only.</t>
-        </is>
-      </c>
+      <c r="I17" s="18" t="n"/>
+      <c r="J17" s="18" t="n"/>
+      <c r="K17" s="18" t="n"/>
+      <c r="L17" s="18" t="n"/>
+      <c r="M17" s="18" t="n"/>
+      <c r="N17" s="18" t="n"/>
+      <c r="O17" s="18" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>▸ Maine / VT / Northern NH  (5)</t>
+        </is>
+      </c>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="12" t="n"/>
+      <c r="H18" s="12" t="n"/>
+      <c r="I18" s="12" t="n"/>
+      <c r="J18" s="12" t="n"/>
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="12" t="n"/>
+      <c r="M18" s="12" t="n"/>
+      <c r="N18" s="12" t="n"/>
+      <c r="O18" s="12" t="n"/>
     </row>
     <row r="19" outlineLevel="1">
       <c r="A19" s="13" t="inlineStr">
@@ -19425,17 +19636,17 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>Event-rental business closing – 300+ chairs, 40+ rounds, 1,300+ china, linens (all at once)</t>
+          <t>Oola Bowls secured-party sale – restaurant equipment bought new 2024-25 (Electro Freeze, Scotsman, Atosa)</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>business closing</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>Woolwich</t>
+          <t>Scarborough</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
@@ -19444,28 +19655,28 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>No price listed</t>
+          <t>Online auction (freezers $80–150 when seen)</t>
         </is>
       </c>
       <c r="H19" s="15" t="n"/>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="J19" s="13" t="inlineStr"/>
+      <c r="I19" s="13" t="inlineStr"/>
+      <c r="J19" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 01:00 PM ET</t>
+        </is>
+      </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L19" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Keenan Auction / Proxibid</t>
+        </is>
+      </c>
+      <c r="L19" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M19" s="13" t="inlineStr"/>
@@ -19476,7 +19687,7 @@
       </c>
       <c r="O19" s="14" t="inlineStr">
         <is>
-          <t>Updated Oct 7. Replacement cost &gt;$72K per post.</t>
+          <t>Pickup Oct 21 only.</t>
         </is>
       </c>
     </row>
@@ -19488,42 +19699,42 @@
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>Pellet/wood stoves, heating stock, tools &amp; heavy equipment – "business liquidation", 380 lots</t>
+          <t>Contractor appliance lot – 3 refrigerators, Bosch wall oven, gas range, washer/dryer set</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>contractor lot</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>Lunenburg</t>
+          <t>Scarborough</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>VT</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>168</v>
+        <v>104</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>$200 OBO each, less as a bundle</t>
         </is>
       </c>
       <c r="H20" s="15" t="n"/>
-      <c r="I20" s="13" t="inlineStr"/>
-      <c r="J20" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-04 10:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="J20" s="13" t="inlineStr"/>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>Thomas Hirchak Co.</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L20" s="13" t="inlineStr">
@@ -19539,7 +19750,7 @@
       </c>
       <c r="O20" s="14" t="inlineStr">
         <is>
-          <t>Closes Wed Nov 4 10 AM, preview Oct 28, removal Nov 9, no shipping.</t>
+          <t>Working units pulled from jobs. Complete appliances, not parts.</t>
         </is>
       </c>
     </row>
@@ -19551,42 +19762,42 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>Bread Loaf Corp wind-down – contractor equipment, staging, telehandler</t>
+          <t>Event-rental business closing – 300+ chairs, 40+ rounds, 1,300+ china, linens (all at once)</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>contractor liquidation</t>
+          <t>business closing</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>Middlebury</t>
+          <t>Woolwich</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>VT</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>No price listed</t>
         </is>
       </c>
       <c r="H21" s="15" t="n"/>
-      <c r="I21" s="13" t="inlineStr"/>
-      <c r="J21" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-28 09:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J21" s="13" t="inlineStr"/>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>THC Auction</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L21" s="13" t="inlineStr">
@@ -19602,183 +19813,183 @@
       </c>
       <c r="O21" s="14" t="inlineStr">
         <is>
+          <t>Updated Oct 7. Replacement cost &gt;$72K per post.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" outlineLevel="1">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Maine / VT / Northern NH</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Pellet/wood stoves, heating stock, tools &amp; heavy equipment – "business liquidation", 380 lots</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>auction</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>Lunenburg</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>VT</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>168</v>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>Online auction</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="n"/>
+      <c r="I22" s="13" t="inlineStr"/>
+      <c r="J22" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-04 10:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>Thomas Hirchak Co.</t>
+        </is>
+      </c>
+      <c r="L22" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M22" s="13" t="inlineStr"/>
+      <c r="N22" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O22" s="14" t="inlineStr">
+        <is>
+          <t>Closes Wed Nov 4 10 AM, preview Oct 28, removal Nov 9, no shipping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" outlineLevel="1">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Maine / VT / Northern NH</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Bread Loaf Corp wind-down – contractor equipment, staging, telehandler</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>contractor liquidation</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>Middlebury</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>VT</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>177</v>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>Online auction</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="n"/>
+      <c r="I23" s="13" t="inlineStr"/>
+      <c r="J23" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>THC Auction</t>
+        </is>
+      </c>
+      <c r="L23" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M23" s="13" t="inlineStr"/>
+      <c r="N23" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O23" s="14" t="inlineStr">
+        <is>
           <t>Company wind-down.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Maine / VT / Northern NH</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
-        <is>
-          <t>4 item(s)</t>
-        </is>
-      </c>
-      <c r="C22" s="18" t="n"/>
-      <c r="D22" s="18" t="n"/>
-      <c r="E22" s="18" t="n"/>
-      <c r="F22" s="18" t="n"/>
-      <c r="G22" s="18" t="n"/>
-      <c r="H22" s="19" t="n">
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>5 item(s)</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="18" t="n"/>
+      <c r="G24" s="18" t="n"/>
+      <c r="H24" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I22" s="18" t="n"/>
-      <c r="J22" s="18" t="n"/>
-      <c r="K22" s="18" t="n"/>
-      <c r="L22" s="18" t="n"/>
-      <c r="M22" s="18" t="n"/>
-      <c r="N22" s="18" t="n"/>
-      <c r="O22" s="18" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
+      <c r="I24" s="18" t="n"/>
+      <c r="J24" s="18" t="n"/>
+      <c r="K24" s="18" t="n"/>
+      <c r="L24" s="18" t="n"/>
+      <c r="M24" s="18" t="n"/>
+      <c r="N24" s="18" t="n"/>
+      <c r="O24" s="18" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>▸ CT / Hudson Valley  (4)</t>
         </is>
       </c>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="12" t="n"/>
-      <c r="G23" s="12" t="n"/>
-      <c r="H23" s="12" t="n"/>
-      <c r="I23" s="12" t="n"/>
-      <c r="J23" s="12" t="n"/>
-      <c r="K23" s="12" t="n"/>
-      <c r="L23" s="12" t="n"/>
-      <c r="M23" s="12" t="n"/>
-      <c r="N23" s="12" t="n"/>
-      <c r="O23" s="12" t="n"/>
-    </row>
-    <row r="24" outlineLevel="1">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>CT / Hudson Valley</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>Bank-ordered electrical contractor sale – Greenlee/Hilti/Milwaukee tools, GE/Siemens breakers</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>contractor liquidation</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>Clinton</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="n">
-        <v>106</v>
-      </c>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>Online auction</t>
-        </is>
-      </c>
-      <c r="H24" s="15" t="n"/>
-      <c r="I24" s="13" t="inlineStr"/>
-      <c r="J24" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-29 05:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K24" s="13" t="inlineStr">
-        <is>
-          <t>Hamilton Group / EstateSales.net</t>
-        </is>
-      </c>
-      <c r="L24" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M24" s="13" t="inlineStr"/>
-      <c r="N24" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O24" s="14" t="inlineStr">
-        <is>
-          <t>Listed "Oct 29 2 PM PST" (= 5 PM ET).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" outlineLevel="1">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>CT / Hudson Valley</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>Major Intl Chain Surplus – 225 lots commercial refrigeration/kitchen (True, Traulsen, Hobart, Blodgett, Taylor)</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>commercial surplus</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
-          <t>Pleasant Valley</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="n">
-        <v>157</v>
-      </c>
-      <c r="G25" s="13" t="inlineStr">
-        <is>
-          <t>Online auction</t>
-        </is>
-      </c>
-      <c r="H25" s="15" t="n"/>
-      <c r="I25" s="13" t="inlineStr"/>
-      <c r="J25" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-20 02:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K25" s="13" t="inlineStr">
-        <is>
-          <t>Adams / BidWrangler</t>
-        </is>
-      </c>
-      <c r="L25" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M25" s="13" t="inlineStr"/>
-      <c r="N25" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O25" s="14" t="inlineStr">
-        <is>
-          <t>Tested and new units.</t>
-        </is>
-      </c>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="12" t="n"/>
+      <c r="N25" s="12" t="n"/>
+      <c r="O25" s="12" t="n"/>
     </row>
     <row r="26" outlineLevel="1">
       <c r="A26" s="13" t="inlineStr">
@@ -19788,17 +19999,17 @@
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>Café/bakery liquidation – Traulsen, Vulcan ovens, mixers, Hobart slicer (~74 lots)</t>
+          <t>Bank-ordered electrical contractor sale – Greenlee/Hilti/Milwaukee tools, GE/Siemens breakers</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>contractor liquidation</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>Greenwich</t>
+          <t>Clinton</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
@@ -19807,23 +20018,23 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>164</v>
+        <v>106</v>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>Live auction + webcast</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H26" s="15" t="n"/>
       <c r="I26" s="13" t="inlineStr"/>
       <c r="J26" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 06:00 PM ET</t>
+          <t>2026-10-29 05:00 PM ET</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>Best Buy Auctioneers / AuctionGuide</t>
+          <t>Hamilton Group / EstateSales.net</t>
         </is>
       </c>
       <c r="L26" s="13" t="inlineStr">
@@ -19839,7 +20050,7 @@
       </c>
       <c r="O26" s="14" t="inlineStr">
         <is>
-          <t>Oct 21; start time not captured (placeholder 6 PM).</t>
+          <t>Listed "Oct 29 2 PM PST" (= 5 PM ET).</t>
         </is>
       </c>
     </row>
@@ -19851,17 +20062,17 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>BJ's Wholesale closeout – racking, forklifts, Hobart</t>
+          <t>Major Intl Chain Surplus – 225 lots commercial refrigeration/kitchen (True, Traulsen, Hobart, Blodgett, Taylor)</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>commercial surplus</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>Rotterdam</t>
+          <t>Pleasant Valley</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
@@ -19870,7 +20081,7 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
@@ -19881,17 +20092,17 @@
       <c r="I27" s="13" t="inlineStr"/>
       <c r="J27" s="13" t="inlineStr">
         <is>
-          <t>2026-11-10 10:00 AM ET</t>
+          <t>2026-10-20 02:00 PM ET</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L27" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Adams / BidWrangler</t>
+        </is>
+      </c>
+      <c r="L27" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M27" s="13" t="inlineStr"/>
@@ -19902,191 +20113,183 @@
       </c>
       <c r="O27" s="14" t="inlineStr">
         <is>
+          <t>Tested and new units.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" outlineLevel="1">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>CT / Hudson Valley</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Café/bakery liquidation – Traulsen, Vulcan ovens, mixers, Hobart slicer (~74 lots)</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>Greenwich</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>164</v>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>Live auction + webcast</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="n"/>
+      <c r="I28" s="13" t="inlineStr"/>
+      <c r="J28" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>Best Buy Auctioneers / AuctionGuide</t>
+        </is>
+      </c>
+      <c r="L28" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M28" s="13" t="inlineStr"/>
+      <c r="N28" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O28" s="14" t="inlineStr">
+        <is>
+          <t>Oct 21; start time not captured (placeholder 6 PM).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" outlineLevel="1">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>CT / Hudson Valley</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>BJ's Wholesale closeout – racking, forklifts, Hobart</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>store closing</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>Rotterdam</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>168</v>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>Online auction</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="n"/>
+      <c r="I29" s="13" t="inlineStr"/>
+      <c r="J29" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-10 10:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L29" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M29" s="13" t="inlineStr"/>
+      <c r="N29" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O29" s="14" t="inlineStr">
+        <is>
           <t>Closes from Nov 10 10 AM.</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="17" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
         <is>
           <t>Subtotal — CT / Hudson Valley</t>
         </is>
       </c>
-      <c r="B28" s="17" t="inlineStr">
+      <c r="B30" s="17" t="inlineStr">
         <is>
           <t>4 item(s)</t>
         </is>
       </c>
-      <c r="C28" s="18" t="n"/>
-      <c r="D28" s="18" t="n"/>
-      <c r="E28" s="18" t="n"/>
-      <c r="F28" s="18" t="n"/>
-      <c r="G28" s="18" t="n"/>
-      <c r="H28" s="19" t="n">
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="18" t="n"/>
+      <c r="E30" s="18" t="n"/>
+      <c r="F30" s="18" t="n"/>
+      <c r="G30" s="18" t="n"/>
+      <c r="H30" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="18" t="n"/>
-      <c r="J28" s="18" t="n"/>
-      <c r="K28" s="18" t="n"/>
-      <c r="L28" s="18" t="n"/>
-      <c r="M28" s="18" t="n"/>
-      <c r="N28" s="18" t="n"/>
-      <c r="O28" s="18" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="I30" s="18" t="n"/>
+      <c r="J30" s="18" t="n"/>
+      <c r="K30" s="18" t="n"/>
+      <c r="L30" s="18" t="n"/>
+      <c r="M30" s="18" t="n"/>
+      <c r="N30" s="18" t="n"/>
+      <c r="O30" s="18" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>▸ NYC / Long Island / NJ  (16)</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="12" t="n"/>
-      <c r="E29" s="12" t="n"/>
-      <c r="F29" s="12" t="n"/>
-      <c r="G29" s="12" t="n"/>
-      <c r="H29" s="12" t="n"/>
-      <c r="I29" s="12" t="n"/>
-      <c r="J29" s="12" t="n"/>
-      <c r="K29" s="12" t="n"/>
-      <c r="L29" s="12" t="n"/>
-      <c r="M29" s="12" t="n"/>
-      <c r="N29" s="12" t="n"/>
-      <c r="O29" s="12" t="n"/>
-    </row>
-    <row r="30" outlineLevel="1">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>NYC / Long Island / NJ</t>
-        </is>
-      </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>Japanese BBQ &amp; bar – ~47 lots: Turbo Air, Hoshizaki ice machine, Pitco, Beverage-Air</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>restaurant closing</t>
-        </is>
-      </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="F30" s="13" t="n">
-        <v>191</v>
-      </c>
-      <c r="G30" s="13" t="inlineStr">
-        <is>
-          <t>Live + webcast, 18% BP + 3%</t>
-        </is>
-      </c>
-      <c r="H30" s="15" t="n"/>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="J30" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 04:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K30" s="13" t="inlineStr">
-        <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
-        </is>
-      </c>
-      <c r="L30" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M30" s="13" t="inlineStr"/>
-      <c r="N30" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O30" s="14" t="inlineStr">
-        <is>
-          <t>Wed Oct 21 4 PM. NYC 10013.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" outlineLevel="1">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>NYC / Long Island / NJ</t>
-        </is>
-      </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>Corporate caterer – Alto-Shaam, new boxed Avantco rice cookers &amp; Cadco oven, Perlick, MerryChef</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="inlineStr">
-        <is>
-          <t>auction</t>
-        </is>
-      </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>Jersey City</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>NJ</t>
-        </is>
-      </c>
-      <c r="F31" s="13" t="n">
-        <v>193</v>
-      </c>
-      <c r="G31" s="13" t="inlineStr">
-        <is>
-          <t>Live + webcast, 18% BP + 3%</t>
-        </is>
-      </c>
-      <c r="H31" s="15" t="n"/>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="J31" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-22 02:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K31" s="13" t="inlineStr">
-        <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
-        </is>
-      </c>
-      <c r="L31" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M31" s="13" t="inlineStr"/>
-      <c r="N31" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O31" s="14" t="inlineStr">
-        <is>
-          <t>Thu Oct 22 2 PM.</t>
-        </is>
-      </c>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="12" t="n"/>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="12" t="n"/>
+      <c r="N31" s="12" t="n"/>
+      <c r="O31" s="12" t="n"/>
     </row>
     <row r="32" outlineLevel="1">
       <c r="A32" s="13" t="inlineStr">
@@ -20096,42 +20299,46 @@
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>Tools / plumbing / MRO supply inventory – Hilti/DeWalt/Milwaukee, fittings, heat pumps</t>
+          <t>Japanese BBQ &amp; bar – ~47 lots: Turbo Air, Hoshizaki ice machine, Pitco, Beverage-Air</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>restaurant closing</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>Riverdale</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H32" s="15" t="n"/>
-      <c r="I32" s="13" t="inlineStr"/>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="J32" s="13" t="inlineStr">
         <is>
-          <t>2026-10-30 11:00 AM ET</t>
+          <t>2026-10-21 04:00 PM ET</t>
         </is>
       </c>
       <c r="K32" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
       <c r="L32" s="13" t="inlineStr">
@@ -20147,7 +20354,7 @@
       </c>
       <c r="O32" s="14" t="inlineStr">
         <is>
-          <t>Bulk resale inventory.</t>
+          <t>Wed Oct 21 4 PM. NYC 10013.</t>
         </is>
       </c>
     </row>
@@ -20159,17 +20366,17 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>Ice cream + cookie franchise equipment – Taylor soft-serve, Atosa, Blodgett</t>
+          <t>Corporate caterer – Alto-Shaam, new boxed Avantco rice cookers &amp; Cadco oven, Perlick, MerryChef</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>Riverdale</t>
+          <t>Jersey City</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
@@ -20178,23 +20385,27 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H33" s="15" t="n"/>
-      <c r="I33" s="13" t="inlineStr"/>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="J33" s="13" t="inlineStr">
         <is>
-          <t>2026-11-05 11:00 AM ET</t>
+          <t>2026-10-22 02:00 PM ET</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
       <c r="L33" s="13" t="inlineStr">
@@ -20210,7 +20421,7 @@
       </c>
       <c r="O33" s="14" t="inlineStr">
         <is>
-          <t>Resellable units.</t>
+          <t>Thu Oct 22 2 PM.</t>
         </is>
       </c>
     </row>
@@ -20222,51 +20433,47 @@
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>Like-new restaurant – steam tables, Coldline, Cleveland cook-and-hold, fryers, True freezers</t>
+          <t>Tools / plumbing / MRO supply inventory – Hilti/DeWalt/Milwaukee, fittings, heat pumps</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>Staten Island</t>
+          <t>Riverdale</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H34" s="15" t="n"/>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+      <c r="I34" s="13" t="inlineStr"/>
       <c r="J34" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00 PM ET</t>
+          <t>2026-10-30 11:00 AM ET</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
-        </is>
-      </c>
-      <c r="L34" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>A.J. Willner</t>
+        </is>
+      </c>
+      <c r="L34" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M34" s="13" t="inlineStr"/>
@@ -20277,7 +20484,7 @@
       </c>
       <c r="O34" s="14" t="inlineStr">
         <is>
-          <t>"Short notice" auction Mon Oct 19 1 PM.</t>
+          <t>Bulk resale inventory.</t>
         </is>
       </c>
     </row>
@@ -20289,17 +20496,17 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>Major food-service caterer – new-in-box True reach-ins, Beverage-Air, TurboChef, Resfab ventless fryer</t>
+          <t>Ice cream + cookie franchise equipment – Taylor soft-serve, Atosa, Blodgett</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>Parsippany</t>
+          <t>Riverdale</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
@@ -20308,27 +20515,23 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H35" s="15" t="n"/>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
+      <c r="I35" s="13" t="inlineStr"/>
       <c r="J35" s="13" t="inlineStr">
         <is>
-          <t>2026-11-03 02:00 PM ET</t>
+          <t>2026-11-05 11:00 AM ET</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L35" s="13" t="inlineStr">
@@ -20344,7 +20547,7 @@
       </c>
       <c r="O35" s="14" t="inlineStr">
         <is>
-          <t>Tue Nov 3 2 PM, checkout Nov 4.</t>
+          <t>Resellable units.</t>
         </is>
       </c>
     </row>
@@ -20356,47 +20559,51 @@
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>Serpico's Pizzeria (lost lease) – Bari ovens, walk-in, Hobart 60qt, Vulcan range</t>
+          <t>Like-new restaurant – steam tables, Coldline, Cleveland cook-and-hold, fryers, True freezers</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>Allenhurst</t>
+          <t>Staten Island</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
-          <t>No-reserve online auction</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H36" s="15" t="n"/>
-      <c r="I36" s="13" t="inlineStr"/>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="J36" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 11:00 AM ET</t>
+          <t>2026-10-19 01:00 PM ET</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>Peter Costanzo / EstateSales.net</t>
-        </is>
-      </c>
-      <c r="L36" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L36" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M36" s="13" t="inlineStr"/>
@@ -20407,7 +20614,7 @@
       </c>
       <c r="O36" s="14" t="inlineStr">
         <is>
-          <t>Absolute / no reserve.</t>
+          <t>"Short notice" auction Mon Oct 19 1 PM.</t>
         </is>
       </c>
     </row>
@@ -20419,17 +20626,17 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>Altitude Trampoline Park liquidation – partial: Atosa, TurboChef, stainless</t>
+          <t>Major food-service caterer – new-in-box True reach-ins, Beverage-Air, TurboChef, Resfab ventless fryer</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>facility contents</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>Iselin</t>
+          <t>Parsippany</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
@@ -20438,23 +20645,27 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H37" s="15" t="n"/>
-      <c r="I37" s="13" t="inlineStr"/>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
       <c r="J37" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 11:00 AM ET</t>
+          <t>2026-11-03 02:00 PM ET</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
       <c r="L37" s="13" t="inlineStr">
@@ -20470,7 +20681,7 @@
       </c>
       <c r="O37" s="14" t="inlineStr">
         <is>
-          <t>Some kitchen gear only.</t>
+          <t>Tue Nov 3 2 PM, checkout Nov 4.</t>
         </is>
       </c>
     </row>
@@ -20482,17 +20693,17 @@
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>Restaurant / pizzeria (contents not described)</t>
+          <t>Serpico's Pizzeria (lost lease) – Bari ovens, walk-in, Hobart 60qt, Vulcan range</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>Berkeley Heights</t>
+          <t>Allenhurst</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
@@ -20501,27 +20712,23 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>No-reserve online auction</t>
         </is>
       </c>
       <c r="H38" s="15" t="n"/>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
+      <c r="I38" s="13" t="inlineStr"/>
       <c r="J38" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 02:00 PM ET</t>
+          <t>2026-10-21 11:00 AM ET</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>Peter Costanzo / EstateSales.net</t>
         </is>
       </c>
       <c r="L38" s="20" t="inlineStr">
@@ -20537,7 +20744,7 @@
       </c>
       <c r="O38" s="14" t="inlineStr">
         <is>
-          <t>Tue Oct 20 2 PM. No item description on page.</t>
+          <t>Absolute / no reserve.</t>
         </is>
       </c>
     </row>
@@ -20549,17 +20756,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
+          <t>Altitude Trampoline Park liquidation – partial: Atosa, TurboChef, stainless</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>lien sale</t>
+          <t>facility contents</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>Edison</t>
+          <t>Iselin</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -20568,24 +20775,28 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
-          <t>Online auction, $2K load-out fee</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H39" s="15" t="n"/>
       <c r="I39" s="13" t="inlineStr"/>
-      <c r="J39" s="13" t="inlineStr"/>
+      <c r="J39" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
           <t>A.J. Willner</t>
         </is>
       </c>
-      <c r="L39" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="L39" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M39" s="13" t="inlineStr"/>
@@ -20596,7 +20807,7 @@
       </c>
       <c r="O39" s="14" t="inlineStr">
         <is>
-          <t>&gt;$100K new. Close date not captured.</t>
+          <t>Some kitchen gear only.</t>
         </is>
       </c>
     </row>
@@ -20608,17 +20819,17 @@
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
+          <t>Restaurant / pizzeria (contents not described)</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>restaurant closing</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>Edison</t>
+          <t>Berkeley Heights</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -20627,22 +20838,22 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
-          <t>Live + HiBid webcast, 18% BP + 3% card</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H40" s="15" t="n"/>
       <c r="I40" s="13" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J40" s="13" t="inlineStr">
         <is>
-          <t>2026-10-25 01:00 PM ET</t>
+          <t>2026-10-20 02:00 PM ET</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
@@ -20650,16 +20861,12 @@
           <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
-      <c r="L40" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M40" s="21" t="inlineStr">
-        <is>
-          <t>FLIP</t>
-        </is>
-      </c>
+      <c r="L40" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M40" s="13" t="inlineStr"/>
       <c r="N40" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -20667,7 +20874,7 @@
       </c>
       <c r="O40" s="14" t="inlineStr">
         <is>
-          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
+          <t>Tue Oct 20 2 PM. No item description on page.</t>
         </is>
       </c>
     </row>
@@ -20679,17 +20886,17 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
+          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>lien sale</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>East Brunswick</t>
+          <t>Edison</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -20698,20 +20905,16 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Online auction, $2K load-out fee</t>
         </is>
       </c>
       <c r="H41" s="15" t="n"/>
       <c r="I41" s="13" t="inlineStr"/>
-      <c r="J41" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-03 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="J41" s="13" t="inlineStr"/>
       <c r="K41" s="13" t="inlineStr">
         <is>
           <t>A.J. Willner</t>
@@ -20730,7 +20933,7 @@
       </c>
       <c r="O41" s="14" t="inlineStr">
         <is>
-          <t>Store inventory.</t>
+          <t>&gt;$100K new. Close date not captured.</t>
         </is>
       </c>
     </row>
@@ -20742,17 +20945,17 @@
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>High-end deli (contents not described)</t>
+          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>Manalapan Township</t>
+          <t>Edison</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -20761,22 +20964,22 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Live + HiBid webcast, 18% BP + 3% card</t>
         </is>
       </c>
       <c r="H42" s="15" t="n"/>
       <c r="I42" s="13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J42" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 04:00 PM ET</t>
+          <t>2026-10-25 01:00 PM ET</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
@@ -20784,12 +20987,16 @@
           <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
-      <c r="L42" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M42" s="13" t="inlineStr"/>
+      <c r="L42" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M42" s="21" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
       <c r="N42" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -20797,7 +21004,7 @@
       </c>
       <c r="O42" s="14" t="inlineStr">
         <is>
-          <t>Mon Oct 19 4 PM. No item description on page.</t>
+          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
         </is>
       </c>
     </row>
@@ -20809,17 +21016,17 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
+          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>showroom closing</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>Lawrenceville</t>
+          <t>East Brunswick</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -20828,23 +21035,23 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t>Online auction, 18% BP</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H43" s="15" t="n"/>
       <c r="I43" s="13" t="inlineStr"/>
       <c r="J43" s="13" t="inlineStr">
         <is>
-          <t>2026-10-27 09:00 AM ET</t>
+          <t>2026-11-03 11:00 AM ET</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L43" s="13" t="inlineStr">
@@ -20860,7 +21067,7 @@
       </c>
       <c r="O43" s="14" t="inlineStr">
         <is>
-          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
+          <t>Store inventory.</t>
         </is>
       </c>
     </row>
@@ -20872,17 +21079,17 @@
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>Milwaukee / Walmart / hardware store mega auction pt 3</t>
+          <t>High-end deli (contents not described)</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>restaurant closing</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>Mount Holly</t>
+          <t>Manalapan Township</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -20891,23 +21098,27 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>254</v>
+        <v>223</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>HiBid online auction</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H44" s="15" t="n"/>
-      <c r="I44" s="13" t="inlineStr"/>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="J44" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 06:00 PM ET</t>
+          <t>2026-10-19 04:00 PM ET</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>HiBid</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
       <c r="L44" s="20" t="inlineStr">
@@ -20923,7 +21134,7 @@
       </c>
       <c r="O44" s="14" t="inlineStr">
         <is>
-          <t>Close Oct 18 or 19 6 PM (later used).</t>
+          <t>Mon Oct 19 4 PM. No item description on page.</t>
         </is>
       </c>
     </row>
@@ -20935,7 +21146,7 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
+          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
@@ -20945,7 +21156,7 @@
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>Cherry Hill</t>
+          <t>Lawrenceville</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -20954,18 +21165,18 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>Online auction, openers ~$0.50</t>
+          <t>Online auction, 18% BP</t>
         </is>
       </c>
       <c r="H45" s="15" t="n"/>
       <c r="I45" s="13" t="inlineStr"/>
       <c r="J45" s="13" t="inlineStr">
         <is>
-          <t>2026-11-02 11:00 AM ET</t>
+          <t>2026-10-27 09:00 AM ET</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
@@ -20986,294 +21197,294 @@
       </c>
       <c r="O45" s="14" t="inlineStr">
         <is>
+          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" outlineLevel="1">
+      <c r="A46" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B46" s="14" t="inlineStr">
+        <is>
+          <t>Milwaukee / Walmart / hardware store mega auction pt 3</t>
+        </is>
+      </c>
+      <c r="C46" s="13" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="D46" s="13" t="inlineStr">
+        <is>
+          <t>Mount Holly</t>
+        </is>
+      </c>
+      <c r="E46" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F46" s="13" t="n">
+        <v>254</v>
+      </c>
+      <c r="G46" s="13" t="inlineStr">
+        <is>
+          <t>HiBid online auction</t>
+        </is>
+      </c>
+      <c r="H46" s="15" t="n"/>
+      <c r="I46" s="13" t="inlineStr"/>
+      <c r="J46" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K46" s="13" t="inlineStr">
+        <is>
+          <t>HiBid</t>
+        </is>
+      </c>
+      <c r="L46" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M46" s="13" t="inlineStr"/>
+      <c r="N46" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O46" s="14" t="inlineStr">
+        <is>
+          <t>Close Oct 18 or 19 6 PM (later used).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" outlineLevel="1">
+      <c r="A47" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B47" s="14" t="inlineStr">
+        <is>
+          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
+        </is>
+      </c>
+      <c r="C47" s="13" t="inlineStr">
+        <is>
+          <t>showroom closing</t>
+        </is>
+      </c>
+      <c r="D47" s="13" t="inlineStr">
+        <is>
+          <t>Cherry Hill</t>
+        </is>
+      </c>
+      <c r="E47" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F47" s="13" t="n">
+        <v>266</v>
+      </c>
+      <c r="G47" s="13" t="inlineStr">
+        <is>
+          <t>Online auction, openers ~$0.50</t>
+        </is>
+      </c>
+      <c r="H47" s="15" t="n"/>
+      <c r="I47" s="13" t="inlineStr"/>
+      <c r="J47" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-02 11:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K47" s="13" t="inlineStr">
+        <is>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L47" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M47" s="13" t="inlineStr"/>
+      <c r="N47" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O47" s="14" t="inlineStr">
+        <is>
           <t>Lots close from Nov 2 11 AM.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="17" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="17" t="inlineStr">
         <is>
           <t>Subtotal — NYC / Long Island / NJ</t>
         </is>
       </c>
-      <c r="B46" s="17" t="inlineStr">
+      <c r="B48" s="17" t="inlineStr">
         <is>
           <t>16 item(s)</t>
         </is>
       </c>
-      <c r="C46" s="18" t="n"/>
-      <c r="D46" s="18" t="n"/>
-      <c r="E46" s="18" t="n"/>
-      <c r="F46" s="18" t="n"/>
-      <c r="G46" s="18" t="n"/>
-      <c r="H46" s="19" t="n">
+      <c r="C48" s="18" t="n"/>
+      <c r="D48" s="18" t="n"/>
+      <c r="E48" s="18" t="n"/>
+      <c r="F48" s="18" t="n"/>
+      <c r="G48" s="18" t="n"/>
+      <c r="H48" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I46" s="18" t="n"/>
-      <c r="J46" s="18" t="n"/>
-      <c r="K46" s="18" t="n"/>
-      <c r="L46" s="18" t="n"/>
-      <c r="M46" s="18" t="n"/>
-      <c r="N46" s="18" t="n"/>
-      <c r="O46" s="18" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="11" t="inlineStr">
+      <c r="I48" s="18" t="n"/>
+      <c r="J48" s="18" t="n"/>
+      <c r="K48" s="18" t="n"/>
+      <c r="L48" s="18" t="n"/>
+      <c r="M48" s="18" t="n"/>
+      <c r="N48" s="18" t="n"/>
+      <c r="O48" s="18" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
         <is>
           <t>▸ Eastern PA / Mid-Atlantic  (1)</t>
         </is>
       </c>
-      <c r="B47" s="12" t="n"/>
-      <c r="C47" s="12" t="n"/>
-      <c r="D47" s="12" t="n"/>
-      <c r="E47" s="12" t="n"/>
-      <c r="F47" s="12" t="n"/>
-      <c r="G47" s="12" t="n"/>
-      <c r="H47" s="12" t="n"/>
-      <c r="I47" s="12" t="n"/>
-      <c r="J47" s="12" t="n"/>
-      <c r="K47" s="12" t="n"/>
-      <c r="L47" s="12" t="n"/>
-      <c r="M47" s="12" t="n"/>
-      <c r="N47" s="12" t="n"/>
-      <c r="O47" s="12" t="n"/>
-    </row>
-    <row r="48" outlineLevel="1">
-      <c r="A48" s="13" t="inlineStr">
+      <c r="B49" s="12" t="n"/>
+      <c r="C49" s="12" t="n"/>
+      <c r="D49" s="12" t="n"/>
+      <c r="E49" s="12" t="n"/>
+      <c r="F49" s="12" t="n"/>
+      <c r="G49" s="12" t="n"/>
+      <c r="H49" s="12" t="n"/>
+      <c r="I49" s="12" t="n"/>
+      <c r="J49" s="12" t="n"/>
+      <c r="K49" s="12" t="n"/>
+      <c r="L49" s="12" t="n"/>
+      <c r="M49" s="12" t="n"/>
+      <c r="N49" s="12" t="n"/>
+      <c r="O49" s="12" t="n"/>
+    </row>
+    <row r="50" outlineLevel="1">
+      <c r="A50" s="13" t="inlineStr">
         <is>
           <t>Eastern PA / Mid-Atlantic</t>
         </is>
       </c>
-      <c r="B48" s="14" t="inlineStr">
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>October restaurant consignment – Hobart, Rational, True + NEW scratch-and-dent Migali/Avantco</t>
         </is>
       </c>
-      <c r="C48" s="13" t="inlineStr">
+      <c r="C50" s="13" t="inlineStr">
         <is>
           <t>restaurant</t>
         </is>
       </c>
-      <c r="D48" s="13" t="inlineStr">
+      <c r="D50" s="13" t="inlineStr">
         <is>
           <t>Harrisburg</t>
         </is>
       </c>
-      <c r="E48" s="13" t="inlineStr">
+      <c r="E50" s="13" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="F48" s="13" t="n">
+      <c r="F50" s="13" t="n">
         <v>340</v>
       </c>
-      <c r="G48" s="13" t="inlineStr">
+      <c r="G50" s="13" t="inlineStr">
         <is>
           <t>Online auction, 15% BP, ships $55/pallet</t>
         </is>
       </c>
-      <c r="H48" s="15" t="n"/>
-      <c r="I48" s="13" t="inlineStr"/>
-      <c r="J48" s="13" t="inlineStr">
+      <c r="H50" s="15" t="n"/>
+      <c r="I50" s="13" t="inlineStr"/>
+      <c r="J50" s="13" t="inlineStr">
         <is>
           <t>2026-10-21 11:00 AM ET</t>
         </is>
       </c>
-      <c r="K48" s="13" t="inlineStr">
+      <c r="K50" s="13" t="inlineStr">
         <is>
           <t>Restaurant Auction Co</t>
         </is>
       </c>
-      <c r="L48" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M48" s="13" t="inlineStr"/>
-      <c r="N48" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O48" s="14" t="inlineStr">
+      <c r="L50" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M50" s="13" t="inlineStr"/>
+      <c r="N50" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O50" s="14" t="inlineStr">
         <is>
           <t>Closes Oct 21 10 or 11 AM (later used). Shippable.</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="17" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Eastern PA / Mid-Atlantic</t>
         </is>
       </c>
-      <c r="B49" s="17" t="inlineStr">
+      <c r="B51" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C49" s="18" t="n"/>
-      <c r="D49" s="18" t="n"/>
-      <c r="E49" s="18" t="n"/>
-      <c r="F49" s="18" t="n"/>
-      <c r="G49" s="18" t="n"/>
-      <c r="H49" s="19" t="n">
+      <c r="C51" s="18" t="n"/>
+      <c r="D51" s="18" t="n"/>
+      <c r="E51" s="18" t="n"/>
+      <c r="F51" s="18" t="n"/>
+      <c r="G51" s="18" t="n"/>
+      <c r="H51" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I49" s="18" t="n"/>
-      <c r="J49" s="18" t="n"/>
-      <c r="K49" s="18" t="n"/>
-      <c r="L49" s="18" t="n"/>
-      <c r="M49" s="18" t="n"/>
-      <c r="N49" s="18" t="n"/>
-      <c r="O49" s="18" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="11" t="inlineStr">
+      <c r="I51" s="18" t="n"/>
+      <c r="J51" s="18" t="n"/>
+      <c r="K51" s="18" t="n"/>
+      <c r="L51" s="18" t="n"/>
+      <c r="M51" s="18" t="n"/>
+      <c r="N51" s="18" t="n"/>
+      <c r="O51" s="18" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
         <is>
           <t>▸ Upstate / Western NY  (3)</t>
         </is>
       </c>
-      <c r="B50" s="12" t="n"/>
-      <c r="C50" s="12" t="n"/>
-      <c r="D50" s="12" t="n"/>
-      <c r="E50" s="12" t="n"/>
-      <c r="F50" s="12" t="n"/>
-      <c r="G50" s="12" t="n"/>
-      <c r="H50" s="12" t="n"/>
-      <c r="I50" s="12" t="n"/>
-      <c r="J50" s="12" t="n"/>
-      <c r="K50" s="12" t="n"/>
-      <c r="L50" s="12" t="n"/>
-      <c r="M50" s="12" t="n"/>
-      <c r="N50" s="12" t="n"/>
-      <c r="O50" s="12" t="n"/>
-    </row>
-    <row r="51" outlineLevel="1">
-      <c r="A51" s="13" t="inlineStr">
-        <is>
-          <t>Upstate / Western NY</t>
-        </is>
-      </c>
-      <c r="B51" s="14" t="inlineStr">
-        <is>
-          <t>Former Taco Del Mar – stainless, warmers, walk-in panels</t>
-        </is>
-      </c>
-      <c r="C51" s="13" t="inlineStr">
-        <is>
-          <t>restaurant</t>
-        </is>
-      </c>
-      <c r="D51" s="13" t="inlineStr">
-        <is>
-          <t>Watson</t>
-        </is>
-      </c>
-      <c r="E51" s="13" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="F51" s="13" t="n">
-        <v>260</v>
-      </c>
-      <c r="G51" s="13" t="inlineStr">
-        <is>
-          <t>HiBid online auction</t>
-        </is>
-      </c>
-      <c r="H51" s="15" t="n"/>
-      <c r="I51" s="13" t="inlineStr"/>
-      <c r="J51" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-20 06:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K51" s="13" t="inlineStr">
-        <is>
-          <t>Adirondack Asset / HiBid</t>
-        </is>
-      </c>
-      <c r="L51" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M51" s="13" t="inlineStr"/>
-      <c r="N51" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O51" s="14" t="inlineStr">
-        <is>
-          <t>Small lot.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" outlineLevel="1">
-      <c r="A52" s="13" t="inlineStr">
-        <is>
-          <t>Upstate / Western NY</t>
-        </is>
-      </c>
-      <c r="B52" s="14" t="inlineStr">
-        <is>
-          <t>Closed restaurant – coolers, fridges, prep tables</t>
-        </is>
-      </c>
-      <c r="C52" s="13" t="inlineStr">
-        <is>
-          <t>restaurant</t>
-        </is>
-      </c>
-      <c r="D52" s="13" t="inlineStr">
-        <is>
-          <t>Palmyra</t>
-        </is>
-      </c>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="F52" s="13" t="n">
-        <v>333</v>
-      </c>
-      <c r="G52" s="13" t="inlineStr">
-        <is>
-          <t>HiBid, 15% BP</t>
-        </is>
-      </c>
-      <c r="H52" s="15" t="n"/>
-      <c r="I52" s="13" t="inlineStr"/>
-      <c r="J52" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-19 07:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K52" s="13" t="inlineStr">
-        <is>
-          <t>Reynolds Auction Co / HiBid</t>
-        </is>
-      </c>
-      <c r="L52" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M52" s="13" t="inlineStr"/>
-      <c r="N52" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O52" s="14" t="inlineStr">
-        <is>
-          <t>No new out-of-state bidders. Small.</t>
-        </is>
-      </c>
+      <c r="B52" s="12" t="n"/>
+      <c r="C52" s="12" t="n"/>
+      <c r="D52" s="12" t="n"/>
+      <c r="E52" s="12" t="n"/>
+      <c r="F52" s="12" t="n"/>
+      <c r="G52" s="12" t="n"/>
+      <c r="H52" s="12" t="n"/>
+      <c r="I52" s="12" t="n"/>
+      <c r="J52" s="12" t="n"/>
+      <c r="K52" s="12" t="n"/>
+      <c r="L52" s="12" t="n"/>
+      <c r="M52" s="12" t="n"/>
+      <c r="N52" s="12" t="n"/>
+      <c r="O52" s="12" t="n"/>
     </row>
     <row r="53" outlineLevel="1">
       <c r="A53" s="13" t="inlineStr">
@@ -21283,7 +21494,7 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>Restaurant &amp; fitness equipment</t>
+          <t>Former Taco Del Mar – stainless, warmers, walk-in panels</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
@@ -21293,7 +21504,7 @@
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>Williamsville</t>
+          <t>Watson</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -21302,28 +21513,28 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>408</v>
+        <v>260</v>
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>HiBid online auction</t>
         </is>
       </c>
       <c r="H53" s="15" t="n"/>
       <c r="I53" s="13" t="inlineStr"/>
       <c r="J53" s="13" t="inlineStr">
         <is>
-          <t>2026-10-26 07:30 PM ET</t>
+          <t>2026-10-20 06:00 PM ET</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>Cash Auctions</t>
-        </is>
-      </c>
-      <c r="L53" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Adirondack Asset / HiBid</t>
+        </is>
+      </c>
+      <c r="L53" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M53" s="13" t="inlineStr"/>
@@ -21334,455 +21545,692 @@
       </c>
       <c r="O53" s="14" t="inlineStr">
         <is>
+          <t>Small lot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" outlineLevel="1">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>Upstate / Western NY</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>Closed restaurant – coolers, fridges, prep tables</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="inlineStr">
+        <is>
+          <t>Palmyra</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>333</v>
+      </c>
+      <c r="G54" s="13" t="inlineStr">
+        <is>
+          <t>HiBid, 15% BP</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="n"/>
+      <c r="I54" s="13" t="inlineStr"/>
+      <c r="J54" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 07:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="inlineStr">
+        <is>
+          <t>Reynolds Auction Co / HiBid</t>
+        </is>
+      </c>
+      <c r="L54" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M54" s="13" t="inlineStr"/>
+      <c r="N54" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O54" s="14" t="inlineStr">
+        <is>
+          <t>No new out-of-state bidders. Small.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" outlineLevel="1">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>Upstate / Western NY</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant &amp; fitness equipment</t>
+        </is>
+      </c>
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="D55" s="13" t="inlineStr">
+        <is>
+          <t>Williamsville</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F55" s="13" t="n">
+        <v>408</v>
+      </c>
+      <c r="G55" s="13" t="inlineStr">
+        <is>
+          <t>Online auction</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n"/>
+      <c r="I55" s="13" t="inlineStr"/>
+      <c r="J55" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-26 07:30 PM ET</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>Cash Auctions</t>
+        </is>
+      </c>
+      <c r="L55" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M55" s="13" t="inlineStr"/>
+      <c r="N55" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O55" s="14" t="inlineStr">
+        <is>
           <t>Lots not reviewed.</t>
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="17" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Upstate / Western NY</t>
         </is>
       </c>
-      <c r="B54" s="17" t="inlineStr">
+      <c r="B56" s="17" t="inlineStr">
         <is>
           <t>3 item(s)</t>
         </is>
       </c>
-      <c r="C54" s="18" t="n"/>
-      <c r="D54" s="18" t="n"/>
-      <c r="E54" s="18" t="n"/>
-      <c r="F54" s="18" t="n"/>
-      <c r="G54" s="18" t="n"/>
-      <c r="H54" s="19" t="n">
+      <c r="C56" s="18" t="n"/>
+      <c r="D56" s="18" t="n"/>
+      <c r="E56" s="18" t="n"/>
+      <c r="F56" s="18" t="n"/>
+      <c r="G56" s="18" t="n"/>
+      <c r="H56" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I54" s="18" t="n"/>
-      <c r="J54" s="18" t="n"/>
-      <c r="K54" s="18" t="n"/>
-      <c r="L54" s="18" t="n"/>
-      <c r="M54" s="18" t="n"/>
-      <c r="N54" s="18" t="n"/>
-      <c r="O54" s="18" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="11" t="inlineStr">
+      <c r="I56" s="18" t="n"/>
+      <c r="J56" s="18" t="n"/>
+      <c r="K56" s="18" t="n"/>
+      <c r="L56" s="18" t="n"/>
+      <c r="M56" s="18" t="n"/>
+      <c r="N56" s="18" t="n"/>
+      <c r="O56" s="18" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
         <is>
           <t>▸ Virginia  (1)</t>
         </is>
       </c>
-      <c r="B55" s="12" t="n"/>
-      <c r="C55" s="12" t="n"/>
-      <c r="D55" s="12" t="n"/>
-      <c r="E55" s="12" t="n"/>
-      <c r="F55" s="12" t="n"/>
-      <c r="G55" s="12" t="n"/>
-      <c r="H55" s="12" t="n"/>
-      <c r="I55" s="12" t="n"/>
-      <c r="J55" s="12" t="n"/>
-      <c r="K55" s="12" t="n"/>
-      <c r="L55" s="12" t="n"/>
-      <c r="M55" s="12" t="n"/>
-      <c r="N55" s="12" t="n"/>
-      <c r="O55" s="12" t="n"/>
-    </row>
-    <row r="56" outlineLevel="1">
-      <c r="A56" s="13" t="inlineStr">
+      <c r="B57" s="12" t="n"/>
+      <c r="C57" s="12" t="n"/>
+      <c r="D57" s="12" t="n"/>
+      <c r="E57" s="12" t="n"/>
+      <c r="F57" s="12" t="n"/>
+      <c r="G57" s="12" t="n"/>
+      <c r="H57" s="12" t="n"/>
+      <c r="I57" s="12" t="n"/>
+      <c r="J57" s="12" t="n"/>
+      <c r="K57" s="12" t="n"/>
+      <c r="L57" s="12" t="n"/>
+      <c r="M57" s="12" t="n"/>
+      <c r="N57" s="12" t="n"/>
+      <c r="O57" s="12" t="n"/>
+    </row>
+    <row r="58" outlineLevel="1">
+      <c r="A58" s="13" t="inlineStr">
         <is>
           <t>Virginia</t>
         </is>
       </c>
-      <c r="B56" s="14" t="inlineStr">
+      <c r="B58" s="14" t="inlineStr">
         <is>
           <t>Haynes Furniture / The Dump – 12 stores closing (furniture, mattresses)</t>
         </is>
       </c>
-      <c r="C56" s="13" t="inlineStr">
+      <c r="C58" s="13" t="inlineStr">
         <is>
           <t>retail GOB</t>
         </is>
       </c>
-      <c r="D56" s="13" t="inlineStr">
+      <c r="D58" s="13" t="inlineStr">
         <is>
           <t>Virginia Beach</t>
         </is>
       </c>
-      <c r="E56" s="13" t="inlineStr">
+      <c r="E58" s="13" t="inlineStr">
         <is>
           <t>VA</t>
         </is>
       </c>
-      <c r="F56" s="13" t="n">
+      <c r="F58" s="13" t="n">
         <v>456</v>
       </c>
-      <c r="G56" s="13" t="inlineStr">
+      <c r="G58" s="13" t="inlineStr">
         <is>
           <t>Retail GOB markdowns</t>
         </is>
       </c>
-      <c r="H56" s="15" t="n"/>
-      <c r="I56" s="13" t="inlineStr">
+      <c r="H58" s="15" t="n"/>
+      <c r="I58" s="13" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="J56" s="13" t="inlineStr"/>
-      <c r="K56" s="13" t="inlineStr">
+      <c r="J58" s="13" t="inlineStr"/>
+      <c r="K58" s="13" t="inlineStr">
         <is>
           <t>SB360 (PR Newswire)</t>
         </is>
       </c>
-      <c r="L56" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M56" s="13" t="inlineStr"/>
-      <c r="N56" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O56" s="14" t="inlineStr">
+      <c r="L58" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M58" s="13" t="inlineStr"/>
+      <c r="N58" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O58" s="14" t="inlineStr">
         <is>
           <t>Posted Oct 8. Multi-state (VA/AZ/GA/IL/TX); pinned at Virginia Beach. Home goods only.</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="17" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Virginia</t>
         </is>
       </c>
-      <c r="B57" s="17" t="inlineStr">
+      <c r="B59" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C57" s="18" t="n"/>
-      <c r="D57" s="18" t="n"/>
-      <c r="E57" s="18" t="n"/>
-      <c r="F57" s="18" t="n"/>
-      <c r="G57" s="18" t="n"/>
-      <c r="H57" s="19" t="n">
+      <c r="C59" s="18" t="n"/>
+      <c r="D59" s="18" t="n"/>
+      <c r="E59" s="18" t="n"/>
+      <c r="F59" s="18" t="n"/>
+      <c r="G59" s="18" t="n"/>
+      <c r="H59" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I57" s="18" t="n"/>
-      <c r="J57" s="18" t="n"/>
-      <c r="K57" s="18" t="n"/>
-      <c r="L57" s="18" t="n"/>
-      <c r="M57" s="18" t="n"/>
-      <c r="N57" s="18" t="n"/>
-      <c r="O57" s="18" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="11" t="inlineStr">
+      <c r="I59" s="18" t="n"/>
+      <c r="J59" s="18" t="n"/>
+      <c r="K59" s="18" t="n"/>
+      <c r="L59" s="18" t="n"/>
+      <c r="M59" s="18" t="n"/>
+      <c r="N59" s="18" t="n"/>
+      <c r="O59" s="18" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
         <is>
           <t>▸ Midwest  (2)</t>
         </is>
       </c>
-      <c r="B58" s="12" t="n"/>
-      <c r="C58" s="12" t="n"/>
-      <c r="D58" s="12" t="n"/>
-      <c r="E58" s="12" t="n"/>
-      <c r="F58" s="12" t="n"/>
-      <c r="G58" s="12" t="n"/>
-      <c r="H58" s="12" t="n"/>
-      <c r="I58" s="12" t="n"/>
-      <c r="J58" s="12" t="n"/>
-      <c r="K58" s="12" t="n"/>
-      <c r="L58" s="12" t="n"/>
-      <c r="M58" s="12" t="n"/>
-      <c r="N58" s="12" t="n"/>
-      <c r="O58" s="12" t="n"/>
-    </row>
-    <row r="59" outlineLevel="1">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="B60" s="12" t="n"/>
+      <c r="C60" s="12" t="n"/>
+      <c r="D60" s="12" t="n"/>
+      <c r="E60" s="12" t="n"/>
+      <c r="F60" s="12" t="n"/>
+      <c r="G60" s="12" t="n"/>
+      <c r="H60" s="12" t="n"/>
+      <c r="I60" s="12" t="n"/>
+      <c r="J60" s="12" t="n"/>
+      <c r="K60" s="12" t="n"/>
+      <c r="L60" s="12" t="n"/>
+      <c r="M60" s="12" t="n"/>
+      <c r="N60" s="12" t="n"/>
+      <c r="O60" s="12" t="n"/>
+    </row>
+    <row r="61" outlineLevel="1">
+      <c r="A61" s="13" t="inlineStr">
         <is>
           <t>Midwest</t>
         </is>
       </c>
-      <c r="B59" s="14" t="inlineStr">
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>Freshway Market whole-grocery liquidation – refrigeration racks, cases, walk-ins, generator</t>
         </is>
       </c>
-      <c r="C59" s="13" t="inlineStr">
+      <c r="C61" s="13" t="inlineStr">
         <is>
           <t>store closing</t>
         </is>
       </c>
-      <c r="D59" s="13" t="inlineStr">
+      <c r="D61" s="13" t="inlineStr">
         <is>
           <t>Chicago</t>
         </is>
       </c>
-      <c r="E59" s="13" t="inlineStr">
+      <c r="E61" s="13" t="inlineStr">
         <is>
           <t>IL</t>
         </is>
       </c>
-      <c r="F59" s="13" t="n">
+      <c r="F61" s="13" t="n">
         <v>862</v>
       </c>
-      <c r="G59" s="13" t="inlineStr">
+      <c r="G61" s="13" t="inlineStr">
         <is>
           <t>Online auction</t>
         </is>
       </c>
-      <c r="H59" s="15" t="n"/>
-      <c r="I59" s="13" t="inlineStr"/>
-      <c r="J59" s="13" t="inlineStr">
+      <c r="H61" s="15" t="n"/>
+      <c r="I61" s="13" t="inlineStr"/>
+      <c r="J61" s="13" t="inlineStr">
         <is>
           <t>2026-10-20 11:00 AM ET</t>
         </is>
       </c>
-      <c r="K59" s="13" t="inlineStr">
+      <c r="K61" s="13" t="inlineStr">
         <is>
           <t>Grafe Auction</t>
         </is>
       </c>
-      <c r="L59" s="20" t="inlineStr">
+      <c r="L61" s="20" t="inlineStr">
         <is>
           <t>ENDING SOON</t>
         </is>
       </c>
-      <c r="M59" s="13" t="inlineStr"/>
-      <c r="N59" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O59" s="14" t="inlineStr">
+      <c r="M61" s="13" t="inlineStr"/>
+      <c r="N61" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O61" s="14" t="inlineStr">
         <is>
           <t>Closes from Oct 20 10 AM CDT.</t>
         </is>
       </c>
     </row>
-    <row r="60" outlineLevel="1">
-      <c r="A60" s="13" t="inlineStr">
+    <row r="62" outlineLevel="1">
+      <c r="A62" s="13" t="inlineStr">
         <is>
           <t>Midwest</t>
         </is>
       </c>
-      <c r="B60" s="14" t="inlineStr">
+      <c r="B62" s="14" t="inlineStr">
         <is>
           <t>American Sale – total liquidation, all 7 stores (pools, hot tubs, grills, holiday decor)</t>
         </is>
       </c>
-      <c r="C60" s="13" t="inlineStr">
+      <c r="C62" s="13" t="inlineStr">
         <is>
           <t>retail GOB</t>
         </is>
       </c>
-      <c r="D60" s="13" t="inlineStr">
+      <c r="D62" s="13" t="inlineStr">
         <is>
           <t>Chicagoland</t>
         </is>
       </c>
-      <c r="E60" s="13" t="inlineStr">
+      <c r="E62" s="13" t="inlineStr">
         <is>
           <t>IL</t>
         </is>
       </c>
-      <c r="F60" s="13" t="n">
+      <c r="F62" s="13" t="n">
         <v>876</v>
       </c>
-      <c r="G60" s="13" t="inlineStr">
+      <c r="G62" s="13" t="inlineStr">
         <is>
           <t>Retail GOB, up to 70% off</t>
         </is>
       </c>
-      <c r="H60" s="15" t="n"/>
-      <c r="I60" s="13" t="inlineStr">
+      <c r="H62" s="15" t="n"/>
+      <c r="I62" s="13" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="J60" s="13" t="inlineStr"/>
-      <c r="K60" s="13" t="inlineStr">
+      <c r="J62" s="13" t="inlineStr"/>
+      <c r="K62" s="13" t="inlineStr">
         <is>
           <t>Tiger Group (PR Newswire)</t>
         </is>
       </c>
-      <c r="L60" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M60" s="13" t="inlineStr"/>
-      <c r="N60" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O60" s="14" t="inlineStr">
+      <c r="L62" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M62" s="13" t="inlineStr"/>
+      <c r="N62" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O62" s="14" t="inlineStr">
         <is>
           <t>Posted Oct 15. Watch for a bulk/fixture auction.</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="17" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Midwest</t>
         </is>
       </c>
-      <c r="B61" s="17" t="inlineStr">
+      <c r="B63" s="17" t="inlineStr">
         <is>
           <t>2 item(s)</t>
         </is>
       </c>
-      <c r="C61" s="18" t="n"/>
-      <c r="D61" s="18" t="n"/>
-      <c r="E61" s="18" t="n"/>
-      <c r="F61" s="18" t="n"/>
-      <c r="G61" s="18" t="n"/>
-      <c r="H61" s="19" t="n">
+      <c r="C63" s="18" t="n"/>
+      <c r="D63" s="18" t="n"/>
+      <c r="E63" s="18" t="n"/>
+      <c r="F63" s="18" t="n"/>
+      <c r="G63" s="18" t="n"/>
+      <c r="H63" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I61" s="18" t="n"/>
-      <c r="J61" s="18" t="n"/>
-      <c r="K61" s="18" t="n"/>
-      <c r="L61" s="18" t="n"/>
-      <c r="M61" s="18" t="n"/>
-      <c r="N61" s="18" t="n"/>
-      <c r="O61" s="18" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="11" t="inlineStr">
+      <c r="I63" s="18" t="n"/>
+      <c r="J63" s="18" t="n"/>
+      <c r="K63" s="18" t="n"/>
+      <c r="L63" s="18" t="n"/>
+      <c r="M63" s="18" t="n"/>
+      <c r="N63" s="18" t="n"/>
+      <c r="O63" s="18" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t>▸ Texas / South Central  (1)</t>
         </is>
       </c>
-      <c r="B62" s="12" t="n"/>
-      <c r="C62" s="12" t="n"/>
-      <c r="D62" s="12" t="n"/>
-      <c r="E62" s="12" t="n"/>
-      <c r="F62" s="12" t="n"/>
-      <c r="G62" s="12" t="n"/>
-      <c r="H62" s="12" t="n"/>
-      <c r="I62" s="12" t="n"/>
-      <c r="J62" s="12" t="n"/>
-      <c r="K62" s="12" t="n"/>
-      <c r="L62" s="12" t="n"/>
-      <c r="M62" s="12" t="n"/>
-      <c r="N62" s="12" t="n"/>
-      <c r="O62" s="12" t="n"/>
-    </row>
-    <row r="63" outlineLevel="1">
-      <c r="A63" s="13" t="inlineStr">
+      <c r="B64" s="12" t="n"/>
+      <c r="C64" s="12" t="n"/>
+      <c r="D64" s="12" t="n"/>
+      <c r="E64" s="12" t="n"/>
+      <c r="F64" s="12" t="n"/>
+      <c r="G64" s="12" t="n"/>
+      <c r="H64" s="12" t="n"/>
+      <c r="I64" s="12" t="n"/>
+      <c r="J64" s="12" t="n"/>
+      <c r="K64" s="12" t="n"/>
+      <c r="L64" s="12" t="n"/>
+      <c r="M64" s="12" t="n"/>
+      <c r="N64" s="12" t="n"/>
+      <c r="O64" s="12" t="n"/>
+    </row>
+    <row r="65" outlineLevel="1">
+      <c r="A65" s="13" t="inlineStr">
         <is>
           <t>Texas / South Central</t>
         </is>
       </c>
-      <c r="B63" s="14" t="inlineStr">
+      <c r="B65" s="14" t="inlineStr">
         <is>
           <t>Southwest beverage distributor surplus – mostly unused: 16 True merchandisers, 75 Bunn brewers, 100+ micro-market kiosks</t>
         </is>
       </c>
-      <c r="C63" s="13" t="inlineStr">
+      <c r="C65" s="13" t="inlineStr">
         <is>
           <t>distributor surplus</t>
         </is>
       </c>
-      <c r="D63" s="13" t="inlineStr">
+      <c r="D65" s="13" t="inlineStr">
         <is>
           <t>Mesquite</t>
         </is>
       </c>
-      <c r="E63" s="13" t="inlineStr">
+      <c r="E65" s="13" t="inlineStr">
         <is>
           <t>TX</t>
         </is>
       </c>
-      <c r="F63" s="13" t="n">
+      <c r="F65" s="13" t="n">
         <v>1547</v>
       </c>
-      <c r="G63" s="13" t="inlineStr">
+      <c r="G65" s="13" t="inlineStr">
         <is>
           <t>Online auction</t>
         </is>
       </c>
-      <c r="H63" s="15" t="n"/>
-      <c r="I63" s="13" t="inlineStr"/>
-      <c r="J63" s="13" t="inlineStr">
+      <c r="H65" s="15" t="n"/>
+      <c r="I65" s="13" t="inlineStr"/>
+      <c r="J65" s="13" t="inlineStr">
         <is>
           <t>2026-11-13 11:00 AM ET</t>
         </is>
       </c>
-      <c r="K63" s="13" t="inlineStr">
+      <c r="K65" s="13" t="inlineStr">
         <is>
           <t>Heritage Global Partners</t>
         </is>
       </c>
-      <c r="L63" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M63" s="13" t="inlineStr"/>
-      <c r="N63" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O63" s="14" t="inlineStr">
+      <c r="L65" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M65" s="13" t="inlineStr"/>
+      <c r="N65" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O65" s="14" t="inlineStr">
         <is>
           <t>Near-new appliances, resell by unit. Nov 13 10 AM CST.</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="17" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Texas / South Central</t>
         </is>
       </c>
-      <c r="B64" s="17" t="inlineStr">
+      <c r="B66" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C64" s="18" t="n"/>
-      <c r="D64" s="18" t="n"/>
-      <c r="E64" s="18" t="n"/>
-      <c r="F64" s="18" t="n"/>
-      <c r="G64" s="18" t="n"/>
-      <c r="H64" s="19" t="n">
+      <c r="C66" s="18" t="n"/>
+      <c r="D66" s="18" t="n"/>
+      <c r="E66" s="18" t="n"/>
+      <c r="F66" s="18" t="n"/>
+      <c r="G66" s="18" t="n"/>
+      <c r="H66" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I64" s="18" t="n"/>
-      <c r="J64" s="18" t="n"/>
-      <c r="K64" s="18" t="n"/>
-      <c r="L64" s="18" t="n"/>
-      <c r="M64" s="18" t="n"/>
-      <c r="N64" s="18" t="n"/>
-      <c r="O64" s="18" t="n"/>
+      <c r="I66" s="18" t="n"/>
+      <c r="J66" s="18" t="n"/>
+      <c r="K66" s="18" t="n"/>
+      <c r="L66" s="18" t="n"/>
+      <c r="M66" s="18" t="n"/>
+      <c r="N66" s="18" t="n"/>
+      <c r="O66" s="18" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>▸ West / Other  (1)</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="n"/>
+      <c r="C67" s="12" t="n"/>
+      <c r="D67" s="12" t="n"/>
+      <c r="E67" s="12" t="n"/>
+      <c r="F67" s="12" t="n"/>
+      <c r="G67" s="12" t="n"/>
+      <c r="H67" s="12" t="n"/>
+      <c r="I67" s="12" t="n"/>
+      <c r="J67" s="12" t="n"/>
+      <c r="K67" s="12" t="n"/>
+      <c r="L67" s="12" t="n"/>
+      <c r="M67" s="12" t="n"/>
+      <c r="N67" s="12" t="n"/>
+      <c r="O67" s="12" t="n"/>
+    </row>
+    <row r="68" outlineLevel="1">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>West / Other</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>National salad concept liquidation – full contents of 63 fast-casual restaurants (AZ/TX/OK/NV)</t>
+        </is>
+      </c>
+      <c r="C68" s="13" t="inlineStr">
+        <is>
+          <t>restaurant chain liquidation</t>
+        </is>
+      </c>
+      <c r="D68" s="13" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="F68" s="13" t="n">
+        <v>2307</v>
+      </c>
+      <c r="G68" s="13" t="inlineStr">
+        <is>
+          <t>Online auctions, dates TBD</t>
+        </is>
+      </c>
+      <c r="H68" s="15" t="n"/>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="J68" s="13" t="inlineStr"/>
+      <c r="K68" s="13" t="inlineStr">
+        <is>
+          <t>RestaurantEquipment.bid (TAGeX)</t>
+        </is>
+      </c>
+      <c r="L68" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M68" s="13" t="inlineStr"/>
+      <c r="N68" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O68" s="14" t="inlineStr">
+        <is>
+          <t>Rolling market-by-market auctions, none live yet (Phoenix metro 30 locations, DFW 14, Tucson 6, Houston 5, plus OK/NV). Pickup on site at each restaurant. Pinned at Phoenix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — West / Other</t>
+        </is>
+      </c>
+      <c r="B69" s="17" t="inlineStr">
+        <is>
+          <t>1 item(s)</t>
+        </is>
+      </c>
+      <c r="C69" s="18" t="n"/>
+      <c r="D69" s="18" t="n"/>
+      <c r="E69" s="18" t="n"/>
+      <c r="F69" s="18" t="n"/>
+      <c r="G69" s="18" t="n"/>
+      <c r="H69" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="18" t="n"/>
+      <c r="J69" s="18" t="n"/>
+      <c r="K69" s="18" t="n"/>
+      <c r="L69" s="18" t="n"/>
+      <c r="M69" s="18" t="n"/>
+      <c r="N69" s="18" t="n"/>
+      <c r="O69" s="18" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O64"/>
+  <autoFilter ref="A1:O69"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId22"/>
@@ -21797,14 +22245,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N51" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N52" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N60" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N61" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N62" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N65" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N68" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lot_recon.xlsx
+++ b/lot_recon.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wolf New'!$A$1:$O$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wolf Used'!$A$1:$O$188</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Wolf Unclear'!$A$1:$O$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Removed'!$A$1:$O$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -577,7 +577,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Last updated: 2026-10-18 13:59 ET</t>
+          <t>Last updated: 2026-10-18 14:02 ET</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Active listings: 286 · Removed: 2</t>
+          <t>Active listings: 284 · Removed: 2</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
         <v>159696</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F8" t="n">
         <v>34</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0</v>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>975650.08</v>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -1004,7 +1004,7 @@
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H23" s="6" t="n">
         <v>62163</v>
@@ -2727,9 +2727,9 @@
           <t>HiBid (Auctionfuel)</t>
         </is>
       </c>
-      <c r="L30" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="L30" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M30" s="13" t="inlineStr"/>
@@ -18610,7 +18610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:O69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -19851,7 +19851,7 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>▸ CT / Hudson Valley  (6)</t>
+          <t>▸ CT / Hudson Valley  (4)</t>
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
@@ -19940,47 +19940,47 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>Flower shop liquidation – whole inventory: vases, containers, baskets, ribbon/wrap, floral foam, seasonal decor, gift items</t>
+          <t>Major Intl Chain Surplus – 225 lots commercial refrigeration/kitchen (True, Traulsen, Hobart, Blodgett, Taylor)</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>commercial surplus</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>Prospect</t>
+          <t>Pleasant Valley</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
-          <t>$10,000 (whole lot); will split or bundle</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H27" s="15" t="n"/>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="J27" s="13" t="inlineStr"/>
+      <c r="I27" s="13" t="inlineStr"/>
+      <c r="J27" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-20 02:00 PM ET</t>
+        </is>
+      </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L27" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Adams / BidWrangler</t>
+        </is>
+      </c>
+      <c r="L27" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M27" s="13" t="inlineStr"/>
@@ -19991,7 +19991,7 @@
       </c>
       <c r="O27" s="14" t="inlineStr">
         <is>
-          <t>Pickup only. Off-category (floral/gift), FYI only.</t>
+          <t>Tested and new units.</t>
         </is>
       </c>
     </row>
@@ -20003,17 +20003,17 @@
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>Upholstery shop closing – tools, supplies, Singer 95-1 industrial sewing machine, everything for sale</t>
+          <t>Café/bakery liquidation – Traulsen, Vulcan ovens, mixers, Hobart slicer (~74 lots)</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>West Haven</t>
+          <t>Greenwich</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -20022,23 +20022,23 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>125</v>
+        <v>164</v>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>Varies by item ($1 placeholder)</t>
+          <t>Live auction + webcast</t>
         </is>
       </c>
       <c r="H28" s="15" t="n"/>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-13</t>
-        </is>
-      </c>
-      <c r="J28" s="13" t="inlineStr"/>
+      <c r="I28" s="13" t="inlineStr"/>
+      <c r="J28" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:00 PM ET</t>
+        </is>
+      </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>Best Buy Auctioneers / AuctionGuide</t>
         </is>
       </c>
       <c r="L28" s="13" t="inlineStr">
@@ -20054,7 +20054,7 @@
       </c>
       <c r="O28" s="14" t="inlineStr">
         <is>
-          <t>Posted 9/13, updated 10/16. Off-category, FYI only.</t>
+          <t>Oct 21; start time not captured (placeholder 6 PM).</t>
         </is>
       </c>
     </row>
@@ -20066,17 +20066,17 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>Major Intl Chain Surplus – 225 lots commercial refrigeration/kitchen (True, Traulsen, Hobart, Blodgett, Taylor)</t>
+          <t>BJ's Wholesale closeout – racking, forklifts, Hobart</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>commercial surplus</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>Pleasant Valley</t>
+          <t>Rotterdam</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
@@ -20085,7 +20085,7 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
@@ -20096,17 +20096,17 @@
       <c r="I29" s="13" t="inlineStr"/>
       <c r="J29" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 02:00 PM ET</t>
+          <t>2026-11-10 10:00 AM ET</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>Adams / BidWrangler</t>
-        </is>
-      </c>
-      <c r="L29" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L29" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M29" s="13" t="inlineStr"/>
@@ -20117,183 +20117,191 @@
       </c>
       <c r="O29" s="14" t="inlineStr">
         <is>
-          <t>Tested and new units.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" outlineLevel="1">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>CT / Hudson Valley</t>
-        </is>
-      </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>Café/bakery liquidation – Traulsen, Vulcan ovens, mixers, Hobart slicer (~74 lots)</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>restaurant</t>
-        </is>
-      </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>Greenwich</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="F30" s="13" t="n">
-        <v>164</v>
-      </c>
-      <c r="G30" s="13" t="inlineStr">
-        <is>
-          <t>Live auction + webcast</t>
-        </is>
-      </c>
-      <c r="H30" s="15" t="n"/>
-      <c r="I30" s="13" t="inlineStr"/>
-      <c r="J30" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 06:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K30" s="13" t="inlineStr">
-        <is>
-          <t>Best Buy Auctioneers / AuctionGuide</t>
-        </is>
-      </c>
-      <c r="L30" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M30" s="13" t="inlineStr"/>
-      <c r="N30" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O30" s="14" t="inlineStr">
-        <is>
-          <t>Oct 21; start time not captured (placeholder 6 PM).</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" outlineLevel="1">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>CT / Hudson Valley</t>
-        </is>
-      </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>BJ's Wholesale closeout – racking, forklifts, Hobart</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="inlineStr">
-        <is>
-          <t>store closing</t>
-        </is>
-      </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>Rotterdam</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
+          <t>Closes from Nov 10 10 AM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — CT / Hudson Valley</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>4 item(s)</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="18" t="n"/>
+      <c r="E30" s="18" t="n"/>
+      <c r="F30" s="18" t="n"/>
+      <c r="G30" s="18" t="n"/>
+      <c r="H30" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="18" t="n"/>
+      <c r="J30" s="18" t="n"/>
+      <c r="K30" s="18" t="n"/>
+      <c r="L30" s="18" t="n"/>
+      <c r="M30" s="18" t="n"/>
+      <c r="N30" s="18" t="n"/>
+      <c r="O30" s="18" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="inlineStr">
+        <is>
+          <t>▸ NYC / Long Island / NJ  (16)</t>
+        </is>
+      </c>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="12" t="n"/>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="12" t="n"/>
+      <c r="N31" s="12" t="n"/>
+      <c r="O31" s="12" t="n"/>
+    </row>
+    <row r="32" outlineLevel="1">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>Japanese BBQ &amp; bar – ~47 lots: Turbo Air, Hoshizaki ice machine, Pitco, Beverage-Air</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>restaurant closing</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
         <is>
           <t>NY</t>
         </is>
       </c>
-      <c r="F31" s="13" t="n">
-        <v>168</v>
-      </c>
-      <c r="G31" s="13" t="inlineStr">
-        <is>
-          <t>Online auction</t>
-        </is>
-      </c>
-      <c r="H31" s="15" t="n"/>
-      <c r="I31" s="13" t="inlineStr"/>
-      <c r="J31" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-10 10:00 AM ET</t>
-        </is>
-      </c>
-      <c r="K31" s="13" t="inlineStr">
-        <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L31" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M31" s="13" t="inlineStr"/>
-      <c r="N31" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O31" s="14" t="inlineStr">
-        <is>
-          <t>Closes from Nov 10 10 AM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — CT / Hudson Valley</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>6 item(s)</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="n"/>
-      <c r="D32" s="18" t="n"/>
-      <c r="E32" s="18" t="n"/>
-      <c r="F32" s="18" t="n"/>
-      <c r="G32" s="18" t="n"/>
-      <c r="H32" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="18" t="n"/>
-      <c r="J32" s="18" t="n"/>
-      <c r="K32" s="18" t="n"/>
-      <c r="L32" s="18" t="n"/>
-      <c r="M32" s="18" t="n"/>
-      <c r="N32" s="18" t="n"/>
-      <c r="O32" s="18" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
-        <is>
-          <t>▸ NYC / Long Island / NJ  (16)</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="n"/>
-      <c r="C33" s="12" t="n"/>
-      <c r="D33" s="12" t="n"/>
-      <c r="E33" s="12" t="n"/>
-      <c r="F33" s="12" t="n"/>
-      <c r="G33" s="12" t="n"/>
-      <c r="H33" s="12" t="n"/>
-      <c r="I33" s="12" t="n"/>
-      <c r="J33" s="12" t="n"/>
-      <c r="K33" s="12" t="n"/>
-      <c r="L33" s="12" t="n"/>
-      <c r="M33" s="12" t="n"/>
-      <c r="N33" s="12" t="n"/>
-      <c r="O33" s="12" t="n"/>
+      <c r="F32" s="13" t="n">
+        <v>191</v>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>Live + webcast, 18% BP + 3%</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="n"/>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J32" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-21 04:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L32" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M32" s="13" t="inlineStr"/>
+      <c r="N32" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O32" s="14" t="inlineStr">
+        <is>
+          <t>Wed Oct 21 4 PM. NYC 10013.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" outlineLevel="1">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Corporate caterer – Alto-Shaam, new boxed Avantco rice cookers &amp; Cadco oven, Perlick, MerryChef</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>auction</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>Jersey City</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>193</v>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>Live + webcast, 18% BP + 3%</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="n"/>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="J33" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-22 02:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L33" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M33" s="13" t="inlineStr"/>
+      <c r="N33" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O33" s="14" t="inlineStr">
+        <is>
+          <t>Thu Oct 22 2 PM.</t>
+        </is>
+      </c>
     </row>
     <row r="34" outlineLevel="1">
       <c r="A34" s="13" t="inlineStr">
@@ -20303,46 +20311,42 @@
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>Japanese BBQ &amp; bar – ~47 lots: Turbo Air, Hoshizaki ice machine, Pitco, Beverage-Air</t>
+          <t>Tools / plumbing / MRO supply inventory – Hilti/DeWalt/Milwaukee, fittings, heat pumps</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Riverdale</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H34" s="15" t="n"/>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
+      <c r="I34" s="13" t="inlineStr"/>
       <c r="J34" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 04:00 PM ET</t>
+          <t>2026-10-30 11:00 AM ET</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L34" s="13" t="inlineStr">
@@ -20358,7 +20362,7 @@
       </c>
       <c r="O34" s="14" t="inlineStr">
         <is>
-          <t>Wed Oct 21 4 PM. NYC 10013.</t>
+          <t>Bulk resale inventory.</t>
         </is>
       </c>
     </row>
@@ -20370,17 +20374,17 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>Corporate caterer – Alto-Shaam, new boxed Avantco rice cookers &amp; Cadco oven, Perlick, MerryChef</t>
+          <t>Ice cream + cookie franchise equipment – Taylor soft-serve, Atosa, Blodgett</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>Jersey City</t>
+          <t>Riverdale</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
@@ -20389,27 +20393,23 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H35" s="15" t="n"/>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
+      <c r="I35" s="13" t="inlineStr"/>
       <c r="J35" s="13" t="inlineStr">
         <is>
-          <t>2026-10-22 02:00 PM ET</t>
+          <t>2026-11-05 11:00 AM ET</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L35" s="13" t="inlineStr">
@@ -20425,7 +20425,7 @@
       </c>
       <c r="O35" s="14" t="inlineStr">
         <is>
-          <t>Thu Oct 22 2 PM.</t>
+          <t>Resellable units.</t>
         </is>
       </c>
     </row>
@@ -20437,47 +20437,51 @@
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>Tools / plumbing / MRO supply inventory – Hilti/DeWalt/Milwaukee, fittings, heat pumps</t>
+          <t>Like-new restaurant – steam tables, Coldline, Cleveland cook-and-hold, fryers, True freezers</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>Riverdale</t>
+          <t>Staten Island</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H36" s="15" t="n"/>
-      <c r="I36" s="13" t="inlineStr"/>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="J36" s="13" t="inlineStr">
         <is>
-          <t>2026-10-30 11:00 AM ET</t>
+          <t>2026-10-19 01:00 PM ET</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
-        </is>
-      </c>
-      <c r="L36" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L36" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M36" s="13" t="inlineStr"/>
@@ -20488,7 +20492,7 @@
       </c>
       <c r="O36" s="14" t="inlineStr">
         <is>
-          <t>Bulk resale inventory.</t>
+          <t>"Short notice" auction Mon Oct 19 1 PM.</t>
         </is>
       </c>
     </row>
@@ -20500,17 +20504,17 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>Ice cream + cookie franchise equipment – Taylor soft-serve, Atosa, Blodgett</t>
+          <t>Major food-service caterer – new-in-box True reach-ins, Beverage-Air, TurboChef, Resfab ventless fryer</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>Riverdale</t>
+          <t>Parsippany</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
@@ -20519,23 +20523,27 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H37" s="15" t="n"/>
-      <c r="I37" s="13" t="inlineStr"/>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
       <c r="J37" s="13" t="inlineStr">
         <is>
-          <t>2026-11-05 11:00 AM ET</t>
+          <t>2026-11-03 02:00 PM ET</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
       <c r="L37" s="13" t="inlineStr">
@@ -20551,7 +20559,7 @@
       </c>
       <c r="O37" s="14" t="inlineStr">
         <is>
-          <t>Resellable units.</t>
+          <t>Tue Nov 3 2 PM, checkout Nov 4.</t>
         </is>
       </c>
     </row>
@@ -20563,46 +20571,42 @@
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>Like-new restaurant – steam tables, Coldline, Cleveland cook-and-hold, fryers, True freezers</t>
+          <t>Serpico's Pizzeria (lost lease) – Bari ovens, walk-in, Hobart 60qt, Vulcan range</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>Staten Island</t>
+          <t>Allenhurst</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>No-reserve online auction</t>
         </is>
       </c>
       <c r="H38" s="15" t="n"/>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+      <c r="I38" s="13" t="inlineStr"/>
       <c r="J38" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00 PM ET</t>
+          <t>2026-10-21 11:00 AM ET</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>Peter Costanzo / EstateSales.net</t>
         </is>
       </c>
       <c r="L38" s="20" t="inlineStr">
@@ -20618,7 +20622,7 @@
       </c>
       <c r="O38" s="14" t="inlineStr">
         <is>
-          <t>"Short notice" auction Mon Oct 19 1 PM.</t>
+          <t>Absolute / no reserve.</t>
         </is>
       </c>
     </row>
@@ -20630,17 +20634,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>Major food-service caterer – new-in-box True reach-ins, Beverage-Air, TurboChef, Resfab ventless fryer</t>
+          <t>Altitude Trampoline Park liquidation – partial: Atosa, TurboChef, stainless</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>facility contents</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>Parsippany</t>
+          <t>Iselin</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -20649,32 +20653,28 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H39" s="15" t="n"/>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
+      <c r="I39" s="13" t="inlineStr"/>
       <c r="J39" s="13" t="inlineStr">
         <is>
-          <t>2026-11-03 02:00 PM ET</t>
+          <t>2026-10-21 11:00 AM ET</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
-        </is>
-      </c>
-      <c r="L39" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>A.J. Willner</t>
+        </is>
+      </c>
+      <c r="L39" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M39" s="13" t="inlineStr"/>
@@ -20685,7 +20685,7 @@
       </c>
       <c r="O39" s="14" t="inlineStr">
         <is>
-          <t>Tue Nov 3 2 PM, checkout Nov 4.</t>
+          <t>Some kitchen gear only.</t>
         </is>
       </c>
     </row>
@@ -20697,17 +20697,17 @@
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>Serpico's Pizzeria (lost lease) – Bari ovens, walk-in, Hobart 60qt, Vulcan range</t>
+          <t>Restaurant / pizzeria (contents not described)</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>restaurant closing</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>Allenhurst</t>
+          <t>Berkeley Heights</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -20716,23 +20716,27 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
-          <t>No-reserve online auction</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H40" s="15" t="n"/>
-      <c r="I40" s="13" t="inlineStr"/>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="J40" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 11:00 AM ET</t>
+          <t>2026-10-20 02:00 PM ET</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>Peter Costanzo / EstateSales.net</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
       <c r="L40" s="20" t="inlineStr">
@@ -20748,7 +20752,7 @@
       </c>
       <c r="O40" s="14" t="inlineStr">
         <is>
-          <t>Absolute / no reserve.</t>
+          <t>Tue Oct 20 2 PM. No item description on page.</t>
         </is>
       </c>
     </row>
@@ -20760,17 +20764,17 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>Altitude Trampoline Park liquidation – partial: Atosa, TurboChef, stainless</t>
+          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>facility contents</t>
+          <t>lien sale</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>Iselin</t>
+          <t>Edison</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -20779,28 +20783,24 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Online auction, $2K load-out fee</t>
         </is>
       </c>
       <c r="H41" s="15" t="n"/>
       <c r="I41" s="13" t="inlineStr"/>
-      <c r="J41" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="J41" s="13" t="inlineStr"/>
       <c r="K41" s="13" t="inlineStr">
         <is>
           <t>A.J. Willner</t>
         </is>
       </c>
-      <c r="L41" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+      <c r="L41" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M41" s="13" t="inlineStr"/>
@@ -20811,7 +20811,7 @@
       </c>
       <c r="O41" s="14" t="inlineStr">
         <is>
-          <t>Some kitchen gear only.</t>
+          <t>&gt;$100K new. Close date not captured.</t>
         </is>
       </c>
     </row>
@@ -20823,17 +20823,17 @@
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>Restaurant / pizzeria (contents not described)</t>
+          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>Berkeley Heights</t>
+          <t>Edison</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -20842,22 +20842,22 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Live + HiBid webcast, 18% BP + 3% card</t>
         </is>
       </c>
       <c r="H42" s="15" t="n"/>
       <c r="I42" s="13" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J42" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 02:00 PM ET</t>
+          <t>2026-10-25 01:00 PM ET</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
@@ -20865,12 +20865,16 @@
           <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
-      <c r="L42" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M42" s="13" t="inlineStr"/>
+      <c r="L42" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M42" s="21" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
       <c r="N42" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -20878,7 +20882,7 @@
       </c>
       <c r="O42" s="14" t="inlineStr">
         <is>
-          <t>Tue Oct 20 2 PM. No item description on page.</t>
+          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
         </is>
       </c>
     </row>
@@ -20890,17 +20894,17 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
+          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>lien sale</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>Edison</t>
+          <t>East Brunswick</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -20909,16 +20913,20 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t>Online auction, $2K load-out fee</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H43" s="15" t="n"/>
       <c r="I43" s="13" t="inlineStr"/>
-      <c r="J43" s="13" t="inlineStr"/>
+      <c r="J43" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-03 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
           <t>A.J. Willner</t>
@@ -20937,7 +20945,7 @@
       </c>
       <c r="O43" s="14" t="inlineStr">
         <is>
-          <t>&gt;$100K new. Close date not captured.</t>
+          <t>Store inventory.</t>
         </is>
       </c>
     </row>
@@ -20949,17 +20957,17 @@
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
+          <t>High-end deli (contents not described)</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>restaurant closing</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>Edison</t>
+          <t>Manalapan Township</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -20968,22 +20976,22 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>Live + HiBid webcast, 18% BP + 3% card</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H44" s="15" t="n"/>
       <c r="I44" s="13" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="J44" s="13" t="inlineStr">
         <is>
-          <t>2026-10-25 01:00 PM ET</t>
+          <t>2026-10-19 04:00 PM ET</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
@@ -20991,16 +20999,12 @@
           <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
-      <c r="L44" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M44" s="21" t="inlineStr">
-        <is>
-          <t>FLIP</t>
-        </is>
-      </c>
+      <c r="L44" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M44" s="13" t="inlineStr"/>
       <c r="N44" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -21008,7 +21012,7 @@
       </c>
       <c r="O44" s="14" t="inlineStr">
         <is>
-          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
+          <t>Mon Oct 19 4 PM. No item description on page.</t>
         </is>
       </c>
     </row>
@@ -21020,17 +21024,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
+          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>showroom closing</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>East Brunswick</t>
+          <t>Lawrenceville</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -21039,23 +21043,23 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>220</v>
+        <v>239</v>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Online auction, 18% BP</t>
         </is>
       </c>
       <c r="H45" s="15" t="n"/>
       <c r="I45" s="13" t="inlineStr"/>
       <c r="J45" s="13" t="inlineStr">
         <is>
-          <t>2026-11-03 11:00 AM ET</t>
+          <t>2026-10-27 09:00 AM ET</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>Grafe Auction</t>
         </is>
       </c>
       <c r="L45" s="13" t="inlineStr">
@@ -21071,7 +21075,7 @@
       </c>
       <c r="O45" s="14" t="inlineStr">
         <is>
-          <t>Store inventory.</t>
+          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
         </is>
       </c>
     </row>
@@ -21083,17 +21087,17 @@
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>High-end deli (contents not described)</t>
+          <t>Milwaukee / Walmart / hardware store mega auction pt 3</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>Manalapan Township</t>
+          <t>Mount Holly</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -21102,27 +21106,23 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>223</v>
+        <v>254</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>HiBid online auction</t>
         </is>
       </c>
       <c r="H46" s="15" t="n"/>
-      <c r="I46" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+      <c r="I46" s="13" t="inlineStr"/>
       <c r="J46" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 04:00 PM ET</t>
+          <t>2026-10-19 06:00 PM ET</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>HiBid</t>
         </is>
       </c>
       <c r="L46" s="20" t="inlineStr">
@@ -21138,7 +21138,7 @@
       </c>
       <c r="O46" s="14" t="inlineStr">
         <is>
-          <t>Mon Oct 19 4 PM. No item description on page.</t>
+          <t>Close Oct 18 or 19 6 PM (later used).</t>
         </is>
       </c>
     </row>
@@ -21150,7 +21150,7 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
+          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
@@ -21160,7 +21160,7 @@
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>Lawrenceville</t>
+          <t>Cherry Hill</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -21169,18 +21169,18 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>239</v>
+        <v>266</v>
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
-          <t>Online auction, 18% BP</t>
+          <t>Online auction, openers ~$0.50</t>
         </is>
       </c>
       <c r="H47" s="15" t="n"/>
       <c r="I47" s="13" t="inlineStr"/>
       <c r="J47" s="13" t="inlineStr">
         <is>
-          <t>2026-10-27 09:00 AM ET</t>
+          <t>2026-11-02 11:00 AM ET</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -21201,294 +21201,294 @@
       </c>
       <c r="O47" s="14" t="inlineStr">
         <is>
-          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" outlineLevel="1">
-      <c r="A48" s="13" t="inlineStr">
-        <is>
-          <t>NYC / Long Island / NJ</t>
-        </is>
-      </c>
-      <c r="B48" s="14" t="inlineStr">
-        <is>
-          <t>Milwaukee / Walmart / hardware store mega auction pt 3</t>
-        </is>
-      </c>
-      <c r="C48" s="13" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="D48" s="13" t="inlineStr">
-        <is>
-          <t>Mount Holly</t>
-        </is>
-      </c>
-      <c r="E48" s="13" t="inlineStr">
-        <is>
-          <t>NJ</t>
-        </is>
-      </c>
-      <c r="F48" s="13" t="n">
-        <v>254</v>
-      </c>
-      <c r="G48" s="13" t="inlineStr">
+          <t>Lots close from Nov 2 11 AM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B48" s="17" t="inlineStr">
+        <is>
+          <t>16 item(s)</t>
+        </is>
+      </c>
+      <c r="C48" s="18" t="n"/>
+      <c r="D48" s="18" t="n"/>
+      <c r="E48" s="18" t="n"/>
+      <c r="F48" s="18" t="n"/>
+      <c r="G48" s="18" t="n"/>
+      <c r="H48" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="18" t="n"/>
+      <c r="J48" s="18" t="n"/>
+      <c r="K48" s="18" t="n"/>
+      <c r="L48" s="18" t="n"/>
+      <c r="M48" s="18" t="n"/>
+      <c r="N48" s="18" t="n"/>
+      <c r="O48" s="18" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>▸ Eastern PA / Mid-Atlantic  (1)</t>
+        </is>
+      </c>
+      <c r="B49" s="12" t="n"/>
+      <c r="C49" s="12" t="n"/>
+      <c r="D49" s="12" t="n"/>
+      <c r="E49" s="12" t="n"/>
+      <c r="F49" s="12" t="n"/>
+      <c r="G49" s="12" t="n"/>
+      <c r="H49" s="12" t="n"/>
+      <c r="I49" s="12" t="n"/>
+      <c r="J49" s="12" t="n"/>
+      <c r="K49" s="12" t="n"/>
+      <c r="L49" s="12" t="n"/>
+      <c r="M49" s="12" t="n"/>
+      <c r="N49" s="12" t="n"/>
+      <c r="O49" s="12" t="n"/>
+    </row>
+    <row r="50" outlineLevel="1">
+      <c r="A50" s="13" t="inlineStr">
+        <is>
+          <t>Eastern PA / Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
+        <is>
+          <t>October restaurant consignment – Hobart, Rational, True + NEW scratch-and-dent Migali/Avantco</t>
+        </is>
+      </c>
+      <c r="C50" s="13" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="D50" s="13" t="inlineStr">
+        <is>
+          <t>Harrisburg</t>
+        </is>
+      </c>
+      <c r="E50" s="13" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="F50" s="13" t="n">
+        <v>340</v>
+      </c>
+      <c r="G50" s="13" t="inlineStr">
+        <is>
+          <t>Online auction, 15% BP, ships $55/pallet</t>
+        </is>
+      </c>
+      <c r="H50" s="15" t="n"/>
+      <c r="I50" s="13" t="inlineStr"/>
+      <c r="J50" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K50" s="13" t="inlineStr">
+        <is>
+          <t>Restaurant Auction Co</t>
+        </is>
+      </c>
+      <c r="L50" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M50" s="13" t="inlineStr"/>
+      <c r="N50" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O50" s="14" t="inlineStr">
+        <is>
+          <t>Closes Oct 21 10 or 11 AM (later used). Shippable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Eastern PA / Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="B51" s="17" t="inlineStr">
+        <is>
+          <t>1 item(s)</t>
+        </is>
+      </c>
+      <c r="C51" s="18" t="n"/>
+      <c r="D51" s="18" t="n"/>
+      <c r="E51" s="18" t="n"/>
+      <c r="F51" s="18" t="n"/>
+      <c r="G51" s="18" t="n"/>
+      <c r="H51" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="18" t="n"/>
+      <c r="J51" s="18" t="n"/>
+      <c r="K51" s="18" t="n"/>
+      <c r="L51" s="18" t="n"/>
+      <c r="M51" s="18" t="n"/>
+      <c r="N51" s="18" t="n"/>
+      <c r="O51" s="18" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="11" t="inlineStr">
+        <is>
+          <t>▸ Upstate / Western NY  (3)</t>
+        </is>
+      </c>
+      <c r="B52" s="12" t="n"/>
+      <c r="C52" s="12" t="n"/>
+      <c r="D52" s="12" t="n"/>
+      <c r="E52" s="12" t="n"/>
+      <c r="F52" s="12" t="n"/>
+      <c r="G52" s="12" t="n"/>
+      <c r="H52" s="12" t="n"/>
+      <c r="I52" s="12" t="n"/>
+      <c r="J52" s="12" t="n"/>
+      <c r="K52" s="12" t="n"/>
+      <c r="L52" s="12" t="n"/>
+      <c r="M52" s="12" t="n"/>
+      <c r="N52" s="12" t="n"/>
+      <c r="O52" s="12" t="n"/>
+    </row>
+    <row r="53" outlineLevel="1">
+      <c r="A53" s="13" t="inlineStr">
+        <is>
+          <t>Upstate / Western NY</t>
+        </is>
+      </c>
+      <c r="B53" s="14" t="inlineStr">
+        <is>
+          <t>Former Taco Del Mar – stainless, warmers, walk-in panels</t>
+        </is>
+      </c>
+      <c r="C53" s="13" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="D53" s="13" t="inlineStr">
+        <is>
+          <t>Watson</t>
+        </is>
+      </c>
+      <c r="E53" s="13" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F53" s="13" t="n">
+        <v>260</v>
+      </c>
+      <c r="G53" s="13" t="inlineStr">
         <is>
           <t>HiBid online auction</t>
         </is>
       </c>
-      <c r="H48" s="15" t="n"/>
-      <c r="I48" s="13" t="inlineStr"/>
-      <c r="J48" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-19 06:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K48" s="13" t="inlineStr">
-        <is>
-          <t>HiBid</t>
-        </is>
-      </c>
-      <c r="L48" s="20" t="inlineStr">
+      <c r="H53" s="15" t="n"/>
+      <c r="I53" s="13" t="inlineStr"/>
+      <c r="J53" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K53" s="13" t="inlineStr">
+        <is>
+          <t>Adirondack Asset / HiBid</t>
+        </is>
+      </c>
+      <c r="L53" s="20" t="inlineStr">
         <is>
           <t>ENDING SOON</t>
         </is>
       </c>
-      <c r="M48" s="13" t="inlineStr"/>
-      <c r="N48" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O48" s="14" t="inlineStr">
-        <is>
-          <t>Close Oct 18 or 19 6 PM (later used).</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" outlineLevel="1">
-      <c r="A49" s="13" t="inlineStr">
-        <is>
-          <t>NYC / Long Island / NJ</t>
-        </is>
-      </c>
-      <c r="B49" s="14" t="inlineStr">
-        <is>
-          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
-        </is>
-      </c>
-      <c r="C49" s="13" t="inlineStr">
-        <is>
-          <t>showroom closing</t>
-        </is>
-      </c>
-      <c r="D49" s="13" t="inlineStr">
-        <is>
-          <t>Cherry Hill</t>
-        </is>
-      </c>
-      <c r="E49" s="13" t="inlineStr">
-        <is>
-          <t>NJ</t>
-        </is>
-      </c>
-      <c r="F49" s="13" t="n">
-        <v>266</v>
-      </c>
-      <c r="G49" s="13" t="inlineStr">
-        <is>
-          <t>Online auction, openers ~$0.50</t>
-        </is>
-      </c>
-      <c r="H49" s="15" t="n"/>
-      <c r="I49" s="13" t="inlineStr"/>
-      <c r="J49" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-02 11:00 AM ET</t>
-        </is>
-      </c>
-      <c r="K49" s="13" t="inlineStr">
-        <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L49" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M49" s="13" t="inlineStr"/>
-      <c r="N49" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O49" s="14" t="inlineStr">
-        <is>
-          <t>Lots close from Nov 2 11 AM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — NYC / Long Island / NJ</t>
-        </is>
-      </c>
-      <c r="B50" s="17" t="inlineStr">
-        <is>
-          <t>16 item(s)</t>
-        </is>
-      </c>
-      <c r="C50" s="18" t="n"/>
-      <c r="D50" s="18" t="n"/>
-      <c r="E50" s="18" t="n"/>
-      <c r="F50" s="18" t="n"/>
-      <c r="G50" s="18" t="n"/>
-      <c r="H50" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="18" t="n"/>
-      <c r="J50" s="18" t="n"/>
-      <c r="K50" s="18" t="n"/>
-      <c r="L50" s="18" t="n"/>
-      <c r="M50" s="18" t="n"/>
-      <c r="N50" s="18" t="n"/>
-      <c r="O50" s="18" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>▸ Eastern PA / Mid-Atlantic  (1)</t>
-        </is>
-      </c>
-      <c r="B51" s="12" t="n"/>
-      <c r="C51" s="12" t="n"/>
-      <c r="D51" s="12" t="n"/>
-      <c r="E51" s="12" t="n"/>
-      <c r="F51" s="12" t="n"/>
-      <c r="G51" s="12" t="n"/>
-      <c r="H51" s="12" t="n"/>
-      <c r="I51" s="12" t="n"/>
-      <c r="J51" s="12" t="n"/>
-      <c r="K51" s="12" t="n"/>
-      <c r="L51" s="12" t="n"/>
-      <c r="M51" s="12" t="n"/>
-      <c r="N51" s="12" t="n"/>
-      <c r="O51" s="12" t="n"/>
-    </row>
-    <row r="52" outlineLevel="1">
-      <c r="A52" s="13" t="inlineStr">
-        <is>
-          <t>Eastern PA / Mid-Atlantic</t>
-        </is>
-      </c>
-      <c r="B52" s="14" t="inlineStr">
-        <is>
-          <t>October restaurant consignment – Hobart, Rational, True + NEW scratch-and-dent Migali/Avantco</t>
-        </is>
-      </c>
-      <c r="C52" s="13" t="inlineStr">
+      <c r="M53" s="13" t="inlineStr"/>
+      <c r="N53" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O53" s="14" t="inlineStr">
+        <is>
+          <t>Small lot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" outlineLevel="1">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>Upstate / Western NY</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>Closed restaurant – coolers, fridges, prep tables</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
         <is>
           <t>restaurant</t>
         </is>
       </c>
-      <c r="D52" s="13" t="inlineStr">
-        <is>
-          <t>Harrisburg</t>
-        </is>
-      </c>
-      <c r="E52" s="13" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="F52" s="13" t="n">
-        <v>340</v>
-      </c>
-      <c r="G52" s="13" t="inlineStr">
-        <is>
-          <t>Online auction, 15% BP, ships $55/pallet</t>
-        </is>
-      </c>
-      <c r="H52" s="15" t="n"/>
-      <c r="I52" s="13" t="inlineStr"/>
-      <c r="J52" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 11:00 AM ET</t>
-        </is>
-      </c>
-      <c r="K52" s="13" t="inlineStr">
-        <is>
-          <t>Restaurant Auction Co</t>
-        </is>
-      </c>
-      <c r="L52" s="20" t="inlineStr">
+      <c r="D54" s="13" t="inlineStr">
+        <is>
+          <t>Palmyra</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>333</v>
+      </c>
+      <c r="G54" s="13" t="inlineStr">
+        <is>
+          <t>HiBid, 15% BP</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="n"/>
+      <c r="I54" s="13" t="inlineStr"/>
+      <c r="J54" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 07:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="inlineStr">
+        <is>
+          <t>Reynolds Auction Co / HiBid</t>
+        </is>
+      </c>
+      <c r="L54" s="20" t="inlineStr">
         <is>
           <t>ENDING SOON</t>
         </is>
       </c>
-      <c r="M52" s="13" t="inlineStr"/>
-      <c r="N52" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O52" s="14" t="inlineStr">
-        <is>
-          <t>Closes Oct 21 10 or 11 AM (later used). Shippable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Eastern PA / Mid-Atlantic</t>
-        </is>
-      </c>
-      <c r="B53" s="17" t="inlineStr">
-        <is>
-          <t>1 item(s)</t>
-        </is>
-      </c>
-      <c r="C53" s="18" t="n"/>
-      <c r="D53" s="18" t="n"/>
-      <c r="E53" s="18" t="n"/>
-      <c r="F53" s="18" t="n"/>
-      <c r="G53" s="18" t="n"/>
-      <c r="H53" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="18" t="n"/>
-      <c r="J53" s="18" t="n"/>
-      <c r="K53" s="18" t="n"/>
-      <c r="L53" s="18" t="n"/>
-      <c r="M53" s="18" t="n"/>
-      <c r="N53" s="18" t="n"/>
-      <c r="O53" s="18" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t>▸ Upstate / Western NY  (3)</t>
-        </is>
-      </c>
-      <c r="B54" s="12" t="n"/>
-      <c r="C54" s="12" t="n"/>
-      <c r="D54" s="12" t="n"/>
-      <c r="E54" s="12" t="n"/>
-      <c r="F54" s="12" t="n"/>
-      <c r="G54" s="12" t="n"/>
-      <c r="H54" s="12" t="n"/>
-      <c r="I54" s="12" t="n"/>
-      <c r="J54" s="12" t="n"/>
-      <c r="K54" s="12" t="n"/>
-      <c r="L54" s="12" t="n"/>
-      <c r="M54" s="12" t="n"/>
-      <c r="N54" s="12" t="n"/>
-      <c r="O54" s="12" t="n"/>
+      <c r="M54" s="13" t="inlineStr"/>
+      <c r="N54" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O54" s="14" t="inlineStr">
+        <is>
+          <t>No new out-of-state bidders. Small.</t>
+        </is>
+      </c>
     </row>
     <row r="55" outlineLevel="1">
       <c r="A55" s="13" t="inlineStr">
@@ -21498,7 +21498,7 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Former Taco Del Mar – stainless, warmers, walk-in panels</t>
+          <t>Restaurant &amp; fitness equipment</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
@@ -21508,7 +21508,7 @@
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>Watson</t>
+          <t>Williamsville</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -21517,28 +21517,28 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>260</v>
+        <v>408</v>
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
-          <t>HiBid online auction</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H55" s="15" t="n"/>
       <c r="I55" s="13" t="inlineStr"/>
       <c r="J55" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 06:00 PM ET</t>
+          <t>2026-10-26 07:30 PM ET</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>Adirondack Asset / HiBid</t>
-        </is>
-      </c>
-      <c r="L55" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Cash Auctions</t>
+        </is>
+      </c>
+      <c r="L55" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M55" s="13" t="inlineStr"/>
@@ -21549,672 +21549,546 @@
       </c>
       <c r="O55" s="14" t="inlineStr">
         <is>
-          <t>Small lot.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" outlineLevel="1">
-      <c r="A56" s="13" t="inlineStr">
-        <is>
-          <t>Upstate / Western NY</t>
-        </is>
-      </c>
-      <c r="B56" s="14" t="inlineStr">
-        <is>
-          <t>Closed restaurant – coolers, fridges, prep tables</t>
-        </is>
-      </c>
-      <c r="C56" s="13" t="inlineStr">
-        <is>
-          <t>restaurant</t>
-        </is>
-      </c>
-      <c r="D56" s="13" t="inlineStr">
-        <is>
-          <t>Palmyra</t>
-        </is>
-      </c>
-      <c r="E56" s="13" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="F56" s="13" t="n">
-        <v>333</v>
-      </c>
-      <c r="G56" s="13" t="inlineStr">
-        <is>
-          <t>HiBid, 15% BP</t>
-        </is>
-      </c>
-      <c r="H56" s="15" t="n"/>
-      <c r="I56" s="13" t="inlineStr"/>
-      <c r="J56" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-19 07:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K56" s="13" t="inlineStr">
-        <is>
-          <t>Reynolds Auction Co / HiBid</t>
-        </is>
-      </c>
-      <c r="L56" s="20" t="inlineStr">
+          <t>Lots not reviewed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Upstate / Western NY</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>3 item(s)</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="n"/>
+      <c r="D56" s="18" t="n"/>
+      <c r="E56" s="18" t="n"/>
+      <c r="F56" s="18" t="n"/>
+      <c r="G56" s="18" t="n"/>
+      <c r="H56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="18" t="n"/>
+      <c r="J56" s="18" t="n"/>
+      <c r="K56" s="18" t="n"/>
+      <c r="L56" s="18" t="n"/>
+      <c r="M56" s="18" t="n"/>
+      <c r="N56" s="18" t="n"/>
+      <c r="O56" s="18" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>▸ Virginia  (1)</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="n"/>
+      <c r="C57" s="12" t="n"/>
+      <c r="D57" s="12" t="n"/>
+      <c r="E57" s="12" t="n"/>
+      <c r="F57" s="12" t="n"/>
+      <c r="G57" s="12" t="n"/>
+      <c r="H57" s="12" t="n"/>
+      <c r="I57" s="12" t="n"/>
+      <c r="J57" s="12" t="n"/>
+      <c r="K57" s="12" t="n"/>
+      <c r="L57" s="12" t="n"/>
+      <c r="M57" s="12" t="n"/>
+      <c r="N57" s="12" t="n"/>
+      <c r="O57" s="12" t="n"/>
+    </row>
+    <row r="58" outlineLevel="1">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>Haynes Furniture / The Dump – 12 stores closing (furniture, mattresses)</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>retail GOB</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>Virginia Beach</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="F58" s="13" t="n">
+        <v>456</v>
+      </c>
+      <c r="G58" s="13" t="inlineStr">
+        <is>
+          <t>Retail GOB markdowns</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="n"/>
+      <c r="I58" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="J58" s="13" t="inlineStr"/>
+      <c r="K58" s="13" t="inlineStr">
+        <is>
+          <t>SB360 (PR Newswire)</t>
+        </is>
+      </c>
+      <c r="L58" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M58" s="13" t="inlineStr"/>
+      <c r="N58" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O58" s="14" t="inlineStr">
+        <is>
+          <t>Posted Oct 8. Multi-state (VA/AZ/GA/IL/TX); pinned at Virginia Beach. Home goods only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Virginia</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>1 item(s)</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="n"/>
+      <c r="D59" s="18" t="n"/>
+      <c r="E59" s="18" t="n"/>
+      <c r="F59" s="18" t="n"/>
+      <c r="G59" s="18" t="n"/>
+      <c r="H59" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="18" t="n"/>
+      <c r="J59" s="18" t="n"/>
+      <c r="K59" s="18" t="n"/>
+      <c r="L59" s="18" t="n"/>
+      <c r="M59" s="18" t="n"/>
+      <c r="N59" s="18" t="n"/>
+      <c r="O59" s="18" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>▸ Midwest  (2)</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="n"/>
+      <c r="C60" s="12" t="n"/>
+      <c r="D60" s="12" t="n"/>
+      <c r="E60" s="12" t="n"/>
+      <c r="F60" s="12" t="n"/>
+      <c r="G60" s="12" t="n"/>
+      <c r="H60" s="12" t="n"/>
+      <c r="I60" s="12" t="n"/>
+      <c r="J60" s="12" t="n"/>
+      <c r="K60" s="12" t="n"/>
+      <c r="L60" s="12" t="n"/>
+      <c r="M60" s="12" t="n"/>
+      <c r="N60" s="12" t="n"/>
+      <c r="O60" s="12" t="n"/>
+    </row>
+    <row r="61" outlineLevel="1">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>Freshway Market whole-grocery liquidation – refrigeration racks, cases, walk-ins, generator</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>store closing</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="F61" s="13" t="n">
+        <v>862</v>
+      </c>
+      <c r="G61" s="13" t="inlineStr">
+        <is>
+          <t>Online auction</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="n"/>
+      <c r="I61" s="13" t="inlineStr"/>
+      <c r="J61" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
+        <is>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L61" s="20" t="inlineStr">
         <is>
           <t>ENDING SOON</t>
         </is>
       </c>
-      <c r="M56" s="13" t="inlineStr"/>
-      <c r="N56" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O56" s="14" t="inlineStr">
-        <is>
-          <t>No new out-of-state bidders. Small.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" outlineLevel="1">
-      <c r="A57" s="13" t="inlineStr">
-        <is>
-          <t>Upstate / Western NY</t>
-        </is>
-      </c>
-      <c r="B57" s="14" t="inlineStr">
-        <is>
-          <t>Restaurant &amp; fitness equipment</t>
-        </is>
-      </c>
-      <c r="C57" s="13" t="inlineStr">
-        <is>
-          <t>restaurant</t>
-        </is>
-      </c>
-      <c r="D57" s="13" t="inlineStr">
-        <is>
-          <t>Williamsville</t>
-        </is>
-      </c>
-      <c r="E57" s="13" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="F57" s="13" t="n">
-        <v>408</v>
-      </c>
-      <c r="G57" s="13" t="inlineStr">
+      <c r="M61" s="13" t="inlineStr"/>
+      <c r="N61" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O61" s="14" t="inlineStr">
+        <is>
+          <t>Closes from Oct 20 10 AM CDT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" outlineLevel="1">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>American Sale – total liquidation, all 7 stores (pools, hot tubs, grills, holiday decor)</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t>retail GOB</t>
+        </is>
+      </c>
+      <c r="D62" s="13" t="inlineStr">
+        <is>
+          <t>Chicagoland</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="F62" s="13" t="n">
+        <v>876</v>
+      </c>
+      <c r="G62" s="13" t="inlineStr">
+        <is>
+          <t>Retail GOB, up to 70% off</t>
+        </is>
+      </c>
+      <c r="H62" s="15" t="n"/>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J62" s="13" t="inlineStr"/>
+      <c r="K62" s="13" t="inlineStr">
+        <is>
+          <t>Tiger Group (PR Newswire)</t>
+        </is>
+      </c>
+      <c r="L62" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M62" s="13" t="inlineStr"/>
+      <c r="N62" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O62" s="14" t="inlineStr">
+        <is>
+          <t>Posted Oct 15. Watch for a bulk/fixture auction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Midwest</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>2 item(s)</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="n"/>
+      <c r="D63" s="18" t="n"/>
+      <c r="E63" s="18" t="n"/>
+      <c r="F63" s="18" t="n"/>
+      <c r="G63" s="18" t="n"/>
+      <c r="H63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="18" t="n"/>
+      <c r="J63" s="18" t="n"/>
+      <c r="K63" s="18" t="n"/>
+      <c r="L63" s="18" t="n"/>
+      <c r="M63" s="18" t="n"/>
+      <c r="N63" s="18" t="n"/>
+      <c r="O63" s="18" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>▸ Texas / South Central  (1)</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="n"/>
+      <c r="C64" s="12" t="n"/>
+      <c r="D64" s="12" t="n"/>
+      <c r="E64" s="12" t="n"/>
+      <c r="F64" s="12" t="n"/>
+      <c r="G64" s="12" t="n"/>
+      <c r="H64" s="12" t="n"/>
+      <c r="I64" s="12" t="n"/>
+      <c r="J64" s="12" t="n"/>
+      <c r="K64" s="12" t="n"/>
+      <c r="L64" s="12" t="n"/>
+      <c r="M64" s="12" t="n"/>
+      <c r="N64" s="12" t="n"/>
+      <c r="O64" s="12" t="n"/>
+    </row>
+    <row r="65" outlineLevel="1">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>Texas / South Central</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>Southwest beverage distributor surplus – mostly unused: 16 True merchandisers, 75 Bunn brewers, 100+ micro-market kiosks</t>
+        </is>
+      </c>
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t>distributor surplus</t>
+        </is>
+      </c>
+      <c r="D65" s="13" t="inlineStr">
+        <is>
+          <t>Mesquite</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="F65" s="13" t="n">
+        <v>1547</v>
+      </c>
+      <c r="G65" s="13" t="inlineStr">
         <is>
           <t>Online auction</t>
         </is>
       </c>
-      <c r="H57" s="15" t="n"/>
-      <c r="I57" s="13" t="inlineStr"/>
-      <c r="J57" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-26 07:30 PM ET</t>
-        </is>
-      </c>
-      <c r="K57" s="13" t="inlineStr">
-        <is>
-          <t>Cash Auctions</t>
-        </is>
-      </c>
-      <c r="L57" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M57" s="13" t="inlineStr"/>
-      <c r="N57" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O57" s="14" t="inlineStr">
-        <is>
-          <t>Lots not reviewed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Upstate / Western NY</t>
-        </is>
-      </c>
-      <c r="B58" s="17" t="inlineStr">
-        <is>
-          <t>3 item(s)</t>
-        </is>
-      </c>
-      <c r="C58" s="18" t="n"/>
-      <c r="D58" s="18" t="n"/>
-      <c r="E58" s="18" t="n"/>
-      <c r="F58" s="18" t="n"/>
-      <c r="G58" s="18" t="n"/>
-      <c r="H58" s="19" t="n">
+      <c r="H65" s="15" t="n"/>
+      <c r="I65" s="13" t="inlineStr"/>
+      <c r="J65" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-13 11:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="inlineStr">
+        <is>
+          <t>Heritage Global Partners</t>
+        </is>
+      </c>
+      <c r="L65" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M65" s="13" t="inlineStr"/>
+      <c r="N65" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O65" s="14" t="inlineStr">
+        <is>
+          <t>Near-new appliances, resell by unit. Nov 13 10 AM CST.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Texas / South Central</t>
+        </is>
+      </c>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>1 item(s)</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="n"/>
+      <c r="D66" s="18" t="n"/>
+      <c r="E66" s="18" t="n"/>
+      <c r="F66" s="18" t="n"/>
+      <c r="G66" s="18" t="n"/>
+      <c r="H66" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I58" s="18" t="n"/>
-      <c r="J58" s="18" t="n"/>
-      <c r="K58" s="18" t="n"/>
-      <c r="L58" s="18" t="n"/>
-      <c r="M58" s="18" t="n"/>
-      <c r="N58" s="18" t="n"/>
-      <c r="O58" s="18" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t>▸ Virginia  (1)</t>
-        </is>
-      </c>
-      <c r="B59" s="12" t="n"/>
-      <c r="C59" s="12" t="n"/>
-      <c r="D59" s="12" t="n"/>
-      <c r="E59" s="12" t="n"/>
-      <c r="F59" s="12" t="n"/>
-      <c r="G59" s="12" t="n"/>
-      <c r="H59" s="12" t="n"/>
-      <c r="I59" s="12" t="n"/>
-      <c r="J59" s="12" t="n"/>
-      <c r="K59" s="12" t="n"/>
-      <c r="L59" s="12" t="n"/>
-      <c r="M59" s="12" t="n"/>
-      <c r="N59" s="12" t="n"/>
-      <c r="O59" s="12" t="n"/>
-    </row>
-    <row r="60" outlineLevel="1">
-      <c r="A60" s="13" t="inlineStr">
-        <is>
-          <t>Virginia</t>
-        </is>
-      </c>
-      <c r="B60" s="14" t="inlineStr">
-        <is>
-          <t>Haynes Furniture / The Dump – 12 stores closing (furniture, mattresses)</t>
-        </is>
-      </c>
-      <c r="C60" s="13" t="inlineStr">
-        <is>
-          <t>retail GOB</t>
-        </is>
-      </c>
-      <c r="D60" s="13" t="inlineStr">
-        <is>
-          <t>Virginia Beach</t>
-        </is>
-      </c>
-      <c r="E60" s="13" t="inlineStr">
-        <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="F60" s="13" t="n">
-        <v>456</v>
-      </c>
-      <c r="G60" s="13" t="inlineStr">
-        <is>
-          <t>Retail GOB markdowns</t>
-        </is>
-      </c>
-      <c r="H60" s="15" t="n"/>
-      <c r="I60" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="J60" s="13" t="inlineStr"/>
-      <c r="K60" s="13" t="inlineStr">
-        <is>
-          <t>SB360 (PR Newswire)</t>
-        </is>
-      </c>
-      <c r="L60" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M60" s="13" t="inlineStr"/>
-      <c r="N60" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O60" s="14" t="inlineStr">
-        <is>
-          <t>Posted Oct 8. Multi-state (VA/AZ/GA/IL/TX); pinned at Virginia Beach. Home goods only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Virginia</t>
-        </is>
-      </c>
-      <c r="B61" s="17" t="inlineStr">
+      <c r="I66" s="18" t="n"/>
+      <c r="J66" s="18" t="n"/>
+      <c r="K66" s="18" t="n"/>
+      <c r="L66" s="18" t="n"/>
+      <c r="M66" s="18" t="n"/>
+      <c r="N66" s="18" t="n"/>
+      <c r="O66" s="18" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>▸ West / Other  (1)</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="n"/>
+      <c r="C67" s="12" t="n"/>
+      <c r="D67" s="12" t="n"/>
+      <c r="E67" s="12" t="n"/>
+      <c r="F67" s="12" t="n"/>
+      <c r="G67" s="12" t="n"/>
+      <c r="H67" s="12" t="n"/>
+      <c r="I67" s="12" t="n"/>
+      <c r="J67" s="12" t="n"/>
+      <c r="K67" s="12" t="n"/>
+      <c r="L67" s="12" t="n"/>
+      <c r="M67" s="12" t="n"/>
+      <c r="N67" s="12" t="n"/>
+      <c r="O67" s="12" t="n"/>
+    </row>
+    <row r="68" outlineLevel="1">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>West / Other</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>National salad concept liquidation – full contents of 63 fast-casual restaurants (AZ/TX/OK/NV)</t>
+        </is>
+      </c>
+      <c r="C68" s="13" t="inlineStr">
+        <is>
+          <t>restaurant chain liquidation</t>
+        </is>
+      </c>
+      <c r="D68" s="13" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="F68" s="13" t="n">
+        <v>2307</v>
+      </c>
+      <c r="G68" s="13" t="inlineStr">
+        <is>
+          <t>Online auctions, dates TBD</t>
+        </is>
+      </c>
+      <c r="H68" s="15" t="n"/>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="J68" s="13" t="inlineStr"/>
+      <c r="K68" s="13" t="inlineStr">
+        <is>
+          <t>RestaurantEquipment.bid (TAGeX)</t>
+        </is>
+      </c>
+      <c r="L68" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M68" s="13" t="inlineStr"/>
+      <c r="N68" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O68" s="14" t="inlineStr">
+        <is>
+          <t>Rolling market-by-market auctions, none live yet (Phoenix metro 30 locations, DFW 14, Tucson 6, Houston 5, plus OK/NV). Pickup on site at each restaurant. Pinned at Phoenix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — West / Other</t>
+        </is>
+      </c>
+      <c r="B69" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C61" s="18" t="n"/>
-      <c r="D61" s="18" t="n"/>
-      <c r="E61" s="18" t="n"/>
-      <c r="F61" s="18" t="n"/>
-      <c r="G61" s="18" t="n"/>
-      <c r="H61" s="19" t="n">
+      <c r="C69" s="18" t="n"/>
+      <c r="D69" s="18" t="n"/>
+      <c r="E69" s="18" t="n"/>
+      <c r="F69" s="18" t="n"/>
+      <c r="G69" s="18" t="n"/>
+      <c r="H69" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I61" s="18" t="n"/>
-      <c r="J61" s="18" t="n"/>
-      <c r="K61" s="18" t="n"/>
-      <c r="L61" s="18" t="n"/>
-      <c r="M61" s="18" t="n"/>
-      <c r="N61" s="18" t="n"/>
-      <c r="O61" s="18" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="11" t="inlineStr">
-        <is>
-          <t>▸ Midwest  (2)</t>
-        </is>
-      </c>
-      <c r="B62" s="12" t="n"/>
-      <c r="C62" s="12" t="n"/>
-      <c r="D62" s="12" t="n"/>
-      <c r="E62" s="12" t="n"/>
-      <c r="F62" s="12" t="n"/>
-      <c r="G62" s="12" t="n"/>
-      <c r="H62" s="12" t="n"/>
-      <c r="I62" s="12" t="n"/>
-      <c r="J62" s="12" t="n"/>
-      <c r="K62" s="12" t="n"/>
-      <c r="L62" s="12" t="n"/>
-      <c r="M62" s="12" t="n"/>
-      <c r="N62" s="12" t="n"/>
-      <c r="O62" s="12" t="n"/>
-    </row>
-    <row r="63" outlineLevel="1">
-      <c r="A63" s="13" t="inlineStr">
-        <is>
-          <t>Midwest</t>
-        </is>
-      </c>
-      <c r="B63" s="14" t="inlineStr">
-        <is>
-          <t>Freshway Market whole-grocery liquidation – refrigeration racks, cases, walk-ins, generator</t>
-        </is>
-      </c>
-      <c r="C63" s="13" t="inlineStr">
-        <is>
-          <t>store closing</t>
-        </is>
-      </c>
-      <c r="D63" s="13" t="inlineStr">
-        <is>
-          <t>Chicago</t>
-        </is>
-      </c>
-      <c r="E63" s="13" t="inlineStr">
-        <is>
-          <t>IL</t>
-        </is>
-      </c>
-      <c r="F63" s="13" t="n">
-        <v>862</v>
-      </c>
-      <c r="G63" s="13" t="inlineStr">
-        <is>
-          <t>Online auction</t>
-        </is>
-      </c>
-      <c r="H63" s="15" t="n"/>
-      <c r="I63" s="13" t="inlineStr"/>
-      <c r="J63" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-20 11:00 AM ET</t>
-        </is>
-      </c>
-      <c r="K63" s="13" t="inlineStr">
-        <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L63" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M63" s="13" t="inlineStr"/>
-      <c r="N63" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O63" s="14" t="inlineStr">
-        <is>
-          <t>Closes from Oct 20 10 AM CDT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" outlineLevel="1">
-      <c r="A64" s="13" t="inlineStr">
-        <is>
-          <t>Midwest</t>
-        </is>
-      </c>
-      <c r="B64" s="14" t="inlineStr">
-        <is>
-          <t>American Sale – total liquidation, all 7 stores (pools, hot tubs, grills, holiday decor)</t>
-        </is>
-      </c>
-      <c r="C64" s="13" t="inlineStr">
-        <is>
-          <t>retail GOB</t>
-        </is>
-      </c>
-      <c r="D64" s="13" t="inlineStr">
-        <is>
-          <t>Chicagoland</t>
-        </is>
-      </c>
-      <c r="E64" s="13" t="inlineStr">
-        <is>
-          <t>IL</t>
-        </is>
-      </c>
-      <c r="F64" s="13" t="n">
-        <v>876</v>
-      </c>
-      <c r="G64" s="13" t="inlineStr">
-        <is>
-          <t>Retail GOB, up to 70% off</t>
-        </is>
-      </c>
-      <c r="H64" s="15" t="n"/>
-      <c r="I64" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="J64" s="13" t="inlineStr"/>
-      <c r="K64" s="13" t="inlineStr">
-        <is>
-          <t>Tiger Group (PR Newswire)</t>
-        </is>
-      </c>
-      <c r="L64" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M64" s="13" t="inlineStr"/>
-      <c r="N64" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O64" s="14" t="inlineStr">
-        <is>
-          <t>Posted Oct 15. Watch for a bulk/fixture auction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Midwest</t>
-        </is>
-      </c>
-      <c r="B65" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C65" s="18" t="n"/>
-      <c r="D65" s="18" t="n"/>
-      <c r="E65" s="18" t="n"/>
-      <c r="F65" s="18" t="n"/>
-      <c r="G65" s="18" t="n"/>
-      <c r="H65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="18" t="n"/>
-      <c r="J65" s="18" t="n"/>
-      <c r="K65" s="18" t="n"/>
-      <c r="L65" s="18" t="n"/>
-      <c r="M65" s="18" t="n"/>
-      <c r="N65" s="18" t="n"/>
-      <c r="O65" s="18" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t>▸ Texas / South Central  (1)</t>
-        </is>
-      </c>
-      <c r="B66" s="12" t="n"/>
-      <c r="C66" s="12" t="n"/>
-      <c r="D66" s="12" t="n"/>
-      <c r="E66" s="12" t="n"/>
-      <c r="F66" s="12" t="n"/>
-      <c r="G66" s="12" t="n"/>
-      <c r="H66" s="12" t="n"/>
-      <c r="I66" s="12" t="n"/>
-      <c r="J66" s="12" t="n"/>
-      <c r="K66" s="12" t="n"/>
-      <c r="L66" s="12" t="n"/>
-      <c r="M66" s="12" t="n"/>
-      <c r="N66" s="12" t="n"/>
-      <c r="O66" s="12" t="n"/>
-    </row>
-    <row r="67" outlineLevel="1">
-      <c r="A67" s="13" t="inlineStr">
-        <is>
-          <t>Texas / South Central</t>
-        </is>
-      </c>
-      <c r="B67" s="14" t="inlineStr">
-        <is>
-          <t>Southwest beverage distributor surplus – mostly unused: 16 True merchandisers, 75 Bunn brewers, 100+ micro-market kiosks</t>
-        </is>
-      </c>
-      <c r="C67" s="13" t="inlineStr">
-        <is>
-          <t>distributor surplus</t>
-        </is>
-      </c>
-      <c r="D67" s="13" t="inlineStr">
-        <is>
-          <t>Mesquite</t>
-        </is>
-      </c>
-      <c r="E67" s="13" t="inlineStr">
-        <is>
-          <t>TX</t>
-        </is>
-      </c>
-      <c r="F67" s="13" t="n">
-        <v>1547</v>
-      </c>
-      <c r="G67" s="13" t="inlineStr">
-        <is>
-          <t>Online auction</t>
-        </is>
-      </c>
-      <c r="H67" s="15" t="n"/>
-      <c r="I67" s="13" t="inlineStr"/>
-      <c r="J67" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-13 11:00 AM ET</t>
-        </is>
-      </c>
-      <c r="K67" s="13" t="inlineStr">
-        <is>
-          <t>Heritage Global Partners</t>
-        </is>
-      </c>
-      <c r="L67" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M67" s="13" t="inlineStr"/>
-      <c r="N67" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O67" s="14" t="inlineStr">
-        <is>
-          <t>Near-new appliances, resell by unit. Nov 13 10 AM CST.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Texas / South Central</t>
-        </is>
-      </c>
-      <c r="B68" s="17" t="inlineStr">
-        <is>
-          <t>1 item(s)</t>
-        </is>
-      </c>
-      <c r="C68" s="18" t="n"/>
-      <c r="D68" s="18" t="n"/>
-      <c r="E68" s="18" t="n"/>
-      <c r="F68" s="18" t="n"/>
-      <c r="G68" s="18" t="n"/>
-      <c r="H68" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="18" t="n"/>
-      <c r="J68" s="18" t="n"/>
-      <c r="K68" s="18" t="n"/>
-      <c r="L68" s="18" t="n"/>
-      <c r="M68" s="18" t="n"/>
-      <c r="N68" s="18" t="n"/>
-      <c r="O68" s="18" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t>▸ West / Other  (1)</t>
-        </is>
-      </c>
-      <c r="B69" s="12" t="n"/>
-      <c r="C69" s="12" t="n"/>
-      <c r="D69" s="12" t="n"/>
-      <c r="E69" s="12" t="n"/>
-      <c r="F69" s="12" t="n"/>
-      <c r="G69" s="12" t="n"/>
-      <c r="H69" s="12" t="n"/>
-      <c r="I69" s="12" t="n"/>
-      <c r="J69" s="12" t="n"/>
-      <c r="K69" s="12" t="n"/>
-      <c r="L69" s="12" t="n"/>
-      <c r="M69" s="12" t="n"/>
-      <c r="N69" s="12" t="n"/>
-      <c r="O69" s="12" t="n"/>
-    </row>
-    <row r="70" outlineLevel="1">
-      <c r="A70" s="13" t="inlineStr">
-        <is>
-          <t>West / Other</t>
-        </is>
-      </c>
-      <c r="B70" s="14" t="inlineStr">
-        <is>
-          <t>National salad concept liquidation – full contents of 63 fast-casual restaurants (AZ/TX/OK/NV)</t>
-        </is>
-      </c>
-      <c r="C70" s="13" t="inlineStr">
-        <is>
-          <t>restaurant chain liquidation</t>
-        </is>
-      </c>
-      <c r="D70" s="13" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="E70" s="13" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="F70" s="13" t="n">
-        <v>2307</v>
-      </c>
-      <c r="G70" s="13" t="inlineStr">
-        <is>
-          <t>Online auctions, dates TBD</t>
-        </is>
-      </c>
-      <c r="H70" s="15" t="n"/>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="J70" s="13" t="inlineStr"/>
-      <c r="K70" s="13" t="inlineStr">
-        <is>
-          <t>RestaurantEquipment.bid (TAGeX)</t>
-        </is>
-      </c>
-      <c r="L70" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M70" s="13" t="inlineStr"/>
-      <c r="N70" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O70" s="14" t="inlineStr">
-        <is>
-          <t>Rolling market-by-market auctions, none live yet (Phoenix metro 30 locations, DFW 14, Tucson 6, Houston 5, plus OK/NV). Pickup on site at each restaurant. Pinned at Phoenix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — West / Other</t>
-        </is>
-      </c>
-      <c r="B71" s="17" t="inlineStr">
-        <is>
-          <t>1 item(s)</t>
-        </is>
-      </c>
-      <c r="C71" s="18" t="n"/>
-      <c r="D71" s="18" t="n"/>
-      <c r="E71" s="18" t="n"/>
-      <c r="F71" s="18" t="n"/>
-      <c r="G71" s="18" t="n"/>
-      <c r="H71" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="18" t="n"/>
-      <c r="J71" s="18" t="n"/>
-      <c r="K71" s="18" t="n"/>
-      <c r="L71" s="18" t="n"/>
-      <c r="M71" s="18" t="n"/>
-      <c r="N71" s="18" t="n"/>
-      <c r="O71" s="18" t="n"/>
+      <c r="I69" s="18" t="n"/>
+      <c r="J69" s="18" t="n"/>
+      <c r="K69" s="18" t="n"/>
+      <c r="L69" s="18" t="n"/>
+      <c r="M69" s="18" t="n"/>
+      <c r="N69" s="18" t="n"/>
+      <c r="O69" s="18" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O71"/>
+  <autoFilter ref="A1:O69"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId2"/>
@@ -22235,8 +22109,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId24"/>
@@ -22251,17 +22125,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N52" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N60" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N64" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N67" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N61" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N62" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N65" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N68" r:id="rId44"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lot_recon.xlsx
+++ b/lot_recon.xlsx
@@ -20,8 +20,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wolf New'!$A$1:$O$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wolf Used'!$A$1:$O$188</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Wolf Unclear'!$A$1:$O$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$69</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Removed'!$A$1:$O$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Removed'!$A$1:$O$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -577,7 +577,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Last updated: 2026-10-18 14:02 ET</t>
+          <t>Last updated: 2026-10-18 17:57 ET</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Active listings: 284 · Removed: 2</t>
+          <t>Active listings: 285 · Removed: 3</t>
         </is>
       </c>
     </row>
@@ -679,10 +679,10 @@
         <v>163</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>603231.6</v>
+        <v>603632.6</v>
       </c>
       <c r="D10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -708,13 +708,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>975650.08</v>
+        <v>976051.08</v>
       </c>
     </row>
     <row r="15">
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -1004,7 +1004,7 @@
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H23" s="6" t="n">
         <v>62163</v>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -1031,7 +1031,7 @@
         <v>7</v>
       </c>
       <c r="E24" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F24" t="n">
         <v>24</v>
@@ -1040,7 +1040,7 @@
         <v>16</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>439641</v>
+        <v>440141</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C34" t="n">
         <v>0</v>
@@ -1361,7 +1361,7 @@
         <v>14</v>
       </c>
       <c r="E34" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F34" t="n">
         <v>0</v>
@@ -1370,7 +1370,7 @@
         <v>0</v>
       </c>
       <c r="H34" s="6" t="n">
-        <v>285195.89</v>
+        <v>285096.89</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>▸ NYC / Long Island / NJ  (64)</t>
+          <t>▸ NYC / Long Island / NJ  (65)</t>
         </is>
       </c>
       <c r="B46" s="12" t="n"/>
@@ -8731,17 +8731,17 @@
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>Wolf 36" Contemporary Gas Cooktop (Model: CG365T/S) – Excellent Condition</t>
+          <t>Wolf M Series CSO30CM/B/TH 30" convection steam oven (black, tubular handle)</t>
         </is>
       </c>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>range/oven/rangetop</t>
+          <t>range/rangetop/oven/cooktop</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Jackson Heights</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
@@ -8750,21 +8750,25 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>$950</t>
+          <t>$500</t>
         </is>
       </c>
       <c r="H62" s="15" t="n">
-        <v>950</v>
-      </c>
-      <c r="I62" s="13" t="inlineStr"/>
+        <v>500</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="J62" s="13" t="inlineStr"/>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>OfferUp</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L62" s="13" t="inlineStr">
@@ -8772,7 +8776,11 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M62" s="13" t="inlineStr"/>
+      <c r="M62" s="21" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
       <c r="N62" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -8780,7 +8788,7 @@
       </c>
       <c r="O62" s="14" t="inlineStr">
         <is>
-          <t>Condition: used.</t>
+          <t>Listed "like new", barely used; uninstalled and stored, seller clearing storage. Non-plumbed water tank. Strong flip at $500 for a current M Series built-in steam oven; verify it powers on and the tank/probe are included.</t>
         </is>
       </c>
     </row>
@@ -8792,7 +8800,7 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>Wolf 36" Contemporary Gas Cooktop (Model: CG365T/S) – Excellent Condit</t>
+          <t>Wolf 36" Contemporary Gas Cooktop (Model: CG365T/S) – Excellent Condition</t>
         </is>
       </c>
       <c r="C63" s="13" t="inlineStr">
@@ -8821,15 +8829,11 @@
       <c r="H63" s="15" t="n">
         <v>950</v>
       </c>
-      <c r="I63" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
+      <c r="I63" s="13" t="inlineStr"/>
       <c r="J63" s="13" t="inlineStr"/>
       <c r="K63" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>OfferUp</t>
         </is>
       </c>
       <c r="L63" s="13" t="inlineStr">
@@ -8857,7 +8861,7 @@
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>Wolf Built In Microwave /Convection Oven</t>
+          <t>Wolf 36" Contemporary Gas Cooktop (Model: CG365T/S) – Excellent Condit</t>
         </is>
       </c>
       <c r="C64" s="13" t="inlineStr">
@@ -8867,7 +8871,7 @@
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
@@ -8876,21 +8880,25 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>$350</t>
+          <t>$950</t>
         </is>
       </c>
       <c r="H64" s="15" t="n">
-        <v>350</v>
-      </c>
-      <c r="I64" s="13" t="inlineStr"/>
+        <v>950</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
       <c r="J64" s="13" t="inlineStr"/>
       <c r="K64" s="13" t="inlineStr">
         <is>
-          <t>OfferUp</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L64" s="13" t="inlineStr">
@@ -8918,7 +8926,7 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>Wolf stove 60"" originally payed $ 18000, barely used</t>
+          <t>Wolf Built In Microwave /Convection Oven</t>
         </is>
       </c>
       <c r="C65" s="13" t="inlineStr">
@@ -8928,12 +8936,12 @@
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>Weehawken</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F65" s="13" t="n">
@@ -8941,11 +8949,11 @@
       </c>
       <c r="G65" s="13" t="inlineStr">
         <is>
-          <t>$11,000</t>
+          <t>$350</t>
         </is>
       </c>
       <c r="H65" s="15" t="n">
-        <v>11000</v>
+        <v>350</v>
       </c>
       <c r="I65" s="13" t="inlineStr"/>
       <c r="J65" s="13" t="inlineStr"/>
@@ -8979,7 +8987,7 @@
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>48" Wolf Oven - Needs TLC But Works Great</t>
+          <t>Wolf stove 60"" originally payed $ 18000, barely used</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
@@ -8989,7 +8997,7 @@
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t>Secaucus</t>
+          <t>Weehawken</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
@@ -8998,15 +9006,15 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="G66" s="13" t="inlineStr">
         <is>
-          <t>$2,000</t>
+          <t>$11,000</t>
         </is>
       </c>
       <c r="H66" s="15" t="n">
-        <v>2000</v>
+        <v>11000</v>
       </c>
       <c r="I66" s="13" t="inlineStr"/>
       <c r="J66" s="13" t="inlineStr"/>
@@ -9020,11 +9028,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M66" s="21" t="inlineStr">
-        <is>
-          <t>FLIP</t>
-        </is>
-      </c>
+      <c r="M66" s="13" t="inlineStr"/>
       <c r="N66" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -9032,7 +9036,7 @@
       </c>
       <c r="O66" s="14" t="inlineStr">
         <is>
-          <t>Condition: used. FLIP: 48" double-oven range $2,000, needs TLC; 48" sold $3.8-3.9k; resale $3.5-5k</t>
+          <t>Condition: used.</t>
         </is>
       </c>
     </row>
@@ -9044,7 +9048,7 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>🔥 WOLF PROFESSIONAL APPLIANCES — COMPLETE KITCHEN SET</t>
+          <t>48" Wolf Oven - Needs TLC But Works Great</t>
         </is>
       </c>
       <c r="C67" s="13" t="inlineStr">
@@ -9054,7 +9058,7 @@
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>Franklin Lakes</t>
+          <t>Secaucus</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
@@ -9067,11 +9071,11 @@
       </c>
       <c r="G67" s="13" t="inlineStr">
         <is>
-          <t>$5,000</t>
+          <t>$2,000</t>
         </is>
       </c>
       <c r="H67" s="15" t="n">
-        <v>5000</v>
+        <v>2000</v>
       </c>
       <c r="I67" s="13" t="inlineStr"/>
       <c r="J67" s="13" t="inlineStr"/>
@@ -9085,7 +9089,11 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M67" s="13" t="inlineStr"/>
+      <c r="M67" s="21" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
       <c r="N67" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -9093,7 +9101,7 @@
       </c>
       <c r="O67" s="14" t="inlineStr">
         <is>
-          <t>Condition: used.</t>
+          <t>Condition: used. FLIP: 48" double-oven range $2,000, needs TLC; 48" sold $3.8-3.9k; resale $3.5-5k</t>
         </is>
       </c>
     </row>
@@ -9105,7 +9113,7 @@
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stove 36 inch used excellent condition</t>
+          <t>🔥 WOLF PROFESSIONAL APPLIANCES — COMPLETE KITCHEN SET</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
@@ -9115,7 +9123,7 @@
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>Secaucus</t>
+          <t>Franklin Lakes</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
@@ -9128,11 +9136,11 @@
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
-          <t>$4,450</t>
+          <t>$5,000</t>
         </is>
       </c>
       <c r="H68" s="15" t="n">
-        <v>4450</v>
+        <v>5000</v>
       </c>
       <c r="I68" s="13" t="inlineStr"/>
       <c r="J68" s="13" t="inlineStr"/>
@@ -9166,7 +9174,7 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 5-Burner Gas Cooktop</t>
+          <t>Wolf Stove 36 inch used excellent condition</t>
         </is>
       </c>
       <c r="C69" s="13" t="inlineStr">
@@ -9176,7 +9184,7 @@
       </c>
       <c r="D69" s="13" t="inlineStr">
         <is>
-          <t>Wallington</t>
+          <t>Secaucus</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
@@ -9185,21 +9193,17 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G69" s="13" t="inlineStr">
         <is>
-          <t>$400</t>
+          <t>$4,450</t>
         </is>
       </c>
       <c r="H69" s="15" t="n">
-        <v>400</v>
-      </c>
-      <c r="I69" s="13" t="inlineStr">
-        <is>
-          <t>posted ~1 day ago</t>
-        </is>
-      </c>
+        <v>4450</v>
+      </c>
+      <c r="I69" s="13" t="inlineStr"/>
       <c r="J69" s="13" t="inlineStr"/>
       <c r="K69" s="13" t="inlineStr">
         <is>
@@ -9231,7 +9235,7 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>Wolf 36 Dual Fuel Range DF366 Natural Gas (Beautiful USED Condition)</t>
+          <t>Wolf Stainless Steel 5-Burner Gas Cooktop</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
@@ -9241,7 +9245,7 @@
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>Paterson</t>
+          <t>Wallington</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
@@ -9254,13 +9258,17 @@
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
-          <t>$6,000</t>
+          <t>$400</t>
         </is>
       </c>
       <c r="H70" s="15" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I70" s="13" t="inlineStr"/>
+        <v>400</v>
+      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>posted ~1 day ago</t>
+        </is>
+      </c>
       <c r="J70" s="13" t="inlineStr"/>
       <c r="K70" s="13" t="inlineStr">
         <is>
@@ -9292,7 +9300,7 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 36” Inch Wide Gas Range 4-Burners w/Grill</t>
+          <t>Wolf 36 Dual Fuel Range DF366 Natural Gas (Beautiful USED Condition)</t>
         </is>
       </c>
       <c r="C71" s="13" t="inlineStr">
@@ -9302,7 +9310,7 @@
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>Clifton</t>
+          <t>Paterson</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
@@ -9311,25 +9319,21 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G71" s="13" t="inlineStr">
         <is>
-          <t>$3,800</t>
+          <t>$6,000</t>
         </is>
       </c>
       <c r="H71" s="15" t="n">
-        <v>3800</v>
-      </c>
-      <c r="I71" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
+        <v>6000</v>
+      </c>
+      <c r="I71" s="13" t="inlineStr"/>
       <c r="J71" s="13" t="inlineStr"/>
       <c r="K71" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>OfferUp</t>
         </is>
       </c>
       <c r="L71" s="13" t="inlineStr">
@@ -9357,7 +9361,7 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 48” Inch Wide Gas Range &amp; Wolf 48” Range Hood</t>
+          <t>Wolf Stainless Steel 36” Inch Wide Gas Range 4-Burners w/Grill</t>
         </is>
       </c>
       <c r="C72" s="13" t="inlineStr">
@@ -9380,11 +9384,11 @@
       </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
-          <t>$6,800</t>
+          <t>$3,800</t>
         </is>
       </c>
       <c r="H72" s="15" t="n">
-        <v>6800</v>
+        <v>3800</v>
       </c>
       <c r="I72" s="13" t="inlineStr">
         <is>
@@ -9422,7 +9426,7 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless 48” Gas Range/Wolf Hood 48”/Subzero Fridge 48” Wide</t>
+          <t>Wolf Stainless Steel 48” Inch Wide Gas Range &amp; Wolf 48” Range Hood</t>
         </is>
       </c>
       <c r="C73" s="13" t="inlineStr">
@@ -9445,11 +9449,11 @@
       </c>
       <c r="G73" s="13" t="inlineStr">
         <is>
-          <t>$12,800</t>
+          <t>$6,800</t>
         </is>
       </c>
       <c r="H73" s="15" t="n">
-        <v>12800</v>
+        <v>6800</v>
       </c>
       <c r="I73" s="13" t="inlineStr">
         <is>
@@ -9487,7 +9491,7 @@
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 36” Wide Gas Range</t>
+          <t>Wolf Stainless 48” Gas Range/Wolf Hood 48”/Subzero Fridge 48” Wide</t>
         </is>
       </c>
       <c r="C74" s="13" t="inlineStr">
@@ -9510,11 +9514,11 @@
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>$2,800</t>
+          <t>$12,800</t>
         </is>
       </c>
       <c r="H74" s="15" t="n">
-        <v>2800</v>
+        <v>12800</v>
       </c>
       <c r="I74" s="13" t="inlineStr">
         <is>
@@ -9552,7 +9556,7 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 48” Inch Wide Gas Range</t>
+          <t>Wolf Stainless Steel 36” Wide Gas Range</t>
         </is>
       </c>
       <c r="C75" s="13" t="inlineStr">
@@ -9575,11 +9579,11 @@
       </c>
       <c r="G75" s="13" t="inlineStr">
         <is>
-          <t>$3,500</t>
+          <t>$2,800</t>
         </is>
       </c>
       <c r="H75" s="15" t="n">
-        <v>3500</v>
+        <v>2800</v>
       </c>
       <c r="I75" s="13" t="inlineStr">
         <is>
@@ -9617,7 +9621,7 @@
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>GE Monogram Stainless 48” Fridge &amp; Wolf Gas Range 48” Wide</t>
+          <t>Wolf Stainless Steel 48” Inch Wide Gas Range</t>
         </is>
       </c>
       <c r="C76" s="13" t="inlineStr">
@@ -9640,11 +9644,11 @@
       </c>
       <c r="G76" s="13" t="inlineStr">
         <is>
-          <t>$8,800</t>
+          <t>$3,500</t>
         </is>
       </c>
       <c r="H76" s="15" t="n">
-        <v>8800</v>
+        <v>3500</v>
       </c>
       <c r="I76" s="13" t="inlineStr">
         <is>
@@ -9682,7 +9686,7 @@
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>Subzero Panel Ready Fridge 48” Wide/Wolf Gas Range 48” Wide</t>
+          <t>GE Monogram Stainless 48” Fridge &amp; Wolf Gas Range 48” Wide</t>
         </is>
       </c>
       <c r="C77" s="13" t="inlineStr">
@@ -9705,11 +9709,11 @@
       </c>
       <c r="G77" s="13" t="inlineStr">
         <is>
-          <t>$11,600</t>
+          <t>$8,800</t>
         </is>
       </c>
       <c r="H77" s="15" t="n">
-        <v>11600</v>
+        <v>8800</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -9747,7 +9751,7 @@
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 48” Inch Wide All Gas Range</t>
+          <t>Subzero Panel Ready Fridge 48” Wide/Wolf Gas Range 48” Wide</t>
         </is>
       </c>
       <c r="C78" s="13" t="inlineStr">
@@ -9770,11 +9774,11 @@
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
-          <t>$4,800</t>
+          <t>$11,600</t>
         </is>
       </c>
       <c r="H78" s="15" t="n">
-        <v>4800</v>
+        <v>11600</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -9812,7 +9816,7 @@
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 36” Gas Range &amp; Subzero Stainless 36” Fridge</t>
+          <t>Wolf Stainless Steel 48” Inch Wide All Gas Range</t>
         </is>
       </c>
       <c r="C79" s="13" t="inlineStr">
@@ -9835,11 +9839,11 @@
       </c>
       <c r="G79" s="13" t="inlineStr">
         <is>
-          <t>$7,800</t>
+          <t>$4,800</t>
         </is>
       </c>
       <c r="H79" s="15" t="n">
-        <v>7800</v>
+        <v>4800</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -9877,7 +9881,7 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>Subzero Panel Ready 3-Door Fridge/Wolf 36” Gas Range/Miele Dishwasher</t>
+          <t>Wolf Stainless Steel 36” Gas Range &amp; Subzero Stainless 36” Fridge</t>
         </is>
       </c>
       <c r="C80" s="13" t="inlineStr">
@@ -9900,11 +9904,11 @@
       </c>
       <c r="G80" s="13" t="inlineStr">
         <is>
-          <t>$9,800</t>
+          <t>$7,800</t>
         </is>
       </c>
       <c r="H80" s="15" t="n">
-        <v>9800</v>
+        <v>7800</v>
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
@@ -9942,7 +9946,7 @@
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel Gas Range 48” /Subzero 48” Fridge Panel Ready</t>
+          <t>Subzero Panel Ready 3-Door Fridge/Wolf 36” Gas Range/Miele Dishwasher</t>
         </is>
       </c>
       <c r="C81" s="13" t="inlineStr">
@@ -10007,7 +10011,7 @@
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 48” Inch Wide Gas Range (Propane Set) w/Grill</t>
+          <t>Wolf Stainless Steel Gas Range 48” /Subzero 48” Fridge Panel Ready</t>
         </is>
       </c>
       <c r="C82" s="13" t="inlineStr">
@@ -10030,11 +10034,11 @@
       </c>
       <c r="G82" s="13" t="inlineStr">
         <is>
-          <t>$4,800</t>
+          <t>$9,800</t>
         </is>
       </c>
       <c r="H82" s="15" t="n">
-        <v>4800</v>
+        <v>9800</v>
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
@@ -10072,7 +10076,7 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>Subzero Two Panel Ready Column Fridges &amp; Wolf Gas Range 48” Wide</t>
+          <t>Wolf Stainless Steel 48” Inch Wide Gas Range (Propane Set) w/Grill</t>
         </is>
       </c>
       <c r="C83" s="13" t="inlineStr">
@@ -10095,11 +10099,11 @@
       </c>
       <c r="G83" s="13" t="inlineStr">
         <is>
-          <t>$9,800</t>
+          <t>$4,800</t>
         </is>
       </c>
       <c r="H83" s="15" t="n">
-        <v>9800</v>
+        <v>4800</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -10137,7 +10141,7 @@
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel Gas Range 36” Wide/Subzero Fridge 48” Panel Ready</t>
+          <t>Subzero Two Panel Ready Column Fridges &amp; Wolf Gas Range 48” Wide</t>
         </is>
       </c>
       <c r="C84" s="13" t="inlineStr">
@@ -10160,11 +10164,11 @@
       </c>
       <c r="G84" s="13" t="inlineStr">
         <is>
-          <t>$7,800</t>
+          <t>$9,800</t>
         </is>
       </c>
       <c r="H84" s="15" t="n">
-        <v>7800</v>
+        <v>9800</v>
       </c>
       <c r="I84" s="13" t="inlineStr">
         <is>
@@ -10202,7 +10206,7 @@
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>Subzero 2017 Model Fridge 48”/Wolf Gas Range 48” Wide</t>
+          <t>Wolf Stainless Steel Gas Range 36” Wide/Subzero Fridge 48” Panel Ready</t>
         </is>
       </c>
       <c r="C85" s="13" t="inlineStr">
@@ -10225,11 +10229,11 @@
       </c>
       <c r="G85" s="13" t="inlineStr">
         <is>
-          <t>$10,800</t>
+          <t>$7,800</t>
         </is>
       </c>
       <c r="H85" s="15" t="n">
-        <v>10800</v>
+        <v>7800</v>
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
@@ -10267,7 +10271,7 @@
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 36” Wide Gas Range/Kitchen Aid 42” Wide Fridge</t>
+          <t>Subzero 2017 Model Fridge 48”/Wolf Gas Range 48” Wide</t>
         </is>
       </c>
       <c r="C86" s="13" t="inlineStr">
@@ -10290,11 +10294,11 @@
       </c>
       <c r="G86" s="13" t="inlineStr">
         <is>
-          <t>$9,800</t>
+          <t>$10,800</t>
         </is>
       </c>
       <c r="H86" s="15" t="n">
-        <v>9800</v>
+        <v>10800</v>
       </c>
       <c r="I86" s="13" t="inlineStr">
         <is>
@@ -10332,7 +10336,7 @@
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel Gas Stove 36” Wide/Subzero 48” Fridge Panel Ready</t>
+          <t>Wolf Stainless Steel 36” Wide Gas Range/Kitchen Aid 42” Wide Fridge</t>
         </is>
       </c>
       <c r="C87" s="13" t="inlineStr">
@@ -10355,11 +10359,11 @@
       </c>
       <c r="G87" s="13" t="inlineStr">
         <is>
-          <t>$8,800</t>
+          <t>$9,800</t>
         </is>
       </c>
       <c r="H87" s="15" t="n">
-        <v>8800</v>
+        <v>9800</v>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
@@ -10397,7 +10401,7 @@
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 36” Wide Gas Range/Subzero 42” Built In Fridge</t>
+          <t>Wolf Stainless Steel Gas Stove 36” Wide/Subzero 48” Fridge Panel Ready</t>
         </is>
       </c>
       <c r="C88" s="13" t="inlineStr">
@@ -10462,7 +10466,7 @@
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless 36” Wide Gas Range/Subzero 42” Wide Fridge Built In</t>
+          <t>Wolf Stainless Steel 36” Wide Gas Range/Subzero 42” Built In Fridge</t>
         </is>
       </c>
       <c r="C89" s="13" t="inlineStr">
@@ -10485,11 +10489,11 @@
       </c>
       <c r="G89" s="13" t="inlineStr">
         <is>
-          <t>$7,800</t>
+          <t>$8,800</t>
         </is>
       </c>
       <c r="H89" s="15" t="n">
-        <v>7800</v>
+        <v>8800</v>
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
@@ -10527,7 +10531,7 @@
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>Kitchen Aid New 42” Fridge/Wolf Stainless 36” Gas Range</t>
+          <t>Wolf Stainless 36” Wide Gas Range/Subzero 42” Wide Fridge Built In</t>
         </is>
       </c>
       <c r="C90" s="13" t="inlineStr">
@@ -10550,11 +10554,11 @@
       </c>
       <c r="G90" s="13" t="inlineStr">
         <is>
-          <t>$9,800</t>
+          <t>$7,800</t>
         </is>
       </c>
       <c r="H90" s="15" t="n">
-        <v>9800</v>
+        <v>7800</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
@@ -10592,7 +10596,7 @@
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 30” Gas Stove/Subzero 36” Built In Fridge</t>
+          <t>Kitchen Aid New 42” Fridge/Wolf Stainless 36” Gas Range</t>
         </is>
       </c>
       <c r="C91" s="13" t="inlineStr">
@@ -10615,11 +10619,11 @@
       </c>
       <c r="G91" s="13" t="inlineStr">
         <is>
-          <t>$6,600</t>
+          <t>$9,800</t>
         </is>
       </c>
       <c r="H91" s="15" t="n">
-        <v>6600</v>
+        <v>9800</v>
       </c>
       <c r="I91" s="13" t="inlineStr">
         <is>
@@ -10657,7 +10661,7 @@
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>Subzero Panel Ready 48” Fridge/Wolf 36” Wide Gas Range</t>
+          <t>Wolf Stainless Steel 30” Gas Stove/Subzero 36” Built In Fridge</t>
         </is>
       </c>
       <c r="C92" s="13" t="inlineStr">
@@ -10680,11 +10684,11 @@
       </c>
       <c r="G92" s="13" t="inlineStr">
         <is>
-          <t>$7,800</t>
+          <t>$6,600</t>
         </is>
       </c>
       <c r="H92" s="15" t="n">
-        <v>7800</v>
+        <v>6600</v>
       </c>
       <c r="I92" s="13" t="inlineStr">
         <is>
@@ -10722,7 +10726,7 @@
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>Subzero Stainless Steel 36” Fridge/Wolf 30” Wide Gas Range Stainless</t>
+          <t>Subzero Panel Ready 48” Fridge/Wolf 36” Wide Gas Range</t>
         </is>
       </c>
       <c r="C93" s="13" t="inlineStr">
@@ -10745,11 +10749,11 @@
       </c>
       <c r="G93" s="13" t="inlineStr">
         <is>
-          <t>$6,600</t>
+          <t>$7,800</t>
         </is>
       </c>
       <c r="H93" s="15" t="n">
-        <v>6600</v>
+        <v>7800</v>
       </c>
       <c r="I93" s="13" t="inlineStr">
         <is>
@@ -10787,7 +10791,7 @@
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 48” Wide Gas Range/Subzero 42” Wide Fridge</t>
+          <t>Subzero Stainless Steel 36” Fridge/Wolf 30” Wide Gas Range Stainless</t>
         </is>
       </c>
       <c r="C94" s="13" t="inlineStr">
@@ -10810,11 +10814,11 @@
       </c>
       <c r="G94" s="13" t="inlineStr">
         <is>
-          <t>$8,200</t>
+          <t>$6,600</t>
         </is>
       </c>
       <c r="H94" s="15" t="n">
-        <v>8200</v>
+        <v>6600</v>
       </c>
       <c r="I94" s="13" t="inlineStr">
         <is>
@@ -10852,7 +10856,7 @@
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>Thermador Stainless 36” Wide 3-Door Fridge/Wolf 36” Gas Range</t>
+          <t>Wolf Stainless Steel 48” Wide Gas Range/Subzero 42” Wide Fridge</t>
         </is>
       </c>
       <c r="C95" s="13" t="inlineStr">
@@ -10875,11 +10879,11 @@
       </c>
       <c r="G95" s="13" t="inlineStr">
         <is>
-          <t>$7,800</t>
+          <t>$8,200</t>
         </is>
       </c>
       <c r="H95" s="15" t="n">
-        <v>7800</v>
+        <v>8200</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
@@ -10917,7 +10921,7 @@
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 36” Inch Wide Gas Range 4-Burners w/Grill</t>
+          <t>Thermador Stainless 36” Wide 3-Door Fridge/Wolf 36” Gas Range</t>
         </is>
       </c>
       <c r="C96" s="13" t="inlineStr">
@@ -10940,11 +10944,11 @@
       </c>
       <c r="G96" s="13" t="inlineStr">
         <is>
-          <t>$3,500</t>
+          <t>$7,800</t>
         </is>
       </c>
       <c r="H96" s="15" t="n">
-        <v>3500</v>
+        <v>7800</v>
       </c>
       <c r="I96" s="13" t="inlineStr">
         <is>
@@ -10982,7 +10986,7 @@
       </c>
       <c r="B97" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 30” Inch Wide Gas Range</t>
+          <t>Wolf Stainless Steel 36” Inch Wide Gas Range 4-Burners w/Grill</t>
         </is>
       </c>
       <c r="C97" s="13" t="inlineStr">
@@ -11005,11 +11009,11 @@
       </c>
       <c r="G97" s="13" t="inlineStr">
         <is>
-          <t>$2,500</t>
+          <t>$3,500</t>
         </is>
       </c>
       <c r="H97" s="15" t="n">
-        <v>2500</v>
+        <v>3500</v>
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
@@ -11047,7 +11051,7 @@
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 48” Inch Wide Gas Range 6-Burners w/Grill</t>
+          <t>Wolf Stainless Steel 30” Inch Wide Gas Range</t>
         </is>
       </c>
       <c r="C98" s="13" t="inlineStr">
@@ -11070,11 +11074,11 @@
       </c>
       <c r="G98" s="13" t="inlineStr">
         <is>
-          <t>$4,500</t>
+          <t>$2,500</t>
         </is>
       </c>
       <c r="H98" s="15" t="n">
-        <v>4500</v>
+        <v>2500</v>
       </c>
       <c r="I98" s="13" t="inlineStr">
         <is>
@@ -11112,7 +11116,7 @@
       </c>
       <c r="B99" s="14" t="inlineStr">
         <is>
-          <t>Kitchen Aid New Stainless 42” Fridge/Wolf 48” Gas Range</t>
+          <t>Wolf Stainless Steel 48” Inch Wide Gas Range 6-Burners w/Grill</t>
         </is>
       </c>
       <c r="C99" s="13" t="inlineStr">
@@ -11135,11 +11139,11 @@
       </c>
       <c r="G99" s="13" t="inlineStr">
         <is>
-          <t>$9,800</t>
+          <t>$4,500</t>
         </is>
       </c>
       <c r="H99" s="15" t="n">
-        <v>9800</v>
+        <v>4500</v>
       </c>
       <c r="I99" s="13" t="inlineStr">
         <is>
@@ -11177,7 +11181,7 @@
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 36” Inch Wide Gas Range 6-Burners</t>
+          <t>Kitchen Aid New Stainless 42” Fridge/Wolf 48” Gas Range</t>
         </is>
       </c>
       <c r="C100" s="13" t="inlineStr">
@@ -11200,11 +11204,11 @@
       </c>
       <c r="G100" s="13" t="inlineStr">
         <is>
-          <t>$3,500</t>
+          <t>$9,800</t>
         </is>
       </c>
       <c r="H100" s="15" t="n">
-        <v>3500</v>
+        <v>9800</v>
       </c>
       <c r="I100" s="13" t="inlineStr">
         <is>
@@ -11242,7 +11246,7 @@
       </c>
       <c r="B101" s="14" t="inlineStr">
         <is>
-          <t>Subzero Stainless 42” Wide Fridge/Wolf 36” Wide Gas Range</t>
+          <t>Wolf Stainless Steel 36” Inch Wide Gas Range 6-Burners</t>
         </is>
       </c>
       <c r="C101" s="13" t="inlineStr">
@@ -11265,11 +11269,11 @@
       </c>
       <c r="G101" s="13" t="inlineStr">
         <is>
-          <t>$7,800</t>
+          <t>$3,500</t>
         </is>
       </c>
       <c r="H101" s="15" t="n">
-        <v>7800</v>
+        <v>3500</v>
       </c>
       <c r="I101" s="13" t="inlineStr">
         <is>
@@ -11307,7 +11311,7 @@
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 48” Wide Gas Range 6-Burner with Grill</t>
+          <t>Subzero Stainless 42” Wide Fridge/Wolf 36” Wide Gas Range</t>
         </is>
       </c>
       <c r="C102" s="13" t="inlineStr">
@@ -11330,11 +11334,11 @@
       </c>
       <c r="G102" s="13" t="inlineStr">
         <is>
-          <t>$4,800</t>
+          <t>$7,800</t>
         </is>
       </c>
       <c r="H102" s="15" t="n">
-        <v>4800</v>
+        <v>7800</v>
       </c>
       <c r="I102" s="13" t="inlineStr">
         <is>
@@ -11372,7 +11376,7 @@
       </c>
       <c r="B103" s="14" t="inlineStr">
         <is>
-          <t>Subzero Stainless Steel 42” Wide Built In Fridge/Wolf Gas Range 36”</t>
+          <t>Wolf Stainless Steel 48” Wide Gas Range 6-Burner with Grill</t>
         </is>
       </c>
       <c r="C103" s="13" t="inlineStr">
@@ -11395,11 +11399,11 @@
       </c>
       <c r="G103" s="13" t="inlineStr">
         <is>
-          <t>$7,800</t>
+          <t>$4,800</t>
         </is>
       </c>
       <c r="H103" s="15" t="n">
-        <v>7800</v>
+        <v>4800</v>
       </c>
       <c r="I103" s="13" t="inlineStr">
         <is>
@@ -11437,7 +11441,7 @@
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>36 INCH WOLF RANGE</t>
+          <t>Subzero Stainless Steel 42” Wide Built In Fridge/Wolf Gas Range 36”</t>
         </is>
       </c>
       <c r="C104" s="13" t="inlineStr">
@@ -11447,7 +11451,7 @@
       </c>
       <c r="D104" s="13" t="inlineStr">
         <is>
-          <t>Tennent</t>
+          <t>Clifton</t>
         </is>
       </c>
       <c r="E104" s="13" t="inlineStr">
@@ -11456,19 +11460,19 @@
         </is>
       </c>
       <c r="F104" s="13" t="n">
-        <v>221</v>
+        <v>194</v>
       </c>
       <c r="G104" s="13" t="inlineStr">
         <is>
-          <t>$3,500</t>
+          <t>$7,800</t>
         </is>
       </c>
       <c r="H104" s="15" t="n">
-        <v>3500</v>
+        <v>7800</v>
       </c>
       <c r="I104" s="13" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-17</t>
         </is>
       </c>
       <c r="J104" s="13" t="inlineStr"/>
@@ -11502,7 +11506,7 @@
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>wolf 30" duel fuel range</t>
+          <t>36 INCH WOLF RANGE</t>
         </is>
       </c>
       <c r="C105" s="13" t="inlineStr">
@@ -11525,11 +11529,11 @@
       </c>
       <c r="G105" s="13" t="inlineStr">
         <is>
-          <t>$4,500</t>
+          <t>$3,500</t>
         </is>
       </c>
       <c r="H105" s="15" t="n">
-        <v>4500</v>
+        <v>3500</v>
       </c>
       <c r="I105" s="13" t="inlineStr">
         <is>
@@ -11567,7 +11571,7 @@
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>48" WOLF RANGETOP</t>
+          <t>wolf 30" duel fuel range</t>
         </is>
       </c>
       <c r="C106" s="13" t="inlineStr">
@@ -11590,11 +11594,11 @@
       </c>
       <c r="G106" s="13" t="inlineStr">
         <is>
-          <t>$2,900</t>
+          <t>$4,500</t>
         </is>
       </c>
       <c r="H106" s="15" t="n">
-        <v>2900</v>
+        <v>4500</v>
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
@@ -11632,7 +11636,7 @@
       </c>
       <c r="B107" s="14" t="inlineStr">
         <is>
-          <t>48” wolf range</t>
+          <t>48" WOLF RANGETOP</t>
         </is>
       </c>
       <c r="C107" s="13" t="inlineStr">
@@ -11655,11 +11659,11 @@
       </c>
       <c r="G107" s="13" t="inlineStr">
         <is>
-          <t>$5,200</t>
+          <t>$2,900</t>
         </is>
       </c>
       <c r="H107" s="15" t="n">
-        <v>5200</v>
+        <v>2900</v>
       </c>
       <c r="I107" s="13" t="inlineStr">
         <is>
@@ -11697,7 +11701,7 @@
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>48” wolf</t>
+          <t>48” wolf range</t>
         </is>
       </c>
       <c r="C108" s="13" t="inlineStr">
@@ -11720,11 +11724,11 @@
       </c>
       <c r="G108" s="13" t="inlineStr">
         <is>
-          <t>$5,300</t>
+          <t>$5,200</t>
         </is>
       </c>
       <c r="H108" s="15" t="n">
-        <v>5300</v>
+        <v>5200</v>
       </c>
       <c r="I108" s="13" t="inlineStr">
         <is>
@@ -11762,7 +11766,7 @@
       </c>
       <c r="B109" s="14" t="inlineStr">
         <is>
-          <t>30” wolf duel fuel range</t>
+          <t>48” wolf</t>
         </is>
       </c>
       <c r="C109" s="13" t="inlineStr">
@@ -11785,11 +11789,11 @@
       </c>
       <c r="G109" s="13" t="inlineStr">
         <is>
-          <t>$4,500</t>
+          <t>$5,300</t>
         </is>
       </c>
       <c r="H109" s="15" t="n">
-        <v>4500</v>
+        <v>5300</v>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
@@ -11827,7 +11831,7 @@
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>Wolf SO36U/S L-Series 36" Electric Single Wall Oven framed Stainless S</t>
+          <t>30” wolf duel fuel range</t>
         </is>
       </c>
       <c r="C110" s="13" t="inlineStr">
@@ -11837,7 +11841,7 @@
       </c>
       <c r="D110" s="13" t="inlineStr">
         <is>
-          <t>Brick</t>
+          <t>Tennent</t>
         </is>
       </c>
       <c r="E110" s="13" t="inlineStr">
@@ -11846,19 +11850,19 @@
         </is>
       </c>
       <c r="F110" s="13" t="n">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G110" s="13" t="inlineStr">
         <is>
-          <t>$150</t>
+          <t>$4,500</t>
         </is>
       </c>
       <c r="H110" s="15" t="n">
-        <v>150</v>
+        <v>4500</v>
       </c>
       <c r="I110" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J110" s="13" t="inlineStr"/>
@@ -11872,364 +11876,364 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M110" s="21" t="inlineStr">
+      <c r="M110" s="13" t="inlineStr"/>
+      <c r="N110" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O110" s="14" t="inlineStr">
+        <is>
+          <t>Condition: used.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" outlineLevel="1">
+      <c r="A111" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B111" s="14" t="inlineStr">
+        <is>
+          <t>Wolf SO36U/S L-Series 36" Electric Single Wall Oven framed Stainless S</t>
+        </is>
+      </c>
+      <c r="C111" s="13" t="inlineStr">
+        <is>
+          <t>range/oven/rangetop</t>
+        </is>
+      </c>
+      <c r="D111" s="13" t="inlineStr">
+        <is>
+          <t>Brick</t>
+        </is>
+      </c>
+      <c r="E111" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F111" s="13" t="n">
+        <v>224</v>
+      </c>
+      <c r="G111" s="13" t="inlineStr">
+        <is>
+          <t>$150</t>
+        </is>
+      </c>
+      <c r="H111" s="15" t="n">
+        <v>150</v>
+      </c>
+      <c r="I111" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J111" s="13" t="inlineStr"/>
+      <c r="K111" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L111" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M111" s="21" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
       </c>
-      <c r="N110" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O110" s="14" t="inlineStr">
+      <c r="N111" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O111" s="14" t="inlineStr">
         <is>
           <t>Condition: used. FLIP: SO36U/S $150 OBO; auction comp $350 w/ drawer; rough resale $600-1k</t>
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="17" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="17" t="inlineStr">
         <is>
           <t>Subtotal — NYC / Long Island / NJ</t>
         </is>
       </c>
-      <c r="B111" s="17" t="inlineStr">
-        <is>
-          <t>64 item(s)</t>
-        </is>
-      </c>
-      <c r="C111" s="18" t="n"/>
-      <c r="D111" s="18" t="n"/>
-      <c r="E111" s="18" t="n"/>
-      <c r="F111" s="18" t="n"/>
-      <c r="G111" s="18" t="n"/>
-      <c r="H111" s="19" t="n">
-        <v>314851</v>
-      </c>
-      <c r="I111" s="18" t="n"/>
-      <c r="J111" s="18" t="n"/>
-      <c r="K111" s="18" t="n"/>
-      <c r="L111" s="18" t="n"/>
-      <c r="M111" s="18" t="n"/>
-      <c r="N111" s="18" t="n"/>
-      <c r="O111" s="18" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" s="11" t="inlineStr">
+      <c r="B112" s="17" t="inlineStr">
+        <is>
+          <t>65 item(s)</t>
+        </is>
+      </c>
+      <c r="C112" s="18" t="n"/>
+      <c r="D112" s="18" t="n"/>
+      <c r="E112" s="18" t="n"/>
+      <c r="F112" s="18" t="n"/>
+      <c r="G112" s="18" t="n"/>
+      <c r="H112" s="19" t="n">
+        <v>315351</v>
+      </c>
+      <c r="I112" s="18" t="n"/>
+      <c r="J112" s="18" t="n"/>
+      <c r="K112" s="18" t="n"/>
+      <c r="L112" s="18" t="n"/>
+      <c r="M112" s="18" t="n"/>
+      <c r="N112" s="18" t="n"/>
+      <c r="O112" s="18" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="11" t="inlineStr">
         <is>
           <t>▸ Eastern PA / Mid-Atlantic  (1)</t>
         </is>
       </c>
-      <c r="B112" s="12" t="n"/>
-      <c r="C112" s="12" t="n"/>
-      <c r="D112" s="12" t="n"/>
-      <c r="E112" s="12" t="n"/>
-      <c r="F112" s="12" t="n"/>
-      <c r="G112" s="12" t="n"/>
-      <c r="H112" s="12" t="n"/>
-      <c r="I112" s="12" t="n"/>
-      <c r="J112" s="12" t="n"/>
-      <c r="K112" s="12" t="n"/>
-      <c r="L112" s="12" t="n"/>
-      <c r="M112" s="12" t="n"/>
-      <c r="N112" s="12" t="n"/>
-      <c r="O112" s="12" t="n"/>
-    </row>
-    <row r="113" outlineLevel="1">
-      <c r="A113" s="13" t="inlineStr">
+      <c r="B113" s="12" t="n"/>
+      <c r="C113" s="12" t="n"/>
+      <c r="D113" s="12" t="n"/>
+      <c r="E113" s="12" t="n"/>
+      <c r="F113" s="12" t="n"/>
+      <c r="G113" s="12" t="n"/>
+      <c r="H113" s="12" t="n"/>
+      <c r="I113" s="12" t="n"/>
+      <c r="J113" s="12" t="n"/>
+      <c r="K113" s="12" t="n"/>
+      <c r="L113" s="12" t="n"/>
+      <c r="M113" s="12" t="n"/>
+      <c r="N113" s="12" t="n"/>
+      <c r="O113" s="12" t="n"/>
+    </row>
+    <row r="114" outlineLevel="1">
+      <c r="A114" s="13" t="inlineStr">
         <is>
           <t>Eastern PA / Mid-Atlantic</t>
         </is>
       </c>
-      <c r="B113" s="14" t="inlineStr">
+      <c r="B114" s="14" t="inlineStr">
         <is>
           <t>Wolf e series oven</t>
         </is>
       </c>
-      <c r="C113" s="13" t="inlineStr">
+      <c r="C114" s="13" t="inlineStr">
         <is>
           <t>range/oven/rangetop</t>
         </is>
       </c>
-      <c r="D113" s="13" t="inlineStr">
+      <c r="D114" s="13" t="inlineStr">
         <is>
           <t>Bryn mawr</t>
         </is>
       </c>
-      <c r="E113" s="13" t="inlineStr">
+      <c r="E114" s="13" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="F113" s="13" t="n">
+      <c r="F114" s="13" t="n">
         <v>276</v>
       </c>
-      <c r="G113" s="13" t="inlineStr">
+      <c r="G114" s="13" t="inlineStr">
         <is>
           <t>$1,500</t>
         </is>
       </c>
-      <c r="H113" s="15" t="n">
+      <c r="H114" s="15" t="n">
         <v>1500</v>
       </c>
-      <c r="I113" s="13" t="inlineStr">
+      <c r="I114" s="13" t="inlineStr">
         <is>
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="J113" s="13" t="inlineStr"/>
-      <c r="K113" s="13" t="inlineStr">
+      <c r="J114" s="13" t="inlineStr"/>
+      <c r="K114" s="13" t="inlineStr">
         <is>
           <t>Craigslist</t>
         </is>
       </c>
-      <c r="L113" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M113" s="13" t="inlineStr"/>
-      <c r="N113" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O113" s="14" t="inlineStr">
+      <c r="L114" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M114" s="13" t="inlineStr"/>
+      <c r="N114" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O114" s="14" t="inlineStr">
         <is>
           <t>Condition: used.</t>
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="17" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Eastern PA / Mid-Atlantic</t>
         </is>
       </c>
-      <c r="B114" s="17" t="inlineStr">
+      <c r="B115" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C114" s="18" t="n"/>
-      <c r="D114" s="18" t="n"/>
-      <c r="E114" s="18" t="n"/>
-      <c r="F114" s="18" t="n"/>
-      <c r="G114" s="18" t="n"/>
-      <c r="H114" s="19" t="n">
+      <c r="C115" s="18" t="n"/>
+      <c r="D115" s="18" t="n"/>
+      <c r="E115" s="18" t="n"/>
+      <c r="F115" s="18" t="n"/>
+      <c r="G115" s="18" t="n"/>
+      <c r="H115" s="19" t="n">
         <v>1500</v>
       </c>
-      <c r="I114" s="18" t="n"/>
-      <c r="J114" s="18" t="n"/>
-      <c r="K114" s="18" t="n"/>
-      <c r="L114" s="18" t="n"/>
-      <c r="M114" s="18" t="n"/>
-      <c r="N114" s="18" t="n"/>
-      <c r="O114" s="18" t="n"/>
-    </row>
-    <row r="115">
-      <c r="A115" s="11" t="inlineStr">
+      <c r="I115" s="18" t="n"/>
+      <c r="J115" s="18" t="n"/>
+      <c r="K115" s="18" t="n"/>
+      <c r="L115" s="18" t="n"/>
+      <c r="M115" s="18" t="n"/>
+      <c r="N115" s="18" t="n"/>
+      <c r="O115" s="18" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="11" t="inlineStr">
         <is>
           <t>▸ Upstate / Western NY  (1)</t>
         </is>
       </c>
-      <c r="B115" s="12" t="n"/>
-      <c r="C115" s="12" t="n"/>
-      <c r="D115" s="12" t="n"/>
-      <c r="E115" s="12" t="n"/>
-      <c r="F115" s="12" t="n"/>
-      <c r="G115" s="12" t="n"/>
-      <c r="H115" s="12" t="n"/>
-      <c r="I115" s="12" t="n"/>
-      <c r="J115" s="12" t="n"/>
-      <c r="K115" s="12" t="n"/>
-      <c r="L115" s="12" t="n"/>
-      <c r="M115" s="12" t="n"/>
-      <c r="N115" s="12" t="n"/>
-      <c r="O115" s="12" t="n"/>
-    </row>
-    <row r="116" outlineLevel="1">
-      <c r="A116" s="13" t="inlineStr">
+      <c r="B116" s="12" t="n"/>
+      <c r="C116" s="12" t="n"/>
+      <c r="D116" s="12" t="n"/>
+      <c r="E116" s="12" t="n"/>
+      <c r="F116" s="12" t="n"/>
+      <c r="G116" s="12" t="n"/>
+      <c r="H116" s="12" t="n"/>
+      <c r="I116" s="12" t="n"/>
+      <c r="J116" s="12" t="n"/>
+      <c r="K116" s="12" t="n"/>
+      <c r="L116" s="12" t="n"/>
+      <c r="M116" s="12" t="n"/>
+      <c r="N116" s="12" t="n"/>
+      <c r="O116" s="12" t="n"/>
+    </row>
+    <row r="117" outlineLevel="1">
+      <c r="A117" s="13" t="inlineStr">
         <is>
           <t>Upstate / Western NY</t>
         </is>
       </c>
-      <c r="B116" s="14" t="inlineStr">
+      <c r="B117" s="14" t="inlineStr">
         <is>
           <t>WOLF GAS RANGE 30”</t>
         </is>
       </c>
-      <c r="C116" s="13" t="inlineStr">
+      <c r="C117" s="13" t="inlineStr">
         <is>
           <t>range/oven/rangetop</t>
         </is>
       </c>
-      <c r="D116" s="13" t="inlineStr">
+      <c r="D117" s="13" t="inlineStr">
         <is>
           <t>Binghamton</t>
         </is>
       </c>
-      <c r="E116" s="13" t="inlineStr">
+      <c r="E117" s="13" t="inlineStr">
         <is>
           <t>NY</t>
         </is>
       </c>
-      <c r="F116" s="13" t="n">
+      <c r="F117" s="13" t="n">
         <v>262</v>
       </c>
-      <c r="G116" s="13" t="inlineStr">
+      <c r="G117" s="13" t="inlineStr">
         <is>
           <t>$1,200</t>
         </is>
       </c>
-      <c r="H116" s="15" t="n">
+      <c r="H117" s="15" t="n">
         <v>1200</v>
       </c>
-      <c r="I116" s="13" t="inlineStr">
+      <c r="I117" s="13" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="J116" s="13" t="inlineStr"/>
-      <c r="K116" s="13" t="inlineStr">
+      <c r="J117" s="13" t="inlineStr"/>
+      <c r="K117" s="13" t="inlineStr">
         <is>
           <t>Craigslist</t>
         </is>
       </c>
-      <c r="L116" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M116" s="21" t="inlineStr">
+      <c r="L117" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M117" s="21" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
       </c>
-      <c r="N116" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O116" s="14" t="inlineStr">
+      <c r="N117" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O117" s="14" t="inlineStr">
         <is>
           <t>Condition: used. FLIP: 30" gas $1,200, needs ~$300 igniter; repaired 30" ask $1.9-3.5k</t>
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="17" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Upstate / Western NY</t>
         </is>
       </c>
-      <c r="B117" s="17" t="inlineStr">
+      <c r="B118" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C117" s="18" t="n"/>
-      <c r="D117" s="18" t="n"/>
-      <c r="E117" s="18" t="n"/>
-      <c r="F117" s="18" t="n"/>
-      <c r="G117" s="18" t="n"/>
-      <c r="H117" s="19" t="n">
+      <c r="C118" s="18" t="n"/>
+      <c r="D118" s="18" t="n"/>
+      <c r="E118" s="18" t="n"/>
+      <c r="F118" s="18" t="n"/>
+      <c r="G118" s="18" t="n"/>
+      <c r="H118" s="19" t="n">
         <v>1200</v>
       </c>
-      <c r="I117" s="18" t="n"/>
-      <c r="J117" s="18" t="n"/>
-      <c r="K117" s="18" t="n"/>
-      <c r="L117" s="18" t="n"/>
-      <c r="M117" s="18" t="n"/>
-      <c r="N117" s="18" t="n"/>
-      <c r="O117" s="18" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="11" t="inlineStr">
+      <c r="I118" s="18" t="n"/>
+      <c r="J118" s="18" t="n"/>
+      <c r="K118" s="18" t="n"/>
+      <c r="L118" s="18" t="n"/>
+      <c r="M118" s="18" t="n"/>
+      <c r="N118" s="18" t="n"/>
+      <c r="O118" s="18" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="11" t="inlineStr">
         <is>
           <t>▸ Virginia  (2)</t>
         </is>
       </c>
-      <c r="B118" s="12" t="n"/>
-      <c r="C118" s="12" t="n"/>
-      <c r="D118" s="12" t="n"/>
-      <c r="E118" s="12" t="n"/>
-      <c r="F118" s="12" t="n"/>
-      <c r="G118" s="12" t="n"/>
-      <c r="H118" s="12" t="n"/>
-      <c r="I118" s="12" t="n"/>
-      <c r="J118" s="12" t="n"/>
-      <c r="K118" s="12" t="n"/>
-      <c r="L118" s="12" t="n"/>
-      <c r="M118" s="12" t="n"/>
-      <c r="N118" s="12" t="n"/>
-      <c r="O118" s="12" t="n"/>
-    </row>
-    <row r="119" outlineLevel="1">
-      <c r="A119" s="13" t="inlineStr">
-        <is>
-          <t>Virginia</t>
-        </is>
-      </c>
-      <c r="B119" s="14" t="inlineStr">
-        <is>
-          <t>Wolf Nat Gas 4 Burner, Flattop, Broiler &amp; Oven</t>
-        </is>
-      </c>
-      <c r="C119" s="13" t="inlineStr">
-        <is>
-          <t>range/oven/rangetop</t>
-        </is>
-      </c>
-      <c r="D119" s="13" t="inlineStr">
-        <is>
-          <t>Alexandria</t>
-        </is>
-      </c>
-      <c r="E119" s="13" t="inlineStr">
-        <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="F119" s="13" t="n">
-        <v>399</v>
-      </c>
-      <c r="G119" s="13" t="inlineStr">
-        <is>
-          <t>$0 current bid + BP</t>
-        </is>
-      </c>
-      <c r="H119" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" s="13" t="inlineStr"/>
-      <c r="J119" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-22 07:16 PM ET</t>
-        </is>
-      </c>
-      <c r="K119" s="13" t="inlineStr">
-        <is>
-          <t>HiBid</t>
-        </is>
-      </c>
-      <c r="L119" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M119" s="13" t="inlineStr"/>
-      <c r="N119" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O119" s="14" t="inlineStr">
-        <is>
-          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf)</t>
-        </is>
-      </c>
+      <c r="B119" s="12" t="n"/>
+      <c r="C119" s="12" t="n"/>
+      <c r="D119" s="12" t="n"/>
+      <c r="E119" s="12" t="n"/>
+      <c r="F119" s="12" t="n"/>
+      <c r="G119" s="12" t="n"/>
+      <c r="H119" s="12" t="n"/>
+      <c r="I119" s="12" t="n"/>
+      <c r="J119" s="12" t="n"/>
+      <c r="K119" s="12" t="n"/>
+      <c r="L119" s="12" t="n"/>
+      <c r="M119" s="12" t="n"/>
+      <c r="N119" s="12" t="n"/>
+      <c r="O119" s="12" t="n"/>
     </row>
     <row r="120" outlineLevel="1">
       <c r="A120" s="13" t="inlineStr">
@@ -12239,7 +12243,7 @@
       </c>
       <c r="B120" s="14" t="inlineStr">
         <is>
-          <t>Wolf Heavy Duty 6 Burner Stepped Range</t>
+          <t>Wolf Nat Gas 4 Burner, Flattop, Broiler &amp; Oven</t>
         </is>
       </c>
       <c r="C120" s="13" t="inlineStr">
@@ -12271,7 +12275,7 @@
       <c r="I120" s="13" t="inlineStr"/>
       <c r="J120" s="13" t="inlineStr">
         <is>
-          <t>2026-10-22 07:30 PM ET</t>
+          <t>2026-10-22 07:16 PM ET</t>
         </is>
       </c>
       <c r="K120" s="13" t="inlineStr">
@@ -12296,118 +12300,118 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="17" t="inlineStr">
+    <row r="121" outlineLevel="1">
+      <c r="A121" s="13" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="B121" s="14" t="inlineStr">
+        <is>
+          <t>Wolf Heavy Duty 6 Burner Stepped Range</t>
+        </is>
+      </c>
+      <c r="C121" s="13" t="inlineStr">
+        <is>
+          <t>range/oven/rangetop</t>
+        </is>
+      </c>
+      <c r="D121" s="13" t="inlineStr">
+        <is>
+          <t>Alexandria</t>
+        </is>
+      </c>
+      <c r="E121" s="13" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="F121" s="13" t="n">
+        <v>399</v>
+      </c>
+      <c r="G121" s="13" t="inlineStr">
+        <is>
+          <t>$0 current bid + BP</t>
+        </is>
+      </c>
+      <c r="H121" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="13" t="inlineStr"/>
+      <c r="J121" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-22 07:30 PM ET</t>
+        </is>
+      </c>
+      <c r="K121" s="13" t="inlineStr">
+        <is>
+          <t>HiBid</t>
+        </is>
+      </c>
+      <c r="L121" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M121" s="13" t="inlineStr"/>
+      <c r="N121" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O121" s="14" t="inlineStr">
+        <is>
+          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Virginia</t>
         </is>
       </c>
-      <c r="B121" s="17" t="inlineStr">
+      <c r="B122" s="17" t="inlineStr">
         <is>
           <t>2 item(s)</t>
         </is>
       </c>
-      <c r="C121" s="18" t="n"/>
-      <c r="D121" s="18" t="n"/>
-      <c r="E121" s="18" t="n"/>
-      <c r="F121" s="18" t="n"/>
-      <c r="G121" s="18" t="n"/>
-      <c r="H121" s="19" t="n">
+      <c r="C122" s="18" t="n"/>
+      <c r="D122" s="18" t="n"/>
+      <c r="E122" s="18" t="n"/>
+      <c r="F122" s="18" t="n"/>
+      <c r="G122" s="18" t="n"/>
+      <c r="H122" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I121" s="18" t="n"/>
-      <c r="J121" s="18" t="n"/>
-      <c r="K121" s="18" t="n"/>
-      <c r="L121" s="18" t="n"/>
-      <c r="M121" s="18" t="n"/>
-      <c r="N121" s="18" t="n"/>
-      <c r="O121" s="18" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="11" t="inlineStr">
+      <c r="I122" s="18" t="n"/>
+      <c r="J122" s="18" t="n"/>
+      <c r="K122" s="18" t="n"/>
+      <c r="L122" s="18" t="n"/>
+      <c r="M122" s="18" t="n"/>
+      <c r="N122" s="18" t="n"/>
+      <c r="O122" s="18" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="11" t="inlineStr">
         <is>
           <t>▸ Midwest  (2)</t>
         </is>
       </c>
-      <c r="B122" s="12" t="n"/>
-      <c r="C122" s="12" t="n"/>
-      <c r="D122" s="12" t="n"/>
-      <c r="E122" s="12" t="n"/>
-      <c r="F122" s="12" t="n"/>
-      <c r="G122" s="12" t="n"/>
-      <c r="H122" s="12" t="n"/>
-      <c r="I122" s="12" t="n"/>
-      <c r="J122" s="12" t="n"/>
-      <c r="K122" s="12" t="n"/>
-      <c r="L122" s="12" t="n"/>
-      <c r="M122" s="12" t="n"/>
-      <c r="N122" s="12" t="n"/>
-      <c r="O122" s="12" t="n"/>
-    </row>
-    <row r="123" outlineLevel="1">
-      <c r="A123" s="13" t="inlineStr">
-        <is>
-          <t>Midwest</t>
-        </is>
-      </c>
-      <c r="B123" s="14" t="inlineStr">
-        <is>
-          <t>Wolf Oven Six Burner Combo</t>
-        </is>
-      </c>
-      <c r="C123" s="13" t="inlineStr">
-        <is>
-          <t>range/oven/rangetop</t>
-        </is>
-      </c>
-      <c r="D123" s="13" t="inlineStr">
-        <is>
-          <t>Anderson</t>
-        </is>
-      </c>
-      <c r="E123" s="13" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="F123" s="13" t="n">
-        <v>785</v>
-      </c>
-      <c r="G123" s="13" t="inlineStr">
-        <is>
-          <t>$3 current bid + BP</t>
-        </is>
-      </c>
-      <c r="H123" s="15" t="n">
-        <v>3</v>
-      </c>
-      <c r="I123" s="13" t="inlineStr"/>
-      <c r="J123" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-18 08:54 PM ET</t>
-        </is>
-      </c>
-      <c r="K123" s="13" t="inlineStr">
-        <is>
-          <t>HiBid</t>
-        </is>
-      </c>
-      <c r="L123" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M123" s="13" t="inlineStr"/>
-      <c r="N123" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O123" s="14" t="inlineStr">
-        <is>
-          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf)</t>
-        </is>
-      </c>
+      <c r="B123" s="12" t="n"/>
+      <c r="C123" s="12" t="n"/>
+      <c r="D123" s="12" t="n"/>
+      <c r="E123" s="12" t="n"/>
+      <c r="F123" s="12" t="n"/>
+      <c r="G123" s="12" t="n"/>
+      <c r="H123" s="12" t="n"/>
+      <c r="I123" s="12" t="n"/>
+      <c r="J123" s="12" t="n"/>
+      <c r="K123" s="12" t="n"/>
+      <c r="L123" s="12" t="n"/>
+      <c r="M123" s="12" t="n"/>
+      <c r="N123" s="12" t="n"/>
+      <c r="O123" s="12" t="n"/>
     </row>
     <row r="124" outlineLevel="1">
       <c r="A124" s="13" t="inlineStr">
@@ -12417,17 +12421,17 @@
       </c>
       <c r="B124" s="14" t="inlineStr">
         <is>
-          <t>Wolf Gourmet High-Performance Blender</t>
+          <t>Wolf Oven Six Burner Combo</t>
         </is>
       </c>
       <c r="C124" s="13" t="inlineStr">
         <is>
-          <t>countertop</t>
+          <t>range/oven/rangetop</t>
         </is>
       </c>
       <c r="D124" s="13" t="inlineStr">
         <is>
-          <t>New Carlisle</t>
+          <t>Anderson</t>
         </is>
       </c>
       <c r="E124" s="13" t="inlineStr">
@@ -12436,162 +12440,160 @@
         </is>
       </c>
       <c r="F124" s="13" t="n">
-        <v>807</v>
+        <v>785</v>
       </c>
       <c r="G124" s="13" t="inlineStr">
         <is>
-          <t>$0 current bid + BP</t>
+          <t>$3 current bid + BP</t>
         </is>
       </c>
       <c r="H124" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I124" s="13" t="inlineStr"/>
       <c r="J124" s="13" t="inlineStr">
         <is>
+          <t>2026-10-18 08:54 PM ET</t>
+        </is>
+      </c>
+      <c r="K124" s="13" t="inlineStr">
+        <is>
+          <t>HiBid</t>
+        </is>
+      </c>
+      <c r="L124" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M124" s="13" t="inlineStr"/>
+      <c r="N124" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O124" s="14" t="inlineStr">
+        <is>
+          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" outlineLevel="1">
+      <c r="A125" s="13" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="B125" s="14" t="inlineStr">
+        <is>
+          <t>Wolf Gourmet High-Performance Blender</t>
+        </is>
+      </c>
+      <c r="C125" s="13" t="inlineStr">
+        <is>
+          <t>countertop</t>
+        </is>
+      </c>
+      <c r="D125" s="13" t="inlineStr">
+        <is>
+          <t>New Carlisle</t>
+        </is>
+      </c>
+      <c r="E125" s="13" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F125" s="13" t="n">
+        <v>807</v>
+      </c>
+      <c r="G125" s="13" t="inlineStr">
+        <is>
+          <t>$0 current bid + BP</t>
+        </is>
+      </c>
+      <c r="H125" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="13" t="inlineStr"/>
+      <c r="J125" s="13" t="inlineStr">
+        <is>
           <t>2026-10-24 08:19 PM ET</t>
         </is>
       </c>
-      <c r="K124" s="13" t="inlineStr">
+      <c r="K125" s="13" t="inlineStr">
         <is>
           <t>HiBid</t>
         </is>
       </c>
-      <c r="L124" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M124" s="21" t="inlineStr">
+      <c r="L125" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M125" s="21" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
       </c>
-      <c r="N124" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O124" s="14" t="inlineStr">
+      <c r="N125" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O125" s="14" t="inlineStr">
         <is>
           <t>Condition: used. FLIP?: Wolf Gourmet blender, bid $0; resale $150-250 but ~800 mi away</t>
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="17" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Midwest</t>
         </is>
       </c>
-      <c r="B125" s="17" t="inlineStr">
+      <c r="B126" s="17" t="inlineStr">
         <is>
           <t>2 item(s)</t>
         </is>
       </c>
-      <c r="C125" s="18" t="n"/>
-      <c r="D125" s="18" t="n"/>
-      <c r="E125" s="18" t="n"/>
-      <c r="F125" s="18" t="n"/>
-      <c r="G125" s="18" t="n"/>
-      <c r="H125" s="19" t="n">
+      <c r="C126" s="18" t="n"/>
+      <c r="D126" s="18" t="n"/>
+      <c r="E126" s="18" t="n"/>
+      <c r="F126" s="18" t="n"/>
+      <c r="G126" s="18" t="n"/>
+      <c r="H126" s="19" t="n">
         <v>3</v>
       </c>
-      <c r="I125" s="18" t="n"/>
-      <c r="J125" s="18" t="n"/>
-      <c r="K125" s="18" t="n"/>
-      <c r="L125" s="18" t="n"/>
-      <c r="M125" s="18" t="n"/>
-      <c r="N125" s="18" t="n"/>
-      <c r="O125" s="18" t="n"/>
-    </row>
-    <row r="126">
-      <c r="A126" s="11" t="inlineStr">
-        <is>
-          <t>▸ Unknown location  (61)</t>
-        </is>
-      </c>
-      <c r="B126" s="12" t="n"/>
-      <c r="C126" s="12" t="n"/>
-      <c r="D126" s="12" t="n"/>
-      <c r="E126" s="12" t="n"/>
-      <c r="F126" s="12" t="n"/>
-      <c r="G126" s="12" t="n"/>
-      <c r="H126" s="12" t="n"/>
-      <c r="I126" s="12" t="n"/>
-      <c r="J126" s="12" t="n"/>
-      <c r="K126" s="12" t="n"/>
-      <c r="L126" s="12" t="n"/>
-      <c r="M126" s="12" t="n"/>
-      <c r="N126" s="12" t="n"/>
-      <c r="O126" s="12" t="n"/>
-    </row>
-    <row r="127" outlineLevel="1">
-      <c r="A127" s="13" t="inlineStr">
-        <is>
-          <t>Unknown location</t>
-        </is>
-      </c>
-      <c r="B127" s="14" t="inlineStr">
-        <is>
-          <t>Wolf 36” Single Electric Wall Built-In Oven SO36U/S - Tested Work</t>
-        </is>
-      </c>
-      <c r="C127" s="13" t="inlineStr">
-        <is>
-          <t>range/oven/rangetop</t>
-        </is>
-      </c>
-      <c r="D127" s="13" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="E127" s="13" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F127" s="13" t="n"/>
-      <c r="G127" s="13" t="inlineStr">
-        <is>
-          <t>$99</t>
-        </is>
-      </c>
-      <c r="H127" s="15" t="n">
-        <v>99</v>
-      </c>
-      <c r="I127" s="13" t="inlineStr"/>
-      <c r="J127" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-18 02:19 PM ET</t>
-        </is>
-      </c>
-      <c r="K127" s="13" t="inlineStr">
-        <is>
-          <t>eBay (pickup only, over 60 mi)</t>
-        </is>
-      </c>
-      <c r="L127" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M127" s="21" t="inlineStr">
-        <is>
-          <t>FLIP</t>
-        </is>
-      </c>
-      <c r="N127" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O127" s="14" t="inlineStr">
-        <is>
-          <t>Condition: Pre-Owned. FLIP: SO36U/S tested, auction $99/0 bids, pickup only; rough resale $600-1k (eBay card shows no city; pickup distance in source.) Ends Oct 18 ~2:19 PM per eBay card (time zone uncertain; could be earlier).</t>
-        </is>
-      </c>
+      <c r="I126" s="18" t="n"/>
+      <c r="J126" s="18" t="n"/>
+      <c r="K126" s="18" t="n"/>
+      <c r="L126" s="18" t="n"/>
+      <c r="M126" s="18" t="n"/>
+      <c r="N126" s="18" t="n"/>
+      <c r="O126" s="18" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="11" t="inlineStr">
+        <is>
+          <t>▸ Unknown location  (60)</t>
+        </is>
+      </c>
+      <c r="B127" s="12" t="n"/>
+      <c r="C127" s="12" t="n"/>
+      <c r="D127" s="12" t="n"/>
+      <c r="E127" s="12" t="n"/>
+      <c r="F127" s="12" t="n"/>
+      <c r="G127" s="12" t="n"/>
+      <c r="H127" s="12" t="n"/>
+      <c r="I127" s="12" t="n"/>
+      <c r="J127" s="12" t="n"/>
+      <c r="K127" s="12" t="n"/>
+      <c r="L127" s="12" t="n"/>
+      <c r="M127" s="12" t="n"/>
+      <c r="N127" s="12" t="n"/>
+      <c r="O127" s="12" t="n"/>
     </row>
     <row r="128" outlineLevel="1">
       <c r="A128" s="13" t="inlineStr">
@@ -16169,7 +16171,7 @@
       </c>
       <c r="B188" s="17" t="inlineStr">
         <is>
-          <t>61 item(s)</t>
+          <t>60 item(s)</t>
         </is>
       </c>
       <c r="C188" s="18" t="n"/>
@@ -16178,7 +16180,7 @@
       <c r="F188" s="18" t="n"/>
       <c r="G188" s="18" t="n"/>
       <c r="H188" s="19" t="n">
-        <v>234980.91</v>
+        <v>234881.91</v>
       </c>
       <c r="I188" s="18" t="n"/>
       <c r="J188" s="18" t="n"/>
@@ -16287,13 +16289,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N108" r:id="rId94"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N109" r:id="rId95"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N110" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N113" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N116" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N119" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N111" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N114" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N117" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N120" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N123" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N121" r:id="rId101"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N124" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N127" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N125" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N128" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N129" r:id="rId105"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N130" r:id="rId106"/>
@@ -18610,7 +18612,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O69"/>
+  <dimension ref="A1:O70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -19851,7 +19853,7 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>▸ CT / Hudson Valley  (4)</t>
+          <t>▸ CT / Hudson Valley  (5)</t>
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
@@ -20003,17 +20005,17 @@
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>Café/bakery liquidation – Traulsen, Vulcan ovens, mixers, Hobart slicer (~74 lots)</t>
+          <t>The Outlaw Grill Steakhouse – used restaurant equipment auction (PCI Auctions CT, e.g. Vulcan EV60 Endurance 60" range)</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>restaurant auction</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>Greenwich</t>
+          <t>Stamford</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -20022,23 +20024,27 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>Live auction + webcast</t>
+          <t>Online auction, current bids</t>
         </is>
       </c>
       <c r="H28" s="15" t="n"/>
-      <c r="I28" s="13" t="inlineStr"/>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="J28" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 06:00 PM ET</t>
+          <t>2026-10-21 08:30 PM ET</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>Best Buy Auctioneers / AuctionGuide</t>
+          <t>PCI Auctions</t>
         </is>
       </c>
       <c r="L28" s="13" t="inlineStr">
@@ -20054,7 +20060,7 @@
       </c>
       <c r="O28" s="14" t="inlineStr">
         <is>
-          <t>Oct 21; start time not captured (placeholder 6 PM).</t>
+          <t>Ends Wed Oct 21 8:30 PM EDT. PCI warehouse, 36 Ludlow St, Stamford CT. Page lists preview Oct 28 and removal Thu Oct 29 11-3 (after close). Shipping/delivery available; payment due on pickup day. Items still being added.</t>
         </is>
       </c>
     </row>
@@ -20066,42 +20072,42 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>BJ's Wholesale closeout – racking, forklifts, Hobart</t>
+          <t>Café/bakery liquidation – Traulsen, Vulcan ovens, mixers, Hobart slicer (~74 lots)</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>Rotterdam</t>
+          <t>Greenwich</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Live auction + webcast</t>
         </is>
       </c>
       <c r="H29" s="15" t="n"/>
       <c r="I29" s="13" t="inlineStr"/>
       <c r="J29" s="13" t="inlineStr">
         <is>
-          <t>2026-11-10 10:00 AM ET</t>
+          <t>2026-10-21 06:00 PM ET</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
+          <t>Best Buy Auctioneers / AuctionGuide</t>
         </is>
       </c>
       <c r="L29" s="13" t="inlineStr">
@@ -20117,124 +20123,120 @@
       </c>
       <c r="O29" s="14" t="inlineStr">
         <is>
+          <t>Oct 21; start time not captured (placeholder 6 PM).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" outlineLevel="1">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>CT / Hudson Valley</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>BJ's Wholesale closeout – racking, forklifts, Hobart</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>store closing</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>Rotterdam</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>168</v>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>Online auction</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="n"/>
+      <c r="I30" s="13" t="inlineStr"/>
+      <c r="J30" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-10 10:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L30" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M30" s="13" t="inlineStr"/>
+      <c r="N30" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O30" s="14" t="inlineStr">
+        <is>
           <t>Closes from Nov 10 10 AM.</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="17" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
         <is>
           <t>Subtotal — CT / Hudson Valley</t>
         </is>
       </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>4 item(s)</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="n"/>
-      <c r="D30" s="18" t="n"/>
-      <c r="E30" s="18" t="n"/>
-      <c r="F30" s="18" t="n"/>
-      <c r="G30" s="18" t="n"/>
-      <c r="H30" s="19" t="n">
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>5 item(s)</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="18" t="n"/>
+      <c r="E31" s="18" t="n"/>
+      <c r="F31" s="18" t="n"/>
+      <c r="G31" s="18" t="n"/>
+      <c r="H31" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="18" t="n"/>
-      <c r="J30" s="18" t="n"/>
-      <c r="K30" s="18" t="n"/>
-      <c r="L30" s="18" t="n"/>
-      <c r="M30" s="18" t="n"/>
-      <c r="N30" s="18" t="n"/>
-      <c r="O30" s="18" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="I31" s="18" t="n"/>
+      <c r="J31" s="18" t="n"/>
+      <c r="K31" s="18" t="n"/>
+      <c r="L31" s="18" t="n"/>
+      <c r="M31" s="18" t="n"/>
+      <c r="N31" s="18" t="n"/>
+      <c r="O31" s="18" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>▸ NYC / Long Island / NJ  (16)</t>
         </is>
       </c>
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="12" t="n"/>
-      <c r="E31" s="12" t="n"/>
-      <c r="F31" s="12" t="n"/>
-      <c r="G31" s="12" t="n"/>
-      <c r="H31" s="12" t="n"/>
-      <c r="I31" s="12" t="n"/>
-      <c r="J31" s="12" t="n"/>
-      <c r="K31" s="12" t="n"/>
-      <c r="L31" s="12" t="n"/>
-      <c r="M31" s="12" t="n"/>
-      <c r="N31" s="12" t="n"/>
-      <c r="O31" s="12" t="n"/>
-    </row>
-    <row r="32" outlineLevel="1">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>NYC / Long Island / NJ</t>
-        </is>
-      </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>Japanese BBQ &amp; bar – ~47 lots: Turbo Air, Hoshizaki ice machine, Pitco, Beverage-Air</t>
-        </is>
-      </c>
-      <c r="C32" s="13" t="inlineStr">
-        <is>
-          <t>restaurant closing</t>
-        </is>
-      </c>
-      <c r="D32" s="13" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>191</v>
-      </c>
-      <c r="G32" s="13" t="inlineStr">
-        <is>
-          <t>Live + webcast, 18% BP + 3%</t>
-        </is>
-      </c>
-      <c r="H32" s="15" t="n"/>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="J32" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 04:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K32" s="13" t="inlineStr">
-        <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
-        </is>
-      </c>
-      <c r="L32" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M32" s="13" t="inlineStr"/>
-      <c r="N32" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O32" s="14" t="inlineStr">
-        <is>
-          <t>Wed Oct 21 4 PM. NYC 10013.</t>
-        </is>
-      </c>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+      <c r="N32" s="12" t="n"/>
+      <c r="O32" s="12" t="n"/>
     </row>
     <row r="33" outlineLevel="1">
       <c r="A33" s="13" t="inlineStr">
@@ -20244,26 +20246,26 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>Corporate caterer – Alto-Shaam, new boxed Avantco rice cookers &amp; Cadco oven, Perlick, MerryChef</t>
+          <t>Japanese BBQ &amp; bar – ~47 lots: Turbo Air, Hoshizaki ice machine, Pitco, Beverage-Air</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>restaurant closing</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>Jersey City</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
@@ -20273,12 +20275,12 @@
       <c r="H33" s="15" t="n"/>
       <c r="I33" s="13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J33" s="13" t="inlineStr">
         <is>
-          <t>2026-10-22 02:00 PM ET</t>
+          <t>2026-10-21 04:00 PM ET</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
@@ -20286,9 +20288,9 @@
           <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
-      <c r="L33" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="L33" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M33" s="13" t="inlineStr"/>
@@ -20299,7 +20301,7 @@
       </c>
       <c r="O33" s="14" t="inlineStr">
         <is>
-          <t>Thu Oct 22 2 PM.</t>
+          <t>Wed Oct 21 4 PM. NYC 10013.</t>
         </is>
       </c>
     </row>
@@ -20311,17 +20313,17 @@
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>Tools / plumbing / MRO supply inventory – Hilti/DeWalt/Milwaukee, fittings, heat pumps</t>
+          <t>Corporate caterer – Alto-Shaam, new boxed Avantco rice cookers &amp; Cadco oven, Perlick, MerryChef</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>Riverdale</t>
+          <t>Jersey City</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
@@ -20330,23 +20332,27 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H34" s="15" t="n"/>
-      <c r="I34" s="13" t="inlineStr"/>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="J34" s="13" t="inlineStr">
         <is>
-          <t>2026-10-30 11:00 AM ET</t>
+          <t>2026-10-22 02:00 PM ET</t>
         </is>
       </c>
       <c r="K34" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
       <c r="L34" s="13" t="inlineStr">
@@ -20362,7 +20368,7 @@
       </c>
       <c r="O34" s="14" t="inlineStr">
         <is>
-          <t>Bulk resale inventory.</t>
+          <t>Thu Oct 22 2 PM.</t>
         </is>
       </c>
     </row>
@@ -20374,12 +20380,12 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>Ice cream + cookie franchise equipment – Taylor soft-serve, Atosa, Blodgett</t>
+          <t>Tools / plumbing / MRO supply inventory – Hilti/DeWalt/Milwaukee, fittings, heat pumps</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
@@ -20404,7 +20410,7 @@
       <c r="I35" s="13" t="inlineStr"/>
       <c r="J35" s="13" t="inlineStr">
         <is>
-          <t>2026-11-05 11:00 AM ET</t>
+          <t>2026-10-30 11:00 AM ET</t>
         </is>
       </c>
       <c r="K35" s="13" t="inlineStr">
@@ -20425,7 +20431,7 @@
       </c>
       <c r="O35" s="14" t="inlineStr">
         <is>
-          <t>Resellable units.</t>
+          <t>Bulk resale inventory.</t>
         </is>
       </c>
     </row>
@@ -20437,51 +20443,47 @@
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>Like-new restaurant – steam tables, Coldline, Cleveland cook-and-hold, fryers, True freezers</t>
+          <t>Ice cream + cookie franchise equipment – Taylor soft-serve, Atosa, Blodgett</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>Staten Island</t>
+          <t>Riverdale</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H36" s="15" t="n"/>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+      <c r="I36" s="13" t="inlineStr"/>
       <c r="J36" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00 PM ET</t>
+          <t>2026-11-05 11:00 AM ET</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
-        </is>
-      </c>
-      <c r="L36" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>A.J. Willner</t>
+        </is>
+      </c>
+      <c r="L36" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M36" s="13" t="inlineStr"/>
@@ -20492,7 +20494,7 @@
       </c>
       <c r="O36" s="14" t="inlineStr">
         <is>
-          <t>"Short notice" auction Mon Oct 19 1 PM.</t>
+          <t>Resellable units.</t>
         </is>
       </c>
     </row>
@@ -20504,7 +20506,7 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>Major food-service caterer – new-in-box True reach-ins, Beverage-Air, TurboChef, Resfab ventless fryer</t>
+          <t>Like-new restaurant – steam tables, Coldline, Cleveland cook-and-hold, fryers, True freezers</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
@@ -20514,16 +20516,16 @@
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>Parsippany</t>
+          <t>Staten Island</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
@@ -20533,12 +20535,12 @@
       <c r="H37" s="15" t="n"/>
       <c r="I37" s="13" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="J37" s="13" t="inlineStr">
         <is>
-          <t>2026-11-03 02:00 PM ET</t>
+          <t>2026-10-19 01:00 PM ET</t>
         </is>
       </c>
       <c r="K37" s="13" t="inlineStr">
@@ -20546,9 +20548,9 @@
           <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
-      <c r="L37" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="L37" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M37" s="13" t="inlineStr"/>
@@ -20559,7 +20561,7 @@
       </c>
       <c r="O37" s="14" t="inlineStr">
         <is>
-          <t>Tue Nov 3 2 PM, checkout Nov 4.</t>
+          <t>"Short notice" auction Mon Oct 19 1 PM.</t>
         </is>
       </c>
     </row>
@@ -20571,17 +20573,17 @@
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>Serpico's Pizzeria (lost lease) – Bari ovens, walk-in, Hobart 60qt, Vulcan range</t>
+          <t>Major food-service caterer – new-in-box True reach-ins, Beverage-Air, TurboChef, Resfab ventless fryer</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>Allenhurst</t>
+          <t>Parsippany</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
@@ -20590,28 +20592,32 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>No-reserve online auction</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H38" s="15" t="n"/>
-      <c r="I38" s="13" t="inlineStr"/>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
       <c r="J38" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 11:00 AM ET</t>
+          <t>2026-11-03 02:00 PM ET</t>
         </is>
       </c>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>Peter Costanzo / EstateSales.net</t>
-        </is>
-      </c>
-      <c r="L38" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L38" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M38" s="13" t="inlineStr"/>
@@ -20622,7 +20628,7 @@
       </c>
       <c r="O38" s="14" t="inlineStr">
         <is>
-          <t>Absolute / no reserve.</t>
+          <t>Tue Nov 3 2 PM, checkout Nov 4.</t>
         </is>
       </c>
     </row>
@@ -20634,17 +20640,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>Altitude Trampoline Park liquidation – partial: Atosa, TurboChef, stainless</t>
+          <t>Serpico's Pizzeria (lost lease) – Bari ovens, walk-in, Hobart 60qt, Vulcan range</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>facility contents</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>Iselin</t>
+          <t>Allenhurst</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -20653,11 +20659,11 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>No-reserve online auction</t>
         </is>
       </c>
       <c r="H39" s="15" t="n"/>
@@ -20669,7 +20675,7 @@
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>Peter Costanzo / EstateSales.net</t>
         </is>
       </c>
       <c r="L39" s="20" t="inlineStr">
@@ -20685,7 +20691,7 @@
       </c>
       <c r="O39" s="14" t="inlineStr">
         <is>
-          <t>Some kitchen gear only.</t>
+          <t>Absolute / no reserve.</t>
         </is>
       </c>
     </row>
@@ -20697,17 +20703,17 @@
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>Restaurant / pizzeria (contents not described)</t>
+          <t>Altitude Trampoline Park liquidation – partial: Atosa, TurboChef, stainless</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>facility contents</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>Berkeley Heights</t>
+          <t>Iselin</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -20716,27 +20722,23 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H40" s="15" t="n"/>
-      <c r="I40" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
+      <c r="I40" s="13" t="inlineStr"/>
       <c r="J40" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 02:00 PM ET</t>
+          <t>2026-10-21 11:00 AM ET</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L40" s="20" t="inlineStr">
@@ -20752,7 +20754,7 @@
       </c>
       <c r="O40" s="14" t="inlineStr">
         <is>
-          <t>Tue Oct 20 2 PM. No item description on page.</t>
+          <t>Some kitchen gear only.</t>
         </is>
       </c>
     </row>
@@ -20764,17 +20766,17 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
+          <t>Restaurant / pizzeria (contents not described)</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>lien sale</t>
+          <t>restaurant closing</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>Edison</t>
+          <t>Berkeley Heights</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -20783,24 +20785,32 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t>Online auction, $2K load-out fee</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H41" s="15" t="n"/>
-      <c r="I41" s="13" t="inlineStr"/>
-      <c r="J41" s="13" t="inlineStr"/>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J41" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-20 02:00 PM ET</t>
+        </is>
+      </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
-        </is>
-      </c>
-      <c r="L41" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L41" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M41" s="13" t="inlineStr"/>
@@ -20811,7 +20821,7 @@
       </c>
       <c r="O41" s="14" t="inlineStr">
         <is>
-          <t>&gt;$100K new. Close date not captured.</t>
+          <t>Tue Oct 20 2 PM. No item description on page.</t>
         </is>
       </c>
     </row>
@@ -20823,12 +20833,12 @@
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
+          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>lien sale</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
@@ -20846,23 +20856,15 @@
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>Live + HiBid webcast, 18% BP + 3% card</t>
+          <t>Online auction, $2K load-out fee</t>
         </is>
       </c>
       <c r="H42" s="15" t="n"/>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="J42" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-25 01:00 PM ET</t>
-        </is>
-      </c>
+      <c r="I42" s="13" t="inlineStr"/>
+      <c r="J42" s="13" t="inlineStr"/>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L42" s="13" t="inlineStr">
@@ -20870,11 +20872,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M42" s="21" t="inlineStr">
-        <is>
-          <t>FLIP</t>
-        </is>
-      </c>
+      <c r="M42" s="13" t="inlineStr"/>
       <c r="N42" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -20882,7 +20880,7 @@
       </c>
       <c r="O42" s="14" t="inlineStr">
         <is>
-          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
+          <t>&gt;$100K new. Close date not captured.</t>
         </is>
       </c>
     </row>
@@ -20894,17 +20892,17 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
+          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>East Brunswick</t>
+          <t>Edison</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -20913,23 +20911,27 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Live + HiBid webcast, 18% BP + 3% card</t>
         </is>
       </c>
       <c r="H43" s="15" t="n"/>
-      <c r="I43" s="13" t="inlineStr"/>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="J43" s="13" t="inlineStr">
         <is>
-          <t>2026-11-03 11:00 AM ET</t>
+          <t>2026-10-25 01:00 PM ET</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
       <c r="L43" s="13" t="inlineStr">
@@ -20937,7 +20939,11 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M43" s="13" t="inlineStr"/>
+      <c r="M43" s="21" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
       <c r="N43" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -20945,7 +20951,7 @@
       </c>
       <c r="O43" s="14" t="inlineStr">
         <is>
-          <t>Store inventory.</t>
+          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
         </is>
       </c>
     </row>
@@ -20957,17 +20963,17 @@
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>High-end deli (contents not described)</t>
+          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>Manalapan Township</t>
+          <t>East Brunswick</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -20976,32 +20982,28 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H44" s="15" t="n"/>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+      <c r="I44" s="13" t="inlineStr"/>
       <c r="J44" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 04:00 PM ET</t>
+          <t>2026-11-03 11:00 AM ET</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
-        </is>
-      </c>
-      <c r="L44" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>A.J. Willner</t>
+        </is>
+      </c>
+      <c r="L44" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M44" s="13" t="inlineStr"/>
@@ -21012,7 +21014,7 @@
       </c>
       <c r="O44" s="14" t="inlineStr">
         <is>
-          <t>Mon Oct 19 4 PM. No item description on page.</t>
+          <t>Store inventory.</t>
         </is>
       </c>
     </row>
@@ -21024,17 +21026,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
+          <t>High-end deli (contents not described)</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>showroom closing</t>
+          <t>restaurant closing</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>Lawrenceville</t>
+          <t>Manalapan Township</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -21043,28 +21045,32 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>Online auction, 18% BP</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H45" s="15" t="n"/>
-      <c r="I45" s="13" t="inlineStr"/>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="J45" s="13" t="inlineStr">
         <is>
-          <t>2026-10-27 09:00 AM ET</t>
+          <t>2026-10-19 04:00 PM ET</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L45" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L45" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M45" s="13" t="inlineStr"/>
@@ -21075,7 +21081,7 @@
       </c>
       <c r="O45" s="14" t="inlineStr">
         <is>
-          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
+          <t>Mon Oct 19 4 PM. No item description on page.</t>
         </is>
       </c>
     </row>
@@ -21087,17 +21093,17 @@
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>Milwaukee / Walmart / hardware store mega auction pt 3</t>
+          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>showroom closing</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>Mount Holly</t>
+          <t>Lawrenceville</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -21106,28 +21112,28 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>HiBid online auction</t>
+          <t>Online auction, 18% BP</t>
         </is>
       </c>
       <c r="H46" s="15" t="n"/>
       <c r="I46" s="13" t="inlineStr"/>
       <c r="J46" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 06:00 PM ET</t>
+          <t>2026-10-27 09:00 AM ET</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>HiBid</t>
-        </is>
-      </c>
-      <c r="L46" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L46" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M46" s="13" t="inlineStr"/>
@@ -21138,7 +21144,7 @@
       </c>
       <c r="O46" s="14" t="inlineStr">
         <is>
-          <t>Close Oct 18 or 19 6 PM (later used).</t>
+          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
         </is>
       </c>
     </row>
@@ -21150,17 +21156,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
+          <t>Milwaukee / Walmart / hardware store mega auction pt 3</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>showroom closing</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>Cherry Hill</t>
+          <t>Mount Holly</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -21169,28 +21175,28 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
-          <t>Online auction, openers ~$0.50</t>
+          <t>HiBid online auction</t>
         </is>
       </c>
       <c r="H47" s="15" t="n"/>
       <c r="I47" s="13" t="inlineStr"/>
       <c r="J47" s="13" t="inlineStr">
         <is>
-          <t>2026-11-02 11:00 AM ET</t>
+          <t>2026-10-19 06:00 PM ET</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L47" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>HiBid</t>
+        </is>
+      </c>
+      <c r="L47" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M47" s="13" t="inlineStr"/>
@@ -21201,231 +21207,231 @@
       </c>
       <c r="O47" s="14" t="inlineStr">
         <is>
+          <t>Close Oct 18 or 19 6 PM (later used).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" outlineLevel="1">
+      <c r="A48" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B48" s="14" t="inlineStr">
+        <is>
+          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
+        </is>
+      </c>
+      <c r="C48" s="13" t="inlineStr">
+        <is>
+          <t>showroom closing</t>
+        </is>
+      </c>
+      <c r="D48" s="13" t="inlineStr">
+        <is>
+          <t>Cherry Hill</t>
+        </is>
+      </c>
+      <c r="E48" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F48" s="13" t="n">
+        <v>266</v>
+      </c>
+      <c r="G48" s="13" t="inlineStr">
+        <is>
+          <t>Online auction, openers ~$0.50</t>
+        </is>
+      </c>
+      <c r="H48" s="15" t="n"/>
+      <c r="I48" s="13" t="inlineStr"/>
+      <c r="J48" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-02 11:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K48" s="13" t="inlineStr">
+        <is>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L48" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M48" s="13" t="inlineStr"/>
+      <c r="N48" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O48" s="14" t="inlineStr">
+        <is>
           <t>Lots close from Nov 2 11 AM.</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="17" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="17" t="inlineStr">
         <is>
           <t>Subtotal — NYC / Long Island / NJ</t>
         </is>
       </c>
-      <c r="B48" s="17" t="inlineStr">
+      <c r="B49" s="17" t="inlineStr">
         <is>
           <t>16 item(s)</t>
         </is>
       </c>
-      <c r="C48" s="18" t="n"/>
-      <c r="D48" s="18" t="n"/>
-      <c r="E48" s="18" t="n"/>
-      <c r="F48" s="18" t="n"/>
-      <c r="G48" s="18" t="n"/>
-      <c r="H48" s="19" t="n">
+      <c r="C49" s="18" t="n"/>
+      <c r="D49" s="18" t="n"/>
+      <c r="E49" s="18" t="n"/>
+      <c r="F49" s="18" t="n"/>
+      <c r="G49" s="18" t="n"/>
+      <c r="H49" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I48" s="18" t="n"/>
-      <c r="J48" s="18" t="n"/>
-      <c r="K48" s="18" t="n"/>
-      <c r="L48" s="18" t="n"/>
-      <c r="M48" s="18" t="n"/>
-      <c r="N48" s="18" t="n"/>
-      <c r="O48" s="18" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="11" t="inlineStr">
+      <c r="I49" s="18" t="n"/>
+      <c r="J49" s="18" t="n"/>
+      <c r="K49" s="18" t="n"/>
+      <c r="L49" s="18" t="n"/>
+      <c r="M49" s="18" t="n"/>
+      <c r="N49" s="18" t="n"/>
+      <c r="O49" s="18" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
         <is>
           <t>▸ Eastern PA / Mid-Atlantic  (1)</t>
         </is>
       </c>
-      <c r="B49" s="12" t="n"/>
-      <c r="C49" s="12" t="n"/>
-      <c r="D49" s="12" t="n"/>
-      <c r="E49" s="12" t="n"/>
-      <c r="F49" s="12" t="n"/>
-      <c r="G49" s="12" t="n"/>
-      <c r="H49" s="12" t="n"/>
-      <c r="I49" s="12" t="n"/>
-      <c r="J49" s="12" t="n"/>
-      <c r="K49" s="12" t="n"/>
-      <c r="L49" s="12" t="n"/>
-      <c r="M49" s="12" t="n"/>
-      <c r="N49" s="12" t="n"/>
-      <c r="O49" s="12" t="n"/>
-    </row>
-    <row r="50" outlineLevel="1">
-      <c r="A50" s="13" t="inlineStr">
+      <c r="B50" s="12" t="n"/>
+      <c r="C50" s="12" t="n"/>
+      <c r="D50" s="12" t="n"/>
+      <c r="E50" s="12" t="n"/>
+      <c r="F50" s="12" t="n"/>
+      <c r="G50" s="12" t="n"/>
+      <c r="H50" s="12" t="n"/>
+      <c r="I50" s="12" t="n"/>
+      <c r="J50" s="12" t="n"/>
+      <c r="K50" s="12" t="n"/>
+      <c r="L50" s="12" t="n"/>
+      <c r="M50" s="12" t="n"/>
+      <c r="N50" s="12" t="n"/>
+      <c r="O50" s="12" t="n"/>
+    </row>
+    <row r="51" outlineLevel="1">
+      <c r="A51" s="13" t="inlineStr">
         <is>
           <t>Eastern PA / Mid-Atlantic</t>
         </is>
       </c>
-      <c r="B50" s="14" t="inlineStr">
+      <c r="B51" s="14" t="inlineStr">
         <is>
           <t>October restaurant consignment – Hobart, Rational, True + NEW scratch-and-dent Migali/Avantco</t>
         </is>
       </c>
-      <c r="C50" s="13" t="inlineStr">
+      <c r="C51" s="13" t="inlineStr">
         <is>
           <t>restaurant</t>
         </is>
       </c>
-      <c r="D50" s="13" t="inlineStr">
+      <c r="D51" s="13" t="inlineStr">
         <is>
           <t>Harrisburg</t>
         </is>
       </c>
-      <c r="E50" s="13" t="inlineStr">
+      <c r="E51" s="13" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="F50" s="13" t="n">
+      <c r="F51" s="13" t="n">
         <v>340</v>
       </c>
-      <c r="G50" s="13" t="inlineStr">
+      <c r="G51" s="13" t="inlineStr">
         <is>
           <t>Online auction, 15% BP, ships $55/pallet</t>
         </is>
       </c>
-      <c r="H50" s="15" t="n"/>
-      <c r="I50" s="13" t="inlineStr"/>
-      <c r="J50" s="13" t="inlineStr">
+      <c r="H51" s="15" t="n"/>
+      <c r="I51" s="13" t="inlineStr"/>
+      <c r="J51" s="13" t="inlineStr">
         <is>
           <t>2026-10-21 11:00 AM ET</t>
         </is>
       </c>
-      <c r="K50" s="13" t="inlineStr">
+      <c r="K51" s="13" t="inlineStr">
         <is>
           <t>Restaurant Auction Co</t>
         </is>
       </c>
-      <c r="L50" s="20" t="inlineStr">
+      <c r="L51" s="20" t="inlineStr">
         <is>
           <t>ENDING SOON</t>
         </is>
       </c>
-      <c r="M50" s="13" t="inlineStr"/>
-      <c r="N50" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O50" s="14" t="inlineStr">
+      <c r="M51" s="13" t="inlineStr"/>
+      <c r="N51" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O51" s="14" t="inlineStr">
         <is>
           <t>Closes Oct 21 10 or 11 AM (later used). Shippable.</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="17" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Eastern PA / Mid-Atlantic</t>
         </is>
       </c>
-      <c r="B51" s="17" t="inlineStr">
+      <c r="B52" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C51" s="18" t="n"/>
-      <c r="D51" s="18" t="n"/>
-      <c r="E51" s="18" t="n"/>
-      <c r="F51" s="18" t="n"/>
-      <c r="G51" s="18" t="n"/>
-      <c r="H51" s="19" t="n">
+      <c r="C52" s="18" t="n"/>
+      <c r="D52" s="18" t="n"/>
+      <c r="E52" s="18" t="n"/>
+      <c r="F52" s="18" t="n"/>
+      <c r="G52" s="18" t="n"/>
+      <c r="H52" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I51" s="18" t="n"/>
-      <c r="J51" s="18" t="n"/>
-      <c r="K51" s="18" t="n"/>
-      <c r="L51" s="18" t="n"/>
-      <c r="M51" s="18" t="n"/>
-      <c r="N51" s="18" t="n"/>
-      <c r="O51" s="18" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
+      <c r="I52" s="18" t="n"/>
+      <c r="J52" s="18" t="n"/>
+      <c r="K52" s="18" t="n"/>
+      <c r="L52" s="18" t="n"/>
+      <c r="M52" s="18" t="n"/>
+      <c r="N52" s="18" t="n"/>
+      <c r="O52" s="18" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="11" t="inlineStr">
         <is>
           <t>▸ Upstate / Western NY  (3)</t>
         </is>
       </c>
-      <c r="B52" s="12" t="n"/>
-      <c r="C52" s="12" t="n"/>
-      <c r="D52" s="12" t="n"/>
-      <c r="E52" s="12" t="n"/>
-      <c r="F52" s="12" t="n"/>
-      <c r="G52" s="12" t="n"/>
-      <c r="H52" s="12" t="n"/>
-      <c r="I52" s="12" t="n"/>
-      <c r="J52" s="12" t="n"/>
-      <c r="K52" s="12" t="n"/>
-      <c r="L52" s="12" t="n"/>
-      <c r="M52" s="12" t="n"/>
-      <c r="N52" s="12" t="n"/>
-      <c r="O52" s="12" t="n"/>
-    </row>
-    <row r="53" outlineLevel="1">
-      <c r="A53" s="13" t="inlineStr">
-        <is>
-          <t>Upstate / Western NY</t>
-        </is>
-      </c>
-      <c r="B53" s="14" t="inlineStr">
-        <is>
-          <t>Former Taco Del Mar – stainless, warmers, walk-in panels</t>
-        </is>
-      </c>
-      <c r="C53" s="13" t="inlineStr">
-        <is>
-          <t>restaurant</t>
-        </is>
-      </c>
-      <c r="D53" s="13" t="inlineStr">
-        <is>
-          <t>Watson</t>
-        </is>
-      </c>
-      <c r="E53" s="13" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="F53" s="13" t="n">
-        <v>260</v>
-      </c>
-      <c r="G53" s="13" t="inlineStr">
-        <is>
-          <t>HiBid online auction</t>
-        </is>
-      </c>
-      <c r="H53" s="15" t="n"/>
-      <c r="I53" s="13" t="inlineStr"/>
-      <c r="J53" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-20 06:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K53" s="13" t="inlineStr">
-        <is>
-          <t>Adirondack Asset / HiBid</t>
-        </is>
-      </c>
-      <c r="L53" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M53" s="13" t="inlineStr"/>
-      <c r="N53" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O53" s="14" t="inlineStr">
-        <is>
-          <t>Small lot.</t>
-        </is>
-      </c>
+      <c r="B53" s="12" t="n"/>
+      <c r="C53" s="12" t="n"/>
+      <c r="D53" s="12" t="n"/>
+      <c r="E53" s="12" t="n"/>
+      <c r="F53" s="12" t="n"/>
+      <c r="G53" s="12" t="n"/>
+      <c r="H53" s="12" t="n"/>
+      <c r="I53" s="12" t="n"/>
+      <c r="J53" s="12" t="n"/>
+      <c r="K53" s="12" t="n"/>
+      <c r="L53" s="12" t="n"/>
+      <c r="M53" s="12" t="n"/>
+      <c r="N53" s="12" t="n"/>
+      <c r="O53" s="12" t="n"/>
     </row>
     <row r="54" outlineLevel="1">
       <c r="A54" s="13" t="inlineStr">
@@ -21435,7 +21441,7 @@
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>Closed restaurant – coolers, fridges, prep tables</t>
+          <t>Former Taco Del Mar – stainless, warmers, walk-in panels</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
@@ -21445,7 +21451,7 @@
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>Palmyra</t>
+          <t>Watson</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -21454,23 +21460,23 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>333</v>
+        <v>260</v>
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>HiBid, 15% BP</t>
+          <t>HiBid online auction</t>
         </is>
       </c>
       <c r="H54" s="15" t="n"/>
       <c r="I54" s="13" t="inlineStr"/>
       <c r="J54" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 07:00 PM ET</t>
+          <t>2026-10-20 06:00 PM ET</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>Reynolds Auction Co / HiBid</t>
+          <t>Adirondack Asset / HiBid</t>
         </is>
       </c>
       <c r="L54" s="20" t="inlineStr">
@@ -21486,7 +21492,7 @@
       </c>
       <c r="O54" s="14" t="inlineStr">
         <is>
-          <t>No new out-of-state bidders. Small.</t>
+          <t>Small lot.</t>
         </is>
       </c>
     </row>
@@ -21498,7 +21504,7 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Restaurant &amp; fitness equipment</t>
+          <t>Closed restaurant – coolers, fridges, prep tables</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
@@ -21508,7 +21514,7 @@
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>Williamsville</t>
+          <t>Palmyra</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -21517,28 +21523,28 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>408</v>
+        <v>333</v>
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>HiBid, 15% BP</t>
         </is>
       </c>
       <c r="H55" s="15" t="n"/>
       <c r="I55" s="13" t="inlineStr"/>
       <c r="J55" s="13" t="inlineStr">
         <is>
-          <t>2026-10-26 07:30 PM ET</t>
+          <t>2026-10-19 07:00 PM ET</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>Cash Auctions</t>
-        </is>
-      </c>
-      <c r="L55" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Reynolds Auction Co / HiBid</t>
+        </is>
+      </c>
+      <c r="L55" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M55" s="13" t="inlineStr"/>
@@ -21549,231 +21555,231 @@
       </c>
       <c r="O55" s="14" t="inlineStr">
         <is>
+          <t>No new out-of-state bidders. Small.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" outlineLevel="1">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>Upstate / Western NY</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant &amp; fitness equipment</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="inlineStr">
+        <is>
+          <t>Williamsville</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F56" s="13" t="n">
+        <v>408</v>
+      </c>
+      <c r="G56" s="13" t="inlineStr">
+        <is>
+          <t>Online auction</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="n"/>
+      <c r="I56" s="13" t="inlineStr"/>
+      <c r="J56" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-26 07:30 PM ET</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>Cash Auctions</t>
+        </is>
+      </c>
+      <c r="L56" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M56" s="13" t="inlineStr"/>
+      <c r="N56" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O56" s="14" t="inlineStr">
+        <is>
           <t>Lots not reviewed.</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="17" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Upstate / Western NY</t>
         </is>
       </c>
-      <c r="B56" s="17" t="inlineStr">
+      <c r="B57" s="17" t="inlineStr">
         <is>
           <t>3 item(s)</t>
         </is>
       </c>
-      <c r="C56" s="18" t="n"/>
-      <c r="D56" s="18" t="n"/>
-      <c r="E56" s="18" t="n"/>
-      <c r="F56" s="18" t="n"/>
-      <c r="G56" s="18" t="n"/>
-      <c r="H56" s="19" t="n">
+      <c r="C57" s="18" t="n"/>
+      <c r="D57" s="18" t="n"/>
+      <c r="E57" s="18" t="n"/>
+      <c r="F57" s="18" t="n"/>
+      <c r="G57" s="18" t="n"/>
+      <c r="H57" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I56" s="18" t="n"/>
-      <c r="J56" s="18" t="n"/>
-      <c r="K56" s="18" t="n"/>
-      <c r="L56" s="18" t="n"/>
-      <c r="M56" s="18" t="n"/>
-      <c r="N56" s="18" t="n"/>
-      <c r="O56" s="18" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr">
+      <c r="I57" s="18" t="n"/>
+      <c r="J57" s="18" t="n"/>
+      <c r="K57" s="18" t="n"/>
+      <c r="L57" s="18" t="n"/>
+      <c r="M57" s="18" t="n"/>
+      <c r="N57" s="18" t="n"/>
+      <c r="O57" s="18" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>▸ Virginia  (1)</t>
         </is>
       </c>
-      <c r="B57" s="12" t="n"/>
-      <c r="C57" s="12" t="n"/>
-      <c r="D57" s="12" t="n"/>
-      <c r="E57" s="12" t="n"/>
-      <c r="F57" s="12" t="n"/>
-      <c r="G57" s="12" t="n"/>
-      <c r="H57" s="12" t="n"/>
-      <c r="I57" s="12" t="n"/>
-      <c r="J57" s="12" t="n"/>
-      <c r="K57" s="12" t="n"/>
-      <c r="L57" s="12" t="n"/>
-      <c r="M57" s="12" t="n"/>
-      <c r="N57" s="12" t="n"/>
-      <c r="O57" s="12" t="n"/>
-    </row>
-    <row r="58" outlineLevel="1">
-      <c r="A58" s="13" t="inlineStr">
+      <c r="B58" s="12" t="n"/>
+      <c r="C58" s="12" t="n"/>
+      <c r="D58" s="12" t="n"/>
+      <c r="E58" s="12" t="n"/>
+      <c r="F58" s="12" t="n"/>
+      <c r="G58" s="12" t="n"/>
+      <c r="H58" s="12" t="n"/>
+      <c r="I58" s="12" t="n"/>
+      <c r="J58" s="12" t="n"/>
+      <c r="K58" s="12" t="n"/>
+      <c r="L58" s="12" t="n"/>
+      <c r="M58" s="12" t="n"/>
+      <c r="N58" s="12" t="n"/>
+      <c r="O58" s="12" t="n"/>
+    </row>
+    <row r="59" outlineLevel="1">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>Virginia</t>
         </is>
       </c>
-      <c r="B58" s="14" t="inlineStr">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>Haynes Furniture / The Dump – 12 stores closing (furniture, mattresses)</t>
         </is>
       </c>
-      <c r="C58" s="13" t="inlineStr">
+      <c r="C59" s="13" t="inlineStr">
         <is>
           <t>retail GOB</t>
         </is>
       </c>
-      <c r="D58" s="13" t="inlineStr">
+      <c r="D59" s="13" t="inlineStr">
         <is>
           <t>Virginia Beach</t>
         </is>
       </c>
-      <c r="E58" s="13" t="inlineStr">
+      <c r="E59" s="13" t="inlineStr">
         <is>
           <t>VA</t>
         </is>
       </c>
-      <c r="F58" s="13" t="n">
+      <c r="F59" s="13" t="n">
         <v>456</v>
       </c>
-      <c r="G58" s="13" t="inlineStr">
+      <c r="G59" s="13" t="inlineStr">
         <is>
           <t>Retail GOB markdowns</t>
         </is>
       </c>
-      <c r="H58" s="15" t="n"/>
-      <c r="I58" s="13" t="inlineStr">
+      <c r="H59" s="15" t="n"/>
+      <c r="I59" s="13" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="J58" s="13" t="inlineStr"/>
-      <c r="K58" s="13" t="inlineStr">
+      <c r="J59" s="13" t="inlineStr"/>
+      <c r="K59" s="13" t="inlineStr">
         <is>
           <t>SB360 (PR Newswire)</t>
         </is>
       </c>
-      <c r="L58" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M58" s="13" t="inlineStr"/>
-      <c r="N58" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O58" s="14" t="inlineStr">
+      <c r="L59" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M59" s="13" t="inlineStr"/>
+      <c r="N59" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O59" s="14" t="inlineStr">
         <is>
           <t>Posted Oct 8. Multi-state (VA/AZ/GA/IL/TX); pinned at Virginia Beach. Home goods only.</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="17" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Virginia</t>
         </is>
       </c>
-      <c r="B59" s="17" t="inlineStr">
+      <c r="B60" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C59" s="18" t="n"/>
-      <c r="D59" s="18" t="n"/>
-      <c r="E59" s="18" t="n"/>
-      <c r="F59" s="18" t="n"/>
-      <c r="G59" s="18" t="n"/>
-      <c r="H59" s="19" t="n">
+      <c r="C60" s="18" t="n"/>
+      <c r="D60" s="18" t="n"/>
+      <c r="E60" s="18" t="n"/>
+      <c r="F60" s="18" t="n"/>
+      <c r="G60" s="18" t="n"/>
+      <c r="H60" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I59" s="18" t="n"/>
-      <c r="J59" s="18" t="n"/>
-      <c r="K59" s="18" t="n"/>
-      <c r="L59" s="18" t="n"/>
-      <c r="M59" s="18" t="n"/>
-      <c r="N59" s="18" t="n"/>
-      <c r="O59" s="18" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="11" t="inlineStr">
+      <c r="I60" s="18" t="n"/>
+      <c r="J60" s="18" t="n"/>
+      <c r="K60" s="18" t="n"/>
+      <c r="L60" s="18" t="n"/>
+      <c r="M60" s="18" t="n"/>
+      <c r="N60" s="18" t="n"/>
+      <c r="O60" s="18" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t>▸ Midwest  (2)</t>
         </is>
       </c>
-      <c r="B60" s="12" t="n"/>
-      <c r="C60" s="12" t="n"/>
-      <c r="D60" s="12" t="n"/>
-      <c r="E60" s="12" t="n"/>
-      <c r="F60" s="12" t="n"/>
-      <c r="G60" s="12" t="n"/>
-      <c r="H60" s="12" t="n"/>
-      <c r="I60" s="12" t="n"/>
-      <c r="J60" s="12" t="n"/>
-      <c r="K60" s="12" t="n"/>
-      <c r="L60" s="12" t="n"/>
-      <c r="M60" s="12" t="n"/>
-      <c r="N60" s="12" t="n"/>
-      <c r="O60" s="12" t="n"/>
-    </row>
-    <row r="61" outlineLevel="1">
-      <c r="A61" s="13" t="inlineStr">
-        <is>
-          <t>Midwest</t>
-        </is>
-      </c>
-      <c r="B61" s="14" t="inlineStr">
-        <is>
-          <t>Freshway Market whole-grocery liquidation – refrigeration racks, cases, walk-ins, generator</t>
-        </is>
-      </c>
-      <c r="C61" s="13" t="inlineStr">
-        <is>
-          <t>store closing</t>
-        </is>
-      </c>
-      <c r="D61" s="13" t="inlineStr">
-        <is>
-          <t>Chicago</t>
-        </is>
-      </c>
-      <c r="E61" s="13" t="inlineStr">
-        <is>
-          <t>IL</t>
-        </is>
-      </c>
-      <c r="F61" s="13" t="n">
-        <v>862</v>
-      </c>
-      <c r="G61" s="13" t="inlineStr">
-        <is>
-          <t>Online auction</t>
-        </is>
-      </c>
-      <c r="H61" s="15" t="n"/>
-      <c r="I61" s="13" t="inlineStr"/>
-      <c r="J61" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-20 11:00 AM ET</t>
-        </is>
-      </c>
-      <c r="K61" s="13" t="inlineStr">
-        <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L61" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M61" s="13" t="inlineStr"/>
-      <c r="N61" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O61" s="14" t="inlineStr">
-        <is>
-          <t>Closes from Oct 20 10 AM CDT.</t>
-        </is>
-      </c>
+      <c r="B61" s="12" t="n"/>
+      <c r="C61" s="12" t="n"/>
+      <c r="D61" s="12" t="n"/>
+      <c r="E61" s="12" t="n"/>
+      <c r="F61" s="12" t="n"/>
+      <c r="G61" s="12" t="n"/>
+      <c r="H61" s="12" t="n"/>
+      <c r="I61" s="12" t="n"/>
+      <c r="J61" s="12" t="n"/>
+      <c r="K61" s="12" t="n"/>
+      <c r="L61" s="12" t="n"/>
+      <c r="M61" s="12" t="n"/>
+      <c r="N61" s="12" t="n"/>
+      <c r="O61" s="12" t="n"/>
     </row>
     <row r="62" outlineLevel="1">
       <c r="A62" s="13" t="inlineStr">
@@ -21783,17 +21789,17 @@
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>American Sale – total liquidation, all 7 stores (pools, hot tubs, grills, holiday decor)</t>
+          <t>Freshway Market whole-grocery liquidation – refrigeration racks, cases, walk-ins, generator</t>
         </is>
       </c>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>retail GOB</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>Chicagoland</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
@@ -21802,28 +21808,28 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>876</v>
+        <v>862</v>
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>Retail GOB, up to 70% off</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H62" s="15" t="n"/>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="J62" s="13" t="inlineStr"/>
+      <c r="I62" s="13" t="inlineStr"/>
+      <c r="J62" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>Tiger Group (PR Newswire)</t>
-        </is>
-      </c>
-      <c r="L62" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L62" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M62" s="13" t="inlineStr"/>
@@ -21834,261 +21840,324 @@
       </c>
       <c r="O62" s="14" t="inlineStr">
         <is>
+          <t>Closes from Oct 20 10 AM CDT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" outlineLevel="1">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>American Sale – total liquidation, all 7 stores (pools, hot tubs, grills, holiday decor)</t>
+        </is>
+      </c>
+      <c r="C63" s="13" t="inlineStr">
+        <is>
+          <t>retail GOB</t>
+        </is>
+      </c>
+      <c r="D63" s="13" t="inlineStr">
+        <is>
+          <t>Chicagoland</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="F63" s="13" t="n">
+        <v>876</v>
+      </c>
+      <c r="G63" s="13" t="inlineStr">
+        <is>
+          <t>Retail GOB, up to 70% off</t>
+        </is>
+      </c>
+      <c r="H63" s="15" t="n"/>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J63" s="13" t="inlineStr"/>
+      <c r="K63" s="13" t="inlineStr">
+        <is>
+          <t>Tiger Group (PR Newswire)</t>
+        </is>
+      </c>
+      <c r="L63" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M63" s="13" t="inlineStr"/>
+      <c r="N63" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O63" s="14" t="inlineStr">
+        <is>
           <t>Posted Oct 15. Watch for a bulk/fixture auction.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="17" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Midwest</t>
         </is>
       </c>
-      <c r="B63" s="17" t="inlineStr">
+      <c r="B64" s="17" t="inlineStr">
         <is>
           <t>2 item(s)</t>
         </is>
       </c>
-      <c r="C63" s="18" t="n"/>
-      <c r="D63" s="18" t="n"/>
-      <c r="E63" s="18" t="n"/>
-      <c r="F63" s="18" t="n"/>
-      <c r="G63" s="18" t="n"/>
-      <c r="H63" s="19" t="n">
+      <c r="C64" s="18" t="n"/>
+      <c r="D64" s="18" t="n"/>
+      <c r="E64" s="18" t="n"/>
+      <c r="F64" s="18" t="n"/>
+      <c r="G64" s="18" t="n"/>
+      <c r="H64" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I63" s="18" t="n"/>
-      <c r="J63" s="18" t="n"/>
-      <c r="K63" s="18" t="n"/>
-      <c r="L63" s="18" t="n"/>
-      <c r="M63" s="18" t="n"/>
-      <c r="N63" s="18" t="n"/>
-      <c r="O63" s="18" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="11" t="inlineStr">
+      <c r="I64" s="18" t="n"/>
+      <c r="J64" s="18" t="n"/>
+      <c r="K64" s="18" t="n"/>
+      <c r="L64" s="18" t="n"/>
+      <c r="M64" s="18" t="n"/>
+      <c r="N64" s="18" t="n"/>
+      <c r="O64" s="18" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>▸ Texas / South Central  (1)</t>
         </is>
       </c>
-      <c r="B64" s="12" t="n"/>
-      <c r="C64" s="12" t="n"/>
-      <c r="D64" s="12" t="n"/>
-      <c r="E64" s="12" t="n"/>
-      <c r="F64" s="12" t="n"/>
-      <c r="G64" s="12" t="n"/>
-      <c r="H64" s="12" t="n"/>
-      <c r="I64" s="12" t="n"/>
-      <c r="J64" s="12" t="n"/>
-      <c r="K64" s="12" t="n"/>
-      <c r="L64" s="12" t="n"/>
-      <c r="M64" s="12" t="n"/>
-      <c r="N64" s="12" t="n"/>
-      <c r="O64" s="12" t="n"/>
-    </row>
-    <row r="65" outlineLevel="1">
-      <c r="A65" s="13" t="inlineStr">
+      <c r="B65" s="12" t="n"/>
+      <c r="C65" s="12" t="n"/>
+      <c r="D65" s="12" t="n"/>
+      <c r="E65" s="12" t="n"/>
+      <c r="F65" s="12" t="n"/>
+      <c r="G65" s="12" t="n"/>
+      <c r="H65" s="12" t="n"/>
+      <c r="I65" s="12" t="n"/>
+      <c r="J65" s="12" t="n"/>
+      <c r="K65" s="12" t="n"/>
+      <c r="L65" s="12" t="n"/>
+      <c r="M65" s="12" t="n"/>
+      <c r="N65" s="12" t="n"/>
+      <c r="O65" s="12" t="n"/>
+    </row>
+    <row r="66" outlineLevel="1">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>Texas / South Central</t>
         </is>
       </c>
-      <c r="B65" s="14" t="inlineStr">
+      <c r="B66" s="14" t="inlineStr">
         <is>
           <t>Southwest beverage distributor surplus – mostly unused: 16 True merchandisers, 75 Bunn brewers, 100+ micro-market kiosks</t>
         </is>
       </c>
-      <c r="C65" s="13" t="inlineStr">
+      <c r="C66" s="13" t="inlineStr">
         <is>
           <t>distributor surplus</t>
         </is>
       </c>
-      <c r="D65" s="13" t="inlineStr">
+      <c r="D66" s="13" t="inlineStr">
         <is>
           <t>Mesquite</t>
         </is>
       </c>
-      <c r="E65" s="13" t="inlineStr">
+      <c r="E66" s="13" t="inlineStr">
         <is>
           <t>TX</t>
         </is>
       </c>
-      <c r="F65" s="13" t="n">
+      <c r="F66" s="13" t="n">
         <v>1547</v>
       </c>
-      <c r="G65" s="13" t="inlineStr">
+      <c r="G66" s="13" t="inlineStr">
         <is>
           <t>Online auction</t>
         </is>
       </c>
-      <c r="H65" s="15" t="n"/>
-      <c r="I65" s="13" t="inlineStr"/>
-      <c r="J65" s="13" t="inlineStr">
+      <c r="H66" s="15" t="n"/>
+      <c r="I66" s="13" t="inlineStr"/>
+      <c r="J66" s="13" t="inlineStr">
         <is>
           <t>2026-11-13 11:00 AM ET</t>
         </is>
       </c>
-      <c r="K65" s="13" t="inlineStr">
+      <c r="K66" s="13" t="inlineStr">
         <is>
           <t>Heritage Global Partners</t>
         </is>
       </c>
-      <c r="L65" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M65" s="13" t="inlineStr"/>
-      <c r="N65" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O65" s="14" t="inlineStr">
+      <c r="L66" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M66" s="13" t="inlineStr"/>
+      <c r="N66" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O66" s="14" t="inlineStr">
         <is>
           <t>Near-new appliances, resell by unit. Nov 13 10 AM CST.</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="17" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Texas / South Central</t>
         </is>
       </c>
-      <c r="B66" s="17" t="inlineStr">
+      <c r="B67" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C66" s="18" t="n"/>
-      <c r="D66" s="18" t="n"/>
-      <c r="E66" s="18" t="n"/>
-      <c r="F66" s="18" t="n"/>
-      <c r="G66" s="18" t="n"/>
-      <c r="H66" s="19" t="n">
+      <c r="C67" s="18" t="n"/>
+      <c r="D67" s="18" t="n"/>
+      <c r="E67" s="18" t="n"/>
+      <c r="F67" s="18" t="n"/>
+      <c r="G67" s="18" t="n"/>
+      <c r="H67" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I66" s="18" t="n"/>
-      <c r="J66" s="18" t="n"/>
-      <c r="K66" s="18" t="n"/>
-      <c r="L66" s="18" t="n"/>
-      <c r="M66" s="18" t="n"/>
-      <c r="N66" s="18" t="n"/>
-      <c r="O66" s="18" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="11" t="inlineStr">
+      <c r="I67" s="18" t="n"/>
+      <c r="J67" s="18" t="n"/>
+      <c r="K67" s="18" t="n"/>
+      <c r="L67" s="18" t="n"/>
+      <c r="M67" s="18" t="n"/>
+      <c r="N67" s="18" t="n"/>
+      <c r="O67" s="18" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
         <is>
           <t>▸ West / Other  (1)</t>
         </is>
       </c>
-      <c r="B67" s="12" t="n"/>
-      <c r="C67" s="12" t="n"/>
-      <c r="D67" s="12" t="n"/>
-      <c r="E67" s="12" t="n"/>
-      <c r="F67" s="12" t="n"/>
-      <c r="G67" s="12" t="n"/>
-      <c r="H67" s="12" t="n"/>
-      <c r="I67" s="12" t="n"/>
-      <c r="J67" s="12" t="n"/>
-      <c r="K67" s="12" t="n"/>
-      <c r="L67" s="12" t="n"/>
-      <c r="M67" s="12" t="n"/>
-      <c r="N67" s="12" t="n"/>
-      <c r="O67" s="12" t="n"/>
-    </row>
-    <row r="68" outlineLevel="1">
-      <c r="A68" s="13" t="inlineStr">
+      <c r="B68" s="12" t="n"/>
+      <c r="C68" s="12" t="n"/>
+      <c r="D68" s="12" t="n"/>
+      <c r="E68" s="12" t="n"/>
+      <c r="F68" s="12" t="n"/>
+      <c r="G68" s="12" t="n"/>
+      <c r="H68" s="12" t="n"/>
+      <c r="I68" s="12" t="n"/>
+      <c r="J68" s="12" t="n"/>
+      <c r="K68" s="12" t="n"/>
+      <c r="L68" s="12" t="n"/>
+      <c r="M68" s="12" t="n"/>
+      <c r="N68" s="12" t="n"/>
+      <c r="O68" s="12" t="n"/>
+    </row>
+    <row r="69" outlineLevel="1">
+      <c r="A69" s="13" t="inlineStr">
         <is>
           <t>West / Other</t>
         </is>
       </c>
-      <c r="B68" s="14" t="inlineStr">
+      <c r="B69" s="14" t="inlineStr">
         <is>
           <t>National salad concept liquidation – full contents of 63 fast-casual restaurants (AZ/TX/OK/NV)</t>
         </is>
       </c>
-      <c r="C68" s="13" t="inlineStr">
+      <c r="C69" s="13" t="inlineStr">
         <is>
           <t>restaurant chain liquidation</t>
         </is>
       </c>
-      <c r="D68" s="13" t="inlineStr">
+      <c r="D69" s="13" t="inlineStr">
         <is>
           <t>Phoenix</t>
         </is>
       </c>
-      <c r="E68" s="13" t="inlineStr">
+      <c r="E69" s="13" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="F68" s="13" t="n">
+      <c r="F69" s="13" t="n">
         <v>2307</v>
       </c>
-      <c r="G68" s="13" t="inlineStr">
+      <c r="G69" s="13" t="inlineStr">
         <is>
           <t>Online auctions, dates TBD</t>
         </is>
       </c>
-      <c r="H68" s="15" t="n"/>
-      <c r="I68" s="13" t="inlineStr">
+      <c r="H69" s="15" t="n"/>
+      <c r="I69" s="13" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="J68" s="13" t="inlineStr"/>
-      <c r="K68" s="13" t="inlineStr">
+      <c r="J69" s="13" t="inlineStr"/>
+      <c r="K69" s="13" t="inlineStr">
         <is>
           <t>RestaurantEquipment.bid (TAGeX)</t>
         </is>
       </c>
-      <c r="L68" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M68" s="13" t="inlineStr"/>
-      <c r="N68" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O68" s="14" t="inlineStr">
+      <c r="L69" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M69" s="13" t="inlineStr"/>
+      <c r="N69" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O69" s="14" t="inlineStr">
         <is>
           <t>Rolling market-by-market auctions, none live yet (Phoenix metro 30 locations, DFW 14, Tucson 6, Houston 5, plus OK/NV). Pickup on site at each restaurant. Pinned at Phoenix.</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="17" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="17" t="inlineStr">
         <is>
           <t>Subtotal — West / Other</t>
         </is>
       </c>
-      <c r="B69" s="17" t="inlineStr">
+      <c r="B70" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C69" s="18" t="n"/>
-      <c r="D69" s="18" t="n"/>
-      <c r="E69" s="18" t="n"/>
-      <c r="F69" s="18" t="n"/>
-      <c r="G69" s="18" t="n"/>
-      <c r="H69" s="19" t="n">
+      <c r="C70" s="18" t="n"/>
+      <c r="D70" s="18" t="n"/>
+      <c r="E70" s="18" t="n"/>
+      <c r="F70" s="18" t="n"/>
+      <c r="G70" s="18" t="n"/>
+      <c r="H70" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I69" s="18" t="n"/>
-      <c r="J69" s="18" t="n"/>
-      <c r="K69" s="18" t="n"/>
-      <c r="L69" s="18" t="n"/>
-      <c r="M69" s="18" t="n"/>
-      <c r="N69" s="18" t="n"/>
-      <c r="O69" s="18" t="n"/>
+      <c r="I70" s="18" t="n"/>
+      <c r="J70" s="18" t="n"/>
+      <c r="K70" s="18" t="n"/>
+      <c r="L70" s="18" t="n"/>
+      <c r="M70" s="18" t="n"/>
+      <c r="N70" s="18" t="n"/>
+      <c r="O70" s="18" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O69"/>
+  <autoFilter ref="A1:O70"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId2"/>
@@ -22109,7 +22178,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId23"/>
@@ -22125,15 +22194,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N51" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N61" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N62" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N65" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N68" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N66" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N69" r:id="rId45"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22145,7 +22215,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O3"/>
+  <dimension ref="A1:O4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -22376,11 +22446,79 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>Unknown location</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>Wolf 36” Single Electric Wall Built-In Oven SO36U/S - Tested Work</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>range/oven/rangetop</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="n"/>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>$99</t>
+        </is>
+      </c>
+      <c r="H4" s="15" t="n">
+        <v>99</v>
+      </c>
+      <c r="I4" s="13" t="inlineStr"/>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-18 02:19 PM ET</t>
+        </is>
+      </c>
+      <c r="K4" s="13" t="inlineStr">
+        <is>
+          <t>eBay (pickup only, over 60 mi)</t>
+        </is>
+      </c>
+      <c r="L4" s="13" t="inlineStr">
+        <is>
+          <t>EXPIRED (2026-10-18 02:19 PM ET)</t>
+        </is>
+      </c>
+      <c r="M4" s="21" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
+      <c r="N4" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O4" s="14" t="inlineStr">
+        <is>
+          <t>Condition: Pre-Owned. FLIP: SO36U/S tested, auction $99/0 bids, pickup only; rough resale $600-1k (eBay card shows no city; pickup distance in source.) Ends Oct 18 ~2:19 PM per eBay card (time zone uncertain; could be earlier). [auto-removed 2026-10-18: closing date passed]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O3"/>
+  <autoFilter ref="A1:O4"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lot_recon.xlsx
+++ b/lot_recon.xlsx
@@ -20,8 +20,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wolf New'!$A$1:$O$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wolf Used'!$A$1:$O$189</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Wolf Unclear'!$A$1:$O$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$75</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Removed'!$A$1:$O$5</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Removed'!$A$1:$O$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -577,7 +577,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Last updated: 2026-10-19 08:00 ET</t>
+          <t>Last updated: 2026-10-19 11:11 ET</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Active listings: 291 · Removed: 4</t>
+          <t>Active listings: 294 · Removed: 5</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
         <v>164</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>607929.6</v>
+        <v>608011.6</v>
       </c>
       <c r="D10" t="n">
         <v>1</v>
@@ -695,7 +695,7 @@
         <v>31</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>137837.5</v>
+        <v>137840</v>
       </c>
       <c r="D11" t="n">
         <v>0</v>
@@ -708,13 +708,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>980348.08</v>
+        <v>980432.58</v>
       </c>
     </row>
     <row r="15">
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -806,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>5398.69</v>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -1004,10 +1004,10 @@
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>64663</v>
+        <v>64740</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -1037,7 +1037,7 @@
         <v>24</v>
       </c>
       <c r="G24" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>440141</v>
@@ -1073,7 +1073,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>1512.5</v>
+        <v>1515</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>2</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -4141,7 +4141,7 @@
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>$0 current bid + BP</t>
+          <t>$0 / prebids open (live Oct 25)</t>
         </is>
       </c>
       <c r="H16" s="15" t="n">
@@ -7060,11 +7060,11 @@
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t>$13 current bid (6 bids) + 18% BP</t>
+          <t>$90 high bid (16 bids)</t>
         </is>
       </c>
       <c r="H34" s="15" t="n">
-        <v>13</v>
+        <v>90</v>
       </c>
       <c r="I34" s="13" t="inlineStr"/>
       <c r="J34" s="13" t="inlineStr">
@@ -7867,7 +7867,7 @@
       <c r="F47" s="18" t="n"/>
       <c r="G47" s="18" t="n"/>
       <c r="H47" s="19" t="n">
-        <v>33063</v>
+        <v>33140</v>
       </c>
       <c r="I47" s="18" t="n"/>
       <c r="J47" s="18" t="n"/>
@@ -12396,7 +12396,7 @@
       </c>
       <c r="G122" s="13" t="inlineStr">
         <is>
-          <t>$0 current bid + BP</t>
+          <t>$0 high bid</t>
         </is>
       </c>
       <c r="H122" s="15" t="n">
@@ -12461,7 +12461,7 @@
       </c>
       <c r="G123" s="13" t="inlineStr">
         <is>
-          <t>$0 current bid + BP</t>
+          <t>$0 high bid</t>
         </is>
       </c>
       <c r="H123" s="15" t="n">
@@ -12574,11 +12574,11 @@
       </c>
       <c r="G126" s="13" t="inlineStr">
         <is>
-          <t>$0 current bid + BP</t>
+          <t>$5 high bid</t>
         </is>
       </c>
       <c r="H126" s="15" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I126" s="13" t="inlineStr"/>
       <c r="J126" s="13" t="inlineStr">
@@ -12629,7 +12629,7 @@
       <c r="F127" s="18" t="n"/>
       <c r="G127" s="18" t="n"/>
       <c r="H127" s="19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I127" s="18" t="n"/>
       <c r="J127" s="18" t="n"/>
@@ -18394,11 +18394,11 @@
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
-          <t>$12.50 high bid</t>
+          <t>$15 high bid</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="I35" s="13" t="inlineStr"/>
       <c r="J35" s="13" t="inlineStr">
@@ -18445,7 +18445,7 @@
       <c r="F36" s="18" t="n"/>
       <c r="G36" s="18" t="n"/>
       <c r="H36" s="19" t="n">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="I36" s="18" t="n"/>
       <c r="J36" s="18" t="n"/>
@@ -18507,7 +18507,7 @@
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>$5 current bid + BP</t>
+          <t>$5 high bid</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
@@ -18572,7 +18572,7 @@
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
-          <t>$0 current bid + BP</t>
+          <t>$0 high bid</t>
         </is>
       </c>
       <c r="H39" s="15" t="n">
@@ -18678,7 +18678,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O75"/>
+  <dimension ref="A1:O78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -18778,7 +18778,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>▸ Greater Boston / South Shore (&lt;50mi)  (5)</t>
+          <t>▸ Greater Boston / South Shore (&lt;50mi)  (4)</t>
         </is>
       </c>
       <c r="B2" s="12" t="n"/>
@@ -18804,17 +18804,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>Closed Best Buy Outlet – pallet racking, Big Joe order pickers, appliance dollies, carts, cages</t>
+          <t>P&amp;S Mechanical contractor liquidation – plumbing stock, hot water tanks, pumps, tools, 2 ProMaster vans</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>store closing fixtures</t>
+          <t>contractor liquidation</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>Brockton</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
@@ -18823,28 +18823,28 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
-          <t>Racking $40/upright, $80/level; pickers $1,000 OBO</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H3" s="15" t="n"/>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="J3" s="13" t="inlineStr"/>
+      <c r="I3" s="13" t="inlineStr"/>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-22 09:00 AM ET</t>
+        </is>
+      </c>
       <c r="K3" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L3" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Salvadore Auctions</t>
+        </is>
+      </c>
+      <c r="L3" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M3" s="13" t="inlineStr"/>
@@ -18855,7 +18855,7 @@
       </c>
       <c r="O3" s="14" t="inlineStr">
         <is>
-          <t>200 Westgate Dr. Fixtures/equipment only, no merchandise. On site daily.</t>
+          <t>Page conflicts: Oct 21 or 22 9 AM (later date used). Closest find.</t>
         </is>
       </c>
     </row>
@@ -18867,17 +18867,17 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>P&amp;S Mechanical contractor liquidation – plumbing stock, hot water tanks, pumps, tools, 2 ProMaster vans</t>
+          <t>"Fire sale" former chain restaurant – AccuTemp AccuSteam 36" griddles, Vulcan hot plate, custom stainless stations</t>
         </is>
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>contractor liquidation</t>
+          <t>restaurant closing</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Plymouth</t>
+          <t>Cambridge</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
@@ -18886,23 +18886,23 @@
         </is>
       </c>
       <c r="F4" s="13" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>$9,500 OBO whole lot (or per piece)</t>
         </is>
       </c>
       <c r="H4" s="15" t="n"/>
-      <c r="I4" s="13" t="inlineStr"/>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-22 09:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr"/>
       <c r="K4" s="13" t="inlineStr">
         <is>
-          <t>Salvadore Auctions</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L4" s="13" t="inlineStr">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="O4" s="14" t="inlineStr">
         <is>
-          <t>Page conflicts: Oct 21 or 22 9 AM (later date used). Closest find.</t>
+          <t>Updated Oct 16. Individually priced $13,250 total. Cash/wire/cashier's check.</t>
         </is>
       </c>
     </row>
@@ -18930,17 +18930,17 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>"Fire sale" former chain restaurant – AccuTemp AccuSteam 36" griddles, Vulcan hot plate, custom stainless stations</t>
+          <t>Retirement bulk tool lot – 10 tools, sold together</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>retirement</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Cambridge</t>
+          <t>Waltham</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
@@ -18949,17 +18949,17 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>$9,500 OBO whole lot (or per piece)</t>
+          <t>$250 all</t>
         </is>
       </c>
       <c r="H5" s="15" t="n"/>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J5" s="13" t="inlineStr"/>
@@ -18981,7 +18981,7 @@
       </c>
       <c r="O5" s="14" t="inlineStr">
         <is>
-          <t>Updated Oct 16. Individually priced $13,250 total. Cash/wire/cashier's check.</t>
+          <t>Small off-category FYI; seller says resell individually. Old CL URL deleted; reposted under new URL 2026-10-19 (same $250 / 10 tools).</t>
         </is>
       </c>
     </row>
@@ -18993,17 +18993,17 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>Retirement bulk tool lot – 10 tools, sold together</t>
+          <t>Cannabis facility contents incl. commercial kitchen / stainless</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>retirement</t>
+          <t>facility contents</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Waltham</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -19012,23 +19012,23 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>$250 all</t>
+          <t>Auction, 18% BP</t>
         </is>
       </c>
       <c r="H6" s="15" t="n"/>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="J6" s="13" t="inlineStr"/>
+      <c r="I6" s="13" t="inlineStr"/>
+      <c r="J6" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-03 10:00 AM ET</t>
+        </is>
+      </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>Paul E. Saperstein (PESCO)</t>
         </is>
       </c>
       <c r="L6" s="13" t="inlineStr">
@@ -19044,120 +19044,120 @@
       </c>
       <c r="O6" s="14" t="inlineStr">
         <is>
-          <t>Small off-category FYI; seller says resell individually. Old CL URL deleted; reposted under new URL 2026-10-19 (same $250 / 10 tools).</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" outlineLevel="1">
-      <c r="A7" s="13" t="inlineStr">
-        <is>
-          <t>Greater Boston / South Shore (&lt;50mi)</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>Cannabis facility contents incl. commercial kitchen / stainless</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>facility contents</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>Milford</t>
-        </is>
-      </c>
-      <c r="E7" s="13" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="F7" s="13" t="n">
-        <v>36</v>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
-        <is>
-          <t>Auction, 18% BP</t>
-        </is>
-      </c>
-      <c r="H7" s="15" t="n"/>
-      <c r="I7" s="13" t="inlineStr"/>
-      <c r="J7" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-03 10:00 AM ET</t>
-        </is>
-      </c>
-      <c r="K7" s="13" t="inlineStr">
-        <is>
-          <t>Paul E. Saperstein (PESCO)</t>
-        </is>
-      </c>
-      <c r="L7" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M7" s="13" t="inlineStr"/>
-      <c r="N7" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O7" s="14" t="inlineStr">
-        <is>
           <t>Calendar page only (no event page yet). ~45 mi.</t>
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Greater Boston / South Shore (&lt;50mi)</t>
+        </is>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>4 item(s)</t>
+        </is>
+      </c>
+      <c r="C7" s="18" t="n"/>
+      <c r="D7" s="18" t="n"/>
+      <c r="E7" s="18" t="n"/>
+      <c r="F7" s="18" t="n"/>
+      <c r="G7" s="18" t="n"/>
+      <c r="H7" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="18" t="n"/>
+      <c r="J7" s="18" t="n"/>
+      <c r="K7" s="18" t="n"/>
+      <c r="L7" s="18" t="n"/>
+      <c r="M7" s="18" t="n"/>
+      <c r="N7" s="18" t="n"/>
+      <c r="O7" s="18" t="n"/>
+    </row>
     <row r="8">
-      <c r="A8" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Greater Boston / South Shore (&lt;50mi)</t>
-        </is>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>5 item(s)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="n"/>
-      <c r="D8" s="18" t="n"/>
-      <c r="E8" s="18" t="n"/>
-      <c r="F8" s="18" t="n"/>
-      <c r="G8" s="18" t="n"/>
-      <c r="H8" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="18" t="n"/>
-      <c r="J8" s="18" t="n"/>
-      <c r="K8" s="18" t="n"/>
-      <c r="L8" s="18" t="n"/>
-      <c r="M8" s="18" t="n"/>
-      <c r="N8" s="18" t="n"/>
-      <c r="O8" s="18" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>▸ North Shore / Merrimack Valley / S. NH  (2)</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
-      <c r="M9" s="12" t="n"/>
-      <c r="N9" s="12" t="n"/>
-      <c r="O9" s="12" t="n"/>
+      <c r="B8" s="12" t="n"/>
+      <c r="C8" s="12" t="n"/>
+      <c r="D8" s="12" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="12" t="n"/>
+      <c r="G8" s="12" t="n"/>
+      <c r="H8" s="12" t="n"/>
+      <c r="I8" s="12" t="n"/>
+      <c r="J8" s="12" t="n"/>
+      <c r="K8" s="12" t="n"/>
+      <c r="L8" s="12" t="n"/>
+      <c r="M8" s="12" t="n"/>
+      <c r="N8" s="12" t="n"/>
+      <c r="O8" s="12" t="n"/>
+    </row>
+    <row r="9" outlineLevel="1">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>North Shore / Merrimack Valley / S. NH</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Commercial mechanical/plumbing/HVAC contractor inventory – multiple pallets of boxed stock, water heater, venting, diffusers</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Merrimack</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>62</v>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>$1 placeholder – make offer on everything</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="n"/>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr"/>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M9" s="13" t="inlineStr"/>
+      <c r="N9" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O9" s="14" t="inlineStr">
+        <is>
+          <t>Bulk buyers preferred.</t>
+        </is>
+      </c>
     </row>
     <row r="10" outlineLevel="1">
       <c r="A10" s="13" t="inlineStr">
@@ -19167,17 +19167,17 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>Commercial mechanical/plumbing/HVAC contractor inventory – multiple pallets of boxed stock, water heater, venting, diffusers</t>
+          <t>Plumbing &amp; heating overstock/returns online auction – 183 lots (fixtures, furnaces, heaters, A/C)</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>Merrimack</t>
+          <t>Concord</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
@@ -19186,23 +19186,27 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>62</v>
+        <v>84</v>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>$1 placeholder – make offer on everything</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H10" s="15" t="n"/>
       <c r="I10" s="13" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="J10" s="13" t="inlineStr"/>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-27 07:00 PM ET</t>
+        </is>
+      </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>HiBid (Atlantic Auction Co.)</t>
         </is>
       </c>
       <c r="L10" s="13" t="inlineStr">
@@ -19218,124 +19222,120 @@
       </c>
       <c r="O10" s="14" t="inlineStr">
         <is>
-          <t>Bulk buyers preferred.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" outlineLevel="1">
-      <c r="A11" s="13" t="inlineStr">
-        <is>
-          <t>North Shore / Merrimack Valley / S. NH</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>Plumbing &amp; heating overstock/returns online auction – 183 lots (fixtures, furnaces, heaters, A/C)</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>auction</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="inlineStr">
-        <is>
-          <t>Concord</t>
-        </is>
-      </c>
-      <c r="E11" s="13" t="inlineStr">
-        <is>
-          <t>NH</t>
-        </is>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>84</v>
-      </c>
-      <c r="G11" s="13" t="inlineStr">
-        <is>
-          <t>Online auction</t>
-        </is>
-      </c>
-      <c r="H11" s="15" t="n"/>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="J11" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-27 07:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K11" s="13" t="inlineStr">
-        <is>
-          <t>HiBid (Atlantic Auction Co.)</t>
-        </is>
-      </c>
-      <c r="L11" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M11" s="13" t="inlineStr"/>
-      <c r="N11" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O11" s="14" t="inlineStr">
-        <is>
           <t>Overstock sale, not a closing. Pickup Oct 29–30.</t>
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — North Shore / Merrimack Valley / S. NH</t>
+        </is>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>2 item(s)</t>
+        </is>
+      </c>
+      <c r="C11" s="18" t="n"/>
+      <c r="D11" s="18" t="n"/>
+      <c r="E11" s="18" t="n"/>
+      <c r="F11" s="18" t="n"/>
+      <c r="G11" s="18" t="n"/>
+      <c r="H11" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="18" t="n"/>
+      <c r="J11" s="18" t="n"/>
+      <c r="K11" s="18" t="n"/>
+      <c r="L11" s="18" t="n"/>
+      <c r="M11" s="18" t="n"/>
+      <c r="N11" s="18" t="n"/>
+      <c r="O11" s="18" t="n"/>
+    </row>
     <row r="12">
-      <c r="A12" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — North Shore / Merrimack Valley / S. NH</t>
-        </is>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C12" s="18" t="n"/>
-      <c r="D12" s="18" t="n"/>
-      <c r="E12" s="18" t="n"/>
-      <c r="F12" s="18" t="n"/>
-      <c r="G12" s="18" t="n"/>
-      <c r="H12" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="18" t="n"/>
-      <c r="J12" s="18" t="n"/>
-      <c r="K12" s="18" t="n"/>
-      <c r="L12" s="18" t="n"/>
-      <c r="M12" s="18" t="n"/>
-      <c r="N12" s="18" t="n"/>
-      <c r="O12" s="18" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>▸ Central / Western MA  (3)</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
-      <c r="H13" s="12" t="n"/>
-      <c r="I13" s="12" t="n"/>
-      <c r="J13" s="12" t="n"/>
-      <c r="K13" s="12" t="n"/>
-      <c r="L13" s="12" t="n"/>
-      <c r="M13" s="12" t="n"/>
-      <c r="N13" s="12" t="n"/>
-      <c r="O13" s="12" t="n"/>
+      <c r="B12" s="12" t="n"/>
+      <c r="C12" s="12" t="n"/>
+      <c r="D12" s="12" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="12" t="n"/>
+      <c r="G12" s="12" t="n"/>
+      <c r="H12" s="12" t="n"/>
+      <c r="I12" s="12" t="n"/>
+      <c r="J12" s="12" t="n"/>
+      <c r="K12" s="12" t="n"/>
+      <c r="L12" s="12" t="n"/>
+      <c r="M12" s="12" t="n"/>
+      <c r="N12" s="12" t="n"/>
+      <c r="O12" s="12" t="n"/>
+    </row>
+    <row r="13" outlineLevel="1">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>Central / Western MA</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Gift/souvenir store closing (retirement) – all new stock</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>store closing</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Thorndike</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>77</v>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>By appointment</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="n"/>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="inlineStr"/>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L13" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M13" s="13" t="inlineStr"/>
+      <c r="N13" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O13" s="14" t="inlineStr">
+        <is>
+          <t>Updated Oct 8. Off-category FYI.</t>
+        </is>
+      </c>
     </row>
     <row r="14" outlineLevel="1">
       <c r="A14" s="13" t="inlineStr">
@@ -19345,17 +19345,17 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Gift/souvenir store closing (retirement) – all new stock</t>
+          <t>UNECO Manufacturing – owners retiring, machine-shop metrology &amp; tooling</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>retirement</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>Thorndike</t>
+          <t>Chicopee</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
@@ -19364,23 +19364,23 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>By appointment</t>
+          <t>Online auction, 18% BP</t>
         </is>
       </c>
       <c r="H14" s="15" t="n"/>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J14" s="13" t="inlineStr"/>
+      <c r="I14" s="13" t="inlineStr"/>
+      <c r="J14" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-04 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>HiBid (DeCosmo Industrial)</t>
         </is>
       </c>
       <c r="L14" s="13" t="inlineStr">
@@ -19396,7 +19396,7 @@
       </c>
       <c r="O14" s="14" t="inlineStr">
         <is>
-          <t>Updated Oct 8. Off-category FYI.</t>
+          <t>Niche tooling only. Bidding opens Oct 19.</t>
         </is>
       </c>
     </row>
@@ -19408,17 +19408,17 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>UNECO Manufacturing – owners retiring, machine-shop metrology &amp; tooling</t>
+          <t>Restaurant closing, everything must go – kitchen equipment, stainless, smallwares</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>retirement</t>
+          <t>restaurant closing</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>Chicopee</t>
+          <t>Westfield</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
@@ -19427,23 +19427,23 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>Online auction, 18% BP</t>
+          <t>Make offer</t>
         </is>
       </c>
       <c r="H15" s="15" t="n"/>
-      <c r="I15" s="13" t="inlineStr"/>
-      <c r="J15" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-04 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J15" s="13" t="inlineStr"/>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>HiBid (DeCosmo Industrial)</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L15" s="13" t="inlineStr">
@@ -19459,120 +19459,120 @@
       </c>
       <c r="O15" s="14" t="inlineStr">
         <is>
-          <t>Niche tooling only. Bidding opens Oct 19.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" outlineLevel="1">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Central / Western MA</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>Restaurant closing, everything must go – kitchen equipment, stainless, smallwares</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>restaurant closing</t>
-        </is>
-      </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>Westfield</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>99</v>
-      </c>
-      <c r="G16" s="13" t="inlineStr">
-        <is>
-          <t>Make offer</t>
-        </is>
-      </c>
-      <c r="H16" s="15" t="n"/>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="J16" s="13" t="inlineStr"/>
-      <c r="K16" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L16" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M16" s="13" t="inlineStr"/>
-      <c r="N16" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O16" s="14" t="inlineStr">
-        <is>
           <t>Related separate post "Complete Restaurant Equipment Package" $3,500 OBO (maybe same restaurant): https://www.craigslist.org/view/d/westfield-complete-restaurant-equipment/9Y5KCdhhgSqEBYbD3wKqVd</t>
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Central / Western MA</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>3 item(s)</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="18" t="n"/>
+      <c r="J16" s="18" t="n"/>
+      <c r="K16" s="18" t="n"/>
+      <c r="L16" s="18" t="n"/>
+      <c r="M16" s="18" t="n"/>
+      <c r="N16" s="18" t="n"/>
+      <c r="O16" s="18" t="n"/>
+    </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Central / Western MA</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>3 item(s)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="n"/>
-      <c r="D17" s="18" t="n"/>
-      <c r="E17" s="18" t="n"/>
-      <c r="F17" s="18" t="n"/>
-      <c r="G17" s="18" t="n"/>
-      <c r="H17" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="18" t="n"/>
-      <c r="J17" s="18" t="n"/>
-      <c r="K17" s="18" t="n"/>
-      <c r="L17" s="18" t="n"/>
-      <c r="M17" s="18" t="n"/>
-      <c r="N17" s="18" t="n"/>
-      <c r="O17" s="18" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>▸ Maine / VT / Northern NH  (5)</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
-      <c r="H18" s="12" t="n"/>
-      <c r="I18" s="12" t="n"/>
-      <c r="J18" s="12" t="n"/>
-      <c r="K18" s="12" t="n"/>
-      <c r="L18" s="12" t="n"/>
-      <c r="M18" s="12" t="n"/>
-      <c r="N18" s="12" t="n"/>
-      <c r="O18" s="12" t="n"/>
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="12" t="n"/>
+      <c r="M17" s="12" t="n"/>
+      <c r="N17" s="12" t="n"/>
+      <c r="O17" s="12" t="n"/>
+    </row>
+    <row r="18" outlineLevel="1">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Maine / VT / Northern NH</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Oola Bowls secured-party sale – restaurant equipment bought new 2024-25 (Electro Freeze, Scotsman, Atosa)</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Scarborough</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>104</v>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>Online auction (freezers $80–150 when seen)</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="n"/>
+      <c r="I18" s="13" t="inlineStr"/>
+      <c r="J18" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 01:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>Keenan Auction / Proxibid</t>
+        </is>
+      </c>
+      <c r="L18" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M18" s="13" t="inlineStr"/>
+      <c r="N18" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O18" s="14" t="inlineStr">
+        <is>
+          <t>Pickup Oct 21 only.</t>
+        </is>
+      </c>
     </row>
     <row r="19" outlineLevel="1">
       <c r="A19" s="13" t="inlineStr">
@@ -19582,12 +19582,12 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>Oola Bowls secured-party sale – restaurant equipment bought new 2024-25 (Electro Freeze, Scotsman, Atosa)</t>
+          <t>Contractor appliance lot – 3 refrigerators, Bosch wall oven, gas range, washer/dryer set</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>contractor lot</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
@@ -19605,24 +19605,24 @@
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>Online auction (freezers $80–150 when seen)</t>
+          <t>$200 OBO each, less as a bundle</t>
         </is>
       </c>
       <c r="H19" s="15" t="n"/>
-      <c r="I19" s="13" t="inlineStr"/>
-      <c r="J19" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-19 01:00 PM ET</t>
-        </is>
-      </c>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="J19" s="13" t="inlineStr"/>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>Keenan Auction / Proxibid</t>
-        </is>
-      </c>
-      <c r="L19" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L19" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M19" s="13" t="inlineStr"/>
@@ -19633,7 +19633,7 @@
       </c>
       <c r="O19" s="14" t="inlineStr">
         <is>
-          <t>Pickup Oct 21 only.</t>
+          <t>Working units pulled from jobs. Complete appliances, not parts.</t>
         </is>
       </c>
     </row>
@@ -19645,17 +19645,17 @@
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>Contractor appliance lot – 3 refrigerators, Bosch wall oven, gas range, washer/dryer set</t>
+          <t>Event-rental business closing – 300+ chairs, 40+ rounds, 1,300+ china, linens (all at once)</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>contractor lot</t>
+          <t>business closing</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>Scarborough</t>
+          <t>Woolwich</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
@@ -19664,17 +19664,17 @@
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>$200 OBO each, less as a bundle</t>
+          <t>No price listed</t>
         </is>
       </c>
       <c r="H20" s="15" t="n"/>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J20" s="13" t="inlineStr"/>
@@ -19696,7 +19696,7 @@
       </c>
       <c r="O20" s="14" t="inlineStr">
         <is>
-          <t>Working units pulled from jobs. Complete appliances, not parts.</t>
+          <t>Updated Oct 7. Replacement cost &gt;$72K per post.</t>
         </is>
       </c>
     </row>
@@ -19708,42 +19708,42 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>Event-rental business closing – 300+ chairs, 40+ rounds, 1,300+ china, linens (all at once)</t>
+          <t>Pellet/wood stoves, heating stock, tools &amp; heavy equipment – "business liquidation", 380 lots</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>business closing</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>Woolwich</t>
+          <t>Lunenburg</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>ME</t>
+          <t>VT</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
-          <t>No price listed</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H21" s="15" t="n"/>
-      <c r="I21" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="J21" s="13" t="inlineStr"/>
+      <c r="I21" s="13" t="inlineStr"/>
+      <c r="J21" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-04 10:00 AM ET</t>
+        </is>
+      </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>Thomas Hirchak Co.</t>
         </is>
       </c>
       <c r="L21" s="13" t="inlineStr">
@@ -19759,7 +19759,7 @@
       </c>
       <c r="O21" s="14" t="inlineStr">
         <is>
-          <t>Updated Oct 7. Replacement cost &gt;$72K per post.</t>
+          <t>Closes Wed Nov 4 10 AM, preview Oct 28, removal Nov 9, no shipping.</t>
         </is>
       </c>
     </row>
@@ -19771,17 +19771,17 @@
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>Pellet/wood stoves, heating stock, tools &amp; heavy equipment – "business liquidation", 380 lots</t>
+          <t>Bread Loaf Corp wind-down – contractor equipment, staging, telehandler</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>contractor liquidation</t>
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>Lunenburg</t>
+          <t>Middlebury</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
@@ -19790,7 +19790,7 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
@@ -19801,12 +19801,12 @@
       <c r="I22" s="13" t="inlineStr"/>
       <c r="J22" s="13" t="inlineStr">
         <is>
-          <t>2026-11-04 10:00 AM ET</t>
+          <t>2026-10-28 09:00 AM ET</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>Thomas Hirchak Co.</t>
+          <t>THC Auction</t>
         </is>
       </c>
       <c r="L22" s="13" t="inlineStr">
@@ -19822,120 +19822,120 @@
       </c>
       <c r="O22" s="14" t="inlineStr">
         <is>
-          <t>Closes Wed Nov 4 10 AM, preview Oct 28, removal Nov 9, no shipping.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" outlineLevel="1">
-      <c r="A23" s="13" t="inlineStr">
-        <is>
-          <t>Maine / VT / Northern NH</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="inlineStr">
-        <is>
-          <t>Bread Loaf Corp wind-down – contractor equipment, staging, telehandler</t>
-        </is>
-      </c>
-      <c r="C23" s="13" t="inlineStr">
+          <t>Company wind-down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Maine / VT / Northern NH</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="inlineStr">
+        <is>
+          <t>5 item(s)</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="18" t="n"/>
+      <c r="G23" s="18" t="n"/>
+      <c r="H23" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="18" t="n"/>
+      <c r="J23" s="18" t="n"/>
+      <c r="K23" s="18" t="n"/>
+      <c r="L23" s="18" t="n"/>
+      <c r="M23" s="18" t="n"/>
+      <c r="N23" s="18" t="n"/>
+      <c r="O23" s="18" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>▸ CT / Hudson Valley  (6)</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="12" t="n"/>
+      <c r="G24" s="12" t="n"/>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="12" t="n"/>
+      <c r="N24" s="12" t="n"/>
+      <c r="O24" s="12" t="n"/>
+    </row>
+    <row r="25" outlineLevel="1">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>CT / Hudson Valley</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="inlineStr">
+        <is>
+          <t>Bank-ordered electrical contractor sale – Greenlee/Hilti/Milwaukee tools, GE/Siemens breakers</t>
+        </is>
+      </c>
+      <c r="C25" s="13" t="inlineStr">
         <is>
           <t>contractor liquidation</t>
         </is>
       </c>
-      <c r="D23" s="13" t="inlineStr">
-        <is>
-          <t>Middlebury</t>
-        </is>
-      </c>
-      <c r="E23" s="13" t="inlineStr">
-        <is>
-          <t>VT</t>
-        </is>
-      </c>
-      <c r="F23" s="13" t="n">
-        <v>177</v>
-      </c>
-      <c r="G23" s="13" t="inlineStr">
+      <c r="D25" s="13" t="inlineStr">
+        <is>
+          <t>Clinton</t>
+        </is>
+      </c>
+      <c r="E25" s="13" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="F25" s="13" t="n">
+        <v>106</v>
+      </c>
+      <c r="G25" s="13" t="inlineStr">
         <is>
           <t>Online auction</t>
         </is>
       </c>
-      <c r="H23" s="15" t="n"/>
-      <c r="I23" s="13" t="inlineStr"/>
-      <c r="J23" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-28 09:00 AM ET</t>
-        </is>
-      </c>
-      <c r="K23" s="13" t="inlineStr">
-        <is>
-          <t>THC Auction</t>
-        </is>
-      </c>
-      <c r="L23" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M23" s="13" t="inlineStr"/>
-      <c r="N23" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O23" s="14" t="inlineStr">
-        <is>
-          <t>Company wind-down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Maine / VT / Northern NH</t>
-        </is>
-      </c>
-      <c r="B24" s="17" t="inlineStr">
-        <is>
-          <t>5 item(s)</t>
-        </is>
-      </c>
-      <c r="C24" s="18" t="n"/>
-      <c r="D24" s="18" t="n"/>
-      <c r="E24" s="18" t="n"/>
-      <c r="F24" s="18" t="n"/>
-      <c r="G24" s="18" t="n"/>
-      <c r="H24" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="18" t="n"/>
-      <c r="J24" s="18" t="n"/>
-      <c r="K24" s="18" t="n"/>
-      <c r="L24" s="18" t="n"/>
-      <c r="M24" s="18" t="n"/>
-      <c r="N24" s="18" t="n"/>
-      <c r="O24" s="18" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="inlineStr">
-        <is>
-          <t>▸ CT / Hudson Valley  (5)</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="12" t="n"/>
-      <c r="F25" s="12" t="n"/>
-      <c r="G25" s="12" t="n"/>
-      <c r="H25" s="12" t="n"/>
-      <c r="I25" s="12" t="n"/>
-      <c r="J25" s="12" t="n"/>
-      <c r="K25" s="12" t="n"/>
-      <c r="L25" s="12" t="n"/>
-      <c r="M25" s="12" t="n"/>
-      <c r="N25" s="12" t="n"/>
-      <c r="O25" s="12" t="n"/>
+      <c r="H25" s="15" t="n"/>
+      <c r="I25" s="13" t="inlineStr"/>
+      <c r="J25" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-29 05:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K25" s="13" t="inlineStr">
+        <is>
+          <t>Hamilton Group / EstateSales.net</t>
+        </is>
+      </c>
+      <c r="L25" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M25" s="13" t="inlineStr"/>
+      <c r="N25" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O25" s="14" t="inlineStr">
+        <is>
+          <t>Listed "Oct 29 2 PM PST" (= 5 PM ET).</t>
+        </is>
+      </c>
     </row>
     <row r="26" outlineLevel="1">
       <c r="A26" s="13" t="inlineStr">
@@ -19945,26 +19945,26 @@
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>Bank-ordered electrical contractor sale – Greenlee/Hilti/Milwaukee tools, GE/Siemens breakers</t>
+          <t>Major Intl Chain Surplus – 225 lots commercial refrigeration/kitchen (True, Traulsen, Hobart, Blodgett, Taylor)</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>contractor liquidation</t>
+          <t>commercial surplus</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>Clinton</t>
+          <t>Pleasant Valley</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>106</v>
+        <v>157</v>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
@@ -19975,17 +19975,17 @@
       <c r="I26" s="13" t="inlineStr"/>
       <c r="J26" s="13" t="inlineStr">
         <is>
-          <t>2026-10-29 05:00 PM ET</t>
+          <t>2026-10-20 02:00 PM ET</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>Hamilton Group / EstateSales.net</t>
-        </is>
-      </c>
-      <c r="L26" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Adams / BidWrangler</t>
+        </is>
+      </c>
+      <c r="L26" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M26" s="13" t="inlineStr"/>
@@ -19996,7 +19996,7 @@
       </c>
       <c r="O26" s="14" t="inlineStr">
         <is>
-          <t>Listed "Oct 29 2 PM PST" (= 5 PM ET).</t>
+          <t>Tested and new units.</t>
         </is>
       </c>
     </row>
@@ -20008,42 +20008,46 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>Major Intl Chain Surplus – 225 lots commercial refrigeration/kitchen (True, Traulsen, Hobart, Blodgett, Taylor)</t>
+          <t>The Outlaw Grill Steakhouse – used restaurant equipment auction (PCI Auctions CT, e.g. Vulcan EV60 Endurance 60" range)</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>commercial surplus</t>
+          <t>restaurant auction</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>Pleasant Valley</t>
+          <t>Stamford</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Online auction, current bids</t>
         </is>
       </c>
       <c r="H27" s="15" t="n"/>
-      <c r="I27" s="13" t="inlineStr"/>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="J27" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 02:00 PM ET</t>
+          <t>2026-10-21 08:30 PM ET</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>Adams / BidWrangler</t>
+          <t>PCI Auctions</t>
         </is>
       </c>
       <c r="L27" s="20" t="inlineStr">
@@ -20059,7 +20063,7 @@
       </c>
       <c r="O27" s="14" t="inlineStr">
         <is>
-          <t>Tested and new units.</t>
+          <t>Ends Wed Oct 21 8:30 PM EDT. PCI warehouse, 36 Ludlow St, Stamford CT. Page lists preview Oct 28 and removal Thu Oct 29 11-3 (after close). Shipping/delivery available; payment due on pickup day. Items still being added.</t>
         </is>
       </c>
     </row>
@@ -20071,17 +20075,17 @@
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>The Outlaw Grill Steakhouse – used restaurant equipment auction (PCI Auctions CT, e.g. Vulcan EV60 Endurance 60" range)</t>
+          <t>Café/bakery liquidation – Traulsen, Vulcan ovens, mixers, Hobart slicer (~74 lots)</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>restaurant auction</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>Stamford</t>
+          <t>Greenwich</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -20090,27 +20094,23 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>Online auction, current bids</t>
+          <t>Live auction + webcast</t>
         </is>
       </c>
       <c r="H28" s="15" t="n"/>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
+      <c r="I28" s="13" t="inlineStr"/>
       <c r="J28" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 08:30 PM ET</t>
+          <t>2026-10-21 06:00 PM ET</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>PCI Auctions</t>
+          <t>Best Buy Auctioneers / AuctionGuide</t>
         </is>
       </c>
       <c r="L28" s="20" t="inlineStr">
@@ -20126,7 +20126,7 @@
       </c>
       <c r="O28" s="14" t="inlineStr">
         <is>
-          <t>Ends Wed Oct 21 8:30 PM EDT. PCI warehouse, 36 Ludlow St, Stamford CT. Page lists preview Oct 28 and removal Thu Oct 29 11-3 (after close). Shipping/delivery available; payment due on pickup day. Items still being added.</t>
+          <t>Oct 21; start time not captured (placeholder 6 PM).</t>
         </is>
       </c>
     </row>
@@ -20138,47 +20138,47 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>Café/bakery liquidation – Traulsen, Vulcan ovens, mixers, Hobart slicer (~74 lots)</t>
+          <t>BJ's Wholesale closeout – racking, forklifts, Hobart</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>Greenwich</t>
+          <t>Rotterdam</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
-          <t>Live auction + webcast</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H29" s="15" t="n"/>
       <c r="I29" s="13" t="inlineStr"/>
       <c r="J29" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 06:00 PM ET</t>
+          <t>2026-11-10 10:00 AM ET</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>Best Buy Auctioneers / AuctionGuide</t>
-        </is>
-      </c>
-      <c r="L29" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L29" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M29" s="13" t="inlineStr"/>
@@ -20189,7 +20189,7 @@
       </c>
       <c r="O29" s="14" t="inlineStr">
         <is>
-          <t>Oct 21; start time not captured (placeholder 6 PM).</t>
+          <t>Closes from Nov 10 10 AM.</t>
         </is>
       </c>
     </row>
@@ -20201,17 +20201,17 @@
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>BJ's Wholesale closeout – racking, forklifts, Hobart</t>
+          <t>Body shop closing after 50 years – tools, welder, generators, plasma</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>tools liquidation</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>Rotterdam</t>
+          <t>West Nyack</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
@@ -20220,23 +20220,23 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Make offer / lot</t>
         </is>
       </c>
       <c r="H30" s="15" t="n"/>
-      <c r="I30" s="13" t="inlineStr"/>
-      <c r="J30" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-10 10:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J30" s="13" t="inlineStr"/>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L30" s="13" t="inlineStr">
@@ -20252,7 +20252,7 @@
       </c>
       <c r="O30" s="14" t="inlineStr">
         <is>
-          <t>Closes from Nov 10 10 AM.</t>
+          <t>One-man auto body shop closing/retirement (Park Ridge / West Nyack NY-NJ border). Heat lamps, Kansas jack pullers, Miller 200 welder, generators, sheet-metal brake, hydraulic press, plasma cutter, engine hoist. Posted Aug 16; still open 2026-10-19.</t>
         </is>
       </c>
     </row>
@@ -20264,7 +20264,7 @@
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>5 item(s)</t>
+          <t>6 item(s)</t>
         </is>
       </c>
       <c r="C31" s="18" t="n"/>
@@ -20286,7 +20286,7 @@
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>▸ NYC / Long Island / NJ  (21)</t>
+          <t>▸ NYC / Long Island / NJ  (24)</t>
         </is>
       </c>
       <c r="B32" s="12" t="n"/>
@@ -21021,17 +21021,17 @@
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>Serpico's Pizzeria (lost lease) – Bari ovens, walk-in, Hobart 60qt, Vulcan range</t>
+          <t>Air Systems Inc – sheet metal / HVAC fabrication shop liquidation</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>HVAC shop liquidation</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>Allenhurst</t>
+          <t>Kenilworth</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -21040,28 +21040,28 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>No-reserve online auction</t>
+          <t>Timed online (15% BP)</t>
         </is>
       </c>
       <c r="H44" s="15" t="n"/>
       <c r="I44" s="13" t="inlineStr"/>
       <c r="J44" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 11:00 AM ET</t>
+          <t>2026-10-29 11:00 AM ET</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>Peter Costanzo / EstateSales.net</t>
-        </is>
-      </c>
-      <c r="L44" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>A.J. Willner Auctions</t>
+        </is>
+      </c>
+      <c r="L44" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M44" s="13" t="inlineStr"/>
@@ -21072,7 +21072,7 @@
       </c>
       <c r="O44" s="14" t="inlineStr">
         <is>
-          <t>Absolute / no reserve.</t>
+          <t>Vicon HVAC plasma; Flagler/Lockformer/Roto-Die/Engel fab; welders; Clark forklift; Genie Superlift; Ridgid/Milwaukee/DeWalt/Bosch/Hilti/Makita tools; AeroVent/Carnes exhaust fans; racking/scaffolding. Preview Oct 28–29 AM; pickup Oct 29 PM–Nov 4. Same town as Carnes fan CL lot.</t>
         </is>
       </c>
     </row>
@@ -21084,17 +21084,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>Altitude Trampoline Park liquidation – partial: Atosa, TurboChef, stainless</t>
+          <t>Serpico's Pizzeria (lost lease) – Bari ovens, walk-in, Hobart 60qt, Vulcan range</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>facility contents</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>Iselin</t>
+          <t>Allenhurst</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -21103,11 +21103,11 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>No-reserve online auction</t>
         </is>
       </c>
       <c r="H45" s="15" t="n"/>
@@ -21119,7 +21119,7 @@
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>Peter Costanzo / EstateSales.net</t>
         </is>
       </c>
       <c r="L45" s="20" t="inlineStr">
@@ -21135,7 +21135,7 @@
       </c>
       <c r="O45" s="14" t="inlineStr">
         <is>
-          <t>Some kitchen gear only.</t>
+          <t>Absolute / no reserve.</t>
         </is>
       </c>
     </row>
@@ -21147,17 +21147,17 @@
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>Restaurant / pizzeria (contents not described)</t>
+          <t>Altitude Trampoline Park liquidation – partial: Atosa, TurboChef, stainless</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>facility contents</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>Berkeley Heights</t>
+          <t>Iselin</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -21166,27 +21166,23 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H46" s="15" t="n"/>
-      <c r="I46" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
+      <c r="I46" s="13" t="inlineStr"/>
       <c r="J46" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 02:00 PM ET</t>
+          <t>2026-10-21 11:00 AM ET</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L46" s="20" t="inlineStr">
@@ -21202,7 +21198,7 @@
       </c>
       <c r="O46" s="14" t="inlineStr">
         <is>
-          <t>Tue Oct 20 2 PM. No item description on page.</t>
+          <t>Some kitchen gear only.</t>
         </is>
       </c>
     </row>
@@ -21214,17 +21210,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
+          <t>Restaurant / pizzeria (contents not described)</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>lien sale</t>
+          <t>restaurant closing</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>Edison</t>
+          <t>Berkeley Heights</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -21233,24 +21229,32 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
-          <t>Online auction, $2K load-out fee</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H47" s="15" t="n"/>
-      <c r="I47" s="13" t="inlineStr"/>
-      <c r="J47" s="13" t="inlineStr"/>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J47" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-20 02:00 PM ET</t>
+        </is>
+      </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
-        </is>
-      </c>
-      <c r="L47" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L47" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M47" s="13" t="inlineStr"/>
@@ -21261,7 +21265,7 @@
       </c>
       <c r="O47" s="14" t="inlineStr">
         <is>
-          <t>&gt;$100K new. Close date not captured.</t>
+          <t>Tue Oct 20 2 PM. No item description on page.</t>
         </is>
       </c>
     </row>
@@ -21273,12 +21277,12 @@
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
+          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>lien sale</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
@@ -21296,23 +21300,15 @@
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>Live + HiBid webcast, 18% BP + 3% card</t>
+          <t>Online auction, $2K load-out fee</t>
         </is>
       </c>
       <c r="H48" s="15" t="n"/>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="J48" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-25 01:00 PM ET</t>
-        </is>
-      </c>
+      <c r="I48" s="13" t="inlineStr"/>
+      <c r="J48" s="13" t="inlineStr"/>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L48" s="13" t="inlineStr">
@@ -21320,11 +21316,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M48" s="21" t="inlineStr">
-        <is>
-          <t>FLIP</t>
-        </is>
-      </c>
+      <c r="M48" s="13" t="inlineStr"/>
       <c r="N48" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -21332,7 +21324,7 @@
       </c>
       <c r="O48" s="14" t="inlineStr">
         <is>
-          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
+          <t>&gt;$100K new. Close date not captured.</t>
         </is>
       </c>
     </row>
@@ -21344,17 +21336,17 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
+          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>East Brunswick</t>
+          <t>Edison</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -21363,23 +21355,27 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Live + HiBid webcast, 18% BP + 3% card</t>
         </is>
       </c>
       <c r="H49" s="15" t="n"/>
-      <c r="I49" s="13" t="inlineStr"/>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="J49" s="13" t="inlineStr">
         <is>
-          <t>2026-11-03 11:00 AM ET</t>
+          <t>2026-10-25 01:00 PM ET</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
       <c r="L49" s="13" t="inlineStr">
@@ -21387,7 +21383,11 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M49" s="13" t="inlineStr"/>
+      <c r="M49" s="21" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
       <c r="N49" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -21395,7 +21395,7 @@
       </c>
       <c r="O49" s="14" t="inlineStr">
         <is>
-          <t>Store inventory.</t>
+          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
         </is>
       </c>
     </row>
@@ -21407,17 +21407,17 @@
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>High-end deli (contents not described)</t>
+          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>Manalapan Township</t>
+          <t>East Brunswick</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -21426,32 +21426,28 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H50" s="15" t="n"/>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+      <c r="I50" s="13" t="inlineStr"/>
       <c r="J50" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 04:00 PM ET</t>
+          <t>2026-11-03 11:00 AM ET</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
-        </is>
-      </c>
-      <c r="L50" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>A.J. Willner</t>
+        </is>
+      </c>
+      <c r="L50" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M50" s="13" t="inlineStr"/>
@@ -21462,7 +21458,7 @@
       </c>
       <c r="O50" s="14" t="inlineStr">
         <is>
-          <t>Mon Oct 19 4 PM. No item description on page.</t>
+          <t>Store inventory.</t>
         </is>
       </c>
     </row>
@@ -21474,17 +21470,17 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
+          <t>High-end deli (contents not described)</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>showroom closing</t>
+          <t>restaurant closing</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>Lawrenceville</t>
+          <t>Manalapan Township</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -21493,28 +21489,32 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>239</v>
+        <v>223</v>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>
-          <t>Online auction, 18% BP</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H51" s="15" t="n"/>
-      <c r="I51" s="13" t="inlineStr"/>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="J51" s="13" t="inlineStr">
         <is>
-          <t>2026-10-27 09:00 AM ET</t>
+          <t>2026-10-19 04:00 PM ET</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L51" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L51" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M51" s="13" t="inlineStr"/>
@@ -21525,7 +21525,7 @@
       </c>
       <c r="O51" s="14" t="inlineStr">
         <is>
-          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
+          <t>Mon Oct 19 4 PM. No item description on page.</t>
         </is>
       </c>
     </row>
@@ -21537,17 +21537,17 @@
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>Milwaukee / Walmart / hardware store mega auction pt 3</t>
+          <t>Bakery/Cafe Somerville NJ – rack ovens, La Marzocco, food truck (~76 lots)</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>Mount Holly</t>
+          <t>Somerville</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -21556,28 +21556,32 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>254</v>
+        <v>224</v>
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
-          <t>HiBid online auction</t>
+          <t>Live webcast + online (18% BP online)</t>
         </is>
       </c>
       <c r="H52" s="15" t="n"/>
-      <c r="I52" s="13" t="inlineStr"/>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="J52" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 06:00 PM ET</t>
+          <t>2026-10-26 02:00 PM ET</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>HiBid</t>
-        </is>
-      </c>
-      <c r="L52" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>HiBid / Best Buy Auctioneers</t>
+        </is>
+      </c>
+      <c r="L52" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M52" s="13" t="inlineStr"/>
@@ -21588,7 +21592,7 @@
       </c>
       <c r="O52" s="14" t="inlineStr">
         <is>
-          <t>Close Oct 18 or 19 6 PM (later used).</t>
+          <t>Full bakery/cafe commercial kitchen: food truck w/ pizza oven, La Marzocco espresso, Mazzer, Baxter + Empire Logiudice rack ovens, dough depositor, Globe floor mixer, Artic Air / SS refrigeration, fryers, Vitamix, Robot Coupe, display cases, dining furniture. Preview 11 AM sale day; checkout Tue 10/27.</t>
         </is>
       </c>
     </row>
@@ -21600,17 +21604,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
+          <t>Ability to Work kitchen and store – commercial kitchen + store fixtures (~135 lots)</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>showroom closing</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>Cherry Hill</t>
+          <t>Flemington</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -21619,23 +21623,23 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>266</v>
+        <v>237</v>
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
-          <t>Online auction, openers ~$0.50</t>
+          <t>Timed online (15% BP)</t>
         </is>
       </c>
       <c r="H53" s="15" t="n"/>
       <c r="I53" s="13" t="inlineStr"/>
       <c r="J53" s="13" t="inlineStr">
         <is>
-          <t>2026-11-02 11:00 AM ET</t>
+          <t>2026-10-27 11:02 AM ET</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
+          <t>HiBid</t>
         </is>
       </c>
       <c r="L53" s="13" t="inlineStr">
@@ -21651,107 +21655,185 @@
       </c>
       <c r="O53" s="14" t="inlineStr">
         <is>
-          <t>Lots close from Nov 2 11 AM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — NYC / Long Island / NJ</t>
-        </is>
-      </c>
-      <c r="B54" s="17" t="inlineStr">
-        <is>
-          <t>21 item(s)</t>
-        </is>
-      </c>
-      <c r="C54" s="18" t="n"/>
-      <c r="D54" s="18" t="n"/>
-      <c r="E54" s="18" t="n"/>
-      <c r="F54" s="18" t="n"/>
-      <c r="G54" s="18" t="n"/>
-      <c r="H54" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="18" t="n"/>
-      <c r="J54" s="18" t="n"/>
-      <c r="K54" s="18" t="n"/>
-      <c r="L54" s="18" t="n"/>
-      <c r="M54" s="18" t="n"/>
-      <c r="N54" s="18" t="n"/>
-      <c r="O54" s="18" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>▸ Eastern PA / Mid-Atlantic  (1)</t>
-        </is>
-      </c>
-      <c r="B55" s="12" t="n"/>
-      <c r="C55" s="12" t="n"/>
-      <c r="D55" s="12" t="n"/>
-      <c r="E55" s="12" t="n"/>
-      <c r="F55" s="12" t="n"/>
-      <c r="G55" s="12" t="n"/>
-      <c r="H55" s="12" t="n"/>
-      <c r="I55" s="12" t="n"/>
-      <c r="J55" s="12" t="n"/>
-      <c r="K55" s="12" t="n"/>
-      <c r="L55" s="12" t="n"/>
-      <c r="M55" s="12" t="n"/>
-      <c r="N55" s="12" t="n"/>
-      <c r="O55" s="12" t="n"/>
+          <t>Apprentice/hospitality training cafe-kitchen and store dispersal. Preview 9–11 AM sale day; removal Oct 27 noon–Oct 29.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" outlineLevel="1">
+      <c r="A54" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B54" s="14" t="inlineStr">
+        <is>
+          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
+        </is>
+      </c>
+      <c r="C54" s="13" t="inlineStr">
+        <is>
+          <t>showroom closing</t>
+        </is>
+      </c>
+      <c r="D54" s="13" t="inlineStr">
+        <is>
+          <t>Lawrenceville</t>
+        </is>
+      </c>
+      <c r="E54" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F54" s="13" t="n">
+        <v>239</v>
+      </c>
+      <c r="G54" s="13" t="inlineStr">
+        <is>
+          <t>Online auction, 18% BP</t>
+        </is>
+      </c>
+      <c r="H54" s="15" t="n"/>
+      <c r="I54" s="13" t="inlineStr"/>
+      <c r="J54" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K54" s="13" t="inlineStr">
+        <is>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L54" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M54" s="13" t="inlineStr"/>
+      <c r="N54" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O54" s="14" t="inlineStr">
+        <is>
+          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" outlineLevel="1">
+      <c r="A55" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B55" s="14" t="inlineStr">
+        <is>
+          <t>Milwaukee / Walmart / hardware store mega auction pt 3</t>
+        </is>
+      </c>
+      <c r="C55" s="13" t="inlineStr">
+        <is>
+          <t>inventory</t>
+        </is>
+      </c>
+      <c r="D55" s="13" t="inlineStr">
+        <is>
+          <t>Mount Holly</t>
+        </is>
+      </c>
+      <c r="E55" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F55" s="13" t="n">
+        <v>254</v>
+      </c>
+      <c r="G55" s="13" t="inlineStr">
+        <is>
+          <t>HiBid online auction</t>
+        </is>
+      </c>
+      <c r="H55" s="15" t="n"/>
+      <c r="I55" s="13" t="inlineStr"/>
+      <c r="J55" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K55" s="13" t="inlineStr">
+        <is>
+          <t>HiBid</t>
+        </is>
+      </c>
+      <c r="L55" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M55" s="13" t="inlineStr"/>
+      <c r="N55" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O55" s="14" t="inlineStr">
+        <is>
+          <t>Close Oct 18 or 19 6 PM (later used).</t>
+        </is>
+      </c>
     </row>
     <row r="56" outlineLevel="1">
       <c r="A56" s="13" t="inlineStr">
         <is>
-          <t>Eastern PA / Mid-Atlantic</t>
+          <t>NYC / Long Island / NJ</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>October restaurant consignment – Hobart, Rational, True + NEW scratch-and-dent Migali/Avantco</t>
+          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>showroom closing</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>Harrisburg</t>
+          <t>Cherry Hill</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>340</v>
+        <v>266</v>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>Online auction, 15% BP, ships $55/pallet</t>
+          <t>Online auction, openers ~$0.50</t>
         </is>
       </c>
       <c r="H56" s="15" t="n"/>
       <c r="I56" s="13" t="inlineStr"/>
       <c r="J56" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 11:00 AM ET</t>
+          <t>2026-11-02 11:00 AM ET</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>Restaurant Auction Co</t>
-        </is>
-      </c>
-      <c r="L56" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L56" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M56" s="13" t="inlineStr"/>
@@ -21762,19 +21844,19 @@
       </c>
       <c r="O56" s="14" t="inlineStr">
         <is>
-          <t>Closes Oct 21 10 or 11 AM (later used). Shippable.</t>
+          <t>Lots close from Nov 2 11 AM.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="17" t="inlineStr">
         <is>
-          <t>Subtotal — Eastern PA / Mid-Atlantic</t>
+          <t>Subtotal — NYC / Long Island / NJ</t>
         </is>
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>1 item(s)</t>
+          <t>24 item(s)</t>
         </is>
       </c>
       <c r="C57" s="18" t="n"/>
@@ -21796,7 +21878,7 @@
     <row r="58">
       <c r="A58" s="11" t="inlineStr">
         <is>
-          <t>▸ Upstate / Western NY  (3)</t>
+          <t>▸ Eastern PA / Mid-Atlantic  (1)</t>
         </is>
       </c>
       <c r="B58" s="12" t="n"/>
@@ -21817,12 +21899,12 @@
     <row r="59" outlineLevel="1">
       <c r="A59" s="13" t="inlineStr">
         <is>
-          <t>Upstate / Western NY</t>
+          <t>Eastern PA / Mid-Atlantic</t>
         </is>
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>Former Taco Del Mar – stainless, warmers, walk-in panels</t>
+          <t>October restaurant consignment – Hobart, Rational, True + NEW scratch-and-dent Migali/Avantco</t>
         </is>
       </c>
       <c r="C59" s="13" t="inlineStr">
@@ -21832,32 +21914,32 @@
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
-          <t>Watson</t>
+          <t>Harrisburg</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>260</v>
+        <v>340</v>
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
-          <t>HiBid online auction</t>
+          <t>Online auction, 15% BP, ships $55/pallet</t>
         </is>
       </c>
       <c r="H59" s="15" t="n"/>
       <c r="I59" s="13" t="inlineStr"/>
       <c r="J59" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 06:00 PM ET</t>
+          <t>2026-10-21 11:00 AM ET</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>Adirondack Asset / HiBid</t>
+          <t>Restaurant Auction Co</t>
         </is>
       </c>
       <c r="L59" s="20" t="inlineStr">
@@ -21873,228 +21955,228 @@
       </c>
       <c r="O59" s="14" t="inlineStr">
         <is>
+          <t>Closes Oct 21 10 or 11 AM (later used). Shippable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Eastern PA / Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>1 item(s)</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="n"/>
+      <c r="D60" s="18" t="n"/>
+      <c r="E60" s="18" t="n"/>
+      <c r="F60" s="18" t="n"/>
+      <c r="G60" s="18" t="n"/>
+      <c r="H60" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="18" t="n"/>
+      <c r="J60" s="18" t="n"/>
+      <c r="K60" s="18" t="n"/>
+      <c r="L60" s="18" t="n"/>
+      <c r="M60" s="18" t="n"/>
+      <c r="N60" s="18" t="n"/>
+      <c r="O60" s="18" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>▸ Upstate / Western NY  (3)</t>
+        </is>
+      </c>
+      <c r="B61" s="12" t="n"/>
+      <c r="C61" s="12" t="n"/>
+      <c r="D61" s="12" t="n"/>
+      <c r="E61" s="12" t="n"/>
+      <c r="F61" s="12" t="n"/>
+      <c r="G61" s="12" t="n"/>
+      <c r="H61" s="12" t="n"/>
+      <c r="I61" s="12" t="n"/>
+      <c r="J61" s="12" t="n"/>
+      <c r="K61" s="12" t="n"/>
+      <c r="L61" s="12" t="n"/>
+      <c r="M61" s="12" t="n"/>
+      <c r="N61" s="12" t="n"/>
+      <c r="O61" s="12" t="n"/>
+    </row>
+    <row r="62" outlineLevel="1">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>Upstate / Western NY</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>Former Taco Del Mar – stainless, warmers, walk-in panels</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="D62" s="13" t="inlineStr">
+        <is>
+          <t>Watson</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F62" s="13" t="n">
+        <v>260</v>
+      </c>
+      <c r="G62" s="13" t="inlineStr">
+        <is>
+          <t>HiBid online auction</t>
+        </is>
+      </c>
+      <c r="H62" s="15" t="n"/>
+      <c r="I62" s="13" t="inlineStr"/>
+      <c r="J62" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="inlineStr">
+        <is>
+          <t>Adirondack Asset / HiBid</t>
+        </is>
+      </c>
+      <c r="L62" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M62" s="13" t="inlineStr"/>
+      <c r="N62" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O62" s="14" t="inlineStr">
+        <is>
           <t>Small lot.</t>
         </is>
       </c>
     </row>
-    <row r="60" outlineLevel="1">
-      <c r="A60" s="13" t="inlineStr">
+    <row r="63" outlineLevel="1">
+      <c r="A63" s="13" t="inlineStr">
         <is>
           <t>Upstate / Western NY</t>
         </is>
       </c>
-      <c r="B60" s="14" t="inlineStr">
+      <c r="B63" s="14" t="inlineStr">
         <is>
           <t>Closed restaurant – coolers, fridges, prep tables</t>
         </is>
       </c>
-      <c r="C60" s="13" t="inlineStr">
+      <c r="C63" s="13" t="inlineStr">
         <is>
           <t>restaurant</t>
         </is>
       </c>
-      <c r="D60" s="13" t="inlineStr">
+      <c r="D63" s="13" t="inlineStr">
         <is>
           <t>Palmyra</t>
         </is>
       </c>
-      <c r="E60" s="13" t="inlineStr">
+      <c r="E63" s="13" t="inlineStr">
         <is>
           <t>NY</t>
         </is>
       </c>
-      <c r="F60" s="13" t="n">
+      <c r="F63" s="13" t="n">
         <v>333</v>
       </c>
-      <c r="G60" s="13" t="inlineStr">
+      <c r="G63" s="13" t="inlineStr">
         <is>
           <t>HiBid, 15% BP</t>
         </is>
       </c>
-      <c r="H60" s="15" t="n"/>
-      <c r="I60" s="13" t="inlineStr"/>
-      <c r="J60" s="13" t="inlineStr">
+      <c r="H63" s="15" t="n"/>
+      <c r="I63" s="13" t="inlineStr"/>
+      <c r="J63" s="13" t="inlineStr">
         <is>
           <t>2026-10-19 07:00 PM ET</t>
         </is>
       </c>
-      <c r="K60" s="13" t="inlineStr">
+      <c r="K63" s="13" t="inlineStr">
         <is>
           <t>Reynolds Auction Co / HiBid</t>
         </is>
       </c>
-      <c r="L60" s="20" t="inlineStr">
+      <c r="L63" s="20" t="inlineStr">
         <is>
           <t>ENDING SOON</t>
         </is>
       </c>
-      <c r="M60" s="13" t="inlineStr"/>
-      <c r="N60" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O60" s="14" t="inlineStr">
+      <c r="M63" s="13" t="inlineStr"/>
+      <c r="N63" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O63" s="14" t="inlineStr">
         <is>
           <t>No new out-of-state bidders. Small.</t>
         </is>
       </c>
-    </row>
-    <row r="61" outlineLevel="1">
-      <c r="A61" s="13" t="inlineStr">
-        <is>
-          <t>Upstate / Western NY</t>
-        </is>
-      </c>
-      <c r="B61" s="14" t="inlineStr">
-        <is>
-          <t>Restaurant &amp; fitness equipment</t>
-        </is>
-      </c>
-      <c r="C61" s="13" t="inlineStr">
-        <is>
-          <t>restaurant</t>
-        </is>
-      </c>
-      <c r="D61" s="13" t="inlineStr">
-        <is>
-          <t>Williamsville</t>
-        </is>
-      </c>
-      <c r="E61" s="13" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="F61" s="13" t="n">
-        <v>408</v>
-      </c>
-      <c r="G61" s="13" t="inlineStr">
-        <is>
-          <t>Online auction</t>
-        </is>
-      </c>
-      <c r="H61" s="15" t="n"/>
-      <c r="I61" s="13" t="inlineStr"/>
-      <c r="J61" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-26 07:30 PM ET</t>
-        </is>
-      </c>
-      <c r="K61" s="13" t="inlineStr">
-        <is>
-          <t>Cash Auctions</t>
-        </is>
-      </c>
-      <c r="L61" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M61" s="13" t="inlineStr"/>
-      <c r="N61" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O61" s="14" t="inlineStr">
-        <is>
-          <t>Lots not reviewed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Upstate / Western NY</t>
-        </is>
-      </c>
-      <c r="B62" s="17" t="inlineStr">
-        <is>
-          <t>3 item(s)</t>
-        </is>
-      </c>
-      <c r="C62" s="18" t="n"/>
-      <c r="D62" s="18" t="n"/>
-      <c r="E62" s="18" t="n"/>
-      <c r="F62" s="18" t="n"/>
-      <c r="G62" s="18" t="n"/>
-      <c r="H62" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="18" t="n"/>
-      <c r="J62" s="18" t="n"/>
-      <c r="K62" s="18" t="n"/>
-      <c r="L62" s="18" t="n"/>
-      <c r="M62" s="18" t="n"/>
-      <c r="N62" s="18" t="n"/>
-      <c r="O62" s="18" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="11" t="inlineStr">
-        <is>
-          <t>▸ Virginia  (1)</t>
-        </is>
-      </c>
-      <c r="B63" s="12" t="n"/>
-      <c r="C63" s="12" t="n"/>
-      <c r="D63" s="12" t="n"/>
-      <c r="E63" s="12" t="n"/>
-      <c r="F63" s="12" t="n"/>
-      <c r="G63" s="12" t="n"/>
-      <c r="H63" s="12" t="n"/>
-      <c r="I63" s="12" t="n"/>
-      <c r="J63" s="12" t="n"/>
-      <c r="K63" s="12" t="n"/>
-      <c r="L63" s="12" t="n"/>
-      <c r="M63" s="12" t="n"/>
-      <c r="N63" s="12" t="n"/>
-      <c r="O63" s="12" t="n"/>
     </row>
     <row r="64" outlineLevel="1">
       <c r="A64" s="13" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Upstate / Western NY</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>Haynes Furniture / The Dump – 12 stores closing (furniture, mattresses)</t>
+          <t>Restaurant &amp; fitness equipment</t>
         </is>
       </c>
       <c r="C64" s="13" t="inlineStr">
         <is>
-          <t>retail GOB</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
-          <t>Virginia Beach</t>
+          <t>Williamsville</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>456</v>
+        <v>408</v>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>Retail GOB markdowns</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H64" s="15" t="n"/>
-      <c r="I64" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="J64" s="13" t="inlineStr"/>
+      <c r="I64" s="13" t="inlineStr"/>
+      <c r="J64" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-26 07:30 PM ET</t>
+        </is>
+      </c>
       <c r="K64" s="13" t="inlineStr">
         <is>
-          <t>SB360 (PR Newswire)</t>
+          <t>Cash Auctions</t>
         </is>
       </c>
       <c r="L64" s="13" t="inlineStr">
@@ -22110,19 +22192,19 @@
       </c>
       <c r="O64" s="14" t="inlineStr">
         <is>
-          <t>Posted Oct 8. Multi-state (VA/AZ/GA/IL/TX); pinned at Virginia Beach. Home goods only.</t>
+          <t>Lots not reviewed.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="17" t="inlineStr">
         <is>
-          <t>Subtotal — Virginia</t>
+          <t>Subtotal — Upstate / Western NY</t>
         </is>
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>1 item(s)</t>
+          <t>3 item(s)</t>
         </is>
       </c>
       <c r="C65" s="18" t="n"/>
@@ -22144,7 +22226,7 @@
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t>▸ Midwest  (2)</t>
+          <t>▸ Virginia  (1)</t>
         </is>
       </c>
       <c r="B66" s="12" t="n"/>
@@ -22165,52 +22247,52 @@
     <row r="67" outlineLevel="1">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>Freshway Market whole-grocery liquidation – refrigeration racks, cases, walk-ins, generator</t>
+          <t>Haynes Furniture / The Dump – 12 stores closing (furniture, mattresses)</t>
         </is>
       </c>
       <c r="C67" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>retail GOB</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Virginia Beach</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>862</v>
+        <v>456</v>
       </c>
       <c r="G67" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Retail GOB markdowns</t>
         </is>
       </c>
       <c r="H67" s="15" t="n"/>
-      <c r="I67" s="13" t="inlineStr"/>
-      <c r="J67" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-20 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="J67" s="13" t="inlineStr"/>
       <c r="K67" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L67" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>SB360 (PR Newswire)</t>
+        </is>
+      </c>
+      <c r="L67" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M67" s="13" t="inlineStr"/>
@@ -22221,165 +22303,165 @@
       </c>
       <c r="O67" s="14" t="inlineStr">
         <is>
+          <t>Posted Oct 8. Multi-state (VA/AZ/GA/IL/TX); pinned at Virginia Beach. Home goods only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Virginia</t>
+        </is>
+      </c>
+      <c r="B68" s="17" t="inlineStr">
+        <is>
+          <t>1 item(s)</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="n"/>
+      <c r="D68" s="18" t="n"/>
+      <c r="E68" s="18" t="n"/>
+      <c r="F68" s="18" t="n"/>
+      <c r="G68" s="18" t="n"/>
+      <c r="H68" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="18" t="n"/>
+      <c r="J68" s="18" t="n"/>
+      <c r="K68" s="18" t="n"/>
+      <c r="L68" s="18" t="n"/>
+      <c r="M68" s="18" t="n"/>
+      <c r="N68" s="18" t="n"/>
+      <c r="O68" s="18" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
+        <is>
+          <t>▸ Midwest  (2)</t>
+        </is>
+      </c>
+      <c r="B69" s="12" t="n"/>
+      <c r="C69" s="12" t="n"/>
+      <c r="D69" s="12" t="n"/>
+      <c r="E69" s="12" t="n"/>
+      <c r="F69" s="12" t="n"/>
+      <c r="G69" s="12" t="n"/>
+      <c r="H69" s="12" t="n"/>
+      <c r="I69" s="12" t="n"/>
+      <c r="J69" s="12" t="n"/>
+      <c r="K69" s="12" t="n"/>
+      <c r="L69" s="12" t="n"/>
+      <c r="M69" s="12" t="n"/>
+      <c r="N69" s="12" t="n"/>
+      <c r="O69" s="12" t="n"/>
+    </row>
+    <row r="70" outlineLevel="1">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>Freshway Market whole-grocery liquidation – refrigeration racks, cases, walk-ins, generator</t>
+        </is>
+      </c>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>store closing</t>
+        </is>
+      </c>
+      <c r="D70" s="13" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="F70" s="13" t="n">
+        <v>862</v>
+      </c>
+      <c r="G70" s="13" t="inlineStr">
+        <is>
+          <t>Online auction</t>
+        </is>
+      </c>
+      <c r="H70" s="15" t="n"/>
+      <c r="I70" s="13" t="inlineStr"/>
+      <c r="J70" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="inlineStr">
+        <is>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L70" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M70" s="13" t="inlineStr"/>
+      <c r="N70" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O70" s="14" t="inlineStr">
+        <is>
           <t>Closes from Oct 20 10 AM CDT.</t>
         </is>
       </c>
-    </row>
-    <row r="68" outlineLevel="1">
-      <c r="A68" s="13" t="inlineStr">
-        <is>
-          <t>Midwest</t>
-        </is>
-      </c>
-      <c r="B68" s="14" t="inlineStr">
-        <is>
-          <t>American Sale – total liquidation, all 7 stores (pools, hot tubs, grills, holiday decor)</t>
-        </is>
-      </c>
-      <c r="C68" s="13" t="inlineStr">
-        <is>
-          <t>retail GOB</t>
-        </is>
-      </c>
-      <c r="D68" s="13" t="inlineStr">
-        <is>
-          <t>Chicagoland</t>
-        </is>
-      </c>
-      <c r="E68" s="13" t="inlineStr">
-        <is>
-          <t>IL</t>
-        </is>
-      </c>
-      <c r="F68" s="13" t="n">
-        <v>876</v>
-      </c>
-      <c r="G68" s="13" t="inlineStr">
-        <is>
-          <t>Retail GOB, up to 70% off</t>
-        </is>
-      </c>
-      <c r="H68" s="15" t="n"/>
-      <c r="I68" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="J68" s="13" t="inlineStr"/>
-      <c r="K68" s="13" t="inlineStr">
-        <is>
-          <t>Tiger Group (PR Newswire)</t>
-        </is>
-      </c>
-      <c r="L68" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M68" s="13" t="inlineStr"/>
-      <c r="N68" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O68" s="14" t="inlineStr">
-        <is>
-          <t>Posted Oct 15. Watch for a bulk/fixture auction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Midwest</t>
-        </is>
-      </c>
-      <c r="B69" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C69" s="18" t="n"/>
-      <c r="D69" s="18" t="n"/>
-      <c r="E69" s="18" t="n"/>
-      <c r="F69" s="18" t="n"/>
-      <c r="G69" s="18" t="n"/>
-      <c r="H69" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="18" t="n"/>
-      <c r="J69" s="18" t="n"/>
-      <c r="K69" s="18" t="n"/>
-      <c r="L69" s="18" t="n"/>
-      <c r="M69" s="18" t="n"/>
-      <c r="N69" s="18" t="n"/>
-      <c r="O69" s="18" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="11" t="inlineStr">
-        <is>
-          <t>▸ Texas / South Central  (1)</t>
-        </is>
-      </c>
-      <c r="B70" s="12" t="n"/>
-      <c r="C70" s="12" t="n"/>
-      <c r="D70" s="12" t="n"/>
-      <c r="E70" s="12" t="n"/>
-      <c r="F70" s="12" t="n"/>
-      <c r="G70" s="12" t="n"/>
-      <c r="H70" s="12" t="n"/>
-      <c r="I70" s="12" t="n"/>
-      <c r="J70" s="12" t="n"/>
-      <c r="K70" s="12" t="n"/>
-      <c r="L70" s="12" t="n"/>
-      <c r="M70" s="12" t="n"/>
-      <c r="N70" s="12" t="n"/>
-      <c r="O70" s="12" t="n"/>
     </row>
     <row r="71" outlineLevel="1">
       <c r="A71" s="13" t="inlineStr">
         <is>
-          <t>Texas / South Central</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>Southwest beverage distributor surplus – mostly unused: 16 True merchandisers, 75 Bunn brewers, 100+ micro-market kiosks</t>
+          <t>American Sale – total liquidation, all 7 stores (pools, hot tubs, grills, holiday decor)</t>
         </is>
       </c>
       <c r="C71" s="13" t="inlineStr">
         <is>
-          <t>distributor surplus</t>
+          <t>retail GOB</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>Mesquite</t>
+          <t>Chicagoland</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>1547</v>
+        <v>876</v>
       </c>
       <c r="G71" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Retail GOB, up to 70% off</t>
         </is>
       </c>
       <c r="H71" s="15" t="n"/>
-      <c r="I71" s="13" t="inlineStr"/>
-      <c r="J71" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-13 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J71" s="13" t="inlineStr"/>
       <c r="K71" s="13" t="inlineStr">
         <is>
-          <t>Heritage Global Partners</t>
+          <t>Tiger Group (PR Newswire)</t>
         </is>
       </c>
       <c r="L71" s="13" t="inlineStr">
@@ -22395,19 +22477,19 @@
       </c>
       <c r="O71" s="14" t="inlineStr">
         <is>
-          <t>Near-new appliances, resell by unit. Nov 13 10 AM CST.</t>
+          <t>Posted Oct 15. Watch for a bulk/fixture auction.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="17" t="inlineStr">
         <is>
-          <t>Subtotal — Texas / South Central</t>
+          <t>Subtotal — Midwest</t>
         </is>
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>1 item(s)</t>
+          <t>2 item(s)</t>
         </is>
       </c>
       <c r="C72" s="18" t="n"/>
@@ -22429,7 +22511,7 @@
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>▸ West / Other  (1)</t>
+          <t>▸ Texas / South Central  (1)</t>
         </is>
       </c>
       <c r="B73" s="12" t="n"/>
@@ -22450,47 +22532,47 @@
     <row r="74" outlineLevel="1">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>West / Other</t>
+          <t>Texas / South Central</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>National salad concept liquidation – full contents of 63 fast-casual restaurants (AZ/TX/OK/NV)</t>
+          <t>Southwest beverage distributor surplus – mostly unused: 16 True merchandisers, 75 Bunn brewers, 100+ micro-market kiosks</t>
         </is>
       </c>
       <c r="C74" s="13" t="inlineStr">
         <is>
-          <t>restaurant chain liquidation</t>
+          <t>distributor surplus</t>
         </is>
       </c>
       <c r="D74" s="13" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Mesquite</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>2307</v>
+        <v>1547</v>
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>Online auctions, dates TBD</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H74" s="15" t="n"/>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="J74" s="13" t="inlineStr"/>
+      <c r="I74" s="13" t="inlineStr"/>
+      <c r="J74" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-13 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K74" s="13" t="inlineStr">
         <is>
-          <t>RestaurantEquipment.bid (TAGeX)</t>
+          <t>Heritage Global Partners</t>
         </is>
       </c>
       <c r="L74" s="13" t="inlineStr">
@@ -22506,14 +22588,14 @@
       </c>
       <c r="O74" s="14" t="inlineStr">
         <is>
-          <t>Rolling market-by-market auctions, none live yet (Phoenix metro 30 locations, DFW 14, Tucson 6, Houston 5, plus OK/NV). Pickup on site at each restaurant. Pinned at Phoenix.</t>
+          <t>Near-new appliances, resell by unit. Nov 13 10 AM CST.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="17" t="inlineStr">
         <is>
-          <t>Subtotal — West / Other</t>
+          <t>Subtotal — Texas / South Central</t>
         </is>
       </c>
       <c r="B75" s="17" t="inlineStr">
@@ -22537,24 +22619,135 @@
       <c r="N75" s="18" t="n"/>
       <c r="O75" s="18" t="n"/>
     </row>
+    <row r="76">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t>▸ West / Other  (1)</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="n"/>
+      <c r="C76" s="12" t="n"/>
+      <c r="D76" s="12" t="n"/>
+      <c r="E76" s="12" t="n"/>
+      <c r="F76" s="12" t="n"/>
+      <c r="G76" s="12" t="n"/>
+      <c r="H76" s="12" t="n"/>
+      <c r="I76" s="12" t="n"/>
+      <c r="J76" s="12" t="n"/>
+      <c r="K76" s="12" t="n"/>
+      <c r="L76" s="12" t="n"/>
+      <c r="M76" s="12" t="n"/>
+      <c r="N76" s="12" t="n"/>
+      <c r="O76" s="12" t="n"/>
+    </row>
+    <row r="77" outlineLevel="1">
+      <c r="A77" s="13" t="inlineStr">
+        <is>
+          <t>West / Other</t>
+        </is>
+      </c>
+      <c r="B77" s="14" t="inlineStr">
+        <is>
+          <t>National salad concept liquidation – full contents of 63 fast-casual restaurants (AZ/TX/OK/NV)</t>
+        </is>
+      </c>
+      <c r="C77" s="13" t="inlineStr">
+        <is>
+          <t>restaurant chain liquidation</t>
+        </is>
+      </c>
+      <c r="D77" s="13" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="E77" s="13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="F77" s="13" t="n">
+        <v>2307</v>
+      </c>
+      <c r="G77" s="13" t="inlineStr">
+        <is>
+          <t>Online auctions, dates TBD</t>
+        </is>
+      </c>
+      <c r="H77" s="15" t="n"/>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="J77" s="13" t="inlineStr"/>
+      <c r="K77" s="13" t="inlineStr">
+        <is>
+          <t>RestaurantEquipment.bid (TAGeX)</t>
+        </is>
+      </c>
+      <c r="L77" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M77" s="13" t="inlineStr"/>
+      <c r="N77" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O77" s="14" t="inlineStr">
+        <is>
+          <t>Rolling market-by-market auctions, none live yet (Phoenix metro 30 locations, DFW 14, Tucson 6, Houston 5, plus OK/NV). Pickup on site at each restaurant. Pinned at Phoenix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — West / Other</t>
+        </is>
+      </c>
+      <c r="B78" s="17" t="inlineStr">
+        <is>
+          <t>1 item(s)</t>
+        </is>
+      </c>
+      <c r="C78" s="18" t="n"/>
+      <c r="D78" s="18" t="n"/>
+      <c r="E78" s="18" t="n"/>
+      <c r="F78" s="18" t="n"/>
+      <c r="G78" s="18" t="n"/>
+      <c r="H78" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="18" t="n"/>
+      <c r="J78" s="18" t="n"/>
+      <c r="K78" s="18" t="n"/>
+      <c r="L78" s="18" t="n"/>
+      <c r="M78" s="18" t="n"/>
+      <c r="N78" s="18" t="n"/>
+      <c r="O78" s="18" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O75"/>
+  <autoFilter ref="A1:O78"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId18"/>
@@ -22581,15 +22774,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N51" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N52" r:id="rId40"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N60" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N61" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N64" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N67" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N68" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N71" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N74" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N62" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N64" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N67" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N71" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N74" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N77" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22601,7 +22797,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O5"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -22895,7 +23091,7 @@
       </c>
       <c r="O4" s="14" t="inlineStr">
         <is>
-          <t>Condition: Pre-Owned. FLIP: SO36U/S tested, auction $99/0 bids, pickup only; rough resale $600-1k (eBay card shows no city; pickup distance in source.) Ends Oct 18 ~2:19 PM per eBay card (time zone uncertain; could be earlier). [auto-removed 2026-10-18: closing date passed] [auto-removed 2026-10-19: closing date passed]</t>
+          <t>Condition: Pre-Owned. FLIP: SO36U/S tested, auction $99/0 bids, pickup only; rough resale $600-1k (eBay card shows no city; pickup distance in source.) Ends Oct 18 ~2:19 PM per eBay card (time zone uncertain; could be earlier). [auto-removed 2026-10-18: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -22960,17 +23156,81 @@
       </c>
       <c r="O5" s="14" t="inlineStr">
         <is>
-          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf) HiBid lot closed/sold ~$37.50 on 2026-10-18. [auto-removed 2026-10-19: closing date passed]</t>
+          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf) HiBid lot closed/sold ~$37.50 on 2026-10-18. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="inlineStr">
+        <is>
+          <t>Greater Boston / South Shore (&lt;50mi)</t>
+        </is>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>Closed Best Buy Outlet – pallet racking, Big Joe order pickers, appliance dollies, carts, cages</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>store closing fixtures</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>Brockton</t>
+        </is>
+      </c>
+      <c r="E6" s="13" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>Racking $40/upright, $80/level; pickers $1,000 OBO</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="n"/>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr"/>
+      <c r="K6" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L6" s="13" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="M6" s="13" t="inlineStr"/>
+      <c r="N6" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O6" s="14" t="inlineStr">
+        <is>
+          <t>200 Westgate Dr. Fixtures/equipment only, no merchandise. On site daily. CL deleted by author (HTTP 410) as of 2026-10-19 midday recheck.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O5"/>
+  <autoFilter ref="A1:O6"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lot_recon.xlsx
+++ b/lot_recon.xlsx
@@ -16,12 +16,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Removed" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Appliance Parts'!$A$1:$O$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Appliance Parts'!$A$1:$O$42</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wolf New'!$A$1:$O$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wolf Used'!$A$1:$O$189</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Wolf Unclear'!$A$1:$O$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Removed'!$A$1:$O$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Removed'!$A$1:$O$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -577,7 +577,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Last updated: 2026-10-19 11:11 ET</t>
+          <t>Last updated: 2026-10-19 14:04 ET</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Active listings: 294 · Removed: 5</t>
+          <t>Active listings: 293 · Removed: 8</t>
         </is>
       </c>
     </row>
@@ -641,13 +641,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>159696</v>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
         <v>34</v>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>980432.58</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -971,7 +971,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H22" s="6" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -1004,7 +1004,7 @@
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H23" s="6" t="n">
         <v>64740</v>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -1037,7 +1037,7 @@
         <v>24</v>
       </c>
       <c r="G24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>440141</v>
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C30" t="n">
         <v>2</v>
@@ -1235,14 +1235,14 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="6" t="n">
         <v>5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>743–876</t>
+          <t>743–1046</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O43"/>
+  <dimension ref="A1:O42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2227,7 +2227,7 @@
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>▸ Southeast  (5)</t>
+          <t>▸ Southeast  (4)</t>
         </is>
       </c>
       <c r="B21" s="12" t="n"/>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Louisville)</t>
+          <t>[SMALL] Whirlpool parts assortment</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>auction catalog</t>
+          <t>small lot</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
@@ -2341,26 +2341,20 @@
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>$0–1 openers + 15% BP + $1/lot</t>
-        </is>
-      </c>
-      <c r="H23" s="15" t="n">
-        <v>0</v>
-      </c>
+          <t>Price n/a</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="n"/>
       <c r="I23" s="13" t="inlineStr"/>
-      <c r="J23" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-19 02:00 PM ET</t>
-        </is>
-      </c>
+      <c r="J23" s="13" t="inlineStr"/>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Auctionfuel)</t>
-        </is>
-      </c>
-      <c r="L23" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L23" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M23" s="13" t="inlineStr"/>
@@ -2371,7 +2365,7 @@
       </c>
       <c r="O23" s="14" t="inlineStr">
         <is>
-          <t>Lots close from Oct 19 2 PM ET.</t>
+          <t>Small lead.</t>
         </is>
       </c>
     </row>
@@ -2383,43 +2377,53 @@
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>[SMALL] Whirlpool parts assortment</t>
+          <t>Misc. appliance parts pallet (parts only)</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>small lot</t>
+          <t>auction pallet</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>Dalton</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>KY</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>832</v>
+        <v>917</v>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>Price n/a</t>
-        </is>
-      </c>
-      <c r="H24" s="15" t="n"/>
-      <c r="I24" s="13" t="inlineStr"/>
-      <c r="J24" s="13" t="inlineStr"/>
+          <t>$50 high bid + 15% BP</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="n">
+        <v>50</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="J24" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 09:18 PM ET</t>
+        </is>
+      </c>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L24" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>HiBid</t>
+        </is>
+      </c>
+      <c r="L24" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M24" s="13" t="inlineStr"/>
@@ -2430,7 +2434,7 @@
       </c>
       <c r="O24" s="14" t="inlineStr">
         <is>
-          <t>Small lead.</t>
+          <t>Integrity Auction House. Internet bidding closes Mon Oct 19 9:18 PM ET. $50 high bid (1 bid) as of 2026-10-18.</t>
         </is>
       </c>
     </row>
@@ -2442,53 +2446,47 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Misc. appliance parts pallet (parts only)</t>
+          <t>Established appliance sales / parts / service business</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>auction pallet</t>
+          <t>business sale</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>Dalton</t>
+          <t>Oakland Park</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>917</v>
+        <v>1222</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
-          <t>$50 high bid + 15% BP</t>
-        </is>
-      </c>
-      <c r="H25" s="15" t="n">
-        <v>50</v>
-      </c>
+          <t>Price n/a</t>
+        </is>
+      </c>
+      <c r="H25" s="15" t="n"/>
       <c r="I25" s="13" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="J25" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-19 09:18 PM ET</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="J25" s="13" t="inlineStr"/>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>HiBid</t>
-        </is>
-      </c>
-      <c r="L25" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L25" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M25" s="13" t="inlineStr"/>
@@ -2499,120 +2497,122 @@
       </c>
       <c r="O25" s="14" t="inlineStr">
         <is>
-          <t>Integrity Auction House. Internet bidding closes Mon Oct 19 9:18 PM ET. $50 high bid (1 bid) as of 2026-10-18.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" outlineLevel="1">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>Southeast</t>
-        </is>
-      </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>Established appliance sales / parts / service business</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>business sale</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>Oakland Park</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="F26" s="13" t="n">
-        <v>1222</v>
-      </c>
-      <c r="G26" s="13" t="inlineStr">
-        <is>
-          <t>Price n/a</t>
-        </is>
-      </c>
-      <c r="H26" s="15" t="n"/>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="J26" s="13" t="inlineStr"/>
-      <c r="K26" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L26" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M26" s="13" t="inlineStr"/>
-      <c r="N26" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O26" s="14" t="inlineStr">
-        <is>
           <t>Whole business sale (Fort Lauderdale area).</t>
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Southeast</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>4 item(s)</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="n"/>
+      <c r="D26" s="18" t="n"/>
+      <c r="E26" s="18" t="n"/>
+      <c r="F26" s="18" t="n"/>
+      <c r="G26" s="18" t="n"/>
+      <c r="H26" s="19" t="n">
+        <v>36050</v>
+      </c>
+      <c r="I26" s="18" t="n"/>
+      <c r="J26" s="18" t="n"/>
+      <c r="K26" s="18" t="n"/>
+      <c r="L26" s="18" t="n"/>
+      <c r="M26" s="18" t="n"/>
+      <c r="N26" s="18" t="n"/>
+      <c r="O26" s="18" t="n"/>
+    </row>
     <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Southeast</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>5 item(s)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="n"/>
-      <c r="D27" s="18" t="n"/>
-      <c r="E27" s="18" t="n"/>
-      <c r="F27" s="18" t="n"/>
-      <c r="G27" s="18" t="n"/>
-      <c r="H27" s="19" t="n">
-        <v>36050</v>
-      </c>
-      <c r="I27" s="18" t="n"/>
-      <c r="J27" s="18" t="n"/>
-      <c r="K27" s="18" t="n"/>
-      <c r="L27" s="18" t="n"/>
-      <c r="M27" s="18" t="n"/>
-      <c r="N27" s="18" t="n"/>
-      <c r="O27" s="18" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>▸ Midwest  (2)</t>
         </is>
       </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="12" t="n"/>
-      <c r="G28" s="12" t="n"/>
-      <c r="H28" s="12" t="n"/>
-      <c r="I28" s="12" t="n"/>
-      <c r="J28" s="12" t="n"/>
-      <c r="K28" s="12" t="n"/>
-      <c r="L28" s="12" t="n"/>
-      <c r="M28" s="12" t="n"/>
-      <c r="N28" s="12" t="n"/>
-      <c r="O28" s="12" t="n"/>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="12" t="n"/>
+      <c r="N27" s="12" t="n"/>
+      <c r="O27" s="12" t="n"/>
+    </row>
+    <row r="28" outlineLevel="1">
+      <c r="A28" s="13" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="B28" s="14" t="inlineStr">
+        <is>
+          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Fort Wayne)</t>
+        </is>
+      </c>
+      <c r="C28" s="13" t="inlineStr">
+        <is>
+          <t>auction catalog</t>
+        </is>
+      </c>
+      <c r="D28" s="13" t="inlineStr">
+        <is>
+          <t>Fort Wayne</t>
+        </is>
+      </c>
+      <c r="E28" s="13" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F28" s="13" t="n">
+        <v>743</v>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>$0–1 openers + 15% BP + $1/lot</t>
+        </is>
+      </c>
+      <c r="H28" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="13" t="inlineStr"/>
+      <c r="J28" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-20 02:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K28" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (Auctionfuel)</t>
+        </is>
+      </c>
+      <c r="L28" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M28" s="13" t="inlineStr"/>
+      <c r="N28" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O28" s="14" t="inlineStr">
+        <is>
+          <t>Lots close from Oct 20 2 PM ET.</t>
+        </is>
+      </c>
     </row>
     <row r="29" outlineLevel="1">
       <c r="A29" s="13" t="inlineStr">
@@ -2622,7 +2622,7 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Fort Wayne)</t>
+          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Indianapolis)</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
@@ -2632,7 +2632,7 @@
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>Fort Wayne</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
@@ -2641,7 +2641,7 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>743</v>
+        <v>816</v>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
       <c r="I29" s="13" t="inlineStr"/>
       <c r="J29" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 02:00 PM ET</t>
+          <t>2026-10-21 02:00 PM ET</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
@@ -2675,122 +2675,120 @@
       </c>
       <c r="O29" s="14" t="inlineStr">
         <is>
-          <t>Lots close from Oct 20 2 PM ET.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" outlineLevel="1">
-      <c r="A30" s="13" t="inlineStr">
-        <is>
-          <t>Midwest</t>
-        </is>
-      </c>
-      <c r="B30" s="14" t="inlineStr">
-        <is>
-          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Indianapolis)</t>
-        </is>
-      </c>
-      <c r="C30" s="13" t="inlineStr">
-        <is>
-          <t>auction catalog</t>
-        </is>
-      </c>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>Indianapolis</t>
-        </is>
-      </c>
-      <c r="E30" s="13" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="F30" s="13" t="n">
-        <v>816</v>
-      </c>
-      <c r="G30" s="13" t="inlineStr">
-        <is>
-          <t>$0–1 openers + 15% BP + $1/lot</t>
-        </is>
-      </c>
-      <c r="H30" s="15" t="n">
+          <t>Lots close in sequence from Oct 21 2 PM ET.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Midwest</t>
+        </is>
+      </c>
+      <c r="B30" s="17" t="inlineStr">
+        <is>
+          <t>2 item(s)</t>
+        </is>
+      </c>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="18" t="n"/>
+      <c r="E30" s="18" t="n"/>
+      <c r="F30" s="18" t="n"/>
+      <c r="G30" s="18" t="n"/>
+      <c r="H30" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I30" s="13" t="inlineStr"/>
-      <c r="J30" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 02:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K30" s="13" t="inlineStr">
-        <is>
-          <t>HiBid (Auctionfuel)</t>
-        </is>
-      </c>
-      <c r="L30" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M30" s="13" t="inlineStr"/>
-      <c r="N30" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O30" s="14" t="inlineStr">
-        <is>
-          <t>Lots close in sequence from Oct 21 2 PM ET.</t>
-        </is>
-      </c>
+      <c r="I30" s="18" t="n"/>
+      <c r="J30" s="18" t="n"/>
+      <c r="K30" s="18" t="n"/>
+      <c r="L30" s="18" t="n"/>
+      <c r="M30" s="18" t="n"/>
+      <c r="N30" s="18" t="n"/>
+      <c r="O30" s="18" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Midwest</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="n"/>
-      <c r="D31" s="18" t="n"/>
-      <c r="E31" s="18" t="n"/>
-      <c r="F31" s="18" t="n"/>
-      <c r="G31" s="18" t="n"/>
-      <c r="H31" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="18" t="n"/>
-      <c r="J31" s="18" t="n"/>
-      <c r="K31" s="18" t="n"/>
-      <c r="L31" s="18" t="n"/>
-      <c r="M31" s="18" t="n"/>
-      <c r="N31" s="18" t="n"/>
-      <c r="O31" s="18" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="A31" s="11" t="inlineStr">
         <is>
           <t>▸ Texas / South Central  (2)</t>
         </is>
       </c>
-      <c r="B32" s="12" t="n"/>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="12" t="n"/>
-      <c r="E32" s="12" t="n"/>
-      <c r="F32" s="12" t="n"/>
-      <c r="G32" s="12" t="n"/>
-      <c r="H32" s="12" t="n"/>
-      <c r="I32" s="12" t="n"/>
-      <c r="J32" s="12" t="n"/>
-      <c r="K32" s="12" t="n"/>
-      <c r="L32" s="12" t="n"/>
-      <c r="M32" s="12" t="n"/>
-      <c r="N32" s="12" t="n"/>
-      <c r="O32" s="12" t="n"/>
+      <c r="B31" s="12" t="n"/>
+      <c r="C31" s="12" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="12" t="n"/>
+      <c r="G31" s="12" t="n"/>
+      <c r="H31" s="12" t="n"/>
+      <c r="I31" s="12" t="n"/>
+      <c r="J31" s="12" t="n"/>
+      <c r="K31" s="12" t="n"/>
+      <c r="L31" s="12" t="n"/>
+      <c r="M31" s="12" t="n"/>
+      <c r="N31" s="12" t="n"/>
+      <c r="O31" s="12" t="n"/>
+    </row>
+    <row r="32" outlineLevel="1">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>Texas / South Central</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>Wholesale Hisense appliance parts – stove &amp; refrigerator parts</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>bulk lot</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>Owasso</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>1395</v>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>Wholesale (price at sale)</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="n"/>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J32" s="13" t="inlineStr"/>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L32" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M32" s="13" t="inlineStr"/>
+      <c r="N32" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O32" s="14" t="inlineStr">
+        <is>
+          <t>Updated 2026-10-12. Seller says LOCAL BUYERS ONLY, out-of-area excluded, cash pickup.</t>
+        </is>
+      </c>
     </row>
     <row r="33" outlineLevel="1">
       <c r="A33" s="13" t="inlineStr">
@@ -2800,7 +2798,7 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>Wholesale Hisense appliance parts – stove &amp; refrigerator parts</t>
+          <t>Huge bulk lot appliance parts – ~2 trailer loads, GE/Whirlpool/Maytag</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
@@ -2810,32 +2808,30 @@
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>Owasso</t>
+          <t>Abilene</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>1395</v>
+        <v>1714</v>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
-          <t>Wholesale (price at sale)</t>
-        </is>
-      </c>
-      <c r="H33" s="15" t="n"/>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
+          <t>$5,001</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>5001</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr"/>
       <c r="J33" s="13" t="inlineStr"/>
       <c r="K33" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>Geebo</t>
         </is>
       </c>
       <c r="L33" s="13" t="inlineStr">
@@ -2851,118 +2847,118 @@
       </c>
       <c r="O33" s="14" t="inlineStr">
         <is>
-          <t>Updated 2026-10-12. Seller says LOCAL BUYERS ONLY, out-of-area excluded, cash pickup.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" outlineLevel="1">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>Texas / South Central</t>
-        </is>
-      </c>
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>Huge bulk lot appliance parts – ~2 trailer loads, GE/Whirlpool/Maytag</t>
-        </is>
-      </c>
-      <c r="C34" s="13" t="inlineStr">
-        <is>
-          <t>bulk lot</t>
-        </is>
-      </c>
-      <c r="D34" s="13" t="inlineStr">
-        <is>
-          <t>Abilene</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>TX</t>
-        </is>
-      </c>
-      <c r="F34" s="13" t="n">
-        <v>1714</v>
-      </c>
-      <c r="G34" s="13" t="inlineStr">
-        <is>
-          <t>$5,001</t>
-        </is>
-      </c>
-      <c r="H34" s="15" t="n">
+          <t>Post date unclear (may be older). Pickup only. User already messaged seller.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Texas / South Central</t>
+        </is>
+      </c>
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>2 item(s)</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="n"/>
+      <c r="D34" s="18" t="n"/>
+      <c r="E34" s="18" t="n"/>
+      <c r="F34" s="18" t="n"/>
+      <c r="G34" s="18" t="n"/>
+      <c r="H34" s="19" t="n">
         <v>5001</v>
       </c>
-      <c r="I34" s="13" t="inlineStr"/>
-      <c r="J34" s="13" t="inlineStr"/>
-      <c r="K34" s="13" t="inlineStr">
-        <is>
-          <t>Geebo</t>
-        </is>
-      </c>
-      <c r="L34" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M34" s="13" t="inlineStr"/>
-      <c r="N34" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O34" s="14" t="inlineStr">
-        <is>
-          <t>Post date unclear (may be older). Pickup only. User already messaged seller.</t>
-        </is>
-      </c>
+      <c r="I34" s="18" t="n"/>
+      <c r="J34" s="18" t="n"/>
+      <c r="K34" s="18" t="n"/>
+      <c r="L34" s="18" t="n"/>
+      <c r="M34" s="18" t="n"/>
+      <c r="N34" s="18" t="n"/>
+      <c r="O34" s="18" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Texas / South Central</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="n"/>
-      <c r="D35" s="18" t="n"/>
-      <c r="E35" s="18" t="n"/>
-      <c r="F35" s="18" t="n"/>
-      <c r="G35" s="18" t="n"/>
-      <c r="H35" s="19" t="n">
-        <v>5001</v>
-      </c>
-      <c r="I35" s="18" t="n"/>
-      <c r="J35" s="18" t="n"/>
-      <c r="K35" s="18" t="n"/>
-      <c r="L35" s="18" t="n"/>
-      <c r="M35" s="18" t="n"/>
-      <c r="N35" s="18" t="n"/>
-      <c r="O35" s="18" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>▸ California  (2)</t>
         </is>
       </c>
-      <c r="B36" s="12" t="n"/>
-      <c r="C36" s="12" t="n"/>
-      <c r="D36" s="12" t="n"/>
-      <c r="E36" s="12" t="n"/>
-      <c r="F36" s="12" t="n"/>
-      <c r="G36" s="12" t="n"/>
-      <c r="H36" s="12" t="n"/>
-      <c r="I36" s="12" t="n"/>
-      <c r="J36" s="12" t="n"/>
-      <c r="K36" s="12" t="n"/>
-      <c r="L36" s="12" t="n"/>
-      <c r="M36" s="12" t="n"/>
-      <c r="N36" s="12" t="n"/>
-      <c r="O36" s="12" t="n"/>
+      <c r="B35" s="12" t="n"/>
+      <c r="C35" s="12" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="12" t="n"/>
+      <c r="G35" s="12" t="n"/>
+      <c r="H35" s="12" t="n"/>
+      <c r="I35" s="12" t="n"/>
+      <c r="J35" s="12" t="n"/>
+      <c r="K35" s="12" t="n"/>
+      <c r="L35" s="12" t="n"/>
+      <c r="M35" s="12" t="n"/>
+      <c r="N35" s="12" t="n"/>
+      <c r="O35" s="12" t="n"/>
+    </row>
+    <row r="36" outlineLevel="1">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>Appliance repair company for sale (incl. parts inventory)</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>business sale</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>Escondido</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>2575</v>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>$40,000</t>
+        </is>
+      </c>
+      <c r="H36" s="15" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr"/>
+      <c r="J36" s="13" t="inlineStr"/>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L36" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M36" s="13" t="inlineStr"/>
+      <c r="N36" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O36" s="14" t="inlineStr">
+        <is>
+          <t>Whole business sale.</t>
+        </is>
+      </c>
     </row>
     <row r="37" outlineLevel="1">
       <c r="A37" s="13" t="inlineStr">
@@ -2972,17 +2968,17 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>Appliance repair company for sale (incl. parts inventory)</t>
+          <t>Coin-op Whirlpool washer &amp; dryer parts (late 80s–mid 90s) – OEM parts, 40+ coin boxes, consoles, 12 transmissions</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>business sale</t>
+          <t>bulk lot</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>Escondido</t>
+          <t>Chico</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
@@ -2991,17 +2987,21 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>2575</v>
+        <v>2629</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t>$40,000</t>
+          <t>$1,000</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
-        <v>40000</v>
-      </c>
-      <c r="I37" s="13" t="inlineStr"/>
+        <v>1000</v>
+      </c>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
       <c r="J37" s="13" t="inlineStr"/>
       <c r="K37" s="13" t="inlineStr">
         <is>
@@ -3021,122 +3021,120 @@
       </c>
       <c r="O37" s="14" t="inlineStr">
         <is>
-          <t>Whole business sale.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" outlineLevel="1">
-      <c r="A38" s="13" t="inlineStr">
-        <is>
-          <t>California</t>
-        </is>
-      </c>
-      <c r="B38" s="14" t="inlineStr">
-        <is>
-          <t>Coin-op Whirlpool washer &amp; dryer parts (late 80s–mid 90s) – OEM parts, 40+ coin boxes, consoles, 12 transmissions</t>
-        </is>
-      </c>
-      <c r="C38" s="13" t="inlineStr">
+          <t>Retired laundry-route owner (35 yrs). Calls only, no shipping, pickup in Chico. No motors or pumps. Niche older coin-op parts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — California</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>2 item(s)</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="n"/>
+      <c r="D38" s="18" t="n"/>
+      <c r="E38" s="18" t="n"/>
+      <c r="F38" s="18" t="n"/>
+      <c r="G38" s="18" t="n"/>
+      <c r="H38" s="19" t="n">
+        <v>41000</v>
+      </c>
+      <c r="I38" s="18" t="n"/>
+      <c r="J38" s="18" t="n"/>
+      <c r="K38" s="18" t="n"/>
+      <c r="L38" s="18" t="n"/>
+      <c r="M38" s="18" t="n"/>
+      <c r="N38" s="18" t="n"/>
+      <c r="O38" s="18" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>▸ West / Other  (2)</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="n"/>
+      <c r="C39" s="12" t="n"/>
+      <c r="D39" s="12" t="n"/>
+      <c r="E39" s="12" t="n"/>
+      <c r="F39" s="12" t="n"/>
+      <c r="G39" s="12" t="n"/>
+      <c r="H39" s="12" t="n"/>
+      <c r="I39" s="12" t="n"/>
+      <c r="J39" s="12" t="n"/>
+      <c r="K39" s="12" t="n"/>
+      <c r="L39" s="12" t="n"/>
+      <c r="M39" s="12" t="n"/>
+      <c r="N39" s="12" t="n"/>
+      <c r="O39" s="12" t="n"/>
+    </row>
+    <row r="40" outlineLevel="1">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>West / Other</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>Storage locker filled with appliance parts – washer/dryer parts, heating elements, cords, rollers, belts, tools</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
         <is>
           <t>bulk lot</t>
         </is>
       </c>
-      <c r="D38" s="13" t="inlineStr">
-        <is>
-          <t>Chico</t>
-        </is>
-      </c>
-      <c r="E38" s="13" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="F38" s="13" t="n">
-        <v>2629</v>
-      </c>
-      <c r="G38" s="13" t="inlineStr">
-        <is>
-          <t>$1,000</t>
-        </is>
-      </c>
-      <c r="H38" s="15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="J38" s="13" t="inlineStr"/>
-      <c r="K38" s="13" t="inlineStr">
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>2307</v>
+      </c>
+      <c r="G40" s="13" t="inlineStr">
+        <is>
+          <t>Message for pricing</t>
+        </is>
+      </c>
+      <c r="H40" s="15" t="n"/>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J40" s="13" t="inlineStr"/>
+      <c r="K40" s="13" t="inlineStr">
         <is>
           <t>Craigslist</t>
         </is>
       </c>
-      <c r="L38" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M38" s="13" t="inlineStr"/>
-      <c r="N38" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O38" s="14" t="inlineStr">
-        <is>
-          <t>Retired laundry-route owner (35 yrs). Calls only, no shipping, pickup in Chico. No motors or pumps. Niche older coin-op parts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — California</t>
-        </is>
-      </c>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="n"/>
-      <c r="D39" s="18" t="n"/>
-      <c r="E39" s="18" t="n"/>
-      <c r="F39" s="18" t="n"/>
-      <c r="G39" s="18" t="n"/>
-      <c r="H39" s="19" t="n">
-        <v>41000</v>
-      </c>
-      <c r="I39" s="18" t="n"/>
-      <c r="J39" s="18" t="n"/>
-      <c r="K39" s="18" t="n"/>
-      <c r="L39" s="18" t="n"/>
-      <c r="M39" s="18" t="n"/>
-      <c r="N39" s="18" t="n"/>
-      <c r="O39" s="18" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
-        <is>
-          <t>▸ West / Other  (2)</t>
-        </is>
-      </c>
-      <c r="B40" s="12" t="n"/>
-      <c r="C40" s="12" t="n"/>
-      <c r="D40" s="12" t="n"/>
-      <c r="E40" s="12" t="n"/>
-      <c r="F40" s="12" t="n"/>
-      <c r="G40" s="12" t="n"/>
-      <c r="H40" s="12" t="n"/>
-      <c r="I40" s="12" t="n"/>
-      <c r="J40" s="12" t="n"/>
-      <c r="K40" s="12" t="n"/>
-      <c r="L40" s="12" t="n"/>
-      <c r="M40" s="12" t="n"/>
-      <c r="N40" s="12" t="n"/>
-      <c r="O40" s="12" t="n"/>
+      <c r="L40" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M40" s="13" t="inlineStr"/>
+      <c r="N40" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O40" s="14" t="inlineStr">
+        <is>
+          <t>Seller is getting out of the appliance business; selling the whole locker (North Phoenix, Deer Valley Rd near 19th Ave). Delivery available per post. Separate from the Phoenix parts-store closing ad.</t>
+        </is>
+      </c>
     </row>
     <row r="41" outlineLevel="1">
       <c r="A41" s="13" t="inlineStr">
@@ -3146,17 +3144,17 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>Storage locker filled with appliance parts – washer/dryer parts, heating elements, cords, rollers, belts, tools</t>
+          <t>Appliance repair &amp; sales business for sale – 100+ appliances (~90% new), liftgate truck, large powered storage unit</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>bulk lot</t>
+          <t>business for sale</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Surprise</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -3165,17 +3163,19 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>2307</v>
+        <v>2317</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t>Message for pricing</t>
-        </is>
-      </c>
-      <c r="H41" s="15" t="n"/>
+          <t>$75,000</t>
+        </is>
+      </c>
+      <c r="H41" s="15" t="n">
+        <v>75000</v>
+      </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J41" s="13" t="inlineStr"/>
@@ -3197,104 +3197,39 @@
       </c>
       <c r="O41" s="14" t="inlineStr">
         <is>
-          <t>Seller is getting out of the appliance business; selling the whole locker (North Phoenix, Deer Valley Rd near 19th Ave). Delivery available per post. Separate from the Phoenix parts-store closing ad.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" outlineLevel="1">
-      <c r="A42" s="13" t="inlineStr">
-        <is>
-          <t>West / Other</t>
-        </is>
-      </c>
-      <c r="B42" s="14" t="inlineStr">
-        <is>
-          <t>Appliance repair &amp; sales business for sale – 100+ appliances (~90% new), liftgate truck, large powered storage unit</t>
-        </is>
-      </c>
-      <c r="C42" s="13" t="inlineStr">
-        <is>
-          <t>business for sale</t>
-        </is>
-      </c>
-      <c r="D42" s="13" t="inlineStr">
-        <is>
-          <t>Surprise</t>
-        </is>
-      </c>
-      <c r="E42" s="13" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="F42" s="13" t="n">
-        <v>2317</v>
-      </c>
-      <c r="G42" s="13" t="inlineStr">
-        <is>
-          <t>$75,000</t>
-        </is>
-      </c>
-      <c r="H42" s="15" t="n">
+          <t>Retiring owner of 14-year business serving rental-property owners. Whole appliances (fridges, stoves, microwaves, dishwashers, W/D), not a parts inventory. Storage unit near Dysart &amp; Bell Rd. By appointment only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — West / Other</t>
+        </is>
+      </c>
+      <c r="B42" s="17" t="inlineStr">
+        <is>
+          <t>2 item(s)</t>
+        </is>
+      </c>
+      <c r="C42" s="18" t="n"/>
+      <c r="D42" s="18" t="n"/>
+      <c r="E42" s="18" t="n"/>
+      <c r="F42" s="18" t="n"/>
+      <c r="G42" s="18" t="n"/>
+      <c r="H42" s="19" t="n">
         <v>75000</v>
       </c>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="J42" s="13" t="inlineStr"/>
-      <c r="K42" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L42" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M42" s="13" t="inlineStr"/>
-      <c r="N42" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O42" s="14" t="inlineStr">
-        <is>
-          <t>Retiring owner of 14-year business serving rental-property owners. Whole appliances (fridges, stoves, microwaves, dishwashers, W/D), not a parts inventory. Storage unit near Dysart &amp; Bell Rd. By appointment only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — West / Other</t>
-        </is>
-      </c>
-      <c r="B43" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C43" s="18" t="n"/>
-      <c r="D43" s="18" t="n"/>
-      <c r="E43" s="18" t="n"/>
-      <c r="F43" s="18" t="n"/>
-      <c r="G43" s="18" t="n"/>
-      <c r="H43" s="19" t="n">
-        <v>75000</v>
-      </c>
-      <c r="I43" s="18" t="n"/>
-      <c r="J43" s="18" t="n"/>
-      <c r="K43" s="18" t="n"/>
-      <c r="L43" s="18" t="n"/>
-      <c r="M43" s="18" t="n"/>
-      <c r="N43" s="18" t="n"/>
-      <c r="O43" s="18" t="n"/>
+      <c r="I42" s="18" t="n"/>
+      <c r="J42" s="18" t="n"/>
+      <c r="K42" s="18" t="n"/>
+      <c r="L42" s="18" t="n"/>
+      <c r="M42" s="18" t="n"/>
+      <c r="N42" s="18" t="n"/>
+      <c r="O42" s="18" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O43"/>
+  <autoFilter ref="A1:O42"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId2"/>
@@ -3307,15 +3242,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId20"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19493,7 +19427,7 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>▸ Maine / VT / Northern NH  (5)</t>
+          <t>▸ Maine / VT / Northern NH  (4)</t>
         </is>
       </c>
       <c r="B17" s="12" t="n"/>
@@ -19519,12 +19453,12 @@
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>Oola Bowls secured-party sale – restaurant equipment bought new 2024-25 (Electro Freeze, Scotsman, Atosa)</t>
+          <t>Contractor appliance lot – 3 refrigerators, Bosch wall oven, gas range, washer/dryer set</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>contractor lot</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
@@ -19542,24 +19476,24 @@
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>Online auction (freezers $80–150 when seen)</t>
+          <t>$200 OBO each, less as a bundle</t>
         </is>
       </c>
       <c r="H18" s="15" t="n"/>
-      <c r="I18" s="13" t="inlineStr"/>
-      <c r="J18" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-19 01:00 PM ET</t>
-        </is>
-      </c>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="inlineStr"/>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>Keenan Auction / Proxibid</t>
-        </is>
-      </c>
-      <c r="L18" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L18" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M18" s="13" t="inlineStr"/>
@@ -19570,7 +19504,7 @@
       </c>
       <c r="O18" s="14" t="inlineStr">
         <is>
-          <t>Pickup Oct 21 only.</t>
+          <t>Working units pulled from jobs. Complete appliances, not parts.</t>
         </is>
       </c>
     </row>
@@ -19582,17 +19516,17 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>Contractor appliance lot – 3 refrigerators, Bosch wall oven, gas range, washer/dryer set</t>
+          <t>Event-rental business closing – 300+ chairs, 40+ rounds, 1,300+ china, linens (all at once)</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>contractor lot</t>
+          <t>business closing</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>Scarborough</t>
+          <t>Woolwich</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
@@ -19601,17 +19535,17 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>$200 OBO each, less as a bundle</t>
+          <t>No price listed</t>
         </is>
       </c>
       <c r="H19" s="15" t="n"/>
       <c r="I19" s="13" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J19" s="13" t="inlineStr"/>
@@ -19633,7 +19567,7 @@
       </c>
       <c r="O19" s="14" t="inlineStr">
         <is>
-          <t>Working units pulled from jobs. Complete appliances, not parts.</t>
+          <t>Updated Oct 7. Replacement cost &gt;$72K per post.</t>
         </is>
       </c>
     </row>
@@ -19645,42 +19579,42 @@
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>Event-rental business closing – 300+ chairs, 40+ rounds, 1,300+ china, linens (all at once)</t>
+          <t>Pellet/wood stoves, heating stock, tools &amp; heavy equipment – "business liquidation", 380 lots</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>business closing</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>Woolwich</t>
+          <t>Lunenburg</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>ME</t>
+          <t>VT</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>135</v>
+        <v>168</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>No price listed</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H20" s="15" t="n"/>
-      <c r="I20" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="J20" s="13" t="inlineStr"/>
+      <c r="I20" s="13" t="inlineStr"/>
+      <c r="J20" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-04 10:00 AM ET</t>
+        </is>
+      </c>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>Thomas Hirchak Co.</t>
         </is>
       </c>
       <c r="L20" s="13" t="inlineStr">
@@ -19696,7 +19630,7 @@
       </c>
       <c r="O20" s="14" t="inlineStr">
         <is>
-          <t>Updated Oct 7. Replacement cost &gt;$72K per post.</t>
+          <t>Closes Wed Nov 4 10 AM, preview Oct 28, removal Nov 9, no shipping.</t>
         </is>
       </c>
     </row>
@@ -19708,17 +19642,17 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>Pellet/wood stoves, heating stock, tools &amp; heavy equipment – "business liquidation", 380 lots</t>
+          <t>Bread Loaf Corp wind-down – contractor equipment, staging, telehandler</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>contractor liquidation</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>Lunenburg</t>
+          <t>Middlebury</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -19727,7 +19661,7 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
@@ -19738,12 +19672,12 @@
       <c r="I21" s="13" t="inlineStr"/>
       <c r="J21" s="13" t="inlineStr">
         <is>
-          <t>2026-11-04 10:00 AM ET</t>
+          <t>2026-10-28 09:00 AM ET</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>Thomas Hirchak Co.</t>
+          <t>THC Auction</t>
         </is>
       </c>
       <c r="L21" s="13" t="inlineStr">
@@ -19759,120 +19693,120 @@
       </c>
       <c r="O21" s="14" t="inlineStr">
         <is>
-          <t>Closes Wed Nov 4 10 AM, preview Oct 28, removal Nov 9, no shipping.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" outlineLevel="1">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>Maine / VT / Northern NH</t>
-        </is>
-      </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>Bread Loaf Corp wind-down – contractor equipment, staging, telehandler</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
+          <t>Company wind-down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Maine / VT / Northern NH</t>
+        </is>
+      </c>
+      <c r="B22" s="17" t="inlineStr">
+        <is>
+          <t>4 item(s)</t>
+        </is>
+      </c>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="18" t="n"/>
+      <c r="H22" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="18" t="n"/>
+      <c r="J22" s="18" t="n"/>
+      <c r="K22" s="18" t="n"/>
+      <c r="L22" s="18" t="n"/>
+      <c r="M22" s="18" t="n"/>
+      <c r="N22" s="18" t="n"/>
+      <c r="O22" s="18" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>▸ CT / Hudson Valley  (7)</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="12" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="12" t="n"/>
+      <c r="G23" s="12" t="n"/>
+      <c r="H23" s="12" t="n"/>
+      <c r="I23" s="12" t="n"/>
+      <c r="J23" s="12" t="n"/>
+      <c r="K23" s="12" t="n"/>
+      <c r="L23" s="12" t="n"/>
+      <c r="M23" s="12" t="n"/>
+      <c r="N23" s="12" t="n"/>
+      <c r="O23" s="12" t="n"/>
+    </row>
+    <row r="24" outlineLevel="1">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>CT / Hudson Valley</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>Bank-ordered electrical contractor sale – Greenlee/Hilti/Milwaukee tools, GE/Siemens breakers</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
         <is>
           <t>contractor liquidation</t>
         </is>
       </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>Middlebury</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>VT</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="n">
-        <v>177</v>
-      </c>
-      <c r="G22" s="13" t="inlineStr">
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>Clinton</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>106</v>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
         <is>
           <t>Online auction</t>
         </is>
       </c>
-      <c r="H22" s="15" t="n"/>
-      <c r="I22" s="13" t="inlineStr"/>
-      <c r="J22" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-28 09:00 AM ET</t>
-        </is>
-      </c>
-      <c r="K22" s="13" t="inlineStr">
-        <is>
-          <t>THC Auction</t>
-        </is>
-      </c>
-      <c r="L22" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M22" s="13" t="inlineStr"/>
-      <c r="N22" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O22" s="14" t="inlineStr">
-        <is>
-          <t>Company wind-down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Maine / VT / Northern NH</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>5 item(s)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="18" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
-      <c r="G23" s="18" t="n"/>
-      <c r="H23" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="18" t="n"/>
-      <c r="J23" s="18" t="n"/>
-      <c r="K23" s="18" t="n"/>
-      <c r="L23" s="18" t="n"/>
-      <c r="M23" s="18" t="n"/>
-      <c r="N23" s="18" t="n"/>
-      <c r="O23" s="18" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>▸ CT / Hudson Valley  (6)</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
-      <c r="G24" s="12" t="n"/>
-      <c r="H24" s="12" t="n"/>
-      <c r="I24" s="12" t="n"/>
-      <c r="J24" s="12" t="n"/>
-      <c r="K24" s="12" t="n"/>
-      <c r="L24" s="12" t="n"/>
-      <c r="M24" s="12" t="n"/>
-      <c r="N24" s="12" t="n"/>
-      <c r="O24" s="12" t="n"/>
+      <c r="H24" s="15" t="n"/>
+      <c r="I24" s="13" t="inlineStr"/>
+      <c r="J24" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-29 05:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>Hamilton Group / EstateSales.net</t>
+        </is>
+      </c>
+      <c r="L24" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M24" s="13" t="inlineStr"/>
+      <c r="N24" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O24" s="14" t="inlineStr">
+        <is>
+          <t>Listed "Oct 29 2 PM PST" (= 5 PM ET).</t>
+        </is>
+      </c>
     </row>
     <row r="25" outlineLevel="1">
       <c r="A25" s="13" t="inlineStr">
@@ -19882,17 +19816,17 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Bank-ordered electrical contractor sale – Greenlee/Hilti/Milwaukee tools, GE/Siemens breakers</t>
+          <t>Fabrication &amp; welding shop liquidation – everything must be sold</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>contractor liquidation</t>
+          <t>machine shop liquidation</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>Clinton</t>
+          <t>Bridgeport</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
@@ -19901,23 +19835,23 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Priced per machine (e.g. W.A. Whitney punch press $4,950; DoAll bandsaw $950)</t>
         </is>
       </c>
       <c r="H25" s="15" t="n"/>
-      <c r="I25" s="13" t="inlineStr"/>
-      <c r="J25" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-29 05:00 PM ET</t>
-        </is>
-      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="J25" s="13" t="inlineStr"/>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>Hamilton Group / EstateSales.net</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L25" s="13" t="inlineStr">
@@ -19933,7 +19867,7 @@
       </c>
       <c r="O25" s="14" t="inlineStr">
         <is>
-          <t>Listed "Oct 29 2 PM PST" (= 5 PM ET).</t>
+          <t>All assets/equipment/tools of a fab &amp; welding shop; machines under power, inspection by appointment, buyer removes (small forklift on site). Several big items already SOLD (Cincinnati brake/shear, plasma table, Lown roll). Remaining: Whitney + Roper Whitney punch presses, DoAll V36 bandsaw, Thompson spot welder, George Ohl 120" brake, Bridgeport mill, etc. Mostly 220V. Posted May 15, updated Oct 19.</t>
         </is>
       </c>
     </row>
@@ -20264,7 +20198,7 @@
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>6 item(s)</t>
+          <t>7 item(s)</t>
         </is>
       </c>
       <c r="C31" s="18" t="n"/>
@@ -20286,7 +20220,7 @@
     <row r="32">
       <c r="A32" s="11" t="inlineStr">
         <is>
-          <t>▸ NYC / Long Island / NJ  (24)</t>
+          <t>▸ NYC / Long Island / NJ  (23)</t>
         </is>
       </c>
       <c r="B32" s="12" t="n"/>
@@ -20547,9 +20481,9 @@
           <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
-      <c r="L36" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="L36" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M36" s="13" t="inlineStr"/>
@@ -20824,7 +20758,7 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>Like-new restaurant – steam tables, Coldline, Cleveland cook-and-hold, fryers, True freezers</t>
+          <t>Major food-service caterer – new-in-box True reach-ins, Beverage-Air, TurboChef, Resfab ventless fryer</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
@@ -20834,16 +20768,16 @@
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>Staten Island</t>
+          <t>Parsippany</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
@@ -20853,12 +20787,12 @@
       <c r="H41" s="15" t="n"/>
       <c r="I41" s="13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J41" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00 PM ET</t>
+          <t>2026-11-03 02:00 PM ET</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
@@ -20866,9 +20800,9 @@
           <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
-      <c r="L41" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+      <c r="L41" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M41" s="13" t="inlineStr"/>
@@ -20879,7 +20813,7 @@
       </c>
       <c r="O41" s="14" t="inlineStr">
         <is>
-          <t>"Short notice" auction Mon Oct 19 1 PM.</t>
+          <t>Tue Nov 3 2 PM, checkout Nov 4.</t>
         </is>
       </c>
     </row>
@@ -20891,17 +20825,17 @@
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>Major food-service caterer – new-in-box True reach-ins, Beverage-Air, TurboChef, Resfab ventless fryer</t>
+          <t>Business closing – 160 new Carnes exhaust fans</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>HVAC inventory</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>Parsippany</t>
+          <t>Kenilworth</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -20914,23 +20848,19 @@
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>$40 each or $5,000 all OBO</t>
         </is>
       </c>
       <c r="H42" s="15" t="n"/>
       <c r="I42" s="13" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="J42" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-03 02:00 PM ET</t>
-        </is>
-      </c>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J42" s="13" t="inlineStr"/>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L42" s="13" t="inlineStr">
@@ -20946,7 +20876,7 @@
       </c>
       <c r="O42" s="14" t="inlineStr">
         <is>
-          <t>Tue Nov 3 2 PM, checkout Nov 4.</t>
+          <t>160 new Carnes 80CFM 1.0 sone exhaust fans. $40 each or $5,000 for all OBO. Business closing HVAC inventory.</t>
         </is>
       </c>
     </row>
@@ -20958,12 +20888,12 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>Business closing – 160 new Carnes exhaust fans</t>
+          <t>Air Systems Inc – sheet metal / HVAC fabrication shop liquidation</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>HVAC inventory</t>
+          <t>HVAC shop liquidation</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
@@ -20981,19 +20911,19 @@
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t>$40 each or $5,000 all OBO</t>
+          <t>Timed online (15% BP)</t>
         </is>
       </c>
       <c r="H43" s="15" t="n"/>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="J43" s="13" t="inlineStr"/>
+      <c r="I43" s="13" t="inlineStr"/>
+      <c r="J43" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>A.J. Willner Auctions</t>
         </is>
       </c>
       <c r="L43" s="13" t="inlineStr">
@@ -21009,7 +20939,7 @@
       </c>
       <c r="O43" s="14" t="inlineStr">
         <is>
-          <t>160 new Carnes 80CFM 1.0 sone exhaust fans. $40 each or $5,000 for all OBO. Business closing HVAC inventory.</t>
+          <t>Vicon HVAC plasma; Flagler/Lockformer/Roto-Die/Engel fab; welders; Clark forklift; Genie Superlift; Ridgid/Milwaukee/DeWalt/Bosch/Hilti/Makita tools; AeroVent/Carnes exhaust fans; racking/scaffolding. Preview Oct 28–29 AM; pickup Oct 29 PM–Nov 4. Same town as Carnes fan CL lot.</t>
         </is>
       </c>
     </row>
@@ -21021,17 +20951,17 @@
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>Air Systems Inc – sheet metal / HVAC fabrication shop liquidation</t>
+          <t>Serpico's Pizzeria (lost lease) – Bari ovens, walk-in, Hobart 60qt, Vulcan range</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>HVAC shop liquidation</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>Kenilworth</t>
+          <t>Allenhurst</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -21040,28 +20970,28 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>Timed online (15% BP)</t>
+          <t>No-reserve online auction</t>
         </is>
       </c>
       <c r="H44" s="15" t="n"/>
       <c r="I44" s="13" t="inlineStr"/>
       <c r="J44" s="13" t="inlineStr">
         <is>
-          <t>2026-10-29 11:00 AM ET</t>
+          <t>2026-10-21 11:00 AM ET</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner Auctions</t>
-        </is>
-      </c>
-      <c r="L44" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Peter Costanzo / EstateSales.net</t>
+        </is>
+      </c>
+      <c r="L44" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M44" s="13" t="inlineStr"/>
@@ -21072,7 +21002,7 @@
       </c>
       <c r="O44" s="14" t="inlineStr">
         <is>
-          <t>Vicon HVAC plasma; Flagler/Lockformer/Roto-Die/Engel fab; welders; Clark forklift; Genie Superlift; Ridgid/Milwaukee/DeWalt/Bosch/Hilti/Makita tools; AeroVent/Carnes exhaust fans; racking/scaffolding. Preview Oct 28–29 AM; pickup Oct 29 PM–Nov 4. Same town as Carnes fan CL lot.</t>
+          <t>Absolute / no reserve.</t>
         </is>
       </c>
     </row>
@@ -21084,17 +21014,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>Serpico's Pizzeria (lost lease) – Bari ovens, walk-in, Hobart 60qt, Vulcan range</t>
+          <t>Altitude Trampoline Park liquidation – partial: Atosa, TurboChef, stainless</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>facility contents</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>Allenhurst</t>
+          <t>Iselin</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -21103,11 +21033,11 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>No-reserve online auction</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H45" s="15" t="n"/>
@@ -21119,7 +21049,7 @@
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>Peter Costanzo / EstateSales.net</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L45" s="20" t="inlineStr">
@@ -21135,7 +21065,7 @@
       </c>
       <c r="O45" s="14" t="inlineStr">
         <is>
-          <t>Absolute / no reserve.</t>
+          <t>Some kitchen gear only.</t>
         </is>
       </c>
     </row>
@@ -21147,17 +21077,17 @@
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>Altitude Trampoline Park liquidation – partial: Atosa, TurboChef, stainless</t>
+          <t>Restaurant / pizzeria (contents not described)</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>facility contents</t>
+          <t>restaurant closing</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>Iselin</t>
+          <t>Berkeley Heights</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -21166,23 +21096,27 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H46" s="15" t="n"/>
-      <c r="I46" s="13" t="inlineStr"/>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="J46" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 11:00 AM ET</t>
+          <t>2026-10-20 02:00 PM ET</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
       <c r="L46" s="20" t="inlineStr">
@@ -21198,7 +21132,7 @@
       </c>
       <c r="O46" s="14" t="inlineStr">
         <is>
-          <t>Some kitchen gear only.</t>
+          <t>Tue Oct 20 2 PM. No item description on page.</t>
         </is>
       </c>
     </row>
@@ -21210,17 +21144,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>Restaurant / pizzeria (contents not described)</t>
+          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>lien sale</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>Berkeley Heights</t>
+          <t>Edison</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -21229,32 +21163,24 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Online auction, $2K load-out fee</t>
         </is>
       </c>
       <c r="H47" s="15" t="n"/>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="J47" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-20 02:00 PM ET</t>
-        </is>
-      </c>
+      <c r="I47" s="13" t="inlineStr"/>
+      <c r="J47" s="13" t="inlineStr"/>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
-        </is>
-      </c>
-      <c r="L47" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>A.J. Willner</t>
+        </is>
+      </c>
+      <c r="L47" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M47" s="13" t="inlineStr"/>
@@ -21265,7 +21191,7 @@
       </c>
       <c r="O47" s="14" t="inlineStr">
         <is>
-          <t>Tue Oct 20 2 PM. No item description on page.</t>
+          <t>&gt;$100K new. Close date not captured.</t>
         </is>
       </c>
     </row>
@@ -21277,12 +21203,12 @@
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
+          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>lien sale</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
@@ -21300,15 +21226,23 @@
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>Online auction, $2K load-out fee</t>
+          <t>Live + HiBid webcast, 18% BP + 3% card</t>
         </is>
       </c>
       <c r="H48" s="15" t="n"/>
-      <c r="I48" s="13" t="inlineStr"/>
-      <c r="J48" s="13" t="inlineStr"/>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="J48" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-25 01:00 PM ET</t>
+        </is>
+      </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
       <c r="L48" s="13" t="inlineStr">
@@ -21316,7 +21250,11 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M48" s="13" t="inlineStr"/>
+      <c r="M48" s="21" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
       <c r="N48" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -21324,7 +21262,7 @@
       </c>
       <c r="O48" s="14" t="inlineStr">
         <is>
-          <t>&gt;$100K new. Close date not captured.</t>
+          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
         </is>
       </c>
     </row>
@@ -21336,17 +21274,17 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
+          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>Edison</t>
+          <t>East Brunswick</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -21355,27 +21293,23 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
-          <t>Live + HiBid webcast, 18% BP + 3% card</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H49" s="15" t="n"/>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
+      <c r="I49" s="13" t="inlineStr"/>
       <c r="J49" s="13" t="inlineStr">
         <is>
-          <t>2026-10-25 01:00 PM ET</t>
+          <t>2026-11-03 11:00 AM ET</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L49" s="13" t="inlineStr">
@@ -21383,11 +21317,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M49" s="21" t="inlineStr">
-        <is>
-          <t>FLIP</t>
-        </is>
-      </c>
+      <c r="M49" s="13" t="inlineStr"/>
       <c r="N49" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -21395,7 +21325,7 @@
       </c>
       <c r="O49" s="14" t="inlineStr">
         <is>
-          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
+          <t>Store inventory.</t>
         </is>
       </c>
     </row>
@@ -21407,17 +21337,17 @@
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
+          <t>High-end deli (contents not described)</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>restaurant closing</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>East Brunswick</t>
+          <t>Manalapan Township</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -21426,28 +21356,32 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H50" s="15" t="n"/>
-      <c r="I50" s="13" t="inlineStr"/>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="J50" s="13" t="inlineStr">
         <is>
-          <t>2026-11-03 11:00 AM ET</t>
+          <t>2026-10-19 04:00 PM ET</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
-        </is>
-      </c>
-      <c r="L50" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L50" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M50" s="13" t="inlineStr"/>
@@ -21458,7 +21392,7 @@
       </c>
       <c r="O50" s="14" t="inlineStr">
         <is>
-          <t>Store inventory.</t>
+          <t>Mon Oct 19 4 PM. No item description on page.</t>
         </is>
       </c>
     </row>
@@ -21470,17 +21404,17 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>High-end deli (contents not described)</t>
+          <t>Bakery/Cafe Somerville NJ – rack ovens, La Marzocco, food truck (~76 lots)</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>Manalapan Township</t>
+          <t>Somerville</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -21489,32 +21423,32 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Live webcast + online (18% BP online)</t>
         </is>
       </c>
       <c r="H51" s="15" t="n"/>
       <c r="I51" s="13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J51" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 04:00 PM ET</t>
+          <t>2026-10-26 02:00 PM ET</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
-        </is>
-      </c>
-      <c r="L51" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>HiBid / Best Buy Auctioneers</t>
+        </is>
+      </c>
+      <c r="L51" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M51" s="13" t="inlineStr"/>
@@ -21525,7 +21459,7 @@
       </c>
       <c r="O51" s="14" t="inlineStr">
         <is>
-          <t>Mon Oct 19 4 PM. No item description on page.</t>
+          <t>Full bakery/cafe commercial kitchen: food truck w/ pizza oven, La Marzocco espresso, Mazzer, Baxter + Empire Logiudice rack ovens, dough depositor, Globe floor mixer, Artic Air / SS refrigeration, fryers, Vitamix, Robot Coupe, display cases, dining furniture. Preview 11 AM sale day; checkout Tue 10/27.</t>
         </is>
       </c>
     </row>
@@ -21537,7 +21471,7 @@
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>Bakery/Cafe Somerville NJ – rack ovens, La Marzocco, food truck (~76 lots)</t>
+          <t>Ability to Work kitchen and store – commercial kitchen + store fixtures (~135 lots)</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
@@ -21547,7 +21481,7 @@
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>Somerville</t>
+          <t>Flemington</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -21556,27 +21490,23 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
-          <t>Live webcast + online (18% BP online)</t>
+          <t>Timed online (15% BP)</t>
         </is>
       </c>
       <c r="H52" s="15" t="n"/>
-      <c r="I52" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
+      <c r="I52" s="13" t="inlineStr"/>
       <c r="J52" s="13" t="inlineStr">
         <is>
-          <t>2026-10-26 02:00 PM ET</t>
+          <t>2026-10-27 11:02 AM ET</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>HiBid / Best Buy Auctioneers</t>
+          <t>HiBid</t>
         </is>
       </c>
       <c r="L52" s="13" t="inlineStr">
@@ -21592,7 +21522,7 @@
       </c>
       <c r="O52" s="14" t="inlineStr">
         <is>
-          <t>Full bakery/cafe commercial kitchen: food truck w/ pizza oven, La Marzocco espresso, Mazzer, Baxter + Empire Logiudice rack ovens, dough depositor, Globe floor mixer, Artic Air / SS refrigeration, fryers, Vitamix, Robot Coupe, display cases, dining furniture. Preview 11 AM sale day; checkout Tue 10/27.</t>
+          <t>Apprentice/hospitality training cafe-kitchen and store dispersal. Preview 9–11 AM sale day; removal Oct 27 noon–Oct 29.</t>
         </is>
       </c>
     </row>
@@ -21604,17 +21534,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>Ability to Work kitchen and store – commercial kitchen + store fixtures (~135 lots)</t>
+          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>showroom closing</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>Flemington</t>
+          <t>Lawrenceville</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -21623,23 +21553,23 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
-          <t>Timed online (15% BP)</t>
+          <t>Online auction, 18% BP</t>
         </is>
       </c>
       <c r="H53" s="15" t="n"/>
       <c r="I53" s="13" t="inlineStr"/>
       <c r="J53" s="13" t="inlineStr">
         <is>
-          <t>2026-10-27 11:02 AM ET</t>
+          <t>2026-10-27 09:00 AM ET</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>HiBid</t>
+          <t>Grafe Auction</t>
         </is>
       </c>
       <c r="L53" s="13" t="inlineStr">
@@ -21655,7 +21585,7 @@
       </c>
       <c r="O53" s="14" t="inlineStr">
         <is>
-          <t>Apprentice/hospitality training cafe-kitchen and store dispersal. Preview 9–11 AM sale day; removal Oct 27 noon–Oct 29.</t>
+          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
         </is>
       </c>
     </row>
@@ -21667,17 +21597,17 @@
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
+          <t>Milwaukee / Walmart / hardware store mega auction pt 3</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>showroom closing</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>Lawrenceville</t>
+          <t>Mount Holly</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -21686,28 +21616,28 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>Online auction, 18% BP</t>
+          <t>HiBid online auction</t>
         </is>
       </c>
       <c r="H54" s="15" t="n"/>
       <c r="I54" s="13" t="inlineStr"/>
       <c r="J54" s="13" t="inlineStr">
         <is>
-          <t>2026-10-27 09:00 AM ET</t>
+          <t>2026-10-19 06:00 PM ET</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L54" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>HiBid</t>
+        </is>
+      </c>
+      <c r="L54" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M54" s="13" t="inlineStr"/>
@@ -21718,7 +21648,7 @@
       </c>
       <c r="O54" s="14" t="inlineStr">
         <is>
-          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
+          <t>Close Oct 18 or 19 6 PM (later used).</t>
         </is>
       </c>
     </row>
@@ -21730,17 +21660,17 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Milwaukee / Walmart / hardware store mega auction pt 3</t>
+          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>showroom closing</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>Mount Holly</t>
+          <t>Cherry Hill</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -21749,28 +21679,28 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>254</v>
+        <v>266</v>
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
-          <t>HiBid online auction</t>
+          <t>Online auction, openers ~$0.50</t>
         </is>
       </c>
       <c r="H55" s="15" t="n"/>
       <c r="I55" s="13" t="inlineStr"/>
       <c r="J55" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 06:00 PM ET</t>
+          <t>2026-11-02 11:00 AM ET</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>HiBid</t>
-        </is>
-      </c>
-      <c r="L55" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L55" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M55" s="13" t="inlineStr"/>
@@ -21781,231 +21711,231 @@
       </c>
       <c r="O55" s="14" t="inlineStr">
         <is>
-          <t>Close Oct 18 or 19 6 PM (later used).</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" outlineLevel="1">
-      <c r="A56" s="13" t="inlineStr">
-        <is>
-          <t>NYC / Long Island / NJ</t>
-        </is>
-      </c>
-      <c r="B56" s="14" t="inlineStr">
-        <is>
-          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
-        </is>
-      </c>
-      <c r="C56" s="13" t="inlineStr">
-        <is>
-          <t>showroom closing</t>
-        </is>
-      </c>
-      <c r="D56" s="13" t="inlineStr">
-        <is>
-          <t>Cherry Hill</t>
-        </is>
-      </c>
-      <c r="E56" s="13" t="inlineStr">
-        <is>
-          <t>NJ</t>
-        </is>
-      </c>
-      <c r="F56" s="13" t="n">
-        <v>266</v>
-      </c>
-      <c r="G56" s="13" t="inlineStr">
-        <is>
-          <t>Online auction, openers ~$0.50</t>
-        </is>
-      </c>
-      <c r="H56" s="15" t="n"/>
-      <c r="I56" s="13" t="inlineStr"/>
-      <c r="J56" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-02 11:00 AM ET</t>
-        </is>
-      </c>
-      <c r="K56" s="13" t="inlineStr">
-        <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L56" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M56" s="13" t="inlineStr"/>
-      <c r="N56" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O56" s="14" t="inlineStr">
-        <is>
           <t>Lots close from Nov 2 11 AM.</t>
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>23 item(s)</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="n"/>
+      <c r="D56" s="18" t="n"/>
+      <c r="E56" s="18" t="n"/>
+      <c r="F56" s="18" t="n"/>
+      <c r="G56" s="18" t="n"/>
+      <c r="H56" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="18" t="n"/>
+      <c r="J56" s="18" t="n"/>
+      <c r="K56" s="18" t="n"/>
+      <c r="L56" s="18" t="n"/>
+      <c r="M56" s="18" t="n"/>
+      <c r="N56" s="18" t="n"/>
+      <c r="O56" s="18" t="n"/>
+    </row>
     <row r="57">
-      <c r="A57" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — NYC / Long Island / NJ</t>
-        </is>
-      </c>
-      <c r="B57" s="17" t="inlineStr">
-        <is>
-          <t>24 item(s)</t>
-        </is>
-      </c>
-      <c r="C57" s="18" t="n"/>
-      <c r="D57" s="18" t="n"/>
-      <c r="E57" s="18" t="n"/>
-      <c r="F57" s="18" t="n"/>
-      <c r="G57" s="18" t="n"/>
-      <c r="H57" s="19" t="n">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>▸ Eastern PA / Mid-Atlantic  (1)</t>
+        </is>
+      </c>
+      <c r="B57" s="12" t="n"/>
+      <c r="C57" s="12" t="n"/>
+      <c r="D57" s="12" t="n"/>
+      <c r="E57" s="12" t="n"/>
+      <c r="F57" s="12" t="n"/>
+      <c r="G57" s="12" t="n"/>
+      <c r="H57" s="12" t="n"/>
+      <c r="I57" s="12" t="n"/>
+      <c r="J57" s="12" t="n"/>
+      <c r="K57" s="12" t="n"/>
+      <c r="L57" s="12" t="n"/>
+      <c r="M57" s="12" t="n"/>
+      <c r="N57" s="12" t="n"/>
+      <c r="O57" s="12" t="n"/>
+    </row>
+    <row r="58" outlineLevel="1">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>Eastern PA / Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>October restaurant consignment – Hobart, Rational, True + NEW scratch-and-dent Migali/Avantco</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>Harrisburg</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="F58" s="13" t="n">
+        <v>340</v>
+      </c>
+      <c r="G58" s="13" t="inlineStr">
+        <is>
+          <t>Online auction, 15% BP, ships $55/pallet</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="n"/>
+      <c r="I58" s="13" t="inlineStr"/>
+      <c r="J58" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="inlineStr">
+        <is>
+          <t>Restaurant Auction Co</t>
+        </is>
+      </c>
+      <c r="L58" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M58" s="13" t="inlineStr"/>
+      <c r="N58" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O58" s="14" t="inlineStr">
+        <is>
+          <t>Closes Oct 21 10 or 11 AM (later used). Shippable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Eastern PA / Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>1 item(s)</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="n"/>
+      <c r="D59" s="18" t="n"/>
+      <c r="E59" s="18" t="n"/>
+      <c r="F59" s="18" t="n"/>
+      <c r="G59" s="18" t="n"/>
+      <c r="H59" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I57" s="18" t="n"/>
-      <c r="J57" s="18" t="n"/>
-      <c r="K57" s="18" t="n"/>
-      <c r="L57" s="18" t="n"/>
-      <c r="M57" s="18" t="n"/>
-      <c r="N57" s="18" t="n"/>
-      <c r="O57" s="18" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t>▸ Eastern PA / Mid-Atlantic  (1)</t>
-        </is>
-      </c>
-      <c r="B58" s="12" t="n"/>
-      <c r="C58" s="12" t="n"/>
-      <c r="D58" s="12" t="n"/>
-      <c r="E58" s="12" t="n"/>
-      <c r="F58" s="12" t="n"/>
-      <c r="G58" s="12" t="n"/>
-      <c r="H58" s="12" t="n"/>
-      <c r="I58" s="12" t="n"/>
-      <c r="J58" s="12" t="n"/>
-      <c r="K58" s="12" t="n"/>
-      <c r="L58" s="12" t="n"/>
-      <c r="M58" s="12" t="n"/>
-      <c r="N58" s="12" t="n"/>
-      <c r="O58" s="12" t="n"/>
-    </row>
-    <row r="59" outlineLevel="1">
-      <c r="A59" s="13" t="inlineStr">
-        <is>
-          <t>Eastern PA / Mid-Atlantic</t>
-        </is>
-      </c>
-      <c r="B59" s="14" t="inlineStr">
-        <is>
-          <t>October restaurant consignment – Hobart, Rational, True + NEW scratch-and-dent Migali/Avantco</t>
-        </is>
-      </c>
-      <c r="C59" s="13" t="inlineStr">
+      <c r="I59" s="18" t="n"/>
+      <c r="J59" s="18" t="n"/>
+      <c r="K59" s="18" t="n"/>
+      <c r="L59" s="18" t="n"/>
+      <c r="M59" s="18" t="n"/>
+      <c r="N59" s="18" t="n"/>
+      <c r="O59" s="18" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>▸ Upstate / Western NY  (3)</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="n"/>
+      <c r="C60" s="12" t="n"/>
+      <c r="D60" s="12" t="n"/>
+      <c r="E60" s="12" t="n"/>
+      <c r="F60" s="12" t="n"/>
+      <c r="G60" s="12" t="n"/>
+      <c r="H60" s="12" t="n"/>
+      <c r="I60" s="12" t="n"/>
+      <c r="J60" s="12" t="n"/>
+      <c r="K60" s="12" t="n"/>
+      <c r="L60" s="12" t="n"/>
+      <c r="M60" s="12" t="n"/>
+      <c r="N60" s="12" t="n"/>
+      <c r="O60" s="12" t="n"/>
+    </row>
+    <row r="61" outlineLevel="1">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>Upstate / Western NY</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>Former Taco Del Mar – stainless, warmers, walk-in panels</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
         <is>
           <t>restaurant</t>
         </is>
       </c>
-      <c r="D59" s="13" t="inlineStr">
-        <is>
-          <t>Harrisburg</t>
-        </is>
-      </c>
-      <c r="E59" s="13" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="F59" s="13" t="n">
-        <v>340</v>
-      </c>
-      <c r="G59" s="13" t="inlineStr">
-        <is>
-          <t>Online auction, 15% BP, ships $55/pallet</t>
-        </is>
-      </c>
-      <c r="H59" s="15" t="n"/>
-      <c r="I59" s="13" t="inlineStr"/>
-      <c r="J59" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 11:00 AM ET</t>
-        </is>
-      </c>
-      <c r="K59" s="13" t="inlineStr">
-        <is>
-          <t>Restaurant Auction Co</t>
-        </is>
-      </c>
-      <c r="L59" s="20" t="inlineStr">
+      <c r="D61" s="13" t="inlineStr">
+        <is>
+          <t>Watson</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F61" s="13" t="n">
+        <v>260</v>
+      </c>
+      <c r="G61" s="13" t="inlineStr">
+        <is>
+          <t>HiBid online auction</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="n"/>
+      <c r="I61" s="13" t="inlineStr"/>
+      <c r="J61" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
+        <is>
+          <t>Adirondack Asset / HiBid</t>
+        </is>
+      </c>
+      <c r="L61" s="20" t="inlineStr">
         <is>
           <t>ENDING SOON</t>
         </is>
       </c>
-      <c r="M59" s="13" t="inlineStr"/>
-      <c r="N59" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O59" s="14" t="inlineStr">
-        <is>
-          <t>Closes Oct 21 10 or 11 AM (later used). Shippable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Eastern PA / Mid-Atlantic</t>
-        </is>
-      </c>
-      <c r="B60" s="17" t="inlineStr">
-        <is>
-          <t>1 item(s)</t>
-        </is>
-      </c>
-      <c r="C60" s="18" t="n"/>
-      <c r="D60" s="18" t="n"/>
-      <c r="E60" s="18" t="n"/>
-      <c r="F60" s="18" t="n"/>
-      <c r="G60" s="18" t="n"/>
-      <c r="H60" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="18" t="n"/>
-      <c r="J60" s="18" t="n"/>
-      <c r="K60" s="18" t="n"/>
-      <c r="L60" s="18" t="n"/>
-      <c r="M60" s="18" t="n"/>
-      <c r="N60" s="18" t="n"/>
-      <c r="O60" s="18" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t>▸ Upstate / Western NY  (3)</t>
-        </is>
-      </c>
-      <c r="B61" s="12" t="n"/>
-      <c r="C61" s="12" t="n"/>
-      <c r="D61" s="12" t="n"/>
-      <c r="E61" s="12" t="n"/>
-      <c r="F61" s="12" t="n"/>
-      <c r="G61" s="12" t="n"/>
-      <c r="H61" s="12" t="n"/>
-      <c r="I61" s="12" t="n"/>
-      <c r="J61" s="12" t="n"/>
-      <c r="K61" s="12" t="n"/>
-      <c r="L61" s="12" t="n"/>
-      <c r="M61" s="12" t="n"/>
-      <c r="N61" s="12" t="n"/>
-      <c r="O61" s="12" t="n"/>
+      <c r="M61" s="13" t="inlineStr"/>
+      <c r="N61" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O61" s="14" t="inlineStr">
+        <is>
+          <t>Small lot.</t>
+        </is>
+      </c>
     </row>
     <row r="62" outlineLevel="1">
       <c r="A62" s="13" t="inlineStr">
@@ -22015,7 +21945,7 @@
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>Former Taco Del Mar – stainless, warmers, walk-in panels</t>
+          <t>Closed restaurant – coolers, fridges, prep tables</t>
         </is>
       </c>
       <c r="C62" s="13" t="inlineStr">
@@ -22025,7 +21955,7 @@
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>Watson</t>
+          <t>Palmyra</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
@@ -22034,23 +21964,23 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>260</v>
+        <v>333</v>
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>HiBid online auction</t>
+          <t>HiBid, 15% BP</t>
         </is>
       </c>
       <c r="H62" s="15" t="n"/>
       <c r="I62" s="13" t="inlineStr"/>
       <c r="J62" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 06:00 PM ET</t>
+          <t>2026-10-19 07:00 PM ET</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>Adirondack Asset / HiBid</t>
+          <t>Reynolds Auction Co / HiBid</t>
         </is>
       </c>
       <c r="L62" s="20" t="inlineStr">
@@ -22066,7 +21996,7 @@
       </c>
       <c r="O62" s="14" t="inlineStr">
         <is>
-          <t>Small lot.</t>
+          <t>No new out-of-state bidders. Small.</t>
         </is>
       </c>
     </row>
@@ -22078,7 +22008,7 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>Closed restaurant – coolers, fridges, prep tables</t>
+          <t>Restaurant &amp; fitness equipment</t>
         </is>
       </c>
       <c r="C63" s="13" t="inlineStr">
@@ -22088,7 +22018,7 @@
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>Palmyra</t>
+          <t>Williamsville</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
@@ -22097,28 +22027,28 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>333</v>
+        <v>408</v>
       </c>
       <c r="G63" s="13" t="inlineStr">
         <is>
-          <t>HiBid, 15% BP</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H63" s="15" t="n"/>
       <c r="I63" s="13" t="inlineStr"/>
       <c r="J63" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 07:00 PM ET</t>
+          <t>2026-10-26 07:30 PM ET</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
         <is>
-          <t>Reynolds Auction Co / HiBid</t>
-        </is>
-      </c>
-      <c r="L63" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Cash Auctions</t>
+        </is>
+      </c>
+      <c r="L63" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M63" s="13" t="inlineStr"/>
@@ -22129,231 +22059,231 @@
       </c>
       <c r="O63" s="14" t="inlineStr">
         <is>
-          <t>No new out-of-state bidders. Small.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" outlineLevel="1">
-      <c r="A64" s="13" t="inlineStr">
-        <is>
-          <t>Upstate / Western NY</t>
-        </is>
-      </c>
-      <c r="B64" s="14" t="inlineStr">
-        <is>
-          <t>Restaurant &amp; fitness equipment</t>
-        </is>
-      </c>
-      <c r="C64" s="13" t="inlineStr">
-        <is>
-          <t>restaurant</t>
-        </is>
-      </c>
-      <c r="D64" s="13" t="inlineStr">
-        <is>
-          <t>Williamsville</t>
-        </is>
-      </c>
-      <c r="E64" s="13" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="F64" s="13" t="n">
-        <v>408</v>
-      </c>
-      <c r="G64" s="13" t="inlineStr">
+          <t>Lots not reviewed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Upstate / Western NY</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>3 item(s)</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="n"/>
+      <c r="D64" s="18" t="n"/>
+      <c r="E64" s="18" t="n"/>
+      <c r="F64" s="18" t="n"/>
+      <c r="G64" s="18" t="n"/>
+      <c r="H64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="18" t="n"/>
+      <c r="J64" s="18" t="n"/>
+      <c r="K64" s="18" t="n"/>
+      <c r="L64" s="18" t="n"/>
+      <c r="M64" s="18" t="n"/>
+      <c r="N64" s="18" t="n"/>
+      <c r="O64" s="18" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>▸ Virginia  (1)</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="n"/>
+      <c r="C65" s="12" t="n"/>
+      <c r="D65" s="12" t="n"/>
+      <c r="E65" s="12" t="n"/>
+      <c r="F65" s="12" t="n"/>
+      <c r="G65" s="12" t="n"/>
+      <c r="H65" s="12" t="n"/>
+      <c r="I65" s="12" t="n"/>
+      <c r="J65" s="12" t="n"/>
+      <c r="K65" s="12" t="n"/>
+      <c r="L65" s="12" t="n"/>
+      <c r="M65" s="12" t="n"/>
+      <c r="N65" s="12" t="n"/>
+      <c r="O65" s="12" t="n"/>
+    </row>
+    <row r="66" outlineLevel="1">
+      <c r="A66" s="13" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>Haynes Furniture / The Dump – 12 stores closing (furniture, mattresses)</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="inlineStr">
+        <is>
+          <t>retail GOB</t>
+        </is>
+      </c>
+      <c r="D66" s="13" t="inlineStr">
+        <is>
+          <t>Virginia Beach</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="F66" s="13" t="n">
+        <v>456</v>
+      </c>
+      <c r="G66" s="13" t="inlineStr">
+        <is>
+          <t>Retail GOB markdowns</t>
+        </is>
+      </c>
+      <c r="H66" s="15" t="n"/>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="J66" s="13" t="inlineStr"/>
+      <c r="K66" s="13" t="inlineStr">
+        <is>
+          <t>SB360 (PR Newswire)</t>
+        </is>
+      </c>
+      <c r="L66" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M66" s="13" t="inlineStr"/>
+      <c r="N66" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O66" s="14" t="inlineStr">
+        <is>
+          <t>Posted Oct 8. Multi-state (VA/AZ/GA/IL/TX); pinned at Virginia Beach. Home goods only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Virginia</t>
+        </is>
+      </c>
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t>1 item(s)</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="n"/>
+      <c r="D67" s="18" t="n"/>
+      <c r="E67" s="18" t="n"/>
+      <c r="F67" s="18" t="n"/>
+      <c r="G67" s="18" t="n"/>
+      <c r="H67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="18" t="n"/>
+      <c r="J67" s="18" t="n"/>
+      <c r="K67" s="18" t="n"/>
+      <c r="L67" s="18" t="n"/>
+      <c r="M67" s="18" t="n"/>
+      <c r="N67" s="18" t="n"/>
+      <c r="O67" s="18" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>▸ Midwest  (3)</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="n"/>
+      <c r="C68" s="12" t="n"/>
+      <c r="D68" s="12" t="n"/>
+      <c r="E68" s="12" t="n"/>
+      <c r="F68" s="12" t="n"/>
+      <c r="G68" s="12" t="n"/>
+      <c r="H68" s="12" t="n"/>
+      <c r="I68" s="12" t="n"/>
+      <c r="J68" s="12" t="n"/>
+      <c r="K68" s="12" t="n"/>
+      <c r="L68" s="12" t="n"/>
+      <c r="M68" s="12" t="n"/>
+      <c r="N68" s="12" t="n"/>
+      <c r="O68" s="12" t="n"/>
+    </row>
+    <row r="69" outlineLevel="1">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>Freshway Market whole-grocery liquidation – refrigeration racks, cases, walk-ins, generator</t>
+        </is>
+      </c>
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>store closing</t>
+        </is>
+      </c>
+      <c r="D69" s="13" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="F69" s="13" t="n">
+        <v>862</v>
+      </c>
+      <c r="G69" s="13" t="inlineStr">
         <is>
           <t>Online auction</t>
         </is>
       </c>
-      <c r="H64" s="15" t="n"/>
-      <c r="I64" s="13" t="inlineStr"/>
-      <c r="J64" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-26 07:30 PM ET</t>
-        </is>
-      </c>
-      <c r="K64" s="13" t="inlineStr">
-        <is>
-          <t>Cash Auctions</t>
-        </is>
-      </c>
-      <c r="L64" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M64" s="13" t="inlineStr"/>
-      <c r="N64" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O64" s="14" t="inlineStr">
-        <is>
-          <t>Lots not reviewed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Upstate / Western NY</t>
-        </is>
-      </c>
-      <c r="B65" s="17" t="inlineStr">
-        <is>
-          <t>3 item(s)</t>
-        </is>
-      </c>
-      <c r="C65" s="18" t="n"/>
-      <c r="D65" s="18" t="n"/>
-      <c r="E65" s="18" t="n"/>
-      <c r="F65" s="18" t="n"/>
-      <c r="G65" s="18" t="n"/>
-      <c r="H65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="18" t="n"/>
-      <c r="J65" s="18" t="n"/>
-      <c r="K65" s="18" t="n"/>
-      <c r="L65" s="18" t="n"/>
-      <c r="M65" s="18" t="n"/>
-      <c r="N65" s="18" t="n"/>
-      <c r="O65" s="18" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t>▸ Virginia  (1)</t>
-        </is>
-      </c>
-      <c r="B66" s="12" t="n"/>
-      <c r="C66" s="12" t="n"/>
-      <c r="D66" s="12" t="n"/>
-      <c r="E66" s="12" t="n"/>
-      <c r="F66" s="12" t="n"/>
-      <c r="G66" s="12" t="n"/>
-      <c r="H66" s="12" t="n"/>
-      <c r="I66" s="12" t="n"/>
-      <c r="J66" s="12" t="n"/>
-      <c r="K66" s="12" t="n"/>
-      <c r="L66" s="12" t="n"/>
-      <c r="M66" s="12" t="n"/>
-      <c r="N66" s="12" t="n"/>
-      <c r="O66" s="12" t="n"/>
-    </row>
-    <row r="67" outlineLevel="1">
-      <c r="A67" s="13" t="inlineStr">
-        <is>
-          <t>Virginia</t>
-        </is>
-      </c>
-      <c r="B67" s="14" t="inlineStr">
-        <is>
-          <t>Haynes Furniture / The Dump – 12 stores closing (furniture, mattresses)</t>
-        </is>
-      </c>
-      <c r="C67" s="13" t="inlineStr">
-        <is>
-          <t>retail GOB</t>
-        </is>
-      </c>
-      <c r="D67" s="13" t="inlineStr">
-        <is>
-          <t>Virginia Beach</t>
-        </is>
-      </c>
-      <c r="E67" s="13" t="inlineStr">
-        <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="F67" s="13" t="n">
-        <v>456</v>
-      </c>
-      <c r="G67" s="13" t="inlineStr">
-        <is>
-          <t>Retail GOB markdowns</t>
-        </is>
-      </c>
-      <c r="H67" s="15" t="n"/>
-      <c r="I67" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="J67" s="13" t="inlineStr"/>
-      <c r="K67" s="13" t="inlineStr">
-        <is>
-          <t>SB360 (PR Newswire)</t>
-        </is>
-      </c>
-      <c r="L67" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M67" s="13" t="inlineStr"/>
-      <c r="N67" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O67" s="14" t="inlineStr">
-        <is>
-          <t>Posted Oct 8. Multi-state (VA/AZ/GA/IL/TX); pinned at Virginia Beach. Home goods only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Virginia</t>
-        </is>
-      </c>
-      <c r="B68" s="17" t="inlineStr">
-        <is>
-          <t>1 item(s)</t>
-        </is>
-      </c>
-      <c r="C68" s="18" t="n"/>
-      <c r="D68" s="18" t="n"/>
-      <c r="E68" s="18" t="n"/>
-      <c r="F68" s="18" t="n"/>
-      <c r="G68" s="18" t="n"/>
-      <c r="H68" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="18" t="n"/>
-      <c r="J68" s="18" t="n"/>
-      <c r="K68" s="18" t="n"/>
-      <c r="L68" s="18" t="n"/>
-      <c r="M68" s="18" t="n"/>
-      <c r="N68" s="18" t="n"/>
-      <c r="O68" s="18" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t>▸ Midwest  (2)</t>
-        </is>
-      </c>
-      <c r="B69" s="12" t="n"/>
-      <c r="C69" s="12" t="n"/>
-      <c r="D69" s="12" t="n"/>
-      <c r="E69" s="12" t="n"/>
-      <c r="F69" s="12" t="n"/>
-      <c r="G69" s="12" t="n"/>
-      <c r="H69" s="12" t="n"/>
-      <c r="I69" s="12" t="n"/>
-      <c r="J69" s="12" t="n"/>
-      <c r="K69" s="12" t="n"/>
-      <c r="L69" s="12" t="n"/>
-      <c r="M69" s="12" t="n"/>
-      <c r="N69" s="12" t="n"/>
-      <c r="O69" s="12" t="n"/>
+      <c r="H69" s="15" t="n"/>
+      <c r="I69" s="13" t="inlineStr"/>
+      <c r="J69" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="inlineStr">
+        <is>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L69" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M69" s="13" t="inlineStr"/>
+      <c r="N69" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O69" s="14" t="inlineStr">
+        <is>
+          <t>Closes from Oct 20 10 AM CDT.</t>
+        </is>
+      </c>
     </row>
     <row r="70" outlineLevel="1">
       <c r="A70" s="13" t="inlineStr">
@@ -22363,17 +22293,17 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>Freshway Market whole-grocery liquidation – refrigeration racks, cases, walk-ins, generator</t>
+          <t>American Sale – total liquidation, all 7 stores (pools, hot tubs, grills, holiday decor)</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>retail GOB</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Chicagoland</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
@@ -22382,28 +22312,28 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>862</v>
+        <v>876</v>
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Retail GOB, up to 70% off</t>
         </is>
       </c>
       <c r="H70" s="15" t="n"/>
-      <c r="I70" s="13" t="inlineStr"/>
-      <c r="J70" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-20 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J70" s="13" t="inlineStr"/>
       <c r="K70" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L70" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Tiger Group (PR Newswire)</t>
+        </is>
+      </c>
+      <c r="L70" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M70" s="13" t="inlineStr"/>
@@ -22414,7 +22344,7 @@
       </c>
       <c r="O70" s="14" t="inlineStr">
         <is>
-          <t>Closes from Oct 20 10 AM CDT.</t>
+          <t>Posted Oct 15. Watch for a bulk/fixture auction.</t>
         </is>
       </c>
     </row>
@@ -22426,47 +22356,47 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>American Sale – total liquidation, all 7 stores (pools, hot tubs, grills, holiday decor)</t>
+          <t>Straub's Fine Foods store equipment – bakery, kitchen, meat room, Hussmann refrigeration</t>
         </is>
       </c>
       <c r="C71" s="13" t="inlineStr">
         <is>
-          <t>retail GOB</t>
+          <t>grocery/restaurant</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>Chicagoland</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>876</v>
+        <v>1046</v>
       </c>
       <c r="G71" s="13" t="inlineStr">
         <is>
-          <t>Retail GOB, up to 70% off</t>
+          <t>Online auction (18% BP)</t>
         </is>
       </c>
       <c r="H71" s="15" t="n"/>
-      <c r="I71" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="J71" s="13" t="inlineStr"/>
+      <c r="I71" s="13" t="inlineStr"/>
+      <c r="J71" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K71" s="13" t="inlineStr">
         <is>
-          <t>Tiger Group (PR Newswire)</t>
-        </is>
-      </c>
-      <c r="L71" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L71" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M71" s="13" t="inlineStr"/>
@@ -22477,7 +22407,7 @@
       </c>
       <c r="O71" s="14" t="inlineStr">
         <is>
-          <t>Posted Oct 15. Watch for a bulk/fixture auction.</t>
+          <t>Kingshighway store: Revent double-rack oven + proofer, Reed revolving oven, Vulcan convection, Groen kettle, Southbend 6-burner, Pitco fryer, Stero dishwasher, Hobart saw/grinders, Berkel slicers, Hussmann cases + compressor racks, walk-ins, Hoshizaki/Scotsman ice machines, Crown pallet jack. Preview Oct 20 3–6 PM CDT; pickup in St. Louis.</t>
         </is>
       </c>
     </row>
@@ -22489,7 +22419,7 @@
       </c>
       <c r="B72" s="17" t="inlineStr">
         <is>
-          <t>2 item(s)</t>
+          <t>3 item(s)</t>
         </is>
       </c>
       <c r="C72" s="18" t="n"/>
@@ -22746,7 +22676,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId17"/>
@@ -22776,12 +22706,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N61" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N62" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N64" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N67" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N66" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N69" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N71" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N74" r:id="rId52"/>
@@ -22797,7 +22727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -23091,7 +23021,7 @@
       </c>
       <c r="O4" s="14" t="inlineStr">
         <is>
-          <t>Condition: Pre-Owned. FLIP: SO36U/S tested, auction $99/0 bids, pickup only; rough resale $600-1k (eBay card shows no city; pickup distance in source.) Ends Oct 18 ~2:19 PM per eBay card (time zone uncertain; could be earlier). [auto-removed 2026-10-18: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed]</t>
+          <t>Condition: Pre-Owned. FLIP: SO36U/S tested, auction $99/0 bids, pickup only; rough resale $600-1k (eBay card shows no city; pickup distance in source.) Ends Oct 18 ~2:19 PM per eBay card (time zone uncertain; could be earlier). [auto-removed 2026-10-18: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23156,59 +23086,61 @@
       </c>
       <c r="O5" s="14" t="inlineStr">
         <is>
-          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf) HiBid lot closed/sold ~$37.50 on 2026-10-18. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed]</t>
+          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf) HiBid lot closed/sold ~$37.50 on 2026-10-18. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Greater Boston / South Shore (&lt;50mi)</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>Closed Best Buy Outlet – pallet racking, Big Joe order pickers, appliance dollies, carts, cages</t>
+          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Louisville)</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>store closing fixtures</t>
+          <t>auction catalog</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Brockton</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>KY</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>11</v>
+        <v>832</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>Racking $40/upright, $80/level; pickers $1,000 OBO</t>
-        </is>
-      </c>
-      <c r="H6" s="15" t="n"/>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="J6" s="13" t="inlineStr"/>
+          <t>$0–1 openers + 15% BP + $1/lot</t>
+        </is>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr"/>
+      <c r="J6" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 02:00 PM ET</t>
+        </is>
+      </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>HiBid (Auctionfuel)</t>
         </is>
       </c>
       <c r="L6" s="13" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>EXPIRED (2026-10-19 02:00 PM ET)</t>
         </is>
       </c>
       <c r="M6" s="13" t="inlineStr"/>
@@ -23219,18 +23151,214 @@
       </c>
       <c r="O6" s="14" t="inlineStr">
         <is>
+          <t>Lots close from Oct 19 2 PM ET. [HiBid catalog closed 2 PM ET Oct 19.] [auto-removed 2026-10-19: closing date passed]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Maine / VT / Northern NH</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Oola Bowls secured-party sale – restaurant equipment bought new 2024-25 (Electro Freeze, Scotsman, Atosa)</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Scarborough</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>104</v>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>Online auction (freezers $80–150 when seen)</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="n"/>
+      <c r="I7" s="13" t="inlineStr"/>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 01:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>Keenan Auction / Proxibid</t>
+        </is>
+      </c>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>EXPIRED (2026-10-19 01:00 PM ET)</t>
+        </is>
+      </c>
+      <c r="M7" s="13" t="inlineStr"/>
+      <c r="N7" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O7" s="14" t="inlineStr">
+        <is>
+          <t>Pickup Oct 21 only. [Lots began closing 1 PM ET Oct 19; ended.] [auto-removed 2026-10-19: closing date passed]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Greater Boston / South Shore (&lt;50mi)</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Closed Best Buy Outlet – pallet racking, Big Joe order pickers, appliance dollies, carts, cages</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>store closing fixtures</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Brockton</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>Racking $40/upright, $80/level; pickers $1,000 OBO</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="n"/>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="J8" s="13" t="inlineStr"/>
+      <c r="K8" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L8" s="13" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="M8" s="13" t="inlineStr"/>
+      <c r="N8" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O8" s="14" t="inlineStr">
+        <is>
           <t>200 Westgate Dr. Fixtures/equipment only, no merchandise. On site daily. CL deleted by author (HTTP 410) as of 2026-10-19 midday recheck.</t>
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Like-new restaurant – steam tables, Coldline, Cleveland cook-and-hold, fryers, True freezers</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>auction</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>Staten Island</t>
+        </is>
+      </c>
+      <c r="E9" s="13" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F9" s="13" t="n">
+        <v>203</v>
+      </c>
+      <c r="G9" s="13" t="inlineStr">
+        <is>
+          <t>Live + webcast, 18% BP + 3%</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="n"/>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J9" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 01:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K9" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>EXPIRED (2026-10-19 01:00 PM ET)</t>
+        </is>
+      </c>
+      <c r="M9" s="13" t="inlineStr"/>
+      <c r="N9" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O9" s="14" t="inlineStr">
+        <is>
+          <t>"Short notice" auction Mon Oct 19 1 PM. [auto-removed 2026-10-19: closing date passed]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O6"/>
+  <autoFilter ref="A1:O9"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lot_recon.xlsx
+++ b/lot_recon.xlsx
@@ -16,12 +16,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Removed" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Appliance Parts'!$A$1:$O$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Appliance Parts'!$A$1:$O$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wolf New'!$A$1:$O$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wolf Used'!$A$1:$O$189</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Wolf Unclear'!$A$1:$O$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$78</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Removed'!$A$1:$O$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Removed'!$A$1:$O$12</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -577,7 +577,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Last updated: 2026-10-19 14:04 ET</t>
+          <t>Last updated: 2026-10-19 18:06 ET</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Active listings: 293 · Removed: 8</t>
+          <t>Active listings: 293 · Removed: 11</t>
         </is>
       </c>
     </row>
@@ -641,13 +641,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>159696</v>
       </c>
       <c r="D8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
         <v>34</v>
@@ -708,13 +708,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13">
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -806,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>5398.69</v>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -1004,7 +1004,7 @@
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H23" s="6" t="n">
         <v>64740</v>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -1037,7 +1037,7 @@
         <v>24</v>
       </c>
       <c r="G24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>440141</v>
@@ -1088,10 +1088,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D26" t="n">
         <v>0</v>
@@ -1110,7 +1110,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>487–499</t>
+          <t>487</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O42"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1938,7 +1938,7 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t>▸ Western PA / Ohio Valley  (2)</t>
+          <t>▸ Western PA / Ohio Valley  (1)</t>
         </is>
       </c>
       <c r="B14" s="12" t="n"/>
@@ -2021,229 +2021,231 @@
         </is>
       </c>
     </row>
-    <row r="16" outlineLevel="1">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>Western PA / Ohio Valley</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>Allshouse Appliance Store &amp; Warehouse Dispersal (mostly whole units, racking, forklift)</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>auction / dispersal</t>
-        </is>
-      </c>
-      <c r="D16" s="13" t="inlineStr">
-        <is>
-          <t>New Castle</t>
-        </is>
-      </c>
-      <c r="E16" s="13" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="F16" s="13" t="n">
-        <v>499</v>
-      </c>
-      <c r="G16" s="13" t="inlineStr">
-        <is>
-          <t>Auction – 5% BP (waived for cash)</t>
-        </is>
-      </c>
-      <c r="H16" s="15" t="n"/>
-      <c r="I16" s="13" t="inlineStr"/>
-      <c r="J16" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-19 04:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K16" s="13" t="inlineStr">
-        <is>
-          <t>Duke Whiting Auctions</t>
-        </is>
-      </c>
-      <c r="L16" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M16" s="13" t="inlineStr"/>
-      <c r="N16" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O16" s="14" t="inlineStr">
-        <is>
-          <t>Live auction Mon Oct 19 4 PM, 3457 Wilmington Rd. Few bulk parts.</t>
-        </is>
-      </c>
+    <row r="16">
+      <c r="A16" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Western PA / Ohio Valley</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>1 item(s)</t>
+        </is>
+      </c>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="18" t="n"/>
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="19" t="n">
+        <v>175</v>
+      </c>
+      <c r="I16" s="18" t="n"/>
+      <c r="J16" s="18" t="n"/>
+      <c r="K16" s="18" t="n"/>
+      <c r="L16" s="18" t="n"/>
+      <c r="M16" s="18" t="n"/>
+      <c r="N16" s="18" t="n"/>
+      <c r="O16" s="18" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Western PA / Ohio Valley</t>
-        </is>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C17" s="18" t="n"/>
-      <c r="D17" s="18" t="n"/>
-      <c r="E17" s="18" t="n"/>
-      <c r="F17" s="18" t="n"/>
-      <c r="G17" s="18" t="n"/>
-      <c r="H17" s="19" t="n">
-        <v>175</v>
-      </c>
-      <c r="I17" s="18" t="n"/>
-      <c r="J17" s="18" t="n"/>
-      <c r="K17" s="18" t="n"/>
-      <c r="L17" s="18" t="n"/>
-      <c r="M17" s="18" t="n"/>
-      <c r="N17" s="18" t="n"/>
-      <c r="O17" s="18" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="A17" s="11" t="inlineStr">
         <is>
           <t>▸ Virginia  (1)</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
-      <c r="H18" s="12" t="n"/>
-      <c r="I18" s="12" t="n"/>
-      <c r="J18" s="12" t="n"/>
-      <c r="K18" s="12" t="n"/>
-      <c r="L18" s="12" t="n"/>
-      <c r="M18" s="12" t="n"/>
-      <c r="N18" s="12" t="n"/>
-      <c r="O18" s="12" t="n"/>
-    </row>
-    <row r="19" outlineLevel="1">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="B17" s="12" t="n"/>
+      <c r="C17" s="12" t="n"/>
+      <c r="D17" s="12" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="12" t="n"/>
+      <c r="G17" s="12" t="n"/>
+      <c r="H17" s="12" t="n"/>
+      <c r="I17" s="12" t="n"/>
+      <c r="J17" s="12" t="n"/>
+      <c r="K17" s="12" t="n"/>
+      <c r="L17" s="12" t="n"/>
+      <c r="M17" s="12" t="n"/>
+      <c r="N17" s="12" t="n"/>
+      <c r="O17" s="12" t="n"/>
+    </row>
+    <row r="18" outlineLevel="1">
+      <c r="A18" s="13" t="inlineStr">
         <is>
           <t>Virginia</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>Appliance parts – OEM wholesale lot</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C18" s="13" t="inlineStr">
         <is>
           <t>bulk lot</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>Suffolk</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>VA</t>
         </is>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F18" s="13" t="n">
         <v>483</v>
       </c>
-      <c r="G19" s="13" t="inlineStr">
+      <c r="G18" s="13" t="inlineStr">
         <is>
           <t>$1,500 OBO</t>
         </is>
       </c>
-      <c r="H19" s="15" t="n">
+      <c r="H18" s="15" t="n">
         <v>1500</v>
       </c>
-      <c r="I19" s="13" t="inlineStr">
+      <c r="I18" s="13" t="inlineStr">
         <is>
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="J19" s="13" t="inlineStr"/>
-      <c r="K19" s="13" t="inlineStr">
+      <c r="J18" s="13" t="inlineStr"/>
+      <c r="K18" s="13" t="inlineStr">
         <is>
           <t>Craigslist</t>
         </is>
       </c>
-      <c r="L19" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M19" s="13" t="inlineStr"/>
-      <c r="N19" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O19" s="14" t="inlineStr">
+      <c r="L18" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M18" s="13" t="inlineStr"/>
+      <c r="N18" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O18" s="14" t="inlineStr">
         <is>
           <t>Seller delivers only within southern VA / eastern NC.</t>
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Virginia</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>1 item(s)</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
+      <c r="F19" s="18" t="n"/>
+      <c r="G19" s="18" t="n"/>
+      <c r="H19" s="19" t="n">
+        <v>1500</v>
+      </c>
+      <c r="I19" s="18" t="n"/>
+      <c r="J19" s="18" t="n"/>
+      <c r="K19" s="18" t="n"/>
+      <c r="L19" s="18" t="n"/>
+      <c r="M19" s="18" t="n"/>
+      <c r="N19" s="18" t="n"/>
+      <c r="O19" s="18" t="n"/>
+    </row>
     <row r="20">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Virginia</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="inlineStr">
-        <is>
-          <t>1 item(s)</t>
-        </is>
-      </c>
-      <c r="C20" s="18" t="n"/>
-      <c r="D20" s="18" t="n"/>
-      <c r="E20" s="18" t="n"/>
-      <c r="F20" s="18" t="n"/>
-      <c r="G20" s="18" t="n"/>
-      <c r="H20" s="19" t="n">
-        <v>1500</v>
-      </c>
-      <c r="I20" s="18" t="n"/>
-      <c r="J20" s="18" t="n"/>
-      <c r="K20" s="18" t="n"/>
-      <c r="L20" s="18" t="n"/>
-      <c r="M20" s="18" t="n"/>
-      <c r="N20" s="18" t="n"/>
-      <c r="O20" s="18" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>▸ Southeast  (4)</t>
         </is>
       </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="12" t="n"/>
-      <c r="H21" s="12" t="n"/>
-      <c r="I21" s="12" t="n"/>
-      <c r="J21" s="12" t="n"/>
-      <c r="K21" s="12" t="n"/>
-      <c r="L21" s="12" t="n"/>
-      <c r="M21" s="12" t="n"/>
-      <c r="N21" s="12" t="n"/>
-      <c r="O21" s="12" t="n"/>
+      <c r="B20" s="12" t="n"/>
+      <c r="C20" s="12" t="n"/>
+      <c r="D20" s="12" t="n"/>
+      <c r="E20" s="12" t="n"/>
+      <c r="F20" s="12" t="n"/>
+      <c r="G20" s="12" t="n"/>
+      <c r="H20" s="12" t="n"/>
+      <c r="I20" s="12" t="n"/>
+      <c r="J20" s="12" t="n"/>
+      <c r="K20" s="12" t="n"/>
+      <c r="L20" s="12" t="n"/>
+      <c r="M20" s="12" t="n"/>
+      <c r="N20" s="12" t="n"/>
+      <c r="O20" s="12" t="n"/>
+    </row>
+    <row r="21" outlineLevel="1">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>Southeast</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Appliance repair business &amp; parts – "over 100k in new and used appliance parts"</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>business + parts inventory</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Hustonville</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>KY</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>808</v>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>$36,000</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="n">
+        <v>36000</v>
+      </c>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="J21" s="13" t="inlineStr"/>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L21" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M21" s="13" t="inlineStr"/>
+      <c r="N21" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O21" s="14" t="inlineStr">
+        <is>
+          <t>By owner. Whole parts inventory (new + used) sold as a start-a-repair-business package. Far (~950 mi) but very large.</t>
+        </is>
+      </c>
     </row>
     <row r="22" outlineLevel="1">
       <c r="A22" s="13" t="inlineStr">
@@ -2253,17 +2255,17 @@
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>Appliance repair business &amp; parts – "over 100k in new and used appliance parts"</t>
+          <t>[SMALL] Whirlpool parts assortment</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>business + parts inventory</t>
+          <t>small lot</t>
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>Hustonville</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
@@ -2272,21 +2274,15 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>808</v>
+        <v>832</v>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>$36,000</t>
-        </is>
-      </c>
-      <c r="H22" s="15" t="n">
-        <v>36000</v>
-      </c>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
+          <t>Price n/a</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="n"/>
+      <c r="I22" s="13" t="inlineStr"/>
       <c r="J22" s="13" t="inlineStr"/>
       <c r="K22" s="13" t="inlineStr">
         <is>
@@ -2306,7 +2302,7 @@
       </c>
       <c r="O22" s="14" t="inlineStr">
         <is>
-          <t>By owner. Whole parts inventory (new + used) sold as a start-a-repair-business package. Far (~950 mi) but very large.</t>
+          <t>Small lead.</t>
         </is>
       </c>
     </row>
@@ -2318,43 +2314,53 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>[SMALL] Whirlpool parts assortment</t>
+          <t>Misc. appliance parts pallet (parts only)</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>small lot</t>
+          <t>auction pallet</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>Dalton</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>KY</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>832</v>
+        <v>917</v>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>Price n/a</t>
-        </is>
-      </c>
-      <c r="H23" s="15" t="n"/>
-      <c r="I23" s="13" t="inlineStr"/>
-      <c r="J23" s="13" t="inlineStr"/>
+          <t>$50 high bid + 15% BP</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="n">
+        <v>50</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 09:18 PM ET</t>
+        </is>
+      </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L23" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>HiBid</t>
+        </is>
+      </c>
+      <c r="L23" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M23" s="13" t="inlineStr"/>
@@ -2365,7 +2371,7 @@
       </c>
       <c r="O23" s="14" t="inlineStr">
         <is>
-          <t>Small lead.</t>
+          <t>Integrity Auction House. Internet bidding closes Mon Oct 19 9:18 PM ET. $50 high bid (1 bid) as of 2026-10-18.</t>
         </is>
       </c>
     </row>
@@ -2377,53 +2383,47 @@
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>Misc. appliance parts pallet (parts only)</t>
+          <t>Established appliance sales / parts / service business</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>auction pallet</t>
+          <t>business sale</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>Dalton</t>
+          <t>Oakland Park</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>917</v>
+        <v>1222</v>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>$50 high bid + 15% BP</t>
-        </is>
-      </c>
-      <c r="H24" s="15" t="n">
-        <v>50</v>
-      </c>
+          <t>Price n/a</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="n"/>
       <c r="I24" s="13" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="J24" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-19 09:18 PM ET</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="J24" s="13" t="inlineStr"/>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>HiBid</t>
-        </is>
-      </c>
-      <c r="L24" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L24" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M24" s="13" t="inlineStr"/>
@@ -2434,120 +2434,122 @@
       </c>
       <c r="O24" s="14" t="inlineStr">
         <is>
-          <t>Integrity Auction House. Internet bidding closes Mon Oct 19 9:18 PM ET. $50 high bid (1 bid) as of 2026-10-18.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" outlineLevel="1">
-      <c r="A25" s="13" t="inlineStr">
-        <is>
-          <t>Southeast</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="inlineStr">
-        <is>
-          <t>Established appliance sales / parts / service business</t>
-        </is>
-      </c>
-      <c r="C25" s="13" t="inlineStr">
-        <is>
-          <t>business sale</t>
-        </is>
-      </c>
-      <c r="D25" s="13" t="inlineStr">
-        <is>
-          <t>Oakland Park</t>
-        </is>
-      </c>
-      <c r="E25" s="13" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="F25" s="13" t="n">
-        <v>1222</v>
-      </c>
-      <c r="G25" s="13" t="inlineStr">
-        <is>
-          <t>Price n/a</t>
-        </is>
-      </c>
-      <c r="H25" s="15" t="n"/>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="J25" s="13" t="inlineStr"/>
-      <c r="K25" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L25" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M25" s="13" t="inlineStr"/>
-      <c r="N25" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O25" s="14" t="inlineStr">
-        <is>
           <t>Whole business sale (Fort Lauderdale area).</t>
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Southeast</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="inlineStr">
+        <is>
+          <t>4 item(s)</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="18" t="n"/>
+      <c r="G25" s="18" t="n"/>
+      <c r="H25" s="19" t="n">
+        <v>36050</v>
+      </c>
+      <c r="I25" s="18" t="n"/>
+      <c r="J25" s="18" t="n"/>
+      <c r="K25" s="18" t="n"/>
+      <c r="L25" s="18" t="n"/>
+      <c r="M25" s="18" t="n"/>
+      <c r="N25" s="18" t="n"/>
+      <c r="O25" s="18" t="n"/>
+    </row>
     <row r="26">
-      <c r="A26" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Southeast</t>
-        </is>
-      </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>4 item(s)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="n"/>
-      <c r="D26" s="18" t="n"/>
-      <c r="E26" s="18" t="n"/>
-      <c r="F26" s="18" t="n"/>
-      <c r="G26" s="18" t="n"/>
-      <c r="H26" s="19" t="n">
-        <v>36050</v>
-      </c>
-      <c r="I26" s="18" t="n"/>
-      <c r="J26" s="18" t="n"/>
-      <c r="K26" s="18" t="n"/>
-      <c r="L26" s="18" t="n"/>
-      <c r="M26" s="18" t="n"/>
-      <c r="N26" s="18" t="n"/>
-      <c r="O26" s="18" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>▸ Midwest  (2)</t>
         </is>
       </c>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="12" t="n"/>
-      <c r="G27" s="12" t="n"/>
-      <c r="H27" s="12" t="n"/>
-      <c r="I27" s="12" t="n"/>
-      <c r="J27" s="12" t="n"/>
-      <c r="K27" s="12" t="n"/>
-      <c r="L27" s="12" t="n"/>
-      <c r="M27" s="12" t="n"/>
-      <c r="N27" s="12" t="n"/>
-      <c r="O27" s="12" t="n"/>
+      <c r="B26" s="12" t="n"/>
+      <c r="C26" s="12" t="n"/>
+      <c r="D26" s="12" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="12" t="n"/>
+      <c r="G26" s="12" t="n"/>
+      <c r="H26" s="12" t="n"/>
+      <c r="I26" s="12" t="n"/>
+      <c r="J26" s="12" t="n"/>
+      <c r="K26" s="12" t="n"/>
+      <c r="L26" s="12" t="n"/>
+      <c r="M26" s="12" t="n"/>
+      <c r="N26" s="12" t="n"/>
+      <c r="O26" s="12" t="n"/>
+    </row>
+    <row r="27" outlineLevel="1">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Fort Wayne)</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>auction catalog</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Fort Wayne</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>743</v>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>$0–1 openers + 15% BP + $1/lot</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr"/>
+      <c r="J27" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-20 02:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (Auctionfuel)</t>
+        </is>
+      </c>
+      <c r="L27" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M27" s="13" t="inlineStr"/>
+      <c r="N27" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O27" s="14" t="inlineStr">
+        <is>
+          <t>Lots close from Oct 20 2 PM ET.</t>
+        </is>
+      </c>
     </row>
     <row r="28" outlineLevel="1">
       <c r="A28" s="13" t="inlineStr">
@@ -2557,7 +2559,7 @@
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Fort Wayne)</t>
+          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Indianapolis)</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
@@ -2567,7 +2569,7 @@
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>Fort Wayne</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -2576,7 +2578,7 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>743</v>
+        <v>816</v>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
@@ -2589,7 +2591,7 @@
       <c r="I28" s="13" t="inlineStr"/>
       <c r="J28" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 02:00 PM ET</t>
+          <t>2026-10-21 02:00 PM ET</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
@@ -2610,122 +2612,120 @@
       </c>
       <c r="O28" s="14" t="inlineStr">
         <is>
-          <t>Lots close from Oct 20 2 PM ET.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" outlineLevel="1">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>Midwest</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Indianapolis)</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>auction catalog</t>
-        </is>
-      </c>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
-          <t>Indianapolis</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="F29" s="13" t="n">
-        <v>816</v>
-      </c>
-      <c r="G29" s="13" t="inlineStr">
-        <is>
-          <t>$0–1 openers + 15% BP + $1/lot</t>
-        </is>
-      </c>
-      <c r="H29" s="15" t="n">
+          <t>Lots close in sequence from Oct 21 2 PM ET.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Midwest</t>
+        </is>
+      </c>
+      <c r="B29" s="17" t="inlineStr">
+        <is>
+          <t>2 item(s)</t>
+        </is>
+      </c>
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="18" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="18" t="n"/>
+      <c r="G29" s="18" t="n"/>
+      <c r="H29" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="13" t="inlineStr"/>
-      <c r="J29" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 02:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K29" s="13" t="inlineStr">
-        <is>
-          <t>HiBid (Auctionfuel)</t>
-        </is>
-      </c>
-      <c r="L29" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M29" s="13" t="inlineStr"/>
-      <c r="N29" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O29" s="14" t="inlineStr">
-        <is>
-          <t>Lots close in sequence from Oct 21 2 PM ET.</t>
-        </is>
-      </c>
+      <c r="I29" s="18" t="n"/>
+      <c r="J29" s="18" t="n"/>
+      <c r="K29" s="18" t="n"/>
+      <c r="L29" s="18" t="n"/>
+      <c r="M29" s="18" t="n"/>
+      <c r="N29" s="18" t="n"/>
+      <c r="O29" s="18" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Midwest</t>
-        </is>
-      </c>
-      <c r="B30" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C30" s="18" t="n"/>
-      <c r="D30" s="18" t="n"/>
-      <c r="E30" s="18" t="n"/>
-      <c r="F30" s="18" t="n"/>
-      <c r="G30" s="18" t="n"/>
-      <c r="H30" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="18" t="n"/>
-      <c r="J30" s="18" t="n"/>
-      <c r="K30" s="18" t="n"/>
-      <c r="L30" s="18" t="n"/>
-      <c r="M30" s="18" t="n"/>
-      <c r="N30" s="18" t="n"/>
-      <c r="O30" s="18" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>▸ Texas / South Central  (2)</t>
         </is>
       </c>
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="12" t="n"/>
-      <c r="E31" s="12" t="n"/>
-      <c r="F31" s="12" t="n"/>
-      <c r="G31" s="12" t="n"/>
-      <c r="H31" s="12" t="n"/>
-      <c r="I31" s="12" t="n"/>
-      <c r="J31" s="12" t="n"/>
-      <c r="K31" s="12" t="n"/>
-      <c r="L31" s="12" t="n"/>
-      <c r="M31" s="12" t="n"/>
-      <c r="N31" s="12" t="n"/>
-      <c r="O31" s="12" t="n"/>
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="12" t="n"/>
+      <c r="F30" s="12" t="n"/>
+      <c r="G30" s="12" t="n"/>
+      <c r="H30" s="12" t="n"/>
+      <c r="I30" s="12" t="n"/>
+      <c r="J30" s="12" t="n"/>
+      <c r="K30" s="12" t="n"/>
+      <c r="L30" s="12" t="n"/>
+      <c r="M30" s="12" t="n"/>
+      <c r="N30" s="12" t="n"/>
+      <c r="O30" s="12" t="n"/>
+    </row>
+    <row r="31" outlineLevel="1">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>Texas / South Central</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Wholesale Hisense appliance parts – stove &amp; refrigerator parts</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>bulk lot</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>Owasso</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>1395</v>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>Wholesale (price at sale)</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="n"/>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J31" s="13" t="inlineStr"/>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L31" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M31" s="13" t="inlineStr"/>
+      <c r="N31" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O31" s="14" t="inlineStr">
+        <is>
+          <t>Updated 2026-10-12. Seller says LOCAL BUYERS ONLY, out-of-area excluded, cash pickup.</t>
+        </is>
+      </c>
     </row>
     <row r="32" outlineLevel="1">
       <c r="A32" s="13" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>Wholesale Hisense appliance parts – stove &amp; refrigerator parts</t>
+          <t>Huge bulk lot appliance parts – ~2 trailer loads, GE/Whirlpool/Maytag</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
@@ -2745,32 +2745,30 @@
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>Owasso</t>
+          <t>Abilene</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>1395</v>
+        <v>1714</v>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>Wholesale (price at sale)</t>
-        </is>
-      </c>
-      <c r="H32" s="15" t="n"/>
-      <c r="I32" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
+          <t>$5,001</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="n">
+        <v>5001</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr"/>
       <c r="J32" s="13" t="inlineStr"/>
       <c r="K32" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>Geebo</t>
         </is>
       </c>
       <c r="L32" s="13" t="inlineStr">
@@ -2786,118 +2784,118 @@
       </c>
       <c r="O32" s="14" t="inlineStr">
         <is>
-          <t>Updated 2026-10-12. Seller says LOCAL BUYERS ONLY, out-of-area excluded, cash pickup.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" outlineLevel="1">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>Texas / South Central</t>
-        </is>
-      </c>
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>Huge bulk lot appliance parts – ~2 trailer loads, GE/Whirlpool/Maytag</t>
-        </is>
-      </c>
-      <c r="C33" s="13" t="inlineStr">
-        <is>
-          <t>bulk lot</t>
-        </is>
-      </c>
-      <c r="D33" s="13" t="inlineStr">
-        <is>
-          <t>Abilene</t>
-        </is>
-      </c>
-      <c r="E33" s="13" t="inlineStr">
-        <is>
-          <t>TX</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="n">
-        <v>1714</v>
-      </c>
-      <c r="G33" s="13" t="inlineStr">
-        <is>
-          <t>$5,001</t>
-        </is>
-      </c>
-      <c r="H33" s="15" t="n">
+          <t>Post date unclear (may be older). Pickup only. User already messaged seller.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Texas / South Central</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>2 item(s)</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="18" t="n"/>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="18" t="n"/>
+      <c r="G33" s="18" t="n"/>
+      <c r="H33" s="19" t="n">
         <v>5001</v>
       </c>
-      <c r="I33" s="13" t="inlineStr"/>
-      <c r="J33" s="13" t="inlineStr"/>
-      <c r="K33" s="13" t="inlineStr">
-        <is>
-          <t>Geebo</t>
-        </is>
-      </c>
-      <c r="L33" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M33" s="13" t="inlineStr"/>
-      <c r="N33" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O33" s="14" t="inlineStr">
-        <is>
-          <t>Post date unclear (may be older). Pickup only. User already messaged seller.</t>
-        </is>
-      </c>
+      <c r="I33" s="18" t="n"/>
+      <c r="J33" s="18" t="n"/>
+      <c r="K33" s="18" t="n"/>
+      <c r="L33" s="18" t="n"/>
+      <c r="M33" s="18" t="n"/>
+      <c r="N33" s="18" t="n"/>
+      <c r="O33" s="18" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Texas / South Central</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="n"/>
-      <c r="D34" s="18" t="n"/>
-      <c r="E34" s="18" t="n"/>
-      <c r="F34" s="18" t="n"/>
-      <c r="G34" s="18" t="n"/>
-      <c r="H34" s="19" t="n">
-        <v>5001</v>
-      </c>
-      <c r="I34" s="18" t="n"/>
-      <c r="J34" s="18" t="n"/>
-      <c r="K34" s="18" t="n"/>
-      <c r="L34" s="18" t="n"/>
-      <c r="M34" s="18" t="n"/>
-      <c r="N34" s="18" t="n"/>
-      <c r="O34" s="18" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+      <c r="A34" s="11" t="inlineStr">
         <is>
           <t>▸ California  (2)</t>
         </is>
       </c>
-      <c r="B35" s="12" t="n"/>
-      <c r="C35" s="12" t="n"/>
-      <c r="D35" s="12" t="n"/>
-      <c r="E35" s="12" t="n"/>
-      <c r="F35" s="12" t="n"/>
-      <c r="G35" s="12" t="n"/>
-      <c r="H35" s="12" t="n"/>
-      <c r="I35" s="12" t="n"/>
-      <c r="J35" s="12" t="n"/>
-      <c r="K35" s="12" t="n"/>
-      <c r="L35" s="12" t="n"/>
-      <c r="M35" s="12" t="n"/>
-      <c r="N35" s="12" t="n"/>
-      <c r="O35" s="12" t="n"/>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="12" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="12" t="n"/>
+      <c r="G34" s="12" t="n"/>
+      <c r="H34" s="12" t="n"/>
+      <c r="I34" s="12" t="n"/>
+      <c r="J34" s="12" t="n"/>
+      <c r="K34" s="12" t="n"/>
+      <c r="L34" s="12" t="n"/>
+      <c r="M34" s="12" t="n"/>
+      <c r="N34" s="12" t="n"/>
+      <c r="O34" s="12" t="n"/>
+    </row>
+    <row r="35" outlineLevel="1">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Appliance repair company for sale (incl. parts inventory)</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>business sale</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>Escondido</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>2575</v>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>$40,000</t>
+        </is>
+      </c>
+      <c r="H35" s="15" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr"/>
+      <c r="J35" s="13" t="inlineStr"/>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L35" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M35" s="13" t="inlineStr"/>
+      <c r="N35" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O35" s="14" t="inlineStr">
+        <is>
+          <t>Whole business sale.</t>
+        </is>
+      </c>
     </row>
     <row r="36" outlineLevel="1">
       <c r="A36" s="13" t="inlineStr">
@@ -2907,17 +2905,17 @@
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>Appliance repair company for sale (incl. parts inventory)</t>
+          <t>Coin-op Whirlpool washer &amp; dryer parts (late 80s–mid 90s) – OEM parts, 40+ coin boxes, consoles, 12 transmissions</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>business sale</t>
+          <t>bulk lot</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>Escondido</t>
+          <t>Chico</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
@@ -2926,17 +2924,21 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>2575</v>
+        <v>2629</v>
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
-          <t>$40,000</t>
+          <t>$1,000</t>
         </is>
       </c>
       <c r="H36" s="15" t="n">
-        <v>40000</v>
-      </c>
-      <c r="I36" s="13" t="inlineStr"/>
+        <v>1000</v>
+      </c>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
       <c r="J36" s="13" t="inlineStr"/>
       <c r="K36" s="13" t="inlineStr">
         <is>
@@ -2956,122 +2958,120 @@
       </c>
       <c r="O36" s="14" t="inlineStr">
         <is>
-          <t>Whole business sale.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" outlineLevel="1">
-      <c r="A37" s="13" t="inlineStr">
-        <is>
-          <t>California</t>
-        </is>
-      </c>
-      <c r="B37" s="14" t="inlineStr">
-        <is>
-          <t>Coin-op Whirlpool washer &amp; dryer parts (late 80s–mid 90s) – OEM parts, 40+ coin boxes, consoles, 12 transmissions</t>
-        </is>
-      </c>
-      <c r="C37" s="13" t="inlineStr">
+          <t>Retired laundry-route owner (35 yrs). Calls only, no shipping, pickup in Chico. No motors or pumps. Niche older coin-op parts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — California</t>
+        </is>
+      </c>
+      <c r="B37" s="17" t="inlineStr">
+        <is>
+          <t>2 item(s)</t>
+        </is>
+      </c>
+      <c r="C37" s="18" t="n"/>
+      <c r="D37" s="18" t="n"/>
+      <c r="E37" s="18" t="n"/>
+      <c r="F37" s="18" t="n"/>
+      <c r="G37" s="18" t="n"/>
+      <c r="H37" s="19" t="n">
+        <v>41000</v>
+      </c>
+      <c r="I37" s="18" t="n"/>
+      <c r="J37" s="18" t="n"/>
+      <c r="K37" s="18" t="n"/>
+      <c r="L37" s="18" t="n"/>
+      <c r="M37" s="18" t="n"/>
+      <c r="N37" s="18" t="n"/>
+      <c r="O37" s="18" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>▸ West / Other  (2)</t>
+        </is>
+      </c>
+      <c r="B38" s="12" t="n"/>
+      <c r="C38" s="12" t="n"/>
+      <c r="D38" s="12" t="n"/>
+      <c r="E38" s="12" t="n"/>
+      <c r="F38" s="12" t="n"/>
+      <c r="G38" s="12" t="n"/>
+      <c r="H38" s="12" t="n"/>
+      <c r="I38" s="12" t="n"/>
+      <c r="J38" s="12" t="n"/>
+      <c r="K38" s="12" t="n"/>
+      <c r="L38" s="12" t="n"/>
+      <c r="M38" s="12" t="n"/>
+      <c r="N38" s="12" t="n"/>
+      <c r="O38" s="12" t="n"/>
+    </row>
+    <row r="39" outlineLevel="1">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>West / Other</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>Storage locker filled with appliance parts – washer/dryer parts, heating elements, cords, rollers, belts, tools</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
         <is>
           <t>bulk lot</t>
         </is>
       </c>
-      <c r="D37" s="13" t="inlineStr">
-        <is>
-          <t>Chico</t>
-        </is>
-      </c>
-      <c r="E37" s="13" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="F37" s="13" t="n">
-        <v>2629</v>
-      </c>
-      <c r="G37" s="13" t="inlineStr">
-        <is>
-          <t>$1,000</t>
-        </is>
-      </c>
-      <c r="H37" s="15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I37" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="J37" s="13" t="inlineStr"/>
-      <c r="K37" s="13" t="inlineStr">
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>2307</v>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>Message for pricing</t>
+        </is>
+      </c>
+      <c r="H39" s="15" t="n"/>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J39" s="13" t="inlineStr"/>
+      <c r="K39" s="13" t="inlineStr">
         <is>
           <t>Craigslist</t>
         </is>
       </c>
-      <c r="L37" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M37" s="13" t="inlineStr"/>
-      <c r="N37" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O37" s="14" t="inlineStr">
-        <is>
-          <t>Retired laundry-route owner (35 yrs). Calls only, no shipping, pickup in Chico. No motors or pumps. Niche older coin-op parts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — California</t>
-        </is>
-      </c>
-      <c r="B38" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C38" s="18" t="n"/>
-      <c r="D38" s="18" t="n"/>
-      <c r="E38" s="18" t="n"/>
-      <c r="F38" s="18" t="n"/>
-      <c r="G38" s="18" t="n"/>
-      <c r="H38" s="19" t="n">
-        <v>41000</v>
-      </c>
-      <c r="I38" s="18" t="n"/>
-      <c r="J38" s="18" t="n"/>
-      <c r="K38" s="18" t="n"/>
-      <c r="L38" s="18" t="n"/>
-      <c r="M38" s="18" t="n"/>
-      <c r="N38" s="18" t="n"/>
-      <c r="O38" s="18" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="11" t="inlineStr">
-        <is>
-          <t>▸ West / Other  (2)</t>
-        </is>
-      </c>
-      <c r="B39" s="12" t="n"/>
-      <c r="C39" s="12" t="n"/>
-      <c r="D39" s="12" t="n"/>
-      <c r="E39" s="12" t="n"/>
-      <c r="F39" s="12" t="n"/>
-      <c r="G39" s="12" t="n"/>
-      <c r="H39" s="12" t="n"/>
-      <c r="I39" s="12" t="n"/>
-      <c r="J39" s="12" t="n"/>
-      <c r="K39" s="12" t="n"/>
-      <c r="L39" s="12" t="n"/>
-      <c r="M39" s="12" t="n"/>
-      <c r="N39" s="12" t="n"/>
-      <c r="O39" s="12" t="n"/>
+      <c r="L39" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M39" s="13" t="inlineStr"/>
+      <c r="N39" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O39" s="14" t="inlineStr">
+        <is>
+          <t>Seller is getting out of the appliance business; selling the whole locker (North Phoenix, Deer Valley Rd near 19th Ave). Delivery available per post. Separate from the Phoenix parts-store closing ad.</t>
+        </is>
+      </c>
     </row>
     <row r="40" outlineLevel="1">
       <c r="A40" s="13" t="inlineStr">
@@ -3081,17 +3081,17 @@
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>Storage locker filled with appliance parts – washer/dryer parts, heating elements, cords, rollers, belts, tools</t>
+          <t>Appliance repair &amp; sales business for sale – 100+ appliances (~90% new), liftgate truck, large powered storage unit</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>bulk lot</t>
+          <t>business for sale</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Surprise</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -3100,17 +3100,19 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>2307</v>
+        <v>2317</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
-          <t>Message for pricing</t>
-        </is>
-      </c>
-      <c r="H40" s="15" t="n"/>
+          <t>$75,000</t>
+        </is>
+      </c>
+      <c r="H40" s="15" t="n">
+        <v>75000</v>
+      </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J40" s="13" t="inlineStr"/>
@@ -3132,124 +3134,58 @@
       </c>
       <c r="O40" s="14" t="inlineStr">
         <is>
-          <t>Seller is getting out of the appliance business; selling the whole locker (North Phoenix, Deer Valley Rd near 19th Ave). Delivery available per post. Separate from the Phoenix parts-store closing ad.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" outlineLevel="1">
-      <c r="A41" s="13" t="inlineStr">
-        <is>
-          <t>West / Other</t>
-        </is>
-      </c>
-      <c r="B41" s="14" t="inlineStr">
-        <is>
-          <t>Appliance repair &amp; sales business for sale – 100+ appliances (~90% new), liftgate truck, large powered storage unit</t>
-        </is>
-      </c>
-      <c r="C41" s="13" t="inlineStr">
-        <is>
-          <t>business for sale</t>
-        </is>
-      </c>
-      <c r="D41" s="13" t="inlineStr">
-        <is>
-          <t>Surprise</t>
-        </is>
-      </c>
-      <c r="E41" s="13" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="F41" s="13" t="n">
-        <v>2317</v>
-      </c>
-      <c r="G41" s="13" t="inlineStr">
-        <is>
-          <t>$75,000</t>
-        </is>
-      </c>
-      <c r="H41" s="15" t="n">
+          <t>Retiring owner of 14-year business serving rental-property owners. Whole appliances (fridges, stoves, microwaves, dishwashers, W/D), not a parts inventory. Storage unit near Dysart &amp; Bell Rd. By appointment only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — West / Other</t>
+        </is>
+      </c>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>2 item(s)</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="n"/>
+      <c r="D41" s="18" t="n"/>
+      <c r="E41" s="18" t="n"/>
+      <c r="F41" s="18" t="n"/>
+      <c r="G41" s="18" t="n"/>
+      <c r="H41" s="19" t="n">
         <v>75000</v>
       </c>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="J41" s="13" t="inlineStr"/>
-      <c r="K41" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L41" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M41" s="13" t="inlineStr"/>
-      <c r="N41" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O41" s="14" t="inlineStr">
-        <is>
-          <t>Retiring owner of 14-year business serving rental-property owners. Whole appliances (fridges, stoves, microwaves, dishwashers, W/D), not a parts inventory. Storage unit near Dysart &amp; Bell Rd. By appointment only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — West / Other</t>
-        </is>
-      </c>
-      <c r="B42" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C42" s="18" t="n"/>
-      <c r="D42" s="18" t="n"/>
-      <c r="E42" s="18" t="n"/>
-      <c r="F42" s="18" t="n"/>
-      <c r="G42" s="18" t="n"/>
-      <c r="H42" s="19" t="n">
-        <v>75000</v>
-      </c>
-      <c r="I42" s="18" t="n"/>
-      <c r="J42" s="18" t="n"/>
-      <c r="K42" s="18" t="n"/>
-      <c r="L42" s="18" t="n"/>
-      <c r="M42" s="18" t="n"/>
-      <c r="N42" s="18" t="n"/>
-      <c r="O42" s="18" t="n"/>
+      <c r="I41" s="18" t="n"/>
+      <c r="J41" s="18" t="n"/>
+      <c r="K41" s="18" t="n"/>
+      <c r="L41" s="18" t="n"/>
+      <c r="M41" s="18" t="n"/>
+      <c r="N41" s="18" t="n"/>
+      <c r="O41" s="18" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O42"/>
+  <autoFilter ref="A1:O41"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18612,7 +18548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O78"/>
+  <dimension ref="A1:O79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -18712,7 +18648,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>▸ Greater Boston / South Shore (&lt;50mi)  (4)</t>
+          <t>▸ Greater Boston / South Shore (&lt;50mi)  (5)</t>
         </is>
       </c>
       <c r="B2" s="12" t="n"/>
@@ -18927,17 +18863,17 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>Cannabis facility contents incl. commercial kitchen / stainless</t>
+          <t>Wholesale bedding lot – 525 pcs new Target overstock (comforters, duvets, quilts)</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>facility contents</t>
+          <t>wholesale overstock lot</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Natick</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -18946,23 +18882,23 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>Auction, 18% BP</t>
+          <t>$3,590 all 525 pcs (per-piece $4–$11)</t>
         </is>
       </c>
       <c r="H6" s="15" t="n"/>
-      <c r="I6" s="13" t="inlineStr"/>
-      <c r="J6" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-03 10:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr"/>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>Paul E. Saperstein (PESCO)</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L6" s="13" t="inlineStr">
@@ -18978,120 +18914,120 @@
       </c>
       <c r="O6" s="14" t="inlineStr">
         <is>
+          <t>Resale business selling bulk new bedding in original packaging: shams, duvet/sham sets, waffle comforter sets, bath runners, quilts, Casaluna pillows. Works out to about $6.84/pc; retail comps $20–$60. Local pickup Natick only, cash.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" outlineLevel="1">
+      <c r="A7" s="13" t="inlineStr">
+        <is>
+          <t>Greater Boston / South Shore (&lt;50mi)</t>
+        </is>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>Cannabis facility contents incl. commercial kitchen / stainless</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>facility contents</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>Milford</t>
+        </is>
+      </c>
+      <c r="E7" s="13" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="F7" s="13" t="n">
+        <v>36</v>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>Auction, 18% BP</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="n"/>
+      <c r="I7" s="13" t="inlineStr"/>
+      <c r="J7" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-03 10:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>Paul E. Saperstein (PESCO)</t>
+        </is>
+      </c>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M7" s="13" t="inlineStr"/>
+      <c r="N7" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O7" s="14" t="inlineStr">
+        <is>
           <t>Calendar page only (no event page yet). ~45 mi.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="17" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Greater Boston / South Shore (&lt;50mi)</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>4 item(s)</t>
-        </is>
-      </c>
-      <c r="C7" s="18" t="n"/>
-      <c r="D7" s="18" t="n"/>
-      <c r="E7" s="18" t="n"/>
-      <c r="F7" s="18" t="n"/>
-      <c r="G7" s="18" t="n"/>
-      <c r="H7" s="19" t="n">
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>5 item(s)</t>
+        </is>
+      </c>
+      <c r="C8" s="18" t="n"/>
+      <c r="D8" s="18" t="n"/>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="18" t="n"/>
+      <c r="G8" s="18" t="n"/>
+      <c r="H8" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I7" s="18" t="n"/>
-      <c r="J7" s="18" t="n"/>
-      <c r="K7" s="18" t="n"/>
-      <c r="L7" s="18" t="n"/>
-      <c r="M7" s="18" t="n"/>
-      <c r="N7" s="18" t="n"/>
-      <c r="O7" s="18" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+      <c r="I8" s="18" t="n"/>
+      <c r="J8" s="18" t="n"/>
+      <c r="K8" s="18" t="n"/>
+      <c r="L8" s="18" t="n"/>
+      <c r="M8" s="18" t="n"/>
+      <c r="N8" s="18" t="n"/>
+      <c r="O8" s="18" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>▸ North Shore / Merrimack Valley / S. NH  (2)</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n"/>
-      <c r="C8" s="12" t="n"/>
-      <c r="D8" s="12" t="n"/>
-      <c r="E8" s="12" t="n"/>
-      <c r="F8" s="12" t="n"/>
-      <c r="G8" s="12" t="n"/>
-      <c r="H8" s="12" t="n"/>
-      <c r="I8" s="12" t="n"/>
-      <c r="J8" s="12" t="n"/>
-      <c r="K8" s="12" t="n"/>
-      <c r="L8" s="12" t="n"/>
-      <c r="M8" s="12" t="n"/>
-      <c r="N8" s="12" t="n"/>
-      <c r="O8" s="12" t="n"/>
-    </row>
-    <row r="9" outlineLevel="1">
-      <c r="A9" s="13" t="inlineStr">
-        <is>
-          <t>North Shore / Merrimack Valley / S. NH</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>Commercial mechanical/plumbing/HVAC contractor inventory – multiple pallets of boxed stock, water heater, venting, diffusers</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>Merrimack</t>
-        </is>
-      </c>
-      <c r="E9" s="13" t="inlineStr">
-        <is>
-          <t>NH</t>
-        </is>
-      </c>
-      <c r="F9" s="13" t="n">
-        <v>62</v>
-      </c>
-      <c r="G9" s="13" t="inlineStr">
-        <is>
-          <t>$1 placeholder – make offer on everything</t>
-        </is>
-      </c>
-      <c r="H9" s="15" t="n"/>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="J9" s="13" t="inlineStr"/>
-      <c r="K9" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L9" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M9" s="13" t="inlineStr"/>
-      <c r="N9" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O9" s="14" t="inlineStr">
-        <is>
-          <t>Bulk buyers preferred.</t>
-        </is>
-      </c>
+      <c r="B9" s="12" t="n"/>
+      <c r="C9" s="12" t="n"/>
+      <c r="D9" s="12" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="12" t="n"/>
+      <c r="G9" s="12" t="n"/>
+      <c r="H9" s="12" t="n"/>
+      <c r="I9" s="12" t="n"/>
+      <c r="J9" s="12" t="n"/>
+      <c r="K9" s="12" t="n"/>
+      <c r="L9" s="12" t="n"/>
+      <c r="M9" s="12" t="n"/>
+      <c r="N9" s="12" t="n"/>
+      <c r="O9" s="12" t="n"/>
     </row>
     <row r="10" outlineLevel="1">
       <c r="A10" s="13" t="inlineStr">
@@ -19101,17 +19037,17 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating overstock/returns online auction – 183 lots (fixtures, furnaces, heaters, A/C)</t>
+          <t>Commercial mechanical/plumbing/HVAC contractor inventory – multiple pallets of boxed stock, water heater, venting, diffusers</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>Concord</t>
+          <t>Merrimack</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
@@ -19120,27 +19056,23 @@
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>$1 placeholder – make offer on everything</t>
         </is>
       </c>
       <c r="H10" s="15" t="n"/>
       <c r="I10" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="J10" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-27 07:00 PM ET</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr"/>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Atlantic Auction Co.)</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L10" s="13" t="inlineStr">
@@ -19156,120 +19088,124 @@
       </c>
       <c r="O10" s="14" t="inlineStr">
         <is>
+          <t>Bulk buyers preferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" outlineLevel="1">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>North Shore / Merrimack Valley / S. NH</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Plumbing &amp; heating overstock/returns online auction – 183 lots (fixtures, furnaces, heaters, A/C)</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>auction</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Concord</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>84</v>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Online auction</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="n"/>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-27 07:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (Atlantic Auction Co.)</t>
+        </is>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M11" s="13" t="inlineStr"/>
+      <c r="N11" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O11" s="14" t="inlineStr">
+        <is>
           <t>Overstock sale, not a closing. Pickup Oct 29–30.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="17" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="17" t="inlineStr">
         <is>
           <t>Subtotal — North Shore / Merrimack Valley / S. NH</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>2 item(s)</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n"/>
-      <c r="D11" s="18" t="n"/>
-      <c r="E11" s="18" t="n"/>
-      <c r="F11" s="18" t="n"/>
-      <c r="G11" s="18" t="n"/>
-      <c r="H11" s="19" t="n">
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="18" t="n"/>
+      <c r="G12" s="18" t="n"/>
+      <c r="H12" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I11" s="18" t="n"/>
-      <c r="J11" s="18" t="n"/>
-      <c r="K11" s="18" t="n"/>
-      <c r="L11" s="18" t="n"/>
-      <c r="M11" s="18" t="n"/>
-      <c r="N11" s="18" t="n"/>
-      <c r="O11" s="18" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="I12" s="18" t="n"/>
+      <c r="J12" s="18" t="n"/>
+      <c r="K12" s="18" t="n"/>
+      <c r="L12" s="18" t="n"/>
+      <c r="M12" s="18" t="n"/>
+      <c r="N12" s="18" t="n"/>
+      <c r="O12" s="18" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>▸ Central / Western MA  (3)</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
-      <c r="H12" s="12" t="n"/>
-      <c r="I12" s="12" t="n"/>
-      <c r="J12" s="12" t="n"/>
-      <c r="K12" s="12" t="n"/>
-      <c r="L12" s="12" t="n"/>
-      <c r="M12" s="12" t="n"/>
-      <c r="N12" s="12" t="n"/>
-      <c r="O12" s="12" t="n"/>
-    </row>
-    <row r="13" outlineLevel="1">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Central / Western MA</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>Gift/souvenir store closing (retirement) – all new stock</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>store closing</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>Thorndike</t>
-        </is>
-      </c>
-      <c r="E13" s="13" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="F13" s="13" t="n">
-        <v>77</v>
-      </c>
-      <c r="G13" s="13" t="inlineStr">
-        <is>
-          <t>By appointment</t>
-        </is>
-      </c>
-      <c r="H13" s="15" t="n"/>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J13" s="13" t="inlineStr"/>
-      <c r="K13" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L13" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M13" s="13" t="inlineStr"/>
-      <c r="N13" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O13" s="14" t="inlineStr">
-        <is>
-          <t>Updated Oct 8. Off-category FYI.</t>
-        </is>
-      </c>
+      <c r="B13" s="12" t="n"/>
+      <c r="C13" s="12" t="n"/>
+      <c r="D13" s="12" t="n"/>
+      <c r="E13" s="12" t="n"/>
+      <c r="F13" s="12" t="n"/>
+      <c r="G13" s="12" t="n"/>
+      <c r="H13" s="12" t="n"/>
+      <c r="I13" s="12" t="n"/>
+      <c r="J13" s="12" t="n"/>
+      <c r="K13" s="12" t="n"/>
+      <c r="L13" s="12" t="n"/>
+      <c r="M13" s="12" t="n"/>
+      <c r="N13" s="12" t="n"/>
+      <c r="O13" s="12" t="n"/>
     </row>
     <row r="14" outlineLevel="1">
       <c r="A14" s="13" t="inlineStr">
@@ -19279,17 +19215,17 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>UNECO Manufacturing – owners retiring, machine-shop metrology &amp; tooling</t>
+          <t>Gift/souvenir store closing (retirement) – all new stock</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>retirement</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>Chicopee</t>
+          <t>Thorndike</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
@@ -19298,23 +19234,23 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>Online auction, 18% BP</t>
+          <t>By appointment</t>
         </is>
       </c>
       <c r="H14" s="15" t="n"/>
-      <c r="I14" s="13" t="inlineStr"/>
-      <c r="J14" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-04 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="J14" s="13" t="inlineStr"/>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>HiBid (DeCosmo Industrial)</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L14" s="13" t="inlineStr">
@@ -19330,7 +19266,7 @@
       </c>
       <c r="O14" s="14" t="inlineStr">
         <is>
-          <t>Niche tooling only. Bidding opens Oct 19.</t>
+          <t>Updated Oct 8. Off-category FYI.</t>
         </is>
       </c>
     </row>
@@ -19342,17 +19278,17 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>Restaurant closing, everything must go – kitchen equipment, stainless, smallwares</t>
+          <t>UNECO Manufacturing – owners retiring, machine-shop metrology &amp; tooling</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>retirement</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>Westfield</t>
+          <t>Chicopee</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
@@ -19361,23 +19297,23 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>Make offer</t>
+          <t>Online auction, 18% BP</t>
         </is>
       </c>
       <c r="H15" s="15" t="n"/>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="J15" s="13" t="inlineStr"/>
+      <c r="I15" s="13" t="inlineStr"/>
+      <c r="J15" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-04 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>HiBid (DeCosmo Industrial)</t>
         </is>
       </c>
       <c r="L15" s="13" t="inlineStr">
@@ -19393,120 +19329,120 @@
       </c>
       <c r="O15" s="14" t="inlineStr">
         <is>
+          <t>Niche tooling only. Bidding opens Oct 19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" outlineLevel="1">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>Central / Western MA</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant closing, everything must go – kitchen equipment, stainless, smallwares</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>restaurant closing</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Westfield</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>99</v>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>Make offer</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="n"/>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="inlineStr"/>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L16" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M16" s="13" t="inlineStr"/>
+      <c r="N16" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O16" s="14" t="inlineStr">
+        <is>
           <t>Related separate post "Complete Restaurant Equipment Package" $3,500 OBO (maybe same restaurant): https://www.craigslist.org/view/d/westfield-complete-restaurant-equipment/9Y5KCdhhgSqEBYbD3wKqVd</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="17" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Central / Western MA</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>3 item(s)</t>
         </is>
       </c>
-      <c r="C16" s="18" t="n"/>
-      <c r="D16" s="18" t="n"/>
-      <c r="E16" s="18" t="n"/>
-      <c r="F16" s="18" t="n"/>
-      <c r="G16" s="18" t="n"/>
-      <c r="H16" s="19" t="n">
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="18" t="n"/>
+      <c r="E17" s="18" t="n"/>
+      <c r="F17" s="18" t="n"/>
+      <c r="G17" s="18" t="n"/>
+      <c r="H17" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="18" t="n"/>
-      <c r="J16" s="18" t="n"/>
-      <c r="K16" s="18" t="n"/>
-      <c r="L16" s="18" t="n"/>
-      <c r="M16" s="18" t="n"/>
-      <c r="N16" s="18" t="n"/>
-      <c r="O16" s="18" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="I17" s="18" t="n"/>
+      <c r="J17" s="18" t="n"/>
+      <c r="K17" s="18" t="n"/>
+      <c r="L17" s="18" t="n"/>
+      <c r="M17" s="18" t="n"/>
+      <c r="N17" s="18" t="n"/>
+      <c r="O17" s="18" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t>▸ Maine / VT / Northern NH  (4)</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="12" t="n"/>
-      <c r="J17" s="12" t="n"/>
-      <c r="K17" s="12" t="n"/>
-      <c r="L17" s="12" t="n"/>
-      <c r="M17" s="12" t="n"/>
-      <c r="N17" s="12" t="n"/>
-      <c r="O17" s="12" t="n"/>
-    </row>
-    <row r="18" outlineLevel="1">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>Maine / VT / Northern NH</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="inlineStr">
-        <is>
-          <t>Contractor appliance lot – 3 refrigerators, Bosch wall oven, gas range, washer/dryer set</t>
-        </is>
-      </c>
-      <c r="C18" s="13" t="inlineStr">
-        <is>
-          <t>contractor lot</t>
-        </is>
-      </c>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>Scarborough</t>
-        </is>
-      </c>
-      <c r="E18" s="13" t="inlineStr">
-        <is>
-          <t>ME</t>
-        </is>
-      </c>
-      <c r="F18" s="13" t="n">
-        <v>104</v>
-      </c>
-      <c r="G18" s="13" t="inlineStr">
-        <is>
-          <t>$200 OBO each, less as a bundle</t>
-        </is>
-      </c>
-      <c r="H18" s="15" t="n"/>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="J18" s="13" t="inlineStr"/>
-      <c r="K18" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L18" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M18" s="13" t="inlineStr"/>
-      <c r="N18" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O18" s="14" t="inlineStr">
-        <is>
-          <t>Working units pulled from jobs. Complete appliances, not parts.</t>
-        </is>
-      </c>
+      <c r="B18" s="12" t="n"/>
+      <c r="C18" s="12" t="n"/>
+      <c r="D18" s="12" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="12" t="n"/>
+      <c r="G18" s="12" t="n"/>
+      <c r="H18" s="12" t="n"/>
+      <c r="I18" s="12" t="n"/>
+      <c r="J18" s="12" t="n"/>
+      <c r="K18" s="12" t="n"/>
+      <c r="L18" s="12" t="n"/>
+      <c r="M18" s="12" t="n"/>
+      <c r="N18" s="12" t="n"/>
+      <c r="O18" s="12" t="n"/>
     </row>
     <row r="19" outlineLevel="1">
       <c r="A19" s="13" t="inlineStr">
@@ -19516,17 +19452,17 @@
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>Event-rental business closing – 300+ chairs, 40+ rounds, 1,300+ china, linens (all at once)</t>
+          <t>Contractor appliance lot – 3 refrigerators, Bosch wall oven, gas range, washer/dryer set</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>business closing</t>
+          <t>contractor lot</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>Woolwich</t>
+          <t>Scarborough</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
@@ -19535,17 +19471,17 @@
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>No price listed</t>
+          <t>$200 OBO each, less as a bundle</t>
         </is>
       </c>
       <c r="H19" s="15" t="n"/>
       <c r="I19" s="13" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="J19" s="13" t="inlineStr"/>
@@ -19567,7 +19503,7 @@
       </c>
       <c r="O19" s="14" t="inlineStr">
         <is>
-          <t>Updated Oct 7. Replacement cost &gt;$72K per post.</t>
+          <t>Working units pulled from jobs. Complete appliances, not parts.</t>
         </is>
       </c>
     </row>
@@ -19579,42 +19515,42 @@
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>Pellet/wood stoves, heating stock, tools &amp; heavy equipment – "business liquidation", 380 lots</t>
+          <t>Event-rental business closing – 300+ chairs, 40+ rounds, 1,300+ china, linens (all at once)</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>business closing</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>Lunenburg</t>
+          <t>Woolwich</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>VT</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>168</v>
+        <v>135</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>No price listed</t>
         </is>
       </c>
       <c r="H20" s="15" t="n"/>
-      <c r="I20" s="13" t="inlineStr"/>
-      <c r="J20" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-04 10:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J20" s="13" t="inlineStr"/>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>Thomas Hirchak Co.</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L20" s="13" t="inlineStr">
@@ -19630,7 +19566,7 @@
       </c>
       <c r="O20" s="14" t="inlineStr">
         <is>
-          <t>Closes Wed Nov 4 10 AM, preview Oct 28, removal Nov 9, no shipping.</t>
+          <t>Updated Oct 7. Replacement cost &gt;$72K per post.</t>
         </is>
       </c>
     </row>
@@ -19642,17 +19578,17 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>Bread Loaf Corp wind-down – contractor equipment, staging, telehandler</t>
+          <t>Pellet/wood stoves, heating stock, tools &amp; heavy equipment – "business liquidation", 380 lots</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>contractor liquidation</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>Middlebury</t>
+          <t>Lunenburg</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
@@ -19661,7 +19597,7 @@
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
@@ -19672,12 +19608,12 @@
       <c r="I21" s="13" t="inlineStr"/>
       <c r="J21" s="13" t="inlineStr">
         <is>
-          <t>2026-10-28 09:00 AM ET</t>
+          <t>2026-11-04 10:00 AM ET</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
         <is>
-          <t>THC Auction</t>
+          <t>Thomas Hirchak Co.</t>
         </is>
       </c>
       <c r="L21" s="13" t="inlineStr">
@@ -19693,120 +19629,120 @@
       </c>
       <c r="O21" s="14" t="inlineStr">
         <is>
+          <t>Closes Wed Nov 4 10 AM, preview Oct 28, removal Nov 9, no shipping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" outlineLevel="1">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>Maine / VT / Northern NH</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>Bread Loaf Corp wind-down – contractor equipment, staging, telehandler</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>contractor liquidation</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>Middlebury</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>VT</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>177</v>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>Online auction</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="n"/>
+      <c r="I22" s="13" t="inlineStr"/>
+      <c r="J22" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>THC Auction</t>
+        </is>
+      </c>
+      <c r="L22" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M22" s="13" t="inlineStr"/>
+      <c r="N22" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O22" s="14" t="inlineStr">
+        <is>
           <t>Company wind-down.</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="17" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Maine / VT / Northern NH</t>
         </is>
       </c>
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B23" s="17" t="inlineStr">
         <is>
           <t>4 item(s)</t>
         </is>
       </c>
-      <c r="C22" s="18" t="n"/>
-      <c r="D22" s="18" t="n"/>
-      <c r="E22" s="18" t="n"/>
-      <c r="F22" s="18" t="n"/>
-      <c r="G22" s="18" t="n"/>
-      <c r="H22" s="19" t="n">
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="18" t="n"/>
+      <c r="G23" s="18" t="n"/>
+      <c r="H23" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I22" s="18" t="n"/>
-      <c r="J22" s="18" t="n"/>
-      <c r="K22" s="18" t="n"/>
-      <c r="L22" s="18" t="n"/>
-      <c r="M22" s="18" t="n"/>
-      <c r="N22" s="18" t="n"/>
-      <c r="O22" s="18" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="inlineStr">
-        <is>
-          <t>▸ CT / Hudson Valley  (7)</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="12" t="n"/>
-      <c r="G23" s="12" t="n"/>
-      <c r="H23" s="12" t="n"/>
-      <c r="I23" s="12" t="n"/>
-      <c r="J23" s="12" t="n"/>
-      <c r="K23" s="12" t="n"/>
-      <c r="L23" s="12" t="n"/>
-      <c r="M23" s="12" t="n"/>
-      <c r="N23" s="12" t="n"/>
-      <c r="O23" s="12" t="n"/>
-    </row>
-    <row r="24" outlineLevel="1">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>CT / Hudson Valley</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>Bank-ordered electrical contractor sale – Greenlee/Hilti/Milwaukee tools, GE/Siemens breakers</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>contractor liquidation</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>Clinton</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="n">
-        <v>106</v>
-      </c>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>Online auction</t>
-        </is>
-      </c>
-      <c r="H24" s="15" t="n"/>
-      <c r="I24" s="13" t="inlineStr"/>
-      <c r="J24" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-29 05:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K24" s="13" t="inlineStr">
-        <is>
-          <t>Hamilton Group / EstateSales.net</t>
-        </is>
-      </c>
-      <c r="L24" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M24" s="13" t="inlineStr"/>
-      <c r="N24" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O24" s="14" t="inlineStr">
-        <is>
-          <t>Listed "Oct 29 2 PM PST" (= 5 PM ET).</t>
-        </is>
-      </c>
+      <c r="I23" s="18" t="n"/>
+      <c r="J23" s="18" t="n"/>
+      <c r="K23" s="18" t="n"/>
+      <c r="L23" s="18" t="n"/>
+      <c r="M23" s="18" t="n"/>
+      <c r="N23" s="18" t="n"/>
+      <c r="O23" s="18" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>▸ CT / Hudson Valley  (8)</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="n"/>
+      <c r="C24" s="12" t="n"/>
+      <c r="D24" s="12" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="12" t="n"/>
+      <c r="G24" s="12" t="n"/>
+      <c r="H24" s="12" t="n"/>
+      <c r="I24" s="12" t="n"/>
+      <c r="J24" s="12" t="n"/>
+      <c r="K24" s="12" t="n"/>
+      <c r="L24" s="12" t="n"/>
+      <c r="M24" s="12" t="n"/>
+      <c r="N24" s="12" t="n"/>
+      <c r="O24" s="12" t="n"/>
     </row>
     <row r="25" outlineLevel="1">
       <c r="A25" s="13" t="inlineStr">
@@ -19816,17 +19752,17 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Fabrication &amp; welding shop liquidation – everything must be sold</t>
+          <t>Bank-ordered electrical contractor sale – Greenlee/Hilti/Milwaukee tools, GE/Siemens breakers</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>machine shop liquidation</t>
+          <t>contractor liquidation</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>Bridgeport</t>
+          <t>Clinton</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
@@ -19835,23 +19771,23 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
-          <t>Priced per machine (e.g. W.A. Whitney punch press $4,950; DoAll bandsaw $950)</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H25" s="15" t="n"/>
-      <c r="I25" s="13" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="J25" s="13" t="inlineStr"/>
+      <c r="I25" s="13" t="inlineStr"/>
+      <c r="J25" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-29 05:00 PM ET</t>
+        </is>
+      </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>Hamilton Group / EstateSales.net</t>
         </is>
       </c>
       <c r="L25" s="13" t="inlineStr">
@@ -19867,7 +19803,7 @@
       </c>
       <c r="O25" s="14" t="inlineStr">
         <is>
-          <t>All assets/equipment/tools of a fab &amp; welding shop; machines under power, inspection by appointment, buyer removes (small forklift on site). Several big items already SOLD (Cincinnati brake/shear, plasma table, Lown roll). Remaining: Whitney + Roper Whitney punch presses, DoAll V36 bandsaw, Thompson spot welder, George Ohl 120" brake, Bridgeport mill, etc. Mostly 220V. Posted May 15, updated Oct 19.</t>
+          <t>Listed "Oct 29 2 PM PST" (= 5 PM ET).</t>
         </is>
       </c>
     </row>
@@ -19879,47 +19815,47 @@
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>Major Intl Chain Surplus – 225 lots commercial refrigeration/kitchen (True, Traulsen, Hobart, Blodgett, Taylor)</t>
+          <t>Fabrication &amp; welding shop liquidation – everything must be sold</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>commercial surplus</t>
+          <t>machine shop liquidation</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>Pleasant Valley</t>
+          <t>Bridgeport</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Priced per machine (e.g. W.A. Whitney punch press $4,950; DoAll bandsaw $950)</t>
         </is>
       </c>
       <c r="H26" s="15" t="n"/>
-      <c r="I26" s="13" t="inlineStr"/>
-      <c r="J26" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-20 02:00 PM ET</t>
-        </is>
-      </c>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="J26" s="13" t="inlineStr"/>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>Adams / BidWrangler</t>
-        </is>
-      </c>
-      <c r="L26" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L26" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M26" s="13" t="inlineStr"/>
@@ -19930,7 +19866,7 @@
       </c>
       <c r="O26" s="14" t="inlineStr">
         <is>
-          <t>Tested and new units.</t>
+          <t>All assets/equipment/tools of a fab &amp; welding shop; machines under power, inspection by appointment, buyer removes (small forklift on site). Several big items already SOLD (Cincinnati brake/shear, plasma table, Lown roll). Remaining: Whitney + Roper Whitney punch presses, DoAll V36 bandsaw, Thompson spot welder, George Ohl 120" brake, Bridgeport mill, etc. Mostly 220V. Posted May 15, updated Oct 19.</t>
         </is>
       </c>
     </row>
@@ -19942,46 +19878,42 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>The Outlaw Grill Steakhouse – used restaurant equipment auction (PCI Auctions CT, e.g. Vulcan EV60 Endurance 60" range)</t>
+          <t>Major Intl Chain Surplus – 225 lots commercial refrigeration/kitchen (True, Traulsen, Hobart, Blodgett, Taylor)</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>restaurant auction</t>
+          <t>commercial surplus</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>Stamford</t>
+          <t>Pleasant Valley</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
-          <t>Online auction, current bids</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H27" s="15" t="n"/>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
+      <c r="I27" s="13" t="inlineStr"/>
       <c r="J27" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 08:30 PM ET</t>
+          <t>2026-10-20 02:00 PM ET</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>PCI Auctions</t>
+          <t>Adams / BidWrangler</t>
         </is>
       </c>
       <c r="L27" s="20" t="inlineStr">
@@ -19997,7 +19929,7 @@
       </c>
       <c r="O27" s="14" t="inlineStr">
         <is>
-          <t>Ends Wed Oct 21 8:30 PM EDT. PCI warehouse, 36 Ludlow St, Stamford CT. Page lists preview Oct 28 and removal Thu Oct 29 11-3 (after close). Shipping/delivery available; payment due on pickup day. Items still being added.</t>
+          <t>Tested and new units.</t>
         </is>
       </c>
     </row>
@@ -20009,17 +19941,17 @@
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>Café/bakery liquidation – Traulsen, Vulcan ovens, mixers, Hobart slicer (~74 lots)</t>
+          <t>The Outlaw Grill Steakhouse – used restaurant equipment auction (PCI Auctions CT, e.g. Vulcan EV60 Endurance 60" range)</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>restaurant auction</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>Greenwich</t>
+          <t>Stamford</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -20028,23 +19960,27 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>Live auction + webcast</t>
+          <t>Online auction, current bids</t>
         </is>
       </c>
       <c r="H28" s="15" t="n"/>
-      <c r="I28" s="13" t="inlineStr"/>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="J28" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 06:00 PM ET</t>
+          <t>2026-10-21 08:30 PM ET</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>Best Buy Auctioneers / AuctionGuide</t>
+          <t>PCI Auctions</t>
         </is>
       </c>
       <c r="L28" s="20" t="inlineStr">
@@ -20060,7 +19996,7 @@
       </c>
       <c r="O28" s="14" t="inlineStr">
         <is>
-          <t>Oct 21; start time not captured (placeholder 6 PM).</t>
+          <t>Ends Wed Oct 21 8:30 PM EDT. PCI warehouse, 36 Ludlow St, Stamford CT. Page lists preview Oct 28 and removal Thu Oct 29 11-3 (after close). Shipping/delivery available; payment due on pickup day. Items still being added.</t>
         </is>
       </c>
     </row>
@@ -20072,47 +20008,47 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>BJ's Wholesale closeout – racking, forklifts, Hobart</t>
+          <t>Café/bakery liquidation – Traulsen, Vulcan ovens, mixers, Hobart slicer (~74 lots)</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>Rotterdam</t>
+          <t>Greenwich</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Live auction + webcast</t>
         </is>
       </c>
       <c r="H29" s="15" t="n"/>
       <c r="I29" s="13" t="inlineStr"/>
       <c r="J29" s="13" t="inlineStr">
         <is>
-          <t>2026-11-10 10:00 AM ET</t>
+          <t>2026-10-21 06:00 PM ET</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L29" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Best Buy Auctioneers / AuctionGuide</t>
+        </is>
+      </c>
+      <c r="L29" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M29" s="13" t="inlineStr"/>
@@ -20123,7 +20059,7 @@
       </c>
       <c r="O29" s="14" t="inlineStr">
         <is>
-          <t>Closes from Nov 10 10 AM.</t>
+          <t>Oct 21; start time not captured (placeholder 6 PM).</t>
         </is>
       </c>
     </row>
@@ -20135,17 +20071,17 @@
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>Body shop closing after 50 years – tools, welder, generators, plasma</t>
+          <t>BJ's Wholesale closeout – racking, forklifts, Hobart</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>tools liquidation</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>West Nyack</t>
+          <t>Rotterdam</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
@@ -20154,23 +20090,23 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>Make offer / lot</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H30" s="15" t="n"/>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="J30" s="13" t="inlineStr"/>
+      <c r="I30" s="13" t="inlineStr"/>
+      <c r="J30" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-10 10:00 AM ET</t>
+        </is>
+      </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>Grafe Auction</t>
         </is>
       </c>
       <c r="L30" s="13" t="inlineStr">
@@ -20186,187 +20122,183 @@
       </c>
       <c r="O30" s="14" t="inlineStr">
         <is>
+          <t>Closes from Nov 10 10 AM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" outlineLevel="1">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>CT / Hudson Valley</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Body shop closing after 50 years – tools, welder, generators, plasma</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>tools liquidation</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>West Nyack</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>178</v>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>Make offer / lot</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="n"/>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J31" s="13" t="inlineStr"/>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L31" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M31" s="13" t="inlineStr"/>
+      <c r="N31" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O31" s="14" t="inlineStr">
+        <is>
           <t>One-man auto body shop closing/retirement (Park Ridge / West Nyack NY-NJ border). Heat lamps, Kansas jack pullers, Miller 200 welder, generators, sheet-metal brake, hydraulic press, plasma cutter, engine hoist. Posted Aug 16; still open 2026-10-19.</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
+    <row r="32" outlineLevel="1">
+      <c r="A32" s="13" t="inlineStr">
+        <is>
+          <t>CT / Hudson Valley</t>
+        </is>
+      </c>
+      <c r="B32" s="14" t="inlineStr">
+        <is>
+          <t>Woodworkers shop closing sale – shop tools &amp; hand tools</t>
+        </is>
+      </c>
+      <c r="C32" s="13" t="inlineStr">
+        <is>
+          <t>woodworking shop closing</t>
+        </is>
+      </c>
+      <c r="D32" s="13" t="inlineStr">
+        <is>
+          <t>Tappan</t>
+        </is>
+      </c>
+      <c r="E32" s="13" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F32" s="13" t="n">
+        <v>179</v>
+      </c>
+      <c r="G32" s="13" t="inlineStr">
+        <is>
+          <t>Priced individually (some free)</t>
+        </is>
+      </c>
+      <c r="H32" s="15" t="n"/>
+      <c r="I32" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="J32" s="13" t="inlineStr"/>
+      <c r="K32" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L32" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M32" s="13" t="inlineStr"/>
+      <c r="N32" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O32" s="14" t="inlineStr">
+        <is>
+          <t>Ongoing shop-closing sale at 61 Main St, Tappan; many shop and hand tools, schedule a visit. Near the West Nyack body-shop sale (bl-054) for one trip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
         <is>
           <t>Subtotal — CT / Hudson Valley</t>
         </is>
       </c>
-      <c r="B31" s="17" t="inlineStr">
-        <is>
-          <t>7 item(s)</t>
-        </is>
-      </c>
-      <c r="C31" s="18" t="n"/>
-      <c r="D31" s="18" t="n"/>
-      <c r="E31" s="18" t="n"/>
-      <c r="F31" s="18" t="n"/>
-      <c r="G31" s="18" t="n"/>
-      <c r="H31" s="19" t="n">
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>8 item(s)</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="18" t="n"/>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="18" t="n"/>
+      <c r="G33" s="18" t="n"/>
+      <c r="H33" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I31" s="18" t="n"/>
-      <c r="J31" s="18" t="n"/>
-      <c r="K31" s="18" t="n"/>
-      <c r="L31" s="18" t="n"/>
-      <c r="M31" s="18" t="n"/>
-      <c r="N31" s="18" t="n"/>
-      <c r="O31" s="18" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>▸ NYC / Long Island / NJ  (23)</t>
-        </is>
-      </c>
-      <c r="B32" s="12" t="n"/>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="12" t="n"/>
-      <c r="E32" s="12" t="n"/>
-      <c r="F32" s="12" t="n"/>
-      <c r="G32" s="12" t="n"/>
-      <c r="H32" s="12" t="n"/>
-      <c r="I32" s="12" t="n"/>
-      <c r="J32" s="12" t="n"/>
-      <c r="K32" s="12" t="n"/>
-      <c r="L32" s="12" t="n"/>
-      <c r="M32" s="12" t="n"/>
-      <c r="N32" s="12" t="n"/>
-      <c r="O32" s="12" t="n"/>
-    </row>
-    <row r="33" outlineLevel="1">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>NYC / Long Island / NJ</t>
-        </is>
-      </c>
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>Viva Margherita restaurant complete contents (building torn down)</t>
-        </is>
-      </c>
-      <c r="C33" s="13" t="inlineStr">
-        <is>
-          <t>restaurant closing</t>
-        </is>
-      </c>
-      <c r="D33" s="13" t="inlineStr">
-        <is>
-          <t>Edgewater</t>
-        </is>
-      </c>
-      <c r="E33" s="13" t="inlineStr">
-        <is>
-          <t>NJ</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="n">
-        <v>186</v>
-      </c>
-      <c r="G33" s="13" t="inlineStr">
-        <is>
-          <t>Complete contents / make offer</t>
-        </is>
-      </c>
-      <c r="H33" s="15" t="n"/>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="J33" s="13" t="inlineStr"/>
-      <c r="K33" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L33" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M33" s="13" t="inlineStr"/>
-      <c r="N33" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O33" s="14" t="inlineStr">
-        <is>
-          <t>Address 163 Old River Road, Edgewater NJ. Building being torn down; complete restaurant contents for sale / make offer.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" outlineLevel="1">
-      <c r="A34" s="13" t="inlineStr">
-        <is>
-          <t>NYC / Long Island / NJ</t>
-        </is>
-      </c>
-      <c r="B34" s="14" t="inlineStr">
-        <is>
-          <t>Japanese BBQ &amp; bar – ~47 lots: Turbo Air, Hoshizaki ice machine, Pitco, Beverage-Air</t>
-        </is>
-      </c>
-      <c r="C34" s="13" t="inlineStr">
-        <is>
-          <t>restaurant closing</t>
-        </is>
-      </c>
-      <c r="D34" s="13" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="E34" s="13" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="F34" s="13" t="n">
-        <v>191</v>
-      </c>
-      <c r="G34" s="13" t="inlineStr">
-        <is>
-          <t>Live + webcast, 18% BP + 3%</t>
-        </is>
-      </c>
-      <c r="H34" s="15" t="n"/>
-      <c r="I34" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="J34" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 04:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K34" s="13" t="inlineStr">
-        <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
-        </is>
-      </c>
-      <c r="L34" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M34" s="13" t="inlineStr"/>
-      <c r="N34" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O34" s="14" t="inlineStr">
-        <is>
-          <t>Wed Oct 21 4 PM. NYC 10013.</t>
-        </is>
-      </c>
+      <c r="I33" s="18" t="n"/>
+      <c r="J33" s="18" t="n"/>
+      <c r="K33" s="18" t="n"/>
+      <c r="L33" s="18" t="n"/>
+      <c r="M33" s="18" t="n"/>
+      <c r="N33" s="18" t="n"/>
+      <c r="O33" s="18" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>▸ NYC / Long Island / NJ  (22)</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="12" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="12" t="n"/>
+      <c r="G34" s="12" t="n"/>
+      <c r="H34" s="12" t="n"/>
+      <c r="I34" s="12" t="n"/>
+      <c r="J34" s="12" t="n"/>
+      <c r="K34" s="12" t="n"/>
+      <c r="L34" s="12" t="n"/>
+      <c r="M34" s="12" t="n"/>
+      <c r="N34" s="12" t="n"/>
+      <c r="O34" s="12" t="n"/>
     </row>
     <row r="35" outlineLevel="1">
       <c r="A35" s="13" t="inlineStr">
@@ -20376,36 +20308,36 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>Flooring company closed – pro tool package</t>
+          <t>Viva Margherita restaurant complete contents (building torn down)</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>tools liquidation</t>
+          <t>restaurant closing</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Edgewater</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
-          <t>$1,000</t>
+          <t>Complete contents / make offer</t>
         </is>
       </c>
       <c r="H35" s="15" t="n"/>
       <c r="I35" s="13" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="J35" s="13" t="inlineStr"/>
@@ -20427,7 +20359,7 @@
       </c>
       <c r="O35" s="14" t="inlineStr">
         <is>
-          <t>Flooring/construction company closed; pro tool package $1,000.</t>
+          <t>Address 163 Old River Road, Edgewater NJ. Building being torn down; complete restaurant contents for sale / make offer.</t>
         </is>
       </c>
     </row>
@@ -20439,26 +20371,26 @@
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>Corporate caterer – Alto-Shaam, new boxed Avantco rice cookers &amp; Cadco oven, Perlick, MerryChef</t>
+          <t>Japanese BBQ &amp; bar – ~47 lots: Turbo Air, Hoshizaki ice machine, Pitco, Beverage-Air</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>restaurant closing</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>Jersey City</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
@@ -20468,12 +20400,12 @@
       <c r="H36" s="15" t="n"/>
       <c r="I36" s="13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J36" s="13" t="inlineStr">
         <is>
-          <t>2026-10-22 02:00 PM ET</t>
+          <t>2026-10-21 04:00 PM ET</t>
         </is>
       </c>
       <c r="K36" s="13" t="inlineStr">
@@ -20494,7 +20426,7 @@
       </c>
       <c r="O36" s="14" t="inlineStr">
         <is>
-          <t>Thu Oct 22 2 PM.</t>
+          <t>Wed Oct 21 4 PM. NYC 10013.</t>
         </is>
       </c>
     </row>
@@ -20506,36 +20438,36 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>Lighting store closing – lease ended, up to 70% off showroom</t>
+          <t>Flooring company closed – pro tool package</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>tools liquidation</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>Jersey City</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t>up to 70% off</t>
+          <t>$1,000</t>
         </is>
       </c>
       <c r="H37" s="15" t="n"/>
       <c r="I37" s="13" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J37" s="13" t="inlineStr"/>
@@ -20557,7 +20489,7 @@
       </c>
       <c r="O37" s="14" t="inlineStr">
         <is>
-          <t>Lighting store closing, lease ended. Showroom inventory up to 70% off.</t>
+          <t>Flooring/construction company closed; pro tool package $1,000.</t>
         </is>
       </c>
     </row>
@@ -20569,42 +20501,42 @@
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>Tools / plumbing / MRO supply inventory – Hilti/DeWalt/Milwaukee, fittings, heat pumps</t>
+          <t>New-in-box commercial refrigeration lot – 10 Beverage-Air &amp; Perlick units (bar never opened)</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>commercial refrigeration lot</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>Riverdale</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>$27,500 all 10 (or per unit $2,800–$4,150)</t>
         </is>
       </c>
       <c r="H38" s="15" t="n"/>
-      <c r="I38" s="13" t="inlineStr"/>
-      <c r="J38" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-30 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="J38" s="13" t="inlineStr"/>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L38" s="13" t="inlineStr">
@@ -20620,7 +20552,7 @@
       </c>
       <c r="O38" s="14" t="inlineStr">
         <is>
-          <t>Bulk resale inventory.</t>
+          <t>Financial District. Never installed, factory packaging: 2 Beverage-Air HBF23HC-1-HS reach-in freezers ($4,150 ea), 3 HBR23HC-1-HS reach-in fridges ($3,550 ea), 1 UCR48AHC 48" undercounter ($2,800), 3 Perlick HC24FS4 glass frosters + 1 HC24RS4 beverage fridge ($2,850 ea). Seller says full retail $47,463 (about 42% off as a bundle). Updated Oct 14.</t>
         </is>
       </c>
     </row>
@@ -20632,17 +20564,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>Ice cream + cookie franchise equipment – Taylor soft-serve, Atosa, Blodgett</t>
+          <t>Corporate caterer – Alto-Shaam, new boxed Avantco rice cookers &amp; Cadco oven, Perlick, MerryChef</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>Riverdale</t>
+          <t>Jersey City</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -20651,28 +20583,32 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H39" s="15" t="n"/>
-      <c r="I39" s="13" t="inlineStr"/>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
       <c r="J39" s="13" t="inlineStr">
         <is>
-          <t>2026-11-05 11:00 AM ET</t>
+          <t>2026-10-22 02:00 PM ET</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
-        </is>
-      </c>
-      <c r="L39" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L39" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M39" s="13" t="inlineStr"/>
@@ -20683,7 +20619,7 @@
       </c>
       <c r="O39" s="14" t="inlineStr">
         <is>
-          <t>Resellable units.</t>
+          <t>Thu Oct 22 2 PM.</t>
         </is>
       </c>
     </row>
@@ -20695,17 +20631,17 @@
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>Wascomat commercial washers liquidation (22× W105, 6× W185, dryer panels)</t>
+          <t>Lighting store closing – lease ended, up to 70% off showroom</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>commercial laundry</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>Newark</t>
+          <t>Jersey City</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -20714,17 +20650,17 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
-          <t>$500–$800 each / panels $150</t>
+          <t>up to 70% off</t>
         </is>
       </c>
       <c r="H40" s="15" t="n"/>
       <c r="I40" s="13" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="J40" s="13" t="inlineStr"/>
@@ -20746,7 +20682,7 @@
       </c>
       <c r="O40" s="14" t="inlineStr">
         <is>
-          <t>22× W105 @ $500, 6× W185 @ $800, 20 dryer panels $150. Commercial laundry liquidation.</t>
+          <t>Lighting store closing, lease ended. Showroom inventory up to 70% off.</t>
         </is>
       </c>
     </row>
@@ -20758,17 +20694,17 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>Major food-service caterer – new-in-box True reach-ins, Beverage-Air, TurboChef, Resfab ventless fryer</t>
+          <t>Tools / plumbing / MRO supply inventory – Hilti/DeWalt/Milwaukee, fittings, heat pumps</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>Parsippany</t>
+          <t>Riverdale</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -20777,27 +20713,23 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H41" s="15" t="n"/>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
+      <c r="I41" s="13" t="inlineStr"/>
       <c r="J41" s="13" t="inlineStr">
         <is>
-          <t>2026-11-03 02:00 PM ET</t>
+          <t>2026-10-30 11:00 AM ET</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L41" s="13" t="inlineStr">
@@ -20813,7 +20745,7 @@
       </c>
       <c r="O41" s="14" t="inlineStr">
         <is>
-          <t>Tue Nov 3 2 PM, checkout Nov 4.</t>
+          <t>Bulk resale inventory.</t>
         </is>
       </c>
     </row>
@@ -20825,17 +20757,17 @@
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>Business closing – 160 new Carnes exhaust fans</t>
+          <t>Ice cream + cookie franchise equipment – Taylor soft-serve, Atosa, Blodgett</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>HVAC inventory</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>Kenilworth</t>
+          <t>Riverdale</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -20844,23 +20776,23 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>$40 each or $5,000 all OBO</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H42" s="15" t="n"/>
-      <c r="I42" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="J42" s="13" t="inlineStr"/>
+      <c r="I42" s="13" t="inlineStr"/>
+      <c r="J42" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-05 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L42" s="13" t="inlineStr">
@@ -20876,7 +20808,7 @@
       </c>
       <c r="O42" s="14" t="inlineStr">
         <is>
-          <t>160 new Carnes 80CFM 1.0 sone exhaust fans. $40 each or $5,000 for all OBO. Business closing HVAC inventory.</t>
+          <t>Resellable units.</t>
         </is>
       </c>
     </row>
@@ -20888,17 +20820,17 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>Air Systems Inc – sheet metal / HVAC fabrication shop liquidation</t>
+          <t>Wascomat commercial washers liquidation (22× W105, 6× W185, dryer panels)</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>HVAC shop liquidation</t>
+          <t>commercial laundry</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>Kenilworth</t>
+          <t>Newark</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -20907,23 +20839,23 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t>Timed online (15% BP)</t>
+          <t>$500–$800 each / panels $150</t>
         </is>
       </c>
       <c r="H43" s="15" t="n"/>
-      <c r="I43" s="13" t="inlineStr"/>
-      <c r="J43" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-29 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="J43" s="13" t="inlineStr"/>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner Auctions</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L43" s="13" t="inlineStr">
@@ -20939,7 +20871,7 @@
       </c>
       <c r="O43" s="14" t="inlineStr">
         <is>
-          <t>Vicon HVAC plasma; Flagler/Lockformer/Roto-Die/Engel fab; welders; Clark forklift; Genie Superlift; Ridgid/Milwaukee/DeWalt/Bosch/Hilti/Makita tools; AeroVent/Carnes exhaust fans; racking/scaffolding. Preview Oct 28–29 AM; pickup Oct 29 PM–Nov 4. Same town as Carnes fan CL lot.</t>
+          <t>22× W105 @ $500, 6× W185 @ $800, 20 dryer panels $150. Commercial laundry liquidation.</t>
         </is>
       </c>
     </row>
@@ -20951,17 +20883,17 @@
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>Serpico's Pizzeria (lost lease) – Bari ovens, walk-in, Hobart 60qt, Vulcan range</t>
+          <t>Major food-service caterer – new-in-box True reach-ins, Beverage-Air, TurboChef, Resfab ventless fryer</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>Allenhurst</t>
+          <t>Parsippany</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -20970,28 +20902,32 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>No-reserve online auction</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H44" s="15" t="n"/>
-      <c r="I44" s="13" t="inlineStr"/>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
       <c r="J44" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 11:00 AM ET</t>
+          <t>2026-11-03 02:00 PM ET</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>Peter Costanzo / EstateSales.net</t>
-        </is>
-      </c>
-      <c r="L44" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L44" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M44" s="13" t="inlineStr"/>
@@ -21002,7 +20938,7 @@
       </c>
       <c r="O44" s="14" t="inlineStr">
         <is>
-          <t>Absolute / no reserve.</t>
+          <t>Tue Nov 3 2 PM, checkout Nov 4.</t>
         </is>
       </c>
     </row>
@@ -21014,17 +20950,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>Altitude Trampoline Park liquidation – partial: Atosa, TurboChef, stainless</t>
+          <t>Business closing – 160 new Carnes exhaust fans</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>facility contents</t>
+          <t>HVAC inventory</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>Iselin</t>
+          <t>Kenilworth</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -21033,28 +20969,28 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>$40 each or $5,000 all OBO</t>
         </is>
       </c>
       <c r="H45" s="15" t="n"/>
-      <c r="I45" s="13" t="inlineStr"/>
-      <c r="J45" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J45" s="13" t="inlineStr"/>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
-        </is>
-      </c>
-      <c r="L45" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L45" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M45" s="13" t="inlineStr"/>
@@ -21065,7 +21001,7 @@
       </c>
       <c r="O45" s="14" t="inlineStr">
         <is>
-          <t>Some kitchen gear only.</t>
+          <t>160 new Carnes 80CFM 1.0 sone exhaust fans. $40 each or $5,000 for all OBO. Business closing HVAC inventory.</t>
         </is>
       </c>
     </row>
@@ -21077,17 +21013,17 @@
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>Restaurant / pizzeria (contents not described)</t>
+          <t>Air Systems Inc – sheet metal / HVAC fabrication shop liquidation</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>HVAC shop liquidation</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>Berkeley Heights</t>
+          <t>Kenilworth</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -21096,32 +21032,28 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Timed online (15% BP)</t>
         </is>
       </c>
       <c r="H46" s="15" t="n"/>
-      <c r="I46" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
+      <c r="I46" s="13" t="inlineStr"/>
       <c r="J46" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 02:00 PM ET</t>
+          <t>2026-10-29 11:00 AM ET</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
-        </is>
-      </c>
-      <c r="L46" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>A.J. Willner Auctions</t>
+        </is>
+      </c>
+      <c r="L46" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M46" s="13" t="inlineStr"/>
@@ -21132,7 +21064,7 @@
       </c>
       <c r="O46" s="14" t="inlineStr">
         <is>
-          <t>Tue Oct 20 2 PM. No item description on page.</t>
+          <t>Vicon HVAC plasma; Flagler/Lockformer/Roto-Die/Engel fab; welders; Clark forklift; Genie Superlift; Ridgid/Milwaukee/DeWalt/Bosch/Hilti/Makita tools; AeroVent/Carnes exhaust fans; racking/scaffolding. Preview Oct 28–29 AM; pickup Oct 29 PM–Nov 4. Same town as Carnes fan CL lot.</t>
         </is>
       </c>
     </row>
@@ -21144,17 +21076,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
+          <t>Serpico's Pizzeria (lost lease) – Bari ovens, walk-in, Hobart 60qt, Vulcan range</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>lien sale</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>Edison</t>
+          <t>Allenhurst</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -21163,24 +21095,28 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
-          <t>Online auction, $2K load-out fee</t>
+          <t>No-reserve online auction</t>
         </is>
       </c>
       <c r="H47" s="15" t="n"/>
       <c r="I47" s="13" t="inlineStr"/>
-      <c r="J47" s="13" t="inlineStr"/>
+      <c r="J47" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
-        </is>
-      </c>
-      <c r="L47" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Peter Costanzo / EstateSales.net</t>
+        </is>
+      </c>
+      <c r="L47" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M47" s="13" t="inlineStr"/>
@@ -21191,7 +21127,7 @@
       </c>
       <c r="O47" s="14" t="inlineStr">
         <is>
-          <t>&gt;$100K new. Close date not captured.</t>
+          <t>Absolute / no reserve.</t>
         </is>
       </c>
     </row>
@@ -21203,17 +21139,17 @@
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
+          <t>Altitude Trampoline Park liquidation – partial: Atosa, TurboChef, stainless</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>facility contents</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>Edison</t>
+          <t>Iselin</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -21222,39 +21158,31 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>Live + HiBid webcast, 18% BP + 3% card</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H48" s="15" t="n"/>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
+      <c r="I48" s="13" t="inlineStr"/>
       <c r="J48" s="13" t="inlineStr">
         <is>
-          <t>2026-10-25 01:00 PM ET</t>
+          <t>2026-10-21 11:00 AM ET</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
-        </is>
-      </c>
-      <c r="L48" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M48" s="21" t="inlineStr">
-        <is>
-          <t>FLIP</t>
-        </is>
-      </c>
+          <t>A.J. Willner</t>
+        </is>
+      </c>
+      <c r="L48" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M48" s="13" t="inlineStr"/>
       <c r="N48" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -21262,7 +21190,7 @@
       </c>
       <c r="O48" s="14" t="inlineStr">
         <is>
-          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
+          <t>Some kitchen gear only.</t>
         </is>
       </c>
     </row>
@@ -21274,17 +21202,17 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
+          <t>Restaurant / pizzeria (contents not described)</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>restaurant closing</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>East Brunswick</t>
+          <t>Berkeley Heights</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -21293,28 +21221,32 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H49" s="15" t="n"/>
-      <c r="I49" s="13" t="inlineStr"/>
+      <c r="I49" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="J49" s="13" t="inlineStr">
         <is>
-          <t>2026-11-03 11:00 AM ET</t>
+          <t>2026-10-20 02:00 PM ET</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
-        </is>
-      </c>
-      <c r="L49" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L49" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M49" s="13" t="inlineStr"/>
@@ -21325,7 +21257,7 @@
       </c>
       <c r="O49" s="14" t="inlineStr">
         <is>
-          <t>Store inventory.</t>
+          <t>Tue Oct 20 2 PM. No item description on page.</t>
         </is>
       </c>
     </row>
@@ -21337,17 +21269,17 @@
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>High-end deli (contents not described)</t>
+          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>lien sale</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>Manalapan Township</t>
+          <t>Edison</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -21356,32 +21288,24 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Online auction, $2K load-out fee</t>
         </is>
       </c>
       <c r="H50" s="15" t="n"/>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="J50" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-19 04:00 PM ET</t>
-        </is>
-      </c>
+      <c r="I50" s="13" t="inlineStr"/>
+      <c r="J50" s="13" t="inlineStr"/>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
-        </is>
-      </c>
-      <c r="L50" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>A.J. Willner</t>
+        </is>
+      </c>
+      <c r="L50" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M50" s="13" t="inlineStr"/>
@@ -21392,7 +21316,7 @@
       </c>
       <c r="O50" s="14" t="inlineStr">
         <is>
-          <t>Mon Oct 19 4 PM. No item description on page.</t>
+          <t>&gt;$100K new. Close date not captured.</t>
         </is>
       </c>
     </row>
@@ -21404,17 +21328,17 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>Bakery/Cafe Somerville NJ – rack ovens, La Marzocco, food truck (~76 lots)</t>
+          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>Somerville</t>
+          <t>Edison</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -21423,27 +21347,27 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>
-          <t>Live webcast + online (18% BP online)</t>
+          <t>Live + HiBid webcast, 18% BP + 3% card</t>
         </is>
       </c>
       <c r="H51" s="15" t="n"/>
       <c r="I51" s="13" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J51" s="13" t="inlineStr">
         <is>
-          <t>2026-10-26 02:00 PM ET</t>
+          <t>2026-10-25 01:00 PM ET</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>HiBid / Best Buy Auctioneers</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
       <c r="L51" s="13" t="inlineStr">
@@ -21451,7 +21375,11 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M51" s="13" t="inlineStr"/>
+      <c r="M51" s="21" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
       <c r="N51" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -21459,7 +21387,7 @@
       </c>
       <c r="O51" s="14" t="inlineStr">
         <is>
-          <t>Full bakery/cafe commercial kitchen: food truck w/ pizza oven, La Marzocco espresso, Mazzer, Baxter + Empire Logiudice rack ovens, dough depositor, Globe floor mixer, Artic Air / SS refrigeration, fryers, Vitamix, Robot Coupe, display cases, dining furniture. Preview 11 AM sale day; checkout Tue 10/27.</t>
+          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
         </is>
       </c>
     </row>
@@ -21471,17 +21399,17 @@
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>Ability to Work kitchen and store – commercial kitchen + store fixtures (~135 lots)</t>
+          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>Flemington</t>
+          <t>East Brunswick</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -21490,23 +21418,23 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
-          <t>Timed online (15% BP)</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H52" s="15" t="n"/>
       <c r="I52" s="13" t="inlineStr"/>
       <c r="J52" s="13" t="inlineStr">
         <is>
-          <t>2026-10-27 11:02 AM ET</t>
+          <t>2026-11-03 11:00 AM ET</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>HiBid</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L52" s="13" t="inlineStr">
@@ -21522,7 +21450,7 @@
       </c>
       <c r="O52" s="14" t="inlineStr">
         <is>
-          <t>Apprentice/hospitality training cafe-kitchen and store dispersal. Preview 9–11 AM sale day; removal Oct 27 noon–Oct 29.</t>
+          <t>Store inventory.</t>
         </is>
       </c>
     </row>
@@ -21534,17 +21462,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
+          <t>Bakery/Cafe Somerville NJ – rack ovens, La Marzocco, food truck (~76 lots)</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>showroom closing</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>Lawrenceville</t>
+          <t>Somerville</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -21553,23 +21481,27 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
-          <t>Online auction, 18% BP</t>
+          <t>Live webcast + online (18% BP online)</t>
         </is>
       </c>
       <c r="H53" s="15" t="n"/>
-      <c r="I53" s="13" t="inlineStr"/>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="J53" s="13" t="inlineStr">
         <is>
-          <t>2026-10-27 09:00 AM ET</t>
+          <t>2026-10-26 02:00 PM ET</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
+          <t>HiBid / Best Buy Auctioneers</t>
         </is>
       </c>
       <c r="L53" s="13" t="inlineStr">
@@ -21585,7 +21517,7 @@
       </c>
       <c r="O53" s="14" t="inlineStr">
         <is>
-          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
+          <t>Full bakery/cafe commercial kitchen: food truck w/ pizza oven, La Marzocco espresso, Mazzer, Baxter + Empire Logiudice rack ovens, dough depositor, Globe floor mixer, Artic Air / SS refrigeration, fryers, Vitamix, Robot Coupe, display cases, dining furniture. Preview 11 AM sale day; checkout Tue 10/27.</t>
         </is>
       </c>
     </row>
@@ -21597,17 +21529,17 @@
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>Milwaukee / Walmart / hardware store mega auction pt 3</t>
+          <t>Ability to Work kitchen and store – commercial kitchen + store fixtures (~135 lots)</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>Mount Holly</t>
+          <t>Flemington</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -21616,18 +21548,18 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>254</v>
+        <v>237</v>
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>HiBid online auction</t>
+          <t>Timed online (15% BP)</t>
         </is>
       </c>
       <c r="H54" s="15" t="n"/>
       <c r="I54" s="13" t="inlineStr"/>
       <c r="J54" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 06:00 PM ET</t>
+          <t>2026-10-27 11:02 AM ET</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
@@ -21635,9 +21567,9 @@
           <t>HiBid</t>
         </is>
       </c>
-      <c r="L54" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+      <c r="L54" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M54" s="13" t="inlineStr"/>
@@ -21648,7 +21580,7 @@
       </c>
       <c r="O54" s="14" t="inlineStr">
         <is>
-          <t>Close Oct 18 or 19 6 PM (later used).</t>
+          <t>Apprentice/hospitality training cafe-kitchen and store dispersal. Preview 9–11 AM sale day; removal Oct 27 noon–Oct 29.</t>
         </is>
       </c>
     </row>
@@ -21660,7 +21592,7 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
+          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
@@ -21670,7 +21602,7 @@
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>Cherry Hill</t>
+          <t>Lawrenceville</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -21679,18 +21611,18 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
-          <t>Online auction, openers ~$0.50</t>
+          <t>Online auction, 18% BP</t>
         </is>
       </c>
       <c r="H55" s="15" t="n"/>
       <c r="I55" s="13" t="inlineStr"/>
       <c r="J55" s="13" t="inlineStr">
         <is>
-          <t>2026-11-02 11:00 AM ET</t>
+          <t>2026-10-27 09:00 AM ET</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
@@ -21711,231 +21643,231 @@
       </c>
       <c r="O55" s="14" t="inlineStr">
         <is>
+          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" outlineLevel="1">
+      <c r="A56" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B56" s="14" t="inlineStr">
+        <is>
+          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
+        </is>
+      </c>
+      <c r="C56" s="13" t="inlineStr">
+        <is>
+          <t>showroom closing</t>
+        </is>
+      </c>
+      <c r="D56" s="13" t="inlineStr">
+        <is>
+          <t>Cherry Hill</t>
+        </is>
+      </c>
+      <c r="E56" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F56" s="13" t="n">
+        <v>266</v>
+      </c>
+      <c r="G56" s="13" t="inlineStr">
+        <is>
+          <t>Online auction, openers ~$0.50</t>
+        </is>
+      </c>
+      <c r="H56" s="15" t="n"/>
+      <c r="I56" s="13" t="inlineStr"/>
+      <c r="J56" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-02 11:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K56" s="13" t="inlineStr">
+        <is>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L56" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M56" s="13" t="inlineStr"/>
+      <c r="N56" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O56" s="14" t="inlineStr">
+        <is>
           <t>Lots close from Nov 2 11 AM.</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="17" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="17" t="inlineStr">
         <is>
           <t>Subtotal — NYC / Long Island / NJ</t>
         </is>
       </c>
-      <c r="B56" s="17" t="inlineStr">
-        <is>
-          <t>23 item(s)</t>
-        </is>
-      </c>
-      <c r="C56" s="18" t="n"/>
-      <c r="D56" s="18" t="n"/>
-      <c r="E56" s="18" t="n"/>
-      <c r="F56" s="18" t="n"/>
-      <c r="G56" s="18" t="n"/>
-      <c r="H56" s="19" t="n">
+      <c r="B57" s="17" t="inlineStr">
+        <is>
+          <t>22 item(s)</t>
+        </is>
+      </c>
+      <c r="C57" s="18" t="n"/>
+      <c r="D57" s="18" t="n"/>
+      <c r="E57" s="18" t="n"/>
+      <c r="F57" s="18" t="n"/>
+      <c r="G57" s="18" t="n"/>
+      <c r="H57" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I56" s="18" t="n"/>
-      <c r="J56" s="18" t="n"/>
-      <c r="K56" s="18" t="n"/>
-      <c r="L56" s="18" t="n"/>
-      <c r="M56" s="18" t="n"/>
-      <c r="N56" s="18" t="n"/>
-      <c r="O56" s="18" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr">
+      <c r="I57" s="18" t="n"/>
+      <c r="J57" s="18" t="n"/>
+      <c r="K57" s="18" t="n"/>
+      <c r="L57" s="18" t="n"/>
+      <c r="M57" s="18" t="n"/>
+      <c r="N57" s="18" t="n"/>
+      <c r="O57" s="18" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>▸ Eastern PA / Mid-Atlantic  (1)</t>
         </is>
       </c>
-      <c r="B57" s="12" t="n"/>
-      <c r="C57" s="12" t="n"/>
-      <c r="D57" s="12" t="n"/>
-      <c r="E57" s="12" t="n"/>
-      <c r="F57" s="12" t="n"/>
-      <c r="G57" s="12" t="n"/>
-      <c r="H57" s="12" t="n"/>
-      <c r="I57" s="12" t="n"/>
-      <c r="J57" s="12" t="n"/>
-      <c r="K57" s="12" t="n"/>
-      <c r="L57" s="12" t="n"/>
-      <c r="M57" s="12" t="n"/>
-      <c r="N57" s="12" t="n"/>
-      <c r="O57" s="12" t="n"/>
-    </row>
-    <row r="58" outlineLevel="1">
-      <c r="A58" s="13" t="inlineStr">
+      <c r="B58" s="12" t="n"/>
+      <c r="C58" s="12" t="n"/>
+      <c r="D58" s="12" t="n"/>
+      <c r="E58" s="12" t="n"/>
+      <c r="F58" s="12" t="n"/>
+      <c r="G58" s="12" t="n"/>
+      <c r="H58" s="12" t="n"/>
+      <c r="I58" s="12" t="n"/>
+      <c r="J58" s="12" t="n"/>
+      <c r="K58" s="12" t="n"/>
+      <c r="L58" s="12" t="n"/>
+      <c r="M58" s="12" t="n"/>
+      <c r="N58" s="12" t="n"/>
+      <c r="O58" s="12" t="n"/>
+    </row>
+    <row r="59" outlineLevel="1">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>Eastern PA / Mid-Atlantic</t>
         </is>
       </c>
-      <c r="B58" s="14" t="inlineStr">
+      <c r="B59" s="14" t="inlineStr">
         <is>
           <t>October restaurant consignment – Hobart, Rational, True + NEW scratch-and-dent Migali/Avantco</t>
         </is>
       </c>
-      <c r="C58" s="13" t="inlineStr">
+      <c r="C59" s="13" t="inlineStr">
         <is>
           <t>restaurant</t>
         </is>
       </c>
-      <c r="D58" s="13" t="inlineStr">
+      <c r="D59" s="13" t="inlineStr">
         <is>
           <t>Harrisburg</t>
         </is>
       </c>
-      <c r="E58" s="13" t="inlineStr">
+      <c r="E59" s="13" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="F58" s="13" t="n">
+      <c r="F59" s="13" t="n">
         <v>340</v>
       </c>
-      <c r="G58" s="13" t="inlineStr">
+      <c r="G59" s="13" t="inlineStr">
         <is>
           <t>Online auction, 15% BP, ships $55/pallet</t>
         </is>
       </c>
-      <c r="H58" s="15" t="n"/>
-      <c r="I58" s="13" t="inlineStr"/>
-      <c r="J58" s="13" t="inlineStr">
+      <c r="H59" s="15" t="n"/>
+      <c r="I59" s="13" t="inlineStr"/>
+      <c r="J59" s="13" t="inlineStr">
         <is>
           <t>2026-10-21 11:00 AM ET</t>
         </is>
       </c>
-      <c r="K58" s="13" t="inlineStr">
+      <c r="K59" s="13" t="inlineStr">
         <is>
           <t>Restaurant Auction Co</t>
         </is>
       </c>
-      <c r="L58" s="20" t="inlineStr">
+      <c r="L59" s="20" t="inlineStr">
         <is>
           <t>ENDING SOON</t>
         </is>
       </c>
-      <c r="M58" s="13" t="inlineStr"/>
-      <c r="N58" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O58" s="14" t="inlineStr">
+      <c r="M59" s="13" t="inlineStr"/>
+      <c r="N59" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O59" s="14" t="inlineStr">
         <is>
           <t>Closes Oct 21 10 or 11 AM (later used). Shippable.</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="17" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Eastern PA / Mid-Atlantic</t>
         </is>
       </c>
-      <c r="B59" s="17" t="inlineStr">
+      <c r="B60" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C59" s="18" t="n"/>
-      <c r="D59" s="18" t="n"/>
-      <c r="E59" s="18" t="n"/>
-      <c r="F59" s="18" t="n"/>
-      <c r="G59" s="18" t="n"/>
-      <c r="H59" s="19" t="n">
+      <c r="C60" s="18" t="n"/>
+      <c r="D60" s="18" t="n"/>
+      <c r="E60" s="18" t="n"/>
+      <c r="F60" s="18" t="n"/>
+      <c r="G60" s="18" t="n"/>
+      <c r="H60" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I59" s="18" t="n"/>
-      <c r="J59" s="18" t="n"/>
-      <c r="K59" s="18" t="n"/>
-      <c r="L59" s="18" t="n"/>
-      <c r="M59" s="18" t="n"/>
-      <c r="N59" s="18" t="n"/>
-      <c r="O59" s="18" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="11" t="inlineStr">
+      <c r="I60" s="18" t="n"/>
+      <c r="J60" s="18" t="n"/>
+      <c r="K60" s="18" t="n"/>
+      <c r="L60" s="18" t="n"/>
+      <c r="M60" s="18" t="n"/>
+      <c r="N60" s="18" t="n"/>
+      <c r="O60" s="18" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t>▸ Upstate / Western NY  (3)</t>
         </is>
       </c>
-      <c r="B60" s="12" t="n"/>
-      <c r="C60" s="12" t="n"/>
-      <c r="D60" s="12" t="n"/>
-      <c r="E60" s="12" t="n"/>
-      <c r="F60" s="12" t="n"/>
-      <c r="G60" s="12" t="n"/>
-      <c r="H60" s="12" t="n"/>
-      <c r="I60" s="12" t="n"/>
-      <c r="J60" s="12" t="n"/>
-      <c r="K60" s="12" t="n"/>
-      <c r="L60" s="12" t="n"/>
-      <c r="M60" s="12" t="n"/>
-      <c r="N60" s="12" t="n"/>
-      <c r="O60" s="12" t="n"/>
-    </row>
-    <row r="61" outlineLevel="1">
-      <c r="A61" s="13" t="inlineStr">
-        <is>
-          <t>Upstate / Western NY</t>
-        </is>
-      </c>
-      <c r="B61" s="14" t="inlineStr">
-        <is>
-          <t>Former Taco Del Mar – stainless, warmers, walk-in panels</t>
-        </is>
-      </c>
-      <c r="C61" s="13" t="inlineStr">
-        <is>
-          <t>restaurant</t>
-        </is>
-      </c>
-      <c r="D61" s="13" t="inlineStr">
-        <is>
-          <t>Watson</t>
-        </is>
-      </c>
-      <c r="E61" s="13" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="F61" s="13" t="n">
-        <v>260</v>
-      </c>
-      <c r="G61" s="13" t="inlineStr">
-        <is>
-          <t>HiBid online auction</t>
-        </is>
-      </c>
-      <c r="H61" s="15" t="n"/>
-      <c r="I61" s="13" t="inlineStr"/>
-      <c r="J61" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-20 06:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K61" s="13" t="inlineStr">
-        <is>
-          <t>Adirondack Asset / HiBid</t>
-        </is>
-      </c>
-      <c r="L61" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M61" s="13" t="inlineStr"/>
-      <c r="N61" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O61" s="14" t="inlineStr">
-        <is>
-          <t>Small lot.</t>
-        </is>
-      </c>
+      <c r="B61" s="12" t="n"/>
+      <c r="C61" s="12" t="n"/>
+      <c r="D61" s="12" t="n"/>
+      <c r="E61" s="12" t="n"/>
+      <c r="F61" s="12" t="n"/>
+      <c r="G61" s="12" t="n"/>
+      <c r="H61" s="12" t="n"/>
+      <c r="I61" s="12" t="n"/>
+      <c r="J61" s="12" t="n"/>
+      <c r="K61" s="12" t="n"/>
+      <c r="L61" s="12" t="n"/>
+      <c r="M61" s="12" t="n"/>
+      <c r="N61" s="12" t="n"/>
+      <c r="O61" s="12" t="n"/>
     </row>
     <row r="62" outlineLevel="1">
       <c r="A62" s="13" t="inlineStr">
@@ -21945,7 +21877,7 @@
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>Closed restaurant – coolers, fridges, prep tables</t>
+          <t>Former Taco Del Mar – stainless, warmers, walk-in panels</t>
         </is>
       </c>
       <c r="C62" s="13" t="inlineStr">
@@ -21955,7 +21887,7 @@
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>Palmyra</t>
+          <t>Watson</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
@@ -21964,23 +21896,23 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>333</v>
+        <v>260</v>
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>HiBid, 15% BP</t>
+          <t>HiBid online auction</t>
         </is>
       </c>
       <c r="H62" s="15" t="n"/>
       <c r="I62" s="13" t="inlineStr"/>
       <c r="J62" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 07:00 PM ET</t>
+          <t>2026-10-20 06:00 PM ET</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>Reynolds Auction Co / HiBid</t>
+          <t>Adirondack Asset / HiBid</t>
         </is>
       </c>
       <c r="L62" s="20" t="inlineStr">
@@ -21996,7 +21928,7 @@
       </c>
       <c r="O62" s="14" t="inlineStr">
         <is>
-          <t>No new out-of-state bidders. Small.</t>
+          <t>Small lot.</t>
         </is>
       </c>
     </row>
@@ -22008,7 +21940,7 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>Restaurant &amp; fitness equipment</t>
+          <t>Closed restaurant – coolers, fridges, prep tables</t>
         </is>
       </c>
       <c r="C63" s="13" t="inlineStr">
@@ -22018,7 +21950,7 @@
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>Williamsville</t>
+          <t>Palmyra</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
@@ -22027,28 +21959,28 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>408</v>
+        <v>333</v>
       </c>
       <c r="G63" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>HiBid, 15% BP</t>
         </is>
       </c>
       <c r="H63" s="15" t="n"/>
       <c r="I63" s="13" t="inlineStr"/>
       <c r="J63" s="13" t="inlineStr">
         <is>
-          <t>2026-10-26 07:30 PM ET</t>
+          <t>2026-10-19 07:00 PM ET</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
         <is>
-          <t>Cash Auctions</t>
-        </is>
-      </c>
-      <c r="L63" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Reynolds Auction Co / HiBid</t>
+        </is>
+      </c>
+      <c r="L63" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M63" s="13" t="inlineStr"/>
@@ -22059,231 +21991,231 @@
       </c>
       <c r="O63" s="14" t="inlineStr">
         <is>
+          <t>No new out-of-state bidders. Small.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" outlineLevel="1">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>Upstate / Western NY</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant &amp; fitness equipment</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="D64" s="13" t="inlineStr">
+        <is>
+          <t>Williamsville</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F64" s="13" t="n">
+        <v>408</v>
+      </c>
+      <c r="G64" s="13" t="inlineStr">
+        <is>
+          <t>Online auction</t>
+        </is>
+      </c>
+      <c r="H64" s="15" t="n"/>
+      <c r="I64" s="13" t="inlineStr"/>
+      <c r="J64" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-26 07:30 PM ET</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>Cash Auctions</t>
+        </is>
+      </c>
+      <c r="L64" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M64" s="13" t="inlineStr"/>
+      <c r="N64" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O64" s="14" t="inlineStr">
+        <is>
           <t>Lots not reviewed.</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="17" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Upstate / Western NY</t>
         </is>
       </c>
-      <c r="B64" s="17" t="inlineStr">
+      <c r="B65" s="17" t="inlineStr">
         <is>
           <t>3 item(s)</t>
         </is>
       </c>
-      <c r="C64" s="18" t="n"/>
-      <c r="D64" s="18" t="n"/>
-      <c r="E64" s="18" t="n"/>
-      <c r="F64" s="18" t="n"/>
-      <c r="G64" s="18" t="n"/>
-      <c r="H64" s="19" t="n">
+      <c r="C65" s="18" t="n"/>
+      <c r="D65" s="18" t="n"/>
+      <c r="E65" s="18" t="n"/>
+      <c r="F65" s="18" t="n"/>
+      <c r="G65" s="18" t="n"/>
+      <c r="H65" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I64" s="18" t="n"/>
-      <c r="J64" s="18" t="n"/>
-      <c r="K64" s="18" t="n"/>
-      <c r="L64" s="18" t="n"/>
-      <c r="M64" s="18" t="n"/>
-      <c r="N64" s="18" t="n"/>
-      <c r="O64" s="18" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="11" t="inlineStr">
+      <c r="I65" s="18" t="n"/>
+      <c r="J65" s="18" t="n"/>
+      <c r="K65" s="18" t="n"/>
+      <c r="L65" s="18" t="n"/>
+      <c r="M65" s="18" t="n"/>
+      <c r="N65" s="18" t="n"/>
+      <c r="O65" s="18" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
         <is>
           <t>▸ Virginia  (1)</t>
         </is>
       </c>
-      <c r="B65" s="12" t="n"/>
-      <c r="C65" s="12" t="n"/>
-      <c r="D65" s="12" t="n"/>
-      <c r="E65" s="12" t="n"/>
-      <c r="F65" s="12" t="n"/>
-      <c r="G65" s="12" t="n"/>
-      <c r="H65" s="12" t="n"/>
-      <c r="I65" s="12" t="n"/>
-      <c r="J65" s="12" t="n"/>
-      <c r="K65" s="12" t="n"/>
-      <c r="L65" s="12" t="n"/>
-      <c r="M65" s="12" t="n"/>
-      <c r="N65" s="12" t="n"/>
-      <c r="O65" s="12" t="n"/>
-    </row>
-    <row r="66" outlineLevel="1">
-      <c r="A66" s="13" t="inlineStr">
+      <c r="B66" s="12" t="n"/>
+      <c r="C66" s="12" t="n"/>
+      <c r="D66" s="12" t="n"/>
+      <c r="E66" s="12" t="n"/>
+      <c r="F66" s="12" t="n"/>
+      <c r="G66" s="12" t="n"/>
+      <c r="H66" s="12" t="n"/>
+      <c r="I66" s="12" t="n"/>
+      <c r="J66" s="12" t="n"/>
+      <c r="K66" s="12" t="n"/>
+      <c r="L66" s="12" t="n"/>
+      <c r="M66" s="12" t="n"/>
+      <c r="N66" s="12" t="n"/>
+      <c r="O66" s="12" t="n"/>
+    </row>
+    <row r="67" outlineLevel="1">
+      <c r="A67" s="13" t="inlineStr">
         <is>
           <t>Virginia</t>
         </is>
       </c>
-      <c r="B66" s="14" t="inlineStr">
+      <c r="B67" s="14" t="inlineStr">
         <is>
           <t>Haynes Furniture / The Dump – 12 stores closing (furniture, mattresses)</t>
         </is>
       </c>
-      <c r="C66" s="13" t="inlineStr">
+      <c r="C67" s="13" t="inlineStr">
         <is>
           <t>retail GOB</t>
         </is>
       </c>
-      <c r="D66" s="13" t="inlineStr">
+      <c r="D67" s="13" t="inlineStr">
         <is>
           <t>Virginia Beach</t>
         </is>
       </c>
-      <c r="E66" s="13" t="inlineStr">
+      <c r="E67" s="13" t="inlineStr">
         <is>
           <t>VA</t>
         </is>
       </c>
-      <c r="F66" s="13" t="n">
+      <c r="F67" s="13" t="n">
         <v>456</v>
       </c>
-      <c r="G66" s="13" t="inlineStr">
+      <c r="G67" s="13" t="inlineStr">
         <is>
           <t>Retail GOB markdowns</t>
         </is>
       </c>
-      <c r="H66" s="15" t="n"/>
-      <c r="I66" s="13" t="inlineStr">
+      <c r="H67" s="15" t="n"/>
+      <c r="I67" s="13" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="J66" s="13" t="inlineStr"/>
-      <c r="K66" s="13" t="inlineStr">
+      <c r="J67" s="13" t="inlineStr"/>
+      <c r="K67" s="13" t="inlineStr">
         <is>
           <t>SB360 (PR Newswire)</t>
         </is>
       </c>
-      <c r="L66" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M66" s="13" t="inlineStr"/>
-      <c r="N66" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O66" s="14" t="inlineStr">
+      <c r="L67" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M67" s="13" t="inlineStr"/>
+      <c r="N67" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O67" s="14" t="inlineStr">
         <is>
           <t>Posted Oct 8. Multi-state (VA/AZ/GA/IL/TX); pinned at Virginia Beach. Home goods only.</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="17" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Virginia</t>
         </is>
       </c>
-      <c r="B67" s="17" t="inlineStr">
+      <c r="B68" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C67" s="18" t="n"/>
-      <c r="D67" s="18" t="n"/>
-      <c r="E67" s="18" t="n"/>
-      <c r="F67" s="18" t="n"/>
-      <c r="G67" s="18" t="n"/>
-      <c r="H67" s="19" t="n">
+      <c r="C68" s="18" t="n"/>
+      <c r="D68" s="18" t="n"/>
+      <c r="E68" s="18" t="n"/>
+      <c r="F68" s="18" t="n"/>
+      <c r="G68" s="18" t="n"/>
+      <c r="H68" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I67" s="18" t="n"/>
-      <c r="J67" s="18" t="n"/>
-      <c r="K67" s="18" t="n"/>
-      <c r="L67" s="18" t="n"/>
-      <c r="M67" s="18" t="n"/>
-      <c r="N67" s="18" t="n"/>
-      <c r="O67" s="18" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="11" t="inlineStr">
+      <c r="I68" s="18" t="n"/>
+      <c r="J68" s="18" t="n"/>
+      <c r="K68" s="18" t="n"/>
+      <c r="L68" s="18" t="n"/>
+      <c r="M68" s="18" t="n"/>
+      <c r="N68" s="18" t="n"/>
+      <c r="O68" s="18" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t>▸ Midwest  (3)</t>
         </is>
       </c>
-      <c r="B68" s="12" t="n"/>
-      <c r="C68" s="12" t="n"/>
-      <c r="D68" s="12" t="n"/>
-      <c r="E68" s="12" t="n"/>
-      <c r="F68" s="12" t="n"/>
-      <c r="G68" s="12" t="n"/>
-      <c r="H68" s="12" t="n"/>
-      <c r="I68" s="12" t="n"/>
-      <c r="J68" s="12" t="n"/>
-      <c r="K68" s="12" t="n"/>
-      <c r="L68" s="12" t="n"/>
-      <c r="M68" s="12" t="n"/>
-      <c r="N68" s="12" t="n"/>
-      <c r="O68" s="12" t="n"/>
-    </row>
-    <row r="69" outlineLevel="1">
-      <c r="A69" s="13" t="inlineStr">
-        <is>
-          <t>Midwest</t>
-        </is>
-      </c>
-      <c r="B69" s="14" t="inlineStr">
-        <is>
-          <t>Freshway Market whole-grocery liquidation – refrigeration racks, cases, walk-ins, generator</t>
-        </is>
-      </c>
-      <c r="C69" s="13" t="inlineStr">
-        <is>
-          <t>store closing</t>
-        </is>
-      </c>
-      <c r="D69" s="13" t="inlineStr">
-        <is>
-          <t>Chicago</t>
-        </is>
-      </c>
-      <c r="E69" s="13" t="inlineStr">
-        <is>
-          <t>IL</t>
-        </is>
-      </c>
-      <c r="F69" s="13" t="n">
-        <v>862</v>
-      </c>
-      <c r="G69" s="13" t="inlineStr">
-        <is>
-          <t>Online auction</t>
-        </is>
-      </c>
-      <c r="H69" s="15" t="n"/>
-      <c r="I69" s="13" t="inlineStr"/>
-      <c r="J69" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-20 11:00 AM ET</t>
-        </is>
-      </c>
-      <c r="K69" s="13" t="inlineStr">
-        <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L69" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M69" s="13" t="inlineStr"/>
-      <c r="N69" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O69" s="14" t="inlineStr">
-        <is>
-          <t>Closes from Oct 20 10 AM CDT.</t>
-        </is>
-      </c>
+      <c r="B69" s="12" t="n"/>
+      <c r="C69" s="12" t="n"/>
+      <c r="D69" s="12" t="n"/>
+      <c r="E69" s="12" t="n"/>
+      <c r="F69" s="12" t="n"/>
+      <c r="G69" s="12" t="n"/>
+      <c r="H69" s="12" t="n"/>
+      <c r="I69" s="12" t="n"/>
+      <c r="J69" s="12" t="n"/>
+      <c r="K69" s="12" t="n"/>
+      <c r="L69" s="12" t="n"/>
+      <c r="M69" s="12" t="n"/>
+      <c r="N69" s="12" t="n"/>
+      <c r="O69" s="12" t="n"/>
     </row>
     <row r="70" outlineLevel="1">
       <c r="A70" s="13" t="inlineStr">
@@ -22293,17 +22225,17 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>American Sale – total liquidation, all 7 stores (pools, hot tubs, grills, holiday decor)</t>
+          <t>Freshway Market whole-grocery liquidation – refrigeration racks, cases, walk-ins, generator</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>retail GOB</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>Chicagoland</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
@@ -22312,28 +22244,28 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>876</v>
+        <v>862</v>
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
-          <t>Retail GOB, up to 70% off</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H70" s="15" t="n"/>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="J70" s="13" t="inlineStr"/>
+      <c r="I70" s="13" t="inlineStr"/>
+      <c r="J70" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K70" s="13" t="inlineStr">
         <is>
-          <t>Tiger Group (PR Newswire)</t>
-        </is>
-      </c>
-      <c r="L70" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L70" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M70" s="13" t="inlineStr"/>
@@ -22344,7 +22276,7 @@
       </c>
       <c r="O70" s="14" t="inlineStr">
         <is>
-          <t>Posted Oct 15. Watch for a bulk/fixture auction.</t>
+          <t>Closes from Oct 20 10 AM CDT.</t>
         </is>
       </c>
     </row>
@@ -22356,47 +22288,47 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>Straub's Fine Foods store equipment – bakery, kitchen, meat room, Hussmann refrigeration</t>
+          <t>American Sale – total liquidation, all 7 stores (pools, hot tubs, grills, holiday decor)</t>
         </is>
       </c>
       <c r="C71" s="13" t="inlineStr">
         <is>
-          <t>grocery/restaurant</t>
+          <t>retail GOB</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Chicagoland</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>1046</v>
+        <v>876</v>
       </c>
       <c r="G71" s="13" t="inlineStr">
         <is>
-          <t>Online auction (18% BP)</t>
+          <t>Retail GOB, up to 70% off</t>
         </is>
       </c>
       <c r="H71" s="15" t="n"/>
-      <c r="I71" s="13" t="inlineStr"/>
-      <c r="J71" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J71" s="13" t="inlineStr"/>
       <c r="K71" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L71" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Tiger Group (PR Newswire)</t>
+        </is>
+      </c>
+      <c r="L71" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M71" s="13" t="inlineStr"/>
@@ -22407,284 +22339,347 @@
       </c>
       <c r="O71" s="14" t="inlineStr">
         <is>
+          <t>Posted Oct 15. Watch for a bulk/fixture auction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" outlineLevel="1">
+      <c r="A72" s="13" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="B72" s="14" t="inlineStr">
+        <is>
+          <t>Straub's Fine Foods store equipment – bakery, kitchen, meat room, Hussmann refrigeration</t>
+        </is>
+      </c>
+      <c r="C72" s="13" t="inlineStr">
+        <is>
+          <t>grocery/restaurant</t>
+        </is>
+      </c>
+      <c r="D72" s="13" t="inlineStr">
+        <is>
+          <t>St. Louis</t>
+        </is>
+      </c>
+      <c r="E72" s="13" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="F72" s="13" t="n">
+        <v>1046</v>
+      </c>
+      <c r="G72" s="13" t="inlineStr">
+        <is>
+          <t>Online auction (18% BP)</t>
+        </is>
+      </c>
+      <c r="H72" s="15" t="n"/>
+      <c r="I72" s="13" t="inlineStr"/>
+      <c r="J72" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K72" s="13" t="inlineStr">
+        <is>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L72" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M72" s="13" t="inlineStr"/>
+      <c r="N72" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O72" s="14" t="inlineStr">
+        <is>
           <t>Kingshighway store: Revent double-rack oven + proofer, Reed revolving oven, Vulcan convection, Groen kettle, Southbend 6-burner, Pitco fryer, Stero dishwasher, Hobart saw/grinders, Berkel slicers, Hussmann cases + compressor racks, walk-ins, Hoshizaki/Scotsman ice machines, Crown pallet jack. Preview Oct 20 3–6 PM CDT; pickup in St. Louis.</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="17" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Midwest</t>
         </is>
       </c>
-      <c r="B72" s="17" t="inlineStr">
+      <c r="B73" s="17" t="inlineStr">
         <is>
           <t>3 item(s)</t>
         </is>
       </c>
-      <c r="C72" s="18" t="n"/>
-      <c r="D72" s="18" t="n"/>
-      <c r="E72" s="18" t="n"/>
-      <c r="F72" s="18" t="n"/>
-      <c r="G72" s="18" t="n"/>
-      <c r="H72" s="19" t="n">
+      <c r="C73" s="18" t="n"/>
+      <c r="D73" s="18" t="n"/>
+      <c r="E73" s="18" t="n"/>
+      <c r="F73" s="18" t="n"/>
+      <c r="G73" s="18" t="n"/>
+      <c r="H73" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I72" s="18" t="n"/>
-      <c r="J72" s="18" t="n"/>
-      <c r="K72" s="18" t="n"/>
-      <c r="L72" s="18" t="n"/>
-      <c r="M72" s="18" t="n"/>
-      <c r="N72" s="18" t="n"/>
-      <c r="O72" s="18" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="11" t="inlineStr">
+      <c r="I73" s="18" t="n"/>
+      <c r="J73" s="18" t="n"/>
+      <c r="K73" s="18" t="n"/>
+      <c r="L73" s="18" t="n"/>
+      <c r="M73" s="18" t="n"/>
+      <c r="N73" s="18" t="n"/>
+      <c r="O73" s="18" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="11" t="inlineStr">
         <is>
           <t>▸ Texas / South Central  (1)</t>
         </is>
       </c>
-      <c r="B73" s="12" t="n"/>
-      <c r="C73" s="12" t="n"/>
-      <c r="D73" s="12" t="n"/>
-      <c r="E73" s="12" t="n"/>
-      <c r="F73" s="12" t="n"/>
-      <c r="G73" s="12" t="n"/>
-      <c r="H73" s="12" t="n"/>
-      <c r="I73" s="12" t="n"/>
-      <c r="J73" s="12" t="n"/>
-      <c r="K73" s="12" t="n"/>
-      <c r="L73" s="12" t="n"/>
-      <c r="M73" s="12" t="n"/>
-      <c r="N73" s="12" t="n"/>
-      <c r="O73" s="12" t="n"/>
-    </row>
-    <row r="74" outlineLevel="1">
-      <c r="A74" s="13" t="inlineStr">
+      <c r="B74" s="12" t="n"/>
+      <c r="C74" s="12" t="n"/>
+      <c r="D74" s="12" t="n"/>
+      <c r="E74" s="12" t="n"/>
+      <c r="F74" s="12" t="n"/>
+      <c r="G74" s="12" t="n"/>
+      <c r="H74" s="12" t="n"/>
+      <c r="I74" s="12" t="n"/>
+      <c r="J74" s="12" t="n"/>
+      <c r="K74" s="12" t="n"/>
+      <c r="L74" s="12" t="n"/>
+      <c r="M74" s="12" t="n"/>
+      <c r="N74" s="12" t="n"/>
+      <c r="O74" s="12" t="n"/>
+    </row>
+    <row r="75" outlineLevel="1">
+      <c r="A75" s="13" t="inlineStr">
         <is>
           <t>Texas / South Central</t>
         </is>
       </c>
-      <c r="B74" s="14" t="inlineStr">
+      <c r="B75" s="14" t="inlineStr">
         <is>
           <t>Southwest beverage distributor surplus – mostly unused: 16 True merchandisers, 75 Bunn brewers, 100+ micro-market kiosks</t>
         </is>
       </c>
-      <c r="C74" s="13" t="inlineStr">
+      <c r="C75" s="13" t="inlineStr">
         <is>
           <t>distributor surplus</t>
         </is>
       </c>
-      <c r="D74" s="13" t="inlineStr">
+      <c r="D75" s="13" t="inlineStr">
         <is>
           <t>Mesquite</t>
         </is>
       </c>
-      <c r="E74" s="13" t="inlineStr">
+      <c r="E75" s="13" t="inlineStr">
         <is>
           <t>TX</t>
         </is>
       </c>
-      <c r="F74" s="13" t="n">
+      <c r="F75" s="13" t="n">
         <v>1547</v>
       </c>
-      <c r="G74" s="13" t="inlineStr">
+      <c r="G75" s="13" t="inlineStr">
         <is>
           <t>Online auction</t>
         </is>
       </c>
-      <c r="H74" s="15" t="n"/>
-      <c r="I74" s="13" t="inlineStr"/>
-      <c r="J74" s="13" t="inlineStr">
+      <c r="H75" s="15" t="n"/>
+      <c r="I75" s="13" t="inlineStr"/>
+      <c r="J75" s="13" t="inlineStr">
         <is>
           <t>2026-11-13 11:00 AM ET</t>
         </is>
       </c>
-      <c r="K74" s="13" t="inlineStr">
+      <c r="K75" s="13" t="inlineStr">
         <is>
           <t>Heritage Global Partners</t>
         </is>
       </c>
-      <c r="L74" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M74" s="13" t="inlineStr"/>
-      <c r="N74" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O74" s="14" t="inlineStr">
+      <c r="L75" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M75" s="13" t="inlineStr"/>
+      <c r="N75" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O75" s="14" t="inlineStr">
         <is>
           <t>Near-new appliances, resell by unit. Nov 13 10 AM CST.</t>
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="17" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Texas / South Central</t>
         </is>
       </c>
-      <c r="B75" s="17" t="inlineStr">
+      <c r="B76" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C75" s="18" t="n"/>
-      <c r="D75" s="18" t="n"/>
-      <c r="E75" s="18" t="n"/>
-      <c r="F75" s="18" t="n"/>
-      <c r="G75" s="18" t="n"/>
-      <c r="H75" s="19" t="n">
+      <c r="C76" s="18" t="n"/>
+      <c r="D76" s="18" t="n"/>
+      <c r="E76" s="18" t="n"/>
+      <c r="F76" s="18" t="n"/>
+      <c r="G76" s="18" t="n"/>
+      <c r="H76" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I75" s="18" t="n"/>
-      <c r="J75" s="18" t="n"/>
-      <c r="K75" s="18" t="n"/>
-      <c r="L75" s="18" t="n"/>
-      <c r="M75" s="18" t="n"/>
-      <c r="N75" s="18" t="n"/>
-      <c r="O75" s="18" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="11" t="inlineStr">
+      <c r="I76" s="18" t="n"/>
+      <c r="J76" s="18" t="n"/>
+      <c r="K76" s="18" t="n"/>
+      <c r="L76" s="18" t="n"/>
+      <c r="M76" s="18" t="n"/>
+      <c r="N76" s="18" t="n"/>
+      <c r="O76" s="18" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="11" t="inlineStr">
         <is>
           <t>▸ West / Other  (1)</t>
         </is>
       </c>
-      <c r="B76" s="12" t="n"/>
-      <c r="C76" s="12" t="n"/>
-      <c r="D76" s="12" t="n"/>
-      <c r="E76" s="12" t="n"/>
-      <c r="F76" s="12" t="n"/>
-      <c r="G76" s="12" t="n"/>
-      <c r="H76" s="12" t="n"/>
-      <c r="I76" s="12" t="n"/>
-      <c r="J76" s="12" t="n"/>
-      <c r="K76" s="12" t="n"/>
-      <c r="L76" s="12" t="n"/>
-      <c r="M76" s="12" t="n"/>
-      <c r="N76" s="12" t="n"/>
-      <c r="O76" s="12" t="n"/>
-    </row>
-    <row r="77" outlineLevel="1">
-      <c r="A77" s="13" t="inlineStr">
+      <c r="B77" s="12" t="n"/>
+      <c r="C77" s="12" t="n"/>
+      <c r="D77" s="12" t="n"/>
+      <c r="E77" s="12" t="n"/>
+      <c r="F77" s="12" t="n"/>
+      <c r="G77" s="12" t="n"/>
+      <c r="H77" s="12" t="n"/>
+      <c r="I77" s="12" t="n"/>
+      <c r="J77" s="12" t="n"/>
+      <c r="K77" s="12" t="n"/>
+      <c r="L77" s="12" t="n"/>
+      <c r="M77" s="12" t="n"/>
+      <c r="N77" s="12" t="n"/>
+      <c r="O77" s="12" t="n"/>
+    </row>
+    <row r="78" outlineLevel="1">
+      <c r="A78" s="13" t="inlineStr">
         <is>
           <t>West / Other</t>
         </is>
       </c>
-      <c r="B77" s="14" t="inlineStr">
+      <c r="B78" s="14" t="inlineStr">
         <is>
           <t>National salad concept liquidation – full contents of 63 fast-casual restaurants (AZ/TX/OK/NV)</t>
         </is>
       </c>
-      <c r="C77" s="13" t="inlineStr">
+      <c r="C78" s="13" t="inlineStr">
         <is>
           <t>restaurant chain liquidation</t>
         </is>
       </c>
-      <c r="D77" s="13" t="inlineStr">
+      <c r="D78" s="13" t="inlineStr">
         <is>
           <t>Phoenix</t>
         </is>
       </c>
-      <c r="E77" s="13" t="inlineStr">
+      <c r="E78" s="13" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="F77" s="13" t="n">
+      <c r="F78" s="13" t="n">
         <v>2307</v>
       </c>
-      <c r="G77" s="13" t="inlineStr">
+      <c r="G78" s="13" t="inlineStr">
         <is>
           <t>Online auctions, dates TBD</t>
         </is>
       </c>
-      <c r="H77" s="15" t="n"/>
-      <c r="I77" s="13" t="inlineStr">
+      <c r="H78" s="15" t="n"/>
+      <c r="I78" s="13" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="J77" s="13" t="inlineStr"/>
-      <c r="K77" s="13" t="inlineStr">
+      <c r="J78" s="13" t="inlineStr"/>
+      <c r="K78" s="13" t="inlineStr">
         <is>
           <t>RestaurantEquipment.bid (TAGeX)</t>
         </is>
       </c>
-      <c r="L77" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M77" s="13" t="inlineStr"/>
-      <c r="N77" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O77" s="14" t="inlineStr">
+      <c r="L78" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M78" s="13" t="inlineStr"/>
+      <c r="N78" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O78" s="14" t="inlineStr">
         <is>
           <t>Rolling market-by-market auctions, none live yet (Phoenix metro 30 locations, DFW 14, Tucson 6, Houston 5, plus OK/NV). Pickup on site at each restaurant. Pinned at Phoenix.</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="17" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="17" t="inlineStr">
         <is>
           <t>Subtotal — West / Other</t>
         </is>
       </c>
-      <c r="B78" s="17" t="inlineStr">
+      <c r="B79" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C78" s="18" t="n"/>
-      <c r="D78" s="18" t="n"/>
-      <c r="E78" s="18" t="n"/>
-      <c r="F78" s="18" t="n"/>
-      <c r="G78" s="18" t="n"/>
-      <c r="H78" s="19" t="n">
+      <c r="C79" s="18" t="n"/>
+      <c r="D79" s="18" t="n"/>
+      <c r="E79" s="18" t="n"/>
+      <c r="F79" s="18" t="n"/>
+      <c r="G79" s="18" t="n"/>
+      <c r="H79" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I78" s="18" t="n"/>
-      <c r="J78" s="18" t="n"/>
-      <c r="K78" s="18" t="n"/>
-      <c r="L78" s="18" t="n"/>
-      <c r="M78" s="18" t="n"/>
-      <c r="N78" s="18" t="n"/>
-      <c r="O78" s="18" t="n"/>
+      <c r="I79" s="18" t="n"/>
+      <c r="J79" s="18" t="n"/>
+      <c r="K79" s="18" t="n"/>
+      <c r="L79" s="18" t="n"/>
+      <c r="M79" s="18" t="n"/>
+      <c r="N79" s="18" t="n"/>
+      <c r="O79" s="18" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O78"/>
+  <autoFilter ref="A1:O79"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N5" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId25"/>
@@ -22706,16 +22701,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N61" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N62" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N66" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N69" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N64" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N67" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N71" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N74" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N77" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N72" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N75" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N78" r:id="rId54"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22727,7 +22723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -22827,54 +22823,52 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>Greater Boston / South Shore (&lt;50mi)</t>
+          <t>Western PA / Ohio Valley</t>
         </is>
       </c>
       <c r="B2" s="14" t="inlineStr">
         <is>
-          <t>Wolf Gourmet Coffee Maker WGCM100S (stainless)</t>
+          <t>Allshouse Appliance Store &amp; Warehouse Dispersal (mostly whole units, racking, forklift)</t>
         </is>
       </c>
       <c r="C2" s="13" t="inlineStr">
         <is>
-          <t>countertop</t>
+          <t>auction / dispersal</t>
         </is>
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>Malden</t>
+          <t>New Castle</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F2" s="13" t="n">
-        <v>25</v>
+        <v>499</v>
       </c>
       <c r="G2" s="13" t="inlineStr">
         <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="H2" s="15" t="n">
-        <v>150</v>
-      </c>
-      <c r="I2" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="J2" s="13" t="inlineStr"/>
+          <t>Auction – 5% BP (waived for cash)</t>
+        </is>
+      </c>
+      <c r="H2" s="15" t="n"/>
+      <c r="I2" s="13" t="inlineStr"/>
+      <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 04:00 PM ET</t>
+        </is>
+      </c>
       <c r="K2" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>Duke Whiting Auctions</t>
         </is>
       </c>
       <c r="L2" s="13" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>EXPIRED (2026-10-19 04:00 PM ET)</t>
         </is>
       </c>
       <c r="M2" s="13" t="inlineStr"/>
@@ -22885,7 +22879,7 @@
       </c>
       <c r="O2" s="14" t="inlineStr">
         <is>
-          <t>Condition not stated. | Removed 2026-10-18: Craigslist posting deleted (HTTP 410).</t>
+          <t>Live auction Mon Oct 19 4 PM, 3457 Wilmington Rd. Few bulk parts. [Live auction held Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -22897,17 +22891,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>wolf gas cooktop</t>
+          <t>Wolf Gourmet Coffee Maker WGCM100S (stainless)</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>range/oven/rangetop</t>
+          <t>countertop</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>Winchester</t>
+          <t>Malden</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
@@ -22916,19 +22910,19 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
-          <t>$275</t>
+          <t>$150</t>
         </is>
       </c>
       <c r="H3" s="15" t="n">
-        <v>275</v>
+        <v>150</v>
       </c>
       <c r="I3" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="J3" s="13" t="inlineStr"/>
@@ -22942,11 +22936,7 @@
           <t>REMOVED</t>
         </is>
       </c>
-      <c r="M3" s="21" t="inlineStr">
-        <is>
-          <t>FLIP</t>
-        </is>
-      </c>
+      <c r="M3" s="13" t="inlineStr"/>
       <c r="N3" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -22954,19 +22944,19 @@
       </c>
       <c r="O3" s="14" t="inlineStr">
         <is>
-          <t>Condition: used. FLIP: 36" gas cooktop $275, missing pads; rough resale $600-900 | Removed 2026-10-18: Craigslist posting deleted (HTTP 410).</t>
+          <t>Condition not stated. | Removed 2026-10-18: Craigslist posting deleted (HTTP 410).</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="13" t="inlineStr">
         <is>
-          <t>Unknown location</t>
+          <t>Greater Boston / South Shore (&lt;50mi)</t>
         </is>
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>Wolf 36” Single Electric Wall Built-In Oven SO36U/S - Tested Work</t>
+          <t>wolf gas cooktop</t>
         </is>
       </c>
       <c r="C4" s="13" t="inlineStr">
@@ -22976,37 +22966,39 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Winchester</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="13" t="n"/>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="n">
+        <v>29</v>
+      </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
-          <t>$99</t>
+          <t>$275</t>
         </is>
       </c>
       <c r="H4" s="15" t="n">
-        <v>99</v>
-      </c>
-      <c r="I4" s="13" t="inlineStr"/>
-      <c r="J4" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-18 02:19 PM ET</t>
-        </is>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr"/>
       <c r="K4" s="13" t="inlineStr">
         <is>
-          <t>eBay (pickup only, over 60 mi)</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L4" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-18 02:19 PM ET)</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="M4" s="21" t="inlineStr">
@@ -23021,19 +23013,19 @@
       </c>
       <c r="O4" s="14" t="inlineStr">
         <is>
-          <t>Condition: Pre-Owned. FLIP: SO36U/S tested, auction $99/0 bids, pickup only; rough resale $600-1k (eBay card shows no city; pickup distance in source.) Ends Oct 18 ~2:19 PM per eBay card (time zone uncertain; could be earlier). [auto-removed 2026-10-18: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed]</t>
+          <t>Condition: used. FLIP: 36" gas cooktop $275, missing pads; rough resale $600-900 | Removed 2026-10-18: Craigslist posting deleted (HTTP 410).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>Unknown location</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>Wolf Oven Six Burner Combo</t>
+          <t>Wolf 36” Single Electric Wall Built-In Oven SO36U/S - Tested Work</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
@@ -23043,42 +23035,44 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Anderson</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="n">
-        <v>785</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="n"/>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>$3 current bid + BP</t>
+          <t>$99</t>
         </is>
       </c>
       <c r="H5" s="15" t="n">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="I5" s="13" t="inlineStr"/>
       <c r="J5" s="13" t="inlineStr">
         <is>
-          <t>2026-10-18 08:54 PM ET</t>
+          <t>2026-10-18 02:19 PM ET</t>
         </is>
       </c>
       <c r="K5" s="13" t="inlineStr">
         <is>
-          <t>HiBid</t>
+          <t>eBay (pickup only, over 60 mi)</t>
         </is>
       </c>
       <c r="L5" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-18 08:54 PM ET)</t>
-        </is>
-      </c>
-      <c r="M5" s="13" t="inlineStr"/>
+          <t>EXPIRED (2026-10-18 02:19 PM ET)</t>
+        </is>
+      </c>
+      <c r="M5" s="21" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
       <c r="N5" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -23086,61 +23080,61 @@
       </c>
       <c r="O5" s="14" t="inlineStr">
         <is>
-          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf) HiBid lot closed/sold ~$37.50 on 2026-10-18. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed]</t>
+          <t>Condition: Pre-Owned. FLIP: SO36U/S tested, auction $99/0 bids, pickup only; rough resale $600-1k (eBay card shows no city; pickup distance in source.) Ends Oct 18 ~2:19 PM per eBay card (time zone uncertain; could be earlier). [auto-removed 2026-10-18: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Louisville)</t>
+          <t>Wolf Oven Six Burner Combo</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>auction catalog</t>
+          <t>range/oven/rangetop</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>Anderson</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>KY</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>832</v>
+        <v>785</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>$0–1 openers + 15% BP + $1/lot</t>
+          <t>$3 current bid + BP</t>
         </is>
       </c>
       <c r="H6" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I6" s="13" t="inlineStr"/>
       <c r="J6" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 02:00 PM ET</t>
+          <t>2026-10-18 08:54 PM ET</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Auctionfuel)</t>
+          <t>HiBid</t>
         </is>
       </c>
       <c r="L6" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 02:00 PM ET)</t>
+          <t>EXPIRED (2026-10-18 08:54 PM ET)</t>
         </is>
       </c>
       <c r="M6" s="13" t="inlineStr"/>
@@ -23151,59 +23145,61 @@
       </c>
       <c r="O6" s="14" t="inlineStr">
         <is>
-          <t>Lots close from Oct 19 2 PM ET. [HiBid catalog closed 2 PM ET Oct 19.] [auto-removed 2026-10-19: closing date passed]</t>
+          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf) HiBid lot closed/sold ~$37.50 on 2026-10-18. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Maine / VT / Northern NH</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>Oola Bowls secured-party sale – restaurant equipment bought new 2024-25 (Electro Freeze, Scotsman, Atosa)</t>
+          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Louisville)</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>auction catalog</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Scarborough</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>ME</t>
+          <t>KY</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>104</v>
+        <v>832</v>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>Online auction (freezers $80–150 when seen)</t>
-        </is>
-      </c>
-      <c r="H7" s="15" t="n"/>
+          <t>$0–1 openers + 15% BP + $1/lot</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="I7" s="13" t="inlineStr"/>
       <c r="J7" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00 PM ET</t>
+          <t>2026-10-19 02:00 PM ET</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>Keenan Auction / Proxibid</t>
+          <t>HiBid (Auctionfuel)</t>
         </is>
       </c>
       <c r="L7" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 01:00 PM ET)</t>
+          <t>EXPIRED (2026-10-19 02:00 PM ET)</t>
         </is>
       </c>
       <c r="M7" s="13" t="inlineStr"/>
@@ -23214,59 +23210,59 @@
       </c>
       <c r="O7" s="14" t="inlineStr">
         <is>
-          <t>Pickup Oct 21 only. [Lots began closing 1 PM ET Oct 19; ended.] [auto-removed 2026-10-19: closing date passed]</t>
+          <t>Lots close from Oct 19 2 PM ET. [HiBid catalog closed 2 PM ET Oct 19.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>Greater Boston / South Shore (&lt;50mi)</t>
+          <t>Maine / VT / Northern NH</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>Closed Best Buy Outlet – pallet racking, Big Joe order pickers, appliance dollies, carts, cages</t>
+          <t>Oola Bowls secured-party sale – restaurant equipment bought new 2024-25 (Electro Freeze, Scotsman, Atosa)</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>store closing fixtures</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>Brockton</t>
+          <t>Scarborough</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>11</v>
+        <v>104</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
-          <t>Racking $40/upright, $80/level; pickers $1,000 OBO</t>
+          <t>Online auction (freezers $80–150 when seen)</t>
         </is>
       </c>
       <c r="H8" s="15" t="n"/>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="J8" s="13" t="inlineStr"/>
+      <c r="I8" s="13" t="inlineStr"/>
+      <c r="J8" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 01:00 PM ET</t>
+        </is>
+      </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>Keenan Auction / Proxibid</t>
         </is>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>EXPIRED (2026-10-19 01:00 PM ET)</t>
         </is>
       </c>
       <c r="M8" s="13" t="inlineStr"/>
@@ -23277,7 +23273,7 @@
       </c>
       <c r="O8" s="14" t="inlineStr">
         <is>
-          <t>200 Westgate Dr. Fixtures/equipment only, no merchandise. On site daily. CL deleted by author (HTTP 410) as of 2026-10-19 midday recheck.</t>
+          <t>Pickup Oct 21 only. [Lots began closing 1 PM ET Oct 19; ended.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23289,51 +23285,47 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>Like-new restaurant – steam tables, Coldline, Cleveland cook-and-hold, fryers, True freezers</t>
+          <t>Milwaukee / Walmart / hardware store mega auction pt 3</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>Staten Island</t>
+          <t>Mount Holly</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>203</v>
+        <v>254</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>HiBid online auction</t>
         </is>
       </c>
       <c r="H9" s="15" t="n"/>
-      <c r="I9" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+      <c r="I9" s="13" t="inlineStr"/>
       <c r="J9" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00 PM ET</t>
+          <t>2026-10-19 06:00 PM ET</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>HiBid</t>
         </is>
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 01:00 PM ET)</t>
+          <t>EXPIRED (2026-10-19 06:00 PM ET)</t>
         </is>
       </c>
       <c r="M9" s="13" t="inlineStr"/>
@@ -23344,12 +23336,209 @@
       </c>
       <c r="O9" s="14" t="inlineStr">
         <is>
-          <t>"Short notice" auction Mon Oct 19 1 PM. [auto-removed 2026-10-19: closing date passed]</t>
+          <t>Close Oct 18 or 19 6 PM (later used). [auto-removed 2026-10-19: closing date passed]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
+          <t>Greater Boston / South Shore (&lt;50mi)</t>
+        </is>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>Closed Best Buy Outlet – pallet racking, Big Joe order pickers, appliance dollies, carts, cages</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>store closing fixtures</t>
+        </is>
+      </c>
+      <c r="D10" s="13" t="inlineStr">
+        <is>
+          <t>Brockton</t>
+        </is>
+      </c>
+      <c r="E10" s="13" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>11</v>
+      </c>
+      <c r="G10" s="13" t="inlineStr">
+        <is>
+          <t>Racking $40/upright, $80/level; pickers $1,000 OBO</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="n"/>
+      <c r="I10" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="J10" s="13" t="inlineStr"/>
+      <c r="K10" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L10" s="13" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="M10" s="13" t="inlineStr"/>
+      <c r="N10" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O10" s="14" t="inlineStr">
+        <is>
+          <t>200 Westgate Dr. Fixtures/equipment only, no merchandise. On site daily. CL deleted by author (HTTP 410) as of 2026-10-19 midday recheck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>Like-new restaurant – steam tables, Coldline, Cleveland cook-and-hold, fryers, True freezers</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>auction</t>
+        </is>
+      </c>
+      <c r="D11" s="13" t="inlineStr">
+        <is>
+          <t>Staten Island</t>
+        </is>
+      </c>
+      <c r="E11" s="13" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F11" s="13" t="n">
+        <v>203</v>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>Live + webcast, 18% BP + 3%</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="n"/>
+      <c r="I11" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 01:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K11" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>EXPIRED (2026-10-19 01:00 PM ET)</t>
+        </is>
+      </c>
+      <c r="M11" s="13" t="inlineStr"/>
+      <c r="N11" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O11" s="14" t="inlineStr">
+        <is>
+          <t>"Short notice" auction Mon Oct 19 1 PM. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>High-end deli (contents not described)</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>restaurant closing</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Manalapan Township</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>223</v>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>Live + webcast, 18% BP + 3%</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="n"/>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 04:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L12" s="13" t="inlineStr">
+        <is>
+          <t>EXPIRED (2026-10-19 04:00 PM ET)</t>
+        </is>
+      </c>
+      <c r="M12" s="13" t="inlineStr"/>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O12" s="14" t="inlineStr">
+        <is>
+          <t>Mon Oct 19 4 PM. No item description on page. [HiBid shows Bidding Closed, Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O9"/>
+  <autoFilter ref="A1:O12"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -23359,6 +23548,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId11"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lot_recon.xlsx
+++ b/lot_recon.xlsx
@@ -16,12 +16,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Removed" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Appliance Parts'!$A$1:$O$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Appliance Parts'!$A$1:$O$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wolf New'!$A$1:$O$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wolf Used'!$A$1:$O$189</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Wolf Unclear'!$A$1:$O$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$79</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Removed'!$A$1:$O$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Removed'!$A$1:$O$14</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -577,7 +577,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Last updated: 2026-10-19 18:06 ET</t>
+          <t>Last updated: 2026-10-20 08:03 ET</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Active listings: 293 · Removed: 11</t>
+          <t>Active listings: 293 · Removed: 13</t>
         </is>
       </c>
     </row>
@@ -641,13 +641,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>159696</v>
+        <v>159646</v>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F8" t="n">
         <v>34</v>
@@ -682,7 +682,7 @@
         <v>608011.6</v>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -698,7 +698,7 @@
         <v>137840</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -708,13 +708,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13">
@@ -727,7 +727,7 @@
         <v>293</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>980432.58</v>
+        <v>980382.58</v>
       </c>
     </row>
     <row r="15">
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -1004,7 +1004,7 @@
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H23" s="6" t="n">
         <v>64740</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
@@ -1103,14 +1103,14 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" s="6" t="n">
         <v>175</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>487</t>
+          <t>478–487</t>
         </is>
       </c>
     </row>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -1136,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="6" t="n">
         <v>2250</v>
@@ -1187,10 +1187,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C29" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="6" t="n">
-        <v>36055</v>
+        <v>36005</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2164,7 +2164,7 @@
     <row r="20">
       <c r="A20" s="11" t="inlineStr">
         <is>
-          <t>▸ Southeast  (4)</t>
+          <t>▸ Southeast  (3)</t>
         </is>
       </c>
       <c r="B20" s="12" t="n"/>
@@ -2314,53 +2314,47 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>Misc. appliance parts pallet (parts only)</t>
+          <t>Established appliance sales / parts / service business</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>auction pallet</t>
+          <t>business sale</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>Dalton</t>
+          <t>Oakland Park</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>FL</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>917</v>
+        <v>1222</v>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>$50 high bid + 15% BP</t>
-        </is>
-      </c>
-      <c r="H23" s="15" t="n">
-        <v>50</v>
-      </c>
+          <t>Price n/a</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="n"/>
       <c r="I23" s="13" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
-        </is>
-      </c>
-      <c r="J23" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-19 09:18 PM ET</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="inlineStr"/>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>HiBid</t>
-        </is>
-      </c>
-      <c r="L23" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L23" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M23" s="13" t="inlineStr"/>
@@ -2371,120 +2365,122 @@
       </c>
       <c r="O23" s="14" t="inlineStr">
         <is>
-          <t>Integrity Auction House. Internet bidding closes Mon Oct 19 9:18 PM ET. $50 high bid (1 bid) as of 2026-10-18.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" outlineLevel="1">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>Southeast</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>Established appliance sales / parts / service business</t>
-        </is>
-      </c>
-      <c r="C24" s="13" t="inlineStr">
-        <is>
-          <t>business sale</t>
-        </is>
-      </c>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>Oakland Park</t>
-        </is>
-      </c>
-      <c r="E24" s="13" t="inlineStr">
-        <is>
-          <t>FL</t>
-        </is>
-      </c>
-      <c r="F24" s="13" t="n">
-        <v>1222</v>
-      </c>
-      <c r="G24" s="13" t="inlineStr">
-        <is>
-          <t>Price n/a</t>
-        </is>
-      </c>
-      <c r="H24" s="15" t="n"/>
-      <c r="I24" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="J24" s="13" t="inlineStr"/>
-      <c r="K24" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L24" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M24" s="13" t="inlineStr"/>
-      <c r="N24" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O24" s="14" t="inlineStr">
-        <is>
           <t>Whole business sale (Fort Lauderdale area).</t>
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Southeast</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="inlineStr">
+        <is>
+          <t>3 item(s)</t>
+        </is>
+      </c>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="18" t="n"/>
+      <c r="G24" s="18" t="n"/>
+      <c r="H24" s="19" t="n">
+        <v>36000</v>
+      </c>
+      <c r="I24" s="18" t="n"/>
+      <c r="J24" s="18" t="n"/>
+      <c r="K24" s="18" t="n"/>
+      <c r="L24" s="18" t="n"/>
+      <c r="M24" s="18" t="n"/>
+      <c r="N24" s="18" t="n"/>
+      <c r="O24" s="18" t="n"/>
+    </row>
     <row r="25">
-      <c r="A25" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Southeast</t>
-        </is>
-      </c>
-      <c r="B25" s="17" t="inlineStr">
-        <is>
-          <t>4 item(s)</t>
-        </is>
-      </c>
-      <c r="C25" s="18" t="n"/>
-      <c r="D25" s="18" t="n"/>
-      <c r="E25" s="18" t="n"/>
-      <c r="F25" s="18" t="n"/>
-      <c r="G25" s="18" t="n"/>
-      <c r="H25" s="19" t="n">
-        <v>36050</v>
-      </c>
-      <c r="I25" s="18" t="n"/>
-      <c r="J25" s="18" t="n"/>
-      <c r="K25" s="18" t="n"/>
-      <c r="L25" s="18" t="n"/>
-      <c r="M25" s="18" t="n"/>
-      <c r="N25" s="18" t="n"/>
-      <c r="O25" s="18" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="A25" s="11" t="inlineStr">
         <is>
           <t>▸ Midwest  (2)</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="12" t="n"/>
-      <c r="G26" s="12" t="n"/>
-      <c r="H26" s="12" t="n"/>
-      <c r="I26" s="12" t="n"/>
-      <c r="J26" s="12" t="n"/>
-      <c r="K26" s="12" t="n"/>
-      <c r="L26" s="12" t="n"/>
-      <c r="M26" s="12" t="n"/>
-      <c r="N26" s="12" t="n"/>
-      <c r="O26" s="12" t="n"/>
+      <c r="B25" s="12" t="n"/>
+      <c r="C25" s="12" t="n"/>
+      <c r="D25" s="12" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="12" t="n"/>
+      <c r="G25" s="12" t="n"/>
+      <c r="H25" s="12" t="n"/>
+      <c r="I25" s="12" t="n"/>
+      <c r="J25" s="12" t="n"/>
+      <c r="K25" s="12" t="n"/>
+      <c r="L25" s="12" t="n"/>
+      <c r="M25" s="12" t="n"/>
+      <c r="N25" s="12" t="n"/>
+      <c r="O25" s="12" t="n"/>
+    </row>
+    <row r="26" outlineLevel="1">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Fort Wayne)</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>auction catalog</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Fort Wayne</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>743</v>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>$0–1 openers + 15% BP + $1/lot</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="13" t="inlineStr"/>
+      <c r="J26" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-20 02:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (Auctionfuel)</t>
+        </is>
+      </c>
+      <c r="L26" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M26" s="13" t="inlineStr"/>
+      <c r="N26" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O26" s="14" t="inlineStr">
+        <is>
+          <t>Lots close from Oct 20 2 PM ET.</t>
+        </is>
+      </c>
     </row>
     <row r="27" outlineLevel="1">
       <c r="A27" s="13" t="inlineStr">
@@ -2494,7 +2490,7 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Fort Wayne)</t>
+          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Indianapolis)</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
@@ -2504,7 +2500,7 @@
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>Fort Wayne</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
@@ -2513,7 +2509,7 @@
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>743</v>
+        <v>816</v>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
@@ -2526,7 +2522,7 @@
       <c r="I27" s="13" t="inlineStr"/>
       <c r="J27" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 02:00 PM ET</t>
+          <t>2026-10-21 02:00 PM ET</t>
         </is>
       </c>
       <c r="K27" s="13" t="inlineStr">
@@ -2547,122 +2543,120 @@
       </c>
       <c r="O27" s="14" t="inlineStr">
         <is>
-          <t>Lots close from Oct 20 2 PM ET.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" outlineLevel="1">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>Midwest</t>
-        </is>
-      </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Indianapolis)</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>auction catalog</t>
-        </is>
-      </c>
-      <c r="D28" s="13" t="inlineStr">
-        <is>
-          <t>Indianapolis</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="F28" s="13" t="n">
-        <v>816</v>
-      </c>
-      <c r="G28" s="13" t="inlineStr">
-        <is>
-          <t>$0–1 openers + 15% BP + $1/lot</t>
-        </is>
-      </c>
-      <c r="H28" s="15" t="n">
+          <t>Lots close in sequence from Oct 21 2 PM ET.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Midwest</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>2 item(s)</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="18" t="n"/>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="18" t="n"/>
+      <c r="G28" s="18" t="n"/>
+      <c r="H28" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I28" s="13" t="inlineStr"/>
-      <c r="J28" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 02:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K28" s="13" t="inlineStr">
-        <is>
-          <t>HiBid (Auctionfuel)</t>
-        </is>
-      </c>
-      <c r="L28" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M28" s="13" t="inlineStr"/>
-      <c r="N28" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O28" s="14" t="inlineStr">
-        <is>
-          <t>Lots close in sequence from Oct 21 2 PM ET.</t>
-        </is>
-      </c>
+      <c r="I28" s="18" t="n"/>
+      <c r="J28" s="18" t="n"/>
+      <c r="K28" s="18" t="n"/>
+      <c r="L28" s="18" t="n"/>
+      <c r="M28" s="18" t="n"/>
+      <c r="N28" s="18" t="n"/>
+      <c r="O28" s="18" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Midwest</t>
-        </is>
-      </c>
-      <c r="B29" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C29" s="18" t="n"/>
-      <c r="D29" s="18" t="n"/>
-      <c r="E29" s="18" t="n"/>
-      <c r="F29" s="18" t="n"/>
-      <c r="G29" s="18" t="n"/>
-      <c r="H29" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="18" t="n"/>
-      <c r="J29" s="18" t="n"/>
-      <c r="K29" s="18" t="n"/>
-      <c r="L29" s="18" t="n"/>
-      <c r="M29" s="18" t="n"/>
-      <c r="N29" s="18" t="n"/>
-      <c r="O29" s="18" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>▸ Texas / South Central  (2)</t>
         </is>
       </c>
-      <c r="B30" s="12" t="n"/>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="12" t="n"/>
-      <c r="E30" s="12" t="n"/>
-      <c r="F30" s="12" t="n"/>
-      <c r="G30" s="12" t="n"/>
-      <c r="H30" s="12" t="n"/>
-      <c r="I30" s="12" t="n"/>
-      <c r="J30" s="12" t="n"/>
-      <c r="K30" s="12" t="n"/>
-      <c r="L30" s="12" t="n"/>
-      <c r="M30" s="12" t="n"/>
-      <c r="N30" s="12" t="n"/>
-      <c r="O30" s="12" t="n"/>
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="12" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="12" t="n"/>
+      <c r="M29" s="12" t="n"/>
+      <c r="N29" s="12" t="n"/>
+      <c r="O29" s="12" t="n"/>
+    </row>
+    <row r="30" outlineLevel="1">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>Texas / South Central</t>
+        </is>
+      </c>
+      <c r="B30" s="14" t="inlineStr">
+        <is>
+          <t>Wholesale Hisense appliance parts – stove &amp; refrigerator parts</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>bulk lot</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>Owasso</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="n">
+        <v>1395</v>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>Wholesale (price at sale)</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="n"/>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J30" s="13" t="inlineStr"/>
+      <c r="K30" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L30" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M30" s="13" t="inlineStr"/>
+      <c r="N30" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O30" s="14" t="inlineStr">
+        <is>
+          <t>Updated 2026-10-12. Seller says LOCAL BUYERS ONLY, out-of-area excluded, cash pickup.</t>
+        </is>
+      </c>
     </row>
     <row r="31" outlineLevel="1">
       <c r="A31" s="13" t="inlineStr">
@@ -2672,7 +2666,7 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>Wholesale Hisense appliance parts – stove &amp; refrigerator parts</t>
+          <t>Huge bulk lot appliance parts – ~2 trailer loads, GE/Whirlpool/Maytag</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
@@ -2682,32 +2676,30 @@
       </c>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>Owasso</t>
+          <t>Abilene</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>1395</v>
+        <v>1714</v>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
-          <t>Wholesale (price at sale)</t>
-        </is>
-      </c>
-      <c r="H31" s="15" t="n"/>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
+          <t>$5,001</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="n">
+        <v>5001</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr"/>
       <c r="J31" s="13" t="inlineStr"/>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>Geebo</t>
         </is>
       </c>
       <c r="L31" s="13" t="inlineStr">
@@ -2723,118 +2715,118 @@
       </c>
       <c r="O31" s="14" t="inlineStr">
         <is>
-          <t>Updated 2026-10-12. Seller says LOCAL BUYERS ONLY, out-of-area excluded, cash pickup.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" outlineLevel="1">
-      <c r="A32" s="13" t="inlineStr">
-        <is>
-          <t>Texas / South Central</t>
-        </is>
-      </c>
-      <c r="B32" s="14" t="inlineStr">
-        <is>
-          <t>Huge bulk lot appliance parts – ~2 trailer loads, GE/Whirlpool/Maytag</t>
-        </is>
-      </c>
-      <c r="C32" s="13" t="inlineStr">
-        <is>
-          <t>bulk lot</t>
-        </is>
-      </c>
-      <c r="D32" s="13" t="inlineStr">
-        <is>
-          <t>Abilene</t>
-        </is>
-      </c>
-      <c r="E32" s="13" t="inlineStr">
-        <is>
-          <t>TX</t>
-        </is>
-      </c>
-      <c r="F32" s="13" t="n">
-        <v>1714</v>
-      </c>
-      <c r="G32" s="13" t="inlineStr">
-        <is>
-          <t>$5,001</t>
-        </is>
-      </c>
-      <c r="H32" s="15" t="n">
+          <t>Post date unclear (may be older). Pickup only. User already messaged seller.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Texas / South Central</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
+        <is>
+          <t>2 item(s)</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="18" t="n"/>
+      <c r="E32" s="18" t="n"/>
+      <c r="F32" s="18" t="n"/>
+      <c r="G32" s="18" t="n"/>
+      <c r="H32" s="19" t="n">
         <v>5001</v>
       </c>
-      <c r="I32" s="13" t="inlineStr"/>
-      <c r="J32" s="13" t="inlineStr"/>
-      <c r="K32" s="13" t="inlineStr">
-        <is>
-          <t>Geebo</t>
-        </is>
-      </c>
-      <c r="L32" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M32" s="13" t="inlineStr"/>
-      <c r="N32" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O32" s="14" t="inlineStr">
-        <is>
-          <t>Post date unclear (may be older). Pickup only. User already messaged seller.</t>
-        </is>
-      </c>
+      <c r="I32" s="18" t="n"/>
+      <c r="J32" s="18" t="n"/>
+      <c r="K32" s="18" t="n"/>
+      <c r="L32" s="18" t="n"/>
+      <c r="M32" s="18" t="n"/>
+      <c r="N32" s="18" t="n"/>
+      <c r="O32" s="18" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Texas / South Central</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="n"/>
-      <c r="D33" s="18" t="n"/>
-      <c r="E33" s="18" t="n"/>
-      <c r="F33" s="18" t="n"/>
-      <c r="G33" s="18" t="n"/>
-      <c r="H33" s="19" t="n">
-        <v>5001</v>
-      </c>
-      <c r="I33" s="18" t="n"/>
-      <c r="J33" s="18" t="n"/>
-      <c r="K33" s="18" t="n"/>
-      <c r="L33" s="18" t="n"/>
-      <c r="M33" s="18" t="n"/>
-      <c r="N33" s="18" t="n"/>
-      <c r="O33" s="18" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="A33" s="11" t="inlineStr">
         <is>
           <t>▸ California  (2)</t>
         </is>
       </c>
-      <c r="B34" s="12" t="n"/>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="12" t="n"/>
-      <c r="E34" s="12" t="n"/>
-      <c r="F34" s="12" t="n"/>
-      <c r="G34" s="12" t="n"/>
-      <c r="H34" s="12" t="n"/>
-      <c r="I34" s="12" t="n"/>
-      <c r="J34" s="12" t="n"/>
-      <c r="K34" s="12" t="n"/>
-      <c r="L34" s="12" t="n"/>
-      <c r="M34" s="12" t="n"/>
-      <c r="N34" s="12" t="n"/>
-      <c r="O34" s="12" t="n"/>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="12" t="n"/>
+      <c r="H33" s="12" t="n"/>
+      <c r="I33" s="12" t="n"/>
+      <c r="J33" s="12" t="n"/>
+      <c r="K33" s="12" t="n"/>
+      <c r="L33" s="12" t="n"/>
+      <c r="M33" s="12" t="n"/>
+      <c r="N33" s="12" t="n"/>
+      <c r="O33" s="12" t="n"/>
+    </row>
+    <row r="34" outlineLevel="1">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>Appliance repair company for sale (incl. parts inventory)</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>business sale</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>Escondido</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>2575</v>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>$40,000</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr"/>
+      <c r="J34" s="13" t="inlineStr"/>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L34" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M34" s="13" t="inlineStr"/>
+      <c r="N34" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O34" s="14" t="inlineStr">
+        <is>
+          <t>Whole business sale.</t>
+        </is>
+      </c>
     </row>
     <row r="35" outlineLevel="1">
       <c r="A35" s="13" t="inlineStr">
@@ -2844,17 +2836,17 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>Appliance repair company for sale (incl. parts inventory)</t>
+          <t>Coin-op Whirlpool washer &amp; dryer parts (late 80s–mid 90s) – OEM parts, 40+ coin boxes, consoles, 12 transmissions</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>business sale</t>
+          <t>bulk lot</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>Escondido</t>
+          <t>Chico</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
@@ -2863,17 +2855,21 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>2575</v>
+        <v>2629</v>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
-          <t>$40,000</t>
+          <t>$1,000</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
-        <v>40000</v>
-      </c>
-      <c r="I35" s="13" t="inlineStr"/>
+        <v>1000</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
       <c r="J35" s="13" t="inlineStr"/>
       <c r="K35" s="13" t="inlineStr">
         <is>
@@ -2893,122 +2889,120 @@
       </c>
       <c r="O35" s="14" t="inlineStr">
         <is>
-          <t>Whole business sale.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" outlineLevel="1">
-      <c r="A36" s="13" t="inlineStr">
-        <is>
-          <t>California</t>
-        </is>
-      </c>
-      <c r="B36" s="14" t="inlineStr">
-        <is>
-          <t>Coin-op Whirlpool washer &amp; dryer parts (late 80s–mid 90s) – OEM parts, 40+ coin boxes, consoles, 12 transmissions</t>
-        </is>
-      </c>
-      <c r="C36" s="13" t="inlineStr">
+          <t>Retired laundry-route owner (35 yrs). Calls only, no shipping, pickup in Chico. No motors or pumps. Niche older coin-op parts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — California</t>
+        </is>
+      </c>
+      <c r="B36" s="17" t="inlineStr">
+        <is>
+          <t>2 item(s)</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="n"/>
+      <c r="D36" s="18" t="n"/>
+      <c r="E36" s="18" t="n"/>
+      <c r="F36" s="18" t="n"/>
+      <c r="G36" s="18" t="n"/>
+      <c r="H36" s="19" t="n">
+        <v>41000</v>
+      </c>
+      <c r="I36" s="18" t="n"/>
+      <c r="J36" s="18" t="n"/>
+      <c r="K36" s="18" t="n"/>
+      <c r="L36" s="18" t="n"/>
+      <c r="M36" s="18" t="n"/>
+      <c r="N36" s="18" t="n"/>
+      <c r="O36" s="18" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>▸ West / Other  (2)</t>
+        </is>
+      </c>
+      <c r="B37" s="12" t="n"/>
+      <c r="C37" s="12" t="n"/>
+      <c r="D37" s="12" t="n"/>
+      <c r="E37" s="12" t="n"/>
+      <c r="F37" s="12" t="n"/>
+      <c r="G37" s="12" t="n"/>
+      <c r="H37" s="12" t="n"/>
+      <c r="I37" s="12" t="n"/>
+      <c r="J37" s="12" t="n"/>
+      <c r="K37" s="12" t="n"/>
+      <c r="L37" s="12" t="n"/>
+      <c r="M37" s="12" t="n"/>
+      <c r="N37" s="12" t="n"/>
+      <c r="O37" s="12" t="n"/>
+    </row>
+    <row r="38" outlineLevel="1">
+      <c r="A38" s="13" t="inlineStr">
+        <is>
+          <t>West / Other</t>
+        </is>
+      </c>
+      <c r="B38" s="14" t="inlineStr">
+        <is>
+          <t>Storage locker filled with appliance parts – washer/dryer parts, heating elements, cords, rollers, belts, tools</t>
+        </is>
+      </c>
+      <c r="C38" s="13" t="inlineStr">
         <is>
           <t>bulk lot</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
-        <is>
-          <t>Chico</t>
-        </is>
-      </c>
-      <c r="E36" s="13" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="F36" s="13" t="n">
-        <v>2629</v>
-      </c>
-      <c r="G36" s="13" t="inlineStr">
-        <is>
-          <t>$1,000</t>
-        </is>
-      </c>
-      <c r="H36" s="15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I36" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="J36" s="13" t="inlineStr"/>
-      <c r="K36" s="13" t="inlineStr">
+      <c r="D38" s="13" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="E38" s="13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="F38" s="13" t="n">
+        <v>2307</v>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>Message for pricing</t>
+        </is>
+      </c>
+      <c r="H38" s="15" t="n"/>
+      <c r="I38" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J38" s="13" t="inlineStr"/>
+      <c r="K38" s="13" t="inlineStr">
         <is>
           <t>Craigslist</t>
         </is>
       </c>
-      <c r="L36" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M36" s="13" t="inlineStr"/>
-      <c r="N36" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O36" s="14" t="inlineStr">
-        <is>
-          <t>Retired laundry-route owner (35 yrs). Calls only, no shipping, pickup in Chico. No motors or pumps. Niche older coin-op parts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — California</t>
-        </is>
-      </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="n"/>
-      <c r="D37" s="18" t="n"/>
-      <c r="E37" s="18" t="n"/>
-      <c r="F37" s="18" t="n"/>
-      <c r="G37" s="18" t="n"/>
-      <c r="H37" s="19" t="n">
-        <v>41000</v>
-      </c>
-      <c r="I37" s="18" t="n"/>
-      <c r="J37" s="18" t="n"/>
-      <c r="K37" s="18" t="n"/>
-      <c r="L37" s="18" t="n"/>
-      <c r="M37" s="18" t="n"/>
-      <c r="N37" s="18" t="n"/>
-      <c r="O37" s="18" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>▸ West / Other  (2)</t>
-        </is>
-      </c>
-      <c r="B38" s="12" t="n"/>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="12" t="n"/>
-      <c r="E38" s="12" t="n"/>
-      <c r="F38" s="12" t="n"/>
-      <c r="G38" s="12" t="n"/>
-      <c r="H38" s="12" t="n"/>
-      <c r="I38" s="12" t="n"/>
-      <c r="J38" s="12" t="n"/>
-      <c r="K38" s="12" t="n"/>
-      <c r="L38" s="12" t="n"/>
-      <c r="M38" s="12" t="n"/>
-      <c r="N38" s="12" t="n"/>
-      <c r="O38" s="12" t="n"/>
+      <c r="L38" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M38" s="13" t="inlineStr"/>
+      <c r="N38" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O38" s="14" t="inlineStr">
+        <is>
+          <t>Seller is getting out of the appliance business; selling the whole locker (North Phoenix, Deer Valley Rd near 19th Ave). Delivery available per post. Separate from the Phoenix parts-store closing ad.</t>
+        </is>
+      </c>
     </row>
     <row r="39" outlineLevel="1">
       <c r="A39" s="13" t="inlineStr">
@@ -3018,17 +3012,17 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>Storage locker filled with appliance parts – washer/dryer parts, heating elements, cords, rollers, belts, tools</t>
+          <t>Appliance repair &amp; sales business for sale – 100+ appliances (~90% new), liftgate truck, large powered storage unit</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>bulk lot</t>
+          <t>business for sale</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Surprise</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
@@ -3037,17 +3031,19 @@
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>2307</v>
+        <v>2317</v>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
-          <t>Message for pricing</t>
-        </is>
-      </c>
-      <c r="H39" s="15" t="n"/>
+          <t>$75,000</t>
+        </is>
+      </c>
+      <c r="H39" s="15" t="n">
+        <v>75000</v>
+      </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J39" s="13" t="inlineStr"/>
@@ -3069,104 +3065,39 @@
       </c>
       <c r="O39" s="14" t="inlineStr">
         <is>
-          <t>Seller is getting out of the appliance business; selling the whole locker (North Phoenix, Deer Valley Rd near 19th Ave). Delivery available per post. Separate from the Phoenix parts-store closing ad.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" outlineLevel="1">
-      <c r="A40" s="13" t="inlineStr">
-        <is>
-          <t>West / Other</t>
-        </is>
-      </c>
-      <c r="B40" s="14" t="inlineStr">
-        <is>
-          <t>Appliance repair &amp; sales business for sale – 100+ appliances (~90% new), liftgate truck, large powered storage unit</t>
-        </is>
-      </c>
-      <c r="C40" s="13" t="inlineStr">
-        <is>
-          <t>business for sale</t>
-        </is>
-      </c>
-      <c r="D40" s="13" t="inlineStr">
-        <is>
-          <t>Surprise</t>
-        </is>
-      </c>
-      <c r="E40" s="13" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="F40" s="13" t="n">
-        <v>2317</v>
-      </c>
-      <c r="G40" s="13" t="inlineStr">
-        <is>
-          <t>$75,000</t>
-        </is>
-      </c>
-      <c r="H40" s="15" t="n">
+          <t>Retiring owner of 14-year business serving rental-property owners. Whole appliances (fridges, stoves, microwaves, dishwashers, W/D), not a parts inventory. Storage unit near Dysart &amp; Bell Rd. By appointment only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — West / Other</t>
+        </is>
+      </c>
+      <c r="B40" s="17" t="inlineStr">
+        <is>
+          <t>2 item(s)</t>
+        </is>
+      </c>
+      <c r="C40" s="18" t="n"/>
+      <c r="D40" s="18" t="n"/>
+      <c r="E40" s="18" t="n"/>
+      <c r="F40" s="18" t="n"/>
+      <c r="G40" s="18" t="n"/>
+      <c r="H40" s="19" t="n">
         <v>75000</v>
       </c>
-      <c r="I40" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="J40" s="13" t="inlineStr"/>
-      <c r="K40" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L40" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M40" s="13" t="inlineStr"/>
-      <c r="N40" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O40" s="14" t="inlineStr">
-        <is>
-          <t>Retiring owner of 14-year business serving rental-property owners. Whole appliances (fridges, stoves, microwaves, dishwashers, W/D), not a parts inventory. Storage unit near Dysart &amp; Bell Rd. By appointment only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — West / Other</t>
-        </is>
-      </c>
-      <c r="B41" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C41" s="18" t="n"/>
-      <c r="D41" s="18" t="n"/>
-      <c r="E41" s="18" t="n"/>
-      <c r="F41" s="18" t="n"/>
-      <c r="G41" s="18" t="n"/>
-      <c r="H41" s="19" t="n">
-        <v>75000</v>
-      </c>
-      <c r="I41" s="18" t="n"/>
-      <c r="J41" s="18" t="n"/>
-      <c r="K41" s="18" t="n"/>
-      <c r="L41" s="18" t="n"/>
-      <c r="M41" s="18" t="n"/>
-      <c r="N41" s="18" t="n"/>
-      <c r="O41" s="18" t="n"/>
+      <c r="I40" s="18" t="n"/>
+      <c r="J40" s="18" t="n"/>
+      <c r="K40" s="18" t="n"/>
+      <c r="L40" s="18" t="n"/>
+      <c r="M40" s="18" t="n"/>
+      <c r="N40" s="18" t="n"/>
+      <c r="O40" s="18" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O41"/>
+  <autoFilter ref="A1:O40"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId2"/>
@@ -3177,15 +3108,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12283,9 +12213,9 @@
           <t>HiBid</t>
         </is>
       </c>
-      <c r="L122" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="L122" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M122" s="13" t="inlineStr"/>
@@ -12348,9 +12278,9 @@
           <t>HiBid</t>
         </is>
       </c>
-      <c r="L123" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="L123" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M123" s="13" t="inlineStr"/>
@@ -18281,9 +18211,9 @@
           <t>HiBid (Tom Hall Auctions)</t>
         </is>
       </c>
-      <c r="L35" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="L35" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M35" s="13" t="inlineStr"/>
@@ -18548,7 +18478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O79"/>
+  <dimension ref="A1:O82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -19726,7 +19656,7 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>▸ CT / Hudson Valley  (8)</t>
+          <t>▸ CT / Hudson Valley  (9)</t>
         </is>
       </c>
       <c r="B24" s="12" t="n"/>
@@ -19815,17 +19745,17 @@
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>Fabrication &amp; welding shop liquidation – everything must be sold</t>
+          <t>Antique / thrift store – entire inventory (fills a 4k sq ft store, 80k+ retail)</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>machine shop liquidation</t>
+          <t>store closing – entire inventory</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>Bridgeport</t>
+          <t>Waterbury</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
@@ -19834,17 +19764,17 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>Priced per machine (e.g. W.A. Whitney punch press $4,950; DoAll bandsaw $950)</t>
+          <t>$6,500 complete inventory (open to offers)</t>
         </is>
       </c>
       <c r="H26" s="15" t="n"/>
       <c r="I26" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="J26" s="13" t="inlineStr"/>
@@ -19866,7 +19796,7 @@
       </c>
       <c r="O26" s="14" t="inlineStr">
         <is>
-          <t>All assets/equipment/tools of a fab &amp; welding shop; machines under power, inspection by appointment, buyer removes (small forklift on site). Several big items already SOLD (Cincinnati brake/shear, plasma table, Lown roll). Remaining: Whitney + Roper Whitney punch presses, DoAll V36 bandsaw, Thompson spot welder, George Ohl 120" brake, Bridgeport mill, etc. Mostly 220V. Posted May 15, updated Oct 19.</t>
+          <t>1155 Thomaston Ave. Sold only as a complete lot: antiques, furniture, tools, hardware, small appliances, electronics, display cabinets, shelving, racks, vending machine. Seller will package with their eBay inventory (jewelry, vinyl, toys, Christmas, contents of 3 box trucks, "easily 100k retail"). Mixed general merchandise, not appliance-specific.</t>
         </is>
       </c>
     </row>
@@ -19878,47 +19808,47 @@
       </c>
       <c r="B27" s="14" t="inlineStr">
         <is>
-          <t>Major Intl Chain Surplus – 225 lots commercial refrigeration/kitchen (True, Traulsen, Hobart, Blodgett, Taylor)</t>
+          <t>Fabrication &amp; welding shop liquidation – everything must be sold</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>commercial surplus</t>
+          <t>machine shop liquidation</t>
         </is>
       </c>
       <c r="D27" s="13" t="inlineStr">
         <is>
-          <t>Pleasant Valley</t>
+          <t>Bridgeport</t>
         </is>
       </c>
       <c r="E27" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="F27" s="13" t="n">
-        <v>157</v>
+        <v>139</v>
       </c>
       <c r="G27" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Priced per machine (e.g. W.A. Whitney punch press $4,950; DoAll bandsaw $950)</t>
         </is>
       </c>
       <c r="H27" s="15" t="n"/>
-      <c r="I27" s="13" t="inlineStr"/>
-      <c r="J27" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-20 02:00 PM ET</t>
-        </is>
-      </c>
+      <c r="I27" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="J27" s="13" t="inlineStr"/>
       <c r="K27" s="13" t="inlineStr">
         <is>
-          <t>Adams / BidWrangler</t>
-        </is>
-      </c>
-      <c r="L27" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L27" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M27" s="13" t="inlineStr"/>
@@ -19929,7 +19859,7 @@
       </c>
       <c r="O27" s="14" t="inlineStr">
         <is>
-          <t>Tested and new units.</t>
+          <t>All assets/equipment/tools of a fab &amp; welding shop; machines under power, inspection by appointment, buyer removes (small forklift on site). Several big items already SOLD (Cincinnati brake/shear, plasma table, Lown roll). Remaining: Whitney + Roper Whitney punch presses, DoAll V36 bandsaw, Thompson spot welder, George Ohl 120" brake, Bridgeport mill, etc. Mostly 220V. Posted May 15, updated Oct 19.</t>
         </is>
       </c>
     </row>
@@ -19941,46 +19871,42 @@
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>The Outlaw Grill Steakhouse – used restaurant equipment auction (PCI Auctions CT, e.g. Vulcan EV60 Endurance 60" range)</t>
+          <t>Major Intl Chain Surplus – 225 lots commercial refrigeration/kitchen (True, Traulsen, Hobart, Blodgett, Taylor)</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>restaurant auction</t>
+          <t>commercial surplus</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>Stamford</t>
+          <t>Pleasant Valley</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>Online auction, current bids</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H28" s="15" t="n"/>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
+      <c r="I28" s="13" t="inlineStr"/>
       <c r="J28" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 08:30 PM ET</t>
+          <t>2026-10-20 02:00 PM ET</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>PCI Auctions</t>
+          <t>Adams / BidWrangler</t>
         </is>
       </c>
       <c r="L28" s="20" t="inlineStr">
@@ -19996,7 +19922,7 @@
       </c>
       <c r="O28" s="14" t="inlineStr">
         <is>
-          <t>Ends Wed Oct 21 8:30 PM EDT. PCI warehouse, 36 Ludlow St, Stamford CT. Page lists preview Oct 28 and removal Thu Oct 29 11-3 (after close). Shipping/delivery available; payment due on pickup day. Items still being added.</t>
+          <t>Tested and new units.</t>
         </is>
       </c>
     </row>
@@ -20008,17 +19934,17 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>Café/bakery liquidation – Traulsen, Vulcan ovens, mixers, Hobart slicer (~74 lots)</t>
+          <t>The Outlaw Grill Steakhouse – used restaurant equipment auction (PCI Auctions CT, e.g. Vulcan EV60 Endurance 60" range)</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>restaurant auction</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>Greenwich</t>
+          <t>Stamford</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
@@ -20027,23 +19953,27 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
-          <t>Live auction + webcast</t>
+          <t>Online auction, current bids</t>
         </is>
       </c>
       <c r="H29" s="15" t="n"/>
-      <c r="I29" s="13" t="inlineStr"/>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="J29" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 06:00 PM ET</t>
+          <t>2026-10-21 08:30 PM ET</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>Best Buy Auctioneers / AuctionGuide</t>
+          <t>PCI Auctions</t>
         </is>
       </c>
       <c r="L29" s="20" t="inlineStr">
@@ -20059,7 +19989,7 @@
       </c>
       <c r="O29" s="14" t="inlineStr">
         <is>
-          <t>Oct 21; start time not captured (placeholder 6 PM).</t>
+          <t>Ends Wed Oct 21 8:30 PM EDT. PCI warehouse, 36 Ludlow St, Stamford CT. Page lists preview Oct 28 and removal Thu Oct 29 11-3 (after close). Shipping/delivery available; payment due on pickup day. Items still being added.</t>
         </is>
       </c>
     </row>
@@ -20071,47 +20001,47 @@
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>BJ's Wholesale closeout – racking, forklifts, Hobart</t>
+          <t>Café/bakery liquidation – Traulsen, Vulcan ovens, mixers, Hobart slicer (~74 lots)</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>Rotterdam</t>
+          <t>Greenwich</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Live auction + webcast</t>
         </is>
       </c>
       <c r="H30" s="15" t="n"/>
       <c r="I30" s="13" t="inlineStr"/>
       <c r="J30" s="13" t="inlineStr">
         <is>
-          <t>2026-11-10 10:00 AM ET</t>
+          <t>2026-10-21 06:00 PM ET</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L30" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Best Buy Auctioneers / AuctionGuide</t>
+        </is>
+      </c>
+      <c r="L30" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M30" s="13" t="inlineStr"/>
@@ -20122,7 +20052,7 @@
       </c>
       <c r="O30" s="14" t="inlineStr">
         <is>
-          <t>Closes from Nov 10 10 AM.</t>
+          <t>Oct 21; start time not captured (placeholder 6 PM).</t>
         </is>
       </c>
     </row>
@@ -20134,17 +20064,17 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>Body shop closing after 50 years – tools, welder, generators, plasma</t>
+          <t>BJ's Wholesale closeout – racking, forklifts, Hobart</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>tools liquidation</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>West Nyack</t>
+          <t>Rotterdam</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
@@ -20153,23 +20083,23 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
-          <t>Make offer / lot</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H31" s="15" t="n"/>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="J31" s="13" t="inlineStr"/>
+      <c r="I31" s="13" t="inlineStr"/>
+      <c r="J31" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-10 10:00 AM ET</t>
+        </is>
+      </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>Grafe Auction</t>
         </is>
       </c>
       <c r="L31" s="13" t="inlineStr">
@@ -20185,7 +20115,7 @@
       </c>
       <c r="O31" s="14" t="inlineStr">
         <is>
-          <t>One-man auto body shop closing/retirement (Park Ridge / West Nyack NY-NJ border). Heat lamps, Kansas jack pullers, Miller 200 welder, generators, sheet-metal brake, hydraulic press, plasma cutter, engine hoist. Posted Aug 16; still open 2026-10-19.</t>
+          <t>Closes from Nov 10 10 AM.</t>
         </is>
       </c>
     </row>
@@ -20197,17 +20127,17 @@
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>Woodworkers shop closing sale – shop tools &amp; hand tools</t>
+          <t>Body shop closing after 50 years – tools, welder, generators, plasma</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>woodworking shop closing</t>
+          <t>tools liquidation</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>Tappan</t>
+          <t>West Nyack</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -20216,17 +20146,17 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>Priced individually (some free)</t>
+          <t>Make offer / lot</t>
         </is>
       </c>
       <c r="H32" s="15" t="n"/>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="J32" s="13" t="inlineStr"/>
@@ -20248,120 +20178,120 @@
       </c>
       <c r="O32" s="14" t="inlineStr">
         <is>
+          <t>One-man auto body shop closing/retirement (Park Ridge / West Nyack NY-NJ border). Heat lamps, Kansas jack pullers, Miller 200 welder, generators, sheet-metal brake, hydraulic press, plasma cutter, engine hoist. Posted Aug 16; still open 2026-10-19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" outlineLevel="1">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>CT / Hudson Valley</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Woodworkers shop closing sale – shop tools &amp; hand tools</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>woodworking shop closing</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>Tappan</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>179</v>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>Priced individually (some free)</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="n"/>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="J33" s="13" t="inlineStr"/>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L33" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M33" s="13" t="inlineStr"/>
+      <c r="N33" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O33" s="14" t="inlineStr">
+        <is>
           <t>Ongoing shop-closing sale at 61 Main St, Tappan; many shop and hand tools, schedule a visit. Near the West Nyack body-shop sale (bl-054) for one trip.</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="17" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="17" t="inlineStr">
         <is>
           <t>Subtotal — CT / Hudson Valley</t>
         </is>
       </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>8 item(s)</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="n"/>
-      <c r="D33" s="18" t="n"/>
-      <c r="E33" s="18" t="n"/>
-      <c r="F33" s="18" t="n"/>
-      <c r="G33" s="18" t="n"/>
-      <c r="H33" s="19" t="n">
+      <c r="B34" s="17" t="inlineStr">
+        <is>
+          <t>9 item(s)</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="n"/>
+      <c r="D34" s="18" t="n"/>
+      <c r="E34" s="18" t="n"/>
+      <c r="F34" s="18" t="n"/>
+      <c r="G34" s="18" t="n"/>
+      <c r="H34" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I33" s="18" t="n"/>
-      <c r="J33" s="18" t="n"/>
-      <c r="K33" s="18" t="n"/>
-      <c r="L33" s="18" t="n"/>
-      <c r="M33" s="18" t="n"/>
-      <c r="N33" s="18" t="n"/>
-      <c r="O33" s="18" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
+      <c r="I34" s="18" t="n"/>
+      <c r="J34" s="18" t="n"/>
+      <c r="K34" s="18" t="n"/>
+      <c r="L34" s="18" t="n"/>
+      <c r="M34" s="18" t="n"/>
+      <c r="N34" s="18" t="n"/>
+      <c r="O34" s="18" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>▸ NYC / Long Island / NJ  (22)</t>
         </is>
       </c>
-      <c r="B34" s="12" t="n"/>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="12" t="n"/>
-      <c r="E34" s="12" t="n"/>
-      <c r="F34" s="12" t="n"/>
-      <c r="G34" s="12" t="n"/>
-      <c r="H34" s="12" t="n"/>
-      <c r="I34" s="12" t="n"/>
-      <c r="J34" s="12" t="n"/>
-      <c r="K34" s="12" t="n"/>
-      <c r="L34" s="12" t="n"/>
-      <c r="M34" s="12" t="n"/>
-      <c r="N34" s="12" t="n"/>
-      <c r="O34" s="12" t="n"/>
-    </row>
-    <row r="35" outlineLevel="1">
-      <c r="A35" s="13" t="inlineStr">
-        <is>
-          <t>NYC / Long Island / NJ</t>
-        </is>
-      </c>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>Viva Margherita restaurant complete contents (building torn down)</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="inlineStr">
-        <is>
-          <t>restaurant closing</t>
-        </is>
-      </c>
-      <c r="D35" s="13" t="inlineStr">
-        <is>
-          <t>Edgewater</t>
-        </is>
-      </c>
-      <c r="E35" s="13" t="inlineStr">
-        <is>
-          <t>NJ</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="n">
-        <v>186</v>
-      </c>
-      <c r="G35" s="13" t="inlineStr">
-        <is>
-          <t>Complete contents / make offer</t>
-        </is>
-      </c>
-      <c r="H35" s="15" t="n"/>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="J35" s="13" t="inlineStr"/>
-      <c r="K35" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L35" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M35" s="13" t="inlineStr"/>
-      <c r="N35" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O35" s="14" t="inlineStr">
-        <is>
-          <t>Address 163 Old River Road, Edgewater NJ. Building being torn down; complete restaurant contents for sale / make offer.</t>
-        </is>
-      </c>
+      <c r="B35" s="12" t="n"/>
+      <c r="C35" s="12" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="12" t="n"/>
+      <c r="G35" s="12" t="n"/>
+      <c r="H35" s="12" t="n"/>
+      <c r="I35" s="12" t="n"/>
+      <c r="J35" s="12" t="n"/>
+      <c r="K35" s="12" t="n"/>
+      <c r="L35" s="12" t="n"/>
+      <c r="M35" s="12" t="n"/>
+      <c r="N35" s="12" t="n"/>
+      <c r="O35" s="12" t="n"/>
     </row>
     <row r="36" outlineLevel="1">
       <c r="A36" s="13" t="inlineStr">
@@ -20371,7 +20301,7 @@
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>Japanese BBQ &amp; bar – ~47 lots: Turbo Air, Hoshizaki ice machine, Pitco, Beverage-Air</t>
+          <t>Viva Margherita restaurant complete contents (building torn down)</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
@@ -20381,41 +20311,37 @@
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Edgewater</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Complete contents / make offer</t>
         </is>
       </c>
       <c r="H36" s="15" t="n"/>
       <c r="I36" s="13" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="J36" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 04:00 PM ET</t>
-        </is>
-      </c>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="J36" s="13" t="inlineStr"/>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
-        </is>
-      </c>
-      <c r="L36" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L36" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M36" s="13" t="inlineStr"/>
@@ -20426,7 +20352,7 @@
       </c>
       <c r="O36" s="14" t="inlineStr">
         <is>
-          <t>Wed Oct 21 4 PM. NYC 10013.</t>
+          <t>Address 163 Old River Road, Edgewater NJ. Building being torn down; complete restaurant contents for sale / make offer.</t>
         </is>
       </c>
     </row>
@@ -20438,12 +20364,12 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>Flooring company closed – pro tool package</t>
+          <t>Japanese BBQ &amp; bar – ~47 lots: Turbo Air, Hoshizaki ice machine, Pitco, Beverage-Air</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>tools liquidation</t>
+          <t>restaurant closing</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
@@ -20457,28 +20383,32 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t>$1,000</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H37" s="15" t="n"/>
       <c r="I37" s="13" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="J37" s="13" t="inlineStr"/>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J37" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-21 04:00 PM ET</t>
+        </is>
+      </c>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L37" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L37" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M37" s="13" t="inlineStr"/>
@@ -20489,7 +20419,7 @@
       </c>
       <c r="O37" s="14" t="inlineStr">
         <is>
-          <t>Flooring/construction company closed; pro tool package $1,000.</t>
+          <t>Wed Oct 21 4 PM. NYC 10013.</t>
         </is>
       </c>
     </row>
@@ -20501,12 +20431,12 @@
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>New-in-box commercial refrigeration lot – 10 Beverage-Air &amp; Perlick units (bar never opened)</t>
+          <t>Flooring company closed – pro tool package</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>commercial refrigeration lot</t>
+          <t>tools liquidation</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
@@ -20524,13 +20454,13 @@
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>$27,500 all 10 (or per unit $2,800–$4,150)</t>
+          <t>$1,000</t>
         </is>
       </c>
       <c r="H38" s="15" t="n"/>
       <c r="I38" s="13" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J38" s="13" t="inlineStr"/>
@@ -20552,7 +20482,7 @@
       </c>
       <c r="O38" s="14" t="inlineStr">
         <is>
-          <t>Financial District. Never installed, factory packaging: 2 Beverage-Air HBF23HC-1-HS reach-in freezers ($4,150 ea), 3 HBR23HC-1-HS reach-in fridges ($3,550 ea), 1 UCR48AHC 48" undercounter ($2,800), 3 Perlick HC24FS4 glass frosters + 1 HC24RS4 beverage fridge ($2,850 ea). Seller says full retail $47,463 (about 42% off as a bundle). Updated Oct 14.</t>
+          <t>Flooring/construction company closed; pro tool package $1,000.</t>
         </is>
       </c>
     </row>
@@ -20564,51 +20494,47 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>Corporate caterer – Alto-Shaam, new boxed Avantco rice cookers &amp; Cadco oven, Perlick, MerryChef</t>
+          <t>New-in-box commercial refrigeration lot – 10 Beverage-Air &amp; Perlick units (bar never opened)</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>commercial refrigeration lot</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>Jersey City</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>$27,500 all 10 (or per unit $2,800–$4,150)</t>
         </is>
       </c>
       <c r="H39" s="15" t="n"/>
       <c r="I39" s="13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="J39" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-22 02:00 PM ET</t>
-        </is>
-      </c>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="J39" s="13" t="inlineStr"/>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
-        </is>
-      </c>
-      <c r="L39" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L39" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M39" s="13" t="inlineStr"/>
@@ -20619,7 +20545,7 @@
       </c>
       <c r="O39" s="14" t="inlineStr">
         <is>
-          <t>Thu Oct 22 2 PM.</t>
+          <t>Financial District. Never installed, factory packaging: 2 Beverage-Air HBF23HC-1-HS reach-in freezers ($4,150 ea), 3 HBR23HC-1-HS reach-in fridges ($3,550 ea), 1 UCR48AHC 48" undercounter ($2,800), 3 Perlick HC24FS4 glass frosters + 1 HC24RS4 beverage fridge ($2,850 ea). Seller says full retail $47,463 (about 42% off as a bundle). Updated Oct 14.</t>
         </is>
       </c>
     </row>
@@ -20631,12 +20557,12 @@
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>Lighting store closing – lease ended, up to 70% off showroom</t>
+          <t>Corporate caterer – Alto-Shaam, new boxed Avantco rice cookers &amp; Cadco oven, Perlick, MerryChef</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
@@ -20654,24 +20580,28 @@
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
-          <t>up to 70% off</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H40" s="15" t="n"/>
       <c r="I40" s="13" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="J40" s="13" t="inlineStr"/>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="J40" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-22 02:00 PM ET</t>
+        </is>
+      </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L40" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L40" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M40" s="13" t="inlineStr"/>
@@ -20682,7 +20612,7 @@
       </c>
       <c r="O40" s="14" t="inlineStr">
         <is>
-          <t>Lighting store closing, lease ended. Showroom inventory up to 70% off.</t>
+          <t>Thu Oct 22 2 PM.</t>
         </is>
       </c>
     </row>
@@ -20694,17 +20624,17 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>Tools / plumbing / MRO supply inventory – Hilti/DeWalt/Milwaukee, fittings, heat pumps</t>
+          <t>Lighting store closing – lease ended, up to 70% off showroom</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>Riverdale</t>
+          <t>Jersey City</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -20713,23 +20643,23 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>up to 70% off</t>
         </is>
       </c>
       <c r="H41" s="15" t="n"/>
-      <c r="I41" s="13" t="inlineStr"/>
-      <c r="J41" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-30 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="J41" s="13" t="inlineStr"/>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L41" s="13" t="inlineStr">
@@ -20745,7 +20675,7 @@
       </c>
       <c r="O41" s="14" t="inlineStr">
         <is>
-          <t>Bulk resale inventory.</t>
+          <t>Lighting store closing, lease ended. Showroom inventory up to 70% off.</t>
         </is>
       </c>
     </row>
@@ -20757,12 +20687,12 @@
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>Ice cream + cookie franchise equipment – Taylor soft-serve, Atosa, Blodgett</t>
+          <t>Tools / plumbing / MRO supply inventory – Hilti/DeWalt/Milwaukee, fittings, heat pumps</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
@@ -20787,7 +20717,7 @@
       <c r="I42" s="13" t="inlineStr"/>
       <c r="J42" s="13" t="inlineStr">
         <is>
-          <t>2026-11-05 11:00 AM ET</t>
+          <t>2026-10-30 11:00 AM ET</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
@@ -20808,7 +20738,7 @@
       </c>
       <c r="O42" s="14" t="inlineStr">
         <is>
-          <t>Resellable units.</t>
+          <t>Bulk resale inventory.</t>
         </is>
       </c>
     </row>
@@ -20820,17 +20750,17 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>Wascomat commercial washers liquidation (22× W105, 6× W185, dryer panels)</t>
+          <t>Ice cream + cookie franchise equipment – Taylor soft-serve, Atosa, Blodgett</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>commercial laundry</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>Newark</t>
+          <t>Riverdale</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
@@ -20839,23 +20769,23 @@
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t>$500–$800 each / panels $150</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H43" s="15" t="n"/>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="J43" s="13" t="inlineStr"/>
+      <c r="I43" s="13" t="inlineStr"/>
+      <c r="J43" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-05 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L43" s="13" t="inlineStr">
@@ -20871,7 +20801,7 @@
       </c>
       <c r="O43" s="14" t="inlineStr">
         <is>
-          <t>22× W105 @ $500, 6× W185 @ $800, 20 dryer panels $150. Commercial laundry liquidation.</t>
+          <t>Resellable units.</t>
         </is>
       </c>
     </row>
@@ -20883,17 +20813,17 @@
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>Major food-service caterer – new-in-box True reach-ins, Beverage-Air, TurboChef, Resfab ventless fryer</t>
+          <t>Wascomat commercial washers liquidation (22× W105, 6× W185, dryer panels)</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>commercial laundry</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>Parsippany</t>
+          <t>Newark</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -20902,27 +20832,23 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>$500–$800 each / panels $150</t>
         </is>
       </c>
       <c r="H44" s="15" t="n"/>
       <c r="I44" s="13" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="J44" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-03 02:00 PM ET</t>
-        </is>
-      </c>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="J44" s="13" t="inlineStr"/>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L44" s="13" t="inlineStr">
@@ -20938,7 +20864,7 @@
       </c>
       <c r="O44" s="14" t="inlineStr">
         <is>
-          <t>Tue Nov 3 2 PM, checkout Nov 4.</t>
+          <t>22× W105 @ $500, 6× W185 @ $800, 20 dryer panels $150. Commercial laundry liquidation.</t>
         </is>
       </c>
     </row>
@@ -20950,17 +20876,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>Business closing – 160 new Carnes exhaust fans</t>
+          <t>Major food-service caterer – new-in-box True reach-ins, Beverage-Air, TurboChef, Resfab ventless fryer</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>HVAC inventory</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>Kenilworth</t>
+          <t>Parsippany</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -20973,19 +20899,23 @@
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>$40 each or $5,000 all OBO</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H45" s="15" t="n"/>
       <c r="I45" s="13" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="J45" s="13" t="inlineStr"/>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="J45" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-03 02:00 PM ET</t>
+        </is>
+      </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
       <c r="L45" s="13" t="inlineStr">
@@ -21001,7 +20931,7 @@
       </c>
       <c r="O45" s="14" t="inlineStr">
         <is>
-          <t>160 new Carnes 80CFM 1.0 sone exhaust fans. $40 each or $5,000 for all OBO. Business closing HVAC inventory.</t>
+          <t>Tue Nov 3 2 PM, checkout Nov 4.</t>
         </is>
       </c>
     </row>
@@ -21013,12 +20943,12 @@
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>Air Systems Inc – sheet metal / HVAC fabrication shop liquidation</t>
+          <t>Business closing – 160 new Carnes exhaust fans</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>HVAC shop liquidation</t>
+          <t>HVAC inventory</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
@@ -21036,19 +20966,19 @@
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>Timed online (15% BP)</t>
+          <t>$40 each or $5,000 all OBO</t>
         </is>
       </c>
       <c r="H46" s="15" t="n"/>
-      <c r="I46" s="13" t="inlineStr"/>
-      <c r="J46" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-29 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J46" s="13" t="inlineStr"/>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner Auctions</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L46" s="13" t="inlineStr">
@@ -21064,7 +20994,7 @@
       </c>
       <c r="O46" s="14" t="inlineStr">
         <is>
-          <t>Vicon HVAC plasma; Flagler/Lockformer/Roto-Die/Engel fab; welders; Clark forklift; Genie Superlift; Ridgid/Milwaukee/DeWalt/Bosch/Hilti/Makita tools; AeroVent/Carnes exhaust fans; racking/scaffolding. Preview Oct 28–29 AM; pickup Oct 29 PM–Nov 4. Same town as Carnes fan CL lot.</t>
+          <t>160 new Carnes 80CFM 1.0 sone exhaust fans. $40 each or $5,000 for all OBO. Business closing HVAC inventory.</t>
         </is>
       </c>
     </row>
@@ -21076,17 +21006,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>Serpico's Pizzeria (lost lease) – Bari ovens, walk-in, Hobart 60qt, Vulcan range</t>
+          <t>Air Systems Inc – sheet metal / HVAC fabrication shop liquidation</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>HVAC shop liquidation</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>Allenhurst</t>
+          <t>Kenilworth</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -21095,28 +21025,28 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
-          <t>No-reserve online auction</t>
+          <t>Timed online (15% BP)</t>
         </is>
       </c>
       <c r="H47" s="15" t="n"/>
       <c r="I47" s="13" t="inlineStr"/>
       <c r="J47" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 11:00 AM ET</t>
+          <t>2026-10-29 11:00 AM ET</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>Peter Costanzo / EstateSales.net</t>
-        </is>
-      </c>
-      <c r="L47" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>A.J. Willner Auctions</t>
+        </is>
+      </c>
+      <c r="L47" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M47" s="13" t="inlineStr"/>
@@ -21127,7 +21057,7 @@
       </c>
       <c r="O47" s="14" t="inlineStr">
         <is>
-          <t>Absolute / no reserve.</t>
+          <t>Vicon HVAC plasma; Flagler/Lockformer/Roto-Die/Engel fab; welders; Clark forklift; Genie Superlift; Ridgid/Milwaukee/DeWalt/Bosch/Hilti/Makita tools; AeroVent/Carnes exhaust fans; racking/scaffolding. Preview Oct 28–29 AM; pickup Oct 29 PM–Nov 4. Same town as Carnes fan CL lot.</t>
         </is>
       </c>
     </row>
@@ -21139,17 +21069,17 @@
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>Altitude Trampoline Park liquidation – partial: Atosa, TurboChef, stainless</t>
+          <t>Serpico's Pizzeria (lost lease) – Bari ovens, walk-in, Hobart 60qt, Vulcan range</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>facility contents</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>Iselin</t>
+          <t>Allenhurst</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -21158,11 +21088,11 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>No-reserve online auction</t>
         </is>
       </c>
       <c r="H48" s="15" t="n"/>
@@ -21174,7 +21104,7 @@
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>Peter Costanzo / EstateSales.net</t>
         </is>
       </c>
       <c r="L48" s="20" t="inlineStr">
@@ -21190,7 +21120,7 @@
       </c>
       <c r="O48" s="14" t="inlineStr">
         <is>
-          <t>Some kitchen gear only.</t>
+          <t>Absolute / no reserve.</t>
         </is>
       </c>
     </row>
@@ -21202,17 +21132,17 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>Restaurant / pizzeria (contents not described)</t>
+          <t>Altitude Trampoline Park liquidation – partial: Atosa, TurboChef, stainless</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>facility contents</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>Berkeley Heights</t>
+          <t>Iselin</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -21221,27 +21151,23 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H49" s="15" t="n"/>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
+      <c r="I49" s="13" t="inlineStr"/>
       <c r="J49" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 02:00 PM ET</t>
+          <t>2026-10-21 11:00 AM ET</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L49" s="20" t="inlineStr">
@@ -21257,7 +21183,7 @@
       </c>
       <c r="O49" s="14" t="inlineStr">
         <is>
-          <t>Tue Oct 20 2 PM. No item description on page.</t>
+          <t>Some kitchen gear only.</t>
         </is>
       </c>
     </row>
@@ -21269,17 +21195,17 @@
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
+          <t>Restaurant / pizzeria (contents not described)</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>lien sale</t>
+          <t>restaurant closing</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>Edison</t>
+          <t>Berkeley Heights</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -21288,24 +21214,32 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
-          <t>Online auction, $2K load-out fee</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H50" s="15" t="n"/>
-      <c r="I50" s="13" t="inlineStr"/>
-      <c r="J50" s="13" t="inlineStr"/>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J50" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-20 02:00 PM ET</t>
+        </is>
+      </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
-        </is>
-      </c>
-      <c r="L50" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L50" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M50" s="13" t="inlineStr"/>
@@ -21316,7 +21250,7 @@
       </c>
       <c r="O50" s="14" t="inlineStr">
         <is>
-          <t>&gt;$100K new. Close date not captured.</t>
+          <t>Tue Oct 20 2 PM. No item description on page.</t>
         </is>
       </c>
     </row>
@@ -21328,12 +21262,12 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
+          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>lien sale</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
@@ -21351,23 +21285,15 @@
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>
-          <t>Live + HiBid webcast, 18% BP + 3% card</t>
+          <t>Online auction, $2K load-out fee</t>
         </is>
       </c>
       <c r="H51" s="15" t="n"/>
-      <c r="I51" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="J51" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-25 01:00 PM ET</t>
-        </is>
-      </c>
+      <c r="I51" s="13" t="inlineStr"/>
+      <c r="J51" s="13" t="inlineStr"/>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L51" s="13" t="inlineStr">
@@ -21375,11 +21301,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M51" s="21" t="inlineStr">
-        <is>
-          <t>FLIP</t>
-        </is>
-      </c>
+      <c r="M51" s="13" t="inlineStr"/>
       <c r="N51" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -21387,7 +21309,7 @@
       </c>
       <c r="O51" s="14" t="inlineStr">
         <is>
-          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
+          <t>&gt;$100K new. Close date not captured.</t>
         </is>
       </c>
     </row>
@@ -21399,17 +21321,17 @@
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
+          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>East Brunswick</t>
+          <t>Edison</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -21418,23 +21340,27 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Live + HiBid webcast, 18% BP + 3% card</t>
         </is>
       </c>
       <c r="H52" s="15" t="n"/>
-      <c r="I52" s="13" t="inlineStr"/>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="J52" s="13" t="inlineStr">
         <is>
-          <t>2026-11-03 11:00 AM ET</t>
+          <t>2026-10-25 01:00 PM ET</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
       <c r="L52" s="13" t="inlineStr">
@@ -21442,7 +21368,11 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M52" s="13" t="inlineStr"/>
+      <c r="M52" s="21" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
       <c r="N52" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -21450,7 +21380,7 @@
       </c>
       <c r="O52" s="14" t="inlineStr">
         <is>
-          <t>Store inventory.</t>
+          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
         </is>
       </c>
     </row>
@@ -21462,17 +21392,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>Bakery/Cafe Somerville NJ – rack ovens, La Marzocco, food truck (~76 lots)</t>
+          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>Somerville</t>
+          <t>East Brunswick</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -21481,27 +21411,23 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
-          <t>Live webcast + online (18% BP online)</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H53" s="15" t="n"/>
-      <c r="I53" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
+      <c r="I53" s="13" t="inlineStr"/>
       <c r="J53" s="13" t="inlineStr">
         <is>
-          <t>2026-10-26 02:00 PM ET</t>
+          <t>2026-11-03 11:00 AM ET</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>HiBid / Best Buy Auctioneers</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L53" s="13" t="inlineStr">
@@ -21517,7 +21443,7 @@
       </c>
       <c r="O53" s="14" t="inlineStr">
         <is>
-          <t>Full bakery/cafe commercial kitchen: food truck w/ pizza oven, La Marzocco espresso, Mazzer, Baxter + Empire Logiudice rack ovens, dough depositor, Globe floor mixer, Artic Air / SS refrigeration, fryers, Vitamix, Robot Coupe, display cases, dining furniture. Preview 11 AM sale day; checkout Tue 10/27.</t>
+          <t>Store inventory.</t>
         </is>
       </c>
     </row>
@@ -21529,7 +21455,7 @@
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>Ability to Work kitchen and store – commercial kitchen + store fixtures (~135 lots)</t>
+          <t>Bakery/Cafe Somerville NJ – rack ovens, La Marzocco, food truck (~76 lots)</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
@@ -21539,7 +21465,7 @@
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>Flemington</t>
+          <t>Somerville</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -21548,23 +21474,27 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>Timed online (15% BP)</t>
+          <t>Live webcast + online (18% BP online)</t>
         </is>
       </c>
       <c r="H54" s="15" t="n"/>
-      <c r="I54" s="13" t="inlineStr"/>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="J54" s="13" t="inlineStr">
         <is>
-          <t>2026-10-27 11:02 AM ET</t>
+          <t>2026-10-26 02:00 PM ET</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>HiBid</t>
+          <t>HiBid / Best Buy Auctioneers</t>
         </is>
       </c>
       <c r="L54" s="13" t="inlineStr">
@@ -21580,7 +21510,7 @@
       </c>
       <c r="O54" s="14" t="inlineStr">
         <is>
-          <t>Apprentice/hospitality training cafe-kitchen and store dispersal. Preview 9–11 AM sale day; removal Oct 27 noon–Oct 29.</t>
+          <t>Full bakery/cafe commercial kitchen: food truck w/ pizza oven, La Marzocco espresso, Mazzer, Baxter + Empire Logiudice rack ovens, dough depositor, Globe floor mixer, Artic Air / SS refrigeration, fryers, Vitamix, Robot Coupe, display cases, dining furniture. Preview 11 AM sale day; checkout Tue 10/27.</t>
         </is>
       </c>
     </row>
@@ -21592,17 +21522,17 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
+          <t>Ability to Work kitchen and store – commercial kitchen + store fixtures (~135 lots)</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>showroom closing</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>Lawrenceville</t>
+          <t>Flemington</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -21611,23 +21541,23 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
-          <t>Online auction, 18% BP</t>
+          <t>Timed online (15% BP)</t>
         </is>
       </c>
       <c r="H55" s="15" t="n"/>
       <c r="I55" s="13" t="inlineStr"/>
       <c r="J55" s="13" t="inlineStr">
         <is>
-          <t>2026-10-27 09:00 AM ET</t>
+          <t>2026-10-27 11:02 AM ET</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
+          <t>HiBid</t>
         </is>
       </c>
       <c r="L55" s="13" t="inlineStr">
@@ -21643,7 +21573,7 @@
       </c>
       <c r="O55" s="14" t="inlineStr">
         <is>
-          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
+          <t>Apprentice/hospitality training cafe-kitchen and store dispersal. Preview 9–11 AM sale day; removal Oct 27 noon–Oct 29.</t>
         </is>
       </c>
     </row>
@@ -21655,7 +21585,7 @@
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
+          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr">
@@ -21665,7 +21595,7 @@
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>Cherry Hill</t>
+          <t>Lawrenceville</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -21674,18 +21604,18 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>Online auction, openers ~$0.50</t>
+          <t>Online auction, 18% BP</t>
         </is>
       </c>
       <c r="H56" s="15" t="n"/>
       <c r="I56" s="13" t="inlineStr"/>
       <c r="J56" s="13" t="inlineStr">
         <is>
-          <t>2026-11-02 11:00 AM ET</t>
+          <t>2026-10-27 09:00 AM ET</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
@@ -21706,281 +21636,281 @@
       </c>
       <c r="O56" s="14" t="inlineStr">
         <is>
+          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" outlineLevel="1">
+      <c r="A57" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B57" s="14" t="inlineStr">
+        <is>
+          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
+        </is>
+      </c>
+      <c r="C57" s="13" t="inlineStr">
+        <is>
+          <t>showroom closing</t>
+        </is>
+      </c>
+      <c r="D57" s="13" t="inlineStr">
+        <is>
+          <t>Cherry Hill</t>
+        </is>
+      </c>
+      <c r="E57" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F57" s="13" t="n">
+        <v>266</v>
+      </c>
+      <c r="G57" s="13" t="inlineStr">
+        <is>
+          <t>Online auction, openers ~$0.50</t>
+        </is>
+      </c>
+      <c r="H57" s="15" t="n"/>
+      <c r="I57" s="13" t="inlineStr"/>
+      <c r="J57" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-02 11:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K57" s="13" t="inlineStr">
+        <is>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L57" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M57" s="13" t="inlineStr"/>
+      <c r="N57" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O57" s="14" t="inlineStr">
+        <is>
           <t>Lots close from Nov 2 11 AM.</t>
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="17" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="17" t="inlineStr">
         <is>
           <t>Subtotal — NYC / Long Island / NJ</t>
         </is>
       </c>
-      <c r="B57" s="17" t="inlineStr">
+      <c r="B58" s="17" t="inlineStr">
         <is>
           <t>22 item(s)</t>
         </is>
       </c>
-      <c r="C57" s="18" t="n"/>
-      <c r="D57" s="18" t="n"/>
-      <c r="E57" s="18" t="n"/>
-      <c r="F57" s="18" t="n"/>
-      <c r="G57" s="18" t="n"/>
-      <c r="H57" s="19" t="n">
+      <c r="C58" s="18" t="n"/>
+      <c r="D58" s="18" t="n"/>
+      <c r="E58" s="18" t="n"/>
+      <c r="F58" s="18" t="n"/>
+      <c r="G58" s="18" t="n"/>
+      <c r="H58" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I57" s="18" t="n"/>
-      <c r="J57" s="18" t="n"/>
-      <c r="K57" s="18" t="n"/>
-      <c r="L57" s="18" t="n"/>
-      <c r="M57" s="18" t="n"/>
-      <c r="N57" s="18" t="n"/>
-      <c r="O57" s="18" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="11" t="inlineStr">
+      <c r="I58" s="18" t="n"/>
+      <c r="J58" s="18" t="n"/>
+      <c r="K58" s="18" t="n"/>
+      <c r="L58" s="18" t="n"/>
+      <c r="M58" s="18" t="n"/>
+      <c r="N58" s="18" t="n"/>
+      <c r="O58" s="18" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t>▸ Eastern PA / Mid-Atlantic  (1)</t>
         </is>
       </c>
-      <c r="B58" s="12" t="n"/>
-      <c r="C58" s="12" t="n"/>
-      <c r="D58" s="12" t="n"/>
-      <c r="E58" s="12" t="n"/>
-      <c r="F58" s="12" t="n"/>
-      <c r="G58" s="12" t="n"/>
-      <c r="H58" s="12" t="n"/>
-      <c r="I58" s="12" t="n"/>
-      <c r="J58" s="12" t="n"/>
-      <c r="K58" s="12" t="n"/>
-      <c r="L58" s="12" t="n"/>
-      <c r="M58" s="12" t="n"/>
-      <c r="N58" s="12" t="n"/>
-      <c r="O58" s="12" t="n"/>
-    </row>
-    <row r="59" outlineLevel="1">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="B59" s="12" t="n"/>
+      <c r="C59" s="12" t="n"/>
+      <c r="D59" s="12" t="n"/>
+      <c r="E59" s="12" t="n"/>
+      <c r="F59" s="12" t="n"/>
+      <c r="G59" s="12" t="n"/>
+      <c r="H59" s="12" t="n"/>
+      <c r="I59" s="12" t="n"/>
+      <c r="J59" s="12" t="n"/>
+      <c r="K59" s="12" t="n"/>
+      <c r="L59" s="12" t="n"/>
+      <c r="M59" s="12" t="n"/>
+      <c r="N59" s="12" t="n"/>
+      <c r="O59" s="12" t="n"/>
+    </row>
+    <row r="60" outlineLevel="1">
+      <c r="A60" s="13" t="inlineStr">
         <is>
           <t>Eastern PA / Mid-Atlantic</t>
         </is>
       </c>
-      <c r="B59" s="14" t="inlineStr">
+      <c r="B60" s="14" t="inlineStr">
         <is>
           <t>October restaurant consignment – Hobart, Rational, True + NEW scratch-and-dent Migali/Avantco</t>
         </is>
       </c>
-      <c r="C59" s="13" t="inlineStr">
+      <c r="C60" s="13" t="inlineStr">
         <is>
           <t>restaurant</t>
         </is>
       </c>
-      <c r="D59" s="13" t="inlineStr">
+      <c r="D60" s="13" t="inlineStr">
         <is>
           <t>Harrisburg</t>
         </is>
       </c>
-      <c r="E59" s="13" t="inlineStr">
+      <c r="E60" s="13" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="F59" s="13" t="n">
+      <c r="F60" s="13" t="n">
         <v>340</v>
       </c>
-      <c r="G59" s="13" t="inlineStr">
+      <c r="G60" s="13" t="inlineStr">
         <is>
           <t>Online auction, 15% BP, ships $55/pallet</t>
         </is>
       </c>
-      <c r="H59" s="15" t="n"/>
-      <c r="I59" s="13" t="inlineStr"/>
-      <c r="J59" s="13" t="inlineStr">
+      <c r="H60" s="15" t="n"/>
+      <c r="I60" s="13" t="inlineStr"/>
+      <c r="J60" s="13" t="inlineStr">
         <is>
           <t>2026-10-21 11:00 AM ET</t>
         </is>
       </c>
-      <c r="K59" s="13" t="inlineStr">
+      <c r="K60" s="13" t="inlineStr">
         <is>
           <t>Restaurant Auction Co</t>
         </is>
       </c>
-      <c r="L59" s="20" t="inlineStr">
+      <c r="L60" s="20" t="inlineStr">
         <is>
           <t>ENDING SOON</t>
         </is>
       </c>
-      <c r="M59" s="13" t="inlineStr"/>
-      <c r="N59" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O59" s="14" t="inlineStr">
+      <c r="M60" s="13" t="inlineStr"/>
+      <c r="N60" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O60" s="14" t="inlineStr">
         <is>
           <t>Closes Oct 21 10 or 11 AM (later used). Shippable.</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="17" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Eastern PA / Mid-Atlantic</t>
         </is>
       </c>
-      <c r="B60" s="17" t="inlineStr">
+      <c r="B61" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C60" s="18" t="n"/>
-      <c r="D60" s="18" t="n"/>
-      <c r="E60" s="18" t="n"/>
-      <c r="F60" s="18" t="n"/>
-      <c r="G60" s="18" t="n"/>
-      <c r="H60" s="19" t="n">
+      <c r="C61" s="18" t="n"/>
+      <c r="D61" s="18" t="n"/>
+      <c r="E61" s="18" t="n"/>
+      <c r="F61" s="18" t="n"/>
+      <c r="G61" s="18" t="n"/>
+      <c r="H61" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I60" s="18" t="n"/>
-      <c r="J60" s="18" t="n"/>
-      <c r="K60" s="18" t="n"/>
-      <c r="L60" s="18" t="n"/>
-      <c r="M60" s="18" t="n"/>
-      <c r="N60" s="18" t="n"/>
-      <c r="O60" s="18" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t>▸ Upstate / Western NY  (3)</t>
-        </is>
-      </c>
-      <c r="B61" s="12" t="n"/>
-      <c r="C61" s="12" t="n"/>
-      <c r="D61" s="12" t="n"/>
-      <c r="E61" s="12" t="n"/>
-      <c r="F61" s="12" t="n"/>
-      <c r="G61" s="12" t="n"/>
-      <c r="H61" s="12" t="n"/>
-      <c r="I61" s="12" t="n"/>
-      <c r="J61" s="12" t="n"/>
-      <c r="K61" s="12" t="n"/>
-      <c r="L61" s="12" t="n"/>
-      <c r="M61" s="12" t="n"/>
-      <c r="N61" s="12" t="n"/>
-      <c r="O61" s="12" t="n"/>
-    </row>
-    <row r="62" outlineLevel="1">
-      <c r="A62" s="13" t="inlineStr">
-        <is>
-          <t>Upstate / Western NY</t>
-        </is>
-      </c>
-      <c r="B62" s="14" t="inlineStr">
-        <is>
-          <t>Former Taco Del Mar – stainless, warmers, walk-in panels</t>
-        </is>
-      </c>
-      <c r="C62" s="13" t="inlineStr">
-        <is>
-          <t>restaurant</t>
-        </is>
-      </c>
-      <c r="D62" s="13" t="inlineStr">
-        <is>
-          <t>Watson</t>
-        </is>
-      </c>
-      <c r="E62" s="13" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="F62" s="13" t="n">
-        <v>260</v>
-      </c>
-      <c r="G62" s="13" t="inlineStr">
-        <is>
-          <t>HiBid online auction</t>
-        </is>
-      </c>
-      <c r="H62" s="15" t="n"/>
-      <c r="I62" s="13" t="inlineStr"/>
-      <c r="J62" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-20 06:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K62" s="13" t="inlineStr">
-        <is>
-          <t>Adirondack Asset / HiBid</t>
-        </is>
-      </c>
-      <c r="L62" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M62" s="13" t="inlineStr"/>
-      <c r="N62" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O62" s="14" t="inlineStr">
-        <is>
-          <t>Small lot.</t>
-        </is>
-      </c>
+      <c r="I61" s="18" t="n"/>
+      <c r="J61" s="18" t="n"/>
+      <c r="K61" s="18" t="n"/>
+      <c r="L61" s="18" t="n"/>
+      <c r="M61" s="18" t="n"/>
+      <c r="N61" s="18" t="n"/>
+      <c r="O61" s="18" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>▸ Western PA / Ohio Valley  (1)</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="n"/>
+      <c r="C62" s="12" t="n"/>
+      <c r="D62" s="12" t="n"/>
+      <c r="E62" s="12" t="n"/>
+      <c r="F62" s="12" t="n"/>
+      <c r="G62" s="12" t="n"/>
+      <c r="H62" s="12" t="n"/>
+      <c r="I62" s="12" t="n"/>
+      <c r="J62" s="12" t="n"/>
+      <c r="K62" s="12" t="n"/>
+      <c r="L62" s="12" t="n"/>
+      <c r="M62" s="12" t="n"/>
+      <c r="N62" s="12" t="n"/>
+      <c r="O62" s="12" t="n"/>
     </row>
     <row r="63" outlineLevel="1">
       <c r="A63" s="13" t="inlineStr">
         <is>
-          <t>Upstate / Western NY</t>
+          <t>Western PA / Ohio Valley</t>
         </is>
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>Closed restaurant – coolers, fridges, prep tables</t>
+          <t>Millers Pizza &amp; More – pizza business, commercial kitchen &amp; event space contents (362 lots)</t>
         </is>
       </c>
       <c r="C63" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>restaurant / commercial kitchen contents</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>Palmyra</t>
+          <t>Everson</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>333</v>
+        <v>478</v>
       </c>
       <c r="G63" s="13" t="inlineStr">
         <is>
-          <t>HiBid, 15% BP</t>
+          <t>Online auction, 15% buyer premium</t>
         </is>
       </c>
       <c r="H63" s="15" t="n"/>
       <c r="I63" s="13" t="inlineStr"/>
       <c r="J63" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 07:00 PM ET</t>
+          <t>2026-10-25 07:00 PM ET</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
         <is>
-          <t>Reynolds Auction Co / HiBid</t>
-        </is>
-      </c>
-      <c r="L63" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>HiBid (Bid Local LLC)</t>
+        </is>
+      </c>
+      <c r="L63" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M63" s="13" t="inlineStr"/>
@@ -21991,165 +21921,165 @@
       </c>
       <c r="O63" s="14" t="inlineStr">
         <is>
-          <t>No new out-of-state bidders. Small.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" outlineLevel="1">
-      <c r="A64" s="13" t="inlineStr">
+          <t>Property of Millers Pizza and More LLC; online-only, 362 lots, lots begin closing Oct 25 7 PM. Pickup Everson PA by appointment Tue 10/27 and Wed 10/28. Building (4,500 sq ft) to be auctioned separately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Western PA / Ohio Valley</t>
+        </is>
+      </c>
+      <c r="B64" s="17" t="inlineStr">
+        <is>
+          <t>1 item(s)</t>
+        </is>
+      </c>
+      <c r="C64" s="18" t="n"/>
+      <c r="D64" s="18" t="n"/>
+      <c r="E64" s="18" t="n"/>
+      <c r="F64" s="18" t="n"/>
+      <c r="G64" s="18" t="n"/>
+      <c r="H64" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="18" t="n"/>
+      <c r="J64" s="18" t="n"/>
+      <c r="K64" s="18" t="n"/>
+      <c r="L64" s="18" t="n"/>
+      <c r="M64" s="18" t="n"/>
+      <c r="N64" s="18" t="n"/>
+      <c r="O64" s="18" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>▸ Upstate / Western NY  (2)</t>
+        </is>
+      </c>
+      <c r="B65" s="12" t="n"/>
+      <c r="C65" s="12" t="n"/>
+      <c r="D65" s="12" t="n"/>
+      <c r="E65" s="12" t="n"/>
+      <c r="F65" s="12" t="n"/>
+      <c r="G65" s="12" t="n"/>
+      <c r="H65" s="12" t="n"/>
+      <c r="I65" s="12" t="n"/>
+      <c r="J65" s="12" t="n"/>
+      <c r="K65" s="12" t="n"/>
+      <c r="L65" s="12" t="n"/>
+      <c r="M65" s="12" t="n"/>
+      <c r="N65" s="12" t="n"/>
+      <c r="O65" s="12" t="n"/>
+    </row>
+    <row r="66" outlineLevel="1">
+      <c r="A66" s="13" t="inlineStr">
         <is>
           <t>Upstate / Western NY</t>
         </is>
       </c>
-      <c r="B64" s="14" t="inlineStr">
-        <is>
-          <t>Restaurant &amp; fitness equipment</t>
-        </is>
-      </c>
-      <c r="C64" s="13" t="inlineStr">
+      <c r="B66" s="14" t="inlineStr">
+        <is>
+          <t>Former Taco Del Mar – stainless, warmers, walk-in panels</t>
+        </is>
+      </c>
+      <c r="C66" s="13" t="inlineStr">
         <is>
           <t>restaurant</t>
         </is>
       </c>
-      <c r="D64" s="13" t="inlineStr">
-        <is>
-          <t>Williamsville</t>
-        </is>
-      </c>
-      <c r="E64" s="13" t="inlineStr">
+      <c r="D66" s="13" t="inlineStr">
+        <is>
+          <t>Watson</t>
+        </is>
+      </c>
+      <c r="E66" s="13" t="inlineStr">
         <is>
           <t>NY</t>
         </is>
       </c>
-      <c r="F64" s="13" t="n">
-        <v>408</v>
-      </c>
-      <c r="G64" s="13" t="inlineStr">
-        <is>
-          <t>Online auction</t>
-        </is>
-      </c>
-      <c r="H64" s="15" t="n"/>
-      <c r="I64" s="13" t="inlineStr"/>
-      <c r="J64" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-26 07:30 PM ET</t>
-        </is>
-      </c>
-      <c r="K64" s="13" t="inlineStr">
-        <is>
-          <t>Cash Auctions</t>
-        </is>
-      </c>
-      <c r="L64" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M64" s="13" t="inlineStr"/>
-      <c r="N64" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O64" s="14" t="inlineStr">
-        <is>
-          <t>Lots not reviewed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Upstate / Western NY</t>
-        </is>
-      </c>
-      <c r="B65" s="17" t="inlineStr">
-        <is>
-          <t>3 item(s)</t>
-        </is>
-      </c>
-      <c r="C65" s="18" t="n"/>
-      <c r="D65" s="18" t="n"/>
-      <c r="E65" s="18" t="n"/>
-      <c r="F65" s="18" t="n"/>
-      <c r="G65" s="18" t="n"/>
-      <c r="H65" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="18" t="n"/>
-      <c r="J65" s="18" t="n"/>
-      <c r="K65" s="18" t="n"/>
-      <c r="L65" s="18" t="n"/>
-      <c r="M65" s="18" t="n"/>
-      <c r="N65" s="18" t="n"/>
-      <c r="O65" s="18" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t>▸ Virginia  (1)</t>
-        </is>
-      </c>
-      <c r="B66" s="12" t="n"/>
-      <c r="C66" s="12" t="n"/>
-      <c r="D66" s="12" t="n"/>
-      <c r="E66" s="12" t="n"/>
-      <c r="F66" s="12" t="n"/>
-      <c r="G66" s="12" t="n"/>
-      <c r="H66" s="12" t="n"/>
-      <c r="I66" s="12" t="n"/>
-      <c r="J66" s="12" t="n"/>
-      <c r="K66" s="12" t="n"/>
-      <c r="L66" s="12" t="n"/>
-      <c r="M66" s="12" t="n"/>
-      <c r="N66" s="12" t="n"/>
-      <c r="O66" s="12" t="n"/>
+      <c r="F66" s="13" t="n">
+        <v>260</v>
+      </c>
+      <c r="G66" s="13" t="inlineStr">
+        <is>
+          <t>HiBid online auction</t>
+        </is>
+      </c>
+      <c r="H66" s="15" t="n"/>
+      <c r="I66" s="13" t="inlineStr"/>
+      <c r="J66" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K66" s="13" t="inlineStr">
+        <is>
+          <t>Adirondack Asset / HiBid</t>
+        </is>
+      </c>
+      <c r="L66" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M66" s="13" t="inlineStr"/>
+      <c r="N66" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O66" s="14" t="inlineStr">
+        <is>
+          <t>Small lot.</t>
+        </is>
+      </c>
     </row>
     <row r="67" outlineLevel="1">
       <c r="A67" s="13" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Upstate / Western NY</t>
         </is>
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>Haynes Furniture / The Dump – 12 stores closing (furniture, mattresses)</t>
+          <t>Restaurant &amp; fitness equipment</t>
         </is>
       </c>
       <c r="C67" s="13" t="inlineStr">
         <is>
-          <t>retail GOB</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>Virginia Beach</t>
+          <t>Williamsville</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>456</v>
+        <v>408</v>
       </c>
       <c r="G67" s="13" t="inlineStr">
         <is>
-          <t>Retail GOB markdowns</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H67" s="15" t="n"/>
-      <c r="I67" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="J67" s="13" t="inlineStr"/>
+      <c r="I67" s="13" t="inlineStr"/>
+      <c r="J67" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-26 07:30 PM ET</t>
+        </is>
+      </c>
       <c r="K67" s="13" t="inlineStr">
         <is>
-          <t>SB360 (PR Newswire)</t>
+          <t>Cash Auctions</t>
         </is>
       </c>
       <c r="L67" s="13" t="inlineStr">
@@ -22165,19 +22095,19 @@
       </c>
       <c r="O67" s="14" t="inlineStr">
         <is>
-          <t>Posted Oct 8. Multi-state (VA/AZ/GA/IL/TX); pinned at Virginia Beach. Home goods only.</t>
+          <t>Lots not reviewed.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="17" t="inlineStr">
         <is>
-          <t>Subtotal — Virginia</t>
+          <t>Subtotal — Upstate / Western NY</t>
         </is>
       </c>
       <c r="B68" s="17" t="inlineStr">
         <is>
-          <t>1 item(s)</t>
+          <t>2 item(s)</t>
         </is>
       </c>
       <c r="C68" s="18" t="n"/>
@@ -22199,7 +22129,7 @@
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>▸ Midwest  (3)</t>
+          <t>▸ Virginia  (1)</t>
         </is>
       </c>
       <c r="B69" s="12" t="n"/>
@@ -22220,52 +22150,52 @@
     <row r="70" outlineLevel="1">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>Freshway Market whole-grocery liquidation – refrigeration racks, cases, walk-ins, generator</t>
+          <t>Haynes Furniture / The Dump – 12 stores closing (furniture, mattresses)</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>retail GOB</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Virginia Beach</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>862</v>
+        <v>456</v>
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Retail GOB markdowns</t>
         </is>
       </c>
       <c r="H70" s="15" t="n"/>
-      <c r="I70" s="13" t="inlineStr"/>
-      <c r="J70" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-20 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I70" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="J70" s="13" t="inlineStr"/>
       <c r="K70" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L70" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>SB360 (PR Newswire)</t>
+        </is>
+      </c>
+      <c r="L70" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M70" s="13" t="inlineStr"/>
@@ -22276,233 +22206,233 @@
       </c>
       <c r="O70" s="14" t="inlineStr">
         <is>
+          <t>Posted Oct 8. Multi-state (VA/AZ/GA/IL/TX); pinned at Virginia Beach. Home goods only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Virginia</t>
+        </is>
+      </c>
+      <c r="B71" s="17" t="inlineStr">
+        <is>
+          <t>1 item(s)</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="n"/>
+      <c r="D71" s="18" t="n"/>
+      <c r="E71" s="18" t="n"/>
+      <c r="F71" s="18" t="n"/>
+      <c r="G71" s="18" t="n"/>
+      <c r="H71" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="18" t="n"/>
+      <c r="J71" s="18" t="n"/>
+      <c r="K71" s="18" t="n"/>
+      <c r="L71" s="18" t="n"/>
+      <c r="M71" s="18" t="n"/>
+      <c r="N71" s="18" t="n"/>
+      <c r="O71" s="18" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>▸ Midwest  (3)</t>
+        </is>
+      </c>
+      <c r="B72" s="12" t="n"/>
+      <c r="C72" s="12" t="n"/>
+      <c r="D72" s="12" t="n"/>
+      <c r="E72" s="12" t="n"/>
+      <c r="F72" s="12" t="n"/>
+      <c r="G72" s="12" t="n"/>
+      <c r="H72" s="12" t="n"/>
+      <c r="I72" s="12" t="n"/>
+      <c r="J72" s="12" t="n"/>
+      <c r="K72" s="12" t="n"/>
+      <c r="L72" s="12" t="n"/>
+      <c r="M72" s="12" t="n"/>
+      <c r="N72" s="12" t="n"/>
+      <c r="O72" s="12" t="n"/>
+    </row>
+    <row r="73" outlineLevel="1">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>Freshway Market whole-grocery liquidation – refrigeration racks, cases, walk-ins, generator</t>
+        </is>
+      </c>
+      <c r="C73" s="13" t="inlineStr">
+        <is>
+          <t>store closing</t>
+        </is>
+      </c>
+      <c r="D73" s="13" t="inlineStr">
+        <is>
+          <t>Chicago</t>
+        </is>
+      </c>
+      <c r="E73" s="13" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="F73" s="13" t="n">
+        <v>862</v>
+      </c>
+      <c r="G73" s="13" t="inlineStr">
+        <is>
+          <t>Online auction</t>
+        </is>
+      </c>
+      <c r="H73" s="15" t="n"/>
+      <c r="I73" s="13" t="inlineStr"/>
+      <c r="J73" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K73" s="13" t="inlineStr">
+        <is>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L73" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M73" s="13" t="inlineStr"/>
+      <c r="N73" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O73" s="14" t="inlineStr">
+        <is>
           <t>Closes from Oct 20 10 AM CDT.</t>
         </is>
       </c>
     </row>
-    <row r="71" outlineLevel="1">
-      <c r="A71" s="13" t="inlineStr">
+    <row r="74" outlineLevel="1">
+      <c r="A74" s="13" t="inlineStr">
         <is>
           <t>Midwest</t>
         </is>
       </c>
-      <c r="B71" s="14" t="inlineStr">
+      <c r="B74" s="14" t="inlineStr">
         <is>
           <t>American Sale – total liquidation, all 7 stores (pools, hot tubs, grills, holiday decor)</t>
         </is>
       </c>
-      <c r="C71" s="13" t="inlineStr">
+      <c r="C74" s="13" t="inlineStr">
         <is>
           <t>retail GOB</t>
         </is>
       </c>
-      <c r="D71" s="13" t="inlineStr">
+      <c r="D74" s="13" t="inlineStr">
         <is>
           <t>Chicagoland</t>
         </is>
       </c>
-      <c r="E71" s="13" t="inlineStr">
+      <c r="E74" s="13" t="inlineStr">
         <is>
           <t>IL</t>
         </is>
       </c>
-      <c r="F71" s="13" t="n">
+      <c r="F74" s="13" t="n">
         <v>876</v>
       </c>
-      <c r="G71" s="13" t="inlineStr">
+      <c r="G74" s="13" t="inlineStr">
         <is>
           <t>Retail GOB, up to 70% off</t>
         </is>
       </c>
-      <c r="H71" s="15" t="n"/>
-      <c r="I71" s="13" t="inlineStr">
+      <c r="H74" s="15" t="n"/>
+      <c r="I74" s="13" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="J71" s="13" t="inlineStr"/>
-      <c r="K71" s="13" t="inlineStr">
+      <c r="J74" s="13" t="inlineStr"/>
+      <c r="K74" s="13" t="inlineStr">
         <is>
           <t>Tiger Group (PR Newswire)</t>
         </is>
       </c>
-      <c r="L71" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M71" s="13" t="inlineStr"/>
-      <c r="N71" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O71" s="14" t="inlineStr">
+      <c r="L74" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M74" s="13" t="inlineStr"/>
+      <c r="N74" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O74" s="14" t="inlineStr">
         <is>
           <t>Posted Oct 15. Watch for a bulk/fixture auction.</t>
         </is>
       </c>
-    </row>
-    <row r="72" outlineLevel="1">
-      <c r="A72" s="13" t="inlineStr">
-        <is>
-          <t>Midwest</t>
-        </is>
-      </c>
-      <c r="B72" s="14" t="inlineStr">
-        <is>
-          <t>Straub's Fine Foods store equipment – bakery, kitchen, meat room, Hussmann refrigeration</t>
-        </is>
-      </c>
-      <c r="C72" s="13" t="inlineStr">
-        <is>
-          <t>grocery/restaurant</t>
-        </is>
-      </c>
-      <c r="D72" s="13" t="inlineStr">
-        <is>
-          <t>St. Louis</t>
-        </is>
-      </c>
-      <c r="E72" s="13" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="F72" s="13" t="n">
-        <v>1046</v>
-      </c>
-      <c r="G72" s="13" t="inlineStr">
-        <is>
-          <t>Online auction (18% BP)</t>
-        </is>
-      </c>
-      <c r="H72" s="15" t="n"/>
-      <c r="I72" s="13" t="inlineStr"/>
-      <c r="J72" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 11:00 AM ET</t>
-        </is>
-      </c>
-      <c r="K72" s="13" t="inlineStr">
-        <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L72" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M72" s="13" t="inlineStr"/>
-      <c r="N72" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O72" s="14" t="inlineStr">
-        <is>
-          <t>Kingshighway store: Revent double-rack oven + proofer, Reed revolving oven, Vulcan convection, Groen kettle, Southbend 6-burner, Pitco fryer, Stero dishwasher, Hobart saw/grinders, Berkel slicers, Hussmann cases + compressor racks, walk-ins, Hoshizaki/Scotsman ice machines, Crown pallet jack. Preview Oct 20 3–6 PM CDT; pickup in St. Louis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Midwest</t>
-        </is>
-      </c>
-      <c r="B73" s="17" t="inlineStr">
-        <is>
-          <t>3 item(s)</t>
-        </is>
-      </c>
-      <c r="C73" s="18" t="n"/>
-      <c r="D73" s="18" t="n"/>
-      <c r="E73" s="18" t="n"/>
-      <c r="F73" s="18" t="n"/>
-      <c r="G73" s="18" t="n"/>
-      <c r="H73" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="18" t="n"/>
-      <c r="J73" s="18" t="n"/>
-      <c r="K73" s="18" t="n"/>
-      <c r="L73" s="18" t="n"/>
-      <c r="M73" s="18" t="n"/>
-      <c r="N73" s="18" t="n"/>
-      <c r="O73" s="18" t="n"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="11" t="inlineStr">
-        <is>
-          <t>▸ Texas / South Central  (1)</t>
-        </is>
-      </c>
-      <c r="B74" s="12" t="n"/>
-      <c r="C74" s="12" t="n"/>
-      <c r="D74" s="12" t="n"/>
-      <c r="E74" s="12" t="n"/>
-      <c r="F74" s="12" t="n"/>
-      <c r="G74" s="12" t="n"/>
-      <c r="H74" s="12" t="n"/>
-      <c r="I74" s="12" t="n"/>
-      <c r="J74" s="12" t="n"/>
-      <c r="K74" s="12" t="n"/>
-      <c r="L74" s="12" t="n"/>
-      <c r="M74" s="12" t="n"/>
-      <c r="N74" s="12" t="n"/>
-      <c r="O74" s="12" t="n"/>
     </row>
     <row r="75" outlineLevel="1">
       <c r="A75" s="13" t="inlineStr">
         <is>
-          <t>Texas / South Central</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>Southwest beverage distributor surplus – mostly unused: 16 True merchandisers, 75 Bunn brewers, 100+ micro-market kiosks</t>
+          <t>Straub's Fine Foods store equipment – bakery, kitchen, meat room, Hussmann refrigeration</t>
         </is>
       </c>
       <c r="C75" s="13" t="inlineStr">
         <is>
-          <t>distributor surplus</t>
+          <t>grocery/restaurant</t>
         </is>
       </c>
       <c r="D75" s="13" t="inlineStr">
         <is>
-          <t>Mesquite</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="F75" s="13" t="n">
-        <v>1547</v>
+        <v>1046</v>
       </c>
       <c r="G75" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Online auction (18% BP)</t>
         </is>
       </c>
       <c r="H75" s="15" t="n"/>
       <c r="I75" s="13" t="inlineStr"/>
       <c r="J75" s="13" t="inlineStr">
         <is>
-          <t>2026-11-13 11:00 AM ET</t>
+          <t>2026-10-21 11:00 AM ET</t>
         </is>
       </c>
       <c r="K75" s="13" t="inlineStr">
         <is>
-          <t>Heritage Global Partners</t>
-        </is>
-      </c>
-      <c r="L75" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L75" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M75" s="13" t="inlineStr"/>
@@ -22513,19 +22443,19 @@
       </c>
       <c r="O75" s="14" t="inlineStr">
         <is>
-          <t>Near-new appliances, resell by unit. Nov 13 10 AM CST.</t>
+          <t>Kingshighway store: Revent double-rack oven + proofer, Reed revolving oven, Vulcan convection, Groen kettle, Southbend 6-burner, Pitco fryer, Stero dishwasher, Hobart saw/grinders, Berkel slicers, Hussmann cases + compressor racks, walk-ins, Hoshizaki/Scotsman ice machines, Crown pallet jack. Preview Oct 20 3–6 PM CDT; pickup in St. Louis.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="17" t="inlineStr">
         <is>
-          <t>Subtotal — Texas / South Central</t>
+          <t>Subtotal — Midwest</t>
         </is>
       </c>
       <c r="B76" s="17" t="inlineStr">
         <is>
-          <t>1 item(s)</t>
+          <t>3 item(s)</t>
         </is>
       </c>
       <c r="C76" s="18" t="n"/>
@@ -22547,7 +22477,7 @@
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t>▸ West / Other  (1)</t>
+          <t>▸ Texas / South Central  (1)</t>
         </is>
       </c>
       <c r="B77" s="12" t="n"/>
@@ -22568,47 +22498,47 @@
     <row r="78" outlineLevel="1">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>West / Other</t>
+          <t>Texas / South Central</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>National salad concept liquidation – full contents of 63 fast-casual restaurants (AZ/TX/OK/NV)</t>
+          <t>Southwest beverage distributor surplus – mostly unused: 16 True merchandisers, 75 Bunn brewers, 100+ micro-market kiosks</t>
         </is>
       </c>
       <c r="C78" s="13" t="inlineStr">
         <is>
-          <t>restaurant chain liquidation</t>
+          <t>distributor surplus</t>
         </is>
       </c>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Mesquite</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>2307</v>
+        <v>1547</v>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
-          <t>Online auctions, dates TBD</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H78" s="15" t="n"/>
-      <c r="I78" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="J78" s="13" t="inlineStr"/>
+      <c r="I78" s="13" t="inlineStr"/>
+      <c r="J78" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-13 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K78" s="13" t="inlineStr">
         <is>
-          <t>RestaurantEquipment.bid (TAGeX)</t>
+          <t>Heritage Global Partners</t>
         </is>
       </c>
       <c r="L78" s="13" t="inlineStr">
@@ -22624,14 +22554,14 @@
       </c>
       <c r="O78" s="14" t="inlineStr">
         <is>
-          <t>Rolling market-by-market auctions, none live yet (Phoenix metro 30 locations, DFW 14, Tucson 6, Houston 5, plus OK/NV). Pickup on site at each restaurant. Pinned at Phoenix.</t>
+          <t>Near-new appliances, resell by unit. Nov 13 10 AM CST.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="17" t="inlineStr">
         <is>
-          <t>Subtotal — West / Other</t>
+          <t>Subtotal — Texas / South Central</t>
         </is>
       </c>
       <c r="B79" s="17" t="inlineStr">
@@ -22655,8 +22585,119 @@
       <c r="N79" s="18" t="n"/>
       <c r="O79" s="18" t="n"/>
     </row>
+    <row r="80">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t>▸ West / Other  (1)</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="n"/>
+      <c r="C80" s="12" t="n"/>
+      <c r="D80" s="12" t="n"/>
+      <c r="E80" s="12" t="n"/>
+      <c r="F80" s="12" t="n"/>
+      <c r="G80" s="12" t="n"/>
+      <c r="H80" s="12" t="n"/>
+      <c r="I80" s="12" t="n"/>
+      <c r="J80" s="12" t="n"/>
+      <c r="K80" s="12" t="n"/>
+      <c r="L80" s="12" t="n"/>
+      <c r="M80" s="12" t="n"/>
+      <c r="N80" s="12" t="n"/>
+      <c r="O80" s="12" t="n"/>
+    </row>
+    <row r="81" outlineLevel="1">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>West / Other</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>National salad concept liquidation – full contents of 63 fast-casual restaurants (AZ/TX/OK/NV)</t>
+        </is>
+      </c>
+      <c r="C81" s="13" t="inlineStr">
+        <is>
+          <t>restaurant chain liquidation</t>
+        </is>
+      </c>
+      <c r="D81" s="13" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="E81" s="13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="F81" s="13" t="n">
+        <v>2307</v>
+      </c>
+      <c r="G81" s="13" t="inlineStr">
+        <is>
+          <t>Online auctions, dates TBD</t>
+        </is>
+      </c>
+      <c r="H81" s="15" t="n"/>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="J81" s="13" t="inlineStr"/>
+      <c r="K81" s="13" t="inlineStr">
+        <is>
+          <t>RestaurantEquipment.bid (TAGeX)</t>
+        </is>
+      </c>
+      <c r="L81" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M81" s="13" t="inlineStr"/>
+      <c r="N81" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O81" s="14" t="inlineStr">
+        <is>
+          <t>Rolling market-by-market auctions, none live yet (Phoenix metro 30 locations, DFW 14, Tucson 6, Houston 5, plus OK/NV). Pickup on site at each restaurant. Pinned at Phoenix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — West / Other</t>
+        </is>
+      </c>
+      <c r="B82" s="17" t="inlineStr">
+        <is>
+          <t>1 item(s)</t>
+        </is>
+      </c>
+      <c r="C82" s="18" t="n"/>
+      <c r="D82" s="18" t="n"/>
+      <c r="E82" s="18" t="n"/>
+      <c r="F82" s="18" t="n"/>
+      <c r="G82" s="18" t="n"/>
+      <c r="H82" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="18" t="n"/>
+      <c r="J82" s="18" t="n"/>
+      <c r="K82" s="18" t="n"/>
+      <c r="L82" s="18" t="n"/>
+      <c r="M82" s="18" t="n"/>
+      <c r="N82" s="18" t="n"/>
+      <c r="O82" s="18" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:O79"/>
+  <autoFilter ref="A1:O82"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId2"/>
@@ -22680,7 +22721,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId26"/>
@@ -22702,16 +22743,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N62" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N60" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N64" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N66" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N67" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N71" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N72" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N73" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N74" r:id="rId52"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N75" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N78" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N81" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22723,7 +22765,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -22823,52 +22865,58 @@
     <row r="2">
       <c r="A2" s="13" t="inlineStr">
         <is>
-          <t>Western PA / Ohio Valley</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="B2" s="14" t="inlineStr">
         <is>
-          <t>Allshouse Appliance Store &amp; Warehouse Dispersal (mostly whole units, racking, forklift)</t>
+          <t>Misc. appliance parts pallet (parts only)</t>
         </is>
       </c>
       <c r="C2" s="13" t="inlineStr">
         <is>
-          <t>auction / dispersal</t>
+          <t>auction pallet</t>
         </is>
       </c>
       <c r="D2" s="13" t="inlineStr">
         <is>
-          <t>New Castle</t>
+          <t>Dalton</t>
         </is>
       </c>
       <c r="E2" s="13" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="F2" s="13" t="n">
-        <v>499</v>
+        <v>917</v>
       </c>
       <c r="G2" s="13" t="inlineStr">
         <is>
-          <t>Auction – 5% BP (waived for cash)</t>
-        </is>
-      </c>
-      <c r="H2" s="15" t="n"/>
-      <c r="I2" s="13" t="inlineStr"/>
+          <t>$50 high bid + 15% BP</t>
+        </is>
+      </c>
+      <c r="H2" s="15" t="n">
+        <v>50</v>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
       <c r="J2" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 04:00 PM ET</t>
+          <t>2026-10-19 09:18 PM ET</t>
         </is>
       </c>
       <c r="K2" s="13" t="inlineStr">
         <is>
-          <t>Duke Whiting Auctions</t>
+          <t>HiBid</t>
         </is>
       </c>
       <c r="L2" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 04:00 PM ET)</t>
+          <t>EXPIRED (2026-10-19 09:18 PM ET)</t>
         </is>
       </c>
       <c r="M2" s="13" t="inlineStr"/>
@@ -22879,61 +22927,59 @@
       </c>
       <c r="O2" s="14" t="inlineStr">
         <is>
-          <t>Live auction Mon Oct 19 4 PM, 3457 Wilmington Rd. Few bulk parts. [Live auction held Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed]</t>
+          <t>Integrity Auction House. Internet bidding closes Mon Oct 19 9:18 PM ET. $50 high bid (1 bid) as of 2026-10-18. [Closed Oct 19; HiBid price realized $50.] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="13" t="inlineStr">
         <is>
-          <t>Greater Boston / South Shore (&lt;50mi)</t>
+          <t>Western PA / Ohio Valley</t>
         </is>
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>Wolf Gourmet Coffee Maker WGCM100S (stainless)</t>
+          <t>Allshouse Appliance Store &amp; Warehouse Dispersal (mostly whole units, racking, forklift)</t>
         </is>
       </c>
       <c r="C3" s="13" t="inlineStr">
         <is>
-          <t>countertop</t>
+          <t>auction / dispersal</t>
         </is>
       </c>
       <c r="D3" s="13" t="inlineStr">
         <is>
-          <t>Malden</t>
+          <t>New Castle</t>
         </is>
       </c>
       <c r="E3" s="13" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>25</v>
+        <v>499</v>
       </c>
       <c r="G3" s="13" t="inlineStr">
         <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="H3" s="15" t="n">
-        <v>150</v>
-      </c>
-      <c r="I3" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="J3" s="13" t="inlineStr"/>
+          <t>Auction – 5% BP (waived for cash)</t>
+        </is>
+      </c>
+      <c r="H3" s="15" t="n"/>
+      <c r="I3" s="13" t="inlineStr"/>
+      <c r="J3" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 04:00 PM ET</t>
+        </is>
+      </c>
       <c r="K3" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>Duke Whiting Auctions</t>
         </is>
       </c>
       <c r="L3" s="13" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>EXPIRED (2026-10-19 04:00 PM ET)</t>
         </is>
       </c>
       <c r="M3" s="13" t="inlineStr"/>
@@ -22944,7 +22990,7 @@
       </c>
       <c r="O3" s="14" t="inlineStr">
         <is>
-          <t>Condition not stated. | Removed 2026-10-18: Craigslist posting deleted (HTTP 410).</t>
+          <t>Live auction Mon Oct 19 4 PM, 3457 Wilmington Rd. Few bulk parts. [Live auction held Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -22956,17 +23002,17 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>wolf gas cooktop</t>
+          <t>Wolf Gourmet Coffee Maker WGCM100S (stainless)</t>
         </is>
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>range/oven/rangetop</t>
+          <t>countertop</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>Winchester</t>
+          <t>Malden</t>
         </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
@@ -22975,19 +23021,19 @@
         </is>
       </c>
       <c r="F4" s="13" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G4" s="13" t="inlineStr">
         <is>
-          <t>$275</t>
+          <t>$150</t>
         </is>
       </c>
       <c r="H4" s="15" t="n">
-        <v>275</v>
+        <v>150</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="J4" s="13" t="inlineStr"/>
@@ -23001,11 +23047,7 @@
           <t>REMOVED</t>
         </is>
       </c>
-      <c r="M4" s="21" t="inlineStr">
-        <is>
-          <t>FLIP</t>
-        </is>
-      </c>
+      <c r="M4" s="13" t="inlineStr"/>
       <c r="N4" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -23013,19 +23055,19 @@
       </c>
       <c r="O4" s="14" t="inlineStr">
         <is>
-          <t>Condition: used. FLIP: 36" gas cooktop $275, missing pads; rough resale $600-900 | Removed 2026-10-18: Craigslist posting deleted (HTTP 410).</t>
+          <t>Condition not stated. | Removed 2026-10-18: Craigslist posting deleted (HTTP 410).</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="13" t="inlineStr">
         <is>
-          <t>Unknown location</t>
+          <t>Greater Boston / South Shore (&lt;50mi)</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>Wolf 36” Single Electric Wall Built-In Oven SO36U/S - Tested Work</t>
+          <t>wolf gas cooktop</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
@@ -23035,37 +23077,39 @@
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Winchester</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="13" t="n"/>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="F5" s="13" t="n">
+        <v>29</v>
+      </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>$99</t>
+          <t>$275</t>
         </is>
       </c>
       <c r="H5" s="15" t="n">
-        <v>99</v>
-      </c>
-      <c r="I5" s="13" t="inlineStr"/>
-      <c r="J5" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-18 02:19 PM ET</t>
-        </is>
-      </c>
+        <v>275</v>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J5" s="13" t="inlineStr"/>
       <c r="K5" s="13" t="inlineStr">
         <is>
-          <t>eBay (pickup only, over 60 mi)</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L5" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-18 02:19 PM ET)</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="M5" s="21" t="inlineStr">
@@ -23080,19 +23124,19 @@
       </c>
       <c r="O5" s="14" t="inlineStr">
         <is>
-          <t>Condition: Pre-Owned. FLIP: SO36U/S tested, auction $99/0 bids, pickup only; rough resale $600-1k (eBay card shows no city; pickup distance in source.) Ends Oct 18 ~2:19 PM per eBay card (time zone uncertain; could be earlier). [auto-removed 2026-10-18: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed]</t>
+          <t>Condition: used. FLIP: 36" gas cooktop $275, missing pads; rough resale $600-900 | Removed 2026-10-18: Craigslist posting deleted (HTTP 410).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="13" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>Unknown location</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>Wolf Oven Six Burner Combo</t>
+          <t>Wolf 36” Single Electric Wall Built-In Oven SO36U/S - Tested Work</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
@@ -23102,42 +23146,44 @@
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Anderson</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="F6" s="13" t="n">
-        <v>785</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="13" t="n"/>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>$3 current bid + BP</t>
+          <t>$99</t>
         </is>
       </c>
       <c r="H6" s="15" t="n">
-        <v>3</v>
+        <v>99</v>
       </c>
       <c r="I6" s="13" t="inlineStr"/>
       <c r="J6" s="13" t="inlineStr">
         <is>
-          <t>2026-10-18 08:54 PM ET</t>
+          <t>2026-10-18 02:19 PM ET</t>
         </is>
       </c>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>HiBid</t>
+          <t>eBay (pickup only, over 60 mi)</t>
         </is>
       </c>
       <c r="L6" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-18 08:54 PM ET)</t>
-        </is>
-      </c>
-      <c r="M6" s="13" t="inlineStr"/>
+          <t>EXPIRED (2026-10-18 02:19 PM ET)</t>
+        </is>
+      </c>
+      <c r="M6" s="21" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
       <c r="N6" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -23145,61 +23191,61 @@
       </c>
       <c r="O6" s="14" t="inlineStr">
         <is>
-          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf) HiBid lot closed/sold ~$37.50 on 2026-10-18. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed]</t>
+          <t>Condition: Pre-Owned. FLIP: SO36U/S tested, auction $99/0 bids, pickup only; rough resale $600-1k (eBay card shows no city; pickup distance in source.) Ends Oct 18 ~2:19 PM per eBay card (time zone uncertain; could be earlier). [auto-removed 2026-10-18: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="13" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Louisville)</t>
+          <t>Wolf Oven Six Burner Combo</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>auction catalog</t>
+          <t>range/oven/rangetop</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>Anderson</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
-          <t>KY</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>832</v>
+        <v>785</v>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>$0–1 openers + 15% BP + $1/lot</t>
+          <t>$3 current bid + BP</t>
         </is>
       </c>
       <c r="H7" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I7" s="13" t="inlineStr"/>
       <c r="J7" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 02:00 PM ET</t>
+          <t>2026-10-18 08:54 PM ET</t>
         </is>
       </c>
       <c r="K7" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Auctionfuel)</t>
+          <t>HiBid</t>
         </is>
       </c>
       <c r="L7" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 02:00 PM ET)</t>
+          <t>EXPIRED (2026-10-18 08:54 PM ET)</t>
         </is>
       </c>
       <c r="M7" s="13" t="inlineStr"/>
@@ -23210,59 +23256,61 @@
       </c>
       <c r="O7" s="14" t="inlineStr">
         <is>
-          <t>Lots close from Oct 19 2 PM ET. [HiBid catalog closed 2 PM ET Oct 19.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed]</t>
+          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf) HiBid lot closed/sold ~$37.50 on 2026-10-18. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>Maine / VT / Northern NH</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>Oola Bowls secured-party sale – restaurant equipment bought new 2024-25 (Electro Freeze, Scotsman, Atosa)</t>
+          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Louisville)</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>auction catalog</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>Scarborough</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>ME</t>
+          <t>KY</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>104</v>
+        <v>832</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
-          <t>Online auction (freezers $80–150 when seen)</t>
-        </is>
-      </c>
-      <c r="H8" s="15" t="n"/>
+          <t>$0–1 openers + 15% BP + $1/lot</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="I8" s="13" t="inlineStr"/>
       <c r="J8" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00 PM ET</t>
+          <t>2026-10-19 02:00 PM ET</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
         <is>
-          <t>Keenan Auction / Proxibid</t>
+          <t>HiBid (Auctionfuel)</t>
         </is>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 01:00 PM ET)</t>
+          <t>EXPIRED (2026-10-19 02:00 PM ET)</t>
         </is>
       </c>
       <c r="M8" s="13" t="inlineStr"/>
@@ -23273,59 +23321,59 @@
       </c>
       <c r="O8" s="14" t="inlineStr">
         <is>
-          <t>Pickup Oct 21 only. [Lots began closing 1 PM ET Oct 19; ended.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed]</t>
+          <t>Lots close from Oct 19 2 PM ET. [HiBid catalog closed 2 PM ET Oct 19.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>NYC / Long Island / NJ</t>
+          <t>Maine / VT / Northern NH</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>Milwaukee / Walmart / hardware store mega auction pt 3</t>
+          <t>Oola Bowls secured-party sale – restaurant equipment bought new 2024-25 (Electro Freeze, Scotsman, Atosa)</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>Mount Holly</t>
+          <t>Scarborough</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>254</v>
+        <v>104</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>HiBid online auction</t>
+          <t>Online auction (freezers $80–150 when seen)</t>
         </is>
       </c>
       <c r="H9" s="15" t="n"/>
       <c r="I9" s="13" t="inlineStr"/>
       <c r="J9" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 06:00 PM ET</t>
+          <t>2026-10-19 01:00 PM ET</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>HiBid</t>
+          <t>Keenan Auction / Proxibid</t>
         </is>
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 06:00 PM ET)</t>
+          <t>EXPIRED (2026-10-19 01:00 PM ET)</t>
         </is>
       </c>
       <c r="M9" s="13" t="inlineStr"/>
@@ -23336,59 +23384,59 @@
       </c>
       <c r="O9" s="14" t="inlineStr">
         <is>
-          <t>Close Oct 18 or 19 6 PM (later used). [auto-removed 2026-10-19: closing date passed]</t>
+          <t>Pickup Oct 21 only. [Lots began closing 1 PM ET Oct 19; ended.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>Greater Boston / South Shore (&lt;50mi)</t>
+          <t>NYC / Long Island / NJ</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>Closed Best Buy Outlet – pallet racking, Big Joe order pickers, appliance dollies, carts, cages</t>
+          <t>Milwaukee / Walmart / hardware store mega auction pt 3</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>store closing fixtures</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>Brockton</t>
+          <t>Mount Holly</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>11</v>
+        <v>254</v>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>Racking $40/upright, $80/level; pickers $1,000 OBO</t>
+          <t>HiBid online auction</t>
         </is>
       </c>
       <c r="H10" s="15" t="n"/>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="J10" s="13" t="inlineStr"/>
+      <c r="I10" s="13" t="inlineStr"/>
+      <c r="J10" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 06:00 PM ET</t>
+        </is>
+      </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>HiBid</t>
         </is>
       </c>
       <c r="L10" s="13" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>EXPIRED (2026-10-19 06:00 PM ET)</t>
         </is>
       </c>
       <c r="M10" s="13" t="inlineStr"/>
@@ -23399,29 +23447,29 @@
       </c>
       <c r="O10" s="14" t="inlineStr">
         <is>
-          <t>200 Westgate Dr. Fixtures/equipment only, no merchandise. On site daily. CL deleted by author (HTTP 410) as of 2026-10-19 midday recheck.</t>
+          <t>Close Oct 18 or 19 6 PM (later used). [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>NYC / Long Island / NJ</t>
+          <t>Upstate / Western NY</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>Like-new restaurant – steam tables, Coldline, Cleveland cook-and-hold, fryers, True freezers</t>
+          <t>Closed restaurant – coolers, fridges, prep tables</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Staten Island</t>
+          <t>Palmyra</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
@@ -23430,32 +23478,28 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>203</v>
+        <v>333</v>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>HiBid, 15% BP</t>
         </is>
       </c>
       <c r="H11" s="15" t="n"/>
-      <c r="I11" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+      <c r="I11" s="13" t="inlineStr"/>
       <c r="J11" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00 PM ET</t>
+          <t>2026-10-19 07:00 PM ET</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>Reynolds Auction Co / HiBid</t>
         </is>
       </c>
       <c r="L11" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 01:00 PM ET)</t>
+          <t>EXPIRED (2026-10-19 07:00 PM ET)</t>
         </is>
       </c>
       <c r="M11" s="13" t="inlineStr"/>
@@ -23466,63 +23510,59 @@
       </c>
       <c r="O11" s="14" t="inlineStr">
         <is>
-          <t>"Short notice" auction Mon Oct 19 1 PM. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed]</t>
+          <t>No new out-of-state bidders. Small. [Ended Oct 19 7 PM.] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>NYC / Long Island / NJ</t>
+          <t>Greater Boston / South Shore (&lt;50mi)</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>High-end deli (contents not described)</t>
+          <t>Closed Best Buy Outlet – pallet racking, Big Joe order pickers, appliance dollies, carts, cages</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>store closing fixtures</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>Manalapan Township</t>
+          <t>Brockton</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>223</v>
+        <v>11</v>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Racking $40/upright, $80/level; pickers $1,000 OBO</t>
         </is>
       </c>
       <c r="H12" s="15" t="n"/>
       <c r="I12" s="13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="J12" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-19 04:00 PM ET</t>
-        </is>
-      </c>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr"/>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L12" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 04:00 PM ET)</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="M12" s="13" t="inlineStr"/>
@@ -23533,12 +23573,146 @@
       </c>
       <c r="O12" s="14" t="inlineStr">
         <is>
-          <t>Mon Oct 19 4 PM. No item description on page. [HiBid shows Bidding Closed, Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed]</t>
+          <t>200 Westgate Dr. Fixtures/equipment only, no merchandise. On site daily. CL deleted by author (HTTP 410) as of 2026-10-19 midday recheck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Like-new restaurant – steam tables, Coldline, Cleveland cook-and-hold, fryers, True freezers</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>auction</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>Staten Island</t>
+        </is>
+      </c>
+      <c r="E13" s="13" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F13" s="13" t="n">
+        <v>203</v>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>Live + webcast, 18% BP + 3%</t>
+        </is>
+      </c>
+      <c r="H13" s="15" t="n"/>
+      <c r="I13" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 01:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K13" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L13" s="13" t="inlineStr">
+        <is>
+          <t>EXPIRED (2026-10-19 01:00 PM ET)</t>
+        </is>
+      </c>
+      <c r="M13" s="13" t="inlineStr"/>
+      <c r="N13" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O13" s="14" t="inlineStr">
+        <is>
+          <t>"Short notice" auction Mon Oct 19 1 PM. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>High-end deli (contents not described)</t>
+        </is>
+      </c>
+      <c r="C14" s="13" t="inlineStr">
+        <is>
+          <t>restaurant closing</t>
+        </is>
+      </c>
+      <c r="D14" s="13" t="inlineStr">
+        <is>
+          <t>Manalapan Township</t>
+        </is>
+      </c>
+      <c r="E14" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F14" s="13" t="n">
+        <v>223</v>
+      </c>
+      <c r="G14" s="13" t="inlineStr">
+        <is>
+          <t>Live + webcast, 18% BP + 3%</t>
+        </is>
+      </c>
+      <c r="H14" s="15" t="n"/>
+      <c r="I14" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J14" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 04:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K14" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L14" s="13" t="inlineStr">
+        <is>
+          <t>EXPIRED (2026-10-19 04:00 PM ET)</t>
+        </is>
+      </c>
+      <c r="M14" s="13" t="inlineStr"/>
+      <c r="N14" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O14" s="14" t="inlineStr">
+        <is>
+          <t>Mon Oct 19 4 PM. No item description on page. [HiBid shows Bidding Closed, Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O12"/>
+  <autoFilter ref="A1:O14"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -23551,6 +23725,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId13"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lot_recon.xlsx
+++ b/lot_recon.xlsx
@@ -20,8 +20,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wolf New'!$A$1:$O$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wolf Used'!$A$1:$O$189</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Wolf Unclear'!$A$1:$O$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$82</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Removed'!$A$1:$O$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Removed'!$A$1:$O$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -577,7 +577,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Last updated: 2026-10-20 08:03 ET</t>
+          <t>Last updated: 2026-10-20 11:04 ET</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Active listings: 293 · Removed: 13</t>
+          <t>Active listings: 295 · Removed: 14</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
         <v>164</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>608011.6</v>
+        <v>608022.6</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
@@ -695,7 +695,7 @@
         <v>31</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>137840</v>
+        <v>137850</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -708,13 +708,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>980382.58</v>
+        <v>980403.58</v>
       </c>
     </row>
     <row r="15">
@@ -1007,7 +1007,7 @@
         <v>9</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>64740</v>
+        <v>64751</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -1037,7 +1037,7 @@
         <v>24</v>
       </c>
       <c r="G24" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>440141</v>
@@ -1073,7 +1073,7 @@
         <v>1</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>1515</v>
+        <v>1525</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
         <v>2</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" s="6" t="n">
         <v>5</v>
@@ -6860,11 +6860,11 @@
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t>$90 high bid (16 bids)</t>
+          <t>$101 high bid (17 bids)</t>
         </is>
       </c>
       <c r="H34" s="15" t="n">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="I34" s="13" t="inlineStr"/>
       <c r="J34" s="13" t="inlineStr">
@@ -7667,7 +7667,7 @@
       <c r="F47" s="18" t="n"/>
       <c r="G47" s="18" t="n"/>
       <c r="H47" s="19" t="n">
-        <v>33140</v>
+        <v>33151</v>
       </c>
       <c r="I47" s="18" t="n"/>
       <c r="J47" s="18" t="n"/>
@@ -18194,11 +18194,11 @@
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
-          <t>$15 high bid</t>
+          <t>$25 high bid (9 bids)</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I35" s="13" t="inlineStr"/>
       <c r="J35" s="13" t="inlineStr">
@@ -18245,7 +18245,7 @@
       <c r="F36" s="18" t="n"/>
       <c r="G36" s="18" t="n"/>
       <c r="H36" s="19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="I36" s="18" t="n"/>
       <c r="J36" s="18" t="n"/>
@@ -18478,7 +18478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O82"/>
+  <dimension ref="A1:O84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -20275,7 +20275,7 @@
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>▸ NYC / Long Island / NJ  (22)</t>
+          <t>▸ NYC / Long Island / NJ  (25)</t>
         </is>
       </c>
       <c r="B35" s="12" t="n"/>
@@ -20687,17 +20687,17 @@
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>Tools / plumbing / MRO supply inventory – Hilti/DeWalt/Milwaukee, fittings, heat pumps</t>
+          <t>Baonanas LLC ABC sale: turnkey ice cream / gelato / dessert shop equipment</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>restaurant / commercial kitchen contents</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>Riverdale</t>
+          <t>Jersey City</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -20706,23 +20706,19 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Accepting offers</t>
         </is>
       </c>
       <c r="H42" s="15" t="n"/>
       <c r="I42" s="13" t="inlineStr"/>
-      <c r="J42" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-30 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="J42" s="13" t="inlineStr"/>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>AuctionAdvisors</t>
         </is>
       </c>
       <c r="L42" s="13" t="inlineStr">
@@ -20738,7 +20734,7 @@
       </c>
       <c r="O42" s="14" t="inlineStr">
         <is>
-          <t>Bulk resale inventory.</t>
+          <t>181 Monticello Ave. Assignment for the benefit of creditors. IFI Panorama gelato display cases, refrigerated topping stations, commercial mixers, refrigerators/freezers, stainless worktables, ice machine, POS, smallwares, gelato carts, catering gear, FF&amp;E.</t>
         </is>
       </c>
     </row>
@@ -20750,12 +20746,12 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>Ice cream + cookie franchise equipment – Taylor soft-serve, Atosa, Blodgett</t>
+          <t>Tools / plumbing / MRO supply inventory – Hilti/DeWalt/Milwaukee, fittings, heat pumps</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
@@ -20780,7 +20776,7 @@
       <c r="I43" s="13" t="inlineStr"/>
       <c r="J43" s="13" t="inlineStr">
         <is>
-          <t>2026-11-05 11:00 AM ET</t>
+          <t>2026-10-30 11:00 AM ET</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
@@ -20801,7 +20797,7 @@
       </c>
       <c r="O43" s="14" t="inlineStr">
         <is>
-          <t>Resellable units.</t>
+          <t>Bulk resale inventory.</t>
         </is>
       </c>
     </row>
@@ -20813,17 +20809,17 @@
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>Wascomat commercial washers liquidation (22× W105, 6× W185, dryer panels)</t>
+          <t>Ice cream + cookie franchise equipment – Taylor soft-serve, Atosa, Blodgett</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>commercial laundry</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>Newark</t>
+          <t>Riverdale</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -20832,23 +20828,23 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>$500–$800 each / panels $150</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H44" s="15" t="n"/>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="J44" s="13" t="inlineStr"/>
+      <c r="I44" s="13" t="inlineStr"/>
+      <c r="J44" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-05 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L44" s="13" t="inlineStr">
@@ -20864,7 +20860,7 @@
       </c>
       <c r="O44" s="14" t="inlineStr">
         <is>
-          <t>22× W105 @ $500, 6× W185 @ $800, 20 dryer panels $150. Commercial laundry liquidation.</t>
+          <t>Resellable units.</t>
         </is>
       </c>
     </row>
@@ -20876,17 +20872,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>Major food-service caterer – new-in-box True reach-ins, Beverage-Air, TurboChef, Resfab ventless fryer</t>
+          <t>U.S. Vision court-ordered liquidation: ~70,000 designer eyeglass/sunglass frames + optical/optometry equipment at ~80 former stores + IP</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>court-ordered retail chain liquidation</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>Parsippany</t>
+          <t>Montclair</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -20895,27 +20891,19 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Accepting offers (terms in offering memo, NDA required)</t>
         </is>
       </c>
       <c r="H45" s="15" t="n"/>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="J45" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-03 02:00 PM ET</t>
-        </is>
-      </c>
+      <c r="I45" s="13" t="inlineStr"/>
+      <c r="J45" s="13" t="inlineStr"/>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>AuctionAdvisors</t>
         </is>
       </c>
       <c r="L45" s="13" t="inlineStr">
@@ -20931,7 +20919,7 @@
       </c>
       <c r="O45" s="14" t="inlineStr">
         <is>
-          <t>Tue Nov 3 2 PM, checkout Nov 4.</t>
+          <t>Three-lot sale pursuant to court order; bids accepted for individual lots, combinations, or substantially all assets. Equipment is spread across ~80 former store locations. Not appliance-related; big-ticket bulk inventory play.</t>
         </is>
       </c>
     </row>
@@ -20943,17 +20931,17 @@
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>Business closing – 160 new Carnes exhaust fans</t>
+          <t>Wascomat commercial washers liquidation (22× W105, 6× W185, dryer panels)</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>HVAC inventory</t>
+          <t>commercial laundry</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>Kenilworth</t>
+          <t>Newark</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -20962,17 +20950,17 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>$40 each or $5,000 all OBO</t>
+          <t>$500–$800 each / panels $150</t>
         </is>
       </c>
       <c r="H46" s="15" t="n"/>
       <c r="I46" s="13" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="J46" s="13" t="inlineStr"/>
@@ -20994,7 +20982,7 @@
       </c>
       <c r="O46" s="14" t="inlineStr">
         <is>
-          <t>160 new Carnes 80CFM 1.0 sone exhaust fans. $40 each or $5,000 for all OBO. Business closing HVAC inventory.</t>
+          <t>22× W105 @ $500, 6× W185 @ $800, 20 dryer panels $150. Commercial laundry liquidation.</t>
         </is>
       </c>
     </row>
@@ -21006,17 +20994,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>Air Systems Inc – sheet metal / HVAC fabrication shop liquidation</t>
+          <t>Major food-service caterer – new-in-box True reach-ins, Beverage-Air, TurboChef, Resfab ventless fryer</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>HVAC shop liquidation</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>Kenilworth</t>
+          <t>Parsippany</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -21029,19 +21017,23 @@
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
-          <t>Timed online (15% BP)</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H47" s="15" t="n"/>
-      <c r="I47" s="13" t="inlineStr"/>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
       <c r="J47" s="13" t="inlineStr">
         <is>
-          <t>2026-10-29 11:00 AM ET</t>
+          <t>2026-11-03 02:00 PM ET</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner Auctions</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
       <c r="L47" s="13" t="inlineStr">
@@ -21057,7 +21049,7 @@
       </c>
       <c r="O47" s="14" t="inlineStr">
         <is>
-          <t>Vicon HVAC plasma; Flagler/Lockformer/Roto-Die/Engel fab; welders; Clark forklift; Genie Superlift; Ridgid/Milwaukee/DeWalt/Bosch/Hilti/Makita tools; AeroVent/Carnes exhaust fans; racking/scaffolding. Preview Oct 28–29 AM; pickup Oct 29 PM–Nov 4. Same town as Carnes fan CL lot.</t>
+          <t>Tue Nov 3 2 PM, checkout Nov 4.</t>
         </is>
       </c>
     </row>
@@ -21069,17 +21061,17 @@
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>Serpico's Pizzeria (lost lease) – Bari ovens, walk-in, Hobart 60qt, Vulcan range</t>
+          <t>Business closing – 160 new Carnes exhaust fans</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>HVAC inventory</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>Allenhurst</t>
+          <t>Kenilworth</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -21088,28 +21080,28 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>No-reserve online auction</t>
+          <t>$40 each or $5,000 all OBO</t>
         </is>
       </c>
       <c r="H48" s="15" t="n"/>
-      <c r="I48" s="13" t="inlineStr"/>
-      <c r="J48" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J48" s="13" t="inlineStr"/>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>Peter Costanzo / EstateSales.net</t>
-        </is>
-      </c>
-      <c r="L48" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L48" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M48" s="13" t="inlineStr"/>
@@ -21120,7 +21112,7 @@
       </c>
       <c r="O48" s="14" t="inlineStr">
         <is>
-          <t>Absolute / no reserve.</t>
+          <t>160 new Carnes 80CFM 1.0 sone exhaust fans. $40 each or $5,000 for all OBO. Business closing HVAC inventory.</t>
         </is>
       </c>
     </row>
@@ -21132,17 +21124,17 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>Altitude Trampoline Park liquidation – partial: Atosa, TurboChef, stainless</t>
+          <t>Air Systems Inc – sheet metal / HVAC fabrication shop liquidation</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>facility contents</t>
+          <t>HVAC shop liquidation</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>Iselin</t>
+          <t>Kenilworth</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -21151,28 +21143,28 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Timed online (15% BP)</t>
         </is>
       </c>
       <c r="H49" s="15" t="n"/>
       <c r="I49" s="13" t="inlineStr"/>
       <c r="J49" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 11:00 AM ET</t>
+          <t>2026-10-29 11:00 AM ET</t>
         </is>
       </c>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
-        </is>
-      </c>
-      <c r="L49" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>A.J. Willner Auctions</t>
+        </is>
+      </c>
+      <c r="L49" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M49" s="13" t="inlineStr"/>
@@ -21183,7 +21175,7 @@
       </c>
       <c r="O49" s="14" t="inlineStr">
         <is>
-          <t>Some kitchen gear only.</t>
+          <t>Vicon HVAC plasma; Flagler/Lockformer/Roto-Die/Engel fab; welders; Clark forklift; Genie Superlift; Ridgid/Milwaukee/DeWalt/Bosch/Hilti/Makita tools; AeroVent/Carnes exhaust fans; racking/scaffolding. Preview Oct 28–29 AM; pickup Oct 29 PM–Nov 4. Same town as Carnes fan CL lot.</t>
         </is>
       </c>
     </row>
@@ -21195,17 +21187,17 @@
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>Restaurant / pizzeria (contents not described)</t>
+          <t>Former Rush Bowls franchise ABC sale: commercial refrigeration, Vitamix blenders, ice &amp; beverage equipment</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>restaurant / commercial kitchen contents</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>Berkeley Heights</t>
+          <t>Westfield</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -21214,32 +21206,24 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Accepting offers</t>
         </is>
       </c>
       <c r="H50" s="15" t="n"/>
-      <c r="I50" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="J50" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-20 02:00 PM ET</t>
-        </is>
-      </c>
+      <c r="I50" s="13" t="inlineStr"/>
+      <c r="J50" s="13" t="inlineStr"/>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
-        </is>
-      </c>
-      <c r="L50" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>AuctionAdvisors</t>
+        </is>
+      </c>
+      <c r="L50" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M50" s="13" t="inlineStr"/>
@@ -21250,7 +21234,7 @@
       </c>
       <c r="O50" s="14" t="inlineStr">
         <is>
-          <t>Tue Oct 20 2 PM. No item description on page.</t>
+          <t>27 East Broad St. Assignment for the benefit of creditors of 333 Star Enterprises (d/b/a Rush Bowls). Commercial refrigeration/freezers, Vitamix blenders, stainless workstations/sinks, ice and beverage equipment, POS, shelving. Inspection by contacting the auctioneer.</t>
         </is>
       </c>
     </row>
@@ -21262,17 +21246,17 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
+          <t>Serpico's Pizzeria (lost lease) – Bari ovens, walk-in, Hobart 60qt, Vulcan range</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>lien sale</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>Edison</t>
+          <t>Allenhurst</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -21281,24 +21265,28 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>
-          <t>Online auction, $2K load-out fee</t>
+          <t>No-reserve online auction</t>
         </is>
       </c>
       <c r="H51" s="15" t="n"/>
       <c r="I51" s="13" t="inlineStr"/>
-      <c r="J51" s="13" t="inlineStr"/>
+      <c r="J51" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
-        </is>
-      </c>
-      <c r="L51" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Peter Costanzo / EstateSales.net</t>
+        </is>
+      </c>
+      <c r="L51" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M51" s="13" t="inlineStr"/>
@@ -21309,7 +21297,7 @@
       </c>
       <c r="O51" s="14" t="inlineStr">
         <is>
-          <t>&gt;$100K new. Close date not captured.</t>
+          <t>Absolute / no reserve.</t>
         </is>
       </c>
     </row>
@@ -21321,17 +21309,17 @@
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
+          <t>Altitude Trampoline Park liquidation – partial: Atosa, TurboChef, stainless</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>facility contents</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>Edison</t>
+          <t>Iselin</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -21340,39 +21328,31 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
-          <t>Live + HiBid webcast, 18% BP + 3% card</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H52" s="15" t="n"/>
-      <c r="I52" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
+      <c r="I52" s="13" t="inlineStr"/>
       <c r="J52" s="13" t="inlineStr">
         <is>
-          <t>2026-10-25 01:00 PM ET</t>
+          <t>2026-10-21 11:00 AM ET</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
-        </is>
-      </c>
-      <c r="L52" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M52" s="21" t="inlineStr">
-        <is>
-          <t>FLIP</t>
-        </is>
-      </c>
+          <t>A.J. Willner</t>
+        </is>
+      </c>
+      <c r="L52" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M52" s="13" t="inlineStr"/>
       <c r="N52" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -21380,7 +21360,7 @@
       </c>
       <c r="O52" s="14" t="inlineStr">
         <is>
-          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
+          <t>Some kitchen gear only.</t>
         </is>
       </c>
     </row>
@@ -21392,17 +21372,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
+          <t>Restaurant / pizzeria (contents not described)</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>restaurant closing</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>East Brunswick</t>
+          <t>Berkeley Heights</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -21411,28 +21391,32 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H53" s="15" t="n"/>
-      <c r="I53" s="13" t="inlineStr"/>
+      <c r="I53" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="J53" s="13" t="inlineStr">
         <is>
-          <t>2026-11-03 11:00 AM ET</t>
+          <t>2026-10-20 02:00 PM ET</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
-        </is>
-      </c>
-      <c r="L53" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L53" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M53" s="13" t="inlineStr"/>
@@ -21443,7 +21427,7 @@
       </c>
       <c r="O53" s="14" t="inlineStr">
         <is>
-          <t>Store inventory.</t>
+          <t>Tue Oct 20 2 PM. No item description on page.</t>
         </is>
       </c>
     </row>
@@ -21455,17 +21439,17 @@
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>Bakery/Cafe Somerville NJ – rack ovens, La Marzocco, food truck (~76 lots)</t>
+          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>lien sale</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>Somerville</t>
+          <t>Edison</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -21474,27 +21458,19 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>224</v>
+        <v>217</v>
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>Live webcast + online (18% BP online)</t>
+          <t>Online auction, $2K load-out fee</t>
         </is>
       </c>
       <c r="H54" s="15" t="n"/>
-      <c r="I54" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="J54" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-26 02:00 PM ET</t>
-        </is>
-      </c>
+      <c r="I54" s="13" t="inlineStr"/>
+      <c r="J54" s="13" t="inlineStr"/>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>HiBid / Best Buy Auctioneers</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L54" s="13" t="inlineStr">
@@ -21510,7 +21486,7 @@
       </c>
       <c r="O54" s="14" t="inlineStr">
         <is>
-          <t>Full bakery/cafe commercial kitchen: food truck w/ pizza oven, La Marzocco espresso, Mazzer, Baxter + Empire Logiudice rack ovens, dough depositor, Globe floor mixer, Artic Air / SS refrigeration, fryers, Vitamix, Robot Coupe, display cases, dining furniture. Preview 11 AM sale day; checkout Tue 10/27.</t>
+          <t>&gt;$100K new. Close date not captured.</t>
         </is>
       </c>
     </row>
@@ -21522,17 +21498,17 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Ability to Work kitchen and store – commercial kitchen + store fixtures (~135 lots)</t>
+          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>Flemington</t>
+          <t>Edison</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -21541,23 +21517,27 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>237</v>
+        <v>217</v>
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
-          <t>Timed online (15% BP)</t>
+          <t>Live + HiBid webcast, 18% BP + 3% card</t>
         </is>
       </c>
       <c r="H55" s="15" t="n"/>
-      <c r="I55" s="13" t="inlineStr"/>
+      <c r="I55" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="J55" s="13" t="inlineStr">
         <is>
-          <t>2026-10-27 11:02 AM ET</t>
+          <t>2026-10-25 01:00 PM ET</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>HiBid</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
       <c r="L55" s="13" t="inlineStr">
@@ -21565,7 +21545,11 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M55" s="13" t="inlineStr"/>
+      <c r="M55" s="21" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
       <c r="N55" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -21573,7 +21557,7 @@
       </c>
       <c r="O55" s="14" t="inlineStr">
         <is>
-          <t>Apprentice/hospitality training cafe-kitchen and store dispersal. Preview 9–11 AM sale day; removal Oct 27 noon–Oct 29.</t>
+          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
         </is>
       </c>
     </row>
@@ -21585,17 +21569,17 @@
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
+          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>showroom closing</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>Lawrenceville</t>
+          <t>East Brunswick</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -21604,23 +21588,23 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>239</v>
+        <v>220</v>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>Online auction, 18% BP</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H56" s="15" t="n"/>
       <c r="I56" s="13" t="inlineStr"/>
       <c r="J56" s="13" t="inlineStr">
         <is>
-          <t>2026-10-27 09:00 AM ET</t>
+          <t>2026-11-03 11:00 AM ET</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L56" s="13" t="inlineStr">
@@ -21636,7 +21620,7 @@
       </c>
       <c r="O56" s="14" t="inlineStr">
         <is>
-          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
+          <t>Store inventory.</t>
         </is>
       </c>
     </row>
@@ -21648,17 +21632,17 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
+          <t>Bakery/Cafe Somerville NJ – rack ovens, La Marzocco, food truck (~76 lots)</t>
         </is>
       </c>
       <c r="C57" s="13" t="inlineStr">
         <is>
-          <t>showroom closing</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>Cherry Hill</t>
+          <t>Somerville</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -21667,23 +21651,27 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>266</v>
+        <v>224</v>
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
-          <t>Online auction, openers ~$0.50</t>
+          <t>Live webcast + online (18% BP online)</t>
         </is>
       </c>
       <c r="H57" s="15" t="n"/>
-      <c r="I57" s="13" t="inlineStr"/>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="J57" s="13" t="inlineStr">
         <is>
-          <t>2026-11-02 11:00 AM ET</t>
+          <t>2026-10-26 02:00 PM ET</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
+          <t>HiBid / Best Buy Auctioneers</t>
         </is>
       </c>
       <c r="L57" s="13" t="inlineStr">
@@ -21699,107 +21687,185 @@
       </c>
       <c r="O57" s="14" t="inlineStr">
         <is>
-          <t>Lots close from Nov 2 11 AM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — NYC / Long Island / NJ</t>
-        </is>
-      </c>
-      <c r="B58" s="17" t="inlineStr">
-        <is>
-          <t>22 item(s)</t>
-        </is>
-      </c>
-      <c r="C58" s="18" t="n"/>
-      <c r="D58" s="18" t="n"/>
-      <c r="E58" s="18" t="n"/>
-      <c r="F58" s="18" t="n"/>
-      <c r="G58" s="18" t="n"/>
-      <c r="H58" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="18" t="n"/>
-      <c r="J58" s="18" t="n"/>
-      <c r="K58" s="18" t="n"/>
-      <c r="L58" s="18" t="n"/>
-      <c r="M58" s="18" t="n"/>
-      <c r="N58" s="18" t="n"/>
-      <c r="O58" s="18" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t>▸ Eastern PA / Mid-Atlantic  (1)</t>
-        </is>
-      </c>
-      <c r="B59" s="12" t="n"/>
-      <c r="C59" s="12" t="n"/>
-      <c r="D59" s="12" t="n"/>
-      <c r="E59" s="12" t="n"/>
-      <c r="F59" s="12" t="n"/>
-      <c r="G59" s="12" t="n"/>
-      <c r="H59" s="12" t="n"/>
-      <c r="I59" s="12" t="n"/>
-      <c r="J59" s="12" t="n"/>
-      <c r="K59" s="12" t="n"/>
-      <c r="L59" s="12" t="n"/>
-      <c r="M59" s="12" t="n"/>
-      <c r="N59" s="12" t="n"/>
-      <c r="O59" s="12" t="n"/>
+          <t>Full bakery/cafe commercial kitchen: food truck w/ pizza oven, La Marzocco espresso, Mazzer, Baxter + Empire Logiudice rack ovens, dough depositor, Globe floor mixer, Artic Air / SS refrigeration, fryers, Vitamix, Robot Coupe, display cases, dining furniture. Preview 11 AM sale day; checkout Tue 10/27.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" outlineLevel="1">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>Ability to Work kitchen and store – commercial kitchen + store fixtures (~135 lots)</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>Flemington</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F58" s="13" t="n">
+        <v>237</v>
+      </c>
+      <c r="G58" s="13" t="inlineStr">
+        <is>
+          <t>Timed online (15% BP)</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="n"/>
+      <c r="I58" s="13" t="inlineStr"/>
+      <c r="J58" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-27 11:02 AM ET</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="inlineStr">
+        <is>
+          <t>HiBid</t>
+        </is>
+      </c>
+      <c r="L58" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M58" s="13" t="inlineStr"/>
+      <c r="N58" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O58" s="14" t="inlineStr">
+        <is>
+          <t>Apprentice/hospitality training cafe-kitchen and store dispersal. Preview 9–11 AM sale day; removal Oct 27 noon–Oct 29.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" outlineLevel="1">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
+        </is>
+      </c>
+      <c r="C59" s="13" t="inlineStr">
+        <is>
+          <t>showroom closing</t>
+        </is>
+      </c>
+      <c r="D59" s="13" t="inlineStr">
+        <is>
+          <t>Lawrenceville</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F59" s="13" t="n">
+        <v>239</v>
+      </c>
+      <c r="G59" s="13" t="inlineStr">
+        <is>
+          <t>Online auction, 18% BP</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="n"/>
+      <c r="I59" s="13" t="inlineStr"/>
+      <c r="J59" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="inlineStr">
+        <is>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L59" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M59" s="13" t="inlineStr"/>
+      <c r="N59" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O59" s="14" t="inlineStr">
+        <is>
+          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
+        </is>
+      </c>
     </row>
     <row r="60" outlineLevel="1">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>Eastern PA / Mid-Atlantic</t>
+          <t>NYC / Long Island / NJ</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>October restaurant consignment – Hobart, Rational, True + NEW scratch-and-dent Migali/Avantco</t>
+          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
         </is>
       </c>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>showroom closing</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>Harrisburg</t>
+          <t>Cherry Hill</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>340</v>
+        <v>266</v>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
-          <t>Online auction, 15% BP, ships $55/pallet</t>
+          <t>Online auction, openers ~$0.50</t>
         </is>
       </c>
       <c r="H60" s="15" t="n"/>
       <c r="I60" s="13" t="inlineStr"/>
       <c r="J60" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 11:00 AM ET</t>
+          <t>2026-11-02 11:00 AM ET</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
         <is>
-          <t>Restaurant Auction Co</t>
-        </is>
-      </c>
-      <c r="L60" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L60" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M60" s="13" t="inlineStr"/>
@@ -21810,19 +21876,19 @@
       </c>
       <c r="O60" s="14" t="inlineStr">
         <is>
-          <t>Closes Oct 21 10 or 11 AM (later used). Shippable.</t>
+          <t>Lots close from Nov 2 11 AM.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="17" t="inlineStr">
         <is>
-          <t>Subtotal — Eastern PA / Mid-Atlantic</t>
+          <t>Subtotal — NYC / Long Island / NJ</t>
         </is>
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>1 item(s)</t>
+          <t>25 item(s)</t>
         </is>
       </c>
       <c r="C61" s="18" t="n"/>
@@ -21844,7 +21910,7 @@
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t>▸ Western PA / Ohio Valley  (1)</t>
+          <t>▸ Eastern PA / Mid-Atlantic  (1)</t>
         </is>
       </c>
       <c r="B62" s="12" t="n"/>
@@ -21865,22 +21931,22 @@
     <row r="63" outlineLevel="1">
       <c r="A63" s="13" t="inlineStr">
         <is>
-          <t>Western PA / Ohio Valley</t>
+          <t>Eastern PA / Mid-Atlantic</t>
         </is>
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>Millers Pizza &amp; More – pizza business, commercial kitchen &amp; event space contents (362 lots)</t>
+          <t>October restaurant consignment – Hobart, Rational, True + NEW scratch-and-dent Migali/Avantco</t>
         </is>
       </c>
       <c r="C63" s="13" t="inlineStr">
         <is>
-          <t>restaurant / commercial kitchen contents</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>Everson</t>
+          <t>Harrisburg</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
@@ -21889,28 +21955,28 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>478</v>
+        <v>340</v>
       </c>
       <c r="G63" s="13" t="inlineStr">
         <is>
-          <t>Online auction, 15% buyer premium</t>
+          <t>Online auction, 15% BP, ships $55/pallet</t>
         </is>
       </c>
       <c r="H63" s="15" t="n"/>
       <c r="I63" s="13" t="inlineStr"/>
       <c r="J63" s="13" t="inlineStr">
         <is>
-          <t>2026-10-25 07:00 PM ET</t>
+          <t>2026-10-21 11:00 AM ET</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Bid Local LLC)</t>
-        </is>
-      </c>
-      <c r="L63" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Restaurant Auction Co</t>
+        </is>
+      </c>
+      <c r="L63" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M63" s="13" t="inlineStr"/>
@@ -21921,14 +21987,14 @@
       </c>
       <c r="O63" s="14" t="inlineStr">
         <is>
-          <t>Property of Millers Pizza and More LLC; online-only, 362 lots, lots begin closing Oct 25 7 PM. Pickup Everson PA by appointment Tue 10/27 and Wed 10/28. Building (4,500 sq ft) to be auctioned separately.</t>
+          <t>Closes Oct 21 10 or 11 AM (later used). Shippable.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="17" t="inlineStr">
         <is>
-          <t>Subtotal — Western PA / Ohio Valley</t>
+          <t>Subtotal — Eastern PA / Mid-Atlantic</t>
         </is>
       </c>
       <c r="B64" s="17" t="inlineStr">
@@ -21955,7 +22021,7 @@
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t>▸ Upstate / Western NY  (2)</t>
+          <t>▸ Western PA / Ohio Valley  (1)</t>
         </is>
       </c>
       <c r="B65" s="12" t="n"/>
@@ -21976,52 +22042,52 @@
     <row r="66" outlineLevel="1">
       <c r="A66" s="13" t="inlineStr">
         <is>
-          <t>Upstate / Western NY</t>
+          <t>Western PA / Ohio Valley</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>Former Taco Del Mar – stainless, warmers, walk-in panels</t>
+          <t>Millers Pizza &amp; More – pizza business, commercial kitchen &amp; event space contents (362 lots)</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>restaurant / commercial kitchen contents</t>
         </is>
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t>Watson</t>
+          <t>Everson</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>260</v>
+        <v>478</v>
       </c>
       <c r="G66" s="13" t="inlineStr">
         <is>
-          <t>HiBid online auction</t>
+          <t>Online auction, 15% buyer premium</t>
         </is>
       </c>
       <c r="H66" s="15" t="n"/>
       <c r="I66" s="13" t="inlineStr"/>
       <c r="J66" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 06:00 PM ET</t>
+          <t>2026-10-25 07:00 PM ET</t>
         </is>
       </c>
       <c r="K66" s="13" t="inlineStr">
         <is>
-          <t>Adirondack Asset / HiBid</t>
-        </is>
-      </c>
-      <c r="L66" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>HiBid (Bid Local LLC)</t>
+        </is>
+      </c>
+      <c r="L66" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M66" s="13" t="inlineStr"/>
@@ -22032,165 +22098,165 @@
       </c>
       <c r="O66" s="14" t="inlineStr">
         <is>
+          <t>Property of Millers Pizza and More LLC; online-only, 362 lots, lots begin closing Oct 25 7 PM. Pickup Everson PA by appointment Tue 10/27 and Wed 10/28. Building (4,500 sq ft) to be auctioned separately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Western PA / Ohio Valley</t>
+        </is>
+      </c>
+      <c r="B67" s="17" t="inlineStr">
+        <is>
+          <t>1 item(s)</t>
+        </is>
+      </c>
+      <c r="C67" s="18" t="n"/>
+      <c r="D67" s="18" t="n"/>
+      <c r="E67" s="18" t="n"/>
+      <c r="F67" s="18" t="n"/>
+      <c r="G67" s="18" t="n"/>
+      <c r="H67" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="18" t="n"/>
+      <c r="J67" s="18" t="n"/>
+      <c r="K67" s="18" t="n"/>
+      <c r="L67" s="18" t="n"/>
+      <c r="M67" s="18" t="n"/>
+      <c r="N67" s="18" t="n"/>
+      <c r="O67" s="18" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>▸ Upstate / Western NY  (2)</t>
+        </is>
+      </c>
+      <c r="B68" s="12" t="n"/>
+      <c r="C68" s="12" t="n"/>
+      <c r="D68" s="12" t="n"/>
+      <c r="E68" s="12" t="n"/>
+      <c r="F68" s="12" t="n"/>
+      <c r="G68" s="12" t="n"/>
+      <c r="H68" s="12" t="n"/>
+      <c r="I68" s="12" t="n"/>
+      <c r="J68" s="12" t="n"/>
+      <c r="K68" s="12" t="n"/>
+      <c r="L68" s="12" t="n"/>
+      <c r="M68" s="12" t="n"/>
+      <c r="N68" s="12" t="n"/>
+      <c r="O68" s="12" t="n"/>
+    </row>
+    <row r="69" outlineLevel="1">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>Upstate / Western NY</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>Former Taco Del Mar – stainless, warmers, walk-in panels</t>
+        </is>
+      </c>
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="D69" s="13" t="inlineStr">
+        <is>
+          <t>Watson</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F69" s="13" t="n">
+        <v>260</v>
+      </c>
+      <c r="G69" s="13" t="inlineStr">
+        <is>
+          <t>HiBid online auction</t>
+        </is>
+      </c>
+      <c r="H69" s="15" t="n"/>
+      <c r="I69" s="13" t="inlineStr"/>
+      <c r="J69" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-20 06:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="inlineStr">
+        <is>
+          <t>Adirondack Asset / HiBid</t>
+        </is>
+      </c>
+      <c r="L69" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M69" s="13" t="inlineStr"/>
+      <c r="N69" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O69" s="14" t="inlineStr">
+        <is>
           <t>Small lot.</t>
         </is>
       </c>
-    </row>
-    <row r="67" outlineLevel="1">
-      <c r="A67" s="13" t="inlineStr">
-        <is>
-          <t>Upstate / Western NY</t>
-        </is>
-      </c>
-      <c r="B67" s="14" t="inlineStr">
-        <is>
-          <t>Restaurant &amp; fitness equipment</t>
-        </is>
-      </c>
-      <c r="C67" s="13" t="inlineStr">
-        <is>
-          <t>restaurant</t>
-        </is>
-      </c>
-      <c r="D67" s="13" t="inlineStr">
-        <is>
-          <t>Williamsville</t>
-        </is>
-      </c>
-      <c r="E67" s="13" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="F67" s="13" t="n">
-        <v>408</v>
-      </c>
-      <c r="G67" s="13" t="inlineStr">
-        <is>
-          <t>Online auction</t>
-        </is>
-      </c>
-      <c r="H67" s="15" t="n"/>
-      <c r="I67" s="13" t="inlineStr"/>
-      <c r="J67" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-26 07:30 PM ET</t>
-        </is>
-      </c>
-      <c r="K67" s="13" t="inlineStr">
-        <is>
-          <t>Cash Auctions</t>
-        </is>
-      </c>
-      <c r="L67" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M67" s="13" t="inlineStr"/>
-      <c r="N67" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O67" s="14" t="inlineStr">
-        <is>
-          <t>Lots not reviewed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Upstate / Western NY</t>
-        </is>
-      </c>
-      <c r="B68" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C68" s="18" t="n"/>
-      <c r="D68" s="18" t="n"/>
-      <c r="E68" s="18" t="n"/>
-      <c r="F68" s="18" t="n"/>
-      <c r="G68" s="18" t="n"/>
-      <c r="H68" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="18" t="n"/>
-      <c r="J68" s="18" t="n"/>
-      <c r="K68" s="18" t="n"/>
-      <c r="L68" s="18" t="n"/>
-      <c r="M68" s="18" t="n"/>
-      <c r="N68" s="18" t="n"/>
-      <c r="O68" s="18" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="11" t="inlineStr">
-        <is>
-          <t>▸ Virginia  (1)</t>
-        </is>
-      </c>
-      <c r="B69" s="12" t="n"/>
-      <c r="C69" s="12" t="n"/>
-      <c r="D69" s="12" t="n"/>
-      <c r="E69" s="12" t="n"/>
-      <c r="F69" s="12" t="n"/>
-      <c r="G69" s="12" t="n"/>
-      <c r="H69" s="12" t="n"/>
-      <c r="I69" s="12" t="n"/>
-      <c r="J69" s="12" t="n"/>
-      <c r="K69" s="12" t="n"/>
-      <c r="L69" s="12" t="n"/>
-      <c r="M69" s="12" t="n"/>
-      <c r="N69" s="12" t="n"/>
-      <c r="O69" s="12" t="n"/>
     </row>
     <row r="70" outlineLevel="1">
       <c r="A70" s="13" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Upstate / Western NY</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>Haynes Furniture / The Dump – 12 stores closing (furniture, mattresses)</t>
+          <t>Restaurant &amp; fitness equipment</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
         <is>
-          <t>retail GOB</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>Virginia Beach</t>
+          <t>Williamsville</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>456</v>
+        <v>408</v>
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
-          <t>Retail GOB markdowns</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H70" s="15" t="n"/>
-      <c r="I70" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="J70" s="13" t="inlineStr"/>
+      <c r="I70" s="13" t="inlineStr"/>
+      <c r="J70" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-26 07:30 PM ET</t>
+        </is>
+      </c>
       <c r="K70" s="13" t="inlineStr">
         <is>
-          <t>SB360 (PR Newswire)</t>
+          <t>Cash Auctions</t>
         </is>
       </c>
       <c r="L70" s="13" t="inlineStr">
@@ -22206,19 +22272,19 @@
       </c>
       <c r="O70" s="14" t="inlineStr">
         <is>
-          <t>Posted Oct 8. Multi-state (VA/AZ/GA/IL/TX); pinned at Virginia Beach. Home goods only.</t>
+          <t>Lots not reviewed.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="17" t="inlineStr">
         <is>
-          <t>Subtotal — Virginia</t>
+          <t>Subtotal — Upstate / Western NY</t>
         </is>
       </c>
       <c r="B71" s="17" t="inlineStr">
         <is>
-          <t>1 item(s)</t>
+          <t>2 item(s)</t>
         </is>
       </c>
       <c r="C71" s="18" t="n"/>
@@ -22240,7 +22306,7 @@
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t>▸ Midwest  (3)</t>
+          <t>▸ Virginia  (1)</t>
         </is>
       </c>
       <c r="B72" s="12" t="n"/>
@@ -22261,52 +22327,52 @@
     <row r="73" outlineLevel="1">
       <c r="A73" s="13" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>Freshway Market whole-grocery liquidation – refrigeration racks, cases, walk-ins, generator</t>
+          <t>Haynes Furniture / The Dump – 12 stores closing (furniture, mattresses)</t>
         </is>
       </c>
       <c r="C73" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>retail GOB</t>
         </is>
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Virginia Beach</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="F73" s="13" t="n">
-        <v>862</v>
+        <v>456</v>
       </c>
       <c r="G73" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Retail GOB markdowns</t>
         </is>
       </c>
       <c r="H73" s="15" t="n"/>
-      <c r="I73" s="13" t="inlineStr"/>
-      <c r="J73" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-20 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="J73" s="13" t="inlineStr"/>
       <c r="K73" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L73" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>SB360 (PR Newswire)</t>
+        </is>
+      </c>
+      <c r="L73" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M73" s="13" t="inlineStr"/>
@@ -22317,387 +22383,435 @@
       </c>
       <c r="O73" s="14" t="inlineStr">
         <is>
-          <t>Closes from Oct 20 10 AM CDT.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" outlineLevel="1">
-      <c r="A74" s="13" t="inlineStr">
+          <t>Posted Oct 8. Multi-state (VA/AZ/GA/IL/TX); pinned at Virginia Beach. Home goods only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Virginia</t>
+        </is>
+      </c>
+      <c r="B74" s="17" t="inlineStr">
+        <is>
+          <t>1 item(s)</t>
+        </is>
+      </c>
+      <c r="C74" s="18" t="n"/>
+      <c r="D74" s="18" t="n"/>
+      <c r="E74" s="18" t="n"/>
+      <c r="F74" s="18" t="n"/>
+      <c r="G74" s="18" t="n"/>
+      <c r="H74" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I74" s="18" t="n"/>
+      <c r="J74" s="18" t="n"/>
+      <c r="K74" s="18" t="n"/>
+      <c r="L74" s="18" t="n"/>
+      <c r="M74" s="18" t="n"/>
+      <c r="N74" s="18" t="n"/>
+      <c r="O74" s="18" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>▸ Midwest  (2)</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="n"/>
+      <c r="C75" s="12" t="n"/>
+      <c r="D75" s="12" t="n"/>
+      <c r="E75" s="12" t="n"/>
+      <c r="F75" s="12" t="n"/>
+      <c r="G75" s="12" t="n"/>
+      <c r="H75" s="12" t="n"/>
+      <c r="I75" s="12" t="n"/>
+      <c r="J75" s="12" t="n"/>
+      <c r="K75" s="12" t="n"/>
+      <c r="L75" s="12" t="n"/>
+      <c r="M75" s="12" t="n"/>
+      <c r="N75" s="12" t="n"/>
+      <c r="O75" s="12" t="n"/>
+    </row>
+    <row r="76" outlineLevel="1">
+      <c r="A76" s="13" t="inlineStr">
         <is>
           <t>Midwest</t>
         </is>
       </c>
-      <c r="B74" s="14" t="inlineStr">
+      <c r="B76" s="14" t="inlineStr">
         <is>
           <t>American Sale – total liquidation, all 7 stores (pools, hot tubs, grills, holiday decor)</t>
         </is>
       </c>
-      <c r="C74" s="13" t="inlineStr">
+      <c r="C76" s="13" t="inlineStr">
         <is>
           <t>retail GOB</t>
         </is>
       </c>
-      <c r="D74" s="13" t="inlineStr">
+      <c r="D76" s="13" t="inlineStr">
         <is>
           <t>Chicagoland</t>
         </is>
       </c>
-      <c r="E74" s="13" t="inlineStr">
+      <c r="E76" s="13" t="inlineStr">
         <is>
           <t>IL</t>
         </is>
       </c>
-      <c r="F74" s="13" t="n">
+      <c r="F76" s="13" t="n">
         <v>876</v>
       </c>
-      <c r="G74" s="13" t="inlineStr">
+      <c r="G76" s="13" t="inlineStr">
         <is>
           <t>Retail GOB, up to 70% off</t>
         </is>
       </c>
-      <c r="H74" s="15" t="n"/>
-      <c r="I74" s="13" t="inlineStr">
+      <c r="H76" s="15" t="n"/>
+      <c r="I76" s="13" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="J74" s="13" t="inlineStr"/>
-      <c r="K74" s="13" t="inlineStr">
+      <c r="J76" s="13" t="inlineStr"/>
+      <c r="K76" s="13" t="inlineStr">
         <is>
           <t>Tiger Group (PR Newswire)</t>
         </is>
       </c>
-      <c r="L74" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M74" s="13" t="inlineStr"/>
-      <c r="N74" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O74" s="14" t="inlineStr">
+      <c r="L76" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M76" s="13" t="inlineStr"/>
+      <c r="N76" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O76" s="14" t="inlineStr">
         <is>
           <t>Posted Oct 15. Watch for a bulk/fixture auction.</t>
         </is>
       </c>
     </row>
-    <row r="75" outlineLevel="1">
-      <c r="A75" s="13" t="inlineStr">
+    <row r="77" outlineLevel="1">
+      <c r="A77" s="13" t="inlineStr">
         <is>
           <t>Midwest</t>
         </is>
       </c>
-      <c r="B75" s="14" t="inlineStr">
+      <c r="B77" s="14" t="inlineStr">
         <is>
           <t>Straub's Fine Foods store equipment – bakery, kitchen, meat room, Hussmann refrigeration</t>
         </is>
       </c>
-      <c r="C75" s="13" t="inlineStr">
+      <c r="C77" s="13" t="inlineStr">
         <is>
           <t>grocery/restaurant</t>
         </is>
       </c>
-      <c r="D75" s="13" t="inlineStr">
+      <c r="D77" s="13" t="inlineStr">
         <is>
           <t>St. Louis</t>
         </is>
       </c>
-      <c r="E75" s="13" t="inlineStr">
+      <c r="E77" s="13" t="inlineStr">
         <is>
           <t>MO</t>
         </is>
       </c>
-      <c r="F75" s="13" t="n">
+      <c r="F77" s="13" t="n">
         <v>1046</v>
       </c>
-      <c r="G75" s="13" t="inlineStr">
+      <c r="G77" s="13" t="inlineStr">
         <is>
           <t>Online auction (18% BP)</t>
         </is>
       </c>
-      <c r="H75" s="15" t="n"/>
-      <c r="I75" s="13" t="inlineStr"/>
-      <c r="J75" s="13" t="inlineStr">
+      <c r="H77" s="15" t="n"/>
+      <c r="I77" s="13" t="inlineStr"/>
+      <c r="J77" s="13" t="inlineStr">
         <is>
           <t>2026-10-21 11:00 AM ET</t>
         </is>
       </c>
-      <c r="K75" s="13" t="inlineStr">
+      <c r="K77" s="13" t="inlineStr">
         <is>
           <t>Grafe Auction</t>
         </is>
       </c>
-      <c r="L75" s="20" t="inlineStr">
+      <c r="L77" s="20" t="inlineStr">
         <is>
           <t>ENDING SOON</t>
         </is>
       </c>
-      <c r="M75" s="13" t="inlineStr"/>
-      <c r="N75" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O75" s="14" t="inlineStr">
+      <c r="M77" s="13" t="inlineStr"/>
+      <c r="N77" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O77" s="14" t="inlineStr">
         <is>
           <t>Kingshighway store: Revent double-rack oven + proofer, Reed revolving oven, Vulcan convection, Groen kettle, Southbend 6-burner, Pitco fryer, Stero dishwasher, Hobart saw/grinders, Berkel slicers, Hussmann cases + compressor racks, walk-ins, Hoshizaki/Scotsman ice machines, Crown pallet jack. Preview Oct 20 3–6 PM CDT; pickup in St. Louis.</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="17" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Midwest</t>
         </is>
       </c>
-      <c r="B76" s="17" t="inlineStr">
-        <is>
-          <t>3 item(s)</t>
-        </is>
-      </c>
-      <c r="C76" s="18" t="n"/>
-      <c r="D76" s="18" t="n"/>
-      <c r="E76" s="18" t="n"/>
-      <c r="F76" s="18" t="n"/>
-      <c r="G76" s="18" t="n"/>
-      <c r="H76" s="19" t="n">
+      <c r="B78" s="17" t="inlineStr">
+        <is>
+          <t>2 item(s)</t>
+        </is>
+      </c>
+      <c r="C78" s="18" t="n"/>
+      <c r="D78" s="18" t="n"/>
+      <c r="E78" s="18" t="n"/>
+      <c r="F78" s="18" t="n"/>
+      <c r="G78" s="18" t="n"/>
+      <c r="H78" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I76" s="18" t="n"/>
-      <c r="J76" s="18" t="n"/>
-      <c r="K76" s="18" t="n"/>
-      <c r="L76" s="18" t="n"/>
-      <c r="M76" s="18" t="n"/>
-      <c r="N76" s="18" t="n"/>
-      <c r="O76" s="18" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="11" t="inlineStr">
+      <c r="I78" s="18" t="n"/>
+      <c r="J78" s="18" t="n"/>
+      <c r="K78" s="18" t="n"/>
+      <c r="L78" s="18" t="n"/>
+      <c r="M78" s="18" t="n"/>
+      <c r="N78" s="18" t="n"/>
+      <c r="O78" s="18" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="inlineStr">
         <is>
           <t>▸ Texas / South Central  (1)</t>
         </is>
       </c>
-      <c r="B77" s="12" t="n"/>
-      <c r="C77" s="12" t="n"/>
-      <c r="D77" s="12" t="n"/>
-      <c r="E77" s="12" t="n"/>
-      <c r="F77" s="12" t="n"/>
-      <c r="G77" s="12" t="n"/>
-      <c r="H77" s="12" t="n"/>
-      <c r="I77" s="12" t="n"/>
-      <c r="J77" s="12" t="n"/>
-      <c r="K77" s="12" t="n"/>
-      <c r="L77" s="12" t="n"/>
-      <c r="M77" s="12" t="n"/>
-      <c r="N77" s="12" t="n"/>
-      <c r="O77" s="12" t="n"/>
-    </row>
-    <row r="78" outlineLevel="1">
-      <c r="A78" s="13" t="inlineStr">
+      <c r="B79" s="12" t="n"/>
+      <c r="C79" s="12" t="n"/>
+      <c r="D79" s="12" t="n"/>
+      <c r="E79" s="12" t="n"/>
+      <c r="F79" s="12" t="n"/>
+      <c r="G79" s="12" t="n"/>
+      <c r="H79" s="12" t="n"/>
+      <c r="I79" s="12" t="n"/>
+      <c r="J79" s="12" t="n"/>
+      <c r="K79" s="12" t="n"/>
+      <c r="L79" s="12" t="n"/>
+      <c r="M79" s="12" t="n"/>
+      <c r="N79" s="12" t="n"/>
+      <c r="O79" s="12" t="n"/>
+    </row>
+    <row r="80" outlineLevel="1">
+      <c r="A80" s="13" t="inlineStr">
         <is>
           <t>Texas / South Central</t>
         </is>
       </c>
-      <c r="B78" s="14" t="inlineStr">
+      <c r="B80" s="14" t="inlineStr">
         <is>
           <t>Southwest beverage distributor surplus – mostly unused: 16 True merchandisers, 75 Bunn brewers, 100+ micro-market kiosks</t>
         </is>
       </c>
-      <c r="C78" s="13" t="inlineStr">
+      <c r="C80" s="13" t="inlineStr">
         <is>
           <t>distributor surplus</t>
         </is>
       </c>
-      <c r="D78" s="13" t="inlineStr">
+      <c r="D80" s="13" t="inlineStr">
         <is>
           <t>Mesquite</t>
         </is>
       </c>
-      <c r="E78" s="13" t="inlineStr">
+      <c r="E80" s="13" t="inlineStr">
         <is>
           <t>TX</t>
         </is>
       </c>
-      <c r="F78" s="13" t="n">
+      <c r="F80" s="13" t="n">
         <v>1547</v>
       </c>
-      <c r="G78" s="13" t="inlineStr">
+      <c r="G80" s="13" t="inlineStr">
         <is>
           <t>Online auction</t>
         </is>
       </c>
-      <c r="H78" s="15" t="n"/>
-      <c r="I78" s="13" t="inlineStr"/>
-      <c r="J78" s="13" t="inlineStr">
+      <c r="H80" s="15" t="n"/>
+      <c r="I80" s="13" t="inlineStr"/>
+      <c r="J80" s="13" t="inlineStr">
         <is>
           <t>2026-11-13 11:00 AM ET</t>
         </is>
       </c>
-      <c r="K78" s="13" t="inlineStr">
+      <c r="K80" s="13" t="inlineStr">
         <is>
           <t>Heritage Global Partners</t>
         </is>
       </c>
-      <c r="L78" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M78" s="13" t="inlineStr"/>
-      <c r="N78" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O78" s="14" t="inlineStr">
+      <c r="L80" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M80" s="13" t="inlineStr"/>
+      <c r="N80" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O80" s="14" t="inlineStr">
         <is>
           <t>Near-new appliances, resell by unit. Nov 13 10 AM CST.</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="17" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Texas / South Central</t>
         </is>
       </c>
-      <c r="B79" s="17" t="inlineStr">
+      <c r="B81" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C79" s="18" t="n"/>
-      <c r="D79" s="18" t="n"/>
-      <c r="E79" s="18" t="n"/>
-      <c r="F79" s="18" t="n"/>
-      <c r="G79" s="18" t="n"/>
-      <c r="H79" s="19" t="n">
+      <c r="C81" s="18" t="n"/>
+      <c r="D81" s="18" t="n"/>
+      <c r="E81" s="18" t="n"/>
+      <c r="F81" s="18" t="n"/>
+      <c r="G81" s="18" t="n"/>
+      <c r="H81" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I79" s="18" t="n"/>
-      <c r="J79" s="18" t="n"/>
-      <c r="K79" s="18" t="n"/>
-      <c r="L79" s="18" t="n"/>
-      <c r="M79" s="18" t="n"/>
-      <c r="N79" s="18" t="n"/>
-      <c r="O79" s="18" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="11" t="inlineStr">
+      <c r="I81" s="18" t="n"/>
+      <c r="J81" s="18" t="n"/>
+      <c r="K81" s="18" t="n"/>
+      <c r="L81" s="18" t="n"/>
+      <c r="M81" s="18" t="n"/>
+      <c r="N81" s="18" t="n"/>
+      <c r="O81" s="18" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="11" t="inlineStr">
         <is>
           <t>▸ West / Other  (1)</t>
         </is>
       </c>
-      <c r="B80" s="12" t="n"/>
-      <c r="C80" s="12" t="n"/>
-      <c r="D80" s="12" t="n"/>
-      <c r="E80" s="12" t="n"/>
-      <c r="F80" s="12" t="n"/>
-      <c r="G80" s="12" t="n"/>
-      <c r="H80" s="12" t="n"/>
-      <c r="I80" s="12" t="n"/>
-      <c r="J80" s="12" t="n"/>
-      <c r="K80" s="12" t="n"/>
-      <c r="L80" s="12" t="n"/>
-      <c r="M80" s="12" t="n"/>
-      <c r="N80" s="12" t="n"/>
-      <c r="O80" s="12" t="n"/>
-    </row>
-    <row r="81" outlineLevel="1">
-      <c r="A81" s="13" t="inlineStr">
+      <c r="B82" s="12" t="n"/>
+      <c r="C82" s="12" t="n"/>
+      <c r="D82" s="12" t="n"/>
+      <c r="E82" s="12" t="n"/>
+      <c r="F82" s="12" t="n"/>
+      <c r="G82" s="12" t="n"/>
+      <c r="H82" s="12" t="n"/>
+      <c r="I82" s="12" t="n"/>
+      <c r="J82" s="12" t="n"/>
+      <c r="K82" s="12" t="n"/>
+      <c r="L82" s="12" t="n"/>
+      <c r="M82" s="12" t="n"/>
+      <c r="N82" s="12" t="n"/>
+      <c r="O82" s="12" t="n"/>
+    </row>
+    <row r="83" outlineLevel="1">
+      <c r="A83" s="13" t="inlineStr">
         <is>
           <t>West / Other</t>
         </is>
       </c>
-      <c r="B81" s="14" t="inlineStr">
+      <c r="B83" s="14" t="inlineStr">
         <is>
           <t>National salad concept liquidation – full contents of 63 fast-casual restaurants (AZ/TX/OK/NV)</t>
         </is>
       </c>
-      <c r="C81" s="13" t="inlineStr">
+      <c r="C83" s="13" t="inlineStr">
         <is>
           <t>restaurant chain liquidation</t>
         </is>
       </c>
-      <c r="D81" s="13" t="inlineStr">
+      <c r="D83" s="13" t="inlineStr">
         <is>
           <t>Phoenix</t>
         </is>
       </c>
-      <c r="E81" s="13" t="inlineStr">
+      <c r="E83" s="13" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="F81" s="13" t="n">
+      <c r="F83" s="13" t="n">
         <v>2307</v>
       </c>
-      <c r="G81" s="13" t="inlineStr">
+      <c r="G83" s="13" t="inlineStr">
         <is>
           <t>Online auctions, dates TBD</t>
         </is>
       </c>
-      <c r="H81" s="15" t="n"/>
-      <c r="I81" s="13" t="inlineStr">
+      <c r="H83" s="15" t="n"/>
+      <c r="I83" s="13" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="J81" s="13" t="inlineStr"/>
-      <c r="K81" s="13" t="inlineStr">
+      <c r="J83" s="13" t="inlineStr"/>
+      <c r="K83" s="13" t="inlineStr">
         <is>
           <t>RestaurantEquipment.bid (TAGeX)</t>
         </is>
       </c>
-      <c r="L81" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M81" s="13" t="inlineStr"/>
-      <c r="N81" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O81" s="14" t="inlineStr">
+      <c r="L83" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M83" s="13" t="inlineStr"/>
+      <c r="N83" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O83" s="14" t="inlineStr">
         <is>
           <t>Rolling market-by-market auctions, none live yet (Phoenix metro 30 locations, DFW 14, Tucson 6, Houston 5, plus OK/NV). Pickup on site at each restaurant. Pinned at Phoenix.</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="17" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="17" t="inlineStr">
         <is>
           <t>Subtotal — West / Other</t>
         </is>
       </c>
-      <c r="B82" s="17" t="inlineStr">
+      <c r="B84" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C82" s="18" t="n"/>
-      <c r="D82" s="18" t="n"/>
-      <c r="E82" s="18" t="n"/>
-      <c r="F82" s="18" t="n"/>
-      <c r="G82" s="18" t="n"/>
-      <c r="H82" s="19" t="n">
+      <c r="C84" s="18" t="n"/>
+      <c r="D84" s="18" t="n"/>
+      <c r="E84" s="18" t="n"/>
+      <c r="F84" s="18" t="n"/>
+      <c r="G84" s="18" t="n"/>
+      <c r="H84" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I82" s="18" t="n"/>
-      <c r="J82" s="18" t="n"/>
-      <c r="K82" s="18" t="n"/>
-      <c r="L82" s="18" t="n"/>
-      <c r="M82" s="18" t="n"/>
-      <c r="N82" s="18" t="n"/>
-      <c r="O82" s="18" t="n"/>
+      <c r="I84" s="18" t="n"/>
+      <c r="J84" s="18" t="n"/>
+      <c r="K84" s="18" t="n"/>
+      <c r="L84" s="18" t="n"/>
+      <c r="M84" s="18" t="n"/>
+      <c r="N84" s="18" t="n"/>
+      <c r="O84" s="18" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O82"/>
+  <autoFilter ref="A1:O84"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId2"/>
@@ -22744,16 +22858,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N60" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N66" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N67" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N73" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N74" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N75" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N78" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N81" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N60" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N66" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N69" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N73" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N76" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N77" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N80" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N83" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22765,7 +22881,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -22927,7 +23043,7 @@
       </c>
       <c r="O2" s="14" t="inlineStr">
         <is>
-          <t>Integrity Auction House. Internet bidding closes Mon Oct 19 9:18 PM ET. $50 high bid (1 bid) as of 2026-10-18. [Closed Oct 19; HiBid price realized $50.] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Integrity Auction House. Internet bidding closes Mon Oct 19 9:18 PM ET. $50 high bid (1 bid) as of 2026-10-18. [Closed Oct 19; HiBid price realized $50.] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -22990,7 +23106,7 @@
       </c>
       <c r="O3" s="14" t="inlineStr">
         <is>
-          <t>Live auction Mon Oct 19 4 PM, 3457 Wilmington Rd. Few bulk parts. [Live auction held Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Live auction Mon Oct 19 4 PM, 3457 Wilmington Rd. Few bulk parts. [Live auction held Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23191,7 +23307,7 @@
       </c>
       <c r="O6" s="14" t="inlineStr">
         <is>
-          <t>Condition: Pre-Owned. FLIP: SO36U/S tested, auction $99/0 bids, pickup only; rough resale $600-1k (eBay card shows no city; pickup distance in source.) Ends Oct 18 ~2:19 PM per eBay card (time zone uncertain; could be earlier). [auto-removed 2026-10-18: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Condition: Pre-Owned. FLIP: SO36U/S tested, auction $99/0 bids, pickup only; rough resale $600-1k (eBay card shows no city; pickup distance in source.) Ends Oct 18 ~2:19 PM per eBay card (time zone uncertain; could be earlier). [auto-removed 2026-10-18: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23256,7 +23372,7 @@
       </c>
       <c r="O7" s="14" t="inlineStr">
         <is>
-          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf) HiBid lot closed/sold ~$37.50 on 2026-10-18. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf) HiBid lot closed/sold ~$37.50 on 2026-10-18. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23321,7 +23437,7 @@
       </c>
       <c r="O8" s="14" t="inlineStr">
         <is>
-          <t>Lots close from Oct 19 2 PM ET. [HiBid catalog closed 2 PM ET Oct 19.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Lots close from Oct 19 2 PM ET. [HiBid catalog closed 2 PM ET Oct 19.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23384,7 +23500,7 @@
       </c>
       <c r="O9" s="14" t="inlineStr">
         <is>
-          <t>Pickup Oct 21 only. [Lots began closing 1 PM ET Oct 19; ended.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Pickup Oct 21 only. [Lots began closing 1 PM ET Oct 19; ended.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23447,7 +23563,7 @@
       </c>
       <c r="O10" s="14" t="inlineStr">
         <is>
-          <t>Close Oct 18 or 19 6 PM (later used). [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Close Oct 18 or 19 6 PM (later used). [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23510,59 +23626,59 @@
       </c>
       <c r="O11" s="14" t="inlineStr">
         <is>
-          <t>No new out-of-state bidders. Small. [Ended Oct 19 7 PM.] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>No new out-of-state bidders. Small. [Ended Oct 19 7 PM.] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>Greater Boston / South Shore (&lt;50mi)</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Closed Best Buy Outlet – pallet racking, Big Joe order pickers, appliance dollies, carts, cages</t>
+          <t>Freshway Market whole-grocery liquidation – refrigeration racks, cases, walk-ins, generator</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>store closing fixtures</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>Brockton</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>11</v>
+        <v>862</v>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>Racking $40/upright, $80/level; pickers $1,000 OBO</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H12" s="15" t="n"/>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="J12" s="13" t="inlineStr"/>
+      <c r="I12" s="13" t="inlineStr"/>
+      <c r="J12" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>Grafe Auction</t>
         </is>
       </c>
       <c r="L12" s="13" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>EXPIRED (2026-10-20 11:00 AM ET)</t>
         </is>
       </c>
       <c r="M12" s="13" t="inlineStr"/>
@@ -23573,63 +23689,59 @@
       </c>
       <c r="O12" s="14" t="inlineStr">
         <is>
-          <t>200 Westgate Dr. Fixtures/equipment only, no merchandise. On site daily. CL deleted by author (HTTP 410) as of 2026-10-19 midday recheck.</t>
+          <t>Closes from Oct 20 10 AM CDT. [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>NYC / Long Island / NJ</t>
+          <t>Greater Boston / South Shore (&lt;50mi)</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>Like-new restaurant – steam tables, Coldline, Cleveland cook-and-hold, fryers, True freezers</t>
+          <t>Closed Best Buy Outlet – pallet racking, Big Joe order pickers, appliance dollies, carts, cages</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>store closing fixtures</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>Staten Island</t>
+          <t>Brockton</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>203</v>
+        <v>11</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Racking $40/upright, $80/level; pickers $1,000 OBO</t>
         </is>
       </c>
       <c r="H13" s="15" t="n"/>
       <c r="I13" s="13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="J13" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-19 01:00 PM ET</t>
-        </is>
-      </c>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="J13" s="13" t="inlineStr"/>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 01:00 PM ET)</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="M13" s="13" t="inlineStr"/>
@@ -23640,7 +23752,7 @@
       </c>
       <c r="O13" s="14" t="inlineStr">
         <is>
-          <t>"Short notice" auction Mon Oct 19 1 PM. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>200 Westgate Dr. Fixtures/equipment only, no merchandise. On site daily. CL deleted by author (HTTP 410) as of 2026-10-19 midday recheck.</t>
         </is>
       </c>
     </row>
@@ -23652,26 +23764,26 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>High-end deli (contents not described)</t>
+          <t>Like-new restaurant – steam tables, Coldline, Cleveland cook-and-hold, fryers, True freezers</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>Manalapan Township</t>
+          <t>Staten Island</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>223</v>
+        <v>203</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
@@ -23686,7 +23798,7 @@
       </c>
       <c r="J14" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 04:00 PM ET</t>
+          <t>2026-10-19 01:00 PM ET</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
@@ -23696,7 +23808,7 @@
       </c>
       <c r="L14" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 04:00 PM ET)</t>
+          <t>EXPIRED (2026-10-19 01:00 PM ET)</t>
         </is>
       </c>
       <c r="M14" s="13" t="inlineStr"/>
@@ -23707,12 +23819,79 @@
       </c>
       <c r="O14" s="14" t="inlineStr">
         <is>
-          <t>Mon Oct 19 4 PM. No item description on page. [HiBid shows Bidding Closed, Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>"Short notice" auction Mon Oct 19 1 PM. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>High-end deli (contents not described)</t>
+        </is>
+      </c>
+      <c r="C15" s="13" t="inlineStr">
+        <is>
+          <t>restaurant closing</t>
+        </is>
+      </c>
+      <c r="D15" s="13" t="inlineStr">
+        <is>
+          <t>Manalapan Township</t>
+        </is>
+      </c>
+      <c r="E15" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F15" s="13" t="n">
+        <v>223</v>
+      </c>
+      <c r="G15" s="13" t="inlineStr">
+        <is>
+          <t>Live + webcast, 18% BP + 3%</t>
+        </is>
+      </c>
+      <c r="H15" s="15" t="n"/>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J15" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 04:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K15" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L15" s="13" t="inlineStr">
+        <is>
+          <t>EXPIRED (2026-10-19 04:00 PM ET)</t>
+        </is>
+      </c>
+      <c r="M15" s="13" t="inlineStr"/>
+      <c r="N15" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O15" s="14" t="inlineStr">
+        <is>
+          <t>Mon Oct 19 4 PM. No item description on page. [HiBid shows Bidding Closed, Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O14"/>
+  <autoFilter ref="A1:O15"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -23727,6 +23906,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N12" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId14"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lot_recon.xlsx
+++ b/lot_recon.xlsx
@@ -16,12 +16,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Removed" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Appliance Parts'!$A$1:$O$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Appliance Parts'!$A$1:$O$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wolf New'!$A$1:$O$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wolf Used'!$A$1:$O$189</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Wolf Unclear'!$A$1:$O$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$84</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Removed'!$A$1:$O$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Removed'!$A$1:$O$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -577,7 +577,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Last updated: 2026-10-20 11:04 ET</t>
+          <t>Last updated: 2026-10-20 14:01 ET</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Active listings: 295 · Removed: 14</t>
+          <t>Active listings: 295 · Removed: 17</t>
         </is>
       </c>
     </row>
@@ -641,13 +641,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>159646</v>
       </c>
       <c r="D8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>34</v>
@@ -679,7 +679,7 @@
         <v>164</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>608022.6</v>
+        <v>608027.6</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
@@ -695,7 +695,7 @@
         <v>31</v>
       </c>
       <c r="C11" s="6" t="n">
-        <v>137850</v>
+        <v>137880</v>
       </c>
       <c r="D11" t="n">
         <v>1</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0</v>
@@ -727,7 +727,7 @@
         <v>295</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>980403.58</v>
+        <v>980438.58</v>
       </c>
     </row>
     <row r="15">
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -1004,10 +1004,10 @@
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>64751</v>
+        <v>64756</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -1037,7 +1037,7 @@
         <v>24</v>
       </c>
       <c r="G24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>440141</v>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -1070,14 +1070,14 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>1525</v>
+        <v>1555</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>268–343</t>
+          <t>250–343</t>
         </is>
       </c>
     </row>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
@@ -1103,14 +1103,14 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H26" s="6" t="n">
         <v>175</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>478–487</t>
+          <t>437–487</t>
         </is>
       </c>
     </row>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1242,7 +1242,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>743–1046</t>
+          <t>807–1046</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2399,7 +2399,7 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>▸ Midwest  (2)</t>
+          <t>▸ Midwest  (1)</t>
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
@@ -2425,7 +2425,7 @@
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Fort Wayne)</t>
+          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Indianapolis)</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>Fort Wayne</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>743</v>
+        <v>816</v>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
       <c r="I26" s="13" t="inlineStr"/>
       <c r="J26" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 02:00 PM ET</t>
+          <t>2026-10-21 02:00 PM ET</t>
         </is>
       </c>
       <c r="K26" s="13" t="inlineStr">
@@ -2478,122 +2478,120 @@
       </c>
       <c r="O26" s="14" t="inlineStr">
         <is>
-          <t>Lots close from Oct 20 2 PM ET.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" outlineLevel="1">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>Midwest</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Indianapolis)</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>auction catalog</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>Indianapolis</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>IN</t>
-        </is>
-      </c>
-      <c r="F27" s="13" t="n">
-        <v>816</v>
-      </c>
-      <c r="G27" s="13" t="inlineStr">
-        <is>
-          <t>$0–1 openers + 15% BP + $1/lot</t>
-        </is>
-      </c>
-      <c r="H27" s="15" t="n">
+          <t>Lots close in sequence from Oct 21 2 PM ET.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Midwest</t>
+        </is>
+      </c>
+      <c r="B27" s="17" t="inlineStr">
+        <is>
+          <t>1 item(s)</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="18" t="n"/>
+      <c r="G27" s="18" t="n"/>
+      <c r="H27" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I27" s="13" t="inlineStr"/>
-      <c r="J27" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 02:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K27" s="13" t="inlineStr">
-        <is>
-          <t>HiBid (Auctionfuel)</t>
-        </is>
-      </c>
-      <c r="L27" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M27" s="13" t="inlineStr"/>
-      <c r="N27" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O27" s="14" t="inlineStr">
-        <is>
-          <t>Lots close in sequence from Oct 21 2 PM ET.</t>
-        </is>
-      </c>
+      <c r="I27" s="18" t="n"/>
+      <c r="J27" s="18" t="n"/>
+      <c r="K27" s="18" t="n"/>
+      <c r="L27" s="18" t="n"/>
+      <c r="M27" s="18" t="n"/>
+      <c r="N27" s="18" t="n"/>
+      <c r="O27" s="18" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Midwest</t>
-        </is>
-      </c>
-      <c r="B28" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C28" s="18" t="n"/>
-      <c r="D28" s="18" t="n"/>
-      <c r="E28" s="18" t="n"/>
-      <c r="F28" s="18" t="n"/>
-      <c r="G28" s="18" t="n"/>
-      <c r="H28" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="18" t="n"/>
-      <c r="J28" s="18" t="n"/>
-      <c r="K28" s="18" t="n"/>
-      <c r="L28" s="18" t="n"/>
-      <c r="M28" s="18" t="n"/>
-      <c r="N28" s="18" t="n"/>
-      <c r="O28" s="18" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>▸ Texas / South Central  (2)</t>
         </is>
       </c>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="12" t="n"/>
-      <c r="E29" s="12" t="n"/>
-      <c r="F29" s="12" t="n"/>
-      <c r="G29" s="12" t="n"/>
-      <c r="H29" s="12" t="n"/>
-      <c r="I29" s="12" t="n"/>
-      <c r="J29" s="12" t="n"/>
-      <c r="K29" s="12" t="n"/>
-      <c r="L29" s="12" t="n"/>
-      <c r="M29" s="12" t="n"/>
-      <c r="N29" s="12" t="n"/>
-      <c r="O29" s="12" t="n"/>
+      <c r="B28" s="12" t="n"/>
+      <c r="C28" s="12" t="n"/>
+      <c r="D28" s="12" t="n"/>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="12" t="n"/>
+      <c r="G28" s="12" t="n"/>
+      <c r="H28" s="12" t="n"/>
+      <c r="I28" s="12" t="n"/>
+      <c r="J28" s="12" t="n"/>
+      <c r="K28" s="12" t="n"/>
+      <c r="L28" s="12" t="n"/>
+      <c r="M28" s="12" t="n"/>
+      <c r="N28" s="12" t="n"/>
+      <c r="O28" s="12" t="n"/>
+    </row>
+    <row r="29" outlineLevel="1">
+      <c r="A29" s="13" t="inlineStr">
+        <is>
+          <t>Texas / South Central</t>
+        </is>
+      </c>
+      <c r="B29" s="14" t="inlineStr">
+        <is>
+          <t>Wholesale Hisense appliance parts – stove &amp; refrigerator parts</t>
+        </is>
+      </c>
+      <c r="C29" s="13" t="inlineStr">
+        <is>
+          <t>bulk lot</t>
+        </is>
+      </c>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>Owasso</t>
+        </is>
+      </c>
+      <c r="E29" s="13" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F29" s="13" t="n">
+        <v>1395</v>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>Wholesale (price at sale)</t>
+        </is>
+      </c>
+      <c r="H29" s="15" t="n"/>
+      <c r="I29" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J29" s="13" t="inlineStr"/>
+      <c r="K29" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L29" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M29" s="13" t="inlineStr"/>
+      <c r="N29" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O29" s="14" t="inlineStr">
+        <is>
+          <t>Updated 2026-10-12. Seller says LOCAL BUYERS ONLY, out-of-area excluded, cash pickup.</t>
+        </is>
+      </c>
     </row>
     <row r="30" outlineLevel="1">
       <c r="A30" s="13" t="inlineStr">
@@ -2603,7 +2601,7 @@
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>Wholesale Hisense appliance parts – stove &amp; refrigerator parts</t>
+          <t>Huge bulk lot appliance parts – ~2 trailer loads, GE/Whirlpool/Maytag</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
@@ -2613,32 +2611,30 @@
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>Owasso</t>
+          <t>Abilene</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>1395</v>
+        <v>1714</v>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>Wholesale (price at sale)</t>
-        </is>
-      </c>
-      <c r="H30" s="15" t="n"/>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
+          <t>$5,001</t>
+        </is>
+      </c>
+      <c r="H30" s="15" t="n">
+        <v>5001</v>
+      </c>
+      <c r="I30" s="13" t="inlineStr"/>
       <c r="J30" s="13" t="inlineStr"/>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>Geebo</t>
         </is>
       </c>
       <c r="L30" s="13" t="inlineStr">
@@ -2654,118 +2650,118 @@
       </c>
       <c r="O30" s="14" t="inlineStr">
         <is>
-          <t>Updated 2026-10-12. Seller says LOCAL BUYERS ONLY, out-of-area excluded, cash pickup.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" outlineLevel="1">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>Texas / South Central</t>
-        </is>
-      </c>
-      <c r="B31" s="14" t="inlineStr">
-        <is>
-          <t>Huge bulk lot appliance parts – ~2 trailer loads, GE/Whirlpool/Maytag</t>
-        </is>
-      </c>
-      <c r="C31" s="13" t="inlineStr">
-        <is>
-          <t>bulk lot</t>
-        </is>
-      </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>Abilene</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr">
-        <is>
-          <t>TX</t>
-        </is>
-      </c>
-      <c r="F31" s="13" t="n">
-        <v>1714</v>
-      </c>
-      <c r="G31" s="13" t="inlineStr">
-        <is>
-          <t>$5,001</t>
-        </is>
-      </c>
-      <c r="H31" s="15" t="n">
+          <t>Post date unclear (may be older). Pickup only. User already messaged seller.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Texas / South Central</t>
+        </is>
+      </c>
+      <c r="B31" s="17" t="inlineStr">
+        <is>
+          <t>2 item(s)</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="18" t="n"/>
+      <c r="E31" s="18" t="n"/>
+      <c r="F31" s="18" t="n"/>
+      <c r="G31" s="18" t="n"/>
+      <c r="H31" s="19" t="n">
         <v>5001</v>
       </c>
-      <c r="I31" s="13" t="inlineStr"/>
-      <c r="J31" s="13" t="inlineStr"/>
-      <c r="K31" s="13" t="inlineStr">
-        <is>
-          <t>Geebo</t>
-        </is>
-      </c>
-      <c r="L31" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M31" s="13" t="inlineStr"/>
-      <c r="N31" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O31" s="14" t="inlineStr">
-        <is>
-          <t>Post date unclear (may be older). Pickup only. User already messaged seller.</t>
-        </is>
-      </c>
+      <c r="I31" s="18" t="n"/>
+      <c r="J31" s="18" t="n"/>
+      <c r="K31" s="18" t="n"/>
+      <c r="L31" s="18" t="n"/>
+      <c r="M31" s="18" t="n"/>
+      <c r="N31" s="18" t="n"/>
+      <c r="O31" s="18" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Texas / South Central</t>
-        </is>
-      </c>
-      <c r="B32" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C32" s="18" t="n"/>
-      <c r="D32" s="18" t="n"/>
-      <c r="E32" s="18" t="n"/>
-      <c r="F32" s="18" t="n"/>
-      <c r="G32" s="18" t="n"/>
-      <c r="H32" s="19" t="n">
-        <v>5001</v>
-      </c>
-      <c r="I32" s="18" t="n"/>
-      <c r="J32" s="18" t="n"/>
-      <c r="K32" s="18" t="n"/>
-      <c r="L32" s="18" t="n"/>
-      <c r="M32" s="18" t="n"/>
-      <c r="N32" s="18" t="n"/>
-      <c r="O32" s="18" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="11" t="inlineStr">
+      <c r="A32" s="11" t="inlineStr">
         <is>
           <t>▸ California  (2)</t>
         </is>
       </c>
-      <c r="B33" s="12" t="n"/>
-      <c r="C33" s="12" t="n"/>
-      <c r="D33" s="12" t="n"/>
-      <c r="E33" s="12" t="n"/>
-      <c r="F33" s="12" t="n"/>
-      <c r="G33" s="12" t="n"/>
-      <c r="H33" s="12" t="n"/>
-      <c r="I33" s="12" t="n"/>
-      <c r="J33" s="12" t="n"/>
-      <c r="K33" s="12" t="n"/>
-      <c r="L33" s="12" t="n"/>
-      <c r="M33" s="12" t="n"/>
-      <c r="N33" s="12" t="n"/>
-      <c r="O33" s="12" t="n"/>
+      <c r="B32" s="12" t="n"/>
+      <c r="C32" s="12" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="12" t="n"/>
+      <c r="G32" s="12" t="n"/>
+      <c r="H32" s="12" t="n"/>
+      <c r="I32" s="12" t="n"/>
+      <c r="J32" s="12" t="n"/>
+      <c r="K32" s="12" t="n"/>
+      <c r="L32" s="12" t="n"/>
+      <c r="M32" s="12" t="n"/>
+      <c r="N32" s="12" t="n"/>
+      <c r="O32" s="12" t="n"/>
+    </row>
+    <row r="33" outlineLevel="1">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>Appliance repair company for sale (incl. parts inventory)</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>business sale</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>Escondido</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>2575</v>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>$40,000</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="n">
+        <v>40000</v>
+      </c>
+      <c r="I33" s="13" t="inlineStr"/>
+      <c r="J33" s="13" t="inlineStr"/>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L33" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M33" s="13" t="inlineStr"/>
+      <c r="N33" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O33" s="14" t="inlineStr">
+        <is>
+          <t>Whole business sale.</t>
+        </is>
+      </c>
     </row>
     <row r="34" outlineLevel="1">
       <c r="A34" s="13" t="inlineStr">
@@ -2775,17 +2771,17 @@
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>Appliance repair company for sale (incl. parts inventory)</t>
+          <t>Coin-op Whirlpool washer &amp; dryer parts (late 80s–mid 90s) – OEM parts, 40+ coin boxes, consoles, 12 transmissions</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>business sale</t>
+          <t>bulk lot</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>Escondido</t>
+          <t>Chico</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
@@ -2794,17 +2790,21 @@
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>2575</v>
+        <v>2629</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t>$40,000</t>
+          <t>$1,000</t>
         </is>
       </c>
       <c r="H34" s="15" t="n">
-        <v>40000</v>
-      </c>
-      <c r="I34" s="13" t="inlineStr"/>
+        <v>1000</v>
+      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
       <c r="J34" s="13" t="inlineStr"/>
       <c r="K34" s="13" t="inlineStr">
         <is>
@@ -2824,122 +2824,120 @@
       </c>
       <c r="O34" s="14" t="inlineStr">
         <is>
-          <t>Whole business sale.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" outlineLevel="1">
-      <c r="A35" s="13" t="inlineStr">
-        <is>
-          <t>California</t>
-        </is>
-      </c>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>Coin-op Whirlpool washer &amp; dryer parts (late 80s–mid 90s) – OEM parts, 40+ coin boxes, consoles, 12 transmissions</t>
-        </is>
-      </c>
-      <c r="C35" s="13" t="inlineStr">
+          <t>Retired laundry-route owner (35 yrs). Calls only, no shipping, pickup in Chico. No motors or pumps. Niche older coin-op parts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — California</t>
+        </is>
+      </c>
+      <c r="B35" s="17" t="inlineStr">
+        <is>
+          <t>2 item(s)</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="n"/>
+      <c r="D35" s="18" t="n"/>
+      <c r="E35" s="18" t="n"/>
+      <c r="F35" s="18" t="n"/>
+      <c r="G35" s="18" t="n"/>
+      <c r="H35" s="19" t="n">
+        <v>41000</v>
+      </c>
+      <c r="I35" s="18" t="n"/>
+      <c r="J35" s="18" t="n"/>
+      <c r="K35" s="18" t="n"/>
+      <c r="L35" s="18" t="n"/>
+      <c r="M35" s="18" t="n"/>
+      <c r="N35" s="18" t="n"/>
+      <c r="O35" s="18" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>▸ West / Other  (2)</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="n"/>
+      <c r="C36" s="12" t="n"/>
+      <c r="D36" s="12" t="n"/>
+      <c r="E36" s="12" t="n"/>
+      <c r="F36" s="12" t="n"/>
+      <c r="G36" s="12" t="n"/>
+      <c r="H36" s="12" t="n"/>
+      <c r="I36" s="12" t="n"/>
+      <c r="J36" s="12" t="n"/>
+      <c r="K36" s="12" t="n"/>
+      <c r="L36" s="12" t="n"/>
+      <c r="M36" s="12" t="n"/>
+      <c r="N36" s="12" t="n"/>
+      <c r="O36" s="12" t="n"/>
+    </row>
+    <row r="37" outlineLevel="1">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>West / Other</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>Storage locker filled with appliance parts – washer/dryer parts, heating elements, cords, rollers, belts, tools</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
         <is>
           <t>bulk lot</t>
         </is>
       </c>
-      <c r="D35" s="13" t="inlineStr">
-        <is>
-          <t>Chico</t>
-        </is>
-      </c>
-      <c r="E35" s="13" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="F35" s="13" t="n">
-        <v>2629</v>
-      </c>
-      <c r="G35" s="13" t="inlineStr">
-        <is>
-          <t>$1,000</t>
-        </is>
-      </c>
-      <c r="H35" s="15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="J35" s="13" t="inlineStr"/>
-      <c r="K35" s="13" t="inlineStr">
+      <c r="D37" s="13" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>2307</v>
+      </c>
+      <c r="G37" s="13" t="inlineStr">
+        <is>
+          <t>Message for pricing</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="n"/>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J37" s="13" t="inlineStr"/>
+      <c r="K37" s="13" t="inlineStr">
         <is>
           <t>Craigslist</t>
         </is>
       </c>
-      <c r="L35" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M35" s="13" t="inlineStr"/>
-      <c r="N35" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O35" s="14" t="inlineStr">
-        <is>
-          <t>Retired laundry-route owner (35 yrs). Calls only, no shipping, pickup in Chico. No motors or pumps. Niche older coin-op parts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — California</t>
-        </is>
-      </c>
-      <c r="B36" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C36" s="18" t="n"/>
-      <c r="D36" s="18" t="n"/>
-      <c r="E36" s="18" t="n"/>
-      <c r="F36" s="18" t="n"/>
-      <c r="G36" s="18" t="n"/>
-      <c r="H36" s="19" t="n">
-        <v>41000</v>
-      </c>
-      <c r="I36" s="18" t="n"/>
-      <c r="J36" s="18" t="n"/>
-      <c r="K36" s="18" t="n"/>
-      <c r="L36" s="18" t="n"/>
-      <c r="M36" s="18" t="n"/>
-      <c r="N36" s="18" t="n"/>
-      <c r="O36" s="18" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="11" t="inlineStr">
-        <is>
-          <t>▸ West / Other  (2)</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="n"/>
-      <c r="C37" s="12" t="n"/>
-      <c r="D37" s="12" t="n"/>
-      <c r="E37" s="12" t="n"/>
-      <c r="F37" s="12" t="n"/>
-      <c r="G37" s="12" t="n"/>
-      <c r="H37" s="12" t="n"/>
-      <c r="I37" s="12" t="n"/>
-      <c r="J37" s="12" t="n"/>
-      <c r="K37" s="12" t="n"/>
-      <c r="L37" s="12" t="n"/>
-      <c r="M37" s="12" t="n"/>
-      <c r="N37" s="12" t="n"/>
-      <c r="O37" s="12" t="n"/>
+      <c r="L37" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M37" s="13" t="inlineStr"/>
+      <c r="N37" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O37" s="14" t="inlineStr">
+        <is>
+          <t>Seller is getting out of the appliance business; selling the whole locker (North Phoenix, Deer Valley Rd near 19th Ave). Delivery available per post. Separate from the Phoenix parts-store closing ad.</t>
+        </is>
+      </c>
     </row>
     <row r="38" outlineLevel="1">
       <c r="A38" s="13" t="inlineStr">
@@ -2949,17 +2947,17 @@
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>Storage locker filled with appliance parts – washer/dryer parts, heating elements, cords, rollers, belts, tools</t>
+          <t>Appliance repair &amp; sales business for sale – 100+ appliances (~90% new), liftgate truck, large powered storage unit</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>bulk lot</t>
+          <t>business for sale</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Surprise</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
@@ -2968,17 +2966,19 @@
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>2307</v>
+        <v>2317</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>Message for pricing</t>
-        </is>
-      </c>
-      <c r="H38" s="15" t="n"/>
+          <t>$75,000</t>
+        </is>
+      </c>
+      <c r="H38" s="15" t="n">
+        <v>75000</v>
+      </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J38" s="13" t="inlineStr"/>
@@ -3000,104 +3000,39 @@
       </c>
       <c r="O38" s="14" t="inlineStr">
         <is>
-          <t>Seller is getting out of the appliance business; selling the whole locker (North Phoenix, Deer Valley Rd near 19th Ave). Delivery available per post. Separate from the Phoenix parts-store closing ad.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" outlineLevel="1">
-      <c r="A39" s="13" t="inlineStr">
-        <is>
-          <t>West / Other</t>
-        </is>
-      </c>
-      <c r="B39" s="14" t="inlineStr">
-        <is>
-          <t>Appliance repair &amp; sales business for sale – 100+ appliances (~90% new), liftgate truck, large powered storage unit</t>
-        </is>
-      </c>
-      <c r="C39" s="13" t="inlineStr">
-        <is>
-          <t>business for sale</t>
-        </is>
-      </c>
-      <c r="D39" s="13" t="inlineStr">
-        <is>
-          <t>Surprise</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="F39" s="13" t="n">
-        <v>2317</v>
-      </c>
-      <c r="G39" s="13" t="inlineStr">
-        <is>
-          <t>$75,000</t>
-        </is>
-      </c>
-      <c r="H39" s="15" t="n">
+          <t>Retiring owner of 14-year business serving rental-property owners. Whole appliances (fridges, stoves, microwaves, dishwashers, W/D), not a parts inventory. Storage unit near Dysart &amp; Bell Rd. By appointment only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — West / Other</t>
+        </is>
+      </c>
+      <c r="B39" s="17" t="inlineStr">
+        <is>
+          <t>2 item(s)</t>
+        </is>
+      </c>
+      <c r="C39" s="18" t="n"/>
+      <c r="D39" s="18" t="n"/>
+      <c r="E39" s="18" t="n"/>
+      <c r="F39" s="18" t="n"/>
+      <c r="G39" s="18" t="n"/>
+      <c r="H39" s="19" t="n">
         <v>75000</v>
       </c>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="J39" s="13" t="inlineStr"/>
-      <c r="K39" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L39" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M39" s="13" t="inlineStr"/>
-      <c r="N39" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O39" s="14" t="inlineStr">
-        <is>
-          <t>Retiring owner of 14-year business serving rental-property owners. Whole appliances (fridges, stoves, microwaves, dishwashers, W/D), not a parts inventory. Storage unit near Dysart &amp; Bell Rd. By appointment only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — West / Other</t>
-        </is>
-      </c>
-      <c r="B40" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C40" s="18" t="n"/>
-      <c r="D40" s="18" t="n"/>
-      <c r="E40" s="18" t="n"/>
-      <c r="F40" s="18" t="n"/>
-      <c r="G40" s="18" t="n"/>
-      <c r="H40" s="19" t="n">
-        <v>75000</v>
-      </c>
-      <c r="I40" s="18" t="n"/>
-      <c r="J40" s="18" t="n"/>
-      <c r="K40" s="18" t="n"/>
-      <c r="L40" s="18" t="n"/>
-      <c r="M40" s="18" t="n"/>
-      <c r="N40" s="18" t="n"/>
-      <c r="O40" s="18" t="n"/>
+      <c r="I39" s="18" t="n"/>
+      <c r="J39" s="18" t="n"/>
+      <c r="K39" s="18" t="n"/>
+      <c r="L39" s="18" t="n"/>
+      <c r="M39" s="18" t="n"/>
+      <c r="N39" s="18" t="n"/>
+      <c r="O39" s="18" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O40"/>
+  <autoFilter ref="A1:O39"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId2"/>
@@ -3109,13 +3044,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6860,11 +6794,11 @@
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t>$101 high bid (17 bids)</t>
+          <t>$106 high bid (18 bids)</t>
         </is>
       </c>
       <c r="H34" s="15" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="I34" s="13" t="inlineStr"/>
       <c r="J34" s="13" t="inlineStr">
@@ -7667,7 +7601,7 @@
       <c r="F47" s="18" t="n"/>
       <c r="G47" s="18" t="n"/>
       <c r="H47" s="19" t="n">
-        <v>33151</v>
+        <v>33156</v>
       </c>
       <c r="I47" s="18" t="n"/>
       <c r="J47" s="18" t="n"/>
@@ -18194,11 +18128,11 @@
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
-          <t>$25 high bid (9 bids)</t>
+          <t>$55 high bid (13 bids)</t>
         </is>
       </c>
       <c r="H35" s="15" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="I35" s="13" t="inlineStr"/>
       <c r="J35" s="13" t="inlineStr">
@@ -18245,7 +18179,7 @@
       <c r="F36" s="18" t="n"/>
       <c r="G36" s="18" t="n"/>
       <c r="H36" s="19" t="n">
-        <v>25</v>
+        <v>55</v>
       </c>
       <c r="I36" s="18" t="n"/>
       <c r="J36" s="18" t="n"/>
@@ -18478,7 +18412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O84"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -19656,7 +19590,7 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t>▸ CT / Hudson Valley  (9)</t>
+          <t>▸ CT / Hudson Valley  (8)</t>
         </is>
       </c>
       <c r="B24" s="12" t="n"/>
@@ -19871,42 +19805,46 @@
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>Major Intl Chain Surplus – 225 lots commercial refrigeration/kitchen (True, Traulsen, Hobart, Blodgett, Taylor)</t>
+          <t>The Outlaw Grill Steakhouse – used restaurant equipment auction (PCI Auctions CT, e.g. Vulcan EV60 Endurance 60" range)</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>commercial surplus</t>
+          <t>restaurant auction</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>Pleasant Valley</t>
+          <t>Stamford</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Online auction, current bids</t>
         </is>
       </c>
       <c r="H28" s="15" t="n"/>
-      <c r="I28" s="13" t="inlineStr"/>
+      <c r="I28" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="J28" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 02:00 PM ET</t>
+          <t>2026-10-21 08:30 PM ET</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>Adams / BidWrangler</t>
+          <t>PCI Auctions</t>
         </is>
       </c>
       <c r="L28" s="20" t="inlineStr">
@@ -19922,7 +19860,7 @@
       </c>
       <c r="O28" s="14" t="inlineStr">
         <is>
-          <t>Tested and new units.</t>
+          <t>Ends Wed Oct 21 8:30 PM EDT. PCI warehouse, 36 Ludlow St, Stamford CT. Page lists preview Oct 28 and removal Thu Oct 29 11-3 (after close). Shipping/delivery available; payment due on pickup day. Items still being added.</t>
         </is>
       </c>
     </row>
@@ -19934,17 +19872,17 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>The Outlaw Grill Steakhouse – used restaurant equipment auction (PCI Auctions CT, e.g. Vulcan EV60 Endurance 60" range)</t>
+          <t>Café/bakery liquidation – Traulsen, Vulcan ovens, mixers, Hobart slicer (~74 lots)</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>restaurant auction</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>Stamford</t>
+          <t>Greenwich</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
@@ -19953,27 +19891,23 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
-          <t>Online auction, current bids</t>
+          <t>Live auction + webcast</t>
         </is>
       </c>
       <c r="H29" s="15" t="n"/>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
+      <c r="I29" s="13" t="inlineStr"/>
       <c r="J29" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 08:30 PM ET</t>
+          <t>2026-10-21 06:00 PM ET</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>PCI Auctions</t>
+          <t>Best Buy Auctioneers / AuctionGuide</t>
         </is>
       </c>
       <c r="L29" s="20" t="inlineStr">
@@ -19989,7 +19923,7 @@
       </c>
       <c r="O29" s="14" t="inlineStr">
         <is>
-          <t>Ends Wed Oct 21 8:30 PM EDT. PCI warehouse, 36 Ludlow St, Stamford CT. Page lists preview Oct 28 and removal Thu Oct 29 11-3 (after close). Shipping/delivery available; payment due on pickup day. Items still being added.</t>
+          <t>Oct 21; start time not captured (placeholder 6 PM).</t>
         </is>
       </c>
     </row>
@@ -20001,47 +19935,47 @@
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>Café/bakery liquidation – Traulsen, Vulcan ovens, mixers, Hobart slicer (~74 lots)</t>
+          <t>BJ's Wholesale closeout – racking, forklifts, Hobart</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>Greenwich</t>
+          <t>Rotterdam</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>Live auction + webcast</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H30" s="15" t="n"/>
       <c r="I30" s="13" t="inlineStr"/>
       <c r="J30" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 06:00 PM ET</t>
+          <t>2026-11-10 10:00 AM ET</t>
         </is>
       </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>Best Buy Auctioneers / AuctionGuide</t>
-        </is>
-      </c>
-      <c r="L30" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L30" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M30" s="13" t="inlineStr"/>
@@ -20052,7 +19986,7 @@
       </c>
       <c r="O30" s="14" t="inlineStr">
         <is>
-          <t>Oct 21; start time not captured (placeholder 6 PM).</t>
+          <t>Closes from Nov 10 10 AM.</t>
         </is>
       </c>
     </row>
@@ -20064,17 +19998,17 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>BJ's Wholesale closeout – racking, forklifts, Hobart</t>
+          <t>Body shop closing after 50 years – tools, welder, generators, plasma</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>tools liquidation</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>Rotterdam</t>
+          <t>West Nyack</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
@@ -20083,23 +20017,23 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Make offer / lot</t>
         </is>
       </c>
       <c r="H31" s="15" t="n"/>
-      <c r="I31" s="13" t="inlineStr"/>
-      <c r="J31" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-10 10:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J31" s="13" t="inlineStr"/>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L31" s="13" t="inlineStr">
@@ -20115,7 +20049,7 @@
       </c>
       <c r="O31" s="14" t="inlineStr">
         <is>
-          <t>Closes from Nov 10 10 AM.</t>
+          <t>One-man auto body shop closing/retirement (Park Ridge / West Nyack NY-NJ border). Heat lamps, Kansas jack pullers, Miller 200 welder, generators, sheet-metal brake, hydraulic press, plasma cutter, engine hoist. Posted Aug 16; still open 2026-10-19.</t>
         </is>
       </c>
     </row>
@@ -20127,17 +20061,17 @@
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>Body shop closing after 50 years – tools, welder, generators, plasma</t>
+          <t>Woodworkers shop closing sale – shop tools &amp; hand tools</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>tools liquidation</t>
+          <t>woodworking shop closing</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>West Nyack</t>
+          <t>Tappan</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -20146,17 +20080,17 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>Make offer / lot</t>
+          <t>Priced individually (some free)</t>
         </is>
       </c>
       <c r="H32" s="15" t="n"/>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="J32" s="13" t="inlineStr"/>
@@ -20178,120 +20112,120 @@
       </c>
       <c r="O32" s="14" t="inlineStr">
         <is>
-          <t>One-man auto body shop closing/retirement (Park Ridge / West Nyack NY-NJ border). Heat lamps, Kansas jack pullers, Miller 200 welder, generators, sheet-metal brake, hydraulic press, plasma cutter, engine hoist. Posted Aug 16; still open 2026-10-19.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" outlineLevel="1">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>CT / Hudson Valley</t>
-        </is>
-      </c>
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>Woodworkers shop closing sale – shop tools &amp; hand tools</t>
-        </is>
-      </c>
-      <c r="C33" s="13" t="inlineStr">
-        <is>
-          <t>woodworking shop closing</t>
-        </is>
-      </c>
-      <c r="D33" s="13" t="inlineStr">
-        <is>
-          <t>Tappan</t>
-        </is>
-      </c>
-      <c r="E33" s="13" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="n">
-        <v>179</v>
-      </c>
-      <c r="G33" s="13" t="inlineStr">
-        <is>
-          <t>Priced individually (some free)</t>
-        </is>
-      </c>
-      <c r="H33" s="15" t="n"/>
-      <c r="I33" s="13" t="inlineStr">
+          <t>Ongoing shop-closing sale at 61 Main St, Tappan; many shop and hand tools, schedule a visit. Near the West Nyack body-shop sale (bl-054) for one trip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — CT / Hudson Valley</t>
+        </is>
+      </c>
+      <c r="B33" s="17" t="inlineStr">
+        <is>
+          <t>8 item(s)</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="18" t="n"/>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="18" t="n"/>
+      <c r="G33" s="18" t="n"/>
+      <c r="H33" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="18" t="n"/>
+      <c r="J33" s="18" t="n"/>
+      <c r="K33" s="18" t="n"/>
+      <c r="L33" s="18" t="n"/>
+      <c r="M33" s="18" t="n"/>
+      <c r="N33" s="18" t="n"/>
+      <c r="O33" s="18" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="inlineStr">
+        <is>
+          <t>▸ NYC / Long Island / NJ  (24)</t>
+        </is>
+      </c>
+      <c r="B34" s="12" t="n"/>
+      <c r="C34" s="12" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="12" t="n"/>
+      <c r="G34" s="12" t="n"/>
+      <c r="H34" s="12" t="n"/>
+      <c r="I34" s="12" t="n"/>
+      <c r="J34" s="12" t="n"/>
+      <c r="K34" s="12" t="n"/>
+      <c r="L34" s="12" t="n"/>
+      <c r="M34" s="12" t="n"/>
+      <c r="N34" s="12" t="n"/>
+      <c r="O34" s="12" t="n"/>
+    </row>
+    <row r="35" outlineLevel="1">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Viva Margherita restaurant complete contents (building torn down)</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>restaurant closing</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>Edgewater</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>186</v>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>Complete contents / make offer</t>
+        </is>
+      </c>
+      <c r="H35" s="15" t="n"/>
+      <c r="I35" s="13" t="inlineStr">
         <is>
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="J33" s="13" t="inlineStr"/>
-      <c r="K33" s="13" t="inlineStr">
+      <c r="J35" s="13" t="inlineStr"/>
+      <c r="K35" s="13" t="inlineStr">
         <is>
           <t>Craigslist</t>
         </is>
       </c>
-      <c r="L33" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M33" s="13" t="inlineStr"/>
-      <c r="N33" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O33" s="14" t="inlineStr">
-        <is>
-          <t>Ongoing shop-closing sale at 61 Main St, Tappan; many shop and hand tools, schedule a visit. Near the West Nyack body-shop sale (bl-054) for one trip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — CT / Hudson Valley</t>
-        </is>
-      </c>
-      <c r="B34" s="17" t="inlineStr">
-        <is>
-          <t>9 item(s)</t>
-        </is>
-      </c>
-      <c r="C34" s="18" t="n"/>
-      <c r="D34" s="18" t="n"/>
-      <c r="E34" s="18" t="n"/>
-      <c r="F34" s="18" t="n"/>
-      <c r="G34" s="18" t="n"/>
-      <c r="H34" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="18" t="n"/>
-      <c r="J34" s="18" t="n"/>
-      <c r="K34" s="18" t="n"/>
-      <c r="L34" s="18" t="n"/>
-      <c r="M34" s="18" t="n"/>
-      <c r="N34" s="18" t="n"/>
-      <c r="O34" s="18" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>▸ NYC / Long Island / NJ  (25)</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="n"/>
-      <c r="C35" s="12" t="n"/>
-      <c r="D35" s="12" t="n"/>
-      <c r="E35" s="12" t="n"/>
-      <c r="F35" s="12" t="n"/>
-      <c r="G35" s="12" t="n"/>
-      <c r="H35" s="12" t="n"/>
-      <c r="I35" s="12" t="n"/>
-      <c r="J35" s="12" t="n"/>
-      <c r="K35" s="12" t="n"/>
-      <c r="L35" s="12" t="n"/>
-      <c r="M35" s="12" t="n"/>
-      <c r="N35" s="12" t="n"/>
-      <c r="O35" s="12" t="n"/>
+      <c r="L35" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M35" s="13" t="inlineStr"/>
+      <c r="N35" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O35" s="14" t="inlineStr">
+        <is>
+          <t>Address 163 Old River Road, Edgewater NJ. Building being torn down; complete restaurant contents for sale / make offer.</t>
+        </is>
+      </c>
     </row>
     <row r="36" outlineLevel="1">
       <c r="A36" s="13" t="inlineStr">
@@ -20301,7 +20235,7 @@
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>Viva Margherita restaurant complete contents (building torn down)</t>
+          <t>Japanese BBQ &amp; bar – ~47 lots: Turbo Air, Hoshizaki ice machine, Pitco, Beverage-Air</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
@@ -20311,37 +20245,41 @@
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>Edgewater</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
-          <t>Complete contents / make offer</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H36" s="15" t="n"/>
       <c r="I36" s="13" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="J36" s="13" t="inlineStr"/>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J36" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-21 04:00 PM ET</t>
+        </is>
+      </c>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L36" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L36" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M36" s="13" t="inlineStr"/>
@@ -20352,7 +20290,7 @@
       </c>
       <c r="O36" s="14" t="inlineStr">
         <is>
-          <t>Address 163 Old River Road, Edgewater NJ. Building being torn down; complete restaurant contents for sale / make offer.</t>
+          <t>Wed Oct 21 4 PM. NYC 10013.</t>
         </is>
       </c>
     </row>
@@ -20364,12 +20302,12 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>Japanese BBQ &amp; bar – ~47 lots: Turbo Air, Hoshizaki ice machine, Pitco, Beverage-Air</t>
+          <t>Flooring company closed – pro tool package</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>tools liquidation</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
@@ -20383,32 +20321,28 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>$1,000</t>
         </is>
       </c>
       <c r="H37" s="15" t="n"/>
       <c r="I37" s="13" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="J37" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 04:00 PM ET</t>
-        </is>
-      </c>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="J37" s="13" t="inlineStr"/>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
-        </is>
-      </c>
-      <c r="L37" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L37" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M37" s="13" t="inlineStr"/>
@@ -20419,7 +20353,7 @@
       </c>
       <c r="O37" s="14" t="inlineStr">
         <is>
-          <t>Wed Oct 21 4 PM. NYC 10013.</t>
+          <t>Flooring/construction company closed; pro tool package $1,000.</t>
         </is>
       </c>
     </row>
@@ -20431,12 +20365,12 @@
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>Flooring company closed – pro tool package</t>
+          <t>New-in-box commercial refrigeration lot – 10 Beverage-Air &amp; Perlick units (bar never opened)</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
         <is>
-          <t>tools liquidation</t>
+          <t>commercial refrigeration lot</t>
         </is>
       </c>
       <c r="D38" s="13" t="inlineStr">
@@ -20454,13 +20388,13 @@
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>$1,000</t>
+          <t>$27,500 all 10 (or per unit $2,800–$4,150)</t>
         </is>
       </c>
       <c r="H38" s="15" t="n"/>
       <c r="I38" s="13" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="J38" s="13" t="inlineStr"/>
@@ -20482,7 +20416,7 @@
       </c>
       <c r="O38" s="14" t="inlineStr">
         <is>
-          <t>Flooring/construction company closed; pro tool package $1,000.</t>
+          <t>Financial District. Never installed, factory packaging: 2 Beverage-Air HBF23HC-1-HS reach-in freezers ($4,150 ea), 3 HBR23HC-1-HS reach-in fridges ($3,550 ea), 1 UCR48AHC 48" undercounter ($2,800), 3 Perlick HC24FS4 glass frosters + 1 HC24RS4 beverage fridge ($2,850 ea). Seller says full retail $47,463 (about 42% off as a bundle). Updated Oct 14.</t>
         </is>
       </c>
     </row>
@@ -20494,47 +20428,51 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>New-in-box commercial refrigeration lot – 10 Beverage-Air &amp; Perlick units (bar never opened)</t>
+          <t>Corporate caterer – Alto-Shaam, new boxed Avantco rice cookers &amp; Cadco oven, Perlick, MerryChef</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>commercial refrigeration lot</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D39" s="13" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Jersey City</t>
         </is>
       </c>
       <c r="E39" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F39" s="13" t="n">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
-          <t>$27,500 all 10 (or per unit $2,800–$4,150)</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H39" s="15" t="n"/>
       <c r="I39" s="13" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="J39" s="13" t="inlineStr"/>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="J39" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-22 02:00 PM ET</t>
+        </is>
+      </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L39" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L39" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M39" s="13" t="inlineStr"/>
@@ -20545,7 +20483,7 @@
       </c>
       <c r="O39" s="14" t="inlineStr">
         <is>
-          <t>Financial District. Never installed, factory packaging: 2 Beverage-Air HBF23HC-1-HS reach-in freezers ($4,150 ea), 3 HBR23HC-1-HS reach-in fridges ($3,550 ea), 1 UCR48AHC 48" undercounter ($2,800), 3 Perlick HC24FS4 glass frosters + 1 HC24RS4 beverage fridge ($2,850 ea). Seller says full retail $47,463 (about 42% off as a bundle). Updated Oct 14.</t>
+          <t>Thu Oct 22 2 PM.</t>
         </is>
       </c>
     </row>
@@ -20557,12 +20495,12 @@
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>Corporate caterer – Alto-Shaam, new boxed Avantco rice cookers &amp; Cadco oven, Perlick, MerryChef</t>
+          <t>Lighting store closing – lease ended, up to 70% off showroom</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
@@ -20580,28 +20518,24 @@
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>up to 70% off</t>
         </is>
       </c>
       <c r="H40" s="15" t="n"/>
       <c r="I40" s="13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="J40" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-22 02:00 PM ET</t>
-        </is>
-      </c>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="J40" s="13" t="inlineStr"/>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
-        </is>
-      </c>
-      <c r="L40" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L40" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M40" s="13" t="inlineStr"/>
@@ -20612,7 +20546,7 @@
       </c>
       <c r="O40" s="14" t="inlineStr">
         <is>
-          <t>Thu Oct 22 2 PM.</t>
+          <t>Lighting store closing, lease ended. Showroom inventory up to 70% off.</t>
         </is>
       </c>
     </row>
@@ -20624,12 +20558,12 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>Lighting store closing – lease ended, up to 70% off showroom</t>
+          <t>Baonanas LLC ABC sale: turnkey ice cream / gelato / dessert shop equipment</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>restaurant / commercial kitchen contents</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
@@ -20647,19 +20581,15 @@
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t>up to 70% off</t>
+          <t>Accepting offers</t>
         </is>
       </c>
       <c r="H41" s="15" t="n"/>
-      <c r="I41" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
+      <c r="I41" s="13" t="inlineStr"/>
       <c r="J41" s="13" t="inlineStr"/>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>AuctionAdvisors</t>
         </is>
       </c>
       <c r="L41" s="13" t="inlineStr">
@@ -20675,7 +20605,7 @@
       </c>
       <c r="O41" s="14" t="inlineStr">
         <is>
-          <t>Lighting store closing, lease ended. Showroom inventory up to 70% off.</t>
+          <t>181 Monticello Ave. Assignment for the benefit of creditors. IFI Panorama gelato display cases, refrigerated topping stations, commercial mixers, refrigerators/freezers, stainless worktables, ice machine, POS, smallwares, gelato carts, catering gear, FF&amp;E.</t>
         </is>
       </c>
     </row>
@@ -20687,17 +20617,17 @@
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>Baonanas LLC ABC sale: turnkey ice cream / gelato / dessert shop equipment</t>
+          <t>Tools / plumbing / MRO supply inventory – Hilti/DeWalt/Milwaukee, fittings, heat pumps</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>restaurant / commercial kitchen contents</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>Jersey City</t>
+          <t>Riverdale</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
@@ -20706,19 +20636,23 @@
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>Accepting offers</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H42" s="15" t="n"/>
       <c r="I42" s="13" t="inlineStr"/>
-      <c r="J42" s="13" t="inlineStr"/>
+      <c r="J42" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>AuctionAdvisors</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L42" s="13" t="inlineStr">
@@ -20734,7 +20668,7 @@
       </c>
       <c r="O42" s="14" t="inlineStr">
         <is>
-          <t>181 Monticello Ave. Assignment for the benefit of creditors. IFI Panorama gelato display cases, refrigerated topping stations, commercial mixers, refrigerators/freezers, stainless worktables, ice machine, POS, smallwares, gelato carts, catering gear, FF&amp;E.</t>
+          <t>Bulk resale inventory.</t>
         </is>
       </c>
     </row>
@@ -20746,12 +20680,12 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>Tools / plumbing / MRO supply inventory – Hilti/DeWalt/Milwaukee, fittings, heat pumps</t>
+          <t>Ice cream + cookie franchise equipment – Taylor soft-serve, Atosa, Blodgett</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
@@ -20776,7 +20710,7 @@
       <c r="I43" s="13" t="inlineStr"/>
       <c r="J43" s="13" t="inlineStr">
         <is>
-          <t>2026-10-30 11:00 AM ET</t>
+          <t>2026-11-05 11:00 AM ET</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
@@ -20797,7 +20731,7 @@
       </c>
       <c r="O43" s="14" t="inlineStr">
         <is>
-          <t>Bulk resale inventory.</t>
+          <t>Resellable units.</t>
         </is>
       </c>
     </row>
@@ -20809,17 +20743,17 @@
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>Ice cream + cookie franchise equipment – Taylor soft-serve, Atosa, Blodgett</t>
+          <t>U.S. Vision court-ordered liquidation: ~70,000 designer eyeglass/sunglass frames + optical/optometry equipment at ~80 former stores + IP</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>court-ordered retail chain liquidation</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>Riverdale</t>
+          <t>Montclair</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -20828,23 +20762,19 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Accepting offers (terms in offering memo, NDA required)</t>
         </is>
       </c>
       <c r="H44" s="15" t="n"/>
       <c r="I44" s="13" t="inlineStr"/>
-      <c r="J44" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-05 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="J44" s="13" t="inlineStr"/>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>AuctionAdvisors</t>
         </is>
       </c>
       <c r="L44" s="13" t="inlineStr">
@@ -20860,7 +20790,7 @@
       </c>
       <c r="O44" s="14" t="inlineStr">
         <is>
-          <t>Resellable units.</t>
+          <t>Three-lot sale pursuant to court order; bids accepted for individual lots, combinations, or substantially all assets. Equipment is spread across ~80 former store locations. Not appliance-related; big-ticket bulk inventory play.</t>
         </is>
       </c>
     </row>
@@ -20872,17 +20802,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>U.S. Vision court-ordered liquidation: ~70,000 designer eyeglass/sunglass frames + optical/optometry equipment at ~80 former stores + IP</t>
+          <t>Wascomat commercial washers liquidation (22× W105, 6× W185, dryer panels)</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>court-ordered retail chain liquidation</t>
+          <t>commercial laundry</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>Montclair</t>
+          <t>Newark</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -20891,19 +20821,23 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>Accepting offers (terms in offering memo, NDA required)</t>
+          <t>$500–$800 each / panels $150</t>
         </is>
       </c>
       <c r="H45" s="15" t="n"/>
-      <c r="I45" s="13" t="inlineStr"/>
+      <c r="I45" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
       <c r="J45" s="13" t="inlineStr"/>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>AuctionAdvisors</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L45" s="13" t="inlineStr">
@@ -20919,7 +20853,7 @@
       </c>
       <c r="O45" s="14" t="inlineStr">
         <is>
-          <t>Three-lot sale pursuant to court order; bids accepted for individual lots, combinations, or substantially all assets. Equipment is spread across ~80 former store locations. Not appliance-related; big-ticket bulk inventory play.</t>
+          <t>22× W105 @ $500, 6× W185 @ $800, 20 dryer panels $150. Commercial laundry liquidation.</t>
         </is>
       </c>
     </row>
@@ -20931,17 +20865,17 @@
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>Wascomat commercial washers liquidation (22× W105, 6× W185, dryer panels)</t>
+          <t>Major food-service caterer – new-in-box True reach-ins, Beverage-Air, TurboChef, Resfab ventless fryer</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>commercial laundry</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>Newark</t>
+          <t>Parsippany</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -20950,23 +20884,27 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>$500–$800 each / panels $150</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H46" s="15" t="n"/>
       <c r="I46" s="13" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
-      <c r="J46" s="13" t="inlineStr"/>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="J46" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-03 02:00 PM ET</t>
+        </is>
+      </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
       <c r="L46" s="13" t="inlineStr">
@@ -20982,7 +20920,7 @@
       </c>
       <c r="O46" s="14" t="inlineStr">
         <is>
-          <t>22× W105 @ $500, 6× W185 @ $800, 20 dryer panels $150. Commercial laundry liquidation.</t>
+          <t>Tue Nov 3 2 PM, checkout Nov 4.</t>
         </is>
       </c>
     </row>
@@ -20994,17 +20932,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>Major food-service caterer – new-in-box True reach-ins, Beverage-Air, TurboChef, Resfab ventless fryer</t>
+          <t>Business closing – 160 new Carnes exhaust fans</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>HVAC inventory</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>Parsippany</t>
+          <t>Kenilworth</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -21017,23 +20955,19 @@
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>$40 each or $5,000 all OBO</t>
         </is>
       </c>
       <c r="H47" s="15" t="n"/>
       <c r="I47" s="13" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="J47" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-03 02:00 PM ET</t>
-        </is>
-      </c>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J47" s="13" t="inlineStr"/>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L47" s="13" t="inlineStr">
@@ -21049,7 +20983,7 @@
       </c>
       <c r="O47" s="14" t="inlineStr">
         <is>
-          <t>Tue Nov 3 2 PM, checkout Nov 4.</t>
+          <t>160 new Carnes 80CFM 1.0 sone exhaust fans. $40 each or $5,000 for all OBO. Business closing HVAC inventory.</t>
         </is>
       </c>
     </row>
@@ -21061,12 +20995,12 @@
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>Business closing – 160 new Carnes exhaust fans</t>
+          <t>Air Systems Inc – sheet metal / HVAC fabrication shop liquidation</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>HVAC inventory</t>
+          <t>HVAC shop liquidation</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
@@ -21084,19 +21018,19 @@
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>$40 each or $5,000 all OBO</t>
+          <t>Timed online (15% BP)</t>
         </is>
       </c>
       <c r="H48" s="15" t="n"/>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="J48" s="13" t="inlineStr"/>
+      <c r="I48" s="13" t="inlineStr"/>
+      <c r="J48" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>A.J. Willner Auctions</t>
         </is>
       </c>
       <c r="L48" s="13" t="inlineStr">
@@ -21112,7 +21046,7 @@
       </c>
       <c r="O48" s="14" t="inlineStr">
         <is>
-          <t>160 new Carnes 80CFM 1.0 sone exhaust fans. $40 each or $5,000 for all OBO. Business closing HVAC inventory.</t>
+          <t>Vicon HVAC plasma; Flagler/Lockformer/Roto-Die/Engel fab; welders; Clark forklift; Genie Superlift; Ridgid/Milwaukee/DeWalt/Bosch/Hilti/Makita tools; AeroVent/Carnes exhaust fans; racking/scaffolding. Preview Oct 28–29 AM; pickup Oct 29 PM–Nov 4. Same town as Carnes fan CL lot.</t>
         </is>
       </c>
     </row>
@@ -21124,17 +21058,17 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>Air Systems Inc – sheet metal / HVAC fabrication shop liquidation</t>
+          <t>Former Rush Bowls franchise ABC sale: commercial refrigeration, Vitamix blenders, ice &amp; beverage equipment</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>HVAC shop liquidation</t>
+          <t>restaurant / commercial kitchen contents</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>Kenilworth</t>
+          <t>Westfield</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -21143,23 +21077,19 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
-          <t>Timed online (15% BP)</t>
+          <t>Accepting offers</t>
         </is>
       </c>
       <c r="H49" s="15" t="n"/>
       <c r="I49" s="13" t="inlineStr"/>
-      <c r="J49" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-29 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="J49" s="13" t="inlineStr"/>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner Auctions</t>
+          <t>AuctionAdvisors</t>
         </is>
       </c>
       <c r="L49" s="13" t="inlineStr">
@@ -21175,7 +21105,7 @@
       </c>
       <c r="O49" s="14" t="inlineStr">
         <is>
-          <t>Vicon HVAC plasma; Flagler/Lockformer/Roto-Die/Engel fab; welders; Clark forklift; Genie Superlift; Ridgid/Milwaukee/DeWalt/Bosch/Hilti/Makita tools; AeroVent/Carnes exhaust fans; racking/scaffolding. Preview Oct 28–29 AM; pickup Oct 29 PM–Nov 4. Same town as Carnes fan CL lot.</t>
+          <t>27 East Broad St. Assignment for the benefit of creditors of 333 Star Enterprises (d/b/a Rush Bowls). Commercial refrigeration/freezers, Vitamix blenders, stainless workstations/sinks, ice and beverage equipment, POS, shelving. Inspection by contacting the auctioneer.</t>
         </is>
       </c>
     </row>
@@ -21187,17 +21117,17 @@
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>Former Rush Bowls franchise ABC sale: commercial refrigeration, Vitamix blenders, ice &amp; beverage equipment</t>
+          <t>Serpico's Pizzeria (lost lease) – Bari ovens, walk-in, Hobart 60qt, Vulcan range</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>restaurant / commercial kitchen contents</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>Westfield</t>
+          <t>Allenhurst</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -21206,24 +21136,28 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
-          <t>Accepting offers</t>
+          <t>No-reserve online auction</t>
         </is>
       </c>
       <c r="H50" s="15" t="n"/>
       <c r="I50" s="13" t="inlineStr"/>
-      <c r="J50" s="13" t="inlineStr"/>
+      <c r="J50" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>AuctionAdvisors</t>
-        </is>
-      </c>
-      <c r="L50" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Peter Costanzo / EstateSales.net</t>
+        </is>
+      </c>
+      <c r="L50" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M50" s="13" t="inlineStr"/>
@@ -21234,7 +21168,7 @@
       </c>
       <c r="O50" s="14" t="inlineStr">
         <is>
-          <t>27 East Broad St. Assignment for the benefit of creditors of 333 Star Enterprises (d/b/a Rush Bowls). Commercial refrigeration/freezers, Vitamix blenders, stainless workstations/sinks, ice and beverage equipment, POS, shelving. Inspection by contacting the auctioneer.</t>
+          <t>Absolute / no reserve.</t>
         </is>
       </c>
     </row>
@@ -21246,17 +21180,17 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>Serpico's Pizzeria (lost lease) – Bari ovens, walk-in, Hobart 60qt, Vulcan range</t>
+          <t>Altitude Trampoline Park liquidation – partial: Atosa, TurboChef, stainless</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>facility contents</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>Allenhurst</t>
+          <t>Iselin</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -21265,11 +21199,11 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>
-          <t>No-reserve online auction</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H51" s="15" t="n"/>
@@ -21281,7 +21215,7 @@
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>Peter Costanzo / EstateSales.net</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L51" s="20" t="inlineStr">
@@ -21297,7 +21231,7 @@
       </c>
       <c r="O51" s="14" t="inlineStr">
         <is>
-          <t>Absolute / no reserve.</t>
+          <t>Some kitchen gear only.</t>
         </is>
       </c>
     </row>
@@ -21309,17 +21243,17 @@
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>Altitude Trampoline Park liquidation – partial: Atosa, TurboChef, stainless</t>
+          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>facility contents</t>
+          <t>lien sale</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>Iselin</t>
+          <t>Edison</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -21328,28 +21262,24 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Online auction, $2K load-out fee</t>
         </is>
       </c>
       <c r="H52" s="15" t="n"/>
       <c r="I52" s="13" t="inlineStr"/>
-      <c r="J52" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="J52" s="13" t="inlineStr"/>
       <c r="K52" s="13" t="inlineStr">
         <is>
           <t>A.J. Willner</t>
         </is>
       </c>
-      <c r="L52" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+      <c r="L52" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M52" s="13" t="inlineStr"/>
@@ -21360,7 +21290,7 @@
       </c>
       <c r="O52" s="14" t="inlineStr">
         <is>
-          <t>Some kitchen gear only.</t>
+          <t>&gt;$100K new. Close date not captured.</t>
         </is>
       </c>
     </row>
@@ -21372,17 +21302,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>Restaurant / pizzeria (contents not described)</t>
+          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>Berkeley Heights</t>
+          <t>Edison</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -21391,22 +21321,22 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Live + HiBid webcast, 18% BP + 3% card</t>
         </is>
       </c>
       <c r="H53" s="15" t="n"/>
       <c r="I53" s="13" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-09</t>
         </is>
       </c>
       <c r="J53" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 02:00 PM ET</t>
+          <t>2026-10-25 01:00 PM ET</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
@@ -21414,12 +21344,16 @@
           <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
-      <c r="L53" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M53" s="13" t="inlineStr"/>
+      <c r="L53" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M53" s="21" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
       <c r="N53" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -21427,7 +21361,7 @@
       </c>
       <c r="O53" s="14" t="inlineStr">
         <is>
-          <t>Tue Oct 20 2 PM. No item description on page.</t>
+          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
         </is>
       </c>
     </row>
@@ -21439,17 +21373,17 @@
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
+          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>lien sale</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>Edison</t>
+          <t>East Brunswick</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -21458,16 +21392,20 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>Online auction, $2K load-out fee</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H54" s="15" t="n"/>
       <c r="I54" s="13" t="inlineStr"/>
-      <c r="J54" s="13" t="inlineStr"/>
+      <c r="J54" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-03 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
           <t>A.J. Willner</t>
@@ -21486,7 +21424,7 @@
       </c>
       <c r="O54" s="14" t="inlineStr">
         <is>
-          <t>&gt;$100K new. Close date not captured.</t>
+          <t>Store inventory.</t>
         </is>
       </c>
     </row>
@@ -21498,17 +21436,17 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
+          <t>Bakery/Cafe Somerville NJ – rack ovens, La Marzocco, food truck (~76 lots)</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>Edison</t>
+          <t>Somerville</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -21517,27 +21455,27 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
-          <t>Live + HiBid webcast, 18% BP + 3% card</t>
+          <t>Live webcast + online (18% BP online)</t>
         </is>
       </c>
       <c r="H55" s="15" t="n"/>
       <c r="I55" s="13" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J55" s="13" t="inlineStr">
         <is>
-          <t>2026-10-25 01:00 PM ET</t>
+          <t>2026-10-26 02:00 PM ET</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>HiBid / Best Buy Auctioneers</t>
         </is>
       </c>
       <c r="L55" s="13" t="inlineStr">
@@ -21545,11 +21483,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M55" s="21" t="inlineStr">
-        <is>
-          <t>FLIP</t>
-        </is>
-      </c>
+      <c r="M55" s="13" t="inlineStr"/>
       <c r="N55" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -21557,7 +21491,7 @@
       </c>
       <c r="O55" s="14" t="inlineStr">
         <is>
-          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
+          <t>Full bakery/cafe commercial kitchen: food truck w/ pizza oven, La Marzocco espresso, Mazzer, Baxter + Empire Logiudice rack ovens, dough depositor, Globe floor mixer, Artic Air / SS refrigeration, fryers, Vitamix, Robot Coupe, display cases, dining furniture. Preview 11 AM sale day; checkout Tue 10/27.</t>
         </is>
       </c>
     </row>
@@ -21569,17 +21503,17 @@
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
+          <t>Ability to Work kitchen and store – commercial kitchen + store fixtures (~135 lots)</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>East Brunswick</t>
+          <t>Flemington</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -21588,23 +21522,23 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Timed online (15% BP)</t>
         </is>
       </c>
       <c r="H56" s="15" t="n"/>
       <c r="I56" s="13" t="inlineStr"/>
       <c r="J56" s="13" t="inlineStr">
         <is>
-          <t>2026-11-03 11:00 AM ET</t>
+          <t>2026-10-27 11:02 AM ET</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>HiBid</t>
         </is>
       </c>
       <c r="L56" s="13" t="inlineStr">
@@ -21620,7 +21554,7 @@
       </c>
       <c r="O56" s="14" t="inlineStr">
         <is>
-          <t>Store inventory.</t>
+          <t>Apprentice/hospitality training cafe-kitchen and store dispersal. Preview 9–11 AM sale day; removal Oct 27 noon–Oct 29.</t>
         </is>
       </c>
     </row>
@@ -21632,17 +21566,17 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>Bakery/Cafe Somerville NJ – rack ovens, La Marzocco, food truck (~76 lots)</t>
+          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
         </is>
       </c>
       <c r="C57" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>showroom closing</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>Somerville</t>
+          <t>Lawrenceville</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -21651,27 +21585,23 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
-          <t>Live webcast + online (18% BP online)</t>
+          <t>Online auction, 18% BP</t>
         </is>
       </c>
       <c r="H57" s="15" t="n"/>
-      <c r="I57" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
+      <c r="I57" s="13" t="inlineStr"/>
       <c r="J57" s="13" t="inlineStr">
         <is>
-          <t>2026-10-26 02:00 PM ET</t>
+          <t>2026-10-27 09:00 AM ET</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>HiBid / Best Buy Auctioneers</t>
+          <t>Grafe Auction</t>
         </is>
       </c>
       <c r="L57" s="13" t="inlineStr">
@@ -21687,7 +21617,7 @@
       </c>
       <c r="O57" s="14" t="inlineStr">
         <is>
-          <t>Full bakery/cafe commercial kitchen: food truck w/ pizza oven, La Marzocco espresso, Mazzer, Baxter + Empire Logiudice rack ovens, dough depositor, Globe floor mixer, Artic Air / SS refrigeration, fryers, Vitamix, Robot Coupe, display cases, dining furniture. Preview 11 AM sale day; checkout Tue 10/27.</t>
+          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
         </is>
       </c>
     </row>
@@ -21699,17 +21629,17 @@
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>Ability to Work kitchen and store – commercial kitchen + store fixtures (~135 lots)</t>
+          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
         </is>
       </c>
       <c r="C58" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>showroom closing</t>
         </is>
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>Flemington</t>
+          <t>Cherry Hill</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -21718,23 +21648,23 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>237</v>
+        <v>266</v>
       </c>
       <c r="G58" s="13" t="inlineStr">
         <is>
-          <t>Timed online (15% BP)</t>
+          <t>Online auction, openers ~$0.50</t>
         </is>
       </c>
       <c r="H58" s="15" t="n"/>
       <c r="I58" s="13" t="inlineStr"/>
       <c r="J58" s="13" t="inlineStr">
         <is>
-          <t>2026-10-27 11:02 AM ET</t>
+          <t>2026-11-02 11:00 AM ET</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>HiBid</t>
+          <t>Grafe Auction</t>
         </is>
       </c>
       <c r="L58" s="13" t="inlineStr">
@@ -21750,294 +21680,302 @@
       </c>
       <c r="O58" s="14" t="inlineStr">
         <is>
-          <t>Apprentice/hospitality training cafe-kitchen and store dispersal. Preview 9–11 AM sale day; removal Oct 27 noon–Oct 29.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" outlineLevel="1">
-      <c r="A59" s="13" t="inlineStr">
-        <is>
-          <t>NYC / Long Island / NJ</t>
-        </is>
-      </c>
-      <c r="B59" s="14" t="inlineStr">
-        <is>
-          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
-        </is>
-      </c>
-      <c r="C59" s="13" t="inlineStr">
-        <is>
-          <t>showroom closing</t>
-        </is>
-      </c>
-      <c r="D59" s="13" t="inlineStr">
-        <is>
-          <t>Lawrenceville</t>
-        </is>
-      </c>
-      <c r="E59" s="13" t="inlineStr">
-        <is>
-          <t>NJ</t>
-        </is>
-      </c>
-      <c r="F59" s="13" t="n">
-        <v>239</v>
-      </c>
-      <c r="G59" s="13" t="inlineStr">
-        <is>
-          <t>Online auction, 18% BP</t>
-        </is>
-      </c>
-      <c r="H59" s="15" t="n"/>
-      <c r="I59" s="13" t="inlineStr"/>
-      <c r="J59" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-27 09:00 AM ET</t>
-        </is>
-      </c>
-      <c r="K59" s="13" t="inlineStr">
-        <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L59" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M59" s="13" t="inlineStr"/>
-      <c r="N59" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O59" s="14" t="inlineStr">
-        <is>
-          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" outlineLevel="1">
-      <c r="A60" s="13" t="inlineStr">
-        <is>
-          <t>NYC / Long Island / NJ</t>
-        </is>
-      </c>
-      <c r="B60" s="14" t="inlineStr">
-        <is>
-          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
-        </is>
-      </c>
-      <c r="C60" s="13" t="inlineStr">
-        <is>
-          <t>showroom closing</t>
-        </is>
-      </c>
-      <c r="D60" s="13" t="inlineStr">
-        <is>
-          <t>Cherry Hill</t>
-        </is>
-      </c>
-      <c r="E60" s="13" t="inlineStr">
-        <is>
-          <t>NJ</t>
-        </is>
-      </c>
-      <c r="F60" s="13" t="n">
-        <v>266</v>
-      </c>
-      <c r="G60" s="13" t="inlineStr">
-        <is>
-          <t>Online auction, openers ~$0.50</t>
-        </is>
-      </c>
-      <c r="H60" s="15" t="n"/>
-      <c r="I60" s="13" t="inlineStr"/>
-      <c r="J60" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-02 11:00 AM ET</t>
-        </is>
-      </c>
-      <c r="K60" s="13" t="inlineStr">
-        <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L60" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M60" s="13" t="inlineStr"/>
-      <c r="N60" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O60" s="14" t="inlineStr">
-        <is>
           <t>Lots close from Nov 2 11 AM.</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="17" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="17" t="inlineStr">
         <is>
           <t>Subtotal — NYC / Long Island / NJ</t>
         </is>
       </c>
-      <c r="B61" s="17" t="inlineStr">
-        <is>
-          <t>25 item(s)</t>
-        </is>
-      </c>
-      <c r="C61" s="18" t="n"/>
-      <c r="D61" s="18" t="n"/>
-      <c r="E61" s="18" t="n"/>
-      <c r="F61" s="18" t="n"/>
-      <c r="G61" s="18" t="n"/>
-      <c r="H61" s="19" t="n">
+      <c r="B59" s="17" t="inlineStr">
+        <is>
+          <t>24 item(s)</t>
+        </is>
+      </c>
+      <c r="C59" s="18" t="n"/>
+      <c r="D59" s="18" t="n"/>
+      <c r="E59" s="18" t="n"/>
+      <c r="F59" s="18" t="n"/>
+      <c r="G59" s="18" t="n"/>
+      <c r="H59" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I61" s="18" t="n"/>
-      <c r="J61" s="18" t="n"/>
-      <c r="K61" s="18" t="n"/>
-      <c r="L61" s="18" t="n"/>
-      <c r="M61" s="18" t="n"/>
-      <c r="N61" s="18" t="n"/>
-      <c r="O61" s="18" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="11" t="inlineStr">
-        <is>
-          <t>▸ Eastern PA / Mid-Atlantic  (1)</t>
-        </is>
-      </c>
-      <c r="B62" s="12" t="n"/>
-      <c r="C62" s="12" t="n"/>
-      <c r="D62" s="12" t="n"/>
-      <c r="E62" s="12" t="n"/>
-      <c r="F62" s="12" t="n"/>
-      <c r="G62" s="12" t="n"/>
-      <c r="H62" s="12" t="n"/>
-      <c r="I62" s="12" t="n"/>
-      <c r="J62" s="12" t="n"/>
-      <c r="K62" s="12" t="n"/>
-      <c r="L62" s="12" t="n"/>
-      <c r="M62" s="12" t="n"/>
-      <c r="N62" s="12" t="n"/>
-      <c r="O62" s="12" t="n"/>
-    </row>
-    <row r="63" outlineLevel="1">
-      <c r="A63" s="13" t="inlineStr">
+      <c r="I59" s="18" t="n"/>
+      <c r="J59" s="18" t="n"/>
+      <c r="K59" s="18" t="n"/>
+      <c r="L59" s="18" t="n"/>
+      <c r="M59" s="18" t="n"/>
+      <c r="N59" s="18" t="n"/>
+      <c r="O59" s="18" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>▸ Eastern PA / Mid-Atlantic  (2)</t>
+        </is>
+      </c>
+      <c r="B60" s="12" t="n"/>
+      <c r="C60" s="12" t="n"/>
+      <c r="D60" s="12" t="n"/>
+      <c r="E60" s="12" t="n"/>
+      <c r="F60" s="12" t="n"/>
+      <c r="G60" s="12" t="n"/>
+      <c r="H60" s="12" t="n"/>
+      <c r="I60" s="12" t="n"/>
+      <c r="J60" s="12" t="n"/>
+      <c r="K60" s="12" t="n"/>
+      <c r="L60" s="12" t="n"/>
+      <c r="M60" s="12" t="n"/>
+      <c r="N60" s="12" t="n"/>
+      <c r="O60" s="12" t="n"/>
+    </row>
+    <row r="61" outlineLevel="1">
+      <c r="A61" s="13" t="inlineStr">
         <is>
           <t>Eastern PA / Mid-Atlantic</t>
         </is>
       </c>
-      <c r="B63" s="14" t="inlineStr">
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>Piscitello's Home Center closing after 68 years: storewide 20% off liquidation (hardware, lumber, doors, windows, kitchen/bath)</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>store closing</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="inlineStr">
+        <is>
+          <t>Wilson</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="F61" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="G61" s="13" t="inlineStr">
+        <is>
+          <t>20% off storewide (all sales final)</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="n"/>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J61" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-30 06:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
+        <is>
+          <t>LehighValley.com article</t>
+        </is>
+      </c>
+      <c r="L61" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M61" s="13" t="inlineStr"/>
+      <c r="N61" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O61" s="14" t="inlineStr">
+        <is>
+          <t>2300 Wood Ave, Wilson Borough (Easton area). Final day Oct 30. Retail-floor sale, not a bulk lot; ask in person about buying remaining stock outright.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" outlineLevel="1">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>Eastern PA / Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
         <is>
           <t>October restaurant consignment – Hobart, Rational, True + NEW scratch-and-dent Migali/Avantco</t>
         </is>
       </c>
-      <c r="C63" s="13" t="inlineStr">
+      <c r="C62" s="13" t="inlineStr">
         <is>
           <t>restaurant</t>
         </is>
       </c>
-      <c r="D63" s="13" t="inlineStr">
+      <c r="D62" s="13" t="inlineStr">
         <is>
           <t>Harrisburg</t>
         </is>
       </c>
-      <c r="E63" s="13" t="inlineStr">
+      <c r="E62" s="13" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="F63" s="13" t="n">
+      <c r="F62" s="13" t="n">
         <v>340</v>
       </c>
-      <c r="G63" s="13" t="inlineStr">
+      <c r="G62" s="13" t="inlineStr">
         <is>
           <t>Online auction, 15% BP, ships $55/pallet</t>
         </is>
       </c>
-      <c r="H63" s="15" t="n"/>
-      <c r="I63" s="13" t="inlineStr"/>
-      <c r="J63" s="13" t="inlineStr">
+      <c r="H62" s="15" t="n"/>
+      <c r="I62" s="13" t="inlineStr"/>
+      <c r="J62" s="13" t="inlineStr">
         <is>
           <t>2026-10-21 11:00 AM ET</t>
         </is>
       </c>
-      <c r="K63" s="13" t="inlineStr">
+      <c r="K62" s="13" t="inlineStr">
         <is>
           <t>Restaurant Auction Co</t>
         </is>
       </c>
-      <c r="L63" s="20" t="inlineStr">
+      <c r="L62" s="20" t="inlineStr">
         <is>
           <t>ENDING SOON</t>
         </is>
       </c>
-      <c r="M63" s="13" t="inlineStr"/>
-      <c r="N63" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O63" s="14" t="inlineStr">
+      <c r="M62" s="13" t="inlineStr"/>
+      <c r="N62" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O62" s="14" t="inlineStr">
         <is>
           <t>Closes Oct 21 10 or 11 AM (later used). Shippable.</t>
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Eastern PA / Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>2 item(s)</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="n"/>
+      <c r="D63" s="18" t="n"/>
+      <c r="E63" s="18" t="n"/>
+      <c r="F63" s="18" t="n"/>
+      <c r="G63" s="18" t="n"/>
+      <c r="H63" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="18" t="n"/>
+      <c r="J63" s="18" t="n"/>
+      <c r="K63" s="18" t="n"/>
+      <c r="L63" s="18" t="n"/>
+      <c r="M63" s="18" t="n"/>
+      <c r="N63" s="18" t="n"/>
+      <c r="O63" s="18" t="n"/>
+    </row>
     <row r="64">
-      <c r="A64" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Eastern PA / Mid-Atlantic</t>
-        </is>
-      </c>
-      <c r="B64" s="17" t="inlineStr">
-        <is>
-          <t>1 item(s)</t>
-        </is>
-      </c>
-      <c r="C64" s="18" t="n"/>
-      <c r="D64" s="18" t="n"/>
-      <c r="E64" s="18" t="n"/>
-      <c r="F64" s="18" t="n"/>
-      <c r="G64" s="18" t="n"/>
-      <c r="H64" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="18" t="n"/>
-      <c r="J64" s="18" t="n"/>
-      <c r="K64" s="18" t="n"/>
-      <c r="L64" s="18" t="n"/>
-      <c r="M64" s="18" t="n"/>
-      <c r="N64" s="18" t="n"/>
-      <c r="O64" s="18" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="11" t="inlineStr">
-        <is>
-          <t>▸ Western PA / Ohio Valley  (1)</t>
-        </is>
-      </c>
-      <c r="B65" s="12" t="n"/>
-      <c r="C65" s="12" t="n"/>
-      <c r="D65" s="12" t="n"/>
-      <c r="E65" s="12" t="n"/>
-      <c r="F65" s="12" t="n"/>
-      <c r="G65" s="12" t="n"/>
-      <c r="H65" s="12" t="n"/>
-      <c r="I65" s="12" t="n"/>
-      <c r="J65" s="12" t="n"/>
-      <c r="K65" s="12" t="n"/>
-      <c r="L65" s="12" t="n"/>
-      <c r="M65" s="12" t="n"/>
-      <c r="N65" s="12" t="n"/>
-      <c r="O65" s="12" t="n"/>
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>▸ Western PA / Ohio Valley  (3)</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="n"/>
+      <c r="C64" s="12" t="n"/>
+      <c r="D64" s="12" t="n"/>
+      <c r="E64" s="12" t="n"/>
+      <c r="F64" s="12" t="n"/>
+      <c r="G64" s="12" t="n"/>
+      <c r="H64" s="12" t="n"/>
+      <c r="I64" s="12" t="n"/>
+      <c r="J64" s="12" t="n"/>
+      <c r="K64" s="12" t="n"/>
+      <c r="L64" s="12" t="n"/>
+      <c r="M64" s="12" t="n"/>
+      <c r="N64" s="12" t="n"/>
+      <c r="O64" s="12" t="n"/>
+    </row>
+    <row r="65" outlineLevel="1">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>Western PA / Ohio Valley</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>Petrunak's Hardware Store liquidation Day 1 (530 lots: doors, hardware, tools, building supplies)</t>
+        </is>
+      </c>
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t>store closing auction</t>
+        </is>
+      </c>
+      <c r="D65" s="13" t="inlineStr">
+        <is>
+          <t>Windber</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="F65" s="13" t="n">
+        <v>437</v>
+      </c>
+      <c r="G65" s="13" t="inlineStr">
+        <is>
+          <t>Timed online auction (530 lots)</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="n"/>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="J65" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-21 08:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="inlineStr">
+        <is>
+          <t>Carey Auctions</t>
+        </is>
+      </c>
+      <c r="L65" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M65" s="13" t="inlineStr"/>
+      <c r="N65" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O65" s="14" t="inlineStr">
+        <is>
+          <t>Ends Oct 21 7 PM CDT (8 PM ET). 1500 Somerset Ave, Windber PA. Pickups Oct 24-28. Hardware store, not appliance parts.</t>
+        </is>
+      </c>
     </row>
     <row r="66" outlineLevel="1">
       <c r="A66" s="13" t="inlineStr">
@@ -22047,17 +21985,17 @@
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>Millers Pizza &amp; More – pizza business, commercial kitchen &amp; event space contents (362 lots)</t>
+          <t>Petrunak's Hardware Store liquidation Day 2 (433 lots)</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
-          <t>restaurant / commercial kitchen contents</t>
+          <t>store closing auction</t>
         </is>
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t>Everson</t>
+          <t>Windber</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
@@ -22066,28 +22004,32 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>478</v>
+        <v>437</v>
       </c>
       <c r="G66" s="13" t="inlineStr">
         <is>
-          <t>Online auction, 15% buyer premium</t>
+          <t>Timed online auction (433 lots)</t>
         </is>
       </c>
       <c r="H66" s="15" t="n"/>
-      <c r="I66" s="13" t="inlineStr"/>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="J66" s="13" t="inlineStr">
         <is>
-          <t>2026-10-25 07:00 PM ET</t>
+          <t>2026-10-22 08:00 PM ET</t>
         </is>
       </c>
       <c r="K66" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Bid Local LLC)</t>
-        </is>
-      </c>
-      <c r="L66" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Carey Auctions</t>
+        </is>
+      </c>
+      <c r="L66" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M66" s="13" t="inlineStr"/>
@@ -22098,120 +22040,120 @@
       </c>
       <c r="O66" s="14" t="inlineStr">
         <is>
+          <t>Ends Oct 22 7 PM CDT (8 PM ET). Same store as Day 1; pickups Oct 24-28.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" outlineLevel="1">
+      <c r="A67" s="13" t="inlineStr">
+        <is>
+          <t>Western PA / Ohio Valley</t>
+        </is>
+      </c>
+      <c r="B67" s="14" t="inlineStr">
+        <is>
+          <t>Millers Pizza &amp; More – pizza business, commercial kitchen &amp; event space contents (362 lots)</t>
+        </is>
+      </c>
+      <c r="C67" s="13" t="inlineStr">
+        <is>
+          <t>restaurant / commercial kitchen contents</t>
+        </is>
+      </c>
+      <c r="D67" s="13" t="inlineStr">
+        <is>
+          <t>Everson</t>
+        </is>
+      </c>
+      <c r="E67" s="13" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="F67" s="13" t="n">
+        <v>478</v>
+      </c>
+      <c r="G67" s="13" t="inlineStr">
+        <is>
+          <t>Online auction, 15% buyer premium</t>
+        </is>
+      </c>
+      <c r="H67" s="15" t="n"/>
+      <c r="I67" s="13" t="inlineStr"/>
+      <c r="J67" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-25 07:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K67" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (Bid Local LLC)</t>
+        </is>
+      </c>
+      <c r="L67" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M67" s="13" t="inlineStr"/>
+      <c r="N67" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O67" s="14" t="inlineStr">
+        <is>
           <t>Property of Millers Pizza and More LLC; online-only, 362 lots, lots begin closing Oct 25 7 PM. Pickup Everson PA by appointment Tue 10/27 and Wed 10/28. Building (4,500 sq ft) to be auctioned separately.</t>
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="17" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Western PA / Ohio Valley</t>
         </is>
       </c>
-      <c r="B67" s="17" t="inlineStr">
-        <is>
-          <t>1 item(s)</t>
-        </is>
-      </c>
-      <c r="C67" s="18" t="n"/>
-      <c r="D67" s="18" t="n"/>
-      <c r="E67" s="18" t="n"/>
-      <c r="F67" s="18" t="n"/>
-      <c r="G67" s="18" t="n"/>
-      <c r="H67" s="19" t="n">
+      <c r="B68" s="17" t="inlineStr">
+        <is>
+          <t>3 item(s)</t>
+        </is>
+      </c>
+      <c r="C68" s="18" t="n"/>
+      <c r="D68" s="18" t="n"/>
+      <c r="E68" s="18" t="n"/>
+      <c r="F68" s="18" t="n"/>
+      <c r="G68" s="18" t="n"/>
+      <c r="H68" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I67" s="18" t="n"/>
-      <c r="J67" s="18" t="n"/>
-      <c r="K67" s="18" t="n"/>
-      <c r="L67" s="18" t="n"/>
-      <c r="M67" s="18" t="n"/>
-      <c r="N67" s="18" t="n"/>
-      <c r="O67" s="18" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="11" t="inlineStr">
+      <c r="I68" s="18" t="n"/>
+      <c r="J68" s="18" t="n"/>
+      <c r="K68" s="18" t="n"/>
+      <c r="L68" s="18" t="n"/>
+      <c r="M68" s="18" t="n"/>
+      <c r="N68" s="18" t="n"/>
+      <c r="O68" s="18" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="11" t="inlineStr">
         <is>
           <t>▸ Upstate / Western NY  (2)</t>
         </is>
       </c>
-      <c r="B68" s="12" t="n"/>
-      <c r="C68" s="12" t="n"/>
-      <c r="D68" s="12" t="n"/>
-      <c r="E68" s="12" t="n"/>
-      <c r="F68" s="12" t="n"/>
-      <c r="G68" s="12" t="n"/>
-      <c r="H68" s="12" t="n"/>
-      <c r="I68" s="12" t="n"/>
-      <c r="J68" s="12" t="n"/>
-      <c r="K68" s="12" t="n"/>
-      <c r="L68" s="12" t="n"/>
-      <c r="M68" s="12" t="n"/>
-      <c r="N68" s="12" t="n"/>
-      <c r="O68" s="12" t="n"/>
-    </row>
-    <row r="69" outlineLevel="1">
-      <c r="A69" s="13" t="inlineStr">
-        <is>
-          <t>Upstate / Western NY</t>
-        </is>
-      </c>
-      <c r="B69" s="14" t="inlineStr">
-        <is>
-          <t>Former Taco Del Mar – stainless, warmers, walk-in panels</t>
-        </is>
-      </c>
-      <c r="C69" s="13" t="inlineStr">
-        <is>
-          <t>restaurant</t>
-        </is>
-      </c>
-      <c r="D69" s="13" t="inlineStr">
-        <is>
-          <t>Watson</t>
-        </is>
-      </c>
-      <c r="E69" s="13" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="F69" s="13" t="n">
-        <v>260</v>
-      </c>
-      <c r="G69" s="13" t="inlineStr">
-        <is>
-          <t>HiBid online auction</t>
-        </is>
-      </c>
-      <c r="H69" s="15" t="n"/>
-      <c r="I69" s="13" t="inlineStr"/>
-      <c r="J69" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-20 06:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K69" s="13" t="inlineStr">
-        <is>
-          <t>Adirondack Asset / HiBid</t>
-        </is>
-      </c>
-      <c r="L69" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M69" s="13" t="inlineStr"/>
-      <c r="N69" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O69" s="14" t="inlineStr">
-        <is>
-          <t>Small lot.</t>
-        </is>
-      </c>
+      <c r="B69" s="12" t="n"/>
+      <c r="C69" s="12" t="n"/>
+      <c r="D69" s="12" t="n"/>
+      <c r="E69" s="12" t="n"/>
+      <c r="F69" s="12" t="n"/>
+      <c r="G69" s="12" t="n"/>
+      <c r="H69" s="12" t="n"/>
+      <c r="I69" s="12" t="n"/>
+      <c r="J69" s="12" t="n"/>
+      <c r="K69" s="12" t="n"/>
+      <c r="L69" s="12" t="n"/>
+      <c r="M69" s="12" t="n"/>
+      <c r="N69" s="12" t="n"/>
+      <c r="O69" s="12" t="n"/>
     </row>
     <row r="70" outlineLevel="1">
       <c r="A70" s="13" t="inlineStr">
@@ -22221,7 +22163,7 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>Restaurant &amp; fitness equipment</t>
+          <t>Former Taco Del Mar – stainless, warmers, walk-in panels</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
@@ -22231,7 +22173,7 @@
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>Williamsville</t>
+          <t>Watson</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
@@ -22240,28 +22182,28 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>408</v>
+        <v>260</v>
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>HiBid online auction</t>
         </is>
       </c>
       <c r="H70" s="15" t="n"/>
       <c r="I70" s="13" t="inlineStr"/>
       <c r="J70" s="13" t="inlineStr">
         <is>
-          <t>2026-10-26 07:30 PM ET</t>
+          <t>2026-10-20 06:00 PM ET</t>
         </is>
       </c>
       <c r="K70" s="13" t="inlineStr">
         <is>
-          <t>Cash Auctions</t>
-        </is>
-      </c>
-      <c r="L70" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Adirondack Asset / HiBid</t>
+        </is>
+      </c>
+      <c r="L70" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M70" s="13" t="inlineStr"/>
@@ -22272,231 +22214,231 @@
       </c>
       <c r="O70" s="14" t="inlineStr">
         <is>
+          <t>Small lot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" outlineLevel="1">
+      <c r="A71" s="13" t="inlineStr">
+        <is>
+          <t>Upstate / Western NY</t>
+        </is>
+      </c>
+      <c r="B71" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant &amp; fitness equipment</t>
+        </is>
+      </c>
+      <c r="C71" s="13" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="D71" s="13" t="inlineStr">
+        <is>
+          <t>Williamsville</t>
+        </is>
+      </c>
+      <c r="E71" s="13" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F71" s="13" t="n">
+        <v>408</v>
+      </c>
+      <c r="G71" s="13" t="inlineStr">
+        <is>
+          <t>Online auction</t>
+        </is>
+      </c>
+      <c r="H71" s="15" t="n"/>
+      <c r="I71" s="13" t="inlineStr"/>
+      <c r="J71" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-26 07:30 PM ET</t>
+        </is>
+      </c>
+      <c r="K71" s="13" t="inlineStr">
+        <is>
+          <t>Cash Auctions</t>
+        </is>
+      </c>
+      <c r="L71" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M71" s="13" t="inlineStr"/>
+      <c r="N71" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O71" s="14" t="inlineStr">
+        <is>
           <t>Lots not reviewed.</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="17" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Upstate / Western NY</t>
         </is>
       </c>
-      <c r="B71" s="17" t="inlineStr">
+      <c r="B72" s="17" t="inlineStr">
         <is>
           <t>2 item(s)</t>
         </is>
       </c>
-      <c r="C71" s="18" t="n"/>
-      <c r="D71" s="18" t="n"/>
-      <c r="E71" s="18" t="n"/>
-      <c r="F71" s="18" t="n"/>
-      <c r="G71" s="18" t="n"/>
-      <c r="H71" s="19" t="n">
+      <c r="C72" s="18" t="n"/>
+      <c r="D72" s="18" t="n"/>
+      <c r="E72" s="18" t="n"/>
+      <c r="F72" s="18" t="n"/>
+      <c r="G72" s="18" t="n"/>
+      <c r="H72" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I71" s="18" t="n"/>
-      <c r="J71" s="18" t="n"/>
-      <c r="K71" s="18" t="n"/>
-      <c r="L71" s="18" t="n"/>
-      <c r="M71" s="18" t="n"/>
-      <c r="N71" s="18" t="n"/>
-      <c r="O71" s="18" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="11" t="inlineStr">
+      <c r="I72" s="18" t="n"/>
+      <c r="J72" s="18" t="n"/>
+      <c r="K72" s="18" t="n"/>
+      <c r="L72" s="18" t="n"/>
+      <c r="M72" s="18" t="n"/>
+      <c r="N72" s="18" t="n"/>
+      <c r="O72" s="18" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
         <is>
           <t>▸ Virginia  (1)</t>
         </is>
       </c>
-      <c r="B72" s="12" t="n"/>
-      <c r="C72" s="12" t="n"/>
-      <c r="D72" s="12" t="n"/>
-      <c r="E72" s="12" t="n"/>
-      <c r="F72" s="12" t="n"/>
-      <c r="G72" s="12" t="n"/>
-      <c r="H72" s="12" t="n"/>
-      <c r="I72" s="12" t="n"/>
-      <c r="J72" s="12" t="n"/>
-      <c r="K72" s="12" t="n"/>
-      <c r="L72" s="12" t="n"/>
-      <c r="M72" s="12" t="n"/>
-      <c r="N72" s="12" t="n"/>
-      <c r="O72" s="12" t="n"/>
-    </row>
-    <row r="73" outlineLevel="1">
-      <c r="A73" s="13" t="inlineStr">
+      <c r="B73" s="12" t="n"/>
+      <c r="C73" s="12" t="n"/>
+      <c r="D73" s="12" t="n"/>
+      <c r="E73" s="12" t="n"/>
+      <c r="F73" s="12" t="n"/>
+      <c r="G73" s="12" t="n"/>
+      <c r="H73" s="12" t="n"/>
+      <c r="I73" s="12" t="n"/>
+      <c r="J73" s="12" t="n"/>
+      <c r="K73" s="12" t="n"/>
+      <c r="L73" s="12" t="n"/>
+      <c r="M73" s="12" t="n"/>
+      <c r="N73" s="12" t="n"/>
+      <c r="O73" s="12" t="n"/>
+    </row>
+    <row r="74" outlineLevel="1">
+      <c r="A74" s="13" t="inlineStr">
         <is>
           <t>Virginia</t>
         </is>
       </c>
-      <c r="B73" s="14" t="inlineStr">
+      <c r="B74" s="14" t="inlineStr">
         <is>
           <t>Haynes Furniture / The Dump – 12 stores closing (furniture, mattresses)</t>
         </is>
       </c>
-      <c r="C73" s="13" t="inlineStr">
+      <c r="C74" s="13" t="inlineStr">
         <is>
           <t>retail GOB</t>
         </is>
       </c>
-      <c r="D73" s="13" t="inlineStr">
+      <c r="D74" s="13" t="inlineStr">
         <is>
           <t>Virginia Beach</t>
         </is>
       </c>
-      <c r="E73" s="13" t="inlineStr">
+      <c r="E74" s="13" t="inlineStr">
         <is>
           <t>VA</t>
         </is>
       </c>
-      <c r="F73" s="13" t="n">
+      <c r="F74" s="13" t="n">
         <v>456</v>
       </c>
-      <c r="G73" s="13" t="inlineStr">
+      <c r="G74" s="13" t="inlineStr">
         <is>
           <t>Retail GOB markdowns</t>
         </is>
       </c>
-      <c r="H73" s="15" t="n"/>
-      <c r="I73" s="13" t="inlineStr">
+      <c r="H74" s="15" t="n"/>
+      <c r="I74" s="13" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="J73" s="13" t="inlineStr"/>
-      <c r="K73" s="13" t="inlineStr">
+      <c r="J74" s="13" t="inlineStr"/>
+      <c r="K74" s="13" t="inlineStr">
         <is>
           <t>SB360 (PR Newswire)</t>
         </is>
       </c>
-      <c r="L73" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M73" s="13" t="inlineStr"/>
-      <c r="N73" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O73" s="14" t="inlineStr">
+      <c r="L74" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M74" s="13" t="inlineStr"/>
+      <c r="N74" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O74" s="14" t="inlineStr">
         <is>
           <t>Posted Oct 8. Multi-state (VA/AZ/GA/IL/TX); pinned at Virginia Beach. Home goods only.</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="17" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Virginia</t>
         </is>
       </c>
-      <c r="B74" s="17" t="inlineStr">
+      <c r="B75" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C74" s="18" t="n"/>
-      <c r="D74" s="18" t="n"/>
-      <c r="E74" s="18" t="n"/>
-      <c r="F74" s="18" t="n"/>
-      <c r="G74" s="18" t="n"/>
-      <c r="H74" s="19" t="n">
+      <c r="C75" s="18" t="n"/>
+      <c r="D75" s="18" t="n"/>
+      <c r="E75" s="18" t="n"/>
+      <c r="F75" s="18" t="n"/>
+      <c r="G75" s="18" t="n"/>
+      <c r="H75" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I74" s="18" t="n"/>
-      <c r="J74" s="18" t="n"/>
-      <c r="K74" s="18" t="n"/>
-      <c r="L74" s="18" t="n"/>
-      <c r="M74" s="18" t="n"/>
-      <c r="N74" s="18" t="n"/>
-      <c r="O74" s="18" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="11" t="inlineStr">
+      <c r="I75" s="18" t="n"/>
+      <c r="J75" s="18" t="n"/>
+      <c r="K75" s="18" t="n"/>
+      <c r="L75" s="18" t="n"/>
+      <c r="M75" s="18" t="n"/>
+      <c r="N75" s="18" t="n"/>
+      <c r="O75" s="18" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="11" t="inlineStr">
         <is>
           <t>▸ Midwest  (2)</t>
         </is>
       </c>
-      <c r="B75" s="12" t="n"/>
-      <c r="C75" s="12" t="n"/>
-      <c r="D75" s="12" t="n"/>
-      <c r="E75" s="12" t="n"/>
-      <c r="F75" s="12" t="n"/>
-      <c r="G75" s="12" t="n"/>
-      <c r="H75" s="12" t="n"/>
-      <c r="I75" s="12" t="n"/>
-      <c r="J75" s="12" t="n"/>
-      <c r="K75" s="12" t="n"/>
-      <c r="L75" s="12" t="n"/>
-      <c r="M75" s="12" t="n"/>
-      <c r="N75" s="12" t="n"/>
-      <c r="O75" s="12" t="n"/>
-    </row>
-    <row r="76" outlineLevel="1">
-      <c r="A76" s="13" t="inlineStr">
-        <is>
-          <t>Midwest</t>
-        </is>
-      </c>
-      <c r="B76" s="14" t="inlineStr">
-        <is>
-          <t>American Sale – total liquidation, all 7 stores (pools, hot tubs, grills, holiday decor)</t>
-        </is>
-      </c>
-      <c r="C76" s="13" t="inlineStr">
-        <is>
-          <t>retail GOB</t>
-        </is>
-      </c>
-      <c r="D76" s="13" t="inlineStr">
-        <is>
-          <t>Chicagoland</t>
-        </is>
-      </c>
-      <c r="E76" s="13" t="inlineStr">
-        <is>
-          <t>IL</t>
-        </is>
-      </c>
-      <c r="F76" s="13" t="n">
-        <v>876</v>
-      </c>
-      <c r="G76" s="13" t="inlineStr">
-        <is>
-          <t>Retail GOB, up to 70% off</t>
-        </is>
-      </c>
-      <c r="H76" s="15" t="n"/>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="J76" s="13" t="inlineStr"/>
-      <c r="K76" s="13" t="inlineStr">
-        <is>
-          <t>Tiger Group (PR Newswire)</t>
-        </is>
-      </c>
-      <c r="L76" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M76" s="13" t="inlineStr"/>
-      <c r="N76" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O76" s="14" t="inlineStr">
-        <is>
-          <t>Posted Oct 15. Watch for a bulk/fixture auction.</t>
-        </is>
-      </c>
+      <c r="B76" s="12" t="n"/>
+      <c r="C76" s="12" t="n"/>
+      <c r="D76" s="12" t="n"/>
+      <c r="E76" s="12" t="n"/>
+      <c r="F76" s="12" t="n"/>
+      <c r="G76" s="12" t="n"/>
+      <c r="H76" s="12" t="n"/>
+      <c r="I76" s="12" t="n"/>
+      <c r="J76" s="12" t="n"/>
+      <c r="K76" s="12" t="n"/>
+      <c r="L76" s="12" t="n"/>
+      <c r="M76" s="12" t="n"/>
+      <c r="N76" s="12" t="n"/>
+      <c r="O76" s="12" t="n"/>
     </row>
     <row r="77" outlineLevel="1">
       <c r="A77" s="13" t="inlineStr">
@@ -22506,47 +22448,47 @@
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>Straub's Fine Foods store equipment – bakery, kitchen, meat room, Hussmann refrigeration</t>
+          <t>American Sale – total liquidation, all 7 stores (pools, hot tubs, grills, holiday decor)</t>
         </is>
       </c>
       <c r="C77" s="13" t="inlineStr">
         <is>
-          <t>grocery/restaurant</t>
+          <t>retail GOB</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Chicagoland</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>1046</v>
+        <v>876</v>
       </c>
       <c r="G77" s="13" t="inlineStr">
         <is>
-          <t>Online auction (18% BP)</t>
+          <t>Retail GOB, up to 70% off</t>
         </is>
       </c>
       <c r="H77" s="15" t="n"/>
-      <c r="I77" s="13" t="inlineStr"/>
-      <c r="J77" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J77" s="13" t="inlineStr"/>
       <c r="K77" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L77" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Tiger Group (PR Newswire)</t>
+        </is>
+      </c>
+      <c r="L77" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M77" s="13" t="inlineStr"/>
@@ -22557,261 +22499,324 @@
       </c>
       <c r="O77" s="14" t="inlineStr">
         <is>
+          <t>Posted Oct 15. Watch for a bulk/fixture auction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" outlineLevel="1">
+      <c r="A78" s="13" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>Straub's Fine Foods store equipment – bakery, kitchen, meat room, Hussmann refrigeration</t>
+        </is>
+      </c>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>grocery/restaurant</t>
+        </is>
+      </c>
+      <c r="D78" s="13" t="inlineStr">
+        <is>
+          <t>St. Louis</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="F78" s="13" t="n">
+        <v>1046</v>
+      </c>
+      <c r="G78" s="13" t="inlineStr">
+        <is>
+          <t>Online auction (18% BP)</t>
+        </is>
+      </c>
+      <c r="H78" s="15" t="n"/>
+      <c r="I78" s="13" t="inlineStr"/>
+      <c r="J78" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K78" s="13" t="inlineStr">
+        <is>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L78" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M78" s="13" t="inlineStr"/>
+      <c r="N78" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O78" s="14" t="inlineStr">
+        <is>
           <t>Kingshighway store: Revent double-rack oven + proofer, Reed revolving oven, Vulcan convection, Groen kettle, Southbend 6-burner, Pitco fryer, Stero dishwasher, Hobart saw/grinders, Berkel slicers, Hussmann cases + compressor racks, walk-ins, Hoshizaki/Scotsman ice machines, Crown pallet jack. Preview Oct 20 3–6 PM CDT; pickup in St. Louis.</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="17" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Midwest</t>
         </is>
       </c>
-      <c r="B78" s="17" t="inlineStr">
+      <c r="B79" s="17" t="inlineStr">
         <is>
           <t>2 item(s)</t>
         </is>
       </c>
-      <c r="C78" s="18" t="n"/>
-      <c r="D78" s="18" t="n"/>
-      <c r="E78" s="18" t="n"/>
-      <c r="F78" s="18" t="n"/>
-      <c r="G78" s="18" t="n"/>
-      <c r="H78" s="19" t="n">
+      <c r="C79" s="18" t="n"/>
+      <c r="D79" s="18" t="n"/>
+      <c r="E79" s="18" t="n"/>
+      <c r="F79" s="18" t="n"/>
+      <c r="G79" s="18" t="n"/>
+      <c r="H79" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I78" s="18" t="n"/>
-      <c r="J78" s="18" t="n"/>
-      <c r="K78" s="18" t="n"/>
-      <c r="L78" s="18" t="n"/>
-      <c r="M78" s="18" t="n"/>
-      <c r="N78" s="18" t="n"/>
-      <c r="O78" s="18" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="11" t="inlineStr">
+      <c r="I79" s="18" t="n"/>
+      <c r="J79" s="18" t="n"/>
+      <c r="K79" s="18" t="n"/>
+      <c r="L79" s="18" t="n"/>
+      <c r="M79" s="18" t="n"/>
+      <c r="N79" s="18" t="n"/>
+      <c r="O79" s="18" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="inlineStr">
         <is>
           <t>▸ Texas / South Central  (1)</t>
         </is>
       </c>
-      <c r="B79" s="12" t="n"/>
-      <c r="C79" s="12" t="n"/>
-      <c r="D79" s="12" t="n"/>
-      <c r="E79" s="12" t="n"/>
-      <c r="F79" s="12" t="n"/>
-      <c r="G79" s="12" t="n"/>
-      <c r="H79" s="12" t="n"/>
-      <c r="I79" s="12" t="n"/>
-      <c r="J79" s="12" t="n"/>
-      <c r="K79" s="12" t="n"/>
-      <c r="L79" s="12" t="n"/>
-      <c r="M79" s="12" t="n"/>
-      <c r="N79" s="12" t="n"/>
-      <c r="O79" s="12" t="n"/>
-    </row>
-    <row r="80" outlineLevel="1">
-      <c r="A80" s="13" t="inlineStr">
+      <c r="B80" s="12" t="n"/>
+      <c r="C80" s="12" t="n"/>
+      <c r="D80" s="12" t="n"/>
+      <c r="E80" s="12" t="n"/>
+      <c r="F80" s="12" t="n"/>
+      <c r="G80" s="12" t="n"/>
+      <c r="H80" s="12" t="n"/>
+      <c r="I80" s="12" t="n"/>
+      <c r="J80" s="12" t="n"/>
+      <c r="K80" s="12" t="n"/>
+      <c r="L80" s="12" t="n"/>
+      <c r="M80" s="12" t="n"/>
+      <c r="N80" s="12" t="n"/>
+      <c r="O80" s="12" t="n"/>
+    </row>
+    <row r="81" outlineLevel="1">
+      <c r="A81" s="13" t="inlineStr">
         <is>
           <t>Texas / South Central</t>
         </is>
       </c>
-      <c r="B80" s="14" t="inlineStr">
+      <c r="B81" s="14" t="inlineStr">
         <is>
           <t>Southwest beverage distributor surplus – mostly unused: 16 True merchandisers, 75 Bunn brewers, 100+ micro-market kiosks</t>
         </is>
       </c>
-      <c r="C80" s="13" t="inlineStr">
+      <c r="C81" s="13" t="inlineStr">
         <is>
           <t>distributor surplus</t>
         </is>
       </c>
-      <c r="D80" s="13" t="inlineStr">
+      <c r="D81" s="13" t="inlineStr">
         <is>
           <t>Mesquite</t>
         </is>
       </c>
-      <c r="E80" s="13" t="inlineStr">
+      <c r="E81" s="13" t="inlineStr">
         <is>
           <t>TX</t>
         </is>
       </c>
-      <c r="F80" s="13" t="n">
+      <c r="F81" s="13" t="n">
         <v>1547</v>
       </c>
-      <c r="G80" s="13" t="inlineStr">
+      <c r="G81" s="13" t="inlineStr">
         <is>
           <t>Online auction</t>
         </is>
       </c>
-      <c r="H80" s="15" t="n"/>
-      <c r="I80" s="13" t="inlineStr"/>
-      <c r="J80" s="13" t="inlineStr">
+      <c r="H81" s="15" t="n"/>
+      <c r="I81" s="13" t="inlineStr"/>
+      <c r="J81" s="13" t="inlineStr">
         <is>
           <t>2026-11-13 11:00 AM ET</t>
         </is>
       </c>
-      <c r="K80" s="13" t="inlineStr">
+      <c r="K81" s="13" t="inlineStr">
         <is>
           <t>Heritage Global Partners</t>
         </is>
       </c>
-      <c r="L80" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M80" s="13" t="inlineStr"/>
-      <c r="N80" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O80" s="14" t="inlineStr">
+      <c r="L81" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M81" s="13" t="inlineStr"/>
+      <c r="N81" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O81" s="14" t="inlineStr">
         <is>
           <t>Near-new appliances, resell by unit. Nov 13 10 AM CST.</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="17" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Texas / South Central</t>
         </is>
       </c>
-      <c r="B81" s="17" t="inlineStr">
+      <c r="B82" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C81" s="18" t="n"/>
-      <c r="D81" s="18" t="n"/>
-      <c r="E81" s="18" t="n"/>
-      <c r="F81" s="18" t="n"/>
-      <c r="G81" s="18" t="n"/>
-      <c r="H81" s="19" t="n">
+      <c r="C82" s="18" t="n"/>
+      <c r="D82" s="18" t="n"/>
+      <c r="E82" s="18" t="n"/>
+      <c r="F82" s="18" t="n"/>
+      <c r="G82" s="18" t="n"/>
+      <c r="H82" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I81" s="18" t="n"/>
-      <c r="J81" s="18" t="n"/>
-      <c r="K81" s="18" t="n"/>
-      <c r="L81" s="18" t="n"/>
-      <c r="M81" s="18" t="n"/>
-      <c r="N81" s="18" t="n"/>
-      <c r="O81" s="18" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="11" t="inlineStr">
+      <c r="I82" s="18" t="n"/>
+      <c r="J82" s="18" t="n"/>
+      <c r="K82" s="18" t="n"/>
+      <c r="L82" s="18" t="n"/>
+      <c r="M82" s="18" t="n"/>
+      <c r="N82" s="18" t="n"/>
+      <c r="O82" s="18" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="11" t="inlineStr">
         <is>
           <t>▸ West / Other  (1)</t>
         </is>
       </c>
-      <c r="B82" s="12" t="n"/>
-      <c r="C82" s="12" t="n"/>
-      <c r="D82" s="12" t="n"/>
-      <c r="E82" s="12" t="n"/>
-      <c r="F82" s="12" t="n"/>
-      <c r="G82" s="12" t="n"/>
-      <c r="H82" s="12" t="n"/>
-      <c r="I82" s="12" t="n"/>
-      <c r="J82" s="12" t="n"/>
-      <c r="K82" s="12" t="n"/>
-      <c r="L82" s="12" t="n"/>
-      <c r="M82" s="12" t="n"/>
-      <c r="N82" s="12" t="n"/>
-      <c r="O82" s="12" t="n"/>
-    </row>
-    <row r="83" outlineLevel="1">
-      <c r="A83" s="13" t="inlineStr">
+      <c r="B83" s="12" t="n"/>
+      <c r="C83" s="12" t="n"/>
+      <c r="D83" s="12" t="n"/>
+      <c r="E83" s="12" t="n"/>
+      <c r="F83" s="12" t="n"/>
+      <c r="G83" s="12" t="n"/>
+      <c r="H83" s="12" t="n"/>
+      <c r="I83" s="12" t="n"/>
+      <c r="J83" s="12" t="n"/>
+      <c r="K83" s="12" t="n"/>
+      <c r="L83" s="12" t="n"/>
+      <c r="M83" s="12" t="n"/>
+      <c r="N83" s="12" t="n"/>
+      <c r="O83" s="12" t="n"/>
+    </row>
+    <row r="84" outlineLevel="1">
+      <c r="A84" s="13" t="inlineStr">
         <is>
           <t>West / Other</t>
         </is>
       </c>
-      <c r="B83" s="14" t="inlineStr">
+      <c r="B84" s="14" t="inlineStr">
         <is>
           <t>National salad concept liquidation – full contents of 63 fast-casual restaurants (AZ/TX/OK/NV)</t>
         </is>
       </c>
-      <c r="C83" s="13" t="inlineStr">
+      <c r="C84" s="13" t="inlineStr">
         <is>
           <t>restaurant chain liquidation</t>
         </is>
       </c>
-      <c r="D83" s="13" t="inlineStr">
+      <c r="D84" s="13" t="inlineStr">
         <is>
           <t>Phoenix</t>
         </is>
       </c>
-      <c r="E83" s="13" t="inlineStr">
+      <c r="E84" s="13" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="F83" s="13" t="n">
+      <c r="F84" s="13" t="n">
         <v>2307</v>
       </c>
-      <c r="G83" s="13" t="inlineStr">
+      <c r="G84" s="13" t="inlineStr">
         <is>
           <t>Online auctions, dates TBD</t>
         </is>
       </c>
-      <c r="H83" s="15" t="n"/>
-      <c r="I83" s="13" t="inlineStr">
+      <c r="H84" s="15" t="n"/>
+      <c r="I84" s="13" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="J83" s="13" t="inlineStr"/>
-      <c r="K83" s="13" t="inlineStr">
+      <c r="J84" s="13" t="inlineStr"/>
+      <c r="K84" s="13" t="inlineStr">
         <is>
           <t>RestaurantEquipment.bid (TAGeX)</t>
         </is>
       </c>
-      <c r="L83" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M83" s="13" t="inlineStr"/>
-      <c r="N83" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O83" s="14" t="inlineStr">
+      <c r="L84" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M84" s="13" t="inlineStr"/>
+      <c r="N84" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O84" s="14" t="inlineStr">
         <is>
           <t>Rolling market-by-market auctions, none live yet (Phoenix metro 30 locations, DFW 14, Tucson 6, Houston 5, plus OK/NV). Pickup on site at each restaurant. Pinned at Phoenix.</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="17" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="17" t="inlineStr">
         <is>
           <t>Subtotal — West / Other</t>
         </is>
       </c>
-      <c r="B84" s="17" t="inlineStr">
+      <c r="B85" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C84" s="18" t="n"/>
-      <c r="D84" s="18" t="n"/>
-      <c r="E84" s="18" t="n"/>
-      <c r="F84" s="18" t="n"/>
-      <c r="G84" s="18" t="n"/>
-      <c r="H84" s="19" t="n">
+      <c r="C85" s="18" t="n"/>
+      <c r="D85" s="18" t="n"/>
+      <c r="E85" s="18" t="n"/>
+      <c r="F85" s="18" t="n"/>
+      <c r="G85" s="18" t="n"/>
+      <c r="H85" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I84" s="18" t="n"/>
-      <c r="J84" s="18" t="n"/>
-      <c r="K84" s="18" t="n"/>
-      <c r="L84" s="18" t="n"/>
-      <c r="M84" s="18" t="n"/>
-      <c r="N84" s="18" t="n"/>
-      <c r="O84" s="18" t="n"/>
+      <c r="I85" s="18" t="n"/>
+      <c r="J85" s="18" t="n"/>
+      <c r="K85" s="18" t="n"/>
+      <c r="L85" s="18" t="n"/>
+      <c r="M85" s="18" t="n"/>
+      <c r="N85" s="18" t="n"/>
+      <c r="O85" s="18" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O84"/>
+  <autoFilter ref="A1:O85"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId2"/>
@@ -22835,7 +22840,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId26"/>
@@ -22859,17 +22864,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N60" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N61" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N62" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N65" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N66" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N69" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N67" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N73" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N76" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N71" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N74" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N77" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N80" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N83" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N78" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N81" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N84" r:id="rId58"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22881,7 +22887,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -23043,7 +23049,7 @@
       </c>
       <c r="O2" s="14" t="inlineStr">
         <is>
-          <t>Integrity Auction House. Internet bidding closes Mon Oct 19 9:18 PM ET. $50 high bid (1 bid) as of 2026-10-18. [Closed Oct 19; HiBid price realized $50.] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Integrity Auction House. Internet bidding closes Mon Oct 19 9:18 PM ET. $50 high bid (1 bid) as of 2026-10-18. [Closed Oct 19; HiBid price realized $50.] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23106,7 +23112,7 @@
       </c>
       <c r="O3" s="14" t="inlineStr">
         <is>
-          <t>Live auction Mon Oct 19 4 PM, 3457 Wilmington Rd. Few bulk parts. [Live auction held Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Live auction Mon Oct 19 4 PM, 3457 Wilmington Rd. Few bulk parts. [Live auction held Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23307,7 +23313,7 @@
       </c>
       <c r="O6" s="14" t="inlineStr">
         <is>
-          <t>Condition: Pre-Owned. FLIP: SO36U/S tested, auction $99/0 bids, pickup only; rough resale $600-1k (eBay card shows no city; pickup distance in source.) Ends Oct 18 ~2:19 PM per eBay card (time zone uncertain; could be earlier). [auto-removed 2026-10-18: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Condition: Pre-Owned. FLIP: SO36U/S tested, auction $99/0 bids, pickup only; rough resale $600-1k (eBay card shows no city; pickup distance in source.) Ends Oct 18 ~2:19 PM per eBay card (time zone uncertain; could be earlier). [auto-removed 2026-10-18: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23372,7 +23378,7 @@
       </c>
       <c r="O7" s="14" t="inlineStr">
         <is>
-          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf) HiBid lot closed/sold ~$37.50 on 2026-10-18. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf) HiBid lot closed/sold ~$37.50 on 2026-10-18. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23437,59 +23443,61 @@
       </c>
       <c r="O8" s="14" t="inlineStr">
         <is>
-          <t>Lots close from Oct 19 2 PM ET. [HiBid catalog closed 2 PM ET Oct 19.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Lots close from Oct 19 2 PM ET. [HiBid catalog closed 2 PM ET Oct 19.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>Maine / VT / Northern NH</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>Oola Bowls secured-party sale – restaurant equipment bought new 2024-25 (Electro Freeze, Scotsman, Atosa)</t>
+          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Fort Wayne)</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>auction catalog</t>
         </is>
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>Scarborough</t>
+          <t>Fort Wayne</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>ME</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>104</v>
+        <v>743</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
-          <t>Online auction (freezers $80–150 when seen)</t>
-        </is>
-      </c>
-      <c r="H9" s="15" t="n"/>
+          <t>$0–1 openers + 15% BP + $1/lot</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="I9" s="13" t="inlineStr"/>
       <c r="J9" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00 PM ET</t>
+          <t>2026-10-20 02:00 PM ET</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
         <is>
-          <t>Keenan Auction / Proxibid</t>
+          <t>HiBid (Auctionfuel)</t>
         </is>
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 01:00 PM ET)</t>
+          <t>EXPIRED (2026-10-20 02:00 PM ET)</t>
         </is>
       </c>
       <c r="M9" s="13" t="inlineStr"/>
@@ -23500,59 +23508,59 @@
       </c>
       <c r="O9" s="14" t="inlineStr">
         <is>
-          <t>Pickup Oct 21 only. [Lots began closing 1 PM ET Oct 19; ended.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Lots close from Oct 20 2 PM ET. [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>NYC / Long Island / NJ</t>
+          <t>CT / Hudson Valley</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>Milwaukee / Walmart / hardware store mega auction pt 3</t>
+          <t>Major Intl Chain Surplus – 225 lots commercial refrigeration/kitchen (True, Traulsen, Hobart, Blodgett, Taylor)</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>commercial surplus</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>Mount Holly</t>
+          <t>Pleasant Valley</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>254</v>
+        <v>157</v>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>HiBid online auction</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H10" s="15" t="n"/>
       <c r="I10" s="13" t="inlineStr"/>
       <c r="J10" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 06:00 PM ET</t>
+          <t>2026-10-20 02:00 PM ET</t>
         </is>
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>HiBid</t>
+          <t>Adams / BidWrangler</t>
         </is>
       </c>
       <c r="L10" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 06:00 PM ET)</t>
+          <t>EXPIRED (2026-10-20 02:00 PM ET)</t>
         </is>
       </c>
       <c r="M10" s="13" t="inlineStr"/>
@@ -23563,19 +23571,19 @@
       </c>
       <c r="O10" s="14" t="inlineStr">
         <is>
-          <t>Close Oct 18 or 19 6 PM (later used). [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Tested and new units. [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Upstate / Western NY</t>
+          <t>Maine / VT / Northern NH</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>Closed restaurant – coolers, fridges, prep tables</t>
+          <t>Oola Bowls secured-party sale – restaurant equipment bought new 2024-25 (Electro Freeze, Scotsman, Atosa)</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
@@ -23585,37 +23593,37 @@
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Palmyra</t>
+          <t>Scarborough</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>333</v>
+        <v>104</v>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>HiBid, 15% BP</t>
+          <t>Online auction (freezers $80–150 when seen)</t>
         </is>
       </c>
       <c r="H11" s="15" t="n"/>
       <c r="I11" s="13" t="inlineStr"/>
       <c r="J11" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 07:00 PM ET</t>
+          <t>2026-10-19 01:00 PM ET</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>Reynolds Auction Co / HiBid</t>
+          <t>Keenan Auction / Proxibid</t>
         </is>
       </c>
       <c r="L11" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 07:00 PM ET)</t>
+          <t>EXPIRED (2026-10-19 01:00 PM ET)</t>
         </is>
       </c>
       <c r="M11" s="13" t="inlineStr"/>
@@ -23626,59 +23634,59 @@
       </c>
       <c r="O11" s="14" t="inlineStr">
         <is>
-          <t>No new out-of-state bidders. Small. [Ended Oct 19 7 PM.] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Pickup Oct 21 only. [Lots began closing 1 PM ET Oct 19; ended.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>NYC / Long Island / NJ</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Freshway Market whole-grocery liquidation – refrigeration racks, cases, walk-ins, generator</t>
+          <t>Milwaukee / Walmart / hardware store mega auction pt 3</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Mount Holly</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>862</v>
+        <v>254</v>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>HiBid online auction</t>
         </is>
       </c>
       <c r="H12" s="15" t="n"/>
       <c r="I12" s="13" t="inlineStr"/>
       <c r="J12" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 11:00 AM ET</t>
+          <t>2026-10-19 06:00 PM ET</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
+          <t>HiBid</t>
         </is>
       </c>
       <c r="L12" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-20 11:00 AM ET)</t>
+          <t>EXPIRED (2026-10-19 06:00 PM ET)</t>
         </is>
       </c>
       <c r="M12" s="13" t="inlineStr"/>
@@ -23689,59 +23697,59 @@
       </c>
       <c r="O12" s="14" t="inlineStr">
         <is>
-          <t>Closes from Oct 20 10 AM CDT. [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Close Oct 18 or 19 6 PM (later used). [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>Greater Boston / South Shore (&lt;50mi)</t>
+          <t>Upstate / Western NY</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>Closed Best Buy Outlet – pallet racking, Big Joe order pickers, appliance dollies, carts, cages</t>
+          <t>Closed restaurant – coolers, fridges, prep tables</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>store closing fixtures</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>Brockton</t>
+          <t>Palmyra</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>11</v>
+        <v>333</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>Racking $40/upright, $80/level; pickers $1,000 OBO</t>
+          <t>HiBid, 15% BP</t>
         </is>
       </c>
       <c r="H13" s="15" t="n"/>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="J13" s="13" t="inlineStr"/>
+      <c r="I13" s="13" t="inlineStr"/>
+      <c r="J13" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 07:00 PM ET</t>
+        </is>
+      </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>Reynolds Auction Co / HiBid</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>EXPIRED (2026-10-19 07:00 PM ET)</t>
         </is>
       </c>
       <c r="M13" s="13" t="inlineStr"/>
@@ -23752,63 +23760,59 @@
       </c>
       <c r="O13" s="14" t="inlineStr">
         <is>
-          <t>200 Westgate Dr. Fixtures/equipment only, no merchandise. On site daily. CL deleted by author (HTTP 410) as of 2026-10-19 midday recheck.</t>
+          <t>No new out-of-state bidders. Small. [Ended Oct 19 7 PM.] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>NYC / Long Island / NJ</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Like-new restaurant – steam tables, Coldline, Cleveland cook-and-hold, fryers, True freezers</t>
+          <t>Freshway Market whole-grocery liquidation – refrigeration racks, cases, walk-ins, generator</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>Staten Island</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>203</v>
+        <v>862</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H14" s="15" t="n"/>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+      <c r="I14" s="13" t="inlineStr"/>
       <c r="J14" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00 PM ET</t>
+          <t>2026-10-20 11:00 AM ET</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>Grafe Auction</t>
         </is>
       </c>
       <c r="L14" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 01:00 PM ET)</t>
+          <t>EXPIRED (2026-10-20 11:00 AM ET)</t>
         </is>
       </c>
       <c r="M14" s="13" t="inlineStr"/>
@@ -23819,63 +23823,59 @@
       </c>
       <c r="O14" s="14" t="inlineStr">
         <is>
-          <t>"Short notice" auction Mon Oct 19 1 PM. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Closes from Oct 20 10 AM CDT. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>NYC / Long Island / NJ</t>
+          <t>Greater Boston / South Shore (&lt;50mi)</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>High-end deli (contents not described)</t>
+          <t>Closed Best Buy Outlet – pallet racking, Big Joe order pickers, appliance dollies, carts, cages</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>store closing fixtures</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>Manalapan Township</t>
+          <t>Brockton</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>223</v>
+        <v>11</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Racking $40/upright, $80/level; pickers $1,000 OBO</t>
         </is>
       </c>
       <c r="H15" s="15" t="n"/>
       <c r="I15" s="13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="J15" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-19 04:00 PM ET</t>
-        </is>
-      </c>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="J15" s="13" t="inlineStr"/>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 04:00 PM ET)</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="M15" s="13" t="inlineStr"/>
@@ -23886,12 +23886,213 @@
       </c>
       <c r="O15" s="14" t="inlineStr">
         <is>
-          <t>Mon Oct 19 4 PM. No item description on page. [HiBid shows Bidding Closed, Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>200 Westgate Dr. Fixtures/equipment only, no merchandise. On site daily. CL deleted by author (HTTP 410) as of 2026-10-19 midday recheck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B16" s="14" t="inlineStr">
+        <is>
+          <t>Like-new restaurant – steam tables, Coldline, Cleveland cook-and-hold, fryers, True freezers</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
+        <is>
+          <t>auction</t>
+        </is>
+      </c>
+      <c r="D16" s="13" t="inlineStr">
+        <is>
+          <t>Staten Island</t>
+        </is>
+      </c>
+      <c r="E16" s="13" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F16" s="13" t="n">
+        <v>203</v>
+      </c>
+      <c r="G16" s="13" t="inlineStr">
+        <is>
+          <t>Live + webcast, 18% BP + 3%</t>
+        </is>
+      </c>
+      <c r="H16" s="15" t="n"/>
+      <c r="I16" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 01:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K16" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L16" s="13" t="inlineStr">
+        <is>
+          <t>EXPIRED (2026-10-19 01:00 PM ET)</t>
+        </is>
+      </c>
+      <c r="M16" s="13" t="inlineStr"/>
+      <c r="N16" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O16" s="14" t="inlineStr">
+        <is>
+          <t>"Short notice" auction Mon Oct 19 1 PM. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant / pizzeria (contents not described)</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>restaurant closing</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Berkeley Heights</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>213</v>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Live + webcast, 18% BP + 3%</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="n"/>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J17" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-20 02:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L17" s="13" t="inlineStr">
+        <is>
+          <t>EXPIRED (2026-10-20 02:00 PM ET)</t>
+        </is>
+      </c>
+      <c r="M17" s="13" t="inlineStr"/>
+      <c r="N17" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O17" s="14" t="inlineStr">
+        <is>
+          <t>Tue Oct 20 2 PM. No item description on page. [auto-removed 2026-10-20: closing date passed]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>High-end deli (contents not described)</t>
+        </is>
+      </c>
+      <c r="C18" s="13" t="inlineStr">
+        <is>
+          <t>restaurant closing</t>
+        </is>
+      </c>
+      <c r="D18" s="13" t="inlineStr">
+        <is>
+          <t>Manalapan Township</t>
+        </is>
+      </c>
+      <c r="E18" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F18" s="13" t="n">
+        <v>223</v>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>Live + webcast, 18% BP + 3%</t>
+        </is>
+      </c>
+      <c r="H18" s="15" t="n"/>
+      <c r="I18" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J18" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 04:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K18" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L18" s="13" t="inlineStr">
+        <is>
+          <t>EXPIRED (2026-10-19 04:00 PM ET)</t>
+        </is>
+      </c>
+      <c r="M18" s="13" t="inlineStr"/>
+      <c r="N18" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O18" s="14" t="inlineStr">
+        <is>
+          <t>Mon Oct 19 4 PM. No item description on page. [HiBid shows Bidding Closed, Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O15"/>
+  <autoFilter ref="A1:O18"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -23907,6 +24108,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lot_recon.xlsx
+++ b/lot_recon.xlsx
@@ -20,8 +20,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wolf New'!$A$1:$O$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wolf Used'!$A$1:$O$189</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Wolf Unclear'!$A$1:$O$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$85</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Removed'!$A$1:$O$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Removed'!$A$1:$O$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -577,7 +577,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Last updated: 2026-10-20 14:01 ET</t>
+          <t>Last updated: 2026-10-20 18:00 ET</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Active listings: 295 · Removed: 17</t>
+          <t>Active listings: 294 · Removed: 18</t>
         </is>
       </c>
     </row>
@@ -708,13 +708,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13">
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>980438.58</v>
@@ -1121,7 +1121,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C27" t="n">
         <v>0</v>
@@ -1136,7 +1136,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="6" t="n">
         <v>2250</v>
@@ -18412,7 +18412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -22137,7 +22137,7 @@
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t>▸ Upstate / Western NY  (2)</t>
+          <t>▸ Upstate / Western NY  (1)</t>
         </is>
       </c>
       <c r="B69" s="12" t="n"/>
@@ -22163,7 +22163,7 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>Former Taco Del Mar – stainless, warmers, walk-in panels</t>
+          <t>Restaurant &amp; fitness equipment</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
@@ -22173,7 +22173,7 @@
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>Watson</t>
+          <t>Williamsville</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
@@ -22182,28 +22182,28 @@
         </is>
       </c>
       <c r="F70" s="13" t="n">
-        <v>260</v>
+        <v>408</v>
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
-          <t>HiBid online auction</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H70" s="15" t="n"/>
       <c r="I70" s="13" t="inlineStr"/>
       <c r="J70" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 06:00 PM ET</t>
+          <t>2026-10-26 07:30 PM ET</t>
         </is>
       </c>
       <c r="K70" s="13" t="inlineStr">
         <is>
-          <t>Adirondack Asset / HiBid</t>
-        </is>
-      </c>
-      <c r="L70" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Cash Auctions</t>
+        </is>
+      </c>
+      <c r="L70" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M70" s="13" t="inlineStr"/>
@@ -22214,231 +22214,231 @@
       </c>
       <c r="O70" s="14" t="inlineStr">
         <is>
-          <t>Small lot.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" outlineLevel="1">
-      <c r="A71" s="13" t="inlineStr">
-        <is>
-          <t>Upstate / Western NY</t>
-        </is>
-      </c>
-      <c r="B71" s="14" t="inlineStr">
-        <is>
-          <t>Restaurant &amp; fitness equipment</t>
-        </is>
-      </c>
-      <c r="C71" s="13" t="inlineStr">
-        <is>
-          <t>restaurant</t>
-        </is>
-      </c>
-      <c r="D71" s="13" t="inlineStr">
-        <is>
-          <t>Williamsville</t>
-        </is>
-      </c>
-      <c r="E71" s="13" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="F71" s="13" t="n">
-        <v>408</v>
-      </c>
-      <c r="G71" s="13" t="inlineStr">
-        <is>
-          <t>Online auction</t>
-        </is>
-      </c>
-      <c r="H71" s="15" t="n"/>
-      <c r="I71" s="13" t="inlineStr"/>
-      <c r="J71" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-26 07:30 PM ET</t>
-        </is>
-      </c>
-      <c r="K71" s="13" t="inlineStr">
-        <is>
-          <t>Cash Auctions</t>
-        </is>
-      </c>
-      <c r="L71" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M71" s="13" t="inlineStr"/>
-      <c r="N71" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O71" s="14" t="inlineStr">
-        <is>
           <t>Lots not reviewed.</t>
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Upstate / Western NY</t>
+        </is>
+      </c>
+      <c r="B71" s="17" t="inlineStr">
+        <is>
+          <t>1 item(s)</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="n"/>
+      <c r="D71" s="18" t="n"/>
+      <c r="E71" s="18" t="n"/>
+      <c r="F71" s="18" t="n"/>
+      <c r="G71" s="18" t="n"/>
+      <c r="H71" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="18" t="n"/>
+      <c r="J71" s="18" t="n"/>
+      <c r="K71" s="18" t="n"/>
+      <c r="L71" s="18" t="n"/>
+      <c r="M71" s="18" t="n"/>
+      <c r="N71" s="18" t="n"/>
+      <c r="O71" s="18" t="n"/>
+    </row>
     <row r="72">
-      <c r="A72" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Upstate / Western NY</t>
-        </is>
-      </c>
-      <c r="B72" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C72" s="18" t="n"/>
-      <c r="D72" s="18" t="n"/>
-      <c r="E72" s="18" t="n"/>
-      <c r="F72" s="18" t="n"/>
-      <c r="G72" s="18" t="n"/>
-      <c r="H72" s="19" t="n">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>▸ Virginia  (1)</t>
+        </is>
+      </c>
+      <c r="B72" s="12" t="n"/>
+      <c r="C72" s="12" t="n"/>
+      <c r="D72" s="12" t="n"/>
+      <c r="E72" s="12" t="n"/>
+      <c r="F72" s="12" t="n"/>
+      <c r="G72" s="12" t="n"/>
+      <c r="H72" s="12" t="n"/>
+      <c r="I72" s="12" t="n"/>
+      <c r="J72" s="12" t="n"/>
+      <c r="K72" s="12" t="n"/>
+      <c r="L72" s="12" t="n"/>
+      <c r="M72" s="12" t="n"/>
+      <c r="N72" s="12" t="n"/>
+      <c r="O72" s="12" t="n"/>
+    </row>
+    <row r="73" outlineLevel="1">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>Haynes Furniture / The Dump – 12 stores closing (furniture, mattresses)</t>
+        </is>
+      </c>
+      <c r="C73" s="13" t="inlineStr">
+        <is>
+          <t>retail GOB</t>
+        </is>
+      </c>
+      <c r="D73" s="13" t="inlineStr">
+        <is>
+          <t>Virginia Beach</t>
+        </is>
+      </c>
+      <c r="E73" s="13" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="F73" s="13" t="n">
+        <v>456</v>
+      </c>
+      <c r="G73" s="13" t="inlineStr">
+        <is>
+          <t>Retail GOB markdowns</t>
+        </is>
+      </c>
+      <c r="H73" s="15" t="n"/>
+      <c r="I73" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="J73" s="13" t="inlineStr"/>
+      <c r="K73" s="13" t="inlineStr">
+        <is>
+          <t>SB360 (PR Newswire)</t>
+        </is>
+      </c>
+      <c r="L73" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M73" s="13" t="inlineStr"/>
+      <c r="N73" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O73" s="14" t="inlineStr">
+        <is>
+          <t>Posted Oct 8. Multi-state (VA/AZ/GA/IL/TX); pinned at Virginia Beach. Home goods only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Virginia</t>
+        </is>
+      </c>
+      <c r="B74" s="17" t="inlineStr">
+        <is>
+          <t>1 item(s)</t>
+        </is>
+      </c>
+      <c r="C74" s="18" t="n"/>
+      <c r="D74" s="18" t="n"/>
+      <c r="E74" s="18" t="n"/>
+      <c r="F74" s="18" t="n"/>
+      <c r="G74" s="18" t="n"/>
+      <c r="H74" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I72" s="18" t="n"/>
-      <c r="J72" s="18" t="n"/>
-      <c r="K72" s="18" t="n"/>
-      <c r="L72" s="18" t="n"/>
-      <c r="M72" s="18" t="n"/>
-      <c r="N72" s="18" t="n"/>
-      <c r="O72" s="18" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="11" t="inlineStr">
-        <is>
-          <t>▸ Virginia  (1)</t>
-        </is>
-      </c>
-      <c r="B73" s="12" t="n"/>
-      <c r="C73" s="12" t="n"/>
-      <c r="D73" s="12" t="n"/>
-      <c r="E73" s="12" t="n"/>
-      <c r="F73" s="12" t="n"/>
-      <c r="G73" s="12" t="n"/>
-      <c r="H73" s="12" t="n"/>
-      <c r="I73" s="12" t="n"/>
-      <c r="J73" s="12" t="n"/>
-      <c r="K73" s="12" t="n"/>
-      <c r="L73" s="12" t="n"/>
-      <c r="M73" s="12" t="n"/>
-      <c r="N73" s="12" t="n"/>
-      <c r="O73" s="12" t="n"/>
-    </row>
-    <row r="74" outlineLevel="1">
-      <c r="A74" s="13" t="inlineStr">
-        <is>
-          <t>Virginia</t>
-        </is>
-      </c>
-      <c r="B74" s="14" t="inlineStr">
-        <is>
-          <t>Haynes Furniture / The Dump – 12 stores closing (furniture, mattresses)</t>
-        </is>
-      </c>
-      <c r="C74" s="13" t="inlineStr">
+      <c r="I74" s="18" t="n"/>
+      <c r="J74" s="18" t="n"/>
+      <c r="K74" s="18" t="n"/>
+      <c r="L74" s="18" t="n"/>
+      <c r="M74" s="18" t="n"/>
+      <c r="N74" s="18" t="n"/>
+      <c r="O74" s="18" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>▸ Midwest  (2)</t>
+        </is>
+      </c>
+      <c r="B75" s="12" t="n"/>
+      <c r="C75" s="12" t="n"/>
+      <c r="D75" s="12" t="n"/>
+      <c r="E75" s="12" t="n"/>
+      <c r="F75" s="12" t="n"/>
+      <c r="G75" s="12" t="n"/>
+      <c r="H75" s="12" t="n"/>
+      <c r="I75" s="12" t="n"/>
+      <c r="J75" s="12" t="n"/>
+      <c r="K75" s="12" t="n"/>
+      <c r="L75" s="12" t="n"/>
+      <c r="M75" s="12" t="n"/>
+      <c r="N75" s="12" t="n"/>
+      <c r="O75" s="12" t="n"/>
+    </row>
+    <row r="76" outlineLevel="1">
+      <c r="A76" s="13" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="B76" s="14" t="inlineStr">
+        <is>
+          <t>American Sale – total liquidation, all 7 stores (pools, hot tubs, grills, holiday decor)</t>
+        </is>
+      </c>
+      <c r="C76" s="13" t="inlineStr">
         <is>
           <t>retail GOB</t>
         </is>
       </c>
-      <c r="D74" s="13" t="inlineStr">
-        <is>
-          <t>Virginia Beach</t>
-        </is>
-      </c>
-      <c r="E74" s="13" t="inlineStr">
-        <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="F74" s="13" t="n">
-        <v>456</v>
-      </c>
-      <c r="G74" s="13" t="inlineStr">
-        <is>
-          <t>Retail GOB markdowns</t>
-        </is>
-      </c>
-      <c r="H74" s="15" t="n"/>
-      <c r="I74" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-08</t>
-        </is>
-      </c>
-      <c r="J74" s="13" t="inlineStr"/>
-      <c r="K74" s="13" t="inlineStr">
-        <is>
-          <t>SB360 (PR Newswire)</t>
-        </is>
-      </c>
-      <c r="L74" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M74" s="13" t="inlineStr"/>
-      <c r="N74" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O74" s="14" t="inlineStr">
-        <is>
-          <t>Posted Oct 8. Multi-state (VA/AZ/GA/IL/TX); pinned at Virginia Beach. Home goods only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Virginia</t>
-        </is>
-      </c>
-      <c r="B75" s="17" t="inlineStr">
-        <is>
-          <t>1 item(s)</t>
-        </is>
-      </c>
-      <c r="C75" s="18" t="n"/>
-      <c r="D75" s="18" t="n"/>
-      <c r="E75" s="18" t="n"/>
-      <c r="F75" s="18" t="n"/>
-      <c r="G75" s="18" t="n"/>
-      <c r="H75" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="18" t="n"/>
-      <c r="J75" s="18" t="n"/>
-      <c r="K75" s="18" t="n"/>
-      <c r="L75" s="18" t="n"/>
-      <c r="M75" s="18" t="n"/>
-      <c r="N75" s="18" t="n"/>
-      <c r="O75" s="18" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t>▸ Midwest  (2)</t>
-        </is>
-      </c>
-      <c r="B76" s="12" t="n"/>
-      <c r="C76" s="12" t="n"/>
-      <c r="D76" s="12" t="n"/>
-      <c r="E76" s="12" t="n"/>
-      <c r="F76" s="12" t="n"/>
-      <c r="G76" s="12" t="n"/>
-      <c r="H76" s="12" t="n"/>
-      <c r="I76" s="12" t="n"/>
-      <c r="J76" s="12" t="n"/>
-      <c r="K76" s="12" t="n"/>
-      <c r="L76" s="12" t="n"/>
-      <c r="M76" s="12" t="n"/>
-      <c r="N76" s="12" t="n"/>
-      <c r="O76" s="12" t="n"/>
+      <c r="D76" s="13" t="inlineStr">
+        <is>
+          <t>Chicagoland</t>
+        </is>
+      </c>
+      <c r="E76" s="13" t="inlineStr">
+        <is>
+          <t>IL</t>
+        </is>
+      </c>
+      <c r="F76" s="13" t="n">
+        <v>876</v>
+      </c>
+      <c r="G76" s="13" t="inlineStr">
+        <is>
+          <t>Retail GOB, up to 70% off</t>
+        </is>
+      </c>
+      <c r="H76" s="15" t="n"/>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J76" s="13" t="inlineStr"/>
+      <c r="K76" s="13" t="inlineStr">
+        <is>
+          <t>Tiger Group (PR Newswire)</t>
+        </is>
+      </c>
+      <c r="L76" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M76" s="13" t="inlineStr"/>
+      <c r="N76" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O76" s="14" t="inlineStr">
+        <is>
+          <t>Posted Oct 15. Watch for a bulk/fixture auction.</t>
+        </is>
+      </c>
     </row>
     <row r="77" outlineLevel="1">
       <c r="A77" s="13" t="inlineStr">
@@ -22448,47 +22448,47 @@
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>American Sale – total liquidation, all 7 stores (pools, hot tubs, grills, holiday decor)</t>
+          <t>Straub's Fine Foods store equipment – bakery, kitchen, meat room, Hussmann refrigeration</t>
         </is>
       </c>
       <c r="C77" s="13" t="inlineStr">
         <is>
-          <t>retail GOB</t>
+          <t>grocery/restaurant</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>Chicagoland</t>
+          <t>St. Louis</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>876</v>
+        <v>1046</v>
       </c>
       <c r="G77" s="13" t="inlineStr">
         <is>
-          <t>Retail GOB, up to 70% off</t>
+          <t>Online auction (18% BP)</t>
         </is>
       </c>
       <c r="H77" s="15" t="n"/>
-      <c r="I77" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="J77" s="13" t="inlineStr"/>
+      <c r="I77" s="13" t="inlineStr"/>
+      <c r="J77" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K77" s="13" t="inlineStr">
         <is>
-          <t>Tiger Group (PR Newswire)</t>
-        </is>
-      </c>
-      <c r="L77" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L77" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M77" s="13" t="inlineStr"/>
@@ -22499,324 +22499,261 @@
       </c>
       <c r="O77" s="14" t="inlineStr">
         <is>
-          <t>Posted Oct 15. Watch for a bulk/fixture auction.</t>
-        </is>
-      </c>
-    </row>
-    <row r="78" outlineLevel="1">
-      <c r="A78" s="13" t="inlineStr">
-        <is>
-          <t>Midwest</t>
-        </is>
-      </c>
-      <c r="B78" s="14" t="inlineStr">
-        <is>
-          <t>Straub's Fine Foods store equipment – bakery, kitchen, meat room, Hussmann refrigeration</t>
-        </is>
-      </c>
-      <c r="C78" s="13" t="inlineStr">
-        <is>
-          <t>grocery/restaurant</t>
-        </is>
-      </c>
-      <c r="D78" s="13" t="inlineStr">
-        <is>
-          <t>St. Louis</t>
-        </is>
-      </c>
-      <c r="E78" s="13" t="inlineStr">
-        <is>
-          <t>MO</t>
-        </is>
-      </c>
-      <c r="F78" s="13" t="n">
-        <v>1046</v>
-      </c>
-      <c r="G78" s="13" t="inlineStr">
-        <is>
-          <t>Online auction (18% BP)</t>
-        </is>
-      </c>
-      <c r="H78" s="15" t="n"/>
-      <c r="I78" s="13" t="inlineStr"/>
-      <c r="J78" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 11:00 AM ET</t>
-        </is>
-      </c>
-      <c r="K78" s="13" t="inlineStr">
-        <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L78" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M78" s="13" t="inlineStr"/>
-      <c r="N78" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O78" s="14" t="inlineStr">
-        <is>
           <t>Kingshighway store: Revent double-rack oven + proofer, Reed revolving oven, Vulcan convection, Groen kettle, Southbend 6-burner, Pitco fryer, Stero dishwasher, Hobart saw/grinders, Berkel slicers, Hussmann cases + compressor racks, walk-ins, Hoshizaki/Scotsman ice machines, Crown pallet jack. Preview Oct 20 3–6 PM CDT; pickup in St. Louis.</t>
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Midwest</t>
+        </is>
+      </c>
+      <c r="B78" s="17" t="inlineStr">
+        <is>
+          <t>2 item(s)</t>
+        </is>
+      </c>
+      <c r="C78" s="18" t="n"/>
+      <c r="D78" s="18" t="n"/>
+      <c r="E78" s="18" t="n"/>
+      <c r="F78" s="18" t="n"/>
+      <c r="G78" s="18" t="n"/>
+      <c r="H78" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="18" t="n"/>
+      <c r="J78" s="18" t="n"/>
+      <c r="K78" s="18" t="n"/>
+      <c r="L78" s="18" t="n"/>
+      <c r="M78" s="18" t="n"/>
+      <c r="N78" s="18" t="n"/>
+      <c r="O78" s="18" t="n"/>
+    </row>
     <row r="79">
-      <c r="A79" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Midwest</t>
-        </is>
-      </c>
-      <c r="B79" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C79" s="18" t="n"/>
-      <c r="D79" s="18" t="n"/>
-      <c r="E79" s="18" t="n"/>
-      <c r="F79" s="18" t="n"/>
-      <c r="G79" s="18" t="n"/>
-      <c r="H79" s="19" t="n">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>▸ Texas / South Central  (1)</t>
+        </is>
+      </c>
+      <c r="B79" s="12" t="n"/>
+      <c r="C79" s="12" t="n"/>
+      <c r="D79" s="12" t="n"/>
+      <c r="E79" s="12" t="n"/>
+      <c r="F79" s="12" t="n"/>
+      <c r="G79" s="12" t="n"/>
+      <c r="H79" s="12" t="n"/>
+      <c r="I79" s="12" t="n"/>
+      <c r="J79" s="12" t="n"/>
+      <c r="K79" s="12" t="n"/>
+      <c r="L79" s="12" t="n"/>
+      <c r="M79" s="12" t="n"/>
+      <c r="N79" s="12" t="n"/>
+      <c r="O79" s="12" t="n"/>
+    </row>
+    <row r="80" outlineLevel="1">
+      <c r="A80" s="13" t="inlineStr">
+        <is>
+          <t>Texas / South Central</t>
+        </is>
+      </c>
+      <c r="B80" s="14" t="inlineStr">
+        <is>
+          <t>Southwest beverage distributor surplus – mostly unused: 16 True merchandisers, 75 Bunn brewers, 100+ micro-market kiosks</t>
+        </is>
+      </c>
+      <c r="C80" s="13" t="inlineStr">
+        <is>
+          <t>distributor surplus</t>
+        </is>
+      </c>
+      <c r="D80" s="13" t="inlineStr">
+        <is>
+          <t>Mesquite</t>
+        </is>
+      </c>
+      <c r="E80" s="13" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="F80" s="13" t="n">
+        <v>1547</v>
+      </c>
+      <c r="G80" s="13" t="inlineStr">
+        <is>
+          <t>Online auction</t>
+        </is>
+      </c>
+      <c r="H80" s="15" t="n"/>
+      <c r="I80" s="13" t="inlineStr"/>
+      <c r="J80" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-13 11:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K80" s="13" t="inlineStr">
+        <is>
+          <t>Heritage Global Partners</t>
+        </is>
+      </c>
+      <c r="L80" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M80" s="13" t="inlineStr"/>
+      <c r="N80" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O80" s="14" t="inlineStr">
+        <is>
+          <t>Near-new appliances, resell by unit. Nov 13 10 AM CST.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Texas / South Central</t>
+        </is>
+      </c>
+      <c r="B81" s="17" t="inlineStr">
+        <is>
+          <t>1 item(s)</t>
+        </is>
+      </c>
+      <c r="C81" s="18" t="n"/>
+      <c r="D81" s="18" t="n"/>
+      <c r="E81" s="18" t="n"/>
+      <c r="F81" s="18" t="n"/>
+      <c r="G81" s="18" t="n"/>
+      <c r="H81" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I79" s="18" t="n"/>
-      <c r="J79" s="18" t="n"/>
-      <c r="K79" s="18" t="n"/>
-      <c r="L79" s="18" t="n"/>
-      <c r="M79" s="18" t="n"/>
-      <c r="N79" s="18" t="n"/>
-      <c r="O79" s="18" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="11" t="inlineStr">
-        <is>
-          <t>▸ Texas / South Central  (1)</t>
-        </is>
-      </c>
-      <c r="B80" s="12" t="n"/>
-      <c r="C80" s="12" t="n"/>
-      <c r="D80" s="12" t="n"/>
-      <c r="E80" s="12" t="n"/>
-      <c r="F80" s="12" t="n"/>
-      <c r="G80" s="12" t="n"/>
-      <c r="H80" s="12" t="n"/>
-      <c r="I80" s="12" t="n"/>
-      <c r="J80" s="12" t="n"/>
-      <c r="K80" s="12" t="n"/>
-      <c r="L80" s="12" t="n"/>
-      <c r="M80" s="12" t="n"/>
-      <c r="N80" s="12" t="n"/>
-      <c r="O80" s="12" t="n"/>
-    </row>
-    <row r="81" outlineLevel="1">
-      <c r="A81" s="13" t="inlineStr">
-        <is>
-          <t>Texas / South Central</t>
-        </is>
-      </c>
-      <c r="B81" s="14" t="inlineStr">
-        <is>
-          <t>Southwest beverage distributor surplus – mostly unused: 16 True merchandisers, 75 Bunn brewers, 100+ micro-market kiosks</t>
-        </is>
-      </c>
-      <c r="C81" s="13" t="inlineStr">
-        <is>
-          <t>distributor surplus</t>
-        </is>
-      </c>
-      <c r="D81" s="13" t="inlineStr">
-        <is>
-          <t>Mesquite</t>
-        </is>
-      </c>
-      <c r="E81" s="13" t="inlineStr">
-        <is>
-          <t>TX</t>
-        </is>
-      </c>
-      <c r="F81" s="13" t="n">
-        <v>1547</v>
-      </c>
-      <c r="G81" s="13" t="inlineStr">
-        <is>
-          <t>Online auction</t>
-        </is>
-      </c>
-      <c r="H81" s="15" t="n"/>
-      <c r="I81" s="13" t="inlineStr"/>
-      <c r="J81" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-13 11:00 AM ET</t>
-        </is>
-      </c>
-      <c r="K81" s="13" t="inlineStr">
-        <is>
-          <t>Heritage Global Partners</t>
-        </is>
-      </c>
-      <c r="L81" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M81" s="13" t="inlineStr"/>
-      <c r="N81" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O81" s="14" t="inlineStr">
-        <is>
-          <t>Near-new appliances, resell by unit. Nov 13 10 AM CST.</t>
-        </is>
-      </c>
+      <c r="I81" s="18" t="n"/>
+      <c r="J81" s="18" t="n"/>
+      <c r="K81" s="18" t="n"/>
+      <c r="L81" s="18" t="n"/>
+      <c r="M81" s="18" t="n"/>
+      <c r="N81" s="18" t="n"/>
+      <c r="O81" s="18" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Texas / South Central</t>
-        </is>
-      </c>
-      <c r="B82" s="17" t="inlineStr">
+      <c r="A82" s="11" t="inlineStr">
+        <is>
+          <t>▸ West / Other  (1)</t>
+        </is>
+      </c>
+      <c r="B82" s="12" t="n"/>
+      <c r="C82" s="12" t="n"/>
+      <c r="D82" s="12" t="n"/>
+      <c r="E82" s="12" t="n"/>
+      <c r="F82" s="12" t="n"/>
+      <c r="G82" s="12" t="n"/>
+      <c r="H82" s="12" t="n"/>
+      <c r="I82" s="12" t="n"/>
+      <c r="J82" s="12" t="n"/>
+      <c r="K82" s="12" t="n"/>
+      <c r="L82" s="12" t="n"/>
+      <c r="M82" s="12" t="n"/>
+      <c r="N82" s="12" t="n"/>
+      <c r="O82" s="12" t="n"/>
+    </row>
+    <row r="83" outlineLevel="1">
+      <c r="A83" s="13" t="inlineStr">
+        <is>
+          <t>West / Other</t>
+        </is>
+      </c>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>National salad concept liquidation – full contents of 63 fast-casual restaurants (AZ/TX/OK/NV)</t>
+        </is>
+      </c>
+      <c r="C83" s="13" t="inlineStr">
+        <is>
+          <t>restaurant chain liquidation</t>
+        </is>
+      </c>
+      <c r="D83" s="13" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="E83" s="13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="F83" s="13" t="n">
+        <v>2307</v>
+      </c>
+      <c r="G83" s="13" t="inlineStr">
+        <is>
+          <t>Online auctions, dates TBD</t>
+        </is>
+      </c>
+      <c r="H83" s="15" t="n"/>
+      <c r="I83" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="J83" s="13" t="inlineStr"/>
+      <c r="K83" s="13" t="inlineStr">
+        <is>
+          <t>RestaurantEquipment.bid (TAGeX)</t>
+        </is>
+      </c>
+      <c r="L83" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M83" s="13" t="inlineStr"/>
+      <c r="N83" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O83" s="14" t="inlineStr">
+        <is>
+          <t>Rolling market-by-market auctions, none live yet (Phoenix metro 30 locations, DFW 14, Tucson 6, Houston 5, plus OK/NV). Pickup on site at each restaurant. Pinned at Phoenix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — West / Other</t>
+        </is>
+      </c>
+      <c r="B84" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C82" s="18" t="n"/>
-      <c r="D82" s="18" t="n"/>
-      <c r="E82" s="18" t="n"/>
-      <c r="F82" s="18" t="n"/>
-      <c r="G82" s="18" t="n"/>
-      <c r="H82" s="19" t="n">
+      <c r="C84" s="18" t="n"/>
+      <c r="D84" s="18" t="n"/>
+      <c r="E84" s="18" t="n"/>
+      <c r="F84" s="18" t="n"/>
+      <c r="G84" s="18" t="n"/>
+      <c r="H84" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I82" s="18" t="n"/>
-      <c r="J82" s="18" t="n"/>
-      <c r="K82" s="18" t="n"/>
-      <c r="L82" s="18" t="n"/>
-      <c r="M82" s="18" t="n"/>
-      <c r="N82" s="18" t="n"/>
-      <c r="O82" s="18" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="11" t="inlineStr">
-        <is>
-          <t>▸ West / Other  (1)</t>
-        </is>
-      </c>
-      <c r="B83" s="12" t="n"/>
-      <c r="C83" s="12" t="n"/>
-      <c r="D83" s="12" t="n"/>
-      <c r="E83" s="12" t="n"/>
-      <c r="F83" s="12" t="n"/>
-      <c r="G83" s="12" t="n"/>
-      <c r="H83" s="12" t="n"/>
-      <c r="I83" s="12" t="n"/>
-      <c r="J83" s="12" t="n"/>
-      <c r="K83" s="12" t="n"/>
-      <c r="L83" s="12" t="n"/>
-      <c r="M83" s="12" t="n"/>
-      <c r="N83" s="12" t="n"/>
-      <c r="O83" s="12" t="n"/>
-    </row>
-    <row r="84" outlineLevel="1">
-      <c r="A84" s="13" t="inlineStr">
-        <is>
-          <t>West / Other</t>
-        </is>
-      </c>
-      <c r="B84" s="14" t="inlineStr">
-        <is>
-          <t>National salad concept liquidation – full contents of 63 fast-casual restaurants (AZ/TX/OK/NV)</t>
-        </is>
-      </c>
-      <c r="C84" s="13" t="inlineStr">
-        <is>
-          <t>restaurant chain liquidation</t>
-        </is>
-      </c>
-      <c r="D84" s="13" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="E84" s="13" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="F84" s="13" t="n">
-        <v>2307</v>
-      </c>
-      <c r="G84" s="13" t="inlineStr">
-        <is>
-          <t>Online auctions, dates TBD</t>
-        </is>
-      </c>
-      <c r="H84" s="15" t="n"/>
-      <c r="I84" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="J84" s="13" t="inlineStr"/>
-      <c r="K84" s="13" t="inlineStr">
-        <is>
-          <t>RestaurantEquipment.bid (TAGeX)</t>
-        </is>
-      </c>
-      <c r="L84" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M84" s="13" t="inlineStr"/>
-      <c r="N84" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O84" s="14" t="inlineStr">
-        <is>
-          <t>Rolling market-by-market auctions, none live yet (Phoenix metro 30 locations, DFW 14, Tucson 6, Houston 5, plus OK/NV). Pickup on site at each restaurant. Pinned at Phoenix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — West / Other</t>
-        </is>
-      </c>
-      <c r="B85" s="17" t="inlineStr">
-        <is>
-          <t>1 item(s)</t>
-        </is>
-      </c>
-      <c r="C85" s="18" t="n"/>
-      <c r="D85" s="18" t="n"/>
-      <c r="E85" s="18" t="n"/>
-      <c r="F85" s="18" t="n"/>
-      <c r="G85" s="18" t="n"/>
-      <c r="H85" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="18" t="n"/>
-      <c r="J85" s="18" t="n"/>
-      <c r="K85" s="18" t="n"/>
-      <c r="L85" s="18" t="n"/>
-      <c r="M85" s="18" t="n"/>
-      <c r="N85" s="18" t="n"/>
-      <c r="O85" s="18" t="n"/>
+      <c r="I84" s="18" t="n"/>
+      <c r="J84" s="18" t="n"/>
+      <c r="K84" s="18" t="n"/>
+      <c r="L84" s="18" t="n"/>
+      <c r="M84" s="18" t="n"/>
+      <c r="N84" s="18" t="n"/>
+      <c r="O84" s="18" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O85"/>
+  <autoFilter ref="A1:O84"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId2"/>
@@ -22870,12 +22807,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N66" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N67" r:id="rId51"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N71" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N74" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N73" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N76" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N77" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N78" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N81" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N84" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N80" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N83" r:id="rId57"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22887,7 +22823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O18"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -23049,7 +22985,7 @@
       </c>
       <c r="O2" s="14" t="inlineStr">
         <is>
-          <t>Integrity Auction House. Internet bidding closes Mon Oct 19 9:18 PM ET. $50 high bid (1 bid) as of 2026-10-18. [Closed Oct 19; HiBid price realized $50.] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Integrity Auction House. Internet bidding closes Mon Oct 19 9:18 PM ET. $50 high bid (1 bid) as of 2026-10-18. [Closed Oct 19; HiBid price realized $50.] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23112,7 +23048,7 @@
       </c>
       <c r="O3" s="14" t="inlineStr">
         <is>
-          <t>Live auction Mon Oct 19 4 PM, 3457 Wilmington Rd. Few bulk parts. [Live auction held Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Live auction Mon Oct 19 4 PM, 3457 Wilmington Rd. Few bulk parts. [Live auction held Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23313,7 +23249,7 @@
       </c>
       <c r="O6" s="14" t="inlineStr">
         <is>
-          <t>Condition: Pre-Owned. FLIP: SO36U/S tested, auction $99/0 bids, pickup only; rough resale $600-1k (eBay card shows no city; pickup distance in source.) Ends Oct 18 ~2:19 PM per eBay card (time zone uncertain; could be earlier). [auto-removed 2026-10-18: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Condition: Pre-Owned. FLIP: SO36U/S tested, auction $99/0 bids, pickup only; rough resale $600-1k (eBay card shows no city; pickup distance in source.) Ends Oct 18 ~2:19 PM per eBay card (time zone uncertain; could be earlier). [auto-removed 2026-10-18: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23378,7 +23314,7 @@
       </c>
       <c r="O7" s="14" t="inlineStr">
         <is>
-          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf) HiBid lot closed/sold ~$37.50 on 2026-10-18. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf) HiBid lot closed/sold ~$37.50 on 2026-10-18. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23443,7 +23379,7 @@
       </c>
       <c r="O8" s="14" t="inlineStr">
         <is>
-          <t>Lots close from Oct 19 2 PM ET. [HiBid catalog closed 2 PM ET Oct 19.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Lots close from Oct 19 2 PM ET. [HiBid catalog closed 2 PM ET Oct 19.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23508,7 +23444,7 @@
       </c>
       <c r="O9" s="14" t="inlineStr">
         <is>
-          <t>Lots close from Oct 20 2 PM ET. [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Lots close from Oct 20 2 PM ET. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23571,7 +23507,7 @@
       </c>
       <c r="O10" s="14" t="inlineStr">
         <is>
-          <t>Tested and new units. [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Tested and new units. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23634,7 +23570,7 @@
       </c>
       <c r="O11" s="14" t="inlineStr">
         <is>
-          <t>Pickup Oct 21 only. [Lots began closing 1 PM ET Oct 19; ended.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Pickup Oct 21 only. [Lots began closing 1 PM ET Oct 19; ended.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23697,7 +23633,7 @@
       </c>
       <c r="O12" s="14" t="inlineStr">
         <is>
-          <t>Close Oct 18 or 19 6 PM (later used). [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Close Oct 18 or 19 6 PM (later used). [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23760,59 +23696,59 @@
       </c>
       <c r="O13" s="14" t="inlineStr">
         <is>
-          <t>No new out-of-state bidders. Small. [Ended Oct 19 7 PM.] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>No new out-of-state bidders. Small. [Ended Oct 19 7 PM.] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>Upstate / Western NY</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Freshway Market whole-grocery liquidation – refrigeration racks, cases, walk-ins, generator</t>
+          <t>Former Taco Del Mar – stainless, warmers, walk-in panels</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Watson</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>862</v>
+        <v>260</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>HiBid online auction</t>
         </is>
       </c>
       <c r="H14" s="15" t="n"/>
       <c r="I14" s="13" t="inlineStr"/>
       <c r="J14" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 11:00 AM ET</t>
+          <t>2026-10-20 06:00 PM ET</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
+          <t>Adirondack Asset / HiBid</t>
         </is>
       </c>
       <c r="L14" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-20 11:00 AM ET)</t>
+          <t>EXPIRED (2026-10-20 06:00 PM ET)</t>
         </is>
       </c>
       <c r="M14" s="13" t="inlineStr"/>
@@ -23823,59 +23759,59 @@
       </c>
       <c r="O14" s="14" t="inlineStr">
         <is>
-          <t>Closes from Oct 20 10 AM CDT. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Small lot. [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>Greater Boston / South Shore (&lt;50mi)</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>Closed Best Buy Outlet – pallet racking, Big Joe order pickers, appliance dollies, carts, cages</t>
+          <t>Freshway Market whole-grocery liquidation – refrigeration racks, cases, walk-ins, generator</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>store closing fixtures</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>Brockton</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>11</v>
+        <v>862</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>Racking $40/upright, $80/level; pickers $1,000 OBO</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H15" s="15" t="n"/>
-      <c r="I15" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="J15" s="13" t="inlineStr"/>
+      <c r="I15" s="13" t="inlineStr"/>
+      <c r="J15" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>Grafe Auction</t>
         </is>
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>EXPIRED (2026-10-20 11:00 AM ET)</t>
         </is>
       </c>
       <c r="M15" s="13" t="inlineStr"/>
@@ -23886,63 +23822,59 @@
       </c>
       <c r="O15" s="14" t="inlineStr">
         <is>
-          <t>200 Westgate Dr. Fixtures/equipment only, no merchandise. On site daily. CL deleted by author (HTTP 410) as of 2026-10-19 midday recheck.</t>
+          <t>Closes from Oct 20 10 AM CDT. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>NYC / Long Island / NJ</t>
+          <t>Greater Boston / South Shore (&lt;50mi)</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>Like-new restaurant – steam tables, Coldline, Cleveland cook-and-hold, fryers, True freezers</t>
+          <t>Closed Best Buy Outlet – pallet racking, Big Joe order pickers, appliance dollies, carts, cages</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>store closing fixtures</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>Staten Island</t>
+          <t>Brockton</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>203</v>
+        <v>11</v>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Racking $40/upright, $80/level; pickers $1,000 OBO</t>
         </is>
       </c>
       <c r="H16" s="15" t="n"/>
       <c r="I16" s="13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="J16" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-19 01:00 PM ET</t>
-        </is>
-      </c>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="J16" s="13" t="inlineStr"/>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L16" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 01:00 PM ET)</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="M16" s="13" t="inlineStr"/>
@@ -23953,7 +23885,7 @@
       </c>
       <c r="O16" s="14" t="inlineStr">
         <is>
-          <t>"Short notice" auction Mon Oct 19 1 PM. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>200 Westgate Dr. Fixtures/equipment only, no merchandise. On site daily. CL deleted by author (HTTP 410) as of 2026-10-19 midday recheck.</t>
         </is>
       </c>
     </row>
@@ -23965,26 +23897,26 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>Restaurant / pizzeria (contents not described)</t>
+          <t>Like-new restaurant – steam tables, Coldline, Cleveland cook-and-hold, fryers, True freezers</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>Berkeley Heights</t>
+          <t>Staten Island</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
@@ -23994,12 +23926,12 @@
       <c r="H17" s="15" t="n"/>
       <c r="I17" s="13" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="J17" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 02:00 PM ET</t>
+          <t>2026-10-19 01:00 PM ET</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
@@ -24009,7 +23941,7 @@
       </c>
       <c r="L17" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-20 02:00 PM ET)</t>
+          <t>EXPIRED (2026-10-19 01:00 PM ET)</t>
         </is>
       </c>
       <c r="M17" s="13" t="inlineStr"/>
@@ -24020,7 +23952,7 @@
       </c>
       <c r="O17" s="14" t="inlineStr">
         <is>
-          <t>Tue Oct 20 2 PM. No item description on page. [auto-removed 2026-10-20: closing date passed]</t>
+          <t>"Short notice" auction Mon Oct 19 1 PM. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -24032,7 +23964,7 @@
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>High-end deli (contents not described)</t>
+          <t>Restaurant / pizzeria (contents not described)</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
@@ -24042,7 +23974,7 @@
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>Manalapan Township</t>
+          <t>Berkeley Heights</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
@@ -24051,7 +23983,7 @@
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
@@ -24061,12 +23993,12 @@
       <c r="H18" s="15" t="n"/>
       <c r="I18" s="13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J18" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 04:00 PM ET</t>
+          <t>2026-10-20 02:00 PM ET</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
@@ -24076,7 +24008,7 @@
       </c>
       <c r="L18" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 04:00 PM ET)</t>
+          <t>EXPIRED (2026-10-20 02:00 PM ET)</t>
         </is>
       </c>
       <c r="M18" s="13" t="inlineStr"/>
@@ -24087,12 +24019,79 @@
       </c>
       <c r="O18" s="14" t="inlineStr">
         <is>
-          <t>Mon Oct 19 4 PM. No item description on page. [HiBid shows Bidding Closed, Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Tue Oct 20 2 PM. No item description on page. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>High-end deli (contents not described)</t>
+        </is>
+      </c>
+      <c r="C19" s="13" t="inlineStr">
+        <is>
+          <t>restaurant closing</t>
+        </is>
+      </c>
+      <c r="D19" s="13" t="inlineStr">
+        <is>
+          <t>Manalapan Township</t>
+        </is>
+      </c>
+      <c r="E19" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F19" s="13" t="n">
+        <v>223</v>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>Live + webcast, 18% BP + 3%</t>
+        </is>
+      </c>
+      <c r="H19" s="15" t="n"/>
+      <c r="I19" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J19" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 04:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K19" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L19" s="13" t="inlineStr">
+        <is>
+          <t>EXPIRED (2026-10-19 04:00 PM ET)</t>
+        </is>
+      </c>
+      <c r="M19" s="13" t="inlineStr"/>
+      <c r="N19" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O19" s="14" t="inlineStr">
+        <is>
+          <t>Mon Oct 19 4 PM. No item description on page. [HiBid shows Bidding Closed, Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O18"/>
+  <autoFilter ref="A1:O19"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -24111,6 +24110,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lot_recon.xlsx
+++ b/lot_recon.xlsx
@@ -16,11 +16,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Removed" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Appliance Parts'!$A$1:$O$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Appliance Parts'!$A$1:$O$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wolf New'!$A$1:$O$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wolf Used'!$A$1:$O$189</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Wolf Unclear'!$A$1:$O$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$86</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Removed'!$A$1:$O$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -577,7 +577,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Last updated: 2026-10-20 18:00 ET</t>
+          <t>Last updated: 2026-10-21 08:05 ET</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Active listings: 294 · Removed: 18</t>
+          <t>Active listings: 298 · Removed: 18</t>
         </is>
       </c>
     </row>
@@ -641,10 +641,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>159646</v>
+        <v>454646</v>
       </c>
       <c r="D8" t="n">
         <v>1</v>
@@ -679,7 +679,7 @@
         <v>164</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>608027.6</v>
+        <v>608029.6</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0</v>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>980438.58</v>
+        <v>1275440.58</v>
       </c>
     </row>
     <row r="15">
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -1037,7 +1037,7 @@
         <v>24</v>
       </c>
       <c r="G24" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>440141</v>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
@@ -1235,14 +1235,14 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H30" s="6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>807–1046</t>
+          <t>807–1124</t>
         </is>
       </c>
     </row>
@@ -1319,10 +1319,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D33" t="n">
         <v>0</v>
@@ -1337,11 +1337,11 @@
         <v>1</v>
       </c>
       <c r="H33" s="6" t="n">
-        <v>75000</v>
+        <v>370000</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2307–2317</t>
+          <t>1954–2317</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O39"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2858,7 +2858,7 @@
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t>▸ West / Other  (2)</t>
+          <t>▸ West / Other  (4)</t>
         </is>
       </c>
       <c r="B36" s="12" t="n"/>
@@ -2884,36 +2884,38 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>Storage locker filled with appliance parts – washer/dryer parts, heating elements, cords, rollers, belts, tools</t>
+          <t>Appliance service business for sale (Western Slope) - established warranty-servicer setups with many manufacturers</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>bulk lot</t>
+          <t>business for sale</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>Phoenix</t>
+          <t>Montrose</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>2307</v>
+        <v>1954</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t>Message for pricing</t>
-        </is>
-      </c>
-      <c r="H37" s="15" t="n"/>
+          <t>$110,000</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="n">
+        <v>110000</v>
+      </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="J37" s="13" t="inlineStr"/>
@@ -2935,7 +2937,7 @@
       </c>
       <c r="O37" s="14" t="inlineStr">
         <is>
-          <t>Seller is getting out of the appliance business; selling the whole locker (North Phoenix, Deer Valley Rd near 19th Ave). Delivery available per post. Separate from the Phoenix parts-store closing ad.</t>
+          <t>Going-concern service business; possible seller financing; no parts inventory mentioned. Updated 2026-10-17.</t>
         </is>
       </c>
     </row>
@@ -2947,7 +2949,7 @@
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>Appliance repair &amp; sales business for sale – 100+ appliances (~90% new), liftgate truck, large powered storage unit</t>
+          <t>Appliance Repair Technicians: Own the Business - $65K parts inventory/stock + $25K FF&amp;E + 2022 Promaster van</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
@@ -2957,34 +2959,30 @@
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>Surprise</t>
+          <t>Salt Lake City</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>UT</t>
         </is>
       </c>
       <c r="F38" s="13" t="n">
-        <v>2317</v>
+        <v>2109</v>
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>$75,000</t>
+          <t>$185,000 (price reduced)</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
-        <v>75000</v>
-      </c>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
+        <v>185000</v>
+      </c>
+      <c r="I38" s="13" t="inlineStr"/>
       <c r="J38" s="13" t="inlineStr"/>
       <c r="K38" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>BusinessesForSale (First Choice Business Brokers #3924670)</t>
         </is>
       </c>
       <c r="L38" s="13" t="inlineStr">
@@ -3000,39 +2998,167 @@
       </c>
       <c r="O38" s="14" t="inlineStr">
         <is>
+          <t>Home-based, est. March 2020, Salt Lake County UT. Includes ~$65K inventory/stock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" outlineLevel="1">
+      <c r="A39" s="13" t="inlineStr">
+        <is>
+          <t>West / Other</t>
+        </is>
+      </c>
+      <c r="B39" s="14" t="inlineStr">
+        <is>
+          <t>Storage locker filled with appliance parts – washer/dryer parts, heating elements, cords, rollers, belts, tools</t>
+        </is>
+      </c>
+      <c r="C39" s="13" t="inlineStr">
+        <is>
+          <t>bulk lot</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="E39" s="13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="F39" s="13" t="n">
+        <v>2307</v>
+      </c>
+      <c r="G39" s="13" t="inlineStr">
+        <is>
+          <t>Message for pricing</t>
+        </is>
+      </c>
+      <c r="H39" s="15" t="n"/>
+      <c r="I39" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J39" s="13" t="inlineStr"/>
+      <c r="K39" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L39" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M39" s="13" t="inlineStr"/>
+      <c r="N39" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O39" s="14" t="inlineStr">
+        <is>
+          <t>Seller is getting out of the appliance business; selling the whole locker (North Phoenix, Deer Valley Rd near 19th Ave). Delivery available per post. Separate from the Phoenix parts-store closing ad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" outlineLevel="1">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>West / Other</t>
+        </is>
+      </c>
+      <c r="B40" s="14" t="inlineStr">
+        <is>
+          <t>Appliance repair &amp; sales business for sale – 100+ appliances (~90% new), liftgate truck, large powered storage unit</t>
+        </is>
+      </c>
+      <c r="C40" s="13" t="inlineStr">
+        <is>
+          <t>business for sale</t>
+        </is>
+      </c>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>Surprise</t>
+        </is>
+      </c>
+      <c r="E40" s="13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="F40" s="13" t="n">
+        <v>2317</v>
+      </c>
+      <c r="G40" s="13" t="inlineStr">
+        <is>
+          <t>$75,000</t>
+        </is>
+      </c>
+      <c r="H40" s="15" t="n">
+        <v>75000</v>
+      </c>
+      <c r="I40" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="J40" s="13" t="inlineStr"/>
+      <c r="K40" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L40" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M40" s="13" t="inlineStr"/>
+      <c r="N40" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O40" s="14" t="inlineStr">
+        <is>
           <t>Retiring owner of 14-year business serving rental-property owners. Whole appliances (fridges, stoves, microwaves, dishwashers, W/D), not a parts inventory. Storage unit near Dysart &amp; Bell Rd. By appointment only.</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="17" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="17" t="inlineStr">
         <is>
           <t>Subtotal — West / Other</t>
         </is>
       </c>
-      <c r="B39" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C39" s="18" t="n"/>
-      <c r="D39" s="18" t="n"/>
-      <c r="E39" s="18" t="n"/>
-      <c r="F39" s="18" t="n"/>
-      <c r="G39" s="18" t="n"/>
-      <c r="H39" s="19" t="n">
-        <v>75000</v>
-      </c>
-      <c r="I39" s="18" t="n"/>
-      <c r="J39" s="18" t="n"/>
-      <c r="K39" s="18" t="n"/>
-      <c r="L39" s="18" t="n"/>
-      <c r="M39" s="18" t="n"/>
-      <c r="N39" s="18" t="n"/>
-      <c r="O39" s="18" t="n"/>
+      <c r="B41" s="17" t="inlineStr">
+        <is>
+          <t>4 item(s)</t>
+        </is>
+      </c>
+      <c r="C41" s="18" t="n"/>
+      <c r="D41" s="18" t="n"/>
+      <c r="E41" s="18" t="n"/>
+      <c r="F41" s="18" t="n"/>
+      <c r="G41" s="18" t="n"/>
+      <c r="H41" s="19" t="n">
+        <v>370000</v>
+      </c>
+      <c r="I41" s="18" t="n"/>
+      <c r="J41" s="18" t="n"/>
+      <c r="K41" s="18" t="n"/>
+      <c r="L41" s="18" t="n"/>
+      <c r="M41" s="18" t="n"/>
+      <c r="N41" s="18" t="n"/>
+      <c r="O41" s="18" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O39"/>
+  <autoFilter ref="A1:O41"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId2"/>
@@ -3050,6 +3176,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -12308,11 +12436,11 @@
       </c>
       <c r="G126" s="13" t="inlineStr">
         <is>
-          <t>$5 high bid</t>
+          <t>$7 high bid (3 bids)</t>
         </is>
       </c>
       <c r="H126" s="15" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I126" s="13" t="inlineStr"/>
       <c r="J126" s="13" t="inlineStr">
@@ -12363,7 +12491,7 @@
       <c r="F127" s="18" t="n"/>
       <c r="G127" s="18" t="n"/>
       <c r="H127" s="19" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I127" s="18" t="n"/>
       <c r="J127" s="18" t="n"/>
@@ -18412,7 +18540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O84"/>
+  <dimension ref="A1:O86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -18715,7 +18843,7 @@
       </c>
       <c r="O5" s="14" t="inlineStr">
         <is>
-          <t>Small off-category FYI; seller says resell individually. Old CL URL deleted; reposted under new URL 2026-10-19 (same $250 / 10 tools).</t>
+          <t>Small off-category FYI; seller says resell individually. Old CL URL deleted; reposted under new URL 2026-10-19 (same $250 / 10 tools). Reposted again 2026-10-21 under new URL (same $250 / 10 tools).</t>
         </is>
       </c>
     </row>
@@ -20146,7 +20274,7 @@
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>▸ NYC / Long Island / NJ  (24)</t>
+          <t>▸ NYC / Long Island / NJ  (25)</t>
         </is>
       </c>
       <c r="B34" s="12" t="n"/>
@@ -21243,17 +21371,17 @@
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
+          <t>Bimmer Clinic business liquidation (BMW repair shop): vehicle lifts, forklift, skid steer, refrigerant recovery, shop tools &amp; equipment</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>lien sale</t>
+          <t>business liquidation auction</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>Edison</t>
+          <t>South Amboy</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -21262,19 +21390,23 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
-          <t>Online auction, $2K load-out fee</t>
+          <t>Timed online auction</t>
         </is>
       </c>
       <c r="H52" s="15" t="n"/>
       <c r="I52" s="13" t="inlineStr"/>
-      <c r="J52" s="13" t="inlineStr"/>
+      <c r="J52" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-12 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>AJ Willner Auctions</t>
         </is>
       </c>
       <c r="L52" s="13" t="inlineStr">
@@ -21290,7 +21422,7 @@
       </c>
       <c r="O52" s="14" t="inlineStr">
         <is>
-          <t>&gt;$100K new. Close date not captured.</t>
+          <t>Ends Nov 12 11 AM EST.</t>
         </is>
       </c>
     </row>
@@ -21302,12 +21434,12 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
+          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>lien sale</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
@@ -21325,23 +21457,15 @@
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
-          <t>Live + HiBid webcast, 18% BP + 3% card</t>
+          <t>Online auction, $2K load-out fee</t>
         </is>
       </c>
       <c r="H53" s="15" t="n"/>
-      <c r="I53" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="J53" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-25 01:00 PM ET</t>
-        </is>
-      </c>
+      <c r="I53" s="13" t="inlineStr"/>
+      <c r="J53" s="13" t="inlineStr"/>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L53" s="13" t="inlineStr">
@@ -21349,11 +21473,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M53" s="21" t="inlineStr">
-        <is>
-          <t>FLIP</t>
-        </is>
-      </c>
+      <c r="M53" s="13" t="inlineStr"/>
       <c r="N53" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -21361,7 +21481,7 @@
       </c>
       <c r="O53" s="14" t="inlineStr">
         <is>
-          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
+          <t>&gt;$100K new. Close date not captured.</t>
         </is>
       </c>
     </row>
@@ -21373,17 +21493,17 @@
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
+          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>East Brunswick</t>
+          <t>Edison</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -21392,23 +21512,27 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Live + HiBid webcast, 18% BP + 3% card</t>
         </is>
       </c>
       <c r="H54" s="15" t="n"/>
-      <c r="I54" s="13" t="inlineStr"/>
+      <c r="I54" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="J54" s="13" t="inlineStr">
         <is>
-          <t>2026-11-03 11:00 AM ET</t>
+          <t>2026-10-25 01:00 PM ET</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
       <c r="L54" s="13" t="inlineStr">
@@ -21416,7 +21540,11 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M54" s="13" t="inlineStr"/>
+      <c r="M54" s="21" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
       <c r="N54" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -21424,7 +21552,7 @@
       </c>
       <c r="O54" s="14" t="inlineStr">
         <is>
-          <t>Store inventory.</t>
+          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
         </is>
       </c>
     </row>
@@ -21436,17 +21564,17 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Bakery/Cafe Somerville NJ – rack ovens, La Marzocco, food truck (~76 lots)</t>
+          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>Somerville</t>
+          <t>East Brunswick</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -21455,27 +21583,23 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
-          <t>Live webcast + online (18% BP online)</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H55" s="15" t="n"/>
-      <c r="I55" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
+      <c r="I55" s="13" t="inlineStr"/>
       <c r="J55" s="13" t="inlineStr">
         <is>
-          <t>2026-10-26 02:00 PM ET</t>
+          <t>2026-11-03 11:00 AM ET</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>HiBid / Best Buy Auctioneers</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L55" s="13" t="inlineStr">
@@ -21491,7 +21615,7 @@
       </c>
       <c r="O55" s="14" t="inlineStr">
         <is>
-          <t>Full bakery/cafe commercial kitchen: food truck w/ pizza oven, La Marzocco espresso, Mazzer, Baxter + Empire Logiudice rack ovens, dough depositor, Globe floor mixer, Artic Air / SS refrigeration, fryers, Vitamix, Robot Coupe, display cases, dining furniture. Preview 11 AM sale day; checkout Tue 10/27.</t>
+          <t>Store inventory.</t>
         </is>
       </c>
     </row>
@@ -21503,7 +21627,7 @@
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>Ability to Work kitchen and store – commercial kitchen + store fixtures (~135 lots)</t>
+          <t>Bakery/Cafe Somerville NJ – rack ovens, La Marzocco, food truck (~76 lots)</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr">
@@ -21513,7 +21637,7 @@
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>Flemington</t>
+          <t>Somerville</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -21522,23 +21646,27 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>Timed online (15% BP)</t>
+          <t>Live webcast + online (18% BP online)</t>
         </is>
       </c>
       <c r="H56" s="15" t="n"/>
-      <c r="I56" s="13" t="inlineStr"/>
+      <c r="I56" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="J56" s="13" t="inlineStr">
         <is>
-          <t>2026-10-27 11:02 AM ET</t>
+          <t>2026-10-26 02:00 PM ET</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>HiBid</t>
+          <t>HiBid / Best Buy Auctioneers</t>
         </is>
       </c>
       <c r="L56" s="13" t="inlineStr">
@@ -21554,7 +21682,7 @@
       </c>
       <c r="O56" s="14" t="inlineStr">
         <is>
-          <t>Apprentice/hospitality training cafe-kitchen and store dispersal. Preview 9–11 AM sale day; removal Oct 27 noon–Oct 29.</t>
+          <t>Full bakery/cafe commercial kitchen: food truck w/ pizza oven, La Marzocco espresso, Mazzer, Baxter + Empire Logiudice rack ovens, dough depositor, Globe floor mixer, Artic Air / SS refrigeration, fryers, Vitamix, Robot Coupe, display cases, dining furniture. Preview 11 AM sale day; checkout Tue 10/27.</t>
         </is>
       </c>
     </row>
@@ -21566,17 +21694,17 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
+          <t>Ability to Work kitchen and store – commercial kitchen + store fixtures (~135 lots)</t>
         </is>
       </c>
       <c r="C57" s="13" t="inlineStr">
         <is>
-          <t>showroom closing</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>Lawrenceville</t>
+          <t>Flemington</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -21585,23 +21713,23 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
-          <t>Online auction, 18% BP</t>
+          <t>Timed online (15% BP)</t>
         </is>
       </c>
       <c r="H57" s="15" t="n"/>
       <c r="I57" s="13" t="inlineStr"/>
       <c r="J57" s="13" t="inlineStr">
         <is>
-          <t>2026-10-27 09:00 AM ET</t>
+          <t>2026-10-27 11:02 AM ET</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
+          <t>HiBid</t>
         </is>
       </c>
       <c r="L57" s="13" t="inlineStr">
@@ -21617,7 +21745,7 @@
       </c>
       <c r="O57" s="14" t="inlineStr">
         <is>
-          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
+          <t>Apprentice/hospitality training cafe-kitchen and store dispersal. Preview 9–11 AM sale day; removal Oct 27 noon–Oct 29.</t>
         </is>
       </c>
     </row>
@@ -21629,7 +21757,7 @@
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
+          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
         </is>
       </c>
       <c r="C58" s="13" t="inlineStr">
@@ -21639,7 +21767,7 @@
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>Cherry Hill</t>
+          <t>Lawrenceville</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -21648,18 +21776,18 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="G58" s="13" t="inlineStr">
         <is>
-          <t>Online auction, openers ~$0.50</t>
+          <t>Online auction, 18% BP</t>
         </is>
       </c>
       <c r="H58" s="15" t="n"/>
       <c r="I58" s="13" t="inlineStr"/>
       <c r="J58" s="13" t="inlineStr">
         <is>
-          <t>2026-11-02 11:00 AM ET</t>
+          <t>2026-10-27 09:00 AM ET</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
@@ -21680,124 +21808,120 @@
       </c>
       <c r="O58" s="14" t="inlineStr">
         <is>
+          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" outlineLevel="1">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
+        </is>
+      </c>
+      <c r="C59" s="13" t="inlineStr">
+        <is>
+          <t>showroom closing</t>
+        </is>
+      </c>
+      <c r="D59" s="13" t="inlineStr">
+        <is>
+          <t>Cherry Hill</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F59" s="13" t="n">
+        <v>266</v>
+      </c>
+      <c r="G59" s="13" t="inlineStr">
+        <is>
+          <t>Online auction, openers ~$0.50</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="n"/>
+      <c r="I59" s="13" t="inlineStr"/>
+      <c r="J59" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-02 11:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="inlineStr">
+        <is>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L59" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M59" s="13" t="inlineStr"/>
+      <c r="N59" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O59" s="14" t="inlineStr">
+        <is>
           <t>Lots close from Nov 2 11 AM.</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="17" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="17" t="inlineStr">
         <is>
           <t>Subtotal — NYC / Long Island / NJ</t>
         </is>
       </c>
-      <c r="B59" s="17" t="inlineStr">
-        <is>
-          <t>24 item(s)</t>
-        </is>
-      </c>
-      <c r="C59" s="18" t="n"/>
-      <c r="D59" s="18" t="n"/>
-      <c r="E59" s="18" t="n"/>
-      <c r="F59" s="18" t="n"/>
-      <c r="G59" s="18" t="n"/>
-      <c r="H59" s="19" t="n">
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>25 item(s)</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="n"/>
+      <c r="D60" s="18" t="n"/>
+      <c r="E60" s="18" t="n"/>
+      <c r="F60" s="18" t="n"/>
+      <c r="G60" s="18" t="n"/>
+      <c r="H60" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I59" s="18" t="n"/>
-      <c r="J59" s="18" t="n"/>
-      <c r="K59" s="18" t="n"/>
-      <c r="L59" s="18" t="n"/>
-      <c r="M59" s="18" t="n"/>
-      <c r="N59" s="18" t="n"/>
-      <c r="O59" s="18" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="11" t="inlineStr">
+      <c r="I60" s="18" t="n"/>
+      <c r="J60" s="18" t="n"/>
+      <c r="K60" s="18" t="n"/>
+      <c r="L60" s="18" t="n"/>
+      <c r="M60" s="18" t="n"/>
+      <c r="N60" s="18" t="n"/>
+      <c r="O60" s="18" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
         <is>
           <t>▸ Eastern PA / Mid-Atlantic  (2)</t>
         </is>
       </c>
-      <c r="B60" s="12" t="n"/>
-      <c r="C60" s="12" t="n"/>
-      <c r="D60" s="12" t="n"/>
-      <c r="E60" s="12" t="n"/>
-      <c r="F60" s="12" t="n"/>
-      <c r="G60" s="12" t="n"/>
-      <c r="H60" s="12" t="n"/>
-      <c r="I60" s="12" t="n"/>
-      <c r="J60" s="12" t="n"/>
-      <c r="K60" s="12" t="n"/>
-      <c r="L60" s="12" t="n"/>
-      <c r="M60" s="12" t="n"/>
-      <c r="N60" s="12" t="n"/>
-      <c r="O60" s="12" t="n"/>
-    </row>
-    <row r="61" outlineLevel="1">
-      <c r="A61" s="13" t="inlineStr">
-        <is>
-          <t>Eastern PA / Mid-Atlantic</t>
-        </is>
-      </c>
-      <c r="B61" s="14" t="inlineStr">
-        <is>
-          <t>Piscitello's Home Center closing after 68 years: storewide 20% off liquidation (hardware, lumber, doors, windows, kitchen/bath)</t>
-        </is>
-      </c>
-      <c r="C61" s="13" t="inlineStr">
-        <is>
-          <t>store closing</t>
-        </is>
-      </c>
-      <c r="D61" s="13" t="inlineStr">
-        <is>
-          <t>Wilson</t>
-        </is>
-      </c>
-      <c r="E61" s="13" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="F61" s="13" t="n">
-        <v>250</v>
-      </c>
-      <c r="G61" s="13" t="inlineStr">
-        <is>
-          <t>20% off storewide (all sales final)</t>
-        </is>
-      </c>
-      <c r="H61" s="15" t="n"/>
-      <c r="I61" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="J61" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-30 06:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K61" s="13" t="inlineStr">
-        <is>
-          <t>LehighValley.com article</t>
-        </is>
-      </c>
-      <c r="L61" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M61" s="13" t="inlineStr"/>
-      <c r="N61" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O61" s="14" t="inlineStr">
-        <is>
-          <t>2300 Wood Ave, Wilson Borough (Easton area). Final day Oct 30. Retail-floor sale, not a bulk lot; ask in person about buying remaining stock outright.</t>
-        </is>
-      </c>
+      <c r="B61" s="12" t="n"/>
+      <c r="C61" s="12" t="n"/>
+      <c r="D61" s="12" t="n"/>
+      <c r="E61" s="12" t="n"/>
+      <c r="F61" s="12" t="n"/>
+      <c r="G61" s="12" t="n"/>
+      <c r="H61" s="12" t="n"/>
+      <c r="I61" s="12" t="n"/>
+      <c r="J61" s="12" t="n"/>
+      <c r="K61" s="12" t="n"/>
+      <c r="L61" s="12" t="n"/>
+      <c r="M61" s="12" t="n"/>
+      <c r="N61" s="12" t="n"/>
+      <c r="O61" s="12" t="n"/>
     </row>
     <row r="62" outlineLevel="1">
       <c r="A62" s="13" t="inlineStr">
@@ -21807,17 +21931,17 @@
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>October restaurant consignment – Hobart, Rational, True + NEW scratch-and-dent Migali/Avantco</t>
+          <t>Piscitello's Home Center closing after 68 years: storewide 20% off liquidation (hardware, lumber, doors, windows, kitchen/bath)</t>
         </is>
       </c>
       <c r="C62" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>Harrisburg</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
@@ -21826,28 +21950,32 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>340</v>
+        <v>250</v>
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>Online auction, 15% BP, ships $55/pallet</t>
+          <t>20% off storewide (all sales final)</t>
         </is>
       </c>
       <c r="H62" s="15" t="n"/>
-      <c r="I62" s="13" t="inlineStr"/>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="J62" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 11:00 AM ET</t>
+          <t>2026-10-30 06:00 PM ET</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>Restaurant Auction Co</t>
-        </is>
-      </c>
-      <c r="L62" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>LehighValley.com article</t>
+        </is>
+      </c>
+      <c r="L62" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M62" s="13" t="inlineStr"/>
@@ -21858,124 +21986,120 @@
       </c>
       <c r="O62" s="14" t="inlineStr">
         <is>
+          <t>2300 Wood Ave, Wilson Borough (Easton area). Final day Oct 30. Retail-floor sale, not a bulk lot; ask in person about buying remaining stock outright.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" outlineLevel="1">
+      <c r="A63" s="13" t="inlineStr">
+        <is>
+          <t>Eastern PA / Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>October restaurant consignment – Hobart, Rational, True + NEW scratch-and-dent Migali/Avantco</t>
+        </is>
+      </c>
+      <c r="C63" s="13" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="D63" s="13" t="inlineStr">
+        <is>
+          <t>Harrisburg</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="F63" s="13" t="n">
+        <v>340</v>
+      </c>
+      <c r="G63" s="13" t="inlineStr">
+        <is>
+          <t>Online auction, 15% BP, ships $55/pallet</t>
+        </is>
+      </c>
+      <c r="H63" s="15" t="n"/>
+      <c r="I63" s="13" t="inlineStr"/>
+      <c r="J63" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K63" s="13" t="inlineStr">
+        <is>
+          <t>Restaurant Auction Co</t>
+        </is>
+      </c>
+      <c r="L63" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M63" s="13" t="inlineStr"/>
+      <c r="N63" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O63" s="14" t="inlineStr">
+        <is>
           <t>Closes Oct 21 10 or 11 AM (later used). Shippable.</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="17" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Eastern PA / Mid-Atlantic</t>
         </is>
       </c>
-      <c r="B63" s="17" t="inlineStr">
+      <c r="B64" s="17" t="inlineStr">
         <is>
           <t>2 item(s)</t>
         </is>
       </c>
-      <c r="C63" s="18" t="n"/>
-      <c r="D63" s="18" t="n"/>
-      <c r="E63" s="18" t="n"/>
-      <c r="F63" s="18" t="n"/>
-      <c r="G63" s="18" t="n"/>
-      <c r="H63" s="19" t="n">
+      <c r="C64" s="18" t="n"/>
+      <c r="D64" s="18" t="n"/>
+      <c r="E64" s="18" t="n"/>
+      <c r="F64" s="18" t="n"/>
+      <c r="G64" s="18" t="n"/>
+      <c r="H64" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I63" s="18" t="n"/>
-      <c r="J63" s="18" t="n"/>
-      <c r="K63" s="18" t="n"/>
-      <c r="L63" s="18" t="n"/>
-      <c r="M63" s="18" t="n"/>
-      <c r="N63" s="18" t="n"/>
-      <c r="O63" s="18" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="11" t="inlineStr">
+      <c r="I64" s="18" t="n"/>
+      <c r="J64" s="18" t="n"/>
+      <c r="K64" s="18" t="n"/>
+      <c r="L64" s="18" t="n"/>
+      <c r="M64" s="18" t="n"/>
+      <c r="N64" s="18" t="n"/>
+      <c r="O64" s="18" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
         <is>
           <t>▸ Western PA / Ohio Valley  (3)</t>
         </is>
       </c>
-      <c r="B64" s="12" t="n"/>
-      <c r="C64" s="12" t="n"/>
-      <c r="D64" s="12" t="n"/>
-      <c r="E64" s="12" t="n"/>
-      <c r="F64" s="12" t="n"/>
-      <c r="G64" s="12" t="n"/>
-      <c r="H64" s="12" t="n"/>
-      <c r="I64" s="12" t="n"/>
-      <c r="J64" s="12" t="n"/>
-      <c r="K64" s="12" t="n"/>
-      <c r="L64" s="12" t="n"/>
-      <c r="M64" s="12" t="n"/>
-      <c r="N64" s="12" t="n"/>
-      <c r="O64" s="12" t="n"/>
-    </row>
-    <row r="65" outlineLevel="1">
-      <c r="A65" s="13" t="inlineStr">
-        <is>
-          <t>Western PA / Ohio Valley</t>
-        </is>
-      </c>
-      <c r="B65" s="14" t="inlineStr">
-        <is>
-          <t>Petrunak's Hardware Store liquidation Day 1 (530 lots: doors, hardware, tools, building supplies)</t>
-        </is>
-      </c>
-      <c r="C65" s="13" t="inlineStr">
-        <is>
-          <t>store closing auction</t>
-        </is>
-      </c>
-      <c r="D65" s="13" t="inlineStr">
-        <is>
-          <t>Windber</t>
-        </is>
-      </c>
-      <c r="E65" s="13" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="F65" s="13" t="n">
-        <v>437</v>
-      </c>
-      <c r="G65" s="13" t="inlineStr">
-        <is>
-          <t>Timed online auction (530 lots)</t>
-        </is>
-      </c>
-      <c r="H65" s="15" t="n"/>
-      <c r="I65" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="J65" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 08:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K65" s="13" t="inlineStr">
-        <is>
-          <t>Carey Auctions</t>
-        </is>
-      </c>
-      <c r="L65" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M65" s="13" t="inlineStr"/>
-      <c r="N65" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O65" s="14" t="inlineStr">
-        <is>
-          <t>Ends Oct 21 7 PM CDT (8 PM ET). 1500 Somerset Ave, Windber PA. Pickups Oct 24-28. Hardware store, not appliance parts.</t>
-        </is>
-      </c>
+      <c r="B65" s="12" t="n"/>
+      <c r="C65" s="12" t="n"/>
+      <c r="D65" s="12" t="n"/>
+      <c r="E65" s="12" t="n"/>
+      <c r="F65" s="12" t="n"/>
+      <c r="G65" s="12" t="n"/>
+      <c r="H65" s="12" t="n"/>
+      <c r="I65" s="12" t="n"/>
+      <c r="J65" s="12" t="n"/>
+      <c r="K65" s="12" t="n"/>
+      <c r="L65" s="12" t="n"/>
+      <c r="M65" s="12" t="n"/>
+      <c r="N65" s="12" t="n"/>
+      <c r="O65" s="12" t="n"/>
     </row>
     <row r="66" outlineLevel="1">
       <c r="A66" s="13" t="inlineStr">
@@ -21985,7 +22109,7 @@
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>Petrunak's Hardware Store liquidation Day 2 (433 lots)</t>
+          <t>Petrunak's Hardware Store liquidation Day 1 (530 lots: doors, hardware, tools, building supplies)</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
@@ -22008,7 +22132,7 @@
       </c>
       <c r="G66" s="13" t="inlineStr">
         <is>
-          <t>Timed online auction (433 lots)</t>
+          <t>Timed online auction (530 lots)</t>
         </is>
       </c>
       <c r="H66" s="15" t="n"/>
@@ -22019,7 +22143,7 @@
       </c>
       <c r="J66" s="13" t="inlineStr">
         <is>
-          <t>2026-10-22 08:00 PM ET</t>
+          <t>2026-10-21 08:00 PM ET</t>
         </is>
       </c>
       <c r="K66" s="13" t="inlineStr">
@@ -22040,7 +22164,7 @@
       </c>
       <c r="O66" s="14" t="inlineStr">
         <is>
-          <t>Ends Oct 22 7 PM CDT (8 PM ET). Same store as Day 1; pickups Oct 24-28.</t>
+          <t>Ends Oct 21 7 PM CDT (8 PM ET). 1500 Somerset Ave, Windber PA. Pickups Oct 24-28. Hardware store, not appliance parts.</t>
         </is>
       </c>
     </row>
@@ -22052,17 +22176,17 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>Millers Pizza &amp; More – pizza business, commercial kitchen &amp; event space contents (362 lots)</t>
+          <t>Petrunak's Hardware Store liquidation Day 2 (433 lots)</t>
         </is>
       </c>
       <c r="C67" s="13" t="inlineStr">
         <is>
-          <t>restaurant / commercial kitchen contents</t>
+          <t>store closing auction</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>Everson</t>
+          <t>Windber</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
@@ -22071,28 +22195,32 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>478</v>
+        <v>437</v>
       </c>
       <c r="G67" s="13" t="inlineStr">
         <is>
-          <t>Online auction, 15% buyer premium</t>
+          <t>Timed online auction (433 lots)</t>
         </is>
       </c>
       <c r="H67" s="15" t="n"/>
-      <c r="I67" s="13" t="inlineStr"/>
+      <c r="I67" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="J67" s="13" t="inlineStr">
         <is>
-          <t>2026-10-25 07:00 PM ET</t>
+          <t>2026-10-22 08:00 PM ET</t>
         </is>
       </c>
       <c r="K67" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Bid Local LLC)</t>
-        </is>
-      </c>
-      <c r="L67" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Carey Auctions</t>
+        </is>
+      </c>
+      <c r="L67" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M67" s="13" t="inlineStr"/>
@@ -22103,342 +22231,342 @@
       </c>
       <c r="O67" s="14" t="inlineStr">
         <is>
+          <t>Ends Oct 22 7 PM CDT (8 PM ET). Same store as Day 1; pickups Oct 24-28.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" outlineLevel="1">
+      <c r="A68" s="13" t="inlineStr">
+        <is>
+          <t>Western PA / Ohio Valley</t>
+        </is>
+      </c>
+      <c r="B68" s="14" t="inlineStr">
+        <is>
+          <t>Millers Pizza &amp; More – pizza business, commercial kitchen &amp; event space contents (362 lots)</t>
+        </is>
+      </c>
+      <c r="C68" s="13" t="inlineStr">
+        <is>
+          <t>restaurant / commercial kitchen contents</t>
+        </is>
+      </c>
+      <c r="D68" s="13" t="inlineStr">
+        <is>
+          <t>Everson</t>
+        </is>
+      </c>
+      <c r="E68" s="13" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="F68" s="13" t="n">
+        <v>478</v>
+      </c>
+      <c r="G68" s="13" t="inlineStr">
+        <is>
+          <t>Online auction, 15% buyer premium</t>
+        </is>
+      </c>
+      <c r="H68" s="15" t="n"/>
+      <c r="I68" s="13" t="inlineStr"/>
+      <c r="J68" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-25 07:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K68" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (Bid Local LLC)</t>
+        </is>
+      </c>
+      <c r="L68" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M68" s="13" t="inlineStr"/>
+      <c r="N68" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O68" s="14" t="inlineStr">
+        <is>
           <t>Property of Millers Pizza and More LLC; online-only, 362 lots, lots begin closing Oct 25 7 PM. Pickup Everson PA by appointment Tue 10/27 and Wed 10/28. Building (4,500 sq ft) to be auctioned separately.</t>
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="17" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Western PA / Ohio Valley</t>
         </is>
       </c>
-      <c r="B68" s="17" t="inlineStr">
+      <c r="B69" s="17" t="inlineStr">
         <is>
           <t>3 item(s)</t>
         </is>
       </c>
-      <c r="C68" s="18" t="n"/>
-      <c r="D68" s="18" t="n"/>
-      <c r="E68" s="18" t="n"/>
-      <c r="F68" s="18" t="n"/>
-      <c r="G68" s="18" t="n"/>
-      <c r="H68" s="19" t="n">
+      <c r="C69" s="18" t="n"/>
+      <c r="D69" s="18" t="n"/>
+      <c r="E69" s="18" t="n"/>
+      <c r="F69" s="18" t="n"/>
+      <c r="G69" s="18" t="n"/>
+      <c r="H69" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I68" s="18" t="n"/>
-      <c r="J68" s="18" t="n"/>
-      <c r="K68" s="18" t="n"/>
-      <c r="L68" s="18" t="n"/>
-      <c r="M68" s="18" t="n"/>
-      <c r="N68" s="18" t="n"/>
-      <c r="O68" s="18" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="11" t="inlineStr">
+      <c r="I69" s="18" t="n"/>
+      <c r="J69" s="18" t="n"/>
+      <c r="K69" s="18" t="n"/>
+      <c r="L69" s="18" t="n"/>
+      <c r="M69" s="18" t="n"/>
+      <c r="N69" s="18" t="n"/>
+      <c r="O69" s="18" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="11" t="inlineStr">
         <is>
           <t>▸ Upstate / Western NY  (1)</t>
         </is>
       </c>
-      <c r="B69" s="12" t="n"/>
-      <c r="C69" s="12" t="n"/>
-      <c r="D69" s="12" t="n"/>
-      <c r="E69" s="12" t="n"/>
-      <c r="F69" s="12" t="n"/>
-      <c r="G69" s="12" t="n"/>
-      <c r="H69" s="12" t="n"/>
-      <c r="I69" s="12" t="n"/>
-      <c r="J69" s="12" t="n"/>
-      <c r="K69" s="12" t="n"/>
-      <c r="L69" s="12" t="n"/>
-      <c r="M69" s="12" t="n"/>
-      <c r="N69" s="12" t="n"/>
-      <c r="O69" s="12" t="n"/>
-    </row>
-    <row r="70" outlineLevel="1">
-      <c r="A70" s="13" t="inlineStr">
+      <c r="B70" s="12" t="n"/>
+      <c r="C70" s="12" t="n"/>
+      <c r="D70" s="12" t="n"/>
+      <c r="E70" s="12" t="n"/>
+      <c r="F70" s="12" t="n"/>
+      <c r="G70" s="12" t="n"/>
+      <c r="H70" s="12" t="n"/>
+      <c r="I70" s="12" t="n"/>
+      <c r="J70" s="12" t="n"/>
+      <c r="K70" s="12" t="n"/>
+      <c r="L70" s="12" t="n"/>
+      <c r="M70" s="12" t="n"/>
+      <c r="N70" s="12" t="n"/>
+      <c r="O70" s="12" t="n"/>
+    </row>
+    <row r="71" outlineLevel="1">
+      <c r="A71" s="13" t="inlineStr">
         <is>
           <t>Upstate / Western NY</t>
         </is>
       </c>
-      <c r="B70" s="14" t="inlineStr">
+      <c r="B71" s="14" t="inlineStr">
         <is>
           <t>Restaurant &amp; fitness equipment</t>
         </is>
       </c>
-      <c r="C70" s="13" t="inlineStr">
+      <c r="C71" s="13" t="inlineStr">
         <is>
           <t>restaurant</t>
         </is>
       </c>
-      <c r="D70" s="13" t="inlineStr">
+      <c r="D71" s="13" t="inlineStr">
         <is>
           <t>Williamsville</t>
         </is>
       </c>
-      <c r="E70" s="13" t="inlineStr">
+      <c r="E71" s="13" t="inlineStr">
         <is>
           <t>NY</t>
         </is>
       </c>
-      <c r="F70" s="13" t="n">
+      <c r="F71" s="13" t="n">
         <v>408</v>
       </c>
-      <c r="G70" s="13" t="inlineStr">
+      <c r="G71" s="13" t="inlineStr">
         <is>
           <t>Online auction</t>
         </is>
       </c>
-      <c r="H70" s="15" t="n"/>
-      <c r="I70" s="13" t="inlineStr"/>
-      <c r="J70" s="13" t="inlineStr">
+      <c r="H71" s="15" t="n"/>
+      <c r="I71" s="13" t="inlineStr"/>
+      <c r="J71" s="13" t="inlineStr">
         <is>
           <t>2026-10-26 07:30 PM ET</t>
         </is>
       </c>
-      <c r="K70" s="13" t="inlineStr">
+      <c r="K71" s="13" t="inlineStr">
         <is>
           <t>Cash Auctions</t>
         </is>
       </c>
-      <c r="L70" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M70" s="13" t="inlineStr"/>
-      <c r="N70" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O70" s="14" t="inlineStr">
+      <c r="L71" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M71" s="13" t="inlineStr"/>
+      <c r="N71" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O71" s="14" t="inlineStr">
         <is>
           <t>Lots not reviewed.</t>
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="17" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Upstate / Western NY</t>
         </is>
       </c>
-      <c r="B71" s="17" t="inlineStr">
+      <c r="B72" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C71" s="18" t="n"/>
-      <c r="D71" s="18" t="n"/>
-      <c r="E71" s="18" t="n"/>
-      <c r="F71" s="18" t="n"/>
-      <c r="G71" s="18" t="n"/>
-      <c r="H71" s="19" t="n">
+      <c r="C72" s="18" t="n"/>
+      <c r="D72" s="18" t="n"/>
+      <c r="E72" s="18" t="n"/>
+      <c r="F72" s="18" t="n"/>
+      <c r="G72" s="18" t="n"/>
+      <c r="H72" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I71" s="18" t="n"/>
-      <c r="J71" s="18" t="n"/>
-      <c r="K71" s="18" t="n"/>
-      <c r="L71" s="18" t="n"/>
-      <c r="M71" s="18" t="n"/>
-      <c r="N71" s="18" t="n"/>
-      <c r="O71" s="18" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="11" t="inlineStr">
+      <c r="I72" s="18" t="n"/>
+      <c r="J72" s="18" t="n"/>
+      <c r="K72" s="18" t="n"/>
+      <c r="L72" s="18" t="n"/>
+      <c r="M72" s="18" t="n"/>
+      <c r="N72" s="18" t="n"/>
+      <c r="O72" s="18" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
         <is>
           <t>▸ Virginia  (1)</t>
         </is>
       </c>
-      <c r="B72" s="12" t="n"/>
-      <c r="C72" s="12" t="n"/>
-      <c r="D72" s="12" t="n"/>
-      <c r="E72" s="12" t="n"/>
-      <c r="F72" s="12" t="n"/>
-      <c r="G72" s="12" t="n"/>
-      <c r="H72" s="12" t="n"/>
-      <c r="I72" s="12" t="n"/>
-      <c r="J72" s="12" t="n"/>
-      <c r="K72" s="12" t="n"/>
-      <c r="L72" s="12" t="n"/>
-      <c r="M72" s="12" t="n"/>
-      <c r="N72" s="12" t="n"/>
-      <c r="O72" s="12" t="n"/>
-    </row>
-    <row r="73" outlineLevel="1">
-      <c r="A73" s="13" t="inlineStr">
+      <c r="B73" s="12" t="n"/>
+      <c r="C73" s="12" t="n"/>
+      <c r="D73" s="12" t="n"/>
+      <c r="E73" s="12" t="n"/>
+      <c r="F73" s="12" t="n"/>
+      <c r="G73" s="12" t="n"/>
+      <c r="H73" s="12" t="n"/>
+      <c r="I73" s="12" t="n"/>
+      <c r="J73" s="12" t="n"/>
+      <c r="K73" s="12" t="n"/>
+      <c r="L73" s="12" t="n"/>
+      <c r="M73" s="12" t="n"/>
+      <c r="N73" s="12" t="n"/>
+      <c r="O73" s="12" t="n"/>
+    </row>
+    <row r="74" outlineLevel="1">
+      <c r="A74" s="13" t="inlineStr">
         <is>
           <t>Virginia</t>
         </is>
       </c>
-      <c r="B73" s="14" t="inlineStr">
+      <c r="B74" s="14" t="inlineStr">
         <is>
           <t>Haynes Furniture / The Dump – 12 stores closing (furniture, mattresses)</t>
         </is>
       </c>
-      <c r="C73" s="13" t="inlineStr">
+      <c r="C74" s="13" t="inlineStr">
         <is>
           <t>retail GOB</t>
         </is>
       </c>
-      <c r="D73" s="13" t="inlineStr">
+      <c r="D74" s="13" t="inlineStr">
         <is>
           <t>Virginia Beach</t>
         </is>
       </c>
-      <c r="E73" s="13" t="inlineStr">
+      <c r="E74" s="13" t="inlineStr">
         <is>
           <t>VA</t>
         </is>
       </c>
-      <c r="F73" s="13" t="n">
+      <c r="F74" s="13" t="n">
         <v>456</v>
       </c>
-      <c r="G73" s="13" t="inlineStr">
+      <c r="G74" s="13" t="inlineStr">
         <is>
           <t>Retail GOB markdowns</t>
         </is>
       </c>
-      <c r="H73" s="15" t="n"/>
-      <c r="I73" s="13" t="inlineStr">
+      <c r="H74" s="15" t="n"/>
+      <c r="I74" s="13" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="J73" s="13" t="inlineStr"/>
-      <c r="K73" s="13" t="inlineStr">
+      <c r="J74" s="13" t="inlineStr"/>
+      <c r="K74" s="13" t="inlineStr">
         <is>
           <t>SB360 (PR Newswire)</t>
         </is>
       </c>
-      <c r="L73" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M73" s="13" t="inlineStr"/>
-      <c r="N73" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O73" s="14" t="inlineStr">
+      <c r="L74" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M74" s="13" t="inlineStr"/>
+      <c r="N74" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O74" s="14" t="inlineStr">
         <is>
           <t>Posted Oct 8. Multi-state (VA/AZ/GA/IL/TX); pinned at Virginia Beach. Home goods only.</t>
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="17" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Virginia</t>
         </is>
       </c>
-      <c r="B74" s="17" t="inlineStr">
+      <c r="B75" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C74" s="18" t="n"/>
-      <c r="D74" s="18" t="n"/>
-      <c r="E74" s="18" t="n"/>
-      <c r="F74" s="18" t="n"/>
-      <c r="G74" s="18" t="n"/>
-      <c r="H74" s="19" t="n">
+      <c r="C75" s="18" t="n"/>
+      <c r="D75" s="18" t="n"/>
+      <c r="E75" s="18" t="n"/>
+      <c r="F75" s="18" t="n"/>
+      <c r="G75" s="18" t="n"/>
+      <c r="H75" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I74" s="18" t="n"/>
-      <c r="J74" s="18" t="n"/>
-      <c r="K74" s="18" t="n"/>
-      <c r="L74" s="18" t="n"/>
-      <c r="M74" s="18" t="n"/>
-      <c r="N74" s="18" t="n"/>
-      <c r="O74" s="18" t="n"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t>▸ Midwest  (2)</t>
-        </is>
-      </c>
-      <c r="B75" s="12" t="n"/>
-      <c r="C75" s="12" t="n"/>
-      <c r="D75" s="12" t="n"/>
-      <c r="E75" s="12" t="n"/>
-      <c r="F75" s="12" t="n"/>
-      <c r="G75" s="12" t="n"/>
-      <c r="H75" s="12" t="n"/>
-      <c r="I75" s="12" t="n"/>
-      <c r="J75" s="12" t="n"/>
-      <c r="K75" s="12" t="n"/>
-      <c r="L75" s="12" t="n"/>
-      <c r="M75" s="12" t="n"/>
-      <c r="N75" s="12" t="n"/>
-      <c r="O75" s="12" t="n"/>
-    </row>
-    <row r="76" outlineLevel="1">
-      <c r="A76" s="13" t="inlineStr">
-        <is>
-          <t>Midwest</t>
-        </is>
-      </c>
-      <c r="B76" s="14" t="inlineStr">
-        <is>
-          <t>American Sale – total liquidation, all 7 stores (pools, hot tubs, grills, holiday decor)</t>
-        </is>
-      </c>
-      <c r="C76" s="13" t="inlineStr">
-        <is>
-          <t>retail GOB</t>
-        </is>
-      </c>
-      <c r="D76" s="13" t="inlineStr">
-        <is>
-          <t>Chicagoland</t>
-        </is>
-      </c>
-      <c r="E76" s="13" t="inlineStr">
-        <is>
-          <t>IL</t>
-        </is>
-      </c>
-      <c r="F76" s="13" t="n">
-        <v>876</v>
-      </c>
-      <c r="G76" s="13" t="inlineStr">
-        <is>
-          <t>Retail GOB, up to 70% off</t>
-        </is>
-      </c>
-      <c r="H76" s="15" t="n"/>
-      <c r="I76" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="J76" s="13" t="inlineStr"/>
-      <c r="K76" s="13" t="inlineStr">
-        <is>
-          <t>Tiger Group (PR Newswire)</t>
-        </is>
-      </c>
-      <c r="L76" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M76" s="13" t="inlineStr"/>
-      <c r="N76" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O76" s="14" t="inlineStr">
-        <is>
-          <t>Posted Oct 15. Watch for a bulk/fixture auction.</t>
-        </is>
-      </c>
+      <c r="I75" s="18" t="n"/>
+      <c r="J75" s="18" t="n"/>
+      <c r="K75" s="18" t="n"/>
+      <c r="L75" s="18" t="n"/>
+      <c r="M75" s="18" t="n"/>
+      <c r="N75" s="18" t="n"/>
+      <c r="O75" s="18" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t>▸ Midwest  (3)</t>
+        </is>
+      </c>
+      <c r="B76" s="12" t="n"/>
+      <c r="C76" s="12" t="n"/>
+      <c r="D76" s="12" t="n"/>
+      <c r="E76" s="12" t="n"/>
+      <c r="F76" s="12" t="n"/>
+      <c r="G76" s="12" t="n"/>
+      <c r="H76" s="12" t="n"/>
+      <c r="I76" s="12" t="n"/>
+      <c r="J76" s="12" t="n"/>
+      <c r="K76" s="12" t="n"/>
+      <c r="L76" s="12" t="n"/>
+      <c r="M76" s="12" t="n"/>
+      <c r="N76" s="12" t="n"/>
+      <c r="O76" s="12" t="n"/>
     </row>
     <row r="77" outlineLevel="1">
       <c r="A77" s="13" t="inlineStr">
@@ -22448,47 +22576,47 @@
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>Straub's Fine Foods store equipment – bakery, kitchen, meat room, Hussmann refrigeration</t>
+          <t>American Sale – total liquidation, all 7 stores (pools, hot tubs, grills, holiday decor)</t>
         </is>
       </c>
       <c r="C77" s="13" t="inlineStr">
         <is>
-          <t>grocery/restaurant</t>
+          <t>retail GOB</t>
         </is>
       </c>
       <c r="D77" s="13" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Chicagoland</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>1046</v>
+        <v>876</v>
       </c>
       <c r="G77" s="13" t="inlineStr">
         <is>
-          <t>Online auction (18% BP)</t>
+          <t>Retail GOB, up to 70% off</t>
         </is>
       </c>
       <c r="H77" s="15" t="n"/>
-      <c r="I77" s="13" t="inlineStr"/>
-      <c r="J77" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J77" s="13" t="inlineStr"/>
       <c r="K77" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L77" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Tiger Group (PR Newswire)</t>
+        </is>
+      </c>
+      <c r="L77" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M77" s="13" t="inlineStr"/>
@@ -22499,261 +22627,387 @@
       </c>
       <c r="O77" s="14" t="inlineStr">
         <is>
+          <t>Posted Oct 15. Watch for a bulk/fixture auction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" outlineLevel="1">
+      <c r="A78" s="13" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="B78" s="14" t="inlineStr">
+        <is>
+          <t>Straub's Fine Foods store equipment – bakery, kitchen, meat room, Hussmann refrigeration</t>
+        </is>
+      </c>
+      <c r="C78" s="13" t="inlineStr">
+        <is>
+          <t>grocery/restaurant</t>
+        </is>
+      </c>
+      <c r="D78" s="13" t="inlineStr">
+        <is>
+          <t>St. Louis</t>
+        </is>
+      </c>
+      <c r="E78" s="13" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="F78" s="13" t="n">
+        <v>1046</v>
+      </c>
+      <c r="G78" s="13" t="inlineStr">
+        <is>
+          <t>Online auction (18% BP)</t>
+        </is>
+      </c>
+      <c r="H78" s="15" t="n"/>
+      <c r="I78" s="13" t="inlineStr"/>
+      <c r="J78" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K78" s="13" t="inlineStr">
+        <is>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L78" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M78" s="13" t="inlineStr"/>
+      <c r="N78" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O78" s="14" t="inlineStr">
+        <is>
           <t>Kingshighway store: Revent double-rack oven + proofer, Reed revolving oven, Vulcan convection, Groen kettle, Southbend 6-burner, Pitco fryer, Stero dishwasher, Hobart saw/grinders, Berkel slicers, Hussmann cases + compressor racks, walk-ins, Hoshizaki/Scotsman ice machines, Crown pallet jack. Preview Oct 20 3–6 PM CDT; pickup in St. Louis.</t>
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="17" t="inlineStr">
+    <row r="79" outlineLevel="1">
+      <c r="A79" s="13" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant, Bar &amp; DJ Equipment Liquidation: Alto-Shaam combi, Southbend/Blodgett ovens, True refrigeration, Manitowoc, Hobart saw, DJ/AV gear</t>
+        </is>
+      </c>
+      <c r="C79" s="13" t="inlineStr">
+        <is>
+          <t>restaurant liquidation auction</t>
+        </is>
+      </c>
+      <c r="D79" s="13" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
+      <c r="F79" s="13" t="n">
+        <v>1124</v>
+      </c>
+      <c r="G79" s="13" t="inlineStr">
+        <is>
+          <t>Timed online auction</t>
+        </is>
+      </c>
+      <c r="H79" s="15" t="n"/>
+      <c r="I79" s="13" t="inlineStr"/>
+      <c r="J79" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-26 02:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K79" s="13" t="inlineStr">
+        <is>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L79" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M79" s="13" t="inlineStr"/>
+      <c r="N79" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O79" s="14" t="inlineStr">
+        <is>
+          <t>Begins closing Oct 26 1 PM CDT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Midwest</t>
         </is>
       </c>
-      <c r="B78" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C78" s="18" t="n"/>
-      <c r="D78" s="18" t="n"/>
-      <c r="E78" s="18" t="n"/>
-      <c r="F78" s="18" t="n"/>
-      <c r="G78" s="18" t="n"/>
-      <c r="H78" s="19" t="n">
+      <c r="B80" s="17" t="inlineStr">
+        <is>
+          <t>3 item(s)</t>
+        </is>
+      </c>
+      <c r="C80" s="18" t="n"/>
+      <c r="D80" s="18" t="n"/>
+      <c r="E80" s="18" t="n"/>
+      <c r="F80" s="18" t="n"/>
+      <c r="G80" s="18" t="n"/>
+      <c r="H80" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I78" s="18" t="n"/>
-      <c r="J78" s="18" t="n"/>
-      <c r="K78" s="18" t="n"/>
-      <c r="L78" s="18" t="n"/>
-      <c r="M78" s="18" t="n"/>
-      <c r="N78" s="18" t="n"/>
-      <c r="O78" s="18" t="n"/>
-    </row>
-    <row r="79">
-      <c r="A79" s="11" t="inlineStr">
+      <c r="I80" s="18" t="n"/>
+      <c r="J80" s="18" t="n"/>
+      <c r="K80" s="18" t="n"/>
+      <c r="L80" s="18" t="n"/>
+      <c r="M80" s="18" t="n"/>
+      <c r="N80" s="18" t="n"/>
+      <c r="O80" s="18" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
         <is>
           <t>▸ Texas / South Central  (1)</t>
         </is>
       </c>
-      <c r="B79" s="12" t="n"/>
-      <c r="C79" s="12" t="n"/>
-      <c r="D79" s="12" t="n"/>
-      <c r="E79" s="12" t="n"/>
-      <c r="F79" s="12" t="n"/>
-      <c r="G79" s="12" t="n"/>
-      <c r="H79" s="12" t="n"/>
-      <c r="I79" s="12" t="n"/>
-      <c r="J79" s="12" t="n"/>
-      <c r="K79" s="12" t="n"/>
-      <c r="L79" s="12" t="n"/>
-      <c r="M79" s="12" t="n"/>
-      <c r="N79" s="12" t="n"/>
-      <c r="O79" s="12" t="n"/>
-    </row>
-    <row r="80" outlineLevel="1">
-      <c r="A80" s="13" t="inlineStr">
+      <c r="B81" s="12" t="n"/>
+      <c r="C81" s="12" t="n"/>
+      <c r="D81" s="12" t="n"/>
+      <c r="E81" s="12" t="n"/>
+      <c r="F81" s="12" t="n"/>
+      <c r="G81" s="12" t="n"/>
+      <c r="H81" s="12" t="n"/>
+      <c r="I81" s="12" t="n"/>
+      <c r="J81" s="12" t="n"/>
+      <c r="K81" s="12" t="n"/>
+      <c r="L81" s="12" t="n"/>
+      <c r="M81" s="12" t="n"/>
+      <c r="N81" s="12" t="n"/>
+      <c r="O81" s="12" t="n"/>
+    </row>
+    <row r="82" outlineLevel="1">
+      <c r="A82" s="13" t="inlineStr">
         <is>
           <t>Texas / South Central</t>
         </is>
       </c>
-      <c r="B80" s="14" t="inlineStr">
+      <c r="B82" s="14" t="inlineStr">
         <is>
           <t>Southwest beverage distributor surplus – mostly unused: 16 True merchandisers, 75 Bunn brewers, 100+ micro-market kiosks</t>
         </is>
       </c>
-      <c r="C80" s="13" t="inlineStr">
+      <c r="C82" s="13" t="inlineStr">
         <is>
           <t>distributor surplus</t>
         </is>
       </c>
-      <c r="D80" s="13" t="inlineStr">
+      <c r="D82" s="13" t="inlineStr">
         <is>
           <t>Mesquite</t>
         </is>
       </c>
-      <c r="E80" s="13" t="inlineStr">
+      <c r="E82" s="13" t="inlineStr">
         <is>
           <t>TX</t>
         </is>
       </c>
-      <c r="F80" s="13" t="n">
+      <c r="F82" s="13" t="n">
         <v>1547</v>
       </c>
-      <c r="G80" s="13" t="inlineStr">
+      <c r="G82" s="13" t="inlineStr">
         <is>
           <t>Online auction</t>
         </is>
       </c>
-      <c r="H80" s="15" t="n"/>
-      <c r="I80" s="13" t="inlineStr"/>
-      <c r="J80" s="13" t="inlineStr">
+      <c r="H82" s="15" t="n"/>
+      <c r="I82" s="13" t="inlineStr"/>
+      <c r="J82" s="13" t="inlineStr">
         <is>
           <t>2026-11-13 11:00 AM ET</t>
         </is>
       </c>
-      <c r="K80" s="13" t="inlineStr">
+      <c r="K82" s="13" t="inlineStr">
         <is>
           <t>Heritage Global Partners</t>
         </is>
       </c>
-      <c r="L80" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M80" s="13" t="inlineStr"/>
-      <c r="N80" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O80" s="14" t="inlineStr">
+      <c r="L82" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M82" s="13" t="inlineStr"/>
+      <c r="N82" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O82" s="14" t="inlineStr">
         <is>
           <t>Near-new appliances, resell by unit. Nov 13 10 AM CST.</t>
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="17" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Texas / South Central</t>
         </is>
       </c>
-      <c r="B81" s="17" t="inlineStr">
+      <c r="B83" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C81" s="18" t="n"/>
-      <c r="D81" s="18" t="n"/>
-      <c r="E81" s="18" t="n"/>
-      <c r="F81" s="18" t="n"/>
-      <c r="G81" s="18" t="n"/>
-      <c r="H81" s="19" t="n">
+      <c r="C83" s="18" t="n"/>
+      <c r="D83" s="18" t="n"/>
+      <c r="E83" s="18" t="n"/>
+      <c r="F83" s="18" t="n"/>
+      <c r="G83" s="18" t="n"/>
+      <c r="H83" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I81" s="18" t="n"/>
-      <c r="J81" s="18" t="n"/>
-      <c r="K81" s="18" t="n"/>
-      <c r="L81" s="18" t="n"/>
-      <c r="M81" s="18" t="n"/>
-      <c r="N81" s="18" t="n"/>
-      <c r="O81" s="18" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" s="11" t="inlineStr">
+      <c r="I83" s="18" t="n"/>
+      <c r="J83" s="18" t="n"/>
+      <c r="K83" s="18" t="n"/>
+      <c r="L83" s="18" t="n"/>
+      <c r="M83" s="18" t="n"/>
+      <c r="N83" s="18" t="n"/>
+      <c r="O83" s="18" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t>▸ West / Other  (1)</t>
         </is>
       </c>
-      <c r="B82" s="12" t="n"/>
-      <c r="C82" s="12" t="n"/>
-      <c r="D82" s="12" t="n"/>
-      <c r="E82" s="12" t="n"/>
-      <c r="F82" s="12" t="n"/>
-      <c r="G82" s="12" t="n"/>
-      <c r="H82" s="12" t="n"/>
-      <c r="I82" s="12" t="n"/>
-      <c r="J82" s="12" t="n"/>
-      <c r="K82" s="12" t="n"/>
-      <c r="L82" s="12" t="n"/>
-      <c r="M82" s="12" t="n"/>
-      <c r="N82" s="12" t="n"/>
-      <c r="O82" s="12" t="n"/>
-    </row>
-    <row r="83" outlineLevel="1">
-      <c r="A83" s="13" t="inlineStr">
+      <c r="B84" s="12" t="n"/>
+      <c r="C84" s="12" t="n"/>
+      <c r="D84" s="12" t="n"/>
+      <c r="E84" s="12" t="n"/>
+      <c r="F84" s="12" t="n"/>
+      <c r="G84" s="12" t="n"/>
+      <c r="H84" s="12" t="n"/>
+      <c r="I84" s="12" t="n"/>
+      <c r="J84" s="12" t="n"/>
+      <c r="K84" s="12" t="n"/>
+      <c r="L84" s="12" t="n"/>
+      <c r="M84" s="12" t="n"/>
+      <c r="N84" s="12" t="n"/>
+      <c r="O84" s="12" t="n"/>
+    </row>
+    <row r="85" outlineLevel="1">
+      <c r="A85" s="13" t="inlineStr">
         <is>
           <t>West / Other</t>
         </is>
       </c>
-      <c r="B83" s="14" t="inlineStr">
+      <c r="B85" s="14" t="inlineStr">
         <is>
           <t>National salad concept liquidation – full contents of 63 fast-casual restaurants (AZ/TX/OK/NV)</t>
         </is>
       </c>
-      <c r="C83" s="13" t="inlineStr">
+      <c r="C85" s="13" t="inlineStr">
         <is>
           <t>restaurant chain liquidation</t>
         </is>
       </c>
-      <c r="D83" s="13" t="inlineStr">
+      <c r="D85" s="13" t="inlineStr">
         <is>
           <t>Phoenix</t>
         </is>
       </c>
-      <c r="E83" s="13" t="inlineStr">
+      <c r="E85" s="13" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="F83" s="13" t="n">
+      <c r="F85" s="13" t="n">
         <v>2307</v>
       </c>
-      <c r="G83" s="13" t="inlineStr">
+      <c r="G85" s="13" t="inlineStr">
         <is>
           <t>Online auctions, dates TBD</t>
         </is>
       </c>
-      <c r="H83" s="15" t="n"/>
-      <c r="I83" s="13" t="inlineStr">
+      <c r="H85" s="15" t="n"/>
+      <c r="I85" s="13" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="J83" s="13" t="inlineStr"/>
-      <c r="K83" s="13" t="inlineStr">
+      <c r="J85" s="13" t="inlineStr"/>
+      <c r="K85" s="13" t="inlineStr">
         <is>
           <t>RestaurantEquipment.bid (TAGeX)</t>
         </is>
       </c>
-      <c r="L83" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M83" s="13" t="inlineStr"/>
-      <c r="N83" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O83" s="14" t="inlineStr">
+      <c r="L85" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M85" s="13" t="inlineStr"/>
+      <c r="N85" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O85" s="14" t="inlineStr">
         <is>
           <t>Rolling market-by-market auctions, none live yet (Phoenix metro 30 locations, DFW 14, Tucson 6, Houston 5, plus OK/NV). Pickup on site at each restaurant. Pinned at Phoenix.</t>
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="17" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="17" t="inlineStr">
         <is>
           <t>Subtotal — West / Other</t>
         </is>
       </c>
-      <c r="B84" s="17" t="inlineStr">
+      <c r="B86" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C84" s="18" t="n"/>
-      <c r="D84" s="18" t="n"/>
-      <c r="E84" s="18" t="n"/>
-      <c r="F84" s="18" t="n"/>
-      <c r="G84" s="18" t="n"/>
-      <c r="H84" s="19" t="n">
+      <c r="C86" s="18" t="n"/>
+      <c r="D86" s="18" t="n"/>
+      <c r="E86" s="18" t="n"/>
+      <c r="F86" s="18" t="n"/>
+      <c r="G86" s="18" t="n"/>
+      <c r="H86" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I84" s="18" t="n"/>
-      <c r="J84" s="18" t="n"/>
-      <c r="K84" s="18" t="n"/>
-      <c r="L84" s="18" t="n"/>
-      <c r="M84" s="18" t="n"/>
-      <c r="N84" s="18" t="n"/>
-      <c r="O84" s="18" t="n"/>
+      <c r="I86" s="18" t="n"/>
+      <c r="J86" s="18" t="n"/>
+      <c r="K86" s="18" t="n"/>
+      <c r="L86" s="18" t="n"/>
+      <c r="M86" s="18" t="n"/>
+      <c r="N86" s="18" t="n"/>
+      <c r="O86" s="18" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O84"/>
+  <autoFilter ref="A1:O86"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId2"/>
@@ -22801,17 +23055,19 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N61" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId47"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N62" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N65" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N66" r:id="rId50"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N67" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N73" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N76" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N68" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N71" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N74" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N77" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N80" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N83" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N78" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N79" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N82" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N85" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22985,7 +23241,7 @@
       </c>
       <c r="O2" s="14" t="inlineStr">
         <is>
-          <t>Integrity Auction House. Internet bidding closes Mon Oct 19 9:18 PM ET. $50 high bid (1 bid) as of 2026-10-18. [Closed Oct 19; HiBid price realized $50.] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Integrity Auction House. Internet bidding closes Mon Oct 19 9:18 PM ET. $50 high bid (1 bid) as of 2026-10-18. [Closed Oct 19; HiBid price realized $50.] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23048,7 +23304,7 @@
       </c>
       <c r="O3" s="14" t="inlineStr">
         <is>
-          <t>Live auction Mon Oct 19 4 PM, 3457 Wilmington Rd. Few bulk parts. [Live auction held Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Live auction Mon Oct 19 4 PM, 3457 Wilmington Rd. Few bulk parts. [Live auction held Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23249,7 +23505,7 @@
       </c>
       <c r="O6" s="14" t="inlineStr">
         <is>
-          <t>Condition: Pre-Owned. FLIP: SO36U/S tested, auction $99/0 bids, pickup only; rough resale $600-1k (eBay card shows no city; pickup distance in source.) Ends Oct 18 ~2:19 PM per eBay card (time zone uncertain; could be earlier). [auto-removed 2026-10-18: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Condition: Pre-Owned. FLIP: SO36U/S tested, auction $99/0 bids, pickup only; rough resale $600-1k (eBay card shows no city; pickup distance in source.) Ends Oct 18 ~2:19 PM per eBay card (time zone uncertain; could be earlier). [auto-removed 2026-10-18: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23314,7 +23570,7 @@
       </c>
       <c r="O7" s="14" t="inlineStr">
         <is>
-          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf) HiBid lot closed/sold ~$37.50 on 2026-10-18. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf) HiBid lot closed/sold ~$37.50 on 2026-10-18. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23379,7 +23635,7 @@
       </c>
       <c r="O8" s="14" t="inlineStr">
         <is>
-          <t>Lots close from Oct 19 2 PM ET. [HiBid catalog closed 2 PM ET Oct 19.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Lots close from Oct 19 2 PM ET. [HiBid catalog closed 2 PM ET Oct 19.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23444,7 +23700,7 @@
       </c>
       <c r="O9" s="14" t="inlineStr">
         <is>
-          <t>Lots close from Oct 20 2 PM ET. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Lots close from Oct 20 2 PM ET. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23507,7 +23763,7 @@
       </c>
       <c r="O10" s="14" t="inlineStr">
         <is>
-          <t>Tested and new units. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Tested and new units. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23570,7 +23826,7 @@
       </c>
       <c r="O11" s="14" t="inlineStr">
         <is>
-          <t>Pickup Oct 21 only. [Lots began closing 1 PM ET Oct 19; ended.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Pickup Oct 21 only. [Lots began closing 1 PM ET Oct 19; ended.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23633,7 +23889,7 @@
       </c>
       <c r="O12" s="14" t="inlineStr">
         <is>
-          <t>Close Oct 18 or 19 6 PM (later used). [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Close Oct 18 or 19 6 PM (later used). [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23696,7 +23952,7 @@
       </c>
       <c r="O13" s="14" t="inlineStr">
         <is>
-          <t>No new out-of-state bidders. Small. [Ended Oct 19 7 PM.] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>No new out-of-state bidders. Small. [Ended Oct 19 7 PM.] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23759,7 +24015,7 @@
       </c>
       <c r="O14" s="14" t="inlineStr">
         <is>
-          <t>Small lot. [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Small lot. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23822,7 +24078,7 @@
       </c>
       <c r="O15" s="14" t="inlineStr">
         <is>
-          <t>Closes from Oct 20 10 AM CDT. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Closes from Oct 20 10 AM CDT. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23952,7 +24208,7 @@
       </c>
       <c r="O17" s="14" t="inlineStr">
         <is>
-          <t>"Short notice" auction Mon Oct 19 1 PM. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>"Short notice" auction Mon Oct 19 1 PM. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -24019,7 +24275,7 @@
       </c>
       <c r="O18" s="14" t="inlineStr">
         <is>
-          <t>Tue Oct 20 2 PM. No item description on page. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Tue Oct 20 2 PM. No item description on page. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -24086,7 +24342,7 @@
       </c>
       <c r="O19" s="14" t="inlineStr">
         <is>
-          <t>Mon Oct 19 4 PM. No item description on page. [HiBid shows Bidding Closed, Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed]</t>
+          <t>Mon Oct 19 4 PM. No item description on page. [HiBid shows Bidding Closed, Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>

--- a/lot_recon.xlsx
+++ b/lot_recon.xlsx
@@ -20,8 +20,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wolf New'!$A$1:$O$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wolf Used'!$A$1:$O$189</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Wolf Unclear'!$A$1:$O$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$86</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Removed'!$A$1:$O$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Removed'!$A$1:$O$23</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -577,7 +577,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Last updated: 2026-10-21 08:05 ET</t>
+          <t>Last updated: 2026-10-21 11:02 ET</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Active listings: 298 · Removed: 18</t>
+          <t>Active listings: 294 · Removed: 22</t>
         </is>
       </c>
     </row>
@@ -708,13 +708,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>1275440.58</v>
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C24" t="n">
         <v>1</v>
@@ -1037,7 +1037,7 @@
         <v>24</v>
       </c>
       <c r="G24" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H24" s="6" t="n">
         <v>440141</v>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -1070,7 +1070,7 @@
         <v>1</v>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" s="6" t="n">
         <v>1555</v>
@@ -1220,7 +1220,7 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C30" t="n">
         <v>1</v>
@@ -1235,7 +1235,7 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H30" s="6" t="n">
         <v>7</v>
@@ -18540,7 +18540,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -20274,7 +20274,7 @@
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t>▸ NYC / Long Island / NJ  (25)</t>
+          <t>▸ NYC / Long Island / NJ  (23)</t>
         </is>
       </c>
       <c r="B34" s="12" t="n"/>
@@ -21245,17 +21245,17 @@
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>Serpico's Pizzeria (lost lease) – Bari ovens, walk-in, Hobart 60qt, Vulcan range</t>
+          <t>Bimmer Clinic business liquidation (BMW repair shop): vehicle lifts, forklift, skid steer, refrigerant recovery, shop tools &amp; equipment</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>business liquidation auction</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>Allenhurst</t>
+          <t>South Amboy</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -21264,28 +21264,28 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
-          <t>No-reserve online auction</t>
+          <t>Timed online auction</t>
         </is>
       </c>
       <c r="H50" s="15" t="n"/>
       <c r="I50" s="13" t="inlineStr"/>
       <c r="J50" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 11:00 AM ET</t>
+          <t>2026-11-12 11:00 AM ET</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>Peter Costanzo / EstateSales.net</t>
-        </is>
-      </c>
-      <c r="L50" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>AJ Willner Auctions</t>
+        </is>
+      </c>
+      <c r="L50" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M50" s="13" t="inlineStr"/>
@@ -21296,7 +21296,7 @@
       </c>
       <c r="O50" s="14" t="inlineStr">
         <is>
-          <t>Absolute / no reserve.</t>
+          <t>Ends Nov 12 11 AM EST.</t>
         </is>
       </c>
     </row>
@@ -21308,17 +21308,17 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>Altitude Trampoline Park liquidation – partial: Atosa, TurboChef, stainless</t>
+          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>facility contents</t>
+          <t>lien sale</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>Iselin</t>
+          <t>Edison</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -21327,28 +21327,24 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Online auction, $2K load-out fee</t>
         </is>
       </c>
       <c r="H51" s="15" t="n"/>
       <c r="I51" s="13" t="inlineStr"/>
-      <c r="J51" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="J51" s="13" t="inlineStr"/>
       <c r="K51" s="13" t="inlineStr">
         <is>
           <t>A.J. Willner</t>
         </is>
       </c>
-      <c r="L51" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+      <c r="L51" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M51" s="13" t="inlineStr"/>
@@ -21359,7 +21355,7 @@
       </c>
       <c r="O51" s="14" t="inlineStr">
         <is>
-          <t>Some kitchen gear only.</t>
+          <t>&gt;$100K new. Close date not captured.</t>
         </is>
       </c>
     </row>
@@ -21371,17 +21367,17 @@
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>Bimmer Clinic business liquidation (BMW repair shop): vehicle lifts, forklift, skid steer, refrigerant recovery, shop tools &amp; equipment</t>
+          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>business liquidation auction</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>South Amboy</t>
+          <t>Edison</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -21390,23 +21386,27 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
-          <t>Timed online auction</t>
+          <t>Live + HiBid webcast, 18% BP + 3% card</t>
         </is>
       </c>
       <c r="H52" s="15" t="n"/>
-      <c r="I52" s="13" t="inlineStr"/>
+      <c r="I52" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="J52" s="13" t="inlineStr">
         <is>
-          <t>2026-11-12 11:00 AM ET</t>
+          <t>2026-10-25 01:00 PM ET</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>AJ Willner Auctions</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
       <c r="L52" s="13" t="inlineStr">
@@ -21414,7 +21414,11 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M52" s="13" t="inlineStr"/>
+      <c r="M52" s="21" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
       <c r="N52" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -21422,7 +21426,7 @@
       </c>
       <c r="O52" s="14" t="inlineStr">
         <is>
-          <t>Ends Nov 12 11 AM EST.</t>
+          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
         </is>
       </c>
     </row>
@@ -21434,17 +21438,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
+          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>lien sale</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>Edison</t>
+          <t>East Brunswick</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -21453,16 +21457,20 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
-          <t>Online auction, $2K load-out fee</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H53" s="15" t="n"/>
       <c r="I53" s="13" t="inlineStr"/>
-      <c r="J53" s="13" t="inlineStr"/>
+      <c r="J53" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-03 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
           <t>A.J. Willner</t>
@@ -21481,7 +21489,7 @@
       </c>
       <c r="O53" s="14" t="inlineStr">
         <is>
-          <t>&gt;$100K new. Close date not captured.</t>
+          <t>Store inventory.</t>
         </is>
       </c>
     </row>
@@ -21493,17 +21501,17 @@
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
+          <t>Bakery/Cafe Somerville NJ – rack ovens, La Marzocco, food truck (~76 lots)</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>Edison</t>
+          <t>Somerville</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -21512,27 +21520,27 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>Live + HiBid webcast, 18% BP + 3% card</t>
+          <t>Live webcast + online (18% BP online)</t>
         </is>
       </c>
       <c r="H54" s="15" t="n"/>
       <c r="I54" s="13" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J54" s="13" t="inlineStr">
         <is>
-          <t>2026-10-25 01:00 PM ET</t>
+          <t>2026-10-26 02:00 PM ET</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>HiBid / Best Buy Auctioneers</t>
         </is>
       </c>
       <c r="L54" s="13" t="inlineStr">
@@ -21540,11 +21548,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M54" s="21" t="inlineStr">
-        <is>
-          <t>FLIP</t>
-        </is>
-      </c>
+      <c r="M54" s="13" t="inlineStr"/>
       <c r="N54" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -21552,7 +21556,7 @@
       </c>
       <c r="O54" s="14" t="inlineStr">
         <is>
-          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
+          <t>Full bakery/cafe commercial kitchen: food truck w/ pizza oven, La Marzocco espresso, Mazzer, Baxter + Empire Logiudice rack ovens, dough depositor, Globe floor mixer, Artic Air / SS refrigeration, fryers, Vitamix, Robot Coupe, display cases, dining furniture. Preview 11 AM sale day; checkout Tue 10/27.</t>
         </is>
       </c>
     </row>
@@ -21564,17 +21568,17 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
+          <t>Ability to Work kitchen and store – commercial kitchen + store fixtures (~135 lots)</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>East Brunswick</t>
+          <t>Flemington</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -21583,23 +21587,23 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Timed online (15% BP)</t>
         </is>
       </c>
       <c r="H55" s="15" t="n"/>
       <c r="I55" s="13" t="inlineStr"/>
       <c r="J55" s="13" t="inlineStr">
         <is>
-          <t>2026-11-03 11:00 AM ET</t>
+          <t>2026-10-27 11:02 AM ET</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>HiBid</t>
         </is>
       </c>
       <c r="L55" s="13" t="inlineStr">
@@ -21615,7 +21619,7 @@
       </c>
       <c r="O55" s="14" t="inlineStr">
         <is>
-          <t>Store inventory.</t>
+          <t>Apprentice/hospitality training cafe-kitchen and store dispersal. Preview 9–11 AM sale day; removal Oct 27 noon–Oct 29.</t>
         </is>
       </c>
     </row>
@@ -21627,17 +21631,17 @@
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>Bakery/Cafe Somerville NJ – rack ovens, La Marzocco, food truck (~76 lots)</t>
+          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>showroom closing</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>Somerville</t>
+          <t>Lawrenceville</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -21646,27 +21650,23 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>Live webcast + online (18% BP online)</t>
+          <t>Online auction, 18% BP</t>
         </is>
       </c>
       <c r="H56" s="15" t="n"/>
-      <c r="I56" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
+      <c r="I56" s="13" t="inlineStr"/>
       <c r="J56" s="13" t="inlineStr">
         <is>
-          <t>2026-10-26 02:00 PM ET</t>
+          <t>2026-10-27 09:00 AM ET</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>HiBid / Best Buy Auctioneers</t>
+          <t>Grafe Auction</t>
         </is>
       </c>
       <c r="L56" s="13" t="inlineStr">
@@ -21682,7 +21682,7 @@
       </c>
       <c r="O56" s="14" t="inlineStr">
         <is>
-          <t>Full bakery/cafe commercial kitchen: food truck w/ pizza oven, La Marzocco espresso, Mazzer, Baxter + Empire Logiudice rack ovens, dough depositor, Globe floor mixer, Artic Air / SS refrigeration, fryers, Vitamix, Robot Coupe, display cases, dining furniture. Preview 11 AM sale day; checkout Tue 10/27.</t>
+          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
         </is>
       </c>
     </row>
@@ -21694,17 +21694,17 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>Ability to Work kitchen and store – commercial kitchen + store fixtures (~135 lots)</t>
+          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
         </is>
       </c>
       <c r="C57" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>showroom closing</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>Flemington</t>
+          <t>Cherry Hill</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -21713,23 +21713,23 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>237</v>
+        <v>266</v>
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
-          <t>Timed online (15% BP)</t>
+          <t>Online auction, openers ~$0.50</t>
         </is>
       </c>
       <c r="H57" s="15" t="n"/>
       <c r="I57" s="13" t="inlineStr"/>
       <c r="J57" s="13" t="inlineStr">
         <is>
-          <t>2026-10-27 11:02 AM ET</t>
+          <t>2026-11-02 11:00 AM ET</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>HiBid</t>
+          <t>Grafe Auction</t>
         </is>
       </c>
       <c r="L57" s="13" t="inlineStr">
@@ -21745,270 +21745,192 @@
       </c>
       <c r="O57" s="14" t="inlineStr">
         <is>
-          <t>Apprentice/hospitality training cafe-kitchen and store dispersal. Preview 9–11 AM sale day; removal Oct 27 noon–Oct 29.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" outlineLevel="1">
-      <c r="A58" s="13" t="inlineStr">
-        <is>
-          <t>NYC / Long Island / NJ</t>
-        </is>
-      </c>
-      <c r="B58" s="14" t="inlineStr">
-        <is>
-          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
-        </is>
-      </c>
-      <c r="C58" s="13" t="inlineStr">
-        <is>
-          <t>showroom closing</t>
-        </is>
-      </c>
-      <c r="D58" s="13" t="inlineStr">
-        <is>
-          <t>Lawrenceville</t>
-        </is>
-      </c>
-      <c r="E58" s="13" t="inlineStr">
-        <is>
-          <t>NJ</t>
-        </is>
-      </c>
-      <c r="F58" s="13" t="n">
-        <v>239</v>
-      </c>
-      <c r="G58" s="13" t="inlineStr">
-        <is>
-          <t>Online auction, 18% BP</t>
-        </is>
-      </c>
-      <c r="H58" s="15" t="n"/>
-      <c r="I58" s="13" t="inlineStr"/>
-      <c r="J58" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-27 09:00 AM ET</t>
-        </is>
-      </c>
-      <c r="K58" s="13" t="inlineStr">
-        <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L58" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M58" s="13" t="inlineStr"/>
-      <c r="N58" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O58" s="14" t="inlineStr">
-        <is>
-          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" outlineLevel="1">
-      <c r="A59" s="13" t="inlineStr">
-        <is>
-          <t>NYC / Long Island / NJ</t>
-        </is>
-      </c>
-      <c r="B59" s="14" t="inlineStr">
-        <is>
-          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
-        </is>
-      </c>
-      <c r="C59" s="13" t="inlineStr">
-        <is>
-          <t>showroom closing</t>
-        </is>
-      </c>
-      <c r="D59" s="13" t="inlineStr">
-        <is>
-          <t>Cherry Hill</t>
-        </is>
-      </c>
-      <c r="E59" s="13" t="inlineStr">
-        <is>
-          <t>NJ</t>
-        </is>
-      </c>
-      <c r="F59" s="13" t="n">
-        <v>266</v>
-      </c>
-      <c r="G59" s="13" t="inlineStr">
-        <is>
-          <t>Online auction, openers ~$0.50</t>
-        </is>
-      </c>
-      <c r="H59" s="15" t="n"/>
-      <c r="I59" s="13" t="inlineStr"/>
-      <c r="J59" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-02 11:00 AM ET</t>
-        </is>
-      </c>
-      <c r="K59" s="13" t="inlineStr">
-        <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L59" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M59" s="13" t="inlineStr"/>
-      <c r="N59" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O59" s="14" t="inlineStr">
-        <is>
           <t>Lots close from Nov 2 11 AM.</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="17" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="17" t="inlineStr">
         <is>
           <t>Subtotal — NYC / Long Island / NJ</t>
         </is>
       </c>
-      <c r="B60" s="17" t="inlineStr">
-        <is>
-          <t>25 item(s)</t>
-        </is>
-      </c>
-      <c r="C60" s="18" t="n"/>
-      <c r="D60" s="18" t="n"/>
-      <c r="E60" s="18" t="n"/>
-      <c r="F60" s="18" t="n"/>
-      <c r="G60" s="18" t="n"/>
-      <c r="H60" s="19" t="n">
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>23 item(s)</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="n"/>
+      <c r="D58" s="18" t="n"/>
+      <c r="E58" s="18" t="n"/>
+      <c r="F58" s="18" t="n"/>
+      <c r="G58" s="18" t="n"/>
+      <c r="H58" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I60" s="18" t="n"/>
-      <c r="J60" s="18" t="n"/>
-      <c r="K60" s="18" t="n"/>
-      <c r="L60" s="18" t="n"/>
-      <c r="M60" s="18" t="n"/>
-      <c r="N60" s="18" t="n"/>
-      <c r="O60" s="18" t="n"/>
+      <c r="I58" s="18" t="n"/>
+      <c r="J58" s="18" t="n"/>
+      <c r="K58" s="18" t="n"/>
+      <c r="L58" s="18" t="n"/>
+      <c r="M58" s="18" t="n"/>
+      <c r="N58" s="18" t="n"/>
+      <c r="O58" s="18" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>▸ Eastern PA / Mid-Atlantic  (1)</t>
+        </is>
+      </c>
+      <c r="B59" s="12" t="n"/>
+      <c r="C59" s="12" t="n"/>
+      <c r="D59" s="12" t="n"/>
+      <c r="E59" s="12" t="n"/>
+      <c r="F59" s="12" t="n"/>
+      <c r="G59" s="12" t="n"/>
+      <c r="H59" s="12" t="n"/>
+      <c r="I59" s="12" t="n"/>
+      <c r="J59" s="12" t="n"/>
+      <c r="K59" s="12" t="n"/>
+      <c r="L59" s="12" t="n"/>
+      <c r="M59" s="12" t="n"/>
+      <c r="N59" s="12" t="n"/>
+      <c r="O59" s="12" t="n"/>
+    </row>
+    <row r="60" outlineLevel="1">
+      <c r="A60" s="13" t="inlineStr">
+        <is>
+          <t>Eastern PA / Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="B60" s="14" t="inlineStr">
+        <is>
+          <t>Piscitello's Home Center closing after 68 years: storewide 20% off liquidation (hardware, lumber, doors, windows, kitchen/bath)</t>
+        </is>
+      </c>
+      <c r="C60" s="13" t="inlineStr">
+        <is>
+          <t>store closing</t>
+        </is>
+      </c>
+      <c r="D60" s="13" t="inlineStr">
+        <is>
+          <t>Wilson</t>
+        </is>
+      </c>
+      <c r="E60" s="13" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="F60" s="13" t="n">
+        <v>250</v>
+      </c>
+      <c r="G60" s="13" t="inlineStr">
+        <is>
+          <t>20% off storewide (all sales final)</t>
+        </is>
+      </c>
+      <c r="H60" s="15" t="n"/>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J60" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-30 06:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K60" s="13" t="inlineStr">
+        <is>
+          <t>LehighValley.com article</t>
+        </is>
+      </c>
+      <c r="L60" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M60" s="13" t="inlineStr"/>
+      <c r="N60" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O60" s="14" t="inlineStr">
+        <is>
+          <t>2300 Wood Ave, Wilson Borough (Easton area). Final day Oct 30. Retail-floor sale, not a bulk lot; ask in person about buying remaining stock outright.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t>▸ Eastern PA / Mid-Atlantic  (2)</t>
-        </is>
-      </c>
-      <c r="B61" s="12" t="n"/>
-      <c r="C61" s="12" t="n"/>
-      <c r="D61" s="12" t="n"/>
-      <c r="E61" s="12" t="n"/>
-      <c r="F61" s="12" t="n"/>
-      <c r="G61" s="12" t="n"/>
-      <c r="H61" s="12" t="n"/>
-      <c r="I61" s="12" t="n"/>
-      <c r="J61" s="12" t="n"/>
-      <c r="K61" s="12" t="n"/>
-      <c r="L61" s="12" t="n"/>
-      <c r="M61" s="12" t="n"/>
-      <c r="N61" s="12" t="n"/>
-      <c r="O61" s="12" t="n"/>
-    </row>
-    <row r="62" outlineLevel="1">
-      <c r="A62" s="13" t="inlineStr">
-        <is>
-          <t>Eastern PA / Mid-Atlantic</t>
-        </is>
-      </c>
-      <c r="B62" s="14" t="inlineStr">
-        <is>
-          <t>Piscitello's Home Center closing after 68 years: storewide 20% off liquidation (hardware, lumber, doors, windows, kitchen/bath)</t>
-        </is>
-      </c>
-      <c r="C62" s="13" t="inlineStr">
-        <is>
-          <t>store closing</t>
-        </is>
-      </c>
-      <c r="D62" s="13" t="inlineStr">
-        <is>
-          <t>Wilson</t>
-        </is>
-      </c>
-      <c r="E62" s="13" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="F62" s="13" t="n">
-        <v>250</v>
-      </c>
-      <c r="G62" s="13" t="inlineStr">
-        <is>
-          <t>20% off storewide (all sales final)</t>
-        </is>
-      </c>
-      <c r="H62" s="15" t="n"/>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="J62" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-30 06:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K62" s="13" t="inlineStr">
-        <is>
-          <t>LehighValley.com article</t>
-        </is>
-      </c>
-      <c r="L62" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M62" s="13" t="inlineStr"/>
-      <c r="N62" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O62" s="14" t="inlineStr">
-        <is>
-          <t>2300 Wood Ave, Wilson Borough (Easton area). Final day Oct 30. Retail-floor sale, not a bulk lot; ask in person about buying remaining stock outright.</t>
-        </is>
-      </c>
+      <c r="A61" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Eastern PA / Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="B61" s="17" t="inlineStr">
+        <is>
+          <t>1 item(s)</t>
+        </is>
+      </c>
+      <c r="C61" s="18" t="n"/>
+      <c r="D61" s="18" t="n"/>
+      <c r="E61" s="18" t="n"/>
+      <c r="F61" s="18" t="n"/>
+      <c r="G61" s="18" t="n"/>
+      <c r="H61" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="18" t="n"/>
+      <c r="J61" s="18" t="n"/>
+      <c r="K61" s="18" t="n"/>
+      <c r="L61" s="18" t="n"/>
+      <c r="M61" s="18" t="n"/>
+      <c r="N61" s="18" t="n"/>
+      <c r="O61" s="18" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>▸ Western PA / Ohio Valley  (3)</t>
+        </is>
+      </c>
+      <c r="B62" s="12" t="n"/>
+      <c r="C62" s="12" t="n"/>
+      <c r="D62" s="12" t="n"/>
+      <c r="E62" s="12" t="n"/>
+      <c r="F62" s="12" t="n"/>
+      <c r="G62" s="12" t="n"/>
+      <c r="H62" s="12" t="n"/>
+      <c r="I62" s="12" t="n"/>
+      <c r="J62" s="12" t="n"/>
+      <c r="K62" s="12" t="n"/>
+      <c r="L62" s="12" t="n"/>
+      <c r="M62" s="12" t="n"/>
+      <c r="N62" s="12" t="n"/>
+      <c r="O62" s="12" t="n"/>
     </row>
     <row r="63" outlineLevel="1">
       <c r="A63" s="13" t="inlineStr">
         <is>
-          <t>Eastern PA / Mid-Atlantic</t>
+          <t>Western PA / Ohio Valley</t>
         </is>
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>October restaurant consignment – Hobart, Rational, True + NEW scratch-and-dent Migali/Avantco</t>
+          <t>Petrunak's Hardware Store liquidation Day 1 (530 lots: doors, hardware, tools, building supplies)</t>
         </is>
       </c>
       <c r="C63" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>store closing auction</t>
         </is>
       </c>
       <c r="D63" s="13" t="inlineStr">
         <is>
-          <t>Harrisburg</t>
+          <t>Windber</t>
         </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
@@ -22017,23 +21939,27 @@
         </is>
       </c>
       <c r="F63" s="13" t="n">
-        <v>340</v>
+        <v>437</v>
       </c>
       <c r="G63" s="13" t="inlineStr">
         <is>
-          <t>Online auction, 15% BP, ships $55/pallet</t>
+          <t>Timed online auction (530 lots)</t>
         </is>
       </c>
       <c r="H63" s="15" t="n"/>
-      <c r="I63" s="13" t="inlineStr"/>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="J63" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 11:00 AM ET</t>
+          <t>2026-10-21 08:00 PM ET</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
         <is>
-          <t>Restaurant Auction Co</t>
+          <t>Carey Auctions</t>
         </is>
       </c>
       <c r="L63" s="20" t="inlineStr">
@@ -22049,236 +21975,232 @@
       </c>
       <c r="O63" s="14" t="inlineStr">
         <is>
-          <t>Closes Oct 21 10 or 11 AM (later used). Shippable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Eastern PA / Mid-Atlantic</t>
-        </is>
-      </c>
-      <c r="B64" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C64" s="18" t="n"/>
-      <c r="D64" s="18" t="n"/>
-      <c r="E64" s="18" t="n"/>
-      <c r="F64" s="18" t="n"/>
-      <c r="G64" s="18" t="n"/>
-      <c r="H64" s="19" t="n">
+          <t>Ends Oct 21 7 PM CDT (8 PM ET). 1500 Somerset Ave, Windber PA. Pickups Oct 24-28. Hardware store, not appliance parts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" outlineLevel="1">
+      <c r="A64" s="13" t="inlineStr">
+        <is>
+          <t>Western PA / Ohio Valley</t>
+        </is>
+      </c>
+      <c r="B64" s="14" t="inlineStr">
+        <is>
+          <t>Petrunak's Hardware Store liquidation Day 2 (433 lots)</t>
+        </is>
+      </c>
+      <c r="C64" s="13" t="inlineStr">
+        <is>
+          <t>store closing auction</t>
+        </is>
+      </c>
+      <c r="D64" s="13" t="inlineStr">
+        <is>
+          <t>Windber</t>
+        </is>
+      </c>
+      <c r="E64" s="13" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="F64" s="13" t="n">
+        <v>437</v>
+      </c>
+      <c r="G64" s="13" t="inlineStr">
+        <is>
+          <t>Timed online auction (433 lots)</t>
+        </is>
+      </c>
+      <c r="H64" s="15" t="n"/>
+      <c r="I64" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="J64" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-22 08:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>Carey Auctions</t>
+        </is>
+      </c>
+      <c r="L64" s="20" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M64" s="13" t="inlineStr"/>
+      <c r="N64" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O64" s="14" t="inlineStr">
+        <is>
+          <t>Ends Oct 22 7 PM CDT (8 PM ET). Same store as Day 1; pickups Oct 24-28.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" outlineLevel="1">
+      <c r="A65" s="13" t="inlineStr">
+        <is>
+          <t>Western PA / Ohio Valley</t>
+        </is>
+      </c>
+      <c r="B65" s="14" t="inlineStr">
+        <is>
+          <t>Millers Pizza &amp; More – pizza business, commercial kitchen &amp; event space contents (362 lots)</t>
+        </is>
+      </c>
+      <c r="C65" s="13" t="inlineStr">
+        <is>
+          <t>restaurant / commercial kitchen contents</t>
+        </is>
+      </c>
+      <c r="D65" s="13" t="inlineStr">
+        <is>
+          <t>Everson</t>
+        </is>
+      </c>
+      <c r="E65" s="13" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="F65" s="13" t="n">
+        <v>478</v>
+      </c>
+      <c r="G65" s="13" t="inlineStr">
+        <is>
+          <t>Online auction, 15% buyer premium</t>
+        </is>
+      </c>
+      <c r="H65" s="15" t="n"/>
+      <c r="I65" s="13" t="inlineStr"/>
+      <c r="J65" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-25 07:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K65" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (Bid Local LLC)</t>
+        </is>
+      </c>
+      <c r="L65" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M65" s="13" t="inlineStr"/>
+      <c r="N65" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O65" s="14" t="inlineStr">
+        <is>
+          <t>Property of Millers Pizza and More LLC; online-only, 362 lots, lots begin closing Oct 25 7 PM. Pickup Everson PA by appointment Tue 10/27 and Wed 10/28. Building (4,500 sq ft) to be auctioned separately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Western PA / Ohio Valley</t>
+        </is>
+      </c>
+      <c r="B66" s="17" t="inlineStr">
+        <is>
+          <t>3 item(s)</t>
+        </is>
+      </c>
+      <c r="C66" s="18" t="n"/>
+      <c r="D66" s="18" t="n"/>
+      <c r="E66" s="18" t="n"/>
+      <c r="F66" s="18" t="n"/>
+      <c r="G66" s="18" t="n"/>
+      <c r="H66" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I64" s="18" t="n"/>
-      <c r="J64" s="18" t="n"/>
-      <c r="K64" s="18" t="n"/>
-      <c r="L64" s="18" t="n"/>
-      <c r="M64" s="18" t="n"/>
-      <c r="N64" s="18" t="n"/>
-      <c r="O64" s="18" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="11" t="inlineStr">
-        <is>
-          <t>▸ Western PA / Ohio Valley  (3)</t>
-        </is>
-      </c>
-      <c r="B65" s="12" t="n"/>
-      <c r="C65" s="12" t="n"/>
-      <c r="D65" s="12" t="n"/>
-      <c r="E65" s="12" t="n"/>
-      <c r="F65" s="12" t="n"/>
-      <c r="G65" s="12" t="n"/>
-      <c r="H65" s="12" t="n"/>
-      <c r="I65" s="12" t="n"/>
-      <c r="J65" s="12" t="n"/>
-      <c r="K65" s="12" t="n"/>
-      <c r="L65" s="12" t="n"/>
-      <c r="M65" s="12" t="n"/>
-      <c r="N65" s="12" t="n"/>
-      <c r="O65" s="12" t="n"/>
-    </row>
-    <row r="66" outlineLevel="1">
-      <c r="A66" s="13" t="inlineStr">
-        <is>
-          <t>Western PA / Ohio Valley</t>
-        </is>
-      </c>
-      <c r="B66" s="14" t="inlineStr">
-        <is>
-          <t>Petrunak's Hardware Store liquidation Day 1 (530 lots: doors, hardware, tools, building supplies)</t>
-        </is>
-      </c>
-      <c r="C66" s="13" t="inlineStr">
-        <is>
-          <t>store closing auction</t>
-        </is>
-      </c>
-      <c r="D66" s="13" t="inlineStr">
-        <is>
-          <t>Windber</t>
-        </is>
-      </c>
-      <c r="E66" s="13" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="F66" s="13" t="n">
-        <v>437</v>
-      </c>
-      <c r="G66" s="13" t="inlineStr">
-        <is>
-          <t>Timed online auction (530 lots)</t>
-        </is>
-      </c>
-      <c r="H66" s="15" t="n"/>
-      <c r="I66" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="J66" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 08:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K66" s="13" t="inlineStr">
-        <is>
-          <t>Carey Auctions</t>
-        </is>
-      </c>
-      <c r="L66" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M66" s="13" t="inlineStr"/>
-      <c r="N66" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O66" s="14" t="inlineStr">
-        <is>
-          <t>Ends Oct 21 7 PM CDT (8 PM ET). 1500 Somerset Ave, Windber PA. Pickups Oct 24-28. Hardware store, not appliance parts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" outlineLevel="1">
-      <c r="A67" s="13" t="inlineStr">
-        <is>
-          <t>Western PA / Ohio Valley</t>
-        </is>
-      </c>
-      <c r="B67" s="14" t="inlineStr">
-        <is>
-          <t>Petrunak's Hardware Store liquidation Day 2 (433 lots)</t>
-        </is>
-      </c>
-      <c r="C67" s="13" t="inlineStr">
-        <is>
-          <t>store closing auction</t>
-        </is>
-      </c>
-      <c r="D67" s="13" t="inlineStr">
-        <is>
-          <t>Windber</t>
-        </is>
-      </c>
-      <c r="E67" s="13" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="F67" s="13" t="n">
-        <v>437</v>
-      </c>
-      <c r="G67" s="13" t="inlineStr">
-        <is>
-          <t>Timed online auction (433 lots)</t>
-        </is>
-      </c>
-      <c r="H67" s="15" t="n"/>
-      <c r="I67" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="J67" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-22 08:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K67" s="13" t="inlineStr">
-        <is>
-          <t>Carey Auctions</t>
-        </is>
-      </c>
-      <c r="L67" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M67" s="13" t="inlineStr"/>
-      <c r="N67" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O67" s="14" t="inlineStr">
-        <is>
-          <t>Ends Oct 22 7 PM CDT (8 PM ET). Same store as Day 1; pickups Oct 24-28.</t>
-        </is>
-      </c>
+      <c r="I66" s="18" t="n"/>
+      <c r="J66" s="18" t="n"/>
+      <c r="K66" s="18" t="n"/>
+      <c r="L66" s="18" t="n"/>
+      <c r="M66" s="18" t="n"/>
+      <c r="N66" s="18" t="n"/>
+      <c r="O66" s="18" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="11" t="inlineStr">
+        <is>
+          <t>▸ Upstate / Western NY  (1)</t>
+        </is>
+      </c>
+      <c r="B67" s="12" t="n"/>
+      <c r="C67" s="12" t="n"/>
+      <c r="D67" s="12" t="n"/>
+      <c r="E67" s="12" t="n"/>
+      <c r="F67" s="12" t="n"/>
+      <c r="G67" s="12" t="n"/>
+      <c r="H67" s="12" t="n"/>
+      <c r="I67" s="12" t="n"/>
+      <c r="J67" s="12" t="n"/>
+      <c r="K67" s="12" t="n"/>
+      <c r="L67" s="12" t="n"/>
+      <c r="M67" s="12" t="n"/>
+      <c r="N67" s="12" t="n"/>
+      <c r="O67" s="12" t="n"/>
     </row>
     <row r="68" outlineLevel="1">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>Western PA / Ohio Valley</t>
+          <t>Upstate / Western NY</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>Millers Pizza &amp; More – pizza business, commercial kitchen &amp; event space contents (362 lots)</t>
+          <t>Restaurant &amp; fitness equipment</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
         <is>
-          <t>restaurant / commercial kitchen contents</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>Everson</t>
+          <t>Williamsville</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>478</v>
+        <v>408</v>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
-          <t>Online auction, 15% buyer premium</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H68" s="15" t="n"/>
       <c r="I68" s="13" t="inlineStr"/>
       <c r="J68" s="13" t="inlineStr">
         <is>
-          <t>2026-10-25 07:00 PM ET</t>
+          <t>2026-10-26 07:30 PM ET</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Bid Local LLC)</t>
+          <t>Cash Auctions</t>
         </is>
       </c>
       <c r="L68" s="13" t="inlineStr">
@@ -22294,19 +22216,19 @@
       </c>
       <c r="O68" s="14" t="inlineStr">
         <is>
-          <t>Property of Millers Pizza and More LLC; online-only, 362 lots, lots begin closing Oct 25 7 PM. Pickup Everson PA by appointment Tue 10/27 and Wed 10/28. Building (4,500 sq ft) to be auctioned separately.</t>
+          <t>Lots not reviewed.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="17" t="inlineStr">
         <is>
-          <t>Subtotal — Western PA / Ohio Valley</t>
+          <t>Subtotal — Upstate / Western NY</t>
         </is>
       </c>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>3 item(s)</t>
+          <t>1 item(s)</t>
         </is>
       </c>
       <c r="C69" s="18" t="n"/>
@@ -22328,7 +22250,7 @@
     <row r="70">
       <c r="A70" s="11" t="inlineStr">
         <is>
-          <t>▸ Upstate / Western NY  (1)</t>
+          <t>▸ Virginia  (1)</t>
         </is>
       </c>
       <c r="B70" s="12" t="n"/>
@@ -22349,47 +22271,47 @@
     <row r="71" outlineLevel="1">
       <c r="A71" s="13" t="inlineStr">
         <is>
-          <t>Upstate / Western NY</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>Restaurant &amp; fitness equipment</t>
+          <t>Haynes Furniture / The Dump – 12 stores closing (furniture, mattresses)</t>
         </is>
       </c>
       <c r="C71" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>retail GOB</t>
         </is>
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>Williamsville</t>
+          <t>Virginia Beach</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>408</v>
+        <v>456</v>
       </c>
       <c r="G71" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Retail GOB markdowns</t>
         </is>
       </c>
       <c r="H71" s="15" t="n"/>
-      <c r="I71" s="13" t="inlineStr"/>
-      <c r="J71" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-26 07:30 PM ET</t>
-        </is>
-      </c>
+      <c r="I71" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="J71" s="13" t="inlineStr"/>
       <c r="K71" s="13" t="inlineStr">
         <is>
-          <t>Cash Auctions</t>
+          <t>SB360 (PR Newswire)</t>
         </is>
       </c>
       <c r="L71" s="13" t="inlineStr">
@@ -22405,14 +22327,14 @@
       </c>
       <c r="O71" s="14" t="inlineStr">
         <is>
-          <t>Lots not reviewed.</t>
+          <t>Posted Oct 8. Multi-state (VA/AZ/GA/IL/TX); pinned at Virginia Beach. Home goods only.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="17" t="inlineStr">
         <is>
-          <t>Subtotal — Upstate / Western NY</t>
+          <t>Subtotal — Virginia</t>
         </is>
       </c>
       <c r="B72" s="17" t="inlineStr">
@@ -22439,7 +22361,7 @@
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t>▸ Virginia  (1)</t>
+          <t>▸ Midwest  (2)</t>
         </is>
       </c>
       <c r="B73" s="12" t="n"/>
@@ -22460,12 +22382,12 @@
     <row r="74" outlineLevel="1">
       <c r="A74" s="13" t="inlineStr">
         <is>
-          <t>Virginia</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>Haynes Furniture / The Dump – 12 stores closing (furniture, mattresses)</t>
+          <t>American Sale – total liquidation, all 7 stores (pools, hot tubs, grills, holiday decor)</t>
         </is>
       </c>
       <c r="C74" s="13" t="inlineStr">
@@ -22475,32 +22397,32 @@
       </c>
       <c r="D74" s="13" t="inlineStr">
         <is>
-          <t>Virginia Beach</t>
+          <t>Chicagoland</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>456</v>
+        <v>876</v>
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>Retail GOB markdowns</t>
+          <t>Retail GOB, up to 70% off</t>
         </is>
       </c>
       <c r="H74" s="15" t="n"/>
       <c r="I74" s="13" t="inlineStr">
         <is>
-          <t>2026-10-08</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="J74" s="13" t="inlineStr"/>
       <c r="K74" s="13" t="inlineStr">
         <is>
-          <t>SB360 (PR Newswire)</t>
+          <t>Tiger Group (PR Newswire)</t>
         </is>
       </c>
       <c r="L74" s="13" t="inlineStr">
@@ -22516,170 +22438,170 @@
       </c>
       <c r="O74" s="14" t="inlineStr">
         <is>
-          <t>Posted Oct 8. Multi-state (VA/AZ/GA/IL/TX); pinned at Virginia Beach. Home goods only.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Virginia</t>
-        </is>
-      </c>
-      <c r="B75" s="17" t="inlineStr">
-        <is>
-          <t>1 item(s)</t>
-        </is>
-      </c>
-      <c r="C75" s="18" t="n"/>
-      <c r="D75" s="18" t="n"/>
-      <c r="E75" s="18" t="n"/>
-      <c r="F75" s="18" t="n"/>
-      <c r="G75" s="18" t="n"/>
-      <c r="H75" s="19" t="n">
+          <t>Posted Oct 15. Watch for a bulk/fixture auction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" outlineLevel="1">
+      <c r="A75" s="13" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="B75" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant, Bar &amp; DJ Equipment Liquidation: Alto-Shaam combi, Southbend/Blodgett ovens, True refrigeration, Manitowoc, Hobart saw, DJ/AV gear</t>
+        </is>
+      </c>
+      <c r="C75" s="13" t="inlineStr">
+        <is>
+          <t>restaurant liquidation auction</t>
+        </is>
+      </c>
+      <c r="D75" s="13" t="inlineStr">
+        <is>
+          <t>Austin</t>
+        </is>
+      </c>
+      <c r="E75" s="13" t="inlineStr">
+        <is>
+          <t>MN</t>
+        </is>
+      </c>
+      <c r="F75" s="13" t="n">
+        <v>1124</v>
+      </c>
+      <c r="G75" s="13" t="inlineStr">
+        <is>
+          <t>Timed online auction</t>
+        </is>
+      </c>
+      <c r="H75" s="15" t="n"/>
+      <c r="I75" s="13" t="inlineStr"/>
+      <c r="J75" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-26 02:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K75" s="13" t="inlineStr">
+        <is>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L75" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M75" s="13" t="inlineStr"/>
+      <c r="N75" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O75" s="14" t="inlineStr">
+        <is>
+          <t>Begins closing Oct 26 1 PM CDT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Midwest</t>
+        </is>
+      </c>
+      <c r="B76" s="17" t="inlineStr">
+        <is>
+          <t>2 item(s)</t>
+        </is>
+      </c>
+      <c r="C76" s="18" t="n"/>
+      <c r="D76" s="18" t="n"/>
+      <c r="E76" s="18" t="n"/>
+      <c r="F76" s="18" t="n"/>
+      <c r="G76" s="18" t="n"/>
+      <c r="H76" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I75" s="18" t="n"/>
-      <c r="J75" s="18" t="n"/>
-      <c r="K75" s="18" t="n"/>
-      <c r="L75" s="18" t="n"/>
-      <c r="M75" s="18" t="n"/>
-      <c r="N75" s="18" t="n"/>
-      <c r="O75" s="18" t="n"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="11" t="inlineStr">
-        <is>
-          <t>▸ Midwest  (3)</t>
-        </is>
-      </c>
-      <c r="B76" s="12" t="n"/>
-      <c r="C76" s="12" t="n"/>
-      <c r="D76" s="12" t="n"/>
-      <c r="E76" s="12" t="n"/>
-      <c r="F76" s="12" t="n"/>
-      <c r="G76" s="12" t="n"/>
-      <c r="H76" s="12" t="n"/>
-      <c r="I76" s="12" t="n"/>
-      <c r="J76" s="12" t="n"/>
-      <c r="K76" s="12" t="n"/>
-      <c r="L76" s="12" t="n"/>
-      <c r="M76" s="12" t="n"/>
-      <c r="N76" s="12" t="n"/>
-      <c r="O76" s="12" t="n"/>
-    </row>
-    <row r="77" outlineLevel="1">
-      <c r="A77" s="13" t="inlineStr">
-        <is>
-          <t>Midwest</t>
-        </is>
-      </c>
-      <c r="B77" s="14" t="inlineStr">
-        <is>
-          <t>American Sale – total liquidation, all 7 stores (pools, hot tubs, grills, holiday decor)</t>
-        </is>
-      </c>
-      <c r="C77" s="13" t="inlineStr">
-        <is>
-          <t>retail GOB</t>
-        </is>
-      </c>
-      <c r="D77" s="13" t="inlineStr">
-        <is>
-          <t>Chicagoland</t>
-        </is>
-      </c>
-      <c r="E77" s="13" t="inlineStr">
-        <is>
-          <t>IL</t>
-        </is>
-      </c>
-      <c r="F77" s="13" t="n">
-        <v>876</v>
-      </c>
-      <c r="G77" s="13" t="inlineStr">
-        <is>
-          <t>Retail GOB, up to 70% off</t>
-        </is>
-      </c>
-      <c r="H77" s="15" t="n"/>
-      <c r="I77" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="J77" s="13" t="inlineStr"/>
-      <c r="K77" s="13" t="inlineStr">
-        <is>
-          <t>Tiger Group (PR Newswire)</t>
-        </is>
-      </c>
-      <c r="L77" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M77" s="13" t="inlineStr"/>
-      <c r="N77" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O77" s="14" t="inlineStr">
-        <is>
-          <t>Posted Oct 15. Watch for a bulk/fixture auction.</t>
-        </is>
-      </c>
+      <c r="I76" s="18" t="n"/>
+      <c r="J76" s="18" t="n"/>
+      <c r="K76" s="18" t="n"/>
+      <c r="L76" s="18" t="n"/>
+      <c r="M76" s="18" t="n"/>
+      <c r="N76" s="18" t="n"/>
+      <c r="O76" s="18" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t>▸ Texas / South Central  (1)</t>
+        </is>
+      </c>
+      <c r="B77" s="12" t="n"/>
+      <c r="C77" s="12" t="n"/>
+      <c r="D77" s="12" t="n"/>
+      <c r="E77" s="12" t="n"/>
+      <c r="F77" s="12" t="n"/>
+      <c r="G77" s="12" t="n"/>
+      <c r="H77" s="12" t="n"/>
+      <c r="I77" s="12" t="n"/>
+      <c r="J77" s="12" t="n"/>
+      <c r="K77" s="12" t="n"/>
+      <c r="L77" s="12" t="n"/>
+      <c r="M77" s="12" t="n"/>
+      <c r="N77" s="12" t="n"/>
+      <c r="O77" s="12" t="n"/>
     </row>
     <row r="78" outlineLevel="1">
       <c r="A78" s="13" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>Texas / South Central</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>Straub's Fine Foods store equipment – bakery, kitchen, meat room, Hussmann refrigeration</t>
+          <t>Southwest beverage distributor surplus – mostly unused: 16 True merchandisers, 75 Bunn brewers, 100+ micro-market kiosks</t>
         </is>
       </c>
       <c r="C78" s="13" t="inlineStr">
         <is>
-          <t>grocery/restaurant</t>
+          <t>distributor surplus</t>
         </is>
       </c>
       <c r="D78" s="13" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Mesquite</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="F78" s="13" t="n">
-        <v>1046</v>
+        <v>1547</v>
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
-          <t>Online auction (18% BP)</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H78" s="15" t="n"/>
       <c r="I78" s="13" t="inlineStr"/>
       <c r="J78" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 11:00 AM ET</t>
+          <t>2026-11-13 11:00 AM ET</t>
         </is>
       </c>
       <c r="K78" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L78" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Heritage Global Partners</t>
+        </is>
+      </c>
+      <c r="L78" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M78" s="13" t="inlineStr"/>
@@ -22690,324 +22612,150 @@
       </c>
       <c r="O78" s="14" t="inlineStr">
         <is>
-          <t>Kingshighway store: Revent double-rack oven + proofer, Reed revolving oven, Vulcan convection, Groen kettle, Southbend 6-burner, Pitco fryer, Stero dishwasher, Hobart saw/grinders, Berkel slicers, Hussmann cases + compressor racks, walk-ins, Hoshizaki/Scotsman ice machines, Crown pallet jack. Preview Oct 20 3–6 PM CDT; pickup in St. Louis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" outlineLevel="1">
-      <c r="A79" s="13" t="inlineStr">
-        <is>
-          <t>Midwest</t>
-        </is>
-      </c>
-      <c r="B79" s="14" t="inlineStr">
-        <is>
-          <t>Restaurant, Bar &amp; DJ Equipment Liquidation: Alto-Shaam combi, Southbend/Blodgett ovens, True refrigeration, Manitowoc, Hobart saw, DJ/AV gear</t>
-        </is>
-      </c>
-      <c r="C79" s="13" t="inlineStr">
-        <is>
-          <t>restaurant liquidation auction</t>
-        </is>
-      </c>
-      <c r="D79" s="13" t="inlineStr">
-        <is>
-          <t>Austin</t>
-        </is>
-      </c>
-      <c r="E79" s="13" t="inlineStr">
-        <is>
-          <t>MN</t>
-        </is>
-      </c>
-      <c r="F79" s="13" t="n">
-        <v>1124</v>
-      </c>
-      <c r="G79" s="13" t="inlineStr">
-        <is>
-          <t>Timed online auction</t>
-        </is>
-      </c>
-      <c r="H79" s="15" t="n"/>
-      <c r="I79" s="13" t="inlineStr"/>
-      <c r="J79" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-26 02:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K79" s="13" t="inlineStr">
-        <is>
-          <t>Grafe Auction</t>
-        </is>
-      </c>
-      <c r="L79" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M79" s="13" t="inlineStr"/>
-      <c r="N79" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O79" s="14" t="inlineStr">
-        <is>
-          <t>Begins closing Oct 26 1 PM CDT.</t>
-        </is>
-      </c>
+          <t>Near-new appliances, resell by unit. Nov 13 10 AM CST.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Texas / South Central</t>
+        </is>
+      </c>
+      <c r="B79" s="17" t="inlineStr">
+        <is>
+          <t>1 item(s)</t>
+        </is>
+      </c>
+      <c r="C79" s="18" t="n"/>
+      <c r="D79" s="18" t="n"/>
+      <c r="E79" s="18" t="n"/>
+      <c r="F79" s="18" t="n"/>
+      <c r="G79" s="18" t="n"/>
+      <c r="H79" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="18" t="n"/>
+      <c r="J79" s="18" t="n"/>
+      <c r="K79" s="18" t="n"/>
+      <c r="L79" s="18" t="n"/>
+      <c r="M79" s="18" t="n"/>
+      <c r="N79" s="18" t="n"/>
+      <c r="O79" s="18" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Midwest</t>
-        </is>
-      </c>
-      <c r="B80" s="17" t="inlineStr">
-        <is>
-          <t>3 item(s)</t>
-        </is>
-      </c>
-      <c r="C80" s="18" t="n"/>
-      <c r="D80" s="18" t="n"/>
-      <c r="E80" s="18" t="n"/>
-      <c r="F80" s="18" t="n"/>
-      <c r="G80" s="18" t="n"/>
-      <c r="H80" s="19" t="n">
+      <c r="A80" s="11" t="inlineStr">
+        <is>
+          <t>▸ West / Other  (1)</t>
+        </is>
+      </c>
+      <c r="B80" s="12" t="n"/>
+      <c r="C80" s="12" t="n"/>
+      <c r="D80" s="12" t="n"/>
+      <c r="E80" s="12" t="n"/>
+      <c r="F80" s="12" t="n"/>
+      <c r="G80" s="12" t="n"/>
+      <c r="H80" s="12" t="n"/>
+      <c r="I80" s="12" t="n"/>
+      <c r="J80" s="12" t="n"/>
+      <c r="K80" s="12" t="n"/>
+      <c r="L80" s="12" t="n"/>
+      <c r="M80" s="12" t="n"/>
+      <c r="N80" s="12" t="n"/>
+      <c r="O80" s="12" t="n"/>
+    </row>
+    <row r="81" outlineLevel="1">
+      <c r="A81" s="13" t="inlineStr">
+        <is>
+          <t>West / Other</t>
+        </is>
+      </c>
+      <c r="B81" s="14" t="inlineStr">
+        <is>
+          <t>National salad concept liquidation – full contents of 63 fast-casual restaurants (AZ/TX/OK/NV)</t>
+        </is>
+      </c>
+      <c r="C81" s="13" t="inlineStr">
+        <is>
+          <t>restaurant chain liquidation</t>
+        </is>
+      </c>
+      <c r="D81" s="13" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="E81" s="13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="F81" s="13" t="n">
+        <v>2307</v>
+      </c>
+      <c r="G81" s="13" t="inlineStr">
+        <is>
+          <t>Online auctions, dates TBD</t>
+        </is>
+      </c>
+      <c r="H81" s="15" t="n"/>
+      <c r="I81" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="J81" s="13" t="inlineStr"/>
+      <c r="K81" s="13" t="inlineStr">
+        <is>
+          <t>RestaurantEquipment.bid (TAGeX)</t>
+        </is>
+      </c>
+      <c r="L81" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M81" s="13" t="inlineStr"/>
+      <c r="N81" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O81" s="14" t="inlineStr">
+        <is>
+          <t>Rolling market-by-market auctions, none live yet (Phoenix metro 30 locations, DFW 14, Tucson 6, Houston 5, plus OK/NV). Pickup on site at each restaurant. Pinned at Phoenix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — West / Other</t>
+        </is>
+      </c>
+      <c r="B82" s="17" t="inlineStr">
+        <is>
+          <t>1 item(s)</t>
+        </is>
+      </c>
+      <c r="C82" s="18" t="n"/>
+      <c r="D82" s="18" t="n"/>
+      <c r="E82" s="18" t="n"/>
+      <c r="F82" s="18" t="n"/>
+      <c r="G82" s="18" t="n"/>
+      <c r="H82" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I80" s="18" t="n"/>
-      <c r="J80" s="18" t="n"/>
-      <c r="K80" s="18" t="n"/>
-      <c r="L80" s="18" t="n"/>
-      <c r="M80" s="18" t="n"/>
-      <c r="N80" s="18" t="n"/>
-      <c r="O80" s="18" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" s="11" t="inlineStr">
-        <is>
-          <t>▸ Texas / South Central  (1)</t>
-        </is>
-      </c>
-      <c r="B81" s="12" t="n"/>
-      <c r="C81" s="12" t="n"/>
-      <c r="D81" s="12" t="n"/>
-      <c r="E81" s="12" t="n"/>
-      <c r="F81" s="12" t="n"/>
-      <c r="G81" s="12" t="n"/>
-      <c r="H81" s="12" t="n"/>
-      <c r="I81" s="12" t="n"/>
-      <c r="J81" s="12" t="n"/>
-      <c r="K81" s="12" t="n"/>
-      <c r="L81" s="12" t="n"/>
-      <c r="M81" s="12" t="n"/>
-      <c r="N81" s="12" t="n"/>
-      <c r="O81" s="12" t="n"/>
-    </row>
-    <row r="82" outlineLevel="1">
-      <c r="A82" s="13" t="inlineStr">
-        <is>
-          <t>Texas / South Central</t>
-        </is>
-      </c>
-      <c r="B82" s="14" t="inlineStr">
-        <is>
-          <t>Southwest beverage distributor surplus – mostly unused: 16 True merchandisers, 75 Bunn brewers, 100+ micro-market kiosks</t>
-        </is>
-      </c>
-      <c r="C82" s="13" t="inlineStr">
-        <is>
-          <t>distributor surplus</t>
-        </is>
-      </c>
-      <c r="D82" s="13" t="inlineStr">
-        <is>
-          <t>Mesquite</t>
-        </is>
-      </c>
-      <c r="E82" s="13" t="inlineStr">
-        <is>
-          <t>TX</t>
-        </is>
-      </c>
-      <c r="F82" s="13" t="n">
-        <v>1547</v>
-      </c>
-      <c r="G82" s="13" t="inlineStr">
-        <is>
-          <t>Online auction</t>
-        </is>
-      </c>
-      <c r="H82" s="15" t="n"/>
-      <c r="I82" s="13" t="inlineStr"/>
-      <c r="J82" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-13 11:00 AM ET</t>
-        </is>
-      </c>
-      <c r="K82" s="13" t="inlineStr">
-        <is>
-          <t>Heritage Global Partners</t>
-        </is>
-      </c>
-      <c r="L82" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M82" s="13" t="inlineStr"/>
-      <c r="N82" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O82" s="14" t="inlineStr">
-        <is>
-          <t>Near-new appliances, resell by unit. Nov 13 10 AM CST.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Texas / South Central</t>
-        </is>
-      </c>
-      <c r="B83" s="17" t="inlineStr">
-        <is>
-          <t>1 item(s)</t>
-        </is>
-      </c>
-      <c r="C83" s="18" t="n"/>
-      <c r="D83" s="18" t="n"/>
-      <c r="E83" s="18" t="n"/>
-      <c r="F83" s="18" t="n"/>
-      <c r="G83" s="18" t="n"/>
-      <c r="H83" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" s="18" t="n"/>
-      <c r="J83" s="18" t="n"/>
-      <c r="K83" s="18" t="n"/>
-      <c r="L83" s="18" t="n"/>
-      <c r="M83" s="18" t="n"/>
-      <c r="N83" s="18" t="n"/>
-      <c r="O83" s="18" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="11" t="inlineStr">
-        <is>
-          <t>▸ West / Other  (1)</t>
-        </is>
-      </c>
-      <c r="B84" s="12" t="n"/>
-      <c r="C84" s="12" t="n"/>
-      <c r="D84" s="12" t="n"/>
-      <c r="E84" s="12" t="n"/>
-      <c r="F84" s="12" t="n"/>
-      <c r="G84" s="12" t="n"/>
-      <c r="H84" s="12" t="n"/>
-      <c r="I84" s="12" t="n"/>
-      <c r="J84" s="12" t="n"/>
-      <c r="K84" s="12" t="n"/>
-      <c r="L84" s="12" t="n"/>
-      <c r="M84" s="12" t="n"/>
-      <c r="N84" s="12" t="n"/>
-      <c r="O84" s="12" t="n"/>
-    </row>
-    <row r="85" outlineLevel="1">
-      <c r="A85" s="13" t="inlineStr">
-        <is>
-          <t>West / Other</t>
-        </is>
-      </c>
-      <c r="B85" s="14" t="inlineStr">
-        <is>
-          <t>National salad concept liquidation – full contents of 63 fast-casual restaurants (AZ/TX/OK/NV)</t>
-        </is>
-      </c>
-      <c r="C85" s="13" t="inlineStr">
-        <is>
-          <t>restaurant chain liquidation</t>
-        </is>
-      </c>
-      <c r="D85" s="13" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="E85" s="13" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="F85" s="13" t="n">
-        <v>2307</v>
-      </c>
-      <c r="G85" s="13" t="inlineStr">
-        <is>
-          <t>Online auctions, dates TBD</t>
-        </is>
-      </c>
-      <c r="H85" s="15" t="n"/>
-      <c r="I85" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="J85" s="13" t="inlineStr"/>
-      <c r="K85" s="13" t="inlineStr">
-        <is>
-          <t>RestaurantEquipment.bid (TAGeX)</t>
-        </is>
-      </c>
-      <c r="L85" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M85" s="13" t="inlineStr"/>
-      <c r="N85" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O85" s="14" t="inlineStr">
-        <is>
-          <t>Rolling market-by-market auctions, none live yet (Phoenix metro 30 locations, DFW 14, Tucson 6, Houston 5, plus OK/NV). Pickup on site at each restaurant. Pinned at Phoenix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — West / Other</t>
-        </is>
-      </c>
-      <c r="B86" s="17" t="inlineStr">
-        <is>
-          <t>1 item(s)</t>
-        </is>
-      </c>
-      <c r="C86" s="18" t="n"/>
-      <c r="D86" s="18" t="n"/>
-      <c r="E86" s="18" t="n"/>
-      <c r="F86" s="18" t="n"/>
-      <c r="G86" s="18" t="n"/>
-      <c r="H86" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="18" t="n"/>
-      <c r="J86" s="18" t="n"/>
-      <c r="K86" s="18" t="n"/>
-      <c r="L86" s="18" t="n"/>
-      <c r="M86" s="18" t="n"/>
-      <c r="N86" s="18" t="n"/>
-      <c r="O86" s="18" t="n"/>
+      <c r="I82" s="18" t="n"/>
+      <c r="J82" s="18" t="n"/>
+      <c r="K82" s="18" t="n"/>
+      <c r="L82" s="18" t="n"/>
+      <c r="M82" s="18" t="n"/>
+      <c r="N82" s="18" t="n"/>
+      <c r="O82" s="18" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O86"/>
+  <autoFilter ref="A1:O82"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId2"/>
@@ -23054,20 +22802,16 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N62" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N66" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N67" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N68" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N71" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N74" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N77" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N78" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N79" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N82" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N85" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N60" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N64" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N65" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N68" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N71" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N74" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N75" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N78" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N81" r:id="rId55"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23079,7 +22823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -23241,7 +22985,7 @@
       </c>
       <c r="O2" s="14" t="inlineStr">
         <is>
-          <t>Integrity Auction House. Internet bidding closes Mon Oct 19 9:18 PM ET. $50 high bid (1 bid) as of 2026-10-18. [Closed Oct 19; HiBid price realized $50.] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Integrity Auction House. Internet bidding closes Mon Oct 19 9:18 PM ET. $50 high bid (1 bid) as of 2026-10-18. [Closed Oct 19; HiBid price realized $50.] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23304,7 +23048,7 @@
       </c>
       <c r="O3" s="14" t="inlineStr">
         <is>
-          <t>Live auction Mon Oct 19 4 PM, 3457 Wilmington Rd. Few bulk parts. [Live auction held Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Live auction Mon Oct 19 4 PM, 3457 Wilmington Rd. Few bulk parts. [Live auction held Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23505,7 +23249,7 @@
       </c>
       <c r="O6" s="14" t="inlineStr">
         <is>
-          <t>Condition: Pre-Owned. FLIP: SO36U/S tested, auction $99/0 bids, pickup only; rough resale $600-1k (eBay card shows no city; pickup distance in source.) Ends Oct 18 ~2:19 PM per eBay card (time zone uncertain; could be earlier). [auto-removed 2026-10-18: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Condition: Pre-Owned. FLIP: SO36U/S tested, auction $99/0 bids, pickup only; rough resale $600-1k (eBay card shows no city; pickup distance in source.) Ends Oct 18 ~2:19 PM per eBay card (time zone uncertain; could be earlier). [auto-removed 2026-10-18: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23570,7 +23314,7 @@
       </c>
       <c r="O7" s="14" t="inlineStr">
         <is>
-          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf) HiBid lot closed/sold ~$37.50 on 2026-10-18. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf) HiBid lot closed/sold ~$37.50 on 2026-10-18. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23635,7 +23379,7 @@
       </c>
       <c r="O8" s="14" t="inlineStr">
         <is>
-          <t>Lots close from Oct 19 2 PM ET. [HiBid catalog closed 2 PM ET Oct 19.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Lots close from Oct 19 2 PM ET. [HiBid catalog closed 2 PM ET Oct 19.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23700,7 +23444,7 @@
       </c>
       <c r="O9" s="14" t="inlineStr">
         <is>
-          <t>Lots close from Oct 20 2 PM ET. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Lots close from Oct 20 2 PM ET. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23763,7 +23507,7 @@
       </c>
       <c r="O10" s="14" t="inlineStr">
         <is>
-          <t>Tested and new units. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Tested and new units. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23826,59 +23570,59 @@
       </c>
       <c r="O11" s="14" t="inlineStr">
         <is>
-          <t>Pickup Oct 21 only. [Lots began closing 1 PM ET Oct 19; ended.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Pickup Oct 21 only. [Lots began closing 1 PM ET Oct 19; ended.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>NYC / Long Island / NJ</t>
+          <t>Eastern PA / Mid-Atlantic</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Milwaukee / Walmart / hardware store mega auction pt 3</t>
+          <t>October restaurant consignment – Hobart, Rational, True + NEW scratch-and-dent Migali/Avantco</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>Mount Holly</t>
+          <t>Harrisburg</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>254</v>
+        <v>340</v>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>HiBid online auction</t>
+          <t>Online auction, 15% BP, ships $55/pallet</t>
         </is>
       </c>
       <c r="H12" s="15" t="n"/>
       <c r="I12" s="13" t="inlineStr"/>
       <c r="J12" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 06:00 PM ET</t>
+          <t>2026-10-21 11:00 AM ET</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>HiBid</t>
+          <t>Restaurant Auction Co</t>
         </is>
       </c>
       <c r="L12" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 06:00 PM ET)</t>
+          <t>EXPIRED (2026-10-21 11:00 AM ET)</t>
         </is>
       </c>
       <c r="M12" s="13" t="inlineStr"/>
@@ -23889,19 +23633,19 @@
       </c>
       <c r="O12" s="14" t="inlineStr">
         <is>
-          <t>Close Oct 18 or 19 6 PM (later used). [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Closes Oct 21 10 or 11 AM (later used). Shippable. [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>Upstate / Western NY</t>
+          <t>NYC / Long Island / NJ</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>Closed restaurant – coolers, fridges, prep tables</t>
+          <t>Serpico's Pizzeria (lost lease) – Bari ovens, walk-in, Hobart 60qt, Vulcan range</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
@@ -23911,37 +23655,37 @@
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>Palmyra</t>
+          <t>Allenhurst</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>333</v>
+        <v>210</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>HiBid, 15% BP</t>
+          <t>No-reserve online auction</t>
         </is>
       </c>
       <c r="H13" s="15" t="n"/>
       <c r="I13" s="13" t="inlineStr"/>
       <c r="J13" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 07:00 PM ET</t>
+          <t>2026-10-21 11:00 AM ET</t>
         </is>
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>Reynolds Auction Co / HiBid</t>
+          <t>Peter Costanzo / EstateSales.net</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 07:00 PM ET)</t>
+          <t>EXPIRED (2026-10-21 11:00 AM ET)</t>
         </is>
       </c>
       <c r="M13" s="13" t="inlineStr"/>
@@ -23952,38 +23696,38 @@
       </c>
       <c r="O13" s="14" t="inlineStr">
         <is>
-          <t>No new out-of-state bidders. Small. [Ended Oct 19 7 PM.] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Absolute / no reserve. [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="13" t="inlineStr">
         <is>
-          <t>Upstate / Western NY</t>
+          <t>NYC / Long Island / NJ</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Former Taco Del Mar – stainless, warmers, walk-in panels</t>
+          <t>Milwaukee / Walmart / hardware store mega auction pt 3</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>Watson</t>
+          <t>Mount Holly</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
@@ -23994,17 +23738,17 @@
       <c r="I14" s="13" t="inlineStr"/>
       <c r="J14" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 06:00 PM ET</t>
+          <t>2026-10-19 06:00 PM ET</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>Adirondack Asset / HiBid</t>
+          <t>HiBid</t>
         </is>
       </c>
       <c r="L14" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-20 06:00 PM ET)</t>
+          <t>EXPIRED (2026-10-19 06:00 PM ET)</t>
         </is>
       </c>
       <c r="M14" s="13" t="inlineStr"/>
@@ -24015,38 +23759,38 @@
       </c>
       <c r="O14" s="14" t="inlineStr">
         <is>
-          <t>Small lot. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Close Oct 18 or 19 6 PM (later used). [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>NYC / Long Island / NJ</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>Freshway Market whole-grocery liquidation – refrigeration racks, cases, walk-ins, generator</t>
+          <t>Altitude Trampoline Park liquidation – partial: Atosa, TurboChef, stainless</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>facility contents</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Iselin</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>862</v>
+        <v>211</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
@@ -24057,17 +23801,17 @@
       <c r="I15" s="13" t="inlineStr"/>
       <c r="J15" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 11:00 AM ET</t>
+          <t>2026-10-21 11:00 AM ET</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-20 11:00 AM ET)</t>
+          <t>EXPIRED (2026-10-21 11:00 AM ET)</t>
         </is>
       </c>
       <c r="M15" s="13" t="inlineStr"/>
@@ -24078,59 +23822,59 @@
       </c>
       <c r="O15" s="14" t="inlineStr">
         <is>
-          <t>Closes from Oct 20 10 AM CDT. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Some kitchen gear only. [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>Greater Boston / South Shore (&lt;50mi)</t>
+          <t>Upstate / Western NY</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>Closed Best Buy Outlet – pallet racking, Big Joe order pickers, appliance dollies, carts, cages</t>
+          <t>Closed restaurant – coolers, fridges, prep tables</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>store closing fixtures</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>Brockton</t>
+          <t>Palmyra</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>11</v>
+        <v>333</v>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>Racking $40/upright, $80/level; pickers $1,000 OBO</t>
+          <t>HiBid, 15% BP</t>
         </is>
       </c>
       <c r="H16" s="15" t="n"/>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="J16" s="13" t="inlineStr"/>
+      <c r="I16" s="13" t="inlineStr"/>
+      <c r="J16" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 07:00 PM ET</t>
+        </is>
+      </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>Reynolds Auction Co / HiBid</t>
         </is>
       </c>
       <c r="L16" s="13" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>EXPIRED (2026-10-19 07:00 PM ET)</t>
         </is>
       </c>
       <c r="M16" s="13" t="inlineStr"/>
@@ -24141,29 +23885,29 @@
       </c>
       <c r="O16" s="14" t="inlineStr">
         <is>
-          <t>200 Westgate Dr. Fixtures/equipment only, no merchandise. On site daily. CL deleted by author (HTTP 410) as of 2026-10-19 midday recheck.</t>
+          <t>No new out-of-state bidders. Small. [Ended Oct 19 7 PM.] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>NYC / Long Island / NJ</t>
+          <t>Upstate / Western NY</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>Like-new restaurant – steam tables, Coldline, Cleveland cook-and-hold, fryers, True freezers</t>
+          <t>Former Taco Del Mar – stainless, warmers, walk-in panels</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>Staten Island</t>
+          <t>Watson</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
@@ -24172,32 +23916,28 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>203</v>
+        <v>260</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>HiBid online auction</t>
         </is>
       </c>
       <c r="H17" s="15" t="n"/>
-      <c r="I17" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
+      <c r="I17" s="13" t="inlineStr"/>
       <c r="J17" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00 PM ET</t>
+          <t>2026-10-20 06:00 PM ET</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>Adirondack Asset / HiBid</t>
         </is>
       </c>
       <c r="L17" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 01:00 PM ET)</t>
+          <t>EXPIRED (2026-10-20 06:00 PM ET)</t>
         </is>
       </c>
       <c r="M17" s="13" t="inlineStr"/>
@@ -24208,63 +23948,59 @@
       </c>
       <c r="O17" s="14" t="inlineStr">
         <is>
-          <t>"Short notice" auction Mon Oct 19 1 PM. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Small lot. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>NYC / Long Island / NJ</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>Restaurant / pizzeria (contents not described)</t>
+          <t>Freshway Market whole-grocery liquidation – refrigeration racks, cases, walk-ins, generator</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>Berkeley Heights</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>213</v>
+        <v>862</v>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H18" s="15" t="n"/>
-      <c r="I18" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
+      <c r="I18" s="13" t="inlineStr"/>
       <c r="J18" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 02:00 PM ET</t>
+          <t>2026-10-20 11:00 AM ET</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>Grafe Auction</t>
         </is>
       </c>
       <c r="L18" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-20 02:00 PM ET)</t>
+          <t>EXPIRED (2026-10-20 11:00 AM ET)</t>
         </is>
       </c>
       <c r="M18" s="13" t="inlineStr"/>
@@ -24275,63 +24011,59 @@
       </c>
       <c r="O18" s="14" t="inlineStr">
         <is>
-          <t>Tue Oct 20 2 PM. No item description on page. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Closes from Oct 20 10 AM CDT. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>NYC / Long Island / NJ</t>
+          <t>Greater Boston / South Shore (&lt;50mi)</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>High-end deli (contents not described)</t>
+          <t>Closed Best Buy Outlet – pallet racking, Big Joe order pickers, appliance dollies, carts, cages</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>store closing fixtures</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>Manalapan Township</t>
+          <t>Brockton</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>223</v>
+        <v>11</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Racking $40/upright, $80/level; pickers $1,000 OBO</t>
         </is>
       </c>
       <c r="H19" s="15" t="n"/>
       <c r="I19" s="13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="J19" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-19 04:00 PM ET</t>
-        </is>
-      </c>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="J19" s="13" t="inlineStr"/>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L19" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 04:00 PM ET)</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="M19" s="13" t="inlineStr"/>
@@ -24342,12 +24074,276 @@
       </c>
       <c r="O19" s="14" t="inlineStr">
         <is>
-          <t>Mon Oct 19 4 PM. No item description on page. [HiBid shows Bidding Closed, Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>200 Westgate Dr. Fixtures/equipment only, no merchandise. On site daily. CL deleted by author (HTTP 410) as of 2026-10-19 midday recheck.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="inlineStr">
+        <is>
+          <t>Like-new restaurant – steam tables, Coldline, Cleveland cook-and-hold, fryers, True freezers</t>
+        </is>
+      </c>
+      <c r="C20" s="13" t="inlineStr">
+        <is>
+          <t>auction</t>
+        </is>
+      </c>
+      <c r="D20" s="13" t="inlineStr">
+        <is>
+          <t>Staten Island</t>
+        </is>
+      </c>
+      <c r="E20" s="13" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F20" s="13" t="n">
+        <v>203</v>
+      </c>
+      <c r="G20" s="13" t="inlineStr">
+        <is>
+          <t>Live + webcast, 18% BP + 3%</t>
+        </is>
+      </c>
+      <c r="H20" s="15" t="n"/>
+      <c r="I20" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J20" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 01:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K20" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L20" s="13" t="inlineStr">
+        <is>
+          <t>EXPIRED (2026-10-19 01:00 PM ET)</t>
+        </is>
+      </c>
+      <c r="M20" s="13" t="inlineStr"/>
+      <c r="N20" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O20" s="14" t="inlineStr">
+        <is>
+          <t>"Short notice" auction Mon Oct 19 1 PM. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant / pizzeria (contents not described)</t>
+        </is>
+      </c>
+      <c r="C21" s="13" t="inlineStr">
+        <is>
+          <t>restaurant closing</t>
+        </is>
+      </c>
+      <c r="D21" s="13" t="inlineStr">
+        <is>
+          <t>Berkeley Heights</t>
+        </is>
+      </c>
+      <c r="E21" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F21" s="13" t="n">
+        <v>213</v>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>Live + webcast, 18% BP + 3%</t>
+        </is>
+      </c>
+      <c r="H21" s="15" t="n"/>
+      <c r="I21" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J21" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-20 02:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K21" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L21" s="13" t="inlineStr">
+        <is>
+          <t>EXPIRED (2026-10-20 02:00 PM ET)</t>
+        </is>
+      </c>
+      <c r="M21" s="13" t="inlineStr"/>
+      <c r="N21" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O21" s="14" t="inlineStr">
+        <is>
+          <t>Tue Oct 20 2 PM. No item description on page. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="inlineStr">
+        <is>
+          <t>High-end deli (contents not described)</t>
+        </is>
+      </c>
+      <c r="C22" s="13" t="inlineStr">
+        <is>
+          <t>restaurant closing</t>
+        </is>
+      </c>
+      <c r="D22" s="13" t="inlineStr">
+        <is>
+          <t>Manalapan Township</t>
+        </is>
+      </c>
+      <c r="E22" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F22" s="13" t="n">
+        <v>223</v>
+      </c>
+      <c r="G22" s="13" t="inlineStr">
+        <is>
+          <t>Live + webcast, 18% BP + 3%</t>
+        </is>
+      </c>
+      <c r="H22" s="15" t="n"/>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="J22" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19 04:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K22" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L22" s="13" t="inlineStr">
+        <is>
+          <t>EXPIRED (2026-10-19 04:00 PM ET)</t>
+        </is>
+      </c>
+      <c r="M22" s="13" t="inlineStr"/>
+      <c r="N22" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O22" s="14" t="inlineStr">
+        <is>
+          <t>Mon Oct 19 4 PM. No item description on page. [HiBid shows Bidding Closed, Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Straub's Fine Foods store equipment – bakery, kitchen, meat room, Hussmann refrigeration</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>grocery/restaurant</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>St. Louis</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>1046</v>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>Online auction (18% BP)</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="n"/>
+      <c r="I23" s="13" t="inlineStr"/>
+      <c r="J23" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L23" s="13" t="inlineStr">
+        <is>
+          <t>EXPIRED (2026-10-21 11:00 AM ET)</t>
+        </is>
+      </c>
+      <c r="M23" s="13" t="inlineStr"/>
+      <c r="N23" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O23" s="14" t="inlineStr">
+        <is>
+          <t>Kingshighway store: Revent double-rack oven + proofer, Reed revolving oven, Vulcan convection, Groen kettle, Southbend 6-burner, Pitco fryer, Stero dishwasher, Hobart saw/grinders, Berkel slicers, Hussmann cases + compressor racks, walk-ins, Hoshizaki/Scotsman ice machines, Crown pallet jack. Preview Oct 20 3–6 PM CDT; pickup in St. Louis. [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O19"/>
+  <autoFilter ref="A1:O23"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -24367,6 +24363,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lot_recon.xlsx
+++ b/lot_recon.xlsx
@@ -16,12 +16,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Removed" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Appliance Parts'!$A$1:$O$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Appliance Parts'!$A$1:$O$38</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Wolf New'!$A$1:$O$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wolf Used'!$A$1:$O$189</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Wolf Unclear'!$A$1:$O$40</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$82</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Removed'!$A$1:$O$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$90</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Removed'!$A$1:$O$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -88,13 +88,13 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="00C55A11"/>
+      <color rgb="001E8449"/>
       <sz val="10"/>
     </font>
     <font>
       <name val="Calibri"/>
       <b val="1"/>
-      <color rgb="001E8449"/>
+      <color rgb="00C55A11"/>
       <sz val="10"/>
     </font>
   </fonts>
@@ -577,7 +577,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Last updated: 2026-10-21 11:02 ET</t>
+          <t>Last updated: 2026-10-21 14:00 ET</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Active listings: 294 · Removed: 22</t>
+          <t>Active listings: 297 · Removed: 23</t>
         </is>
       </c>
     </row>
@@ -641,13 +641,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="6" t="n">
         <v>454646</v>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>34</v>
@@ -708,7 +708,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="C12" s="6" t="n">
         <v>0</v>
@@ -724,7 +724,7 @@
         </is>
       </c>
       <c r="B13" s="4" t="n">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>1275440.58</v>
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C21" t="n">
         <v>0</v>
@@ -938,14 +938,14 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="6" t="n">
         <v>300</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>50–53</t>
         </is>
       </c>
     </row>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -1004,7 +1004,7 @@
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H23" s="6" t="n">
         <v>64756</v>
@@ -1187,7 +1187,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C29" t="n">
         <v>3</v>
@@ -1202,7 +1202,7 @@
         <v>2</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="6" t="n">
         <v>36005</v>
@@ -1220,10 +1220,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
         <v>0</v>
@@ -1396,7 +1396,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2399,7 +2399,7 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>▸ Midwest  (1)</t>
+          <t>▸ Texas / South Central  (2)</t>
         </is>
       </c>
       <c r="B25" s="12" t="n"/>
@@ -2420,54 +2420,52 @@
     <row r="26" outlineLevel="1">
       <c r="A26" s="13" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>Texas / South Central</t>
         </is>
       </c>
       <c r="B26" s="14" t="inlineStr">
         <is>
-          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Indianapolis)</t>
+          <t>Wholesale Hisense appliance parts – stove &amp; refrigerator parts</t>
         </is>
       </c>
       <c r="C26" s="13" t="inlineStr">
         <is>
-          <t>auction catalog</t>
+          <t>bulk lot</t>
         </is>
       </c>
       <c r="D26" s="13" t="inlineStr">
         <is>
-          <t>Indianapolis</t>
+          <t>Owasso</t>
         </is>
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>816</v>
+        <v>1395</v>
       </c>
       <c r="G26" s="13" t="inlineStr">
         <is>
-          <t>$0–1 openers + 15% BP + $1/lot</t>
-        </is>
-      </c>
-      <c r="H26" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="13" t="inlineStr"/>
-      <c r="J26" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 02:00 PM ET</t>
-        </is>
-      </c>
+          <t>Wholesale (price at sale)</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="n"/>
+      <c r="I26" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="J26" s="13" t="inlineStr"/>
       <c r="K26" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Auctionfuel)</t>
-        </is>
-      </c>
-      <c r="L26" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L26" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M26" s="13" t="inlineStr"/>
@@ -2478,163 +2476,161 @@
       </c>
       <c r="O26" s="14" t="inlineStr">
         <is>
-          <t>Lots close in sequence from Oct 21 2 PM ET.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Midwest</t>
-        </is>
-      </c>
-      <c r="B27" s="17" t="inlineStr">
-        <is>
-          <t>1 item(s)</t>
-        </is>
-      </c>
-      <c r="C27" s="18" t="n"/>
-      <c r="D27" s="18" t="n"/>
-      <c r="E27" s="18" t="n"/>
-      <c r="F27" s="18" t="n"/>
-      <c r="G27" s="18" t="n"/>
-      <c r="H27" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="18" t="n"/>
-      <c r="J27" s="18" t="n"/>
-      <c r="K27" s="18" t="n"/>
-      <c r="L27" s="18" t="n"/>
-      <c r="M27" s="18" t="n"/>
-      <c r="N27" s="18" t="n"/>
-      <c r="O27" s="18" t="n"/>
+          <t>Updated 2026-10-12. Seller says LOCAL BUYERS ONLY, out-of-area excluded, cash pickup.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" outlineLevel="1">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Texas / South Central</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>Huge bulk lot appliance parts – ~2 trailer loads, GE/Whirlpool/Maytag</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>bulk lot</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Abilene</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>TX</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>1714</v>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>$5,001</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="n">
+        <v>5001</v>
+      </c>
+      <c r="I27" s="13" t="inlineStr"/>
+      <c r="J27" s="13" t="inlineStr"/>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>Geebo</t>
+        </is>
+      </c>
+      <c r="L27" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M27" s="13" t="inlineStr"/>
+      <c r="N27" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O27" s="14" t="inlineStr">
+        <is>
+          <t>Post date unclear (may be older). Pickup only. User already messaged seller.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>▸ Texas / South Central  (2)</t>
-        </is>
-      </c>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="12" t="n"/>
-      <c r="G28" s="12" t="n"/>
-      <c r="H28" s="12" t="n"/>
-      <c r="I28" s="12" t="n"/>
-      <c r="J28" s="12" t="n"/>
-      <c r="K28" s="12" t="n"/>
-      <c r="L28" s="12" t="n"/>
-      <c r="M28" s="12" t="n"/>
-      <c r="N28" s="12" t="n"/>
-      <c r="O28" s="12" t="n"/>
-    </row>
-    <row r="29" outlineLevel="1">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>Texas / South Central</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>Wholesale Hisense appliance parts – stove &amp; refrigerator parts</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>bulk lot</t>
-        </is>
-      </c>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
-          <t>Owasso</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F29" s="13" t="n">
-        <v>1395</v>
-      </c>
-      <c r="G29" s="13" t="inlineStr">
-        <is>
-          <t>Wholesale (price at sale)</t>
-        </is>
-      </c>
-      <c r="H29" s="15" t="n"/>
-      <c r="I29" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="J29" s="13" t="inlineStr"/>
-      <c r="K29" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L29" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M29" s="13" t="inlineStr"/>
-      <c r="N29" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O29" s="14" t="inlineStr">
-        <is>
-          <t>Updated 2026-10-12. Seller says LOCAL BUYERS ONLY, out-of-area excluded, cash pickup.</t>
-        </is>
-      </c>
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Texas / South Central</t>
+        </is>
+      </c>
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>2 item(s)</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="18" t="n"/>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="18" t="n"/>
+      <c r="G28" s="18" t="n"/>
+      <c r="H28" s="19" t="n">
+        <v>5001</v>
+      </c>
+      <c r="I28" s="18" t="n"/>
+      <c r="J28" s="18" t="n"/>
+      <c r="K28" s="18" t="n"/>
+      <c r="L28" s="18" t="n"/>
+      <c r="M28" s="18" t="n"/>
+      <c r="N28" s="18" t="n"/>
+      <c r="O28" s="18" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>▸ California  (2)</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="12" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="12" t="n"/>
+      <c r="M29" s="12" t="n"/>
+      <c r="N29" s="12" t="n"/>
+      <c r="O29" s="12" t="n"/>
     </row>
     <row r="30" outlineLevel="1">
       <c r="A30" s="13" t="inlineStr">
         <is>
-          <t>Texas / South Central</t>
+          <t>California</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>Huge bulk lot appliance parts – ~2 trailer loads, GE/Whirlpool/Maytag</t>
+          <t>Appliance repair company for sale (incl. parts inventory)</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>bulk lot</t>
+          <t>business sale</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>Abilene</t>
+          <t>Escondido</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>1714</v>
+        <v>2575</v>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>$5,001</t>
+          <t>$40,000</t>
         </is>
       </c>
       <c r="H30" s="15" t="n">
-        <v>5001</v>
+        <v>40000</v>
       </c>
       <c r="I30" s="13" t="inlineStr"/>
       <c r="J30" s="13" t="inlineStr"/>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>Geebo</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L30" s="13" t="inlineStr">
@@ -2650,159 +2646,163 @@
       </c>
       <c r="O30" s="14" t="inlineStr">
         <is>
-          <t>Post date unclear (may be older). Pickup only. User already messaged seller.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Texas / South Central</t>
-        </is>
-      </c>
-      <c r="B31" s="17" t="inlineStr">
+          <t>Whole business sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" outlineLevel="1">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>California</t>
+        </is>
+      </c>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>Coin-op Whirlpool washer &amp; dryer parts (late 80s–mid 90s) – OEM parts, 40+ coin boxes, consoles, 12 transmissions</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>bulk lot</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>Chico</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>CA</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="n">
+        <v>2629</v>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>$1,000</t>
+        </is>
+      </c>
+      <c r="H31" s="15" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="J31" s="13" t="inlineStr"/>
+      <c r="K31" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L31" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M31" s="13" t="inlineStr"/>
+      <c r="N31" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O31" s="14" t="inlineStr">
+        <is>
+          <t>Retired laundry-route owner (35 yrs). Calls only, no shipping, pickup in Chico. No motors or pumps. Niche older coin-op parts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — California</t>
+        </is>
+      </c>
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>2 item(s)</t>
         </is>
       </c>
-      <c r="C31" s="18" t="n"/>
-      <c r="D31" s="18" t="n"/>
-      <c r="E31" s="18" t="n"/>
-      <c r="F31" s="18" t="n"/>
-      <c r="G31" s="18" t="n"/>
-      <c r="H31" s="19" t="n">
-        <v>5001</v>
-      </c>
-      <c r="I31" s="18" t="n"/>
-      <c r="J31" s="18" t="n"/>
-      <c r="K31" s="18" t="n"/>
-      <c r="L31" s="18" t="n"/>
-      <c r="M31" s="18" t="n"/>
-      <c r="N31" s="18" t="n"/>
-      <c r="O31" s="18" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="11" t="inlineStr">
-        <is>
-          <t>▸ California  (2)</t>
-        </is>
-      </c>
-      <c r="B32" s="12" t="n"/>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="12" t="n"/>
-      <c r="E32" s="12" t="n"/>
-      <c r="F32" s="12" t="n"/>
-      <c r="G32" s="12" t="n"/>
-      <c r="H32" s="12" t="n"/>
-      <c r="I32" s="12" t="n"/>
-      <c r="J32" s="12" t="n"/>
-      <c r="K32" s="12" t="n"/>
-      <c r="L32" s="12" t="n"/>
-      <c r="M32" s="12" t="n"/>
-      <c r="N32" s="12" t="n"/>
-      <c r="O32" s="12" t="n"/>
-    </row>
-    <row r="33" outlineLevel="1">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>California</t>
-        </is>
-      </c>
-      <c r="B33" s="14" t="inlineStr">
-        <is>
-          <t>Appliance repair company for sale (incl. parts inventory)</t>
-        </is>
-      </c>
-      <c r="C33" s="13" t="inlineStr">
-        <is>
-          <t>business sale</t>
-        </is>
-      </c>
-      <c r="D33" s="13" t="inlineStr">
-        <is>
-          <t>Escondido</t>
-        </is>
-      </c>
-      <c r="E33" s="13" t="inlineStr">
-        <is>
-          <t>CA</t>
-        </is>
-      </c>
-      <c r="F33" s="13" t="n">
-        <v>2575</v>
-      </c>
-      <c r="G33" s="13" t="inlineStr">
-        <is>
-          <t>$40,000</t>
-        </is>
-      </c>
-      <c r="H33" s="15" t="n">
-        <v>40000</v>
-      </c>
-      <c r="I33" s="13" t="inlineStr"/>
-      <c r="J33" s="13" t="inlineStr"/>
-      <c r="K33" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L33" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M33" s="13" t="inlineStr"/>
-      <c r="N33" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O33" s="14" t="inlineStr">
-        <is>
-          <t>Whole business sale.</t>
-        </is>
-      </c>
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="18" t="n"/>
+      <c r="E32" s="18" t="n"/>
+      <c r="F32" s="18" t="n"/>
+      <c r="G32" s="18" t="n"/>
+      <c r="H32" s="19" t="n">
+        <v>41000</v>
+      </c>
+      <c r="I32" s="18" t="n"/>
+      <c r="J32" s="18" t="n"/>
+      <c r="K32" s="18" t="n"/>
+      <c r="L32" s="18" t="n"/>
+      <c r="M32" s="18" t="n"/>
+      <c r="N32" s="18" t="n"/>
+      <c r="O32" s="18" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="inlineStr">
+        <is>
+          <t>▸ West / Other  (4)</t>
+        </is>
+      </c>
+      <c r="B33" s="12" t="n"/>
+      <c r="C33" s="12" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="12" t="n"/>
+      <c r="G33" s="12" t="n"/>
+      <c r="H33" s="12" t="n"/>
+      <c r="I33" s="12" t="n"/>
+      <c r="J33" s="12" t="n"/>
+      <c r="K33" s="12" t="n"/>
+      <c r="L33" s="12" t="n"/>
+      <c r="M33" s="12" t="n"/>
+      <c r="N33" s="12" t="n"/>
+      <c r="O33" s="12" t="n"/>
     </row>
     <row r="34" outlineLevel="1">
       <c r="A34" s="13" t="inlineStr">
         <is>
-          <t>California</t>
+          <t>West / Other</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>Coin-op Whirlpool washer &amp; dryer parts (late 80s–mid 90s) – OEM parts, 40+ coin boxes, consoles, 12 transmissions</t>
+          <t>Appliance service business for sale (Western Slope) - established warranty-servicer setups with many manufacturers</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>bulk lot</t>
+          <t>business for sale</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>Chico</t>
+          <t>Montrose</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>2629</v>
+        <v>1954</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t>$1,000</t>
+          <t>$110,000</t>
         </is>
       </c>
       <c r="H34" s="15" t="n">
-        <v>1000</v>
+        <v>110000</v>
       </c>
       <c r="I34" s="13" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="J34" s="13" t="inlineStr"/>
@@ -2824,57 +2824,133 @@
       </c>
       <c r="O34" s="14" t="inlineStr">
         <is>
-          <t>Retired laundry-route owner (35 yrs). Calls only, no shipping, pickup in Chico. No motors or pumps. Niche older coin-op parts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — California</t>
-        </is>
-      </c>
-      <c r="B35" s="17" t="inlineStr">
-        <is>
-          <t>2 item(s)</t>
-        </is>
-      </c>
-      <c r="C35" s="18" t="n"/>
-      <c r="D35" s="18" t="n"/>
-      <c r="E35" s="18" t="n"/>
-      <c r="F35" s="18" t="n"/>
-      <c r="G35" s="18" t="n"/>
-      <c r="H35" s="19" t="n">
-        <v>41000</v>
-      </c>
-      <c r="I35" s="18" t="n"/>
-      <c r="J35" s="18" t="n"/>
-      <c r="K35" s="18" t="n"/>
-      <c r="L35" s="18" t="n"/>
-      <c r="M35" s="18" t="n"/>
-      <c r="N35" s="18" t="n"/>
-      <c r="O35" s="18" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
-        <is>
-          <t>▸ West / Other  (4)</t>
-        </is>
-      </c>
-      <c r="B36" s="12" t="n"/>
-      <c r="C36" s="12" t="n"/>
-      <c r="D36" s="12" t="n"/>
-      <c r="E36" s="12" t="n"/>
-      <c r="F36" s="12" t="n"/>
-      <c r="G36" s="12" t="n"/>
-      <c r="H36" s="12" t="n"/>
-      <c r="I36" s="12" t="n"/>
-      <c r="J36" s="12" t="n"/>
-      <c r="K36" s="12" t="n"/>
-      <c r="L36" s="12" t="n"/>
-      <c r="M36" s="12" t="n"/>
-      <c r="N36" s="12" t="n"/>
-      <c r="O36" s="12" t="n"/>
+          <t>Going-concern service business; possible seller financing; no parts inventory mentioned. Updated 2026-10-17.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" outlineLevel="1">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>West / Other</t>
+        </is>
+      </c>
+      <c r="B35" s="14" t="inlineStr">
+        <is>
+          <t>Appliance Repair Technicians: Own the Business - $65K parts inventory/stock + $25K FF&amp;E + 2022 Promaster van</t>
+        </is>
+      </c>
+      <c r="C35" s="13" t="inlineStr">
+        <is>
+          <t>business for sale</t>
+        </is>
+      </c>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>Salt Lake City</t>
+        </is>
+      </c>
+      <c r="E35" s="13" t="inlineStr">
+        <is>
+          <t>UT</t>
+        </is>
+      </c>
+      <c r="F35" s="13" t="n">
+        <v>2109</v>
+      </c>
+      <c r="G35" s="13" t="inlineStr">
+        <is>
+          <t>$185,000 (price reduced)</t>
+        </is>
+      </c>
+      <c r="H35" s="15" t="n">
+        <v>185000</v>
+      </c>
+      <c r="I35" s="13" t="inlineStr"/>
+      <c r="J35" s="13" t="inlineStr"/>
+      <c r="K35" s="13" t="inlineStr">
+        <is>
+          <t>BusinessesForSale (First Choice Business Brokers #3924670)</t>
+        </is>
+      </c>
+      <c r="L35" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M35" s="13" t="inlineStr"/>
+      <c r="N35" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O35" s="14" t="inlineStr">
+        <is>
+          <t>Home-based, est. March 2020, Salt Lake County UT. Includes ~$65K inventory/stock.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" outlineLevel="1">
+      <c r="A36" s="13" t="inlineStr">
+        <is>
+          <t>West / Other</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="inlineStr">
+        <is>
+          <t>Storage locker filled with appliance parts – washer/dryer parts, heating elements, cords, rollers, belts, tools</t>
+        </is>
+      </c>
+      <c r="C36" s="13" t="inlineStr">
+        <is>
+          <t>bulk lot</t>
+        </is>
+      </c>
+      <c r="D36" s="13" t="inlineStr">
+        <is>
+          <t>Phoenix</t>
+        </is>
+      </c>
+      <c r="E36" s="13" t="inlineStr">
+        <is>
+          <t>AZ</t>
+        </is>
+      </c>
+      <c r="F36" s="13" t="n">
+        <v>2307</v>
+      </c>
+      <c r="G36" s="13" t="inlineStr">
+        <is>
+          <t>Message for pricing</t>
+        </is>
+      </c>
+      <c r="H36" s="15" t="n"/>
+      <c r="I36" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J36" s="13" t="inlineStr"/>
+      <c r="K36" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L36" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M36" s="13" t="inlineStr"/>
+      <c r="N36" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O36" s="14" t="inlineStr">
+        <is>
+          <t>Seller is getting out of the appliance business; selling the whole locker (North Phoenix, Deer Valley Rd near 19th Ave). Delivery available per post. Separate from the Phoenix parts-store closing ad.</t>
+        </is>
+      </c>
     </row>
     <row r="37" outlineLevel="1">
       <c r="A37" s="13" t="inlineStr">
@@ -2884,7 +2960,7 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>Appliance service business for sale (Western Slope) - established warranty-servicer setups with many manufacturers</t>
+          <t>Appliance repair &amp; sales business for sale – 100+ appliances (~90% new), liftgate truck, large powered storage unit</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
@@ -2894,28 +2970,28 @@
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>Montrose</t>
+          <t>Surprise</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>1954</v>
+        <v>2317</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t>$110,000</t>
+          <t>$75,000</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
-        <v>110000</v>
+        <v>75000</v>
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J37" s="13" t="inlineStr"/>
@@ -2937,228 +3013,39 @@
       </c>
       <c r="O37" s="14" t="inlineStr">
         <is>
-          <t>Going-concern service business; possible seller financing; no parts inventory mentioned. Updated 2026-10-17.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" outlineLevel="1">
-      <c r="A38" s="13" t="inlineStr">
-        <is>
-          <t>West / Other</t>
-        </is>
-      </c>
-      <c r="B38" s="14" t="inlineStr">
-        <is>
-          <t>Appliance Repair Technicians: Own the Business - $65K parts inventory/stock + $25K FF&amp;E + 2022 Promaster van</t>
-        </is>
-      </c>
-      <c r="C38" s="13" t="inlineStr">
-        <is>
-          <t>business for sale</t>
-        </is>
-      </c>
-      <c r="D38" s="13" t="inlineStr">
-        <is>
-          <t>Salt Lake City</t>
-        </is>
-      </c>
-      <c r="E38" s="13" t="inlineStr">
-        <is>
-          <t>UT</t>
-        </is>
-      </c>
-      <c r="F38" s="13" t="n">
-        <v>2109</v>
-      </c>
-      <c r="G38" s="13" t="inlineStr">
-        <is>
-          <t>$185,000 (price reduced)</t>
-        </is>
-      </c>
-      <c r="H38" s="15" t="n">
-        <v>185000</v>
-      </c>
-      <c r="I38" s="13" t="inlineStr"/>
-      <c r="J38" s="13" t="inlineStr"/>
-      <c r="K38" s="13" t="inlineStr">
-        <is>
-          <t>BusinessesForSale (First Choice Business Brokers #3924670)</t>
-        </is>
-      </c>
-      <c r="L38" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M38" s="13" t="inlineStr"/>
-      <c r="N38" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O38" s="14" t="inlineStr">
-        <is>
-          <t>Home-based, est. March 2020, Salt Lake County UT. Includes ~$65K inventory/stock.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" outlineLevel="1">
-      <c r="A39" s="13" t="inlineStr">
-        <is>
-          <t>West / Other</t>
-        </is>
-      </c>
-      <c r="B39" s="14" t="inlineStr">
-        <is>
-          <t>Storage locker filled with appliance parts – washer/dryer parts, heating elements, cords, rollers, belts, tools</t>
-        </is>
-      </c>
-      <c r="C39" s="13" t="inlineStr">
-        <is>
-          <t>bulk lot</t>
-        </is>
-      </c>
-      <c r="D39" s="13" t="inlineStr">
-        <is>
-          <t>Phoenix</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="F39" s="13" t="n">
-        <v>2307</v>
-      </c>
-      <c r="G39" s="13" t="inlineStr">
-        <is>
-          <t>Message for pricing</t>
-        </is>
-      </c>
-      <c r="H39" s="15" t="n"/>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="J39" s="13" t="inlineStr"/>
-      <c r="K39" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L39" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M39" s="13" t="inlineStr"/>
-      <c r="N39" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O39" s="14" t="inlineStr">
-        <is>
-          <t>Seller is getting out of the appliance business; selling the whole locker (North Phoenix, Deer Valley Rd near 19th Ave). Delivery available per post. Separate from the Phoenix parts-store closing ad.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" outlineLevel="1">
-      <c r="A40" s="13" t="inlineStr">
-        <is>
-          <t>West / Other</t>
-        </is>
-      </c>
-      <c r="B40" s="14" t="inlineStr">
-        <is>
-          <t>Appliance repair &amp; sales business for sale – 100+ appliances (~90% new), liftgate truck, large powered storage unit</t>
-        </is>
-      </c>
-      <c r="C40" s="13" t="inlineStr">
-        <is>
-          <t>business for sale</t>
-        </is>
-      </c>
-      <c r="D40" s="13" t="inlineStr">
-        <is>
-          <t>Surprise</t>
-        </is>
-      </c>
-      <c r="E40" s="13" t="inlineStr">
-        <is>
-          <t>AZ</t>
-        </is>
-      </c>
-      <c r="F40" s="13" t="n">
-        <v>2317</v>
-      </c>
-      <c r="G40" s="13" t="inlineStr">
-        <is>
-          <t>$75,000</t>
-        </is>
-      </c>
-      <c r="H40" s="15" t="n">
-        <v>75000</v>
-      </c>
-      <c r="I40" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="J40" s="13" t="inlineStr"/>
-      <c r="K40" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L40" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M40" s="13" t="inlineStr"/>
-      <c r="N40" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O40" s="14" t="inlineStr">
-        <is>
           <t>Retiring owner of 14-year business serving rental-property owners. Whole appliances (fridges, stoves, microwaves, dishwashers, W/D), not a parts inventory. Storage unit near Dysart &amp; Bell Rd. By appointment only.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="17" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>Subtotal — West / Other</t>
         </is>
       </c>
-      <c r="B41" s="17" t="inlineStr">
+      <c r="B38" s="17" t="inlineStr">
         <is>
           <t>4 item(s)</t>
         </is>
       </c>
-      <c r="C41" s="18" t="n"/>
-      <c r="D41" s="18" t="n"/>
-      <c r="E41" s="18" t="n"/>
-      <c r="F41" s="18" t="n"/>
-      <c r="G41" s="18" t="n"/>
-      <c r="H41" s="19" t="n">
+      <c r="C38" s="18" t="n"/>
+      <c r="D38" s="18" t="n"/>
+      <c r="E38" s="18" t="n"/>
+      <c r="F38" s="18" t="n"/>
+      <c r="G38" s="18" t="n"/>
+      <c r="H38" s="19" t="n">
         <v>370000</v>
       </c>
-      <c r="I41" s="18" t="n"/>
-      <c r="J41" s="18" t="n"/>
-      <c r="K41" s="18" t="n"/>
-      <c r="L41" s="18" t="n"/>
-      <c r="M41" s="18" t="n"/>
-      <c r="N41" s="18" t="n"/>
-      <c r="O41" s="18" t="n"/>
+      <c r="I38" s="18" t="n"/>
+      <c r="J38" s="18" t="n"/>
+      <c r="K38" s="18" t="n"/>
+      <c r="L38" s="18" t="n"/>
+      <c r="M38" s="18" t="n"/>
+      <c r="N38" s="18" t="n"/>
+      <c r="O38" s="18" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O41"/>
+  <autoFilter ref="A1:O38"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N6" r:id="rId2"/>
@@ -3170,14 +3057,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId11"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3704,7 +3590,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M11" s="21" t="inlineStr">
+      <c r="M11" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -4025,7 +3911,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M16" s="21" t="inlineStr">
+      <c r="M16" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -4310,7 +4196,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M23" s="21" t="inlineStr">
+      <c r="M23" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -4373,7 +4259,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M24" s="21" t="inlineStr">
+      <c r="M24" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -5331,7 +5217,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M3" s="21" t="inlineStr">
+      <c r="M3" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -5639,7 +5525,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M9" s="21" t="inlineStr">
+      <c r="M9" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -5708,7 +5594,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M10" s="21" t="inlineStr">
+      <c r="M10" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -5773,7 +5659,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M11" s="21" t="inlineStr">
+      <c r="M11" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -5890,7 +5776,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M14" s="21" t="inlineStr">
+      <c r="M14" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -5959,7 +5845,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M15" s="21" t="inlineStr">
+      <c r="M15" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -6137,7 +6023,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M19" s="21" t="inlineStr">
+      <c r="M19" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -6206,7 +6092,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M20" s="21" t="inlineStr">
+      <c r="M20" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -6449,7 +6335,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M25" s="21" t="inlineStr">
+      <c r="M25" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -6684,7 +6570,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M30" s="21" t="inlineStr">
+      <c r="M30" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -6939,12 +6825,12 @@
           <t>AuctionNinja (Clearing House Estate Sales)</t>
         </is>
       </c>
-      <c r="L34" s="20" t="inlineStr">
+      <c r="L34" s="21" t="inlineStr">
         <is>
           <t>ENDING SOON</t>
         </is>
       </c>
-      <c r="M34" s="21" t="inlineStr">
+      <c r="M34" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -7009,7 +6895,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M35" s="21" t="inlineStr">
+      <c r="M35" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -7257,7 +7143,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M39" s="21" t="inlineStr">
+      <c r="M39" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -7809,7 +7695,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M49" s="21" t="inlineStr">
+      <c r="M49" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -7874,7 +7760,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M50" s="21" t="inlineStr">
+      <c r="M50" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -8183,7 +8069,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M55" s="21" t="inlineStr">
+      <c r="M55" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -8248,7 +8134,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M56" s="21" t="inlineStr">
+      <c r="M56" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -8504,7 +8390,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M60" s="21" t="inlineStr">
+      <c r="M60" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -8573,7 +8459,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M61" s="21" t="inlineStr">
+      <c r="M61" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -8638,7 +8524,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M62" s="21" t="inlineStr">
+      <c r="M62" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -8768,7 +8654,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M64" s="21" t="inlineStr">
+      <c r="M64" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -9081,7 +8967,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M69" s="21" t="inlineStr">
+      <c r="M69" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -11933,7 +11819,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M113" s="21" t="inlineStr">
+      <c r="M113" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -12163,7 +12049,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M119" s="21" t="inlineStr">
+      <c r="M119" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -12275,7 +12161,7 @@
           <t>HiBid</t>
         </is>
       </c>
-      <c r="L122" s="20" t="inlineStr">
+      <c r="L122" s="21" t="inlineStr">
         <is>
           <t>ENDING SOON</t>
         </is>
@@ -12340,7 +12226,7 @@
           <t>HiBid</t>
         </is>
       </c>
-      <c r="L123" s="20" t="inlineStr">
+      <c r="L123" s="21" t="inlineStr">
         <is>
           <t>ENDING SOON</t>
         </is>
@@ -12458,7 +12344,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M126" s="21" t="inlineStr">
+      <c r="M126" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -12569,7 +12455,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M129" s="21" t="inlineStr">
+      <c r="M129" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -12632,7 +12518,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M130" s="21" t="inlineStr">
+      <c r="M130" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -12695,7 +12581,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M131" s="21" t="inlineStr">
+      <c r="M131" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -17246,7 +17132,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M17" s="21" t="inlineStr">
+      <c r="M17" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -18273,7 +18159,7 @@
           <t>HiBid (Tom Hall Auctions)</t>
         </is>
       </c>
-      <c r="L35" s="20" t="inlineStr">
+      <c r="L35" s="21" t="inlineStr">
         <is>
           <t>ENDING SOON</t>
         </is>
@@ -18540,7 +18426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O82"/>
+  <dimension ref="A1:O90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -18704,7 +18590,7 @@
           <t>Salvadore Auctions</t>
         </is>
       </c>
-      <c r="L3" s="20" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t>ENDING SOON</t>
         </is>
@@ -19418,7 +19304,7 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t>▸ Maine / VT / Northern NH  (4)</t>
+          <t>▸ Rhode Island  (1)</t>
         </is>
       </c>
       <c r="B18" s="12" t="n"/>
@@ -19439,47 +19325,47 @@
     <row r="19" outlineLevel="1">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>Maine / VT / Northern NH</t>
+          <t>Rhode Island</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>Contractor appliance lot – 3 refrigerators, Bosch wall oven, gas range, washer/dryer set</t>
+          <t>Steve's Bounce House business auction: 3 box trucks, trailer, container, 70+ bounce houses, tents, tables/chairs, pallet shelving, concession/food prep equipment</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>contractor lot</t>
+          <t>business auction</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>Scarborough</t>
+          <t>Coventry</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>ME</t>
+          <t>RI</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>104</v>
+        <v>53</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>$200 OBO each, less as a bundle</t>
+          <t>Online-only auction (BidSpotter)</t>
         </is>
       </c>
       <c r="H19" s="15" t="n"/>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="J19" s="13" t="inlineStr"/>
+      <c r="I19" s="13" t="inlineStr"/>
+      <c r="J19" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-10 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>Paul E. Saperstein (PESCO)</t>
         </is>
       </c>
       <c r="L19" s="13" t="inlineStr">
@@ -19495,135 +19381,57 @@
       </c>
       <c r="O19" s="14" t="inlineStr">
         <is>
-          <t>Working units pulled from jobs. Complete appliances, not parts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" outlineLevel="1">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>Maine / VT / Northern NH</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="inlineStr">
-        <is>
-          <t>Event-rental business closing – 300+ chairs, 40+ rounds, 1,300+ china, linens (all at once)</t>
-        </is>
-      </c>
-      <c r="C20" s="13" t="inlineStr">
-        <is>
-          <t>business closing</t>
-        </is>
-      </c>
-      <c r="D20" s="13" t="inlineStr">
-        <is>
-          <t>Woolwich</t>
-        </is>
-      </c>
-      <c r="E20" s="13" t="inlineStr">
-        <is>
-          <t>ME</t>
-        </is>
-      </c>
-      <c r="F20" s="13" t="n">
-        <v>135</v>
-      </c>
-      <c r="G20" s="13" t="inlineStr">
-        <is>
-          <t>No price listed</t>
-        </is>
-      </c>
-      <c r="H20" s="15" t="n"/>
-      <c r="I20" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-07</t>
-        </is>
-      </c>
-      <c r="J20" s="13" t="inlineStr"/>
-      <c r="K20" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L20" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M20" s="13" t="inlineStr"/>
-      <c r="N20" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O20" s="14" t="inlineStr">
-        <is>
-          <t>Updated Oct 7. Replacement cost &gt;$72K per post.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" outlineLevel="1">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>Maine / VT / Northern NH</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="inlineStr">
-        <is>
-          <t>Pellet/wood stoves, heating stock, tools &amp; heavy equipment – "business liquidation", 380 lots</t>
-        </is>
-      </c>
-      <c r="C21" s="13" t="inlineStr">
-        <is>
-          <t>auction</t>
-        </is>
-      </c>
-      <c r="D21" s="13" t="inlineStr">
-        <is>
-          <t>Lunenburg</t>
-        </is>
-      </c>
-      <c r="E21" s="13" t="inlineStr">
-        <is>
-          <t>VT</t>
-        </is>
-      </c>
-      <c r="F21" s="13" t="n">
-        <v>168</v>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>Online auction</t>
-        </is>
-      </c>
-      <c r="H21" s="15" t="n"/>
-      <c r="I21" s="13" t="inlineStr"/>
-      <c r="J21" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-04 10:00 AM ET</t>
-        </is>
-      </c>
-      <c r="K21" s="13" t="inlineStr">
-        <is>
-          <t>Thomas Hirchak Co.</t>
-        </is>
-      </c>
-      <c r="L21" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M21" s="13" t="inlineStr"/>
-      <c r="N21" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O21" s="14" t="inlineStr">
-        <is>
-          <t>Closes Wed Nov 4 10 AM, preview Oct 28, removal Nov 9, no shipping.</t>
-        </is>
-      </c>
+          <t>Nov 10 11 AM online only; 1372 Main St.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Rhode Island</t>
+        </is>
+      </c>
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>1 item(s)</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
+      <c r="F20" s="18" t="n"/>
+      <c r="G20" s="18" t="n"/>
+      <c r="H20" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="18" t="n"/>
+      <c r="J20" s="18" t="n"/>
+      <c r="K20" s="18" t="n"/>
+      <c r="L20" s="18" t="n"/>
+      <c r="M20" s="18" t="n"/>
+      <c r="N20" s="18" t="n"/>
+      <c r="O20" s="18" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="inlineStr">
+        <is>
+          <t>▸ Maine / VT / Northern NH  (4)</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n"/>
+      <c r="C21" s="12" t="n"/>
+      <c r="D21" s="12" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="12" t="n"/>
+      <c r="G21" s="12" t="n"/>
+      <c r="H21" s="12" t="n"/>
+      <c r="I21" s="12" t="n"/>
+      <c r="J21" s="12" t="n"/>
+      <c r="K21" s="12" t="n"/>
+      <c r="L21" s="12" t="n"/>
+      <c r="M21" s="12" t="n"/>
+      <c r="N21" s="12" t="n"/>
+      <c r="O21" s="12" t="n"/>
     </row>
     <row r="22" outlineLevel="1">
       <c r="A22" s="13" t="inlineStr">
@@ -19633,42 +19441,42 @@
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>Bread Loaf Corp wind-down – contractor equipment, staging, telehandler</t>
+          <t>Contractor appliance lot – 3 refrigerators, Bosch wall oven, gas range, washer/dryer set</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
         <is>
-          <t>contractor liquidation</t>
+          <t>contractor lot</t>
         </is>
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>Middlebury</t>
+          <t>Scarborough</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>VT</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>177</v>
+        <v>104</v>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>$200 OBO each, less as a bundle</t>
         </is>
       </c>
       <c r="H22" s="15" t="n"/>
-      <c r="I22" s="13" t="inlineStr"/>
-      <c r="J22" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-28 09:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I22" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="J22" s="13" t="inlineStr"/>
       <c r="K22" s="13" t="inlineStr">
         <is>
-          <t>THC Auction</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L22" s="13" t="inlineStr">
@@ -19684,67 +19492,145 @@
       </c>
       <c r="O22" s="14" t="inlineStr">
         <is>
-          <t>Company wind-down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Maine / VT / Northern NH</t>
-        </is>
-      </c>
-      <c r="B23" s="17" t="inlineStr">
-        <is>
-          <t>4 item(s)</t>
-        </is>
-      </c>
-      <c r="C23" s="18" t="n"/>
-      <c r="D23" s="18" t="n"/>
-      <c r="E23" s="18" t="n"/>
-      <c r="F23" s="18" t="n"/>
-      <c r="G23" s="18" t="n"/>
-      <c r="H23" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="18" t="n"/>
-      <c r="J23" s="18" t="n"/>
-      <c r="K23" s="18" t="n"/>
-      <c r="L23" s="18" t="n"/>
-      <c r="M23" s="18" t="n"/>
-      <c r="N23" s="18" t="n"/>
-      <c r="O23" s="18" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="11" t="inlineStr">
-        <is>
-          <t>▸ CT / Hudson Valley  (8)</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
-      <c r="G24" s="12" t="n"/>
-      <c r="H24" s="12" t="n"/>
-      <c r="I24" s="12" t="n"/>
-      <c r="J24" s="12" t="n"/>
-      <c r="K24" s="12" t="n"/>
-      <c r="L24" s="12" t="n"/>
-      <c r="M24" s="12" t="n"/>
-      <c r="N24" s="12" t="n"/>
-      <c r="O24" s="12" t="n"/>
+          <t>Working units pulled from jobs. Complete appliances, not parts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" outlineLevel="1">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Maine / VT / Northern NH</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Event-rental business closing – 300+ chairs, 40+ rounds, 1,300+ china, linens (all at once)</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="inlineStr">
+        <is>
+          <t>business closing</t>
+        </is>
+      </c>
+      <c r="D23" s="13" t="inlineStr">
+        <is>
+          <t>Woolwich</t>
+        </is>
+      </c>
+      <c r="E23" s="13" t="inlineStr">
+        <is>
+          <t>ME</t>
+        </is>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>135</v>
+      </c>
+      <c r="G23" s="13" t="inlineStr">
+        <is>
+          <t>No price listed</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="n"/>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="inlineStr"/>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L23" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M23" s="13" t="inlineStr"/>
+      <c r="N23" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O23" s="14" t="inlineStr">
+        <is>
+          <t>Updated Oct 7. Replacement cost &gt;$72K per post.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" outlineLevel="1">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Maine / VT / Northern NH</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>Pellet/wood stoves, heating stock, tools &amp; heavy equipment – "business liquidation", 380 lots</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>auction</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>Lunenburg</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>VT</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>168</v>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>Online auction</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="n"/>
+      <c r="I24" s="13" t="inlineStr"/>
+      <c r="J24" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-04 10:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>Thomas Hirchak Co.</t>
+        </is>
+      </c>
+      <c r="L24" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M24" s="13" t="inlineStr"/>
+      <c r="N24" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O24" s="14" t="inlineStr">
+        <is>
+          <t>Closes Wed Nov 4 10 AM, preview Oct 28, removal Nov 9, no shipping.</t>
+        </is>
+      </c>
     </row>
     <row r="25" outlineLevel="1">
       <c r="A25" s="13" t="inlineStr">
         <is>
-          <t>CT / Hudson Valley</t>
+          <t>Maine / VT / Northern NH</t>
         </is>
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Bank-ordered electrical contractor sale – Greenlee/Hilti/Milwaukee tools, GE/Siemens breakers</t>
+          <t>Bread Loaf Corp wind-down – contractor equipment, staging, telehandler</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
@@ -19754,16 +19640,16 @@
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>Clinton</t>
+          <t>Middlebury</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>VT</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>106</v>
+        <v>177</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
@@ -19774,12 +19660,12 @@
       <c r="I25" s="13" t="inlineStr"/>
       <c r="J25" s="13" t="inlineStr">
         <is>
-          <t>2026-10-29 05:00 PM ET</t>
+          <t>2026-10-28 09:00 AM ET</t>
         </is>
       </c>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>Hamilton Group / EstateSales.net</t>
+          <t>THC Auction</t>
         </is>
       </c>
       <c r="L25" s="13" t="inlineStr">
@@ -19795,135 +19681,57 @@
       </c>
       <c r="O25" s="14" t="inlineStr">
         <is>
-          <t>Listed "Oct 29 2 PM PST" (= 5 PM ET).</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" outlineLevel="1">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>CT / Hudson Valley</t>
-        </is>
-      </c>
-      <c r="B26" s="14" t="inlineStr">
-        <is>
-          <t>Antique / thrift store – entire inventory (fills a 4k sq ft store, 80k+ retail)</t>
-        </is>
-      </c>
-      <c r="C26" s="13" t="inlineStr">
-        <is>
-          <t>store closing – entire inventory</t>
-        </is>
-      </c>
-      <c r="D26" s="13" t="inlineStr">
-        <is>
-          <t>Waterbury</t>
-        </is>
-      </c>
-      <c r="E26" s="13" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="F26" s="13" t="n">
-        <v>121</v>
-      </c>
-      <c r="G26" s="13" t="inlineStr">
-        <is>
-          <t>$6,500 complete inventory (open to offers)</t>
-        </is>
-      </c>
-      <c r="H26" s="15" t="n"/>
-      <c r="I26" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="J26" s="13" t="inlineStr"/>
-      <c r="K26" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L26" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M26" s="13" t="inlineStr"/>
-      <c r="N26" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O26" s="14" t="inlineStr">
-        <is>
-          <t>1155 Thomaston Ave. Sold only as a complete lot: antiques, furniture, tools, hardware, small appliances, electronics, display cabinets, shelving, racks, vending machine. Seller will package with their eBay inventory (jewelry, vinyl, toys, Christmas, contents of 3 box trucks, "easily 100k retail"). Mixed general merchandise, not appliance-specific.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" outlineLevel="1">
-      <c r="A27" s="13" t="inlineStr">
-        <is>
-          <t>CT / Hudson Valley</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="inlineStr">
-        <is>
-          <t>Fabrication &amp; welding shop liquidation – everything must be sold</t>
-        </is>
-      </c>
-      <c r="C27" s="13" t="inlineStr">
-        <is>
-          <t>machine shop liquidation</t>
-        </is>
-      </c>
-      <c r="D27" s="13" t="inlineStr">
-        <is>
-          <t>Bridgeport</t>
-        </is>
-      </c>
-      <c r="E27" s="13" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="F27" s="13" t="n">
-        <v>139</v>
-      </c>
-      <c r="G27" s="13" t="inlineStr">
-        <is>
-          <t>Priced per machine (e.g. W.A. Whitney punch press $4,950; DoAll bandsaw $950)</t>
-        </is>
-      </c>
-      <c r="H27" s="15" t="n"/>
-      <c r="I27" s="13" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-      <c r="J27" s="13" t="inlineStr"/>
-      <c r="K27" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L27" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M27" s="13" t="inlineStr"/>
-      <c r="N27" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O27" s="14" t="inlineStr">
-        <is>
-          <t>All assets/equipment/tools of a fab &amp; welding shop; machines under power, inspection by appointment, buyer removes (small forklift on site). Several big items already SOLD (Cincinnati brake/shear, plasma table, Lown roll). Remaining: Whitney + Roper Whitney punch presses, DoAll V36 bandsaw, Thompson spot welder, George Ohl 120" brake, Bridgeport mill, etc. Mostly 220V. Posted May 15, updated Oct 19.</t>
-        </is>
-      </c>
+          <t>Company wind-down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Maine / VT / Northern NH</t>
+        </is>
+      </c>
+      <c r="B26" s="17" t="inlineStr">
+        <is>
+          <t>4 item(s)</t>
+        </is>
+      </c>
+      <c r="C26" s="18" t="n"/>
+      <c r="D26" s="18" t="n"/>
+      <c r="E26" s="18" t="n"/>
+      <c r="F26" s="18" t="n"/>
+      <c r="G26" s="18" t="n"/>
+      <c r="H26" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="18" t="n"/>
+      <c r="J26" s="18" t="n"/>
+      <c r="K26" s="18" t="n"/>
+      <c r="L26" s="18" t="n"/>
+      <c r="M26" s="18" t="n"/>
+      <c r="N26" s="18" t="n"/>
+      <c r="O26" s="18" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="inlineStr">
+        <is>
+          <t>▸ CT / Hudson Valley  (10)</t>
+        </is>
+      </c>
+      <c r="B27" s="12" t="n"/>
+      <c r="C27" s="12" t="n"/>
+      <c r="D27" s="12" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="12" t="n"/>
+      <c r="G27" s="12" t="n"/>
+      <c r="H27" s="12" t="n"/>
+      <c r="I27" s="12" t="n"/>
+      <c r="J27" s="12" t="n"/>
+      <c r="K27" s="12" t="n"/>
+      <c r="L27" s="12" t="n"/>
+      <c r="M27" s="12" t="n"/>
+      <c r="N27" s="12" t="n"/>
+      <c r="O27" s="12" t="n"/>
     </row>
     <row r="28" outlineLevel="1">
       <c r="A28" s="13" t="inlineStr">
@@ -19933,17 +19741,17 @@
       </c>
       <c r="B28" s="14" t="inlineStr">
         <is>
-          <t>The Outlaw Grill Steakhouse – used restaurant equipment auction (PCI Auctions CT, e.g. Vulcan EV60 Endurance 60" range)</t>
+          <t>Bank-ordered electrical contractor sale – Greenlee/Hilti/Milwaukee tools, GE/Siemens breakers</t>
         </is>
       </c>
       <c r="C28" s="13" t="inlineStr">
         <is>
-          <t>restaurant auction</t>
+          <t>contractor liquidation</t>
         </is>
       </c>
       <c r="D28" s="13" t="inlineStr">
         <is>
-          <t>Stamford</t>
+          <t>Clinton</t>
         </is>
       </c>
       <c r="E28" s="13" t="inlineStr">
@@ -19952,32 +19760,28 @@
         </is>
       </c>
       <c r="F28" s="13" t="n">
-        <v>159</v>
+        <v>106</v>
       </c>
       <c r="G28" s="13" t="inlineStr">
         <is>
-          <t>Online auction, current bids</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H28" s="15" t="n"/>
-      <c r="I28" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
+      <c r="I28" s="13" t="inlineStr"/>
       <c r="J28" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 08:30 PM ET</t>
+          <t>2026-10-29 05:00 PM ET</t>
         </is>
       </c>
       <c r="K28" s="13" t="inlineStr">
         <is>
-          <t>PCI Auctions</t>
-        </is>
-      </c>
-      <c r="L28" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Hamilton Group / EstateSales.net</t>
+        </is>
+      </c>
+      <c r="L28" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M28" s="13" t="inlineStr"/>
@@ -19988,7 +19792,7 @@
       </c>
       <c r="O28" s="14" t="inlineStr">
         <is>
-          <t>Ends Wed Oct 21 8:30 PM EDT. PCI warehouse, 36 Ludlow St, Stamford CT. Page lists preview Oct 28 and removal Thu Oct 29 11-3 (after close). Shipping/delivery available; payment due on pickup day. Items still being added.</t>
+          <t>Listed "Oct 29 2 PM PST" (= 5 PM ET).</t>
         </is>
       </c>
     </row>
@@ -20000,17 +19804,17 @@
       </c>
       <c r="B29" s="14" t="inlineStr">
         <is>
-          <t>Café/bakery liquidation – Traulsen, Vulcan ovens, mixers, Hobart slicer (~74 lots)</t>
+          <t>Former Duck Donuts franchise bank-ordered sale: like-new restaurant/coffee shop equipment</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>restaurant equipment auction</t>
         </is>
       </c>
       <c r="D29" s="13" t="inlineStr">
         <is>
-          <t>Greenwich</t>
+          <t>Madison</t>
         </is>
       </c>
       <c r="E29" s="13" t="inlineStr">
@@ -20019,28 +19823,28 @@
         </is>
       </c>
       <c r="F29" s="13" t="n">
-        <v>164</v>
+        <v>109</v>
       </c>
       <c r="G29" s="13" t="inlineStr">
         <is>
-          <t>Live auction + webcast</t>
+          <t>Timed online auction (BidSpotter)</t>
         </is>
       </c>
       <c r="H29" s="15" t="n"/>
       <c r="I29" s="13" t="inlineStr"/>
       <c r="J29" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 06:00 PM ET</t>
+          <t>2026-10-27 05:00 PM ET</t>
         </is>
       </c>
       <c r="K29" s="13" t="inlineStr">
         <is>
-          <t>Best Buy Auctioneers / AuctionGuide</t>
-        </is>
-      </c>
-      <c r="L29" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Hamilton Group via BidSpotter</t>
+        </is>
+      </c>
+      <c r="L29" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M29" s="13" t="inlineStr"/>
@@ -20051,7 +19855,7 @@
       </c>
       <c r="O29" s="14" t="inlineStr">
         <is>
-          <t>Oct 21; start time not captured (placeholder 6 PM).</t>
+          <t>Sale ends Oct 27 (listing says 12 PM; lots begin closing 2 PM PT per description).</t>
         </is>
       </c>
     </row>
@@ -20063,42 +19867,42 @@
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>BJ's Wholesale closeout – racking, forklifts, Hobart</t>
+          <t>Antique / thrift store – entire inventory (fills a 4k sq ft store, 80k+ retail)</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>store closing – entire inventory</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>Rotterdam</t>
+          <t>Waterbury</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>168</v>
+        <v>121</v>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>$6,500 complete inventory (open to offers)</t>
         </is>
       </c>
       <c r="H30" s="15" t="n"/>
-      <c r="I30" s="13" t="inlineStr"/>
-      <c r="J30" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-10 10:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I30" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="J30" s="13" t="inlineStr"/>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L30" s="13" t="inlineStr">
@@ -20114,7 +19918,7 @@
       </c>
       <c r="O30" s="14" t="inlineStr">
         <is>
-          <t>Closes from Nov 10 10 AM.</t>
+          <t>1155 Thomaston Ave. Sold only as a complete lot: antiques, furniture, tools, hardware, small appliances, electronics, display cabinets, shelving, racks, vending machine. Seller will package with their eBay inventory (jewelry, vinyl, toys, Christmas, contents of 3 box trucks, "easily 100k retail"). Mixed general merchandise, not appliance-specific.</t>
         </is>
       </c>
     </row>
@@ -20126,42 +19930,42 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>Body shop closing after 50 years – tools, welder, generators, plasma</t>
+          <t>Sausage processing &amp; packaging complete facility closure: refrigerated box trucks, Velati mixers, Vemag, packaging lines</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>tools liquidation</t>
+          <t>facility closure auction</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>West Nyack</t>
+          <t>New Haven</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>178</v>
+        <v>122</v>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
-          <t>Make offer / lot</t>
+          <t>Timed online auction (BidSpotter)</t>
         </is>
       </c>
       <c r="H31" s="15" t="n"/>
-      <c r="I31" s="13" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="J31" s="13" t="inlineStr"/>
+      <c r="I31" s="13" t="inlineStr"/>
+      <c r="J31" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-17 12:00 PM ET</t>
+        </is>
+      </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>M&amp;M Equipment Corp</t>
         </is>
       </c>
       <c r="L31" s="13" t="inlineStr">
@@ -20177,7 +19981,7 @@
       </c>
       <c r="O31" s="14" t="inlineStr">
         <is>
-          <t>One-man auto body shop closing/retirement (Park Ridge / West Nyack NY-NJ border). Heat lamps, Kansas jack pullers, Miller 200 welder, generators, sheet-metal brake, hydraulic press, plasma cutter, engine hoist. Posted Aug 16; still open 2026-10-19.</t>
+          <t>Bidding opens Nov 10 10 AM CT; lots begin closing Nov 17 11 AM CT.</t>
         </is>
       </c>
     </row>
@@ -20189,36 +19993,36 @@
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>Woodworkers shop closing sale – shop tools &amp; hand tools</t>
+          <t>Fabrication &amp; welding shop liquidation – everything must be sold</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>woodworking shop closing</t>
+          <t>machine shop liquidation</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>Tappan</t>
+          <t>Bridgeport</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>Priced individually (some free)</t>
+          <t>Priced per machine (e.g. W.A. Whitney punch press $4,950; DoAll bandsaw $950)</t>
         </is>
       </c>
       <c r="H32" s="15" t="n"/>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="J32" s="13" t="inlineStr"/>
@@ -20240,102 +20044,184 @@
       </c>
       <c r="O32" s="14" t="inlineStr">
         <is>
-          <t>Ongoing shop-closing sale at 61 Main St, Tappan; many shop and hand tools, schedule a visit. Near the West Nyack body-shop sale (bl-054) for one trip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — CT / Hudson Valley</t>
-        </is>
-      </c>
-      <c r="B33" s="17" t="inlineStr">
-        <is>
-          <t>8 item(s)</t>
-        </is>
-      </c>
-      <c r="C33" s="18" t="n"/>
-      <c r="D33" s="18" t="n"/>
-      <c r="E33" s="18" t="n"/>
-      <c r="F33" s="18" t="n"/>
-      <c r="G33" s="18" t="n"/>
-      <c r="H33" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="18" t="n"/>
-      <c r="J33" s="18" t="n"/>
-      <c r="K33" s="18" t="n"/>
-      <c r="L33" s="18" t="n"/>
-      <c r="M33" s="18" t="n"/>
-      <c r="N33" s="18" t="n"/>
-      <c r="O33" s="18" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>▸ NYC / Long Island / NJ  (23)</t>
-        </is>
-      </c>
-      <c r="B34" s="12" t="n"/>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="12" t="n"/>
-      <c r="E34" s="12" t="n"/>
-      <c r="F34" s="12" t="n"/>
-      <c r="G34" s="12" t="n"/>
-      <c r="H34" s="12" t="n"/>
-      <c r="I34" s="12" t="n"/>
-      <c r="J34" s="12" t="n"/>
-      <c r="K34" s="12" t="n"/>
-      <c r="L34" s="12" t="n"/>
-      <c r="M34" s="12" t="n"/>
-      <c r="N34" s="12" t="n"/>
-      <c r="O34" s="12" t="n"/>
+          <t>All assets/equipment/tools of a fab &amp; welding shop; machines under power, inspection by appointment, buyer removes (small forklift on site). Several big items already SOLD (Cincinnati brake/shear, plasma table, Lown roll). Remaining: Whitney + Roper Whitney punch presses, DoAll V36 bandsaw, Thompson spot welder, George Ohl 120" brake, Bridgeport mill, etc. Mostly 220V. Posted May 15, updated Oct 19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" outlineLevel="1">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>CT / Hudson Valley</t>
+        </is>
+      </c>
+      <c r="B33" s="14" t="inlineStr">
+        <is>
+          <t>The Outlaw Grill Steakhouse – used restaurant equipment auction (PCI Auctions CT, e.g. Vulcan EV60 Endurance 60" range)</t>
+        </is>
+      </c>
+      <c r="C33" s="13" t="inlineStr">
+        <is>
+          <t>restaurant auction</t>
+        </is>
+      </c>
+      <c r="D33" s="13" t="inlineStr">
+        <is>
+          <t>Stamford</t>
+        </is>
+      </c>
+      <c r="E33" s="13" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="F33" s="13" t="n">
+        <v>159</v>
+      </c>
+      <c r="G33" s="13" t="inlineStr">
+        <is>
+          <t>Online auction, current bids</t>
+        </is>
+      </c>
+      <c r="H33" s="15" t="n"/>
+      <c r="I33" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="J33" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-21 08:30 PM ET</t>
+        </is>
+      </c>
+      <c r="K33" s="13" t="inlineStr">
+        <is>
+          <t>PCI Auctions</t>
+        </is>
+      </c>
+      <c r="L33" s="21" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M33" s="13" t="inlineStr"/>
+      <c r="N33" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O33" s="14" t="inlineStr">
+        <is>
+          <t>Ends Wed Oct 21 8:30 PM EDT. PCI warehouse, 36 Ludlow St, Stamford CT. Page lists preview Oct 28 and removal Thu Oct 29 11-3 (after close). Shipping/delivery available; payment due on pickup day. Items still being added.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" outlineLevel="1">
+      <c r="A34" s="13" t="inlineStr">
+        <is>
+          <t>CT / Hudson Valley</t>
+        </is>
+      </c>
+      <c r="B34" s="14" t="inlineStr">
+        <is>
+          <t>Café/bakery liquidation – Traulsen, Vulcan ovens, mixers, Hobart slicer (~74 lots)</t>
+        </is>
+      </c>
+      <c r="C34" s="13" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="D34" s="13" t="inlineStr">
+        <is>
+          <t>Greenwich</t>
+        </is>
+      </c>
+      <c r="E34" s="13" t="inlineStr">
+        <is>
+          <t>CT</t>
+        </is>
+      </c>
+      <c r="F34" s="13" t="n">
+        <v>164</v>
+      </c>
+      <c r="G34" s="13" t="inlineStr">
+        <is>
+          <t>Live auction + webcast</t>
+        </is>
+      </c>
+      <c r="H34" s="15" t="n"/>
+      <c r="I34" s="13" t="inlineStr"/>
+      <c r="J34" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-21 06:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K34" s="13" t="inlineStr">
+        <is>
+          <t>Best Buy Auctioneers / AuctionGuide</t>
+        </is>
+      </c>
+      <c r="L34" s="21" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M34" s="13" t="inlineStr"/>
+      <c r="N34" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O34" s="14" t="inlineStr">
+        <is>
+          <t>Oct 21; start time not captured (placeholder 6 PM).</t>
+        </is>
+      </c>
     </row>
     <row r="35" outlineLevel="1">
       <c r="A35" s="13" t="inlineStr">
         <is>
-          <t>NYC / Long Island / NJ</t>
+          <t>CT / Hudson Valley</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>Viva Margherita restaurant complete contents (building torn down)</t>
+          <t>BJ's Wholesale closeout – racking, forklifts, Hobart</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>Edgewater</t>
+          <t>Rotterdam</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>186</v>
+        <v>168</v>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
-          <t>Complete contents / make offer</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H35" s="15" t="n"/>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="J35" s="13" t="inlineStr"/>
+      <c r="I35" s="13" t="inlineStr"/>
+      <c r="J35" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-10 10:00 AM ET</t>
+        </is>
+      </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>Grafe Auction</t>
         </is>
       </c>
       <c r="L35" s="13" t="inlineStr">
@@ -20351,29 +20237,29 @@
       </c>
       <c r="O35" s="14" t="inlineStr">
         <is>
-          <t>Address 163 Old River Road, Edgewater NJ. Building being torn down; complete restaurant contents for sale / make offer.</t>
+          <t>Closes from Nov 10 10 AM.</t>
         </is>
       </c>
     </row>
     <row r="36" outlineLevel="1">
       <c r="A36" s="13" t="inlineStr">
         <is>
-          <t>NYC / Long Island / NJ</t>
+          <t>CT / Hudson Valley</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>Japanese BBQ &amp; bar – ~47 lots: Turbo Air, Hoshizaki ice machine, Pitco, Beverage-Air</t>
+          <t>Body shop closing after 50 years – tools, welder, generators, plasma</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>tools liquidation</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>West Nyack</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
@@ -20382,32 +20268,28 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Make offer / lot</t>
         </is>
       </c>
       <c r="H36" s="15" t="n"/>
       <c r="I36" s="13" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="J36" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 04:00 PM ET</t>
-        </is>
-      </c>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="J36" s="13" t="inlineStr"/>
       <c r="K36" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
-        </is>
-      </c>
-      <c r="L36" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L36" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M36" s="13" t="inlineStr"/>
@@ -20418,29 +20300,29 @@
       </c>
       <c r="O36" s="14" t="inlineStr">
         <is>
-          <t>Wed Oct 21 4 PM. NYC 10013.</t>
+          <t>One-man auto body shop closing/retirement (Park Ridge / West Nyack NY-NJ border). Heat lamps, Kansas jack pullers, Miller 200 welder, generators, sheet-metal brake, hydraulic press, plasma cutter, engine hoist. Posted Aug 16; still open 2026-10-19.</t>
         </is>
       </c>
     </row>
     <row r="37" outlineLevel="1">
       <c r="A37" s="13" t="inlineStr">
         <is>
-          <t>NYC / Long Island / NJ</t>
+          <t>CT / Hudson Valley</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>Flooring company closed – pro tool package</t>
+          <t>Woodworkers shop closing sale – shop tools &amp; hand tools</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>tools liquidation</t>
+          <t>woodworking shop closing</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Tappan</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
@@ -20449,17 +20331,17 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t>$1,000</t>
+          <t>Priced individually (some free)</t>
         </is>
       </c>
       <c r="H37" s="15" t="n"/>
       <c r="I37" s="13" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="J37" s="13" t="inlineStr"/>
@@ -20481,139 +20363,57 @@
       </c>
       <c r="O37" s="14" t="inlineStr">
         <is>
-          <t>Flooring/construction company closed; pro tool package $1,000.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" outlineLevel="1">
-      <c r="A38" s="13" t="inlineStr">
-        <is>
-          <t>NYC / Long Island / NJ</t>
-        </is>
-      </c>
-      <c r="B38" s="14" t="inlineStr">
-        <is>
-          <t>New-in-box commercial refrigeration lot – 10 Beverage-Air &amp; Perlick units (bar never opened)</t>
-        </is>
-      </c>
-      <c r="C38" s="13" t="inlineStr">
-        <is>
-          <t>commercial refrigeration lot</t>
-        </is>
-      </c>
-      <c r="D38" s="13" t="inlineStr">
-        <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="E38" s="13" t="inlineStr">
-        <is>
-          <t>NY</t>
-        </is>
-      </c>
-      <c r="F38" s="13" t="n">
-        <v>192</v>
-      </c>
-      <c r="G38" s="13" t="inlineStr">
-        <is>
-          <t>$27,500 all 10 (or per unit $2,800–$4,150)</t>
-        </is>
-      </c>
-      <c r="H38" s="15" t="n"/>
-      <c r="I38" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="J38" s="13" t="inlineStr"/>
-      <c r="K38" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L38" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M38" s="13" t="inlineStr"/>
-      <c r="N38" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O38" s="14" t="inlineStr">
-        <is>
-          <t>Financial District. Never installed, factory packaging: 2 Beverage-Air HBF23HC-1-HS reach-in freezers ($4,150 ea), 3 HBR23HC-1-HS reach-in fridges ($3,550 ea), 1 UCR48AHC 48" undercounter ($2,800), 3 Perlick HC24FS4 glass frosters + 1 HC24RS4 beverage fridge ($2,850 ea). Seller says full retail $47,463 (about 42% off as a bundle). Updated Oct 14.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" outlineLevel="1">
-      <c r="A39" s="13" t="inlineStr">
-        <is>
-          <t>NYC / Long Island / NJ</t>
-        </is>
-      </c>
-      <c r="B39" s="14" t="inlineStr">
-        <is>
-          <t>Corporate caterer – Alto-Shaam, new boxed Avantco rice cookers &amp; Cadco oven, Perlick, MerryChef</t>
-        </is>
-      </c>
-      <c r="C39" s="13" t="inlineStr">
-        <is>
-          <t>auction</t>
-        </is>
-      </c>
-      <c r="D39" s="13" t="inlineStr">
-        <is>
-          <t>Jersey City</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="inlineStr">
-        <is>
-          <t>NJ</t>
-        </is>
-      </c>
-      <c r="F39" s="13" t="n">
-        <v>193</v>
-      </c>
-      <c r="G39" s="13" t="inlineStr">
-        <is>
-          <t>Live + webcast, 18% BP + 3%</t>
-        </is>
-      </c>
-      <c r="H39" s="15" t="n"/>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="J39" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-22 02:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K39" s="13" t="inlineStr">
-        <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
-        </is>
-      </c>
-      <c r="L39" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M39" s="13" t="inlineStr"/>
-      <c r="N39" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O39" s="14" t="inlineStr">
-        <is>
-          <t>Thu Oct 22 2 PM.</t>
-        </is>
-      </c>
+          <t>Ongoing shop-closing sale at 61 Main St, Tappan; many shop and hand tools, schedule a visit. Near the West Nyack body-shop sale (bl-054) for one trip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — CT / Hudson Valley</t>
+        </is>
+      </c>
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>10 item(s)</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="n"/>
+      <c r="D38" s="18" t="n"/>
+      <c r="E38" s="18" t="n"/>
+      <c r="F38" s="18" t="n"/>
+      <c r="G38" s="18" t="n"/>
+      <c r="H38" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="18" t="n"/>
+      <c r="J38" s="18" t="n"/>
+      <c r="K38" s="18" t="n"/>
+      <c r="L38" s="18" t="n"/>
+      <c r="M38" s="18" t="n"/>
+      <c r="N38" s="18" t="n"/>
+      <c r="O38" s="18" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>▸ NYC / Long Island / NJ  (23)</t>
+        </is>
+      </c>
+      <c r="B39" s="12" t="n"/>
+      <c r="C39" s="12" t="n"/>
+      <c r="D39" s="12" t="n"/>
+      <c r="E39" s="12" t="n"/>
+      <c r="F39" s="12" t="n"/>
+      <c r="G39" s="12" t="n"/>
+      <c r="H39" s="12" t="n"/>
+      <c r="I39" s="12" t="n"/>
+      <c r="J39" s="12" t="n"/>
+      <c r="K39" s="12" t="n"/>
+      <c r="L39" s="12" t="n"/>
+      <c r="M39" s="12" t="n"/>
+      <c r="N39" s="12" t="n"/>
+      <c r="O39" s="12" t="n"/>
     </row>
     <row r="40" outlineLevel="1">
       <c r="A40" s="13" t="inlineStr">
@@ -20623,17 +20423,17 @@
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>Lighting store closing – lease ended, up to 70% off showroom</t>
+          <t>Viva Margherita restaurant complete contents (building torn down)</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>restaurant closing</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>Jersey City</t>
+          <t>Edgewater</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
@@ -20642,17 +20442,17 @@
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
-          <t>up to 70% off</t>
+          <t>Complete contents / make offer</t>
         </is>
       </c>
       <c r="H40" s="15" t="n"/>
       <c r="I40" s="13" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="J40" s="13" t="inlineStr"/>
@@ -20674,7 +20474,7 @@
       </c>
       <c r="O40" s="14" t="inlineStr">
         <is>
-          <t>Lighting store closing, lease ended. Showroom inventory up to 70% off.</t>
+          <t>Address 163 Old River Road, Edgewater NJ. Building being torn down; complete restaurant contents for sale / make offer.</t>
         </is>
       </c>
     </row>
@@ -20686,43 +20486,51 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>Baonanas LLC ABC sale: turnkey ice cream / gelato / dessert shop equipment</t>
+          <t>Japanese BBQ &amp; bar – ~47 lots: Turbo Air, Hoshizaki ice machine, Pitco, Beverage-Air</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>restaurant / commercial kitchen contents</t>
+          <t>restaurant closing</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>Jersey City</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t>Accepting offers</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H41" s="15" t="n"/>
-      <c r="I41" s="13" t="inlineStr"/>
-      <c r="J41" s="13" t="inlineStr"/>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J41" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-21 04:00 PM ET</t>
+        </is>
+      </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>AuctionAdvisors</t>
-        </is>
-      </c>
-      <c r="L41" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L41" s="21" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M41" s="13" t="inlineStr"/>
@@ -20733,7 +20541,7 @@
       </c>
       <c r="O41" s="14" t="inlineStr">
         <is>
-          <t>181 Monticello Ave. Assignment for the benefit of creditors. IFI Panorama gelato display cases, refrigerated topping stations, commercial mixers, refrigerators/freezers, stainless worktables, ice machine, POS, smallwares, gelato carts, catering gear, FF&amp;E.</t>
+          <t>Wed Oct 21 4 PM. NYC 10013.</t>
         </is>
       </c>
     </row>
@@ -20745,42 +20553,42 @@
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>Tools / plumbing / MRO supply inventory – Hilti/DeWalt/Milwaukee, fittings, heat pumps</t>
+          <t>Flooring company closed – pro tool package</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>tools liquidation</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>Riverdale</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>$1,000</t>
         </is>
       </c>
       <c r="H42" s="15" t="n"/>
-      <c r="I42" s="13" t="inlineStr"/>
-      <c r="J42" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-30 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I42" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="J42" s="13" t="inlineStr"/>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L42" s="13" t="inlineStr">
@@ -20796,7 +20604,7 @@
       </c>
       <c r="O42" s="14" t="inlineStr">
         <is>
-          <t>Bulk resale inventory.</t>
+          <t>Flooring/construction company closed; pro tool package $1,000.</t>
         </is>
       </c>
     </row>
@@ -20808,42 +20616,42 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>Ice cream + cookie franchise equipment – Taylor soft-serve, Atosa, Blodgett</t>
+          <t>New-in-box commercial refrigeration lot – 10 Beverage-Air &amp; Perlick units (bar never opened)</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>commercial refrigeration lot</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
         <is>
-          <t>Riverdale</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="E43" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F43" s="13" t="n">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>$27,500 all 10 (or per unit $2,800–$4,150)</t>
         </is>
       </c>
       <c r="H43" s="15" t="n"/>
-      <c r="I43" s="13" t="inlineStr"/>
-      <c r="J43" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-05 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="J43" s="13" t="inlineStr"/>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L43" s="13" t="inlineStr">
@@ -20859,7 +20667,7 @@
       </c>
       <c r="O43" s="14" t="inlineStr">
         <is>
-          <t>Resellable units.</t>
+          <t>Financial District. Never installed, factory packaging: 2 Beverage-Air HBF23HC-1-HS reach-in freezers ($4,150 ea), 3 HBR23HC-1-HS reach-in fridges ($3,550 ea), 1 UCR48AHC 48" undercounter ($2,800), 3 Perlick HC24FS4 glass frosters + 1 HC24RS4 beverage fridge ($2,850 ea). Seller says full retail $47,463 (about 42% off as a bundle). Updated Oct 14.</t>
         </is>
       </c>
     </row>
@@ -20871,17 +20679,17 @@
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>U.S. Vision court-ordered liquidation: ~70,000 designer eyeglass/sunglass frames + optical/optometry equipment at ~80 former stores + IP</t>
+          <t>Corporate caterer – Alto-Shaam, new boxed Avantco rice cookers &amp; Cadco oven, Perlick, MerryChef</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>court-ordered retail chain liquidation</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>Montclair</t>
+          <t>Jersey City</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
@@ -20890,24 +20698,32 @@
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>Accepting offers (terms in offering memo, NDA required)</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H44" s="15" t="n"/>
-      <c r="I44" s="13" t="inlineStr"/>
-      <c r="J44" s="13" t="inlineStr"/>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="J44" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-22 02:00 PM ET</t>
+        </is>
+      </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>AuctionAdvisors</t>
-        </is>
-      </c>
-      <c r="L44" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L44" s="21" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M44" s="13" t="inlineStr"/>
@@ -20918,7 +20734,7 @@
       </c>
       <c r="O44" s="14" t="inlineStr">
         <is>
-          <t>Three-lot sale pursuant to court order; bids accepted for individual lots, combinations, or substantially all assets. Equipment is spread across ~80 former store locations. Not appliance-related; big-ticket bulk inventory play.</t>
+          <t>Thu Oct 22 2 PM.</t>
         </is>
       </c>
     </row>
@@ -20930,17 +20746,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>Wascomat commercial washers liquidation (22× W105, 6× W185, dryer panels)</t>
+          <t>Lighting store closing – lease ended, up to 70% off showroom</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>commercial laundry</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>Newark</t>
+          <t>Jersey City</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -20949,17 +20765,17 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>$500–$800 each / panels $150</t>
+          <t>up to 70% off</t>
         </is>
       </c>
       <c r="H45" s="15" t="n"/>
       <c r="I45" s="13" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-10-03</t>
         </is>
       </c>
       <c r="J45" s="13" t="inlineStr"/>
@@ -20981,7 +20797,7 @@
       </c>
       <c r="O45" s="14" t="inlineStr">
         <is>
-          <t>22× W105 @ $500, 6× W185 @ $800, 20 dryer panels $150. Commercial laundry liquidation.</t>
+          <t>Lighting store closing, lease ended. Showroom inventory up to 70% off.</t>
         </is>
       </c>
     </row>
@@ -20993,17 +20809,17 @@
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>Major food-service caterer – new-in-box True reach-ins, Beverage-Air, TurboChef, Resfab ventless fryer</t>
+          <t>Baonanas LLC ABC sale: turnkey ice cream / gelato / dessert shop equipment</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>restaurant / commercial kitchen contents</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>Parsippany</t>
+          <t>Jersey City</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -21012,27 +20828,19 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Accepting offers</t>
         </is>
       </c>
       <c r="H46" s="15" t="n"/>
-      <c r="I46" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="J46" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-03 02:00 PM ET</t>
-        </is>
-      </c>
+      <c r="I46" s="13" t="inlineStr"/>
+      <c r="J46" s="13" t="inlineStr"/>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>AuctionAdvisors</t>
         </is>
       </c>
       <c r="L46" s="13" t="inlineStr">
@@ -21048,7 +20856,7 @@
       </c>
       <c r="O46" s="14" t="inlineStr">
         <is>
-          <t>Tue Nov 3 2 PM, checkout Nov 4.</t>
+          <t>181 Monticello Ave. Assignment for the benefit of creditors. IFI Panorama gelato display cases, refrigerated topping stations, commercial mixers, refrigerators/freezers, stainless worktables, ice machine, POS, smallwares, gelato carts, catering gear, FF&amp;E.</t>
         </is>
       </c>
     </row>
@@ -21060,17 +20868,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>Business closing – 160 new Carnes exhaust fans</t>
+          <t>Tools / plumbing / MRO supply inventory – Hilti/DeWalt/Milwaukee, fittings, heat pumps</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>HVAC inventory</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>Kenilworth</t>
+          <t>Riverdale</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -21079,23 +20887,23 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
-          <t>$40 each or $5,000 all OBO</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H47" s="15" t="n"/>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="J47" s="13" t="inlineStr"/>
+      <c r="I47" s="13" t="inlineStr"/>
+      <c r="J47" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-30 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L47" s="13" t="inlineStr">
@@ -21111,7 +20919,7 @@
       </c>
       <c r="O47" s="14" t="inlineStr">
         <is>
-          <t>160 new Carnes 80CFM 1.0 sone exhaust fans. $40 each or $5,000 for all OBO. Business closing HVAC inventory.</t>
+          <t>Bulk resale inventory.</t>
         </is>
       </c>
     </row>
@@ -21123,17 +20931,17 @@
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>Air Systems Inc – sheet metal / HVAC fabrication shop liquidation</t>
+          <t>Ice cream + cookie franchise equipment – Taylor soft-serve, Atosa, Blodgett</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>HVAC shop liquidation</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>Kenilworth</t>
+          <t>Riverdale</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -21142,23 +20950,23 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>Timed online (15% BP)</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H48" s="15" t="n"/>
       <c r="I48" s="13" t="inlineStr"/>
       <c r="J48" s="13" t="inlineStr">
         <is>
-          <t>2026-10-29 11:00 AM ET</t>
+          <t>2026-11-05 11:00 AM ET</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner Auctions</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L48" s="13" t="inlineStr">
@@ -21174,7 +20982,7 @@
       </c>
       <c r="O48" s="14" t="inlineStr">
         <is>
-          <t>Vicon HVAC plasma; Flagler/Lockformer/Roto-Die/Engel fab; welders; Clark forklift; Genie Superlift; Ridgid/Milwaukee/DeWalt/Bosch/Hilti/Makita tools; AeroVent/Carnes exhaust fans; racking/scaffolding. Preview Oct 28–29 AM; pickup Oct 29 PM–Nov 4. Same town as Carnes fan CL lot.</t>
+          <t>Resellable units.</t>
         </is>
       </c>
     </row>
@@ -21186,17 +20994,17 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>Former Rush Bowls franchise ABC sale: commercial refrigeration, Vitamix blenders, ice &amp; beverage equipment</t>
+          <t>U.S. Vision court-ordered liquidation: ~70,000 designer eyeglass/sunglass frames + optical/optometry equipment at ~80 former stores + IP</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>restaurant / commercial kitchen contents</t>
+          <t>court-ordered retail chain liquidation</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>Westfield</t>
+          <t>Montclair</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -21205,11 +21013,11 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
-          <t>Accepting offers</t>
+          <t>Accepting offers (terms in offering memo, NDA required)</t>
         </is>
       </c>
       <c r="H49" s="15" t="n"/>
@@ -21233,7 +21041,7 @@
       </c>
       <c r="O49" s="14" t="inlineStr">
         <is>
-          <t>27 East Broad St. Assignment for the benefit of creditors of 333 Star Enterprises (d/b/a Rush Bowls). Commercial refrigeration/freezers, Vitamix blenders, stainless workstations/sinks, ice and beverage equipment, POS, shelving. Inspection by contacting the auctioneer.</t>
+          <t>Three-lot sale pursuant to court order; bids accepted for individual lots, combinations, or substantially all assets. Equipment is spread across ~80 former store locations. Not appliance-related; big-ticket bulk inventory play.</t>
         </is>
       </c>
     </row>
@@ -21245,17 +21053,17 @@
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>Bimmer Clinic business liquidation (BMW repair shop): vehicle lifts, forklift, skid steer, refrigerant recovery, shop tools &amp; equipment</t>
+          <t>Wascomat commercial washers liquidation (22× W105, 6× W185, dryer panels)</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>business liquidation auction</t>
+          <t>commercial laundry</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>South Amboy</t>
+          <t>Newark</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -21264,23 +21072,23 @@
         </is>
       </c>
       <c r="F50" s="13" t="n">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
-          <t>Timed online auction</t>
+          <t>$500–$800 each / panels $150</t>
         </is>
       </c>
       <c r="H50" s="15" t="n"/>
-      <c r="I50" s="13" t="inlineStr"/>
-      <c r="J50" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-12 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I50" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="J50" s="13" t="inlineStr"/>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>AJ Willner Auctions</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L50" s="13" t="inlineStr">
@@ -21296,7 +21104,7 @@
       </c>
       <c r="O50" s="14" t="inlineStr">
         <is>
-          <t>Ends Nov 12 11 AM EST.</t>
+          <t>22× W105 @ $500, 6× W185 @ $800, 20 dryer panels $150. Commercial laundry liquidation.</t>
         </is>
       </c>
     </row>
@@ -21308,17 +21116,17 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
+          <t>Major food-service caterer – new-in-box True reach-ins, Beverage-Air, TurboChef, Resfab ventless fryer</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>lien sale</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
         <is>
-          <t>Edison</t>
+          <t>Parsippany</t>
         </is>
       </c>
       <c r="E51" s="13" t="inlineStr">
@@ -21327,19 +21135,27 @@
         </is>
       </c>
       <c r="F51" s="13" t="n">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>
-          <t>Online auction, $2K load-out fee</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H51" s="15" t="n"/>
-      <c r="I51" s="13" t="inlineStr"/>
-      <c r="J51" s="13" t="inlineStr"/>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="J51" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-03 02:00 PM ET</t>
+        </is>
+      </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
       <c r="L51" s="13" t="inlineStr">
@@ -21355,7 +21171,7 @@
       </c>
       <c r="O51" s="14" t="inlineStr">
         <is>
-          <t>&gt;$100K new. Close date not captured.</t>
+          <t>Tue Nov 3 2 PM, checkout Nov 4.</t>
         </is>
       </c>
     </row>
@@ -21367,17 +21183,17 @@
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
+          <t>Business closing – 160 new Carnes exhaust fans</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>HVAC inventory</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>Edison</t>
+          <t>Kenilworth</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -21386,27 +21202,23 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
-          <t>Live + HiBid webcast, 18% BP + 3% card</t>
+          <t>$40 each or $5,000 all OBO</t>
         </is>
       </c>
       <c r="H52" s="15" t="n"/>
       <c r="I52" s="13" t="inlineStr">
         <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="J52" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-25 01:00 PM ET</t>
-        </is>
-      </c>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J52" s="13" t="inlineStr"/>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L52" s="13" t="inlineStr">
@@ -21414,11 +21226,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M52" s="21" t="inlineStr">
-        <is>
-          <t>FLIP</t>
-        </is>
-      </c>
+      <c r="M52" s="13" t="inlineStr"/>
       <c r="N52" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -21426,7 +21234,7 @@
       </c>
       <c r="O52" s="14" t="inlineStr">
         <is>
-          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
+          <t>160 new Carnes 80CFM 1.0 sone exhaust fans. $40 each or $5,000 for all OBO. Business closing HVAC inventory.</t>
         </is>
       </c>
     </row>
@@ -21438,17 +21246,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
+          <t>Air Systems Inc – sheet metal / HVAC fabrication shop liquidation</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>HVAC shop liquidation</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>East Brunswick</t>
+          <t>Kenilworth</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -21457,23 +21265,23 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>220</v>
+        <v>206</v>
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Timed online (15% BP)</t>
         </is>
       </c>
       <c r="H53" s="15" t="n"/>
       <c r="I53" s="13" t="inlineStr"/>
       <c r="J53" s="13" t="inlineStr">
         <is>
-          <t>2026-11-03 11:00 AM ET</t>
+          <t>2026-10-29 11:00 AM ET</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>A.J. Willner Auctions</t>
         </is>
       </c>
       <c r="L53" s="13" t="inlineStr">
@@ -21489,7 +21297,7 @@
       </c>
       <c r="O53" s="14" t="inlineStr">
         <is>
-          <t>Store inventory.</t>
+          <t>Vicon HVAC plasma; Flagler/Lockformer/Roto-Die/Engel fab; welders; Clark forklift; Genie Superlift; Ridgid/Milwaukee/DeWalt/Bosch/Hilti/Makita tools; AeroVent/Carnes exhaust fans; racking/scaffolding. Preview Oct 28–29 AM; pickup Oct 29 PM–Nov 4. Same town as Carnes fan CL lot.</t>
         </is>
       </c>
     </row>
@@ -21501,17 +21309,17 @@
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>Bakery/Cafe Somerville NJ – rack ovens, La Marzocco, food truck (~76 lots)</t>
+          <t>Former Rush Bowls franchise ABC sale: commercial refrigeration, Vitamix blenders, ice &amp; beverage equipment</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>restaurant / commercial kitchen contents</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>Somerville</t>
+          <t>Westfield</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -21520,27 +21328,19 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>Live webcast + online (18% BP online)</t>
+          <t>Accepting offers</t>
         </is>
       </c>
       <c r="H54" s="15" t="n"/>
-      <c r="I54" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
-      <c r="J54" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-26 02:00 PM ET</t>
-        </is>
-      </c>
+      <c r="I54" s="13" t="inlineStr"/>
+      <c r="J54" s="13" t="inlineStr"/>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>HiBid / Best Buy Auctioneers</t>
+          <t>AuctionAdvisors</t>
         </is>
       </c>
       <c r="L54" s="13" t="inlineStr">
@@ -21556,7 +21356,7 @@
       </c>
       <c r="O54" s="14" t="inlineStr">
         <is>
-          <t>Full bakery/cafe commercial kitchen: food truck w/ pizza oven, La Marzocco espresso, Mazzer, Baxter + Empire Logiudice rack ovens, dough depositor, Globe floor mixer, Artic Air / SS refrigeration, fryers, Vitamix, Robot Coupe, display cases, dining furniture. Preview 11 AM sale day; checkout Tue 10/27.</t>
+          <t>27 East Broad St. Assignment for the benefit of creditors of 333 Star Enterprises (d/b/a Rush Bowls). Commercial refrigeration/freezers, Vitamix blenders, stainless workstations/sinks, ice and beverage equipment, POS, shelving. Inspection by contacting the auctioneer.</t>
         </is>
       </c>
     </row>
@@ -21568,17 +21368,17 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Ability to Work kitchen and store – commercial kitchen + store fixtures (~135 lots)</t>
+          <t>Bimmer Clinic business liquidation (BMW repair shop): vehicle lifts, forklift, skid steer, refrigerant recovery, shop tools &amp; equipment</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>business liquidation auction</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>Flemington</t>
+          <t>South Amboy</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -21587,23 +21387,23 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>237</v>
+        <v>213</v>
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
-          <t>Timed online (15% BP)</t>
+          <t>Timed online auction</t>
         </is>
       </c>
       <c r="H55" s="15" t="n"/>
       <c r="I55" s="13" t="inlineStr"/>
       <c r="J55" s="13" t="inlineStr">
         <is>
-          <t>2026-10-27 11:02 AM ET</t>
+          <t>2026-11-12 11:00 AM ET</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>HiBid</t>
+          <t>AJ Willner Auctions</t>
         </is>
       </c>
       <c r="L55" s="13" t="inlineStr">
@@ -21619,7 +21419,7 @@
       </c>
       <c r="O55" s="14" t="inlineStr">
         <is>
-          <t>Apprentice/hospitality training cafe-kitchen and store dispersal. Preview 9–11 AM sale day; removal Oct 27 noon–Oct 29.</t>
+          <t>Ends Nov 12 11 AM EST.</t>
         </is>
       </c>
     </row>
@@ -21631,17 +21431,17 @@
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
+          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>showroom closing</t>
+          <t>lien sale</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>Lawrenceville</t>
+          <t>Edison</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -21650,23 +21450,19 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>Online auction, 18% BP</t>
+          <t>Online auction, $2K load-out fee</t>
         </is>
       </c>
       <c r="H56" s="15" t="n"/>
       <c r="I56" s="13" t="inlineStr"/>
-      <c r="J56" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-27 09:00 AM ET</t>
-        </is>
-      </c>
+      <c r="J56" s="13" t="inlineStr"/>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L56" s="13" t="inlineStr">
@@ -21682,7 +21478,7 @@
       </c>
       <c r="O56" s="14" t="inlineStr">
         <is>
-          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
+          <t>&gt;$100K new. Close date not captured.</t>
         </is>
       </c>
     </row>
@@ -21694,17 +21490,17 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
+          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
         </is>
       </c>
       <c r="C57" s="13" t="inlineStr">
         <is>
-          <t>showroom closing</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>Cherry Hill</t>
+          <t>Edison</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -21713,23 +21509,27 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>266</v>
+        <v>217</v>
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
-          <t>Online auction, openers ~$0.50</t>
+          <t>Live + HiBid webcast, 18% BP + 3% card</t>
         </is>
       </c>
       <c r="H57" s="15" t="n"/>
-      <c r="I57" s="13" t="inlineStr"/>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="J57" s="13" t="inlineStr">
         <is>
-          <t>2026-11-02 11:00 AM ET</t>
+          <t>2026-10-25 01:00 PM ET</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
       <c r="L57" s="13" t="inlineStr">
@@ -21737,7 +21537,11 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M57" s="13" t="inlineStr"/>
+      <c r="M57" s="20" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
       <c r="N57" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -21745,106 +21549,184 @@
       </c>
       <c r="O57" s="14" t="inlineStr">
         <is>
-          <t>Lots close from Nov 2 11 AM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — NYC / Long Island / NJ</t>
-        </is>
-      </c>
-      <c r="B58" s="17" t="inlineStr">
-        <is>
-          <t>23 item(s)</t>
-        </is>
-      </c>
-      <c r="C58" s="18" t="n"/>
-      <c r="D58" s="18" t="n"/>
-      <c r="E58" s="18" t="n"/>
-      <c r="F58" s="18" t="n"/>
-      <c r="G58" s="18" t="n"/>
-      <c r="H58" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="18" t="n"/>
-      <c r="J58" s="18" t="n"/>
-      <c r="K58" s="18" t="n"/>
-      <c r="L58" s="18" t="n"/>
-      <c r="M58" s="18" t="n"/>
-      <c r="N58" s="18" t="n"/>
-      <c r="O58" s="18" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t>▸ Eastern PA / Mid-Atlantic  (1)</t>
-        </is>
-      </c>
-      <c r="B59" s="12" t="n"/>
-      <c r="C59" s="12" t="n"/>
-      <c r="D59" s="12" t="n"/>
-      <c r="E59" s="12" t="n"/>
-      <c r="F59" s="12" t="n"/>
-      <c r="G59" s="12" t="n"/>
-      <c r="H59" s="12" t="n"/>
-      <c r="I59" s="12" t="n"/>
-      <c r="J59" s="12" t="n"/>
-      <c r="K59" s="12" t="n"/>
-      <c r="L59" s="12" t="n"/>
-      <c r="M59" s="12" t="n"/>
-      <c r="N59" s="12" t="n"/>
-      <c r="O59" s="12" t="n"/>
+          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" outlineLevel="1">
+      <c r="A58" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B58" s="14" t="inlineStr">
+        <is>
+          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
+        </is>
+      </c>
+      <c r="C58" s="13" t="inlineStr">
+        <is>
+          <t>store closing</t>
+        </is>
+      </c>
+      <c r="D58" s="13" t="inlineStr">
+        <is>
+          <t>East Brunswick</t>
+        </is>
+      </c>
+      <c r="E58" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F58" s="13" t="n">
+        <v>220</v>
+      </c>
+      <c r="G58" s="13" t="inlineStr">
+        <is>
+          <t>Online auction</t>
+        </is>
+      </c>
+      <c r="H58" s="15" t="n"/>
+      <c r="I58" s="13" t="inlineStr"/>
+      <c r="J58" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-03 11:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K58" s="13" t="inlineStr">
+        <is>
+          <t>A.J. Willner</t>
+        </is>
+      </c>
+      <c r="L58" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M58" s="13" t="inlineStr"/>
+      <c r="N58" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O58" s="14" t="inlineStr">
+        <is>
+          <t>Store inventory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" outlineLevel="1">
+      <c r="A59" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B59" s="14" t="inlineStr">
+        <is>
+          <t>Bakery/Cafe Somerville NJ – rack ovens, La Marzocco, food truck (~76 lots)</t>
+        </is>
+      </c>
+      <c r="C59" s="13" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="D59" s="13" t="inlineStr">
+        <is>
+          <t>Somerville</t>
+        </is>
+      </c>
+      <c r="E59" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F59" s="13" t="n">
+        <v>224</v>
+      </c>
+      <c r="G59" s="13" t="inlineStr">
+        <is>
+          <t>Live webcast + online (18% BP online)</t>
+        </is>
+      </c>
+      <c r="H59" s="15" t="n"/>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J59" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-26 02:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K59" s="13" t="inlineStr">
+        <is>
+          <t>HiBid / Best Buy Auctioneers</t>
+        </is>
+      </c>
+      <c r="L59" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M59" s="13" t="inlineStr"/>
+      <c r="N59" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O59" s="14" t="inlineStr">
+        <is>
+          <t>Full bakery/cafe commercial kitchen: food truck w/ pizza oven, La Marzocco espresso, Mazzer, Baxter + Empire Logiudice rack ovens, dough depositor, Globe floor mixer, Artic Air / SS refrigeration, fryers, Vitamix, Robot Coupe, display cases, dining furniture. Preview 11 AM sale day; checkout Tue 10/27.</t>
+        </is>
+      </c>
     </row>
     <row r="60" outlineLevel="1">
       <c r="A60" s="13" t="inlineStr">
         <is>
-          <t>Eastern PA / Mid-Atlantic</t>
+          <t>NYC / Long Island / NJ</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>Piscitello's Home Center closing after 68 years: storewide 20% off liquidation (hardware, lumber, doors, windows, kitchen/bath)</t>
+          <t>Ability to Work kitchen and store – commercial kitchen + store fixtures (~135 lots)</t>
         </is>
       </c>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>Wilson</t>
+          <t>Flemington</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
-          <t>20% off storewide (all sales final)</t>
+          <t>Timed online (15% BP)</t>
         </is>
       </c>
       <c r="H60" s="15" t="n"/>
-      <c r="I60" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
+      <c r="I60" s="13" t="inlineStr"/>
       <c r="J60" s="13" t="inlineStr">
         <is>
-          <t>2026-10-30 06:00 PM ET</t>
+          <t>2026-10-27 11:02 AM ET</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
         <is>
-          <t>LehighValley.com article</t>
+          <t>HiBid</t>
         </is>
       </c>
       <c r="L60" s="13" t="inlineStr">
@@ -21860,211 +21742,203 @@
       </c>
       <c r="O60" s="14" t="inlineStr">
         <is>
-          <t>2300 Wood Ave, Wilson Borough (Easton area). Final day Oct 30. Retail-floor sale, not a bulk lot; ask in person about buying remaining stock outright.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — Eastern PA / Mid-Atlantic</t>
-        </is>
-      </c>
-      <c r="B61" s="17" t="inlineStr">
-        <is>
-          <t>1 item(s)</t>
-        </is>
-      </c>
-      <c r="C61" s="18" t="n"/>
-      <c r="D61" s="18" t="n"/>
-      <c r="E61" s="18" t="n"/>
-      <c r="F61" s="18" t="n"/>
-      <c r="G61" s="18" t="n"/>
-      <c r="H61" s="19" t="n">
+          <t>Apprentice/hospitality training cafe-kitchen and store dispersal. Preview 9–11 AM sale day; removal Oct 27 noon–Oct 29.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" outlineLevel="1">
+      <c r="A61" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
+        <is>
+          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
+        </is>
+      </c>
+      <c r="C61" s="13" t="inlineStr">
+        <is>
+          <t>showroom closing</t>
+        </is>
+      </c>
+      <c r="D61" s="13" t="inlineStr">
+        <is>
+          <t>Lawrenceville</t>
+        </is>
+      </c>
+      <c r="E61" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F61" s="13" t="n">
+        <v>239</v>
+      </c>
+      <c r="G61" s="13" t="inlineStr">
+        <is>
+          <t>Online auction, 18% BP</t>
+        </is>
+      </c>
+      <c r="H61" s="15" t="n"/>
+      <c r="I61" s="13" t="inlineStr"/>
+      <c r="J61" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K61" s="13" t="inlineStr">
+        <is>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L61" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M61" s="13" t="inlineStr"/>
+      <c r="N61" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O61" s="14" t="inlineStr">
+        <is>
+          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" outlineLevel="1">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t>showroom closing</t>
+        </is>
+      </c>
+      <c r="D62" s="13" t="inlineStr">
+        <is>
+          <t>Cherry Hill</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F62" s="13" t="n">
+        <v>266</v>
+      </c>
+      <c r="G62" s="13" t="inlineStr">
+        <is>
+          <t>Online auction, openers ~$0.50</t>
+        </is>
+      </c>
+      <c r="H62" s="15" t="n"/>
+      <c r="I62" s="13" t="inlineStr"/>
+      <c r="J62" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-02 11:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="inlineStr">
+        <is>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L62" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M62" s="13" t="inlineStr"/>
+      <c r="N62" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O62" s="14" t="inlineStr">
+        <is>
+          <t>Lots close from Nov 2 11 AM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B63" s="17" t="inlineStr">
+        <is>
+          <t>23 item(s)</t>
+        </is>
+      </c>
+      <c r="C63" s="18" t="n"/>
+      <c r="D63" s="18" t="n"/>
+      <c r="E63" s="18" t="n"/>
+      <c r="F63" s="18" t="n"/>
+      <c r="G63" s="18" t="n"/>
+      <c r="H63" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I61" s="18" t="n"/>
-      <c r="J61" s="18" t="n"/>
-      <c r="K61" s="18" t="n"/>
-      <c r="L61" s="18" t="n"/>
-      <c r="M61" s="18" t="n"/>
-      <c r="N61" s="18" t="n"/>
-      <c r="O61" s="18" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="11" t="inlineStr">
-        <is>
-          <t>▸ Western PA / Ohio Valley  (3)</t>
-        </is>
-      </c>
-      <c r="B62" s="12" t="n"/>
-      <c r="C62" s="12" t="n"/>
-      <c r="D62" s="12" t="n"/>
-      <c r="E62" s="12" t="n"/>
-      <c r="F62" s="12" t="n"/>
-      <c r="G62" s="12" t="n"/>
-      <c r="H62" s="12" t="n"/>
-      <c r="I62" s="12" t="n"/>
-      <c r="J62" s="12" t="n"/>
-      <c r="K62" s="12" t="n"/>
-      <c r="L62" s="12" t="n"/>
-      <c r="M62" s="12" t="n"/>
-      <c r="N62" s="12" t="n"/>
-      <c r="O62" s="12" t="n"/>
-    </row>
-    <row r="63" outlineLevel="1">
-      <c r="A63" s="13" t="inlineStr">
-        <is>
-          <t>Western PA / Ohio Valley</t>
-        </is>
-      </c>
-      <c r="B63" s="14" t="inlineStr">
-        <is>
-          <t>Petrunak's Hardware Store liquidation Day 1 (530 lots: doors, hardware, tools, building supplies)</t>
-        </is>
-      </c>
-      <c r="C63" s="13" t="inlineStr">
-        <is>
-          <t>store closing auction</t>
-        </is>
-      </c>
-      <c r="D63" s="13" t="inlineStr">
-        <is>
-          <t>Windber</t>
-        </is>
-      </c>
-      <c r="E63" s="13" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="F63" s="13" t="n">
-        <v>437</v>
-      </c>
-      <c r="G63" s="13" t="inlineStr">
-        <is>
-          <t>Timed online auction (530 lots)</t>
-        </is>
-      </c>
-      <c r="H63" s="15" t="n"/>
-      <c r="I63" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="J63" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 08:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K63" s="13" t="inlineStr">
-        <is>
-          <t>Carey Auctions</t>
-        </is>
-      </c>
-      <c r="L63" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M63" s="13" t="inlineStr"/>
-      <c r="N63" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O63" s="14" t="inlineStr">
-        <is>
-          <t>Ends Oct 21 7 PM CDT (8 PM ET). 1500 Somerset Ave, Windber PA. Pickups Oct 24-28. Hardware store, not appliance parts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" outlineLevel="1">
-      <c r="A64" s="13" t="inlineStr">
-        <is>
-          <t>Western PA / Ohio Valley</t>
-        </is>
-      </c>
-      <c r="B64" s="14" t="inlineStr">
-        <is>
-          <t>Petrunak's Hardware Store liquidation Day 2 (433 lots)</t>
-        </is>
-      </c>
-      <c r="C64" s="13" t="inlineStr">
-        <is>
-          <t>store closing auction</t>
-        </is>
-      </c>
-      <c r="D64" s="13" t="inlineStr">
-        <is>
-          <t>Windber</t>
-        </is>
-      </c>
-      <c r="E64" s="13" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="F64" s="13" t="n">
-        <v>437</v>
-      </c>
-      <c r="G64" s="13" t="inlineStr">
-        <is>
-          <t>Timed online auction (433 lots)</t>
-        </is>
-      </c>
-      <c r="H64" s="15" t="n"/>
-      <c r="I64" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="J64" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-22 08:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K64" s="13" t="inlineStr">
-        <is>
-          <t>Carey Auctions</t>
-        </is>
-      </c>
-      <c r="L64" s="20" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
-        </is>
-      </c>
-      <c r="M64" s="13" t="inlineStr"/>
-      <c r="N64" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O64" s="14" t="inlineStr">
-        <is>
-          <t>Ends Oct 22 7 PM CDT (8 PM ET). Same store as Day 1; pickups Oct 24-28.</t>
-        </is>
-      </c>
+      <c r="I63" s="18" t="n"/>
+      <c r="J63" s="18" t="n"/>
+      <c r="K63" s="18" t="n"/>
+      <c r="L63" s="18" t="n"/>
+      <c r="M63" s="18" t="n"/>
+      <c r="N63" s="18" t="n"/>
+      <c r="O63" s="18" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>▸ Eastern PA / Mid-Atlantic  (1)</t>
+        </is>
+      </c>
+      <c r="B64" s="12" t="n"/>
+      <c r="C64" s="12" t="n"/>
+      <c r="D64" s="12" t="n"/>
+      <c r="E64" s="12" t="n"/>
+      <c r="F64" s="12" t="n"/>
+      <c r="G64" s="12" t="n"/>
+      <c r="H64" s="12" t="n"/>
+      <c r="I64" s="12" t="n"/>
+      <c r="J64" s="12" t="n"/>
+      <c r="K64" s="12" t="n"/>
+      <c r="L64" s="12" t="n"/>
+      <c r="M64" s="12" t="n"/>
+      <c r="N64" s="12" t="n"/>
+      <c r="O64" s="12" t="n"/>
     </row>
     <row r="65" outlineLevel="1">
       <c r="A65" s="13" t="inlineStr">
         <is>
-          <t>Western PA / Ohio Valley</t>
+          <t>Eastern PA / Mid-Atlantic</t>
         </is>
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>Millers Pizza &amp; More – pizza business, commercial kitchen &amp; event space contents (362 lots)</t>
+          <t>Piscitello's Home Center closing after 68 years: storewide 20% off liquidation (hardware, lumber, doors, windows, kitchen/bath)</t>
         </is>
       </c>
       <c r="C65" s="13" t="inlineStr">
         <is>
-          <t>restaurant / commercial kitchen contents</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>Everson</t>
+          <t>Wilson</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
@@ -22073,23 +21947,27 @@
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>478</v>
+        <v>250</v>
       </c>
       <c r="G65" s="13" t="inlineStr">
         <is>
-          <t>Online auction, 15% buyer premium</t>
+          <t>20% off storewide (all sales final)</t>
         </is>
       </c>
       <c r="H65" s="15" t="n"/>
-      <c r="I65" s="13" t="inlineStr"/>
+      <c r="I65" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
       <c r="J65" s="13" t="inlineStr">
         <is>
-          <t>2026-10-25 07:00 PM ET</t>
+          <t>2026-10-30 06:00 PM ET</t>
         </is>
       </c>
       <c r="K65" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Bid Local LLC)</t>
+          <t>LehighValley.com article</t>
         </is>
       </c>
       <c r="L65" s="13" t="inlineStr">
@@ -22105,19 +21983,19 @@
       </c>
       <c r="O65" s="14" t="inlineStr">
         <is>
-          <t>Property of Millers Pizza and More LLC; online-only, 362 lots, lots begin closing Oct 25 7 PM. Pickup Everson PA by appointment Tue 10/27 and Wed 10/28. Building (4,500 sq ft) to be auctioned separately.</t>
+          <t>2300 Wood Ave, Wilson Borough (Easton area). Final day Oct 30. Retail-floor sale, not a bulk lot; ask in person about buying remaining stock outright.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="17" t="inlineStr">
         <is>
-          <t>Subtotal — Western PA / Ohio Valley</t>
+          <t>Subtotal — Eastern PA / Mid-Atlantic</t>
         </is>
       </c>
       <c r="B66" s="17" t="inlineStr">
         <is>
-          <t>3 item(s)</t>
+          <t>1 item(s)</t>
         </is>
       </c>
       <c r="C66" s="18" t="n"/>
@@ -22139,7 +22017,7 @@
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t>▸ Upstate / Western NY  (1)</t>
+          <t>▸ Western PA / Ohio Valley  (3)</t>
         </is>
       </c>
       <c r="B67" s="12" t="n"/>
@@ -22160,52 +22038,56 @@
     <row r="68" outlineLevel="1">
       <c r="A68" s="13" t="inlineStr">
         <is>
-          <t>Upstate / Western NY</t>
+          <t>Western PA / Ohio Valley</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>Restaurant &amp; fitness equipment</t>
+          <t>Petrunak's Hardware Store liquidation Day 1 (530 lots: doors, hardware, tools, building supplies)</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>store closing auction</t>
         </is>
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>Williamsville</t>
+          <t>Windber</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F68" s="13" t="n">
-        <v>408</v>
+        <v>437</v>
       </c>
       <c r="G68" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Timed online auction (530 lots)</t>
         </is>
       </c>
       <c r="H68" s="15" t="n"/>
-      <c r="I68" s="13" t="inlineStr"/>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
       <c r="J68" s="13" t="inlineStr">
         <is>
-          <t>2026-10-26 07:30 PM ET</t>
+          <t>2026-10-21 08:00 PM ET</t>
         </is>
       </c>
       <c r="K68" s="13" t="inlineStr">
         <is>
-          <t>Cash Auctions</t>
-        </is>
-      </c>
-      <c r="L68" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>Carey Auctions</t>
+        </is>
+      </c>
+      <c r="L68" s="21" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M68" s="13" t="inlineStr"/>
@@ -22216,546 +22098,898 @@
       </c>
       <c r="O68" s="14" t="inlineStr">
         <is>
+          <t>Ends Oct 21 7 PM CDT (8 PM ET). 1500 Somerset Ave, Windber PA. Pickups Oct 24-28. Hardware store, not appliance parts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" outlineLevel="1">
+      <c r="A69" s="13" t="inlineStr">
+        <is>
+          <t>Western PA / Ohio Valley</t>
+        </is>
+      </c>
+      <c r="B69" s="14" t="inlineStr">
+        <is>
+          <t>Petrunak's Hardware Store liquidation Day 2 (433 lots)</t>
+        </is>
+      </c>
+      <c r="C69" s="13" t="inlineStr">
+        <is>
+          <t>store closing auction</t>
+        </is>
+      </c>
+      <c r="D69" s="13" t="inlineStr">
+        <is>
+          <t>Windber</t>
+        </is>
+      </c>
+      <c r="E69" s="13" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="F69" s="13" t="n">
+        <v>437</v>
+      </c>
+      <c r="G69" s="13" t="inlineStr">
+        <is>
+          <t>Timed online auction (433 lots)</t>
+        </is>
+      </c>
+      <c r="H69" s="15" t="n"/>
+      <c r="I69" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="J69" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-22 08:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K69" s="13" t="inlineStr">
+        <is>
+          <t>Carey Auctions</t>
+        </is>
+      </c>
+      <c r="L69" s="21" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
+        </is>
+      </c>
+      <c r="M69" s="13" t="inlineStr"/>
+      <c r="N69" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O69" s="14" t="inlineStr">
+        <is>
+          <t>Ends Oct 22 7 PM CDT (8 PM ET). Same store as Day 1; pickups Oct 24-28.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" outlineLevel="1">
+      <c r="A70" s="13" t="inlineStr">
+        <is>
+          <t>Western PA / Ohio Valley</t>
+        </is>
+      </c>
+      <c r="B70" s="14" t="inlineStr">
+        <is>
+          <t>Millers Pizza &amp; More – pizza business, commercial kitchen &amp; event space contents (362 lots)</t>
+        </is>
+      </c>
+      <c r="C70" s="13" t="inlineStr">
+        <is>
+          <t>restaurant / commercial kitchen contents</t>
+        </is>
+      </c>
+      <c r="D70" s="13" t="inlineStr">
+        <is>
+          <t>Everson</t>
+        </is>
+      </c>
+      <c r="E70" s="13" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="F70" s="13" t="n">
+        <v>478</v>
+      </c>
+      <c r="G70" s="13" t="inlineStr">
+        <is>
+          <t>Online auction, 15% buyer premium</t>
+        </is>
+      </c>
+      <c r="H70" s="15" t="n"/>
+      <c r="I70" s="13" t="inlineStr"/>
+      <c r="J70" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-25 07:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K70" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (Bid Local LLC)</t>
+        </is>
+      </c>
+      <c r="L70" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M70" s="13" t="inlineStr"/>
+      <c r="N70" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O70" s="14" t="inlineStr">
+        <is>
+          <t>Property of Millers Pizza and More LLC; online-only, 362 lots, lots begin closing Oct 25 7 PM. Pickup Everson PA by appointment Tue 10/27 and Wed 10/28. Building (4,500 sq ft) to be auctioned separately.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Western PA / Ohio Valley</t>
+        </is>
+      </c>
+      <c r="B71" s="17" t="inlineStr">
+        <is>
+          <t>3 item(s)</t>
+        </is>
+      </c>
+      <c r="C71" s="18" t="n"/>
+      <c r="D71" s="18" t="n"/>
+      <c r="E71" s="18" t="n"/>
+      <c r="F71" s="18" t="n"/>
+      <c r="G71" s="18" t="n"/>
+      <c r="H71" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="18" t="n"/>
+      <c r="J71" s="18" t="n"/>
+      <c r="K71" s="18" t="n"/>
+      <c r="L71" s="18" t="n"/>
+      <c r="M71" s="18" t="n"/>
+      <c r="N71" s="18" t="n"/>
+      <c r="O71" s="18" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="11" t="inlineStr">
+        <is>
+          <t>▸ Upstate / Western NY  (1)</t>
+        </is>
+      </c>
+      <c r="B72" s="12" t="n"/>
+      <c r="C72" s="12" t="n"/>
+      <c r="D72" s="12" t="n"/>
+      <c r="E72" s="12" t="n"/>
+      <c r="F72" s="12" t="n"/>
+      <c r="G72" s="12" t="n"/>
+      <c r="H72" s="12" t="n"/>
+      <c r="I72" s="12" t="n"/>
+      <c r="J72" s="12" t="n"/>
+      <c r="K72" s="12" t="n"/>
+      <c r="L72" s="12" t="n"/>
+      <c r="M72" s="12" t="n"/>
+      <c r="N72" s="12" t="n"/>
+      <c r="O72" s="12" t="n"/>
+    </row>
+    <row r="73" outlineLevel="1">
+      <c r="A73" s="13" t="inlineStr">
+        <is>
+          <t>Upstate / Western NY</t>
+        </is>
+      </c>
+      <c r="B73" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant &amp; fitness equipment</t>
+        </is>
+      </c>
+      <c r="C73" s="13" t="inlineStr">
+        <is>
+          <t>restaurant</t>
+        </is>
+      </c>
+      <c r="D73" s="13" t="inlineStr">
+        <is>
+          <t>Williamsville</t>
+        </is>
+      </c>
+      <c r="E73" s="13" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F73" s="13" t="n">
+        <v>408</v>
+      </c>
+      <c r="G73" s="13" t="inlineStr">
+        <is>
+          <t>Online auction</t>
+        </is>
+      </c>
+      <c r="H73" s="15" t="n"/>
+      <c r="I73" s="13" t="inlineStr"/>
+      <c r="J73" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-26 07:30 PM ET</t>
+        </is>
+      </c>
+      <c r="K73" s="13" t="inlineStr">
+        <is>
+          <t>Cash Auctions</t>
+        </is>
+      </c>
+      <c r="L73" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M73" s="13" t="inlineStr"/>
+      <c r="N73" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O73" s="14" t="inlineStr">
+        <is>
           <t>Lots not reviewed.</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="17" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Upstate / Western NY</t>
         </is>
       </c>
-      <c r="B69" s="17" t="inlineStr">
+      <c r="B74" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C69" s="18" t="n"/>
-      <c r="D69" s="18" t="n"/>
-      <c r="E69" s="18" t="n"/>
-      <c r="F69" s="18" t="n"/>
-      <c r="G69" s="18" t="n"/>
-      <c r="H69" s="19" t="n">
+      <c r="C74" s="18" t="n"/>
+      <c r="D74" s="18" t="n"/>
+      <c r="E74" s="18" t="n"/>
+      <c r="F74" s="18" t="n"/>
+      <c r="G74" s="18" t="n"/>
+      <c r="H74" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I69" s="18" t="n"/>
-      <c r="J69" s="18" t="n"/>
-      <c r="K69" s="18" t="n"/>
-      <c r="L69" s="18" t="n"/>
-      <c r="M69" s="18" t="n"/>
-      <c r="N69" s="18" t="n"/>
-      <c r="O69" s="18" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="11" t="inlineStr">
+      <c r="I74" s="18" t="n"/>
+      <c r="J74" s="18" t="n"/>
+      <c r="K74" s="18" t="n"/>
+      <c r="L74" s="18" t="n"/>
+      <c r="M74" s="18" t="n"/>
+      <c r="N74" s="18" t="n"/>
+      <c r="O74" s="18" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
         <is>
           <t>▸ Virginia  (1)</t>
         </is>
       </c>
-      <c r="B70" s="12" t="n"/>
-      <c r="C70" s="12" t="n"/>
-      <c r="D70" s="12" t="n"/>
-      <c r="E70" s="12" t="n"/>
-      <c r="F70" s="12" t="n"/>
-      <c r="G70" s="12" t="n"/>
-      <c r="H70" s="12" t="n"/>
-      <c r="I70" s="12" t="n"/>
-      <c r="J70" s="12" t="n"/>
-      <c r="K70" s="12" t="n"/>
-      <c r="L70" s="12" t="n"/>
-      <c r="M70" s="12" t="n"/>
-      <c r="N70" s="12" t="n"/>
-      <c r="O70" s="12" t="n"/>
-    </row>
-    <row r="71" outlineLevel="1">
-      <c r="A71" s="13" t="inlineStr">
+      <c r="B75" s="12" t="n"/>
+      <c r="C75" s="12" t="n"/>
+      <c r="D75" s="12" t="n"/>
+      <c r="E75" s="12" t="n"/>
+      <c r="F75" s="12" t="n"/>
+      <c r="G75" s="12" t="n"/>
+      <c r="H75" s="12" t="n"/>
+      <c r="I75" s="12" t="n"/>
+      <c r="J75" s="12" t="n"/>
+      <c r="K75" s="12" t="n"/>
+      <c r="L75" s="12" t="n"/>
+      <c r="M75" s="12" t="n"/>
+      <c r="N75" s="12" t="n"/>
+      <c r="O75" s="12" t="n"/>
+    </row>
+    <row r="76" outlineLevel="1">
+      <c r="A76" s="13" t="inlineStr">
         <is>
           <t>Virginia</t>
         </is>
       </c>
-      <c r="B71" s="14" t="inlineStr">
+      <c r="B76" s="14" t="inlineStr">
         <is>
           <t>Haynes Furniture / The Dump – 12 stores closing (furniture, mattresses)</t>
         </is>
       </c>
-      <c r="C71" s="13" t="inlineStr">
+      <c r="C76" s="13" t="inlineStr">
         <is>
           <t>retail GOB</t>
         </is>
       </c>
-      <c r="D71" s="13" t="inlineStr">
+      <c r="D76" s="13" t="inlineStr">
         <is>
           <t>Virginia Beach</t>
         </is>
       </c>
-      <c r="E71" s="13" t="inlineStr">
+      <c r="E76" s="13" t="inlineStr">
         <is>
           <t>VA</t>
         </is>
       </c>
-      <c r="F71" s="13" t="n">
+      <c r="F76" s="13" t="n">
         <v>456</v>
       </c>
-      <c r="G71" s="13" t="inlineStr">
+      <c r="G76" s="13" t="inlineStr">
         <is>
           <t>Retail GOB markdowns</t>
         </is>
       </c>
-      <c r="H71" s="15" t="n"/>
-      <c r="I71" s="13" t="inlineStr">
+      <c r="H76" s="15" t="n"/>
+      <c r="I76" s="13" t="inlineStr">
         <is>
           <t>2026-10-08</t>
         </is>
       </c>
-      <c r="J71" s="13" t="inlineStr"/>
-      <c r="K71" s="13" t="inlineStr">
+      <c r="J76" s="13" t="inlineStr"/>
+      <c r="K76" s="13" t="inlineStr">
         <is>
           <t>SB360 (PR Newswire)</t>
         </is>
       </c>
-      <c r="L71" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M71" s="13" t="inlineStr"/>
-      <c r="N71" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O71" s="14" t="inlineStr">
+      <c r="L76" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M76" s="13" t="inlineStr"/>
+      <c r="N76" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O76" s="14" t="inlineStr">
         <is>
           <t>Posted Oct 8. Multi-state (VA/AZ/GA/IL/TX); pinned at Virginia Beach. Home goods only.</t>
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="17" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Virginia</t>
         </is>
       </c>
-      <c r="B72" s="17" t="inlineStr">
+      <c r="B77" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C72" s="18" t="n"/>
-      <c r="D72" s="18" t="n"/>
-      <c r="E72" s="18" t="n"/>
-      <c r="F72" s="18" t="n"/>
-      <c r="G72" s="18" t="n"/>
-      <c r="H72" s="19" t="n">
+      <c r="C77" s="18" t="n"/>
+      <c r="D77" s="18" t="n"/>
+      <c r="E77" s="18" t="n"/>
+      <c r="F77" s="18" t="n"/>
+      <c r="G77" s="18" t="n"/>
+      <c r="H77" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I72" s="18" t="n"/>
-      <c r="J72" s="18" t="n"/>
-      <c r="K72" s="18" t="n"/>
-      <c r="L72" s="18" t="n"/>
-      <c r="M72" s="18" t="n"/>
-      <c r="N72" s="18" t="n"/>
-      <c r="O72" s="18" t="n"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="11" t="inlineStr">
+      <c r="I77" s="18" t="n"/>
+      <c r="J77" s="18" t="n"/>
+      <c r="K77" s="18" t="n"/>
+      <c r="L77" s="18" t="n"/>
+      <c r="M77" s="18" t="n"/>
+      <c r="N77" s="18" t="n"/>
+      <c r="O77" s="18" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t>▸ Southeast  (1)</t>
+        </is>
+      </c>
+      <c r="B78" s="12" t="n"/>
+      <c r="C78" s="12" t="n"/>
+      <c r="D78" s="12" t="n"/>
+      <c r="E78" s="12" t="n"/>
+      <c r="F78" s="12" t="n"/>
+      <c r="G78" s="12" t="n"/>
+      <c r="H78" s="12" t="n"/>
+      <c r="I78" s="12" t="n"/>
+      <c r="J78" s="12" t="n"/>
+      <c r="K78" s="12" t="n"/>
+      <c r="L78" s="12" t="n"/>
+      <c r="M78" s="12" t="n"/>
+      <c r="N78" s="12" t="n"/>
+      <c r="O78" s="12" t="n"/>
+    </row>
+    <row r="79" outlineLevel="1">
+      <c r="A79" s="13" t="inlineStr">
+        <is>
+          <t>Southeast</t>
+        </is>
+      </c>
+      <c r="B79" s="14" t="inlineStr">
+        <is>
+          <t>Carter Control Systems Inc. bankruptcy Day 2: fabrication equipment + $5MM+ inventory (conveyor systems maker)</t>
+        </is>
+      </c>
+      <c r="C79" s="13" t="inlineStr">
+        <is>
+          <t>bankruptcy auction</t>
+        </is>
+      </c>
+      <c r="D79" s="13" t="inlineStr">
+        <is>
+          <t>Savannah</t>
+        </is>
+      </c>
+      <c r="E79" s="13" t="inlineStr">
+        <is>
+          <t>GA</t>
+        </is>
+      </c>
+      <c r="F79" s="13" t="n">
+        <v>894</v>
+      </c>
+      <c r="G79" s="13" t="inlineStr">
+        <is>
+          <t>Timed online auction</t>
+        </is>
+      </c>
+      <c r="H79" s="15" t="n"/>
+      <c r="I79" s="13" t="inlineStr"/>
+      <c r="J79" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K79" s="13" t="inlineStr">
+        <is>
+          <t>PPL Group</t>
+        </is>
+      </c>
+      <c r="L79" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M79" s="13" t="inlineStr"/>
+      <c r="N79" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O79" s="14" t="inlineStr">
+        <is>
+          <t>Ends Oct 28 10 AM ET; preview Oct 26-27; removal Oct 29-Nov 13.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — Southeast</t>
+        </is>
+      </c>
+      <c r="B80" s="17" t="inlineStr">
+        <is>
+          <t>1 item(s)</t>
+        </is>
+      </c>
+      <c r="C80" s="18" t="n"/>
+      <c r="D80" s="18" t="n"/>
+      <c r="E80" s="18" t="n"/>
+      <c r="F80" s="18" t="n"/>
+      <c r="G80" s="18" t="n"/>
+      <c r="H80" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="18" t="n"/>
+      <c r="J80" s="18" t="n"/>
+      <c r="K80" s="18" t="n"/>
+      <c r="L80" s="18" t="n"/>
+      <c r="M80" s="18" t="n"/>
+      <c r="N80" s="18" t="n"/>
+      <c r="O80" s="18" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
         <is>
           <t>▸ Midwest  (2)</t>
         </is>
       </c>
-      <c r="B73" s="12" t="n"/>
-      <c r="C73" s="12" t="n"/>
-      <c r="D73" s="12" t="n"/>
-      <c r="E73" s="12" t="n"/>
-      <c r="F73" s="12" t="n"/>
-      <c r="G73" s="12" t="n"/>
-      <c r="H73" s="12" t="n"/>
-      <c r="I73" s="12" t="n"/>
-      <c r="J73" s="12" t="n"/>
-      <c r="K73" s="12" t="n"/>
-      <c r="L73" s="12" t="n"/>
-      <c r="M73" s="12" t="n"/>
-      <c r="N73" s="12" t="n"/>
-      <c r="O73" s="12" t="n"/>
-    </row>
-    <row r="74" outlineLevel="1">
-      <c r="A74" s="13" t="inlineStr">
+      <c r="B81" s="12" t="n"/>
+      <c r="C81" s="12" t="n"/>
+      <c r="D81" s="12" t="n"/>
+      <c r="E81" s="12" t="n"/>
+      <c r="F81" s="12" t="n"/>
+      <c r="G81" s="12" t="n"/>
+      <c r="H81" s="12" t="n"/>
+      <c r="I81" s="12" t="n"/>
+      <c r="J81" s="12" t="n"/>
+      <c r="K81" s="12" t="n"/>
+      <c r="L81" s="12" t="n"/>
+      <c r="M81" s="12" t="n"/>
+      <c r="N81" s="12" t="n"/>
+      <c r="O81" s="12" t="n"/>
+    </row>
+    <row r="82" outlineLevel="1">
+      <c r="A82" s="13" t="inlineStr">
         <is>
           <t>Midwest</t>
         </is>
       </c>
-      <c r="B74" s="14" t="inlineStr">
+      <c r="B82" s="14" t="inlineStr">
         <is>
           <t>American Sale – total liquidation, all 7 stores (pools, hot tubs, grills, holiday decor)</t>
         </is>
       </c>
-      <c r="C74" s="13" t="inlineStr">
+      <c r="C82" s="13" t="inlineStr">
         <is>
           <t>retail GOB</t>
         </is>
       </c>
-      <c r="D74" s="13" t="inlineStr">
+      <c r="D82" s="13" t="inlineStr">
         <is>
           <t>Chicagoland</t>
         </is>
       </c>
-      <c r="E74" s="13" t="inlineStr">
+      <c r="E82" s="13" t="inlineStr">
         <is>
           <t>IL</t>
         </is>
       </c>
-      <c r="F74" s="13" t="n">
+      <c r="F82" s="13" t="n">
         <v>876</v>
       </c>
-      <c r="G74" s="13" t="inlineStr">
+      <c r="G82" s="13" t="inlineStr">
         <is>
           <t>Retail GOB, up to 70% off</t>
         </is>
       </c>
-      <c r="H74" s="15" t="n"/>
-      <c r="I74" s="13" t="inlineStr">
+      <c r="H82" s="15" t="n"/>
+      <c r="I82" s="13" t="inlineStr">
         <is>
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="J74" s="13" t="inlineStr"/>
-      <c r="K74" s="13" t="inlineStr">
+      <c r="J82" s="13" t="inlineStr"/>
+      <c r="K82" s="13" t="inlineStr">
         <is>
           <t>Tiger Group (PR Newswire)</t>
         </is>
       </c>
-      <c r="L74" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M74" s="13" t="inlineStr"/>
-      <c r="N74" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O74" s="14" t="inlineStr">
+      <c r="L82" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M82" s="13" t="inlineStr"/>
+      <c r="N82" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O82" s="14" t="inlineStr">
         <is>
           <t>Posted Oct 15. Watch for a bulk/fixture auction.</t>
         </is>
       </c>
     </row>
-    <row r="75" outlineLevel="1">
-      <c r="A75" s="13" t="inlineStr">
+    <row r="83" outlineLevel="1">
+      <c r="A83" s="13" t="inlineStr">
         <is>
           <t>Midwest</t>
         </is>
       </c>
-      <c r="B75" s="14" t="inlineStr">
+      <c r="B83" s="14" t="inlineStr">
         <is>
           <t>Restaurant, Bar &amp; DJ Equipment Liquidation: Alto-Shaam combi, Southbend/Blodgett ovens, True refrigeration, Manitowoc, Hobart saw, DJ/AV gear</t>
         </is>
       </c>
-      <c r="C75" s="13" t="inlineStr">
+      <c r="C83" s="13" t="inlineStr">
         <is>
           <t>restaurant liquidation auction</t>
         </is>
       </c>
-      <c r="D75" s="13" t="inlineStr">
+      <c r="D83" s="13" t="inlineStr">
         <is>
           <t>Austin</t>
         </is>
       </c>
-      <c r="E75" s="13" t="inlineStr">
+      <c r="E83" s="13" t="inlineStr">
         <is>
           <t>MN</t>
         </is>
       </c>
-      <c r="F75" s="13" t="n">
+      <c r="F83" s="13" t="n">
         <v>1124</v>
       </c>
-      <c r="G75" s="13" t="inlineStr">
+      <c r="G83" s="13" t="inlineStr">
         <is>
           <t>Timed online auction</t>
         </is>
       </c>
-      <c r="H75" s="15" t="n"/>
-      <c r="I75" s="13" t="inlineStr"/>
-      <c r="J75" s="13" t="inlineStr">
+      <c r="H83" s="15" t="n"/>
+      <c r="I83" s="13" t="inlineStr"/>
+      <c r="J83" s="13" t="inlineStr">
         <is>
           <t>2026-10-26 02:00 PM ET</t>
         </is>
       </c>
-      <c r="K75" s="13" t="inlineStr">
+      <c r="K83" s="13" t="inlineStr">
         <is>
           <t>Grafe Auction</t>
         </is>
       </c>
-      <c r="L75" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M75" s="13" t="inlineStr"/>
-      <c r="N75" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O75" s="14" t="inlineStr">
+      <c r="L83" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M83" s="13" t="inlineStr"/>
+      <c r="N83" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O83" s="14" t="inlineStr">
         <is>
           <t>Begins closing Oct 26 1 PM CDT.</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="17" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Midwest</t>
         </is>
       </c>
-      <c r="B76" s="17" t="inlineStr">
+      <c r="B84" s="17" t="inlineStr">
         <is>
           <t>2 item(s)</t>
         </is>
       </c>
-      <c r="C76" s="18" t="n"/>
-      <c r="D76" s="18" t="n"/>
-      <c r="E76" s="18" t="n"/>
-      <c r="F76" s="18" t="n"/>
-      <c r="G76" s="18" t="n"/>
-      <c r="H76" s="19" t="n">
+      <c r="C84" s="18" t="n"/>
+      <c r="D84" s="18" t="n"/>
+      <c r="E84" s="18" t="n"/>
+      <c r="F84" s="18" t="n"/>
+      <c r="G84" s="18" t="n"/>
+      <c r="H84" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I76" s="18" t="n"/>
-      <c r="J76" s="18" t="n"/>
-      <c r="K76" s="18" t="n"/>
-      <c r="L76" s="18" t="n"/>
-      <c r="M76" s="18" t="n"/>
-      <c r="N76" s="18" t="n"/>
-      <c r="O76" s="18" t="n"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="11" t="inlineStr">
+      <c r="I84" s="18" t="n"/>
+      <c r="J84" s="18" t="n"/>
+      <c r="K84" s="18" t="n"/>
+      <c r="L84" s="18" t="n"/>
+      <c r="M84" s="18" t="n"/>
+      <c r="N84" s="18" t="n"/>
+      <c r="O84" s="18" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="11" t="inlineStr">
         <is>
           <t>▸ Texas / South Central  (1)</t>
         </is>
       </c>
-      <c r="B77" s="12" t="n"/>
-      <c r="C77" s="12" t="n"/>
-      <c r="D77" s="12" t="n"/>
-      <c r="E77" s="12" t="n"/>
-      <c r="F77" s="12" t="n"/>
-      <c r="G77" s="12" t="n"/>
-      <c r="H77" s="12" t="n"/>
-      <c r="I77" s="12" t="n"/>
-      <c r="J77" s="12" t="n"/>
-      <c r="K77" s="12" t="n"/>
-      <c r="L77" s="12" t="n"/>
-      <c r="M77" s="12" t="n"/>
-      <c r="N77" s="12" t="n"/>
-      <c r="O77" s="12" t="n"/>
-    </row>
-    <row r="78" outlineLevel="1">
-      <c r="A78" s="13" t="inlineStr">
+      <c r="B85" s="12" t="n"/>
+      <c r="C85" s="12" t="n"/>
+      <c r="D85" s="12" t="n"/>
+      <c r="E85" s="12" t="n"/>
+      <c r="F85" s="12" t="n"/>
+      <c r="G85" s="12" t="n"/>
+      <c r="H85" s="12" t="n"/>
+      <c r="I85" s="12" t="n"/>
+      <c r="J85" s="12" t="n"/>
+      <c r="K85" s="12" t="n"/>
+      <c r="L85" s="12" t="n"/>
+      <c r="M85" s="12" t="n"/>
+      <c r="N85" s="12" t="n"/>
+      <c r="O85" s="12" t="n"/>
+    </row>
+    <row r="86" outlineLevel="1">
+      <c r="A86" s="13" t="inlineStr">
         <is>
           <t>Texas / South Central</t>
         </is>
       </c>
-      <c r="B78" s="14" t="inlineStr">
+      <c r="B86" s="14" t="inlineStr">
         <is>
           <t>Southwest beverage distributor surplus – mostly unused: 16 True merchandisers, 75 Bunn brewers, 100+ micro-market kiosks</t>
         </is>
       </c>
-      <c r="C78" s="13" t="inlineStr">
+      <c r="C86" s="13" t="inlineStr">
         <is>
           <t>distributor surplus</t>
         </is>
       </c>
-      <c r="D78" s="13" t="inlineStr">
+      <c r="D86" s="13" t="inlineStr">
         <is>
           <t>Mesquite</t>
         </is>
       </c>
-      <c r="E78" s="13" t="inlineStr">
+      <c r="E86" s="13" t="inlineStr">
         <is>
           <t>TX</t>
         </is>
       </c>
-      <c r="F78" s="13" t="n">
+      <c r="F86" s="13" t="n">
         <v>1547</v>
       </c>
-      <c r="G78" s="13" t="inlineStr">
+      <c r="G86" s="13" t="inlineStr">
         <is>
           <t>Online auction</t>
         </is>
       </c>
-      <c r="H78" s="15" t="n"/>
-      <c r="I78" s="13" t="inlineStr"/>
-      <c r="J78" s="13" t="inlineStr">
+      <c r="H86" s="15" t="n"/>
+      <c r="I86" s="13" t="inlineStr"/>
+      <c r="J86" s="13" t="inlineStr">
         <is>
           <t>2026-11-13 11:00 AM ET</t>
         </is>
       </c>
-      <c r="K78" s="13" t="inlineStr">
+      <c r="K86" s="13" t="inlineStr">
         <is>
           <t>Heritage Global Partners</t>
         </is>
       </c>
-      <c r="L78" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M78" s="13" t="inlineStr"/>
-      <c r="N78" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O78" s="14" t="inlineStr">
+      <c r="L86" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M86" s="13" t="inlineStr"/>
+      <c r="N86" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O86" s="14" t="inlineStr">
         <is>
           <t>Near-new appliances, resell by unit. Nov 13 10 AM CST.</t>
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="17" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Texas / South Central</t>
         </is>
       </c>
-      <c r="B79" s="17" t="inlineStr">
+      <c r="B87" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C79" s="18" t="n"/>
-      <c r="D79" s="18" t="n"/>
-      <c r="E79" s="18" t="n"/>
-      <c r="F79" s="18" t="n"/>
-      <c r="G79" s="18" t="n"/>
-      <c r="H79" s="19" t="n">
+      <c r="C87" s="18" t="n"/>
+      <c r="D87" s="18" t="n"/>
+      <c r="E87" s="18" t="n"/>
+      <c r="F87" s="18" t="n"/>
+      <c r="G87" s="18" t="n"/>
+      <c r="H87" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I79" s="18" t="n"/>
-      <c r="J79" s="18" t="n"/>
-      <c r="K79" s="18" t="n"/>
-      <c r="L79" s="18" t="n"/>
-      <c r="M79" s="18" t="n"/>
-      <c r="N79" s="18" t="n"/>
-      <c r="O79" s="18" t="n"/>
-    </row>
-    <row r="80">
-      <c r="A80" s="11" t="inlineStr">
+      <c r="I87" s="18" t="n"/>
+      <c r="J87" s="18" t="n"/>
+      <c r="K87" s="18" t="n"/>
+      <c r="L87" s="18" t="n"/>
+      <c r="M87" s="18" t="n"/>
+      <c r="N87" s="18" t="n"/>
+      <c r="O87" s="18" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="11" t="inlineStr">
         <is>
           <t>▸ West / Other  (1)</t>
         </is>
       </c>
-      <c r="B80" s="12" t="n"/>
-      <c r="C80" s="12" t="n"/>
-      <c r="D80" s="12" t="n"/>
-      <c r="E80" s="12" t="n"/>
-      <c r="F80" s="12" t="n"/>
-      <c r="G80" s="12" t="n"/>
-      <c r="H80" s="12" t="n"/>
-      <c r="I80" s="12" t="n"/>
-      <c r="J80" s="12" t="n"/>
-      <c r="K80" s="12" t="n"/>
-      <c r="L80" s="12" t="n"/>
-      <c r="M80" s="12" t="n"/>
-      <c r="N80" s="12" t="n"/>
-      <c r="O80" s="12" t="n"/>
-    </row>
-    <row r="81" outlineLevel="1">
-      <c r="A81" s="13" t="inlineStr">
+      <c r="B88" s="12" t="n"/>
+      <c r="C88" s="12" t="n"/>
+      <c r="D88" s="12" t="n"/>
+      <c r="E88" s="12" t="n"/>
+      <c r="F88" s="12" t="n"/>
+      <c r="G88" s="12" t="n"/>
+      <c r="H88" s="12" t="n"/>
+      <c r="I88" s="12" t="n"/>
+      <c r="J88" s="12" t="n"/>
+      <c r="K88" s="12" t="n"/>
+      <c r="L88" s="12" t="n"/>
+      <c r="M88" s="12" t="n"/>
+      <c r="N88" s="12" t="n"/>
+      <c r="O88" s="12" t="n"/>
+    </row>
+    <row r="89" outlineLevel="1">
+      <c r="A89" s="13" t="inlineStr">
         <is>
           <t>West / Other</t>
         </is>
       </c>
-      <c r="B81" s="14" t="inlineStr">
+      <c r="B89" s="14" t="inlineStr">
         <is>
           <t>National salad concept liquidation – full contents of 63 fast-casual restaurants (AZ/TX/OK/NV)</t>
         </is>
       </c>
-      <c r="C81" s="13" t="inlineStr">
+      <c r="C89" s="13" t="inlineStr">
         <is>
           <t>restaurant chain liquidation</t>
         </is>
       </c>
-      <c r="D81" s="13" t="inlineStr">
+      <c r="D89" s="13" t="inlineStr">
         <is>
           <t>Phoenix</t>
         </is>
       </c>
-      <c r="E81" s="13" t="inlineStr">
+      <c r="E89" s="13" t="inlineStr">
         <is>
           <t>AZ</t>
         </is>
       </c>
-      <c r="F81" s="13" t="n">
+      <c r="F89" s="13" t="n">
         <v>2307</v>
       </c>
-      <c r="G81" s="13" t="inlineStr">
+      <c r="G89" s="13" t="inlineStr">
         <is>
           <t>Online auctions, dates TBD</t>
         </is>
       </c>
-      <c r="H81" s="15" t="n"/>
-      <c r="I81" s="13" t="inlineStr">
+      <c r="H89" s="15" t="n"/>
+      <c r="I89" s="13" t="inlineStr">
         <is>
           <t>2026-10-18</t>
         </is>
       </c>
-      <c r="J81" s="13" t="inlineStr"/>
-      <c r="K81" s="13" t="inlineStr">
+      <c r="J89" s="13" t="inlineStr"/>
+      <c r="K89" s="13" t="inlineStr">
         <is>
           <t>RestaurantEquipment.bid (TAGeX)</t>
         </is>
       </c>
-      <c r="L81" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M81" s="13" t="inlineStr"/>
-      <c r="N81" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O81" s="14" t="inlineStr">
+      <c r="L89" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M89" s="13" t="inlineStr"/>
+      <c r="N89" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O89" s="14" t="inlineStr">
         <is>
           <t>Rolling market-by-market auctions, none live yet (Phoenix metro 30 locations, DFW 14, Tucson 6, Houston 5, plus OK/NV). Pickup on site at each restaurant. Pinned at Phoenix.</t>
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="17" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="17" t="inlineStr">
         <is>
           <t>Subtotal — West / Other</t>
         </is>
       </c>
-      <c r="B82" s="17" t="inlineStr">
+      <c r="B90" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C82" s="18" t="n"/>
-      <c r="D82" s="18" t="n"/>
-      <c r="E82" s="18" t="n"/>
-      <c r="F82" s="18" t="n"/>
-      <c r="G82" s="18" t="n"/>
-      <c r="H82" s="19" t="n">
+      <c r="C90" s="18" t="n"/>
+      <c r="D90" s="18" t="n"/>
+      <c r="E90" s="18" t="n"/>
+      <c r="F90" s="18" t="n"/>
+      <c r="G90" s="18" t="n"/>
+      <c r="H90" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I82" s="18" t="n"/>
-      <c r="J82" s="18" t="n"/>
-      <c r="K82" s="18" t="n"/>
-      <c r="L82" s="18" t="n"/>
-      <c r="M82" s="18" t="n"/>
-      <c r="N82" s="18" t="n"/>
-      <c r="O82" s="18" t="n"/>
+      <c r="I90" s="18" t="n"/>
+      <c r="J90" s="18" t="n"/>
+      <c r="K90" s="18" t="n"/>
+      <c r="L90" s="18" t="n"/>
+      <c r="M90" s="18" t="n"/>
+      <c r="N90" s="18" t="n"/>
+      <c r="O90" s="18" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O82"/>
+  <autoFilter ref="A1:O90"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N4" r:id="rId2"/>
@@ -22768,50 +23002,54 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N15" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N16" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N19" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N20" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N25" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N26" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N27" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N28" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N29" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N30" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N31" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N32" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N33" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N34" r:id="rId22"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N35" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N36" r:id="rId24"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N37" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N38" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N39" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N51" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N52" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N40" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N41" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N42" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N43" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N44" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N45" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N50" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N51" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N52" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N55" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N56" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N57" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N58" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N59" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N60" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N63" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N64" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N61" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N62" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N65" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N68" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N71" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N74" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N75" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N78" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N81" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N69" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N70" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N73" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N76" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N79" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N82" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N83" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N86" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N89" r:id="rId59"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -22823,7 +23061,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O23"/>
+  <dimension ref="A1:O24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -22985,7 +23223,7 @@
       </c>
       <c r="O2" s="14" t="inlineStr">
         <is>
-          <t>Integrity Auction House. Internet bidding closes Mon Oct 19 9:18 PM ET. $50 high bid (1 bid) as of 2026-10-18. [Closed Oct 19; HiBid price realized $50.] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Integrity Auction House. Internet bidding closes Mon Oct 19 9:18 PM ET. $50 high bid (1 bid) as of 2026-10-18. [Closed Oct 19; HiBid price realized $50.] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23048,7 +23286,7 @@
       </c>
       <c r="O3" s="14" t="inlineStr">
         <is>
-          <t>Live auction Mon Oct 19 4 PM, 3457 Wilmington Rd. Few bulk parts. [Live auction held Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Live auction Mon Oct 19 4 PM, 3457 Wilmington Rd. Few bulk parts. [Live auction held Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23170,7 +23408,7 @@
           <t>REMOVED</t>
         </is>
       </c>
-      <c r="M5" s="21" t="inlineStr">
+      <c r="M5" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -23237,7 +23475,7 @@
           <t>EXPIRED (2026-10-18 02:19 PM ET)</t>
         </is>
       </c>
-      <c r="M6" s="21" t="inlineStr">
+      <c r="M6" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
@@ -23249,7 +23487,7 @@
       </c>
       <c r="O6" s="14" t="inlineStr">
         <is>
-          <t>Condition: Pre-Owned. FLIP: SO36U/S tested, auction $99/0 bids, pickup only; rough resale $600-1k (eBay card shows no city; pickup distance in source.) Ends Oct 18 ~2:19 PM per eBay card (time zone uncertain; could be earlier). [auto-removed 2026-10-18: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Condition: Pre-Owned. FLIP: SO36U/S tested, auction $99/0 bids, pickup only; rough resale $600-1k (eBay card shows no city; pickup distance in source.) Ends Oct 18 ~2:19 PM per eBay card (time zone uncertain; could be earlier). [auto-removed 2026-10-18: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23314,19 +23552,19 @@
       </c>
       <c r="O7" s="14" t="inlineStr">
         <is>
-          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf) HiBid lot closed/sold ~$37.50 on 2026-10-18. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf) HiBid lot closed/sold ~$37.50 on 2026-10-18. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>Southeast</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Louisville)</t>
+          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Indianapolis)</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
@@ -23336,16 +23574,16 @@
       </c>
       <c r="D8" s="13" t="inlineStr">
         <is>
-          <t>Louisville</t>
+          <t>Indianapolis</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>KY</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F8" s="13" t="n">
-        <v>832</v>
+        <v>816</v>
       </c>
       <c r="G8" s="13" t="inlineStr">
         <is>
@@ -23358,7 +23596,7 @@
       <c r="I8" s="13" t="inlineStr"/>
       <c r="J8" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 02:00 PM ET</t>
+          <t>2026-10-21 02:00 PM ET</t>
         </is>
       </c>
       <c r="K8" s="13" t="inlineStr">
@@ -23368,7 +23606,7 @@
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 02:00 PM ET)</t>
+          <t>EXPIRED (2026-10-21 02:00 PM ET)</t>
         </is>
       </c>
       <c r="M8" s="13" t="inlineStr"/>
@@ -23379,19 +23617,19 @@
       </c>
       <c r="O8" s="14" t="inlineStr">
         <is>
-          <t>Lots close from Oct 19 2 PM ET. [HiBid catalog closed 2 PM ET Oct 19.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Lots close in sequence from Oct 21 2 PM ET. [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>Southeast</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Fort Wayne)</t>
+          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Louisville)</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
@@ -23401,16 +23639,16 @@
       </c>
       <c r="D9" s="13" t="inlineStr">
         <is>
-          <t>Fort Wayne</t>
+          <t>Louisville</t>
         </is>
       </c>
       <c r="E9" s="13" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>KY</t>
         </is>
       </c>
       <c r="F9" s="13" t="n">
-        <v>743</v>
+        <v>832</v>
       </c>
       <c r="G9" s="13" t="inlineStr">
         <is>
@@ -23423,7 +23661,7 @@
       <c r="I9" s="13" t="inlineStr"/>
       <c r="J9" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 02:00 PM ET</t>
+          <t>2026-10-19 02:00 PM ET</t>
         </is>
       </c>
       <c r="K9" s="13" t="inlineStr">
@@ -23433,7 +23671,7 @@
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-20 02:00 PM ET)</t>
+          <t>EXPIRED (2026-10-19 02:00 PM ET)</t>
         </is>
       </c>
       <c r="M9" s="13" t="inlineStr"/>
@@ -23444,45 +23682,47 @@
       </c>
       <c r="O9" s="14" t="inlineStr">
         <is>
-          <t>Lots close from Oct 20 2 PM ET. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Lots close from Oct 19 2 PM ET. [HiBid catalog closed 2 PM ET Oct 19.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="13" t="inlineStr">
         <is>
-          <t>CT / Hudson Valley</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>Major Intl Chain Surplus – 225 lots commercial refrigeration/kitchen (True, Traulsen, Hobart, Blodgett, Taylor)</t>
+          <t>Auctionfuel returns catalog – 100+ single appliance-part lots (Fort Wayne)</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
         <is>
-          <t>commercial surplus</t>
+          <t>auction catalog</t>
         </is>
       </c>
       <c r="D10" s="13" t="inlineStr">
         <is>
-          <t>Pleasant Valley</t>
+          <t>Fort Wayne</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="F10" s="13" t="n">
-        <v>157</v>
+        <v>743</v>
       </c>
       <c r="G10" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
-        </is>
-      </c>
-      <c r="H10" s="15" t="n"/>
+          <t>$0–1 openers + 15% BP + $1/lot</t>
+        </is>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>0</v>
+      </c>
       <c r="I10" s="13" t="inlineStr"/>
       <c r="J10" s="13" t="inlineStr">
         <is>
@@ -23491,7 +23731,7 @@
       </c>
       <c r="K10" s="13" t="inlineStr">
         <is>
-          <t>Adams / BidWrangler</t>
+          <t>HiBid (Auctionfuel)</t>
         </is>
       </c>
       <c r="L10" s="13" t="inlineStr">
@@ -23507,59 +23747,59 @@
       </c>
       <c r="O10" s="14" t="inlineStr">
         <is>
-          <t>Tested and new units. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Lots close from Oct 20 2 PM ET. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="13" t="inlineStr">
         <is>
-          <t>Maine / VT / Northern NH</t>
+          <t>CT / Hudson Valley</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>Oola Bowls secured-party sale – restaurant equipment bought new 2024-25 (Electro Freeze, Scotsman, Atosa)</t>
+          <t>Major Intl Chain Surplus – 225 lots commercial refrigeration/kitchen (True, Traulsen, Hobart, Blodgett, Taylor)</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>commercial surplus</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Scarborough</t>
+          <t>Pleasant Valley</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
         <is>
-          <t>ME</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>104</v>
+        <v>157</v>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>Online auction (freezers $80–150 when seen)</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H11" s="15" t="n"/>
       <c r="I11" s="13" t="inlineStr"/>
       <c r="J11" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 01:00 PM ET</t>
+          <t>2026-10-20 02:00 PM ET</t>
         </is>
       </c>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>Keenan Auction / Proxibid</t>
+          <t>Adams / BidWrangler</t>
         </is>
       </c>
       <c r="L11" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 01:00 PM ET)</t>
+          <t>EXPIRED (2026-10-20 02:00 PM ET)</t>
         </is>
       </c>
       <c r="M11" s="13" t="inlineStr"/>
@@ -23570,19 +23810,19 @@
       </c>
       <c r="O11" s="14" t="inlineStr">
         <is>
-          <t>Pickup Oct 21 only. [Lots began closing 1 PM ET Oct 19; ended.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Tested and new units. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="13" t="inlineStr">
         <is>
-          <t>Eastern PA / Mid-Atlantic</t>
+          <t>Maine / VT / Northern NH</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>October restaurant consignment – Hobart, Rational, True + NEW scratch-and-dent Migali/Avantco</t>
+          <t>Oola Bowls secured-party sale – restaurant equipment bought new 2024-25 (Electro Freeze, Scotsman, Atosa)</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
@@ -23592,37 +23832,37 @@
       </c>
       <c r="D12" s="13" t="inlineStr">
         <is>
-          <t>Harrisburg</t>
+          <t>Scarborough</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>340</v>
+        <v>104</v>
       </c>
       <c r="G12" s="13" t="inlineStr">
         <is>
-          <t>Online auction, 15% BP, ships $55/pallet</t>
+          <t>Online auction (freezers $80–150 when seen)</t>
         </is>
       </c>
       <c r="H12" s="15" t="n"/>
       <c r="I12" s="13" t="inlineStr"/>
       <c r="J12" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 11:00 AM ET</t>
+          <t>2026-10-19 01:00 PM ET</t>
         </is>
       </c>
       <c r="K12" s="13" t="inlineStr">
         <is>
-          <t>Restaurant Auction Co</t>
+          <t>Keenan Auction / Proxibid</t>
         </is>
       </c>
       <c r="L12" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-21 11:00 AM ET)</t>
+          <t>EXPIRED (2026-10-19 01:00 PM ET)</t>
         </is>
       </c>
       <c r="M12" s="13" t="inlineStr"/>
@@ -23633,19 +23873,19 @@
       </c>
       <c r="O12" s="14" t="inlineStr">
         <is>
-          <t>Closes Oct 21 10 or 11 AM (later used). Shippable. [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Pickup Oct 21 only. [Lots began closing 1 PM ET Oct 19; ended.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="13" t="inlineStr">
         <is>
-          <t>NYC / Long Island / NJ</t>
+          <t>Eastern PA / Mid-Atlantic</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>Serpico's Pizzeria (lost lease) – Bari ovens, walk-in, Hobart 60qt, Vulcan range</t>
+          <t>October restaurant consignment – Hobart, Rational, True + NEW scratch-and-dent Migali/Avantco</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
@@ -23655,20 +23895,20 @@
       </c>
       <c r="D13" s="13" t="inlineStr">
         <is>
-          <t>Allenhurst</t>
+          <t>Harrisburg</t>
         </is>
       </c>
       <c r="E13" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="F13" s="13" t="n">
-        <v>210</v>
+        <v>340</v>
       </c>
       <c r="G13" s="13" t="inlineStr">
         <is>
-          <t>No-reserve online auction</t>
+          <t>Online auction, 15% BP, ships $55/pallet</t>
         </is>
       </c>
       <c r="H13" s="15" t="n"/>
@@ -23680,7 +23920,7 @@
       </c>
       <c r="K13" s="13" t="inlineStr">
         <is>
-          <t>Peter Costanzo / EstateSales.net</t>
+          <t>Restaurant Auction Co</t>
         </is>
       </c>
       <c r="L13" s="13" t="inlineStr">
@@ -23696,7 +23936,7 @@
       </c>
       <c r="O13" s="14" t="inlineStr">
         <is>
-          <t>Absolute / no reserve. [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Closes Oct 21 10 or 11 AM (later used). Shippable. [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23708,17 +23948,17 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Milwaukee / Walmart / hardware store mega auction pt 3</t>
+          <t>Serpico's Pizzeria (lost lease) – Bari ovens, walk-in, Hobart 60qt, Vulcan range</t>
         </is>
       </c>
       <c r="C14" s="13" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D14" s="13" t="inlineStr">
         <is>
-          <t>Mount Holly</t>
+          <t>Allenhurst</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
@@ -23727,28 +23967,28 @@
         </is>
       </c>
       <c r="F14" s="13" t="n">
-        <v>254</v>
+        <v>210</v>
       </c>
       <c r="G14" s="13" t="inlineStr">
         <is>
-          <t>HiBid online auction</t>
+          <t>No-reserve online auction</t>
         </is>
       </c>
       <c r="H14" s="15" t="n"/>
       <c r="I14" s="13" t="inlineStr"/>
       <c r="J14" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 06:00 PM ET</t>
+          <t>2026-10-21 11:00 AM ET</t>
         </is>
       </c>
       <c r="K14" s="13" t="inlineStr">
         <is>
-          <t>HiBid</t>
+          <t>Peter Costanzo / EstateSales.net</t>
         </is>
       </c>
       <c r="L14" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 06:00 PM ET)</t>
+          <t>EXPIRED (2026-10-21 11:00 AM ET)</t>
         </is>
       </c>
       <c r="M14" s="13" t="inlineStr"/>
@@ -23759,7 +23999,7 @@
       </c>
       <c r="O14" s="14" t="inlineStr">
         <is>
-          <t>Close Oct 18 or 19 6 PM (later used). [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Absolute / no reserve. [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23771,17 +24011,17 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>Altitude Trampoline Park liquidation – partial: Atosa, TurboChef, stainless</t>
+          <t>Milwaukee / Walmart / hardware store mega auction pt 3</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>facility contents</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>Iselin</t>
+          <t>Mount Holly</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
@@ -23790,28 +24030,28 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>211</v>
+        <v>254</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>HiBid online auction</t>
         </is>
       </c>
       <c r="H15" s="15" t="n"/>
       <c r="I15" s="13" t="inlineStr"/>
       <c r="J15" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 11:00 AM ET</t>
+          <t>2026-10-19 06:00 PM ET</t>
         </is>
       </c>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>HiBid</t>
         </is>
       </c>
       <c r="L15" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-21 11:00 AM ET)</t>
+          <t>EXPIRED (2026-10-19 06:00 PM ET)</t>
         </is>
       </c>
       <c r="M15" s="13" t="inlineStr"/>
@@ -23822,59 +24062,59 @@
       </c>
       <c r="O15" s="14" t="inlineStr">
         <is>
-          <t>Some kitchen gear only. [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Close Oct 18 or 19 6 PM (later used). [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>Upstate / Western NY</t>
+          <t>NYC / Long Island / NJ</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>Closed restaurant – coolers, fridges, prep tables</t>
+          <t>Altitude Trampoline Park liquidation – partial: Atosa, TurboChef, stainless</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>facility contents</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>Palmyra</t>
+          <t>Iselin</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>333</v>
+        <v>211</v>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>HiBid, 15% BP</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H16" s="15" t="n"/>
       <c r="I16" s="13" t="inlineStr"/>
       <c r="J16" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 07:00 PM ET</t>
+          <t>2026-10-21 11:00 AM ET</t>
         </is>
       </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>Reynolds Auction Co / HiBid</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L16" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 07:00 PM ET)</t>
+          <t>EXPIRED (2026-10-21 11:00 AM ET)</t>
         </is>
       </c>
       <c r="M16" s="13" t="inlineStr"/>
@@ -23885,7 +24125,7 @@
       </c>
       <c r="O16" s="14" t="inlineStr">
         <is>
-          <t>No new out-of-state bidders. Small. [Ended Oct 19 7 PM.] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Some kitchen gear only. [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -23897,7 +24137,7 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>Former Taco Del Mar – stainless, warmers, walk-in panels</t>
+          <t>Closed restaurant – coolers, fridges, prep tables</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
@@ -23907,7 +24147,7 @@
       </c>
       <c r="D17" s="13" t="inlineStr">
         <is>
-          <t>Watson</t>
+          <t>Palmyra</t>
         </is>
       </c>
       <c r="E17" s="13" t="inlineStr">
@@ -23916,28 +24156,28 @@
         </is>
       </c>
       <c r="F17" s="13" t="n">
-        <v>260</v>
+        <v>333</v>
       </c>
       <c r="G17" s="13" t="inlineStr">
         <is>
-          <t>HiBid online auction</t>
+          <t>HiBid, 15% BP</t>
         </is>
       </c>
       <c r="H17" s="15" t="n"/>
       <c r="I17" s="13" t="inlineStr"/>
       <c r="J17" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 06:00 PM ET</t>
+          <t>2026-10-19 07:00 PM ET</t>
         </is>
       </c>
       <c r="K17" s="13" t="inlineStr">
         <is>
-          <t>Adirondack Asset / HiBid</t>
+          <t>Reynolds Auction Co / HiBid</t>
         </is>
       </c>
       <c r="L17" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-20 06:00 PM ET)</t>
+          <t>EXPIRED (2026-10-19 07:00 PM ET)</t>
         </is>
       </c>
       <c r="M17" s="13" t="inlineStr"/>
@@ -23948,59 +24188,59 @@
       </c>
       <c r="O17" s="14" t="inlineStr">
         <is>
-          <t>Small lot. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>No new out-of-state bidders. Small. [Ended Oct 19 7 PM.] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="13" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>Upstate / Western NY</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
         <is>
-          <t>Freshway Market whole-grocery liquidation – refrigeration racks, cases, walk-ins, generator</t>
+          <t>Former Taco Del Mar – stainless, warmers, walk-in panels</t>
         </is>
       </c>
       <c r="C18" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D18" s="13" t="inlineStr">
         <is>
-          <t>Chicago</t>
+          <t>Watson</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F18" s="13" t="n">
-        <v>862</v>
+        <v>260</v>
       </c>
       <c r="G18" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>HiBid online auction</t>
         </is>
       </c>
       <c r="H18" s="15" t="n"/>
       <c r="I18" s="13" t="inlineStr"/>
       <c r="J18" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 11:00 AM ET</t>
+          <t>2026-10-20 06:00 PM ET</t>
         </is>
       </c>
       <c r="K18" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
+          <t>Adirondack Asset / HiBid</t>
         </is>
       </c>
       <c r="L18" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-20 11:00 AM ET)</t>
+          <t>EXPIRED (2026-10-20 06:00 PM ET)</t>
         </is>
       </c>
       <c r="M18" s="13" t="inlineStr"/>
@@ -24011,59 +24251,59 @@
       </c>
       <c r="O18" s="14" t="inlineStr">
         <is>
-          <t>Closes from Oct 20 10 AM CDT. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Small lot. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>Greater Boston / South Shore (&lt;50mi)</t>
+          <t>Midwest</t>
         </is>
       </c>
       <c r="B19" s="14" t="inlineStr">
         <is>
-          <t>Closed Best Buy Outlet – pallet racking, Big Joe order pickers, appliance dollies, carts, cages</t>
+          <t>Freshway Market whole-grocery liquidation – refrigeration racks, cases, walk-ins, generator</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>store closing fixtures</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D19" s="13" t="inlineStr">
         <is>
-          <t>Brockton</t>
+          <t>Chicago</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="F19" s="13" t="n">
-        <v>11</v>
+        <v>862</v>
       </c>
       <c r="G19" s="13" t="inlineStr">
         <is>
-          <t>Racking $40/upright, $80/level; pickers $1,000 OBO</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H19" s="15" t="n"/>
-      <c r="I19" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="J19" s="13" t="inlineStr"/>
+      <c r="I19" s="13" t="inlineStr"/>
+      <c r="J19" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-20 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K19" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>Grafe Auction</t>
         </is>
       </c>
       <c r="L19" s="13" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>EXPIRED (2026-10-20 11:00 AM ET)</t>
         </is>
       </c>
       <c r="M19" s="13" t="inlineStr"/>
@@ -24074,63 +24314,59 @@
       </c>
       <c r="O19" s="14" t="inlineStr">
         <is>
-          <t>200 Westgate Dr. Fixtures/equipment only, no merchandise. On site daily. CL deleted by author (HTTP 410) as of 2026-10-19 midday recheck.</t>
+          <t>Closes from Oct 20 10 AM CDT. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
-          <t>NYC / Long Island / NJ</t>
+          <t>Greater Boston / South Shore (&lt;50mi)</t>
         </is>
       </c>
       <c r="B20" s="14" t="inlineStr">
         <is>
-          <t>Like-new restaurant – steam tables, Coldline, Cleveland cook-and-hold, fryers, True freezers</t>
+          <t>Closed Best Buy Outlet – pallet racking, Big Joe order pickers, appliance dollies, carts, cages</t>
         </is>
       </c>
       <c r="C20" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>store closing fixtures</t>
         </is>
       </c>
       <c r="D20" s="13" t="inlineStr">
         <is>
-          <t>Staten Island</t>
+          <t>Brockton</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="F20" s="13" t="n">
-        <v>203</v>
+        <v>11</v>
       </c>
       <c r="G20" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>Racking $40/upright, $80/level; pickers $1,000 OBO</t>
         </is>
       </c>
       <c r="H20" s="15" t="n"/>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
-        </is>
-      </c>
-      <c r="J20" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-19 01:00 PM ET</t>
-        </is>
-      </c>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="J20" s="13" t="inlineStr"/>
       <c r="K20" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L20" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 01:00 PM ET)</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="M20" s="13" t="inlineStr"/>
@@ -24141,7 +24377,7 @@
       </c>
       <c r="O20" s="14" t="inlineStr">
         <is>
-          <t>"Short notice" auction Mon Oct 19 1 PM. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>200 Westgate Dr. Fixtures/equipment only, no merchandise. On site daily. CL deleted by author (HTTP 410) as of 2026-10-19 midday recheck.</t>
         </is>
       </c>
     </row>
@@ -24153,26 +24389,26 @@
       </c>
       <c r="B21" s="14" t="inlineStr">
         <is>
-          <t>Restaurant / pizzeria (contents not described)</t>
+          <t>Like-new restaurant – steam tables, Coldline, Cleveland cook-and-hold, fryers, True freezers</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D21" s="13" t="inlineStr">
         <is>
-          <t>Berkeley Heights</t>
+          <t>Staten Island</t>
         </is>
       </c>
       <c r="E21" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F21" s="13" t="n">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="G21" s="13" t="inlineStr">
         <is>
@@ -24182,12 +24418,12 @@
       <c r="H21" s="15" t="n"/>
       <c r="I21" s="13" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-15</t>
         </is>
       </c>
       <c r="J21" s="13" t="inlineStr">
         <is>
-          <t>2026-10-20 02:00 PM ET</t>
+          <t>2026-10-19 01:00 PM ET</t>
         </is>
       </c>
       <c r="K21" s="13" t="inlineStr">
@@ -24197,7 +24433,7 @@
       </c>
       <c r="L21" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-20 02:00 PM ET)</t>
+          <t>EXPIRED (2026-10-19 01:00 PM ET)</t>
         </is>
       </c>
       <c r="M21" s="13" t="inlineStr"/>
@@ -24208,7 +24444,7 @@
       </c>
       <c r="O21" s="14" t="inlineStr">
         <is>
-          <t>Tue Oct 20 2 PM. No item description on page. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>"Short notice" auction Mon Oct 19 1 PM. [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
@@ -24220,7 +24456,7 @@
       </c>
       <c r="B22" s="14" t="inlineStr">
         <is>
-          <t>High-end deli (contents not described)</t>
+          <t>Restaurant / pizzeria (contents not described)</t>
         </is>
       </c>
       <c r="C22" s="13" t="inlineStr">
@@ -24230,7 +24466,7 @@
       </c>
       <c r="D22" s="13" t="inlineStr">
         <is>
-          <t>Manalapan Township</t>
+          <t>Berkeley Heights</t>
         </is>
       </c>
       <c r="E22" s="13" t="inlineStr">
@@ -24239,7 +24475,7 @@
         </is>
       </c>
       <c r="F22" s="13" t="n">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="G22" s="13" t="inlineStr">
         <is>
@@ -24249,12 +24485,12 @@
       <c r="H22" s="15" t="n"/>
       <c r="I22" s="13" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-14</t>
         </is>
       </c>
       <c r="J22" s="13" t="inlineStr">
         <is>
-          <t>2026-10-19 04:00 PM ET</t>
+          <t>2026-10-20 02:00 PM ET</t>
         </is>
       </c>
       <c r="K22" s="13" t="inlineStr">
@@ -24264,7 +24500,7 @@
       </c>
       <c r="L22" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-19 04:00 PM ET)</t>
+          <t>EXPIRED (2026-10-20 02:00 PM ET)</t>
         </is>
       </c>
       <c r="M22" s="13" t="inlineStr"/>
@@ -24275,59 +24511,63 @@
       </c>
       <c r="O22" s="14" t="inlineStr">
         <is>
-          <t>Mon Oct 19 4 PM. No item description on page. [HiBid shows Bidding Closed, Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Tue Oct 20 2 PM. No item description on page. [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
-          <t>Midwest</t>
+          <t>NYC / Long Island / NJ</t>
         </is>
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>Straub's Fine Foods store equipment – bakery, kitchen, meat room, Hussmann refrigeration</t>
+          <t>High-end deli (contents not described)</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>grocery/restaurant</t>
+          <t>restaurant closing</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>St. Louis</t>
+          <t>Manalapan Township</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>1046</v>
+        <v>223</v>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>Online auction (18% BP)</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H23" s="15" t="n"/>
-      <c r="I23" s="13" t="inlineStr"/>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
       <c r="J23" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 11:00 AM ET</t>
+          <t>2026-10-19 04:00 PM ET</t>
         </is>
       </c>
       <c r="K23" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
       <c r="L23" s="13" t="inlineStr">
         <is>
-          <t>EXPIRED (2026-10-21 11:00 AM ET)</t>
+          <t>EXPIRED (2026-10-19 04:00 PM ET)</t>
         </is>
       </c>
       <c r="M23" s="13" t="inlineStr"/>
@@ -24338,12 +24578,75 @@
       </c>
       <c r="O23" s="14" t="inlineStr">
         <is>
-          <t>Kingshighway store: Revent double-rack oven + proofer, Reed revolving oven, Vulcan convection, Groen kettle, Southbend 6-burner, Pitco fryer, Stero dishwasher, Hobart saw/grinders, Berkel slicers, Hussmann cases + compressor racks, walk-ins, Hoshizaki/Scotsman ice machines, Crown pallet jack. Preview Oct 20 3–6 PM CDT; pickup in St. Louis. [auto-removed 2026-10-21: closing date passed]</t>
+          <t>Mon Oct 19 4 PM. No item description on page. [HiBid shows Bidding Closed, Oct 19 4 PM.] [auto-removed 2026-10-19: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-20: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Midwest</t>
+        </is>
+      </c>
+      <c r="B24" s="14" t="inlineStr">
+        <is>
+          <t>Straub's Fine Foods store equipment – bakery, kitchen, meat room, Hussmann refrigeration</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="inlineStr">
+        <is>
+          <t>grocery/restaurant</t>
+        </is>
+      </c>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>St. Louis</t>
+        </is>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>MO</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>1046</v>
+      </c>
+      <c r="G24" s="13" t="inlineStr">
+        <is>
+          <t>Online auction (18% BP)</t>
+        </is>
+      </c>
+      <c r="H24" s="15" t="n"/>
+      <c r="I24" s="13" t="inlineStr"/>
+      <c r="J24" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-21 11:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L24" s="13" t="inlineStr">
+        <is>
+          <t>EXPIRED (2026-10-21 11:00 AM ET)</t>
+        </is>
+      </c>
+      <c r="M24" s="13" t="inlineStr"/>
+      <c r="N24" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O24" s="14" t="inlineStr">
+        <is>
+          <t>Kingshighway store: Revent double-rack oven + proofer, Reed revolving oven, Vulcan convection, Groen kettle, Southbend 6-burner, Pitco fryer, Stero dishwasher, Hobart saw/grinders, Berkel slicers, Hussmann cases + compressor racks, walk-ins, Hoshizaki/Scotsman ice machines, Crown pallet jack. Preview Oct 20 3–6 PM CDT; pickup in St. Louis. [auto-removed 2026-10-21: closing date passed] [auto-removed 2026-10-21: closing date passed]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O23"/>
+  <autoFilter ref="A1:O24"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N3" r:id="rId2"/>
@@ -24367,6 +24670,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N21" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N22" r:id="rId21"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N24" r:id="rId23"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/lot_recon.xlsx
+++ b/lot_recon.xlsx
@@ -21,7 +21,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Wolf Used'!$A$1:$O$192</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Wolf Unclear'!$A$1:$O$40</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Business Liquidation'!$A$1:$O$89</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Removed'!$A$1:$O$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Removed'!$A$1:$O$29</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -577,7 +577,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Last updated: 2026-10-21 18:03 ET</t>
+          <t>Last updated: 2026-10-22 08:05 ET</t>
         </is>
       </c>
     </row>
@@ -591,7 +591,7 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Active listings: 299 · Removed: 26</t>
+          <t>Active listings: 299 · Removed: 28</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
         <v>167</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>616329.6</v>
+        <v>616223.6</v>
       </c>
       <c r="D10" t="n">
         <v>3</v>
@@ -714,7 +714,7 @@
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -727,7 +727,7 @@
         <v>299</v>
       </c>
       <c r="C13" s="7" t="n">
-        <v>1283740.58</v>
+        <v>1283634.58</v>
       </c>
     </row>
     <row r="15">
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
         <v>1</v>
@@ -806,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H17" s="6" t="n">
         <v>13698.69</v>
@@ -956,7 +956,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -971,7 +971,7 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="6" t="n">
         <v>0</v>
@@ -989,7 +989,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C23" t="n">
         <v>1</v>
@@ -998,16 +998,16 @@
         <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F23" t="n">
         <v>4</v>
       </c>
       <c r="G23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>64756</v>
+        <v>64650</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C25" t="n">
         <v>1</v>
@@ -1064,7 +1064,7 @@
         <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" t="n">
         <v>1</v>
@@ -1088,7 +1088,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C26" t="n">
         <v>1</v>
@@ -1103,7 +1103,7 @@
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H26" s="6" t="n">
         <v>175</v>
@@ -6580,7 +6580,7 @@
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t>▸ CT / Hudson Valley  (19)</t>
+          <t>▸ CT / Hudson Valley  (18)</t>
         </is>
       </c>
       <c r="B30" s="12" t="n"/>
@@ -6984,17 +6984,17 @@
       </c>
       <c r="B37" s="14" t="inlineStr">
         <is>
-          <t>Wolf Gourmet toaster (estate auction lot 60)</t>
+          <t>Wolf Gas/Electric Cooktop 5 burner</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>countertop</t>
+          <t>range/oven/rangetop</t>
         </is>
       </c>
       <c r="D37" s="13" t="inlineStr">
         <is>
-          <t>Clinton Corners</t>
+          <t>Clifton Park</t>
         </is>
       </c>
       <c r="E37" s="13" t="inlineStr">
@@ -7003,30 +7003,26 @@
         </is>
       </c>
       <c r="F37" s="13" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="G37" s="13" t="inlineStr">
         <is>
-          <t>$106 high bid (18 bids)</t>
+          <t>$250</t>
         </is>
       </c>
       <c r="H37" s="15" t="n">
-        <v>106</v>
+        <v>250</v>
       </c>
       <c r="I37" s="13" t="inlineStr"/>
-      <c r="J37" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 07:00 PM ET</t>
-        </is>
-      </c>
+      <c r="J37" s="13" t="inlineStr"/>
       <c r="K37" s="13" t="inlineStr">
         <is>
-          <t>AuctionNinja (Clearing House Estate Sales)</t>
-        </is>
-      </c>
-      <c r="L37" s="21" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>OfferUp</t>
+        </is>
+      </c>
+      <c r="L37" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M37" s="20" t="inlineStr">
@@ -7041,7 +7037,7 @@
       </c>
       <c r="O37" s="14" t="inlineStr">
         <is>
-          <t>About 3 days left as of Oct 18 (~Oct 21; exact time not captured). Pickup Sat Oct 24 12–4 PM by appointment. Used, minor wear. eBay asks $200–420; rough resale $150–250.</t>
+          <t>Condition: used. FLIP: 5-burner cooktop $250, excellent; rough resale $600-900</t>
         </is>
       </c>
     </row>
@@ -7053,7 +7049,7 @@
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>Wolf Gas/Electric Cooktop 5 burner</t>
+          <t>WOLF Range GE Monogram Fridge Wolf Hood Combo Stainless Steel</t>
         </is>
       </c>
       <c r="C38" s="13" t="inlineStr">
@@ -7063,12 +7059,12 @@
       </c>
       <c r="D38" s="13" t="inlineStr">
         <is>
-          <t>Clifton Park</t>
+          <t>Stamford</t>
         </is>
       </c>
       <c r="E38" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="F38" s="13" t="n">
@@ -7076,11 +7072,11 @@
       </c>
       <c r="G38" s="13" t="inlineStr">
         <is>
-          <t>$250</t>
+          <t>$9,000</t>
         </is>
       </c>
       <c r="H38" s="15" t="n">
-        <v>250</v>
+        <v>9000</v>
       </c>
       <c r="I38" s="13" t="inlineStr"/>
       <c r="J38" s="13" t="inlineStr"/>
@@ -7094,11 +7090,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M38" s="20" t="inlineStr">
-        <is>
-          <t>FLIP</t>
-        </is>
-      </c>
+      <c r="M38" s="13" t="inlineStr"/>
       <c r="N38" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -7106,7 +7098,7 @@
       </c>
       <c r="O38" s="14" t="inlineStr">
         <is>
-          <t>Condition: used. FLIP: 5-burner cooktop $250, excellent; rough resale $600-900</t>
+          <t>Condition: used.</t>
         </is>
       </c>
     </row>
@@ -7118,7 +7110,7 @@
       </c>
       <c r="B39" s="14" t="inlineStr">
         <is>
-          <t>WOLF Range GE Monogram Fridge Wolf Hood Combo Stainless Steel</t>
+          <t>Wolf Range With Convection Oven Stainless Steel 30" 4 Burners</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
@@ -7141,11 +7133,11 @@
       </c>
       <c r="G39" s="13" t="inlineStr">
         <is>
-          <t>$9,000</t>
+          <t>$1,900</t>
         </is>
       </c>
       <c r="H39" s="15" t="n">
-        <v>9000</v>
+        <v>1900</v>
       </c>
       <c r="I39" s="13" t="inlineStr"/>
       <c r="J39" s="13" t="inlineStr"/>
@@ -7179,7 +7171,7 @@
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>Wolf Range With Convection Oven Stainless Steel 30" 4 Burners</t>
+          <t>Wolf 30” Double Oven In Great Condition Gas</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
@@ -7202,11 +7194,11 @@
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
-          <t>$1,900</t>
+          <t>$1,500</t>
         </is>
       </c>
       <c r="H40" s="15" t="n">
-        <v>1900</v>
+        <v>1500</v>
       </c>
       <c r="I40" s="13" t="inlineStr"/>
       <c r="J40" s="13" t="inlineStr"/>
@@ -7240,7 +7232,7 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>Wolf 30” Double Oven In Great Condition Gas</t>
+          <t>Spectacular Deal - Wolf Gas Range</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
@@ -7250,7 +7242,7 @@
       </c>
       <c r="D41" s="13" t="inlineStr">
         <is>
-          <t>Stamford</t>
+          <t>Greenwich</t>
         </is>
       </c>
       <c r="E41" s="13" t="inlineStr">
@@ -7259,15 +7251,15 @@
         </is>
       </c>
       <c r="F41" s="13" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t>$1,500</t>
+          <t>$2,000</t>
         </is>
       </c>
       <c r="H41" s="15" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="I41" s="13" t="inlineStr"/>
       <c r="J41" s="13" t="inlineStr"/>
@@ -7281,7 +7273,11 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M41" s="13" t="inlineStr"/>
+      <c r="M41" s="20" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
       <c r="N41" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -7289,7 +7285,7 @@
       </c>
       <c r="O41" s="14" t="inlineStr">
         <is>
-          <t>Condition: used.</t>
+          <t>Condition: used. FLIP?: DF364C-LP 36" dual fuel $2,000; rough resale $3-4k</t>
         </is>
       </c>
     </row>
@@ -7301,7 +7297,7 @@
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>Spectacular Deal - Wolf Gas Range</t>
+          <t>WOLF Subzero 30" Gas Range Conventional Stove Stainless Steel</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
@@ -7324,11 +7320,11 @@
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>$2,000</t>
+          <t>$2,300</t>
         </is>
       </c>
       <c r="H42" s="15" t="n">
-        <v>2000</v>
+        <v>2300</v>
       </c>
       <c r="I42" s="13" t="inlineStr"/>
       <c r="J42" s="13" t="inlineStr"/>
@@ -7342,11 +7338,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M42" s="20" t="inlineStr">
-        <is>
-          <t>FLIP</t>
-        </is>
-      </c>
+      <c r="M42" s="13" t="inlineStr"/>
       <c r="N42" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -7354,7 +7346,7 @@
       </c>
       <c r="O42" s="14" t="inlineStr">
         <is>
-          <t>Condition: used. FLIP?: DF364C-LP 36" dual fuel $2,000; rough resale $3-4k</t>
+          <t>Condition: used.</t>
         </is>
       </c>
     </row>
@@ -7366,7 +7358,7 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>WOLF Subzero 30" Gas Range Conventional Stove Stainless Steel</t>
+          <t>Wolf 36" Electric Stove Range Cooktop 5 Burners</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
@@ -7389,11 +7381,11 @@
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t>$2,300</t>
+          <t>$1,400</t>
         </is>
       </c>
       <c r="H43" s="15" t="n">
-        <v>2300</v>
+        <v>1400</v>
       </c>
       <c r="I43" s="13" t="inlineStr"/>
       <c r="J43" s="13" t="inlineStr"/>
@@ -7427,40 +7419,44 @@
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>Wolf 36" Electric Stove Range Cooktop 5 Burners</t>
+          <t>WOLF Gourmet Elite Countertop Convection Oven (red knob)</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>range/oven/rangetop</t>
+          <t>countertop</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
         <is>
-          <t>Greenwich</t>
+          <t>Armonk</t>
         </is>
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F44" s="13" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>$1,400</t>
+          <t>$650</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
-        <v>1400</v>
-      </c>
-      <c r="I44" s="13" t="inlineStr"/>
+        <v>650</v>
+      </c>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
       <c r="J44" s="13" t="inlineStr"/>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>OfferUp</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L44" s="13" t="inlineStr">
@@ -7476,7 +7472,7 @@
       </c>
       <c r="O44" s="14" t="inlineStr">
         <is>
-          <t>Condition: used.</t>
+          <t>Good working condition; orig. $1,800. Updated 2026-10-15.</t>
         </is>
       </c>
     </row>
@@ -7488,7 +7484,7 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>WOLF Gourmet Elite Countertop Convection Oven (red knob)</t>
+          <t>Wolf Gourmet - Programmable Coffee System</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
@@ -7498,7 +7494,7 @@
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>Armonk</t>
+          <t>Rye</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -7507,25 +7503,21 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>$650</t>
+          <t>$200</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
-        <v>650</v>
-      </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>2026-07-27</t>
-        </is>
-      </c>
+        <v>200</v>
+      </c>
+      <c r="I45" s="13" t="inlineStr"/>
       <c r="J45" s="13" t="inlineStr"/>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>OfferUp</t>
         </is>
       </c>
       <c r="L45" s="13" t="inlineStr">
@@ -7541,7 +7533,7 @@
       </c>
       <c r="O45" s="14" t="inlineStr">
         <is>
-          <t>Good working condition; orig. $1,800. Updated 2026-10-15.</t>
+          <t>Condition: used.</t>
         </is>
       </c>
     </row>
@@ -7553,17 +7545,17 @@
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>Wolf Gourmet - Programmable Coffee System</t>
+          <t>Wolf 30" E Series Built-In Convection Wall Oven SO30TE/S/TH</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>countertop</t>
+          <t>range/rangetop/oven/cooktop</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
         <is>
-          <t>Rye</t>
+          <t>Stony Point</t>
         </is>
       </c>
       <c r="E46" s="13" t="inlineStr">
@@ -7572,21 +7564,25 @@
         </is>
       </c>
       <c r="F46" s="13" t="n">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="G46" s="13" t="inlineStr">
         <is>
-          <t>$200</t>
+          <t>$2,500</t>
         </is>
       </c>
       <c r="H46" s="15" t="n">
-        <v>200</v>
-      </c>
-      <c r="I46" s="13" t="inlineStr"/>
+        <v>2500</v>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="J46" s="13" t="inlineStr"/>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>OfferUp</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L46" s="13" t="inlineStr">
@@ -7602,7 +7598,7 @@
       </c>
       <c r="O46" s="14" t="inlineStr">
         <is>
-          <t>Condition: used.</t>
+          <t>2017 stainless dual convection Wi-Fi; seller says works perfectly, dusty from reno. Pickup Stony Point NY (Garnerville CL). Mid-market ask; flip=false.</t>
         </is>
       </c>
     </row>
@@ -7614,17 +7610,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>Wolf 30" E Series Built-In Convection Wall Oven SO30TE/S/TH</t>
+          <t>WOLF 30" Warming Drawer</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>range/rangetop/oven/cooktop</t>
+          <t>range/oven/rangetop</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>Stony Point</t>
+          <t>Wallkill</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -7633,25 +7629,21 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
-          <t>$2,500</t>
+          <t>$500</t>
         </is>
       </c>
       <c r="H47" s="15" t="n">
-        <v>2500</v>
-      </c>
-      <c r="I47" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
+        <v>500</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr"/>
       <c r="J47" s="13" t="inlineStr"/>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>OfferUp</t>
         </is>
       </c>
       <c r="L47" s="13" t="inlineStr">
@@ -7667,7 +7659,7 @@
       </c>
       <c r="O47" s="14" t="inlineStr">
         <is>
-          <t>2017 stainless dual convection Wi-Fi; seller says works perfectly, dusty from reno. Pickup Stony Point NY (Garnerville CL). Mid-market ask; flip=false.</t>
+          <t>Condition: used.</t>
         </is>
       </c>
     </row>
@@ -7679,7 +7671,7 @@
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>WOLF 30" Warming Drawer</t>
+          <t>Wolf 30inch GR304 natural gas range</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
@@ -7689,7 +7681,7 @@
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>Wallkill</t>
+          <t>Florida</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -7698,21 +7690,25 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>$500</t>
+          <t>$2,500</t>
         </is>
       </c>
       <c r="H48" s="15" t="n">
-        <v>500</v>
-      </c>
-      <c r="I48" s="13" t="inlineStr"/>
+        <v>2500</v>
+      </c>
+      <c r="I48" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
       <c r="J48" s="13" t="inlineStr"/>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>OfferUp</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L48" s="13" t="inlineStr">
@@ -7732,118 +7728,118 @@
         </is>
       </c>
     </row>
-    <row r="49" outlineLevel="1">
-      <c r="A49" s="13" t="inlineStr">
-        <is>
-          <t>CT / Hudson Valley</t>
-        </is>
-      </c>
-      <c r="B49" s="14" t="inlineStr">
-        <is>
-          <t>Wolf 30inch GR304 natural gas range</t>
-        </is>
-      </c>
-      <c r="C49" s="13" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — CT / Hudson Valley</t>
+        </is>
+      </c>
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>18 item(s)</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="n"/>
+      <c r="D49" s="18" t="n"/>
+      <c r="E49" s="18" t="n"/>
+      <c r="F49" s="18" t="n"/>
+      <c r="G49" s="18" t="n"/>
+      <c r="H49" s="19" t="n">
+        <v>33050</v>
+      </c>
+      <c r="I49" s="18" t="n"/>
+      <c r="J49" s="18" t="n"/>
+      <c r="K49" s="18" t="n"/>
+      <c r="L49" s="18" t="n"/>
+      <c r="M49" s="18" t="n"/>
+      <c r="N49" s="18" t="n"/>
+      <c r="O49" s="18" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="11" t="inlineStr">
+        <is>
+          <t>▸ NYC / Long Island / NJ  (65)</t>
+        </is>
+      </c>
+      <c r="B50" s="12" t="n"/>
+      <c r="C50" s="12" t="n"/>
+      <c r="D50" s="12" t="n"/>
+      <c r="E50" s="12" t="n"/>
+      <c r="F50" s="12" t="n"/>
+      <c r="G50" s="12" t="n"/>
+      <c r="H50" s="12" t="n"/>
+      <c r="I50" s="12" t="n"/>
+      <c r="J50" s="12" t="n"/>
+      <c r="K50" s="12" t="n"/>
+      <c r="L50" s="12" t="n"/>
+      <c r="M50" s="12" t="n"/>
+      <c r="N50" s="12" t="n"/>
+      <c r="O50" s="12" t="n"/>
+    </row>
+    <row r="51" outlineLevel="1">
+      <c r="A51" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B51" s="14" t="inlineStr">
+        <is>
+          <t>Wolf Electric Insert</t>
+        </is>
+      </c>
+      <c r="C51" s="13" t="inlineStr">
         <is>
           <t>range/oven/rangetop</t>
         </is>
       </c>
-      <c r="D49" s="13" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="E49" s="13" t="inlineStr">
+      <c r="D51" s="13" t="inlineStr">
+        <is>
+          <t>Central Islip</t>
+        </is>
+      </c>
+      <c r="E51" s="13" t="inlineStr">
         <is>
           <t>NY</t>
         </is>
       </c>
-      <c r="F49" s="13" t="n">
-        <v>191</v>
-      </c>
-      <c r="G49" s="13" t="inlineStr">
-        <is>
-          <t>$2,500</t>
-        </is>
-      </c>
-      <c r="H49" s="15" t="n">
-        <v>2500</v>
-      </c>
-      <c r="I49" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="J49" s="13" t="inlineStr"/>
-      <c r="K49" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L49" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M49" s="13" t="inlineStr"/>
-      <c r="N49" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O49" s="14" t="inlineStr">
-        <is>
-          <t>Condition: used.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — CT / Hudson Valley</t>
-        </is>
-      </c>
-      <c r="B50" s="17" t="inlineStr">
-        <is>
-          <t>19 item(s)</t>
-        </is>
-      </c>
-      <c r="C50" s="18" t="n"/>
-      <c r="D50" s="18" t="n"/>
-      <c r="E50" s="18" t="n"/>
-      <c r="F50" s="18" t="n"/>
-      <c r="G50" s="18" t="n"/>
-      <c r="H50" s="19" t="n">
-        <v>33156</v>
-      </c>
-      <c r="I50" s="18" t="n"/>
-      <c r="J50" s="18" t="n"/>
-      <c r="K50" s="18" t="n"/>
-      <c r="L50" s="18" t="n"/>
-      <c r="M50" s="18" t="n"/>
-      <c r="N50" s="18" t="n"/>
-      <c r="O50" s="18" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>▸ NYC / Long Island / NJ  (65)</t>
-        </is>
-      </c>
-      <c r="B51" s="12" t="n"/>
-      <c r="C51" s="12" t="n"/>
-      <c r="D51" s="12" t="n"/>
-      <c r="E51" s="12" t="n"/>
-      <c r="F51" s="12" t="n"/>
-      <c r="G51" s="12" t="n"/>
-      <c r="H51" s="12" t="n"/>
-      <c r="I51" s="12" t="n"/>
-      <c r="J51" s="12" t="n"/>
-      <c r="K51" s="12" t="n"/>
-      <c r="L51" s="12" t="n"/>
-      <c r="M51" s="12" t="n"/>
-      <c r="N51" s="12" t="n"/>
-      <c r="O51" s="12" t="n"/>
+      <c r="F51" s="13" t="n">
+        <v>154</v>
+      </c>
+      <c r="G51" s="13" t="inlineStr">
+        <is>
+          <t>$100</t>
+        </is>
+      </c>
+      <c r="H51" s="15" t="n">
+        <v>100</v>
+      </c>
+      <c r="I51" s="13" t="inlineStr"/>
+      <c r="J51" s="13" t="inlineStr"/>
+      <c r="K51" s="13" t="inlineStr">
+        <is>
+          <t>OfferUp</t>
+        </is>
+      </c>
+      <c r="L51" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M51" s="20" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
+      <c r="N51" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O51" s="14" t="inlineStr">
+        <is>
+          <t>Condition: used. FLIP?: 30" electric cooktop insert $100; rough resale $300-600</t>
+        </is>
+      </c>
     </row>
     <row r="52" outlineLevel="1">
       <c r="A52" s="13" t="inlineStr">
@@ -7853,7 +7849,7 @@
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>Wolf Electric Insert</t>
+          <t>WOLF STOVE TOP + STOVE TOP &amp; Grill</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
@@ -7863,7 +7859,7 @@
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>Central Islip</t>
+          <t>Jericho</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -7872,15 +7868,15 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>154</v>
+        <v>168</v>
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
-          <t>$100</t>
+          <t>$700</t>
         </is>
       </c>
       <c r="H52" s="15" t="n">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="I52" s="13" t="inlineStr"/>
       <c r="J52" s="13" t="inlineStr"/>
@@ -7906,7 +7902,7 @@
       </c>
       <c r="O52" s="14" t="inlineStr">
         <is>
-          <t>Condition: used. FLIP?: 30" electric cooktop insert $100; rough resale $300-600</t>
+          <t>Condition: used. FLIP: 48" stovetop+grill $700; 48" rangetop ask $2,900; rough resale $1.5-2.5k</t>
         </is>
       </c>
     </row>
@@ -7918,17 +7914,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>WOLF STOVE TOP + STOVE TOP &amp; Grill</t>
+          <t>Wolf Gourmet Toaster Oven</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>range/oven/rangetop</t>
+          <t>countertop</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>Jericho</t>
+          <t>North Massapequa</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -7941,11 +7937,11 @@
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
-          <t>$700</t>
+          <t>$350</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
-        <v>700</v>
+        <v>350</v>
       </c>
       <c r="I53" s="13" t="inlineStr"/>
       <c r="J53" s="13" t="inlineStr"/>
@@ -7959,11 +7955,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M53" s="20" t="inlineStr">
-        <is>
-          <t>FLIP</t>
-        </is>
-      </c>
+      <c r="M53" s="13" t="inlineStr"/>
       <c r="N53" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -7971,7 +7963,7 @@
       </c>
       <c r="O53" s="14" t="inlineStr">
         <is>
-          <t>Condition: used. FLIP: 48" stovetop+grill $700; 48" rangetop ask $2,900; rough resale $1.5-2.5k</t>
+          <t>Condition: used.</t>
         </is>
       </c>
     </row>
@@ -7983,17 +7975,17 @@
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>Wolf Gourmet Toaster Oven</t>
+          <t>Wolf Oven</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>countertop</t>
+          <t>range/oven/rangetop</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>North Massapequa</t>
+          <t>Bethpage</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -8006,11 +7998,11 @@
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>$350</t>
+          <t>$1,000</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="I54" s="13" t="inlineStr"/>
       <c r="J54" s="13" t="inlineStr"/>
@@ -8044,7 +8036,7 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>Wolf Oven</t>
+          <t>Wolf microwave</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
@@ -8054,7 +8046,7 @@
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>Bethpage</t>
+          <t>Massapequa Park</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -8063,15 +8055,15 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
-          <t>$1,000</t>
+          <t>$2,000</t>
         </is>
       </c>
       <c r="H55" s="15" t="n">
-        <v>1000</v>
+        <v>2000</v>
       </c>
       <c r="I55" s="13" t="inlineStr"/>
       <c r="J55" s="13" t="inlineStr"/>
@@ -8105,7 +8097,7 @@
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>Wolf microwave</t>
+          <t>Cook Top Wolf 36 Inch Gas Plus Griddle Wolf Hood Included</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr">
@@ -8115,7 +8107,7 @@
       </c>
       <c r="D56" s="13" t="inlineStr">
         <is>
-          <t>Massapequa Park</t>
+          <t>Plandome</t>
         </is>
       </c>
       <c r="E56" s="13" t="inlineStr">
@@ -8124,15 +8116,15 @@
         </is>
       </c>
       <c r="F56" s="13" t="n">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>$2,000</t>
+          <t>$1,500</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="I56" s="13" t="inlineStr"/>
       <c r="J56" s="13" t="inlineStr"/>
@@ -8166,7 +8158,7 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>Cook Top Wolf 36 Inch Gas Plus Griddle Wolf Hood Included</t>
+          <t>Wolf Electric Double Oven</t>
         </is>
       </c>
       <c r="C57" s="13" t="inlineStr">
@@ -8176,7 +8168,7 @@
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>Plandome</t>
+          <t>Bronx</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -8185,15 +8177,15 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
-          <t>$1,500</t>
+          <t>$600</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
-        <v>1500</v>
+        <v>600</v>
       </c>
       <c r="I57" s="13" t="inlineStr"/>
       <c r="J57" s="13" t="inlineStr"/>
@@ -8207,7 +8199,11 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M57" s="13" t="inlineStr"/>
+      <c r="M57" s="20" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
       <c r="N57" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -8215,7 +8211,7 @@
       </c>
       <c r="O57" s="14" t="inlineStr">
         <is>
-          <t>Condition: used.</t>
+          <t>Condition: used. FLIP: electric double wall oven $600; comp ask $2,800; rough resale $1.5-2.5k</t>
         </is>
       </c>
     </row>
@@ -8227,7 +8223,7 @@
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>Wolf Electric Double Oven</t>
+          <t>Stove Wolf</t>
         </is>
       </c>
       <c r="C58" s="13" t="inlineStr">
@@ -8250,11 +8246,11 @@
       </c>
       <c r="G58" s="13" t="inlineStr">
         <is>
-          <t>$600</t>
+          <t>$950</t>
         </is>
       </c>
       <c r="H58" s="15" t="n">
-        <v>600</v>
+        <v>950</v>
       </c>
       <c r="I58" s="13" t="inlineStr"/>
       <c r="J58" s="13" t="inlineStr"/>
@@ -8280,7 +8276,7 @@
       </c>
       <c r="O58" s="14" t="inlineStr">
         <is>
-          <t>Condition: used. FLIP: electric double wall oven $600; comp ask $2,800; rough resale $1.5-2.5k</t>
+          <t>Condition: used. FLIP?: dealer "Stove Wolf" $950 w/ warranty; size unknown</t>
         </is>
       </c>
     </row>
@@ -8292,7 +8288,7 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>Stove Wolf</t>
+          <t>Stove Wolf 30 Used</t>
         </is>
       </c>
       <c r="C59" s="13" t="inlineStr">
@@ -8315,11 +8311,11 @@
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
-          <t>$950</t>
+          <t>$2,500</t>
         </is>
       </c>
       <c r="H59" s="15" t="n">
-        <v>950</v>
+        <v>2500</v>
       </c>
       <c r="I59" s="13" t="inlineStr"/>
       <c r="J59" s="13" t="inlineStr"/>
@@ -8333,11 +8329,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M59" s="20" t="inlineStr">
-        <is>
-          <t>FLIP</t>
-        </is>
-      </c>
+      <c r="M59" s="13" t="inlineStr"/>
       <c r="N59" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -8345,7 +8337,7 @@
       </c>
       <c r="O59" s="14" t="inlineStr">
         <is>
-          <t>Condition: used. FLIP?: dealer "Stove Wolf" $950 w/ warranty; size unknown</t>
+          <t>Condition: used.</t>
         </is>
       </c>
     </row>
@@ -8357,7 +8349,7 @@
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>Stove Wolf 30 Used</t>
+          <t>Wolf R366 36” 6-Burner Professional Gas Range – $2,500 OBO</t>
         </is>
       </c>
       <c r="C60" s="13" t="inlineStr">
@@ -8367,7 +8359,7 @@
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>Bronx</t>
+          <t>Queens</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
@@ -8376,7 +8368,7 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
@@ -8386,7 +8378,11 @@
       <c r="H60" s="15" t="n">
         <v>2500</v>
       </c>
-      <c r="I60" s="13" t="inlineStr"/>
+      <c r="I60" s="13" t="inlineStr">
+        <is>
+          <t>posted ~13 days ago</t>
+        </is>
+      </c>
       <c r="J60" s="13" t="inlineStr"/>
       <c r="K60" s="13" t="inlineStr">
         <is>
@@ -8418,7 +8414,7 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>Wolf R366 36” 6-Burner Professional Gas Range – $2,500 OBO</t>
+          <t>OVEN WOLF RANGE</t>
         </is>
       </c>
       <c r="C61" s="13" t="inlineStr">
@@ -8441,17 +8437,13 @@
       </c>
       <c r="G61" s="13" t="inlineStr">
         <is>
-          <t>$2,500</t>
+          <t>$1,800</t>
         </is>
       </c>
       <c r="H61" s="15" t="n">
-        <v>2500</v>
-      </c>
-      <c r="I61" s="13" t="inlineStr">
-        <is>
-          <t>posted ~13 days ago</t>
-        </is>
-      </c>
+        <v>1800</v>
+      </c>
+      <c r="I61" s="13" t="inlineStr"/>
       <c r="J61" s="13" t="inlineStr"/>
       <c r="K61" s="13" t="inlineStr">
         <is>
@@ -8483,7 +8475,7 @@
       </c>
       <c r="B62" s="14" t="inlineStr">
         <is>
-          <t>OVEN WOLF RANGE</t>
+          <t>Sub Zero Fridge Wolf Stove and Dishwasher</t>
         </is>
       </c>
       <c r="C62" s="13" t="inlineStr">
@@ -8493,30 +8485,34 @@
       </c>
       <c r="D62" s="13" t="inlineStr">
         <is>
-          <t>Queens</t>
+          <t>Haworth</t>
         </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G62" s="13" t="inlineStr">
         <is>
-          <t>$1,800</t>
+          <t>$0</t>
         </is>
       </c>
       <c r="H62" s="15" t="n">
-        <v>1800</v>
-      </c>
-      <c r="I62" s="13" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="I62" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
       <c r="J62" s="13" t="inlineStr"/>
       <c r="K62" s="13" t="inlineStr">
         <is>
-          <t>OfferUp</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L62" s="13" t="inlineStr">
@@ -8524,7 +8520,11 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M62" s="13" t="inlineStr"/>
+      <c r="M62" s="20" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
       <c r="N62" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -8532,7 +8532,7 @@
       </c>
       <c r="O62" s="14" t="inlineStr">
         <is>
-          <t>Condition: used.</t>
+          <t>Condition: used. FLIP: FREE Sub-Zero+Wolf stove+DW; posted 9/10, may be gone</t>
         </is>
       </c>
     </row>
@@ -8544,7 +8544,7 @@
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>Sub Zero Fridge Wolf Stove and Dishwasher</t>
+          <t>Wolf Stove and Sub Zero Fridge</t>
         </is>
       </c>
       <c r="C63" s="13" t="inlineStr">
@@ -8567,15 +8567,15 @@
       </c>
       <c r="G63" s="13" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>$1</t>
         </is>
       </c>
       <c r="H63" s="15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I63" s="13" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="J63" s="13" t="inlineStr"/>
@@ -8601,7 +8601,7 @@
       </c>
       <c r="O63" s="14" t="inlineStr">
         <is>
-          <t>Condition: used. FLIP: FREE Sub-Zero+Wolf stove+DW; posted 9/10, may be gone</t>
+          <t>Condition: used. FLIP: $1/best offer 30" Wolf + 36" Sub-Zero; posted 9/9, may be stale</t>
         </is>
       </c>
     </row>
@@ -8613,7 +8613,7 @@
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stove and Sub Zero Fridge</t>
+          <t>30in Wolf Gas Stove And Hood</t>
         </is>
       </c>
       <c r="C64" s="13" t="inlineStr">
@@ -8623,34 +8623,30 @@
       </c>
       <c r="D64" s="13" t="inlineStr">
         <is>
-          <t>Haworth</t>
+          <t>East Atlantic Beach</t>
         </is>
       </c>
       <c r="E64" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G64" s="13" t="inlineStr">
         <is>
-          <t>$1</t>
+          <t>$1,000</t>
         </is>
       </c>
       <c r="H64" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="I64" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-09</t>
-        </is>
-      </c>
+        <v>1000</v>
+      </c>
+      <c r="I64" s="13" t="inlineStr"/>
       <c r="J64" s="13" t="inlineStr"/>
       <c r="K64" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>OfferUp</t>
         </is>
       </c>
       <c r="L64" s="13" t="inlineStr">
@@ -8670,7 +8666,7 @@
       </c>
       <c r="O64" s="14" t="inlineStr">
         <is>
-          <t>Condition: used. FLIP: $1/best offer 30" Wolf + 36" Sub-Zero; posted 9/9, may be stale</t>
+          <t>Condition: used. FLIP: 30" gas range + hood $1,000, working; rough resale $2-3k</t>
         </is>
       </c>
     </row>
@@ -8682,7 +8678,7 @@
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>30in Wolf Gas Stove And Hood</t>
+          <t>Wolf Industrial Stove/griddle Combo</t>
         </is>
       </c>
       <c r="C65" s="13" t="inlineStr">
@@ -8692,16 +8688,16 @@
       </c>
       <c r="D65" s="13" t="inlineStr">
         <is>
-          <t>East Atlantic Beach</t>
+          <t>Oradell</t>
         </is>
       </c>
       <c r="E65" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F65" s="13" t="n">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G65" s="13" t="inlineStr">
         <is>
@@ -8723,11 +8719,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M65" s="20" t="inlineStr">
-        <is>
-          <t>FLIP</t>
-        </is>
-      </c>
+      <c r="M65" s="13" t="inlineStr"/>
       <c r="N65" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -8735,7 +8727,7 @@
       </c>
       <c r="O65" s="14" t="inlineStr">
         <is>
-          <t>Condition: used. FLIP: 30" gas range + hood $1,000, working; rough resale $2-3k</t>
+          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf)</t>
         </is>
       </c>
     </row>
@@ -8747,22 +8739,22 @@
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>Wolf Industrial Stove/griddle Combo</t>
+          <t>Wolf M Series CSO30CM/B/TH 30" convection steam oven (black, tubular handle)</t>
         </is>
       </c>
       <c r="C66" s="13" t="inlineStr">
         <is>
-          <t>range/oven/rangetop</t>
+          <t>range/rangetop/oven/cooktop</t>
         </is>
       </c>
       <c r="D66" s="13" t="inlineStr">
         <is>
-          <t>Oradell</t>
+          <t>Jackson Heights</t>
         </is>
       </c>
       <c r="E66" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F66" s="13" t="n">
@@ -8770,17 +8762,21 @@
       </c>
       <c r="G66" s="13" t="inlineStr">
         <is>
-          <t>$1,000</t>
+          <t>$500</t>
         </is>
       </c>
       <c r="H66" s="15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="I66" s="13" t="inlineStr"/>
+        <v>500</v>
+      </c>
+      <c r="I66" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
       <c r="J66" s="13" t="inlineStr"/>
       <c r="K66" s="13" t="inlineStr">
         <is>
-          <t>OfferUp</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L66" s="13" t="inlineStr">
@@ -8788,7 +8784,11 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M66" s="13" t="inlineStr"/>
+      <c r="M66" s="20" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
       <c r="N66" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="O66" s="14" t="inlineStr">
         <is>
-          <t>Condition: used. commercial Wolf (not Sub-Zero Wolf)</t>
+          <t>Listed "like new", barely used; uninstalled and stored, seller clearing storage. Non-plumbed water tank. Strong flip at $500 for a current M Series built-in steam oven; verify it powers on and the tank/probe are included.</t>
         </is>
       </c>
     </row>
@@ -8808,17 +8808,17 @@
       </c>
       <c r="B67" s="14" t="inlineStr">
         <is>
-          <t>Wolf M Series CSO30CM/B/TH 30" convection steam oven (black, tubular handle)</t>
+          <t>Wolf 36" Contemporary Gas Cooktop (Model: CG365T/S) – Excellent Condition</t>
         </is>
       </c>
       <c r="C67" s="13" t="inlineStr">
         <is>
-          <t>range/rangetop/oven/cooktop</t>
+          <t>range/oven/rangetop</t>
         </is>
       </c>
       <c r="D67" s="13" t="inlineStr">
         <is>
-          <t>Jackson Heights</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="E67" s="13" t="inlineStr">
@@ -8827,25 +8827,21 @@
         </is>
       </c>
       <c r="F67" s="13" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G67" s="13" t="inlineStr">
         <is>
-          <t>$500</t>
+          <t>$950</t>
         </is>
       </c>
       <c r="H67" s="15" t="n">
-        <v>500</v>
-      </c>
-      <c r="I67" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
+        <v>950</v>
+      </c>
+      <c r="I67" s="13" t="inlineStr"/>
       <c r="J67" s="13" t="inlineStr"/>
       <c r="K67" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>OfferUp</t>
         </is>
       </c>
       <c r="L67" s="13" t="inlineStr">
@@ -8853,11 +8849,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M67" s="20" t="inlineStr">
-        <is>
-          <t>FLIP</t>
-        </is>
-      </c>
+      <c r="M67" s="13" t="inlineStr"/>
       <c r="N67" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -8865,7 +8857,7 @@
       </c>
       <c r="O67" s="14" t="inlineStr">
         <is>
-          <t>Listed "like new", barely used; uninstalled and stored, seller clearing storage. Non-plumbed water tank. Strong flip at $500 for a current M Series built-in steam oven; verify it powers on and the tank/probe are included.</t>
+          <t>Condition: used.</t>
         </is>
       </c>
     </row>
@@ -8877,7 +8869,7 @@
       </c>
       <c r="B68" s="14" t="inlineStr">
         <is>
-          <t>Wolf 36" Contemporary Gas Cooktop (Model: CG365T/S) – Excellent Condition</t>
+          <t>Wolf 36" Contemporary Gas Cooktop (Model: CG365T/S) – Excellent Condit</t>
         </is>
       </c>
       <c r="C68" s="13" t="inlineStr">
@@ -8906,11 +8898,15 @@
       <c r="H68" s="15" t="n">
         <v>950</v>
       </c>
-      <c r="I68" s="13" t="inlineStr"/>
+      <c r="I68" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
       <c r="J68" s="13" t="inlineStr"/>
       <c r="K68" s="13" t="inlineStr">
         <is>
-          <t>OfferUp</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L68" s="13" t="inlineStr">
@@ -8938,7 +8934,7 @@
       </c>
       <c r="B69" s="14" t="inlineStr">
         <is>
-          <t>Wolf 36" Contemporary Gas Cooktop (Model: CG365T/S) – Excellent Condit</t>
+          <t>Wolf Built In Microwave /Convection Oven</t>
         </is>
       </c>
       <c r="C69" s="13" t="inlineStr">
@@ -8948,7 +8944,7 @@
       </c>
       <c r="D69" s="13" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Brooklyn</t>
         </is>
       </c>
       <c r="E69" s="13" t="inlineStr">
@@ -8957,25 +8953,21 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="G69" s="13" t="inlineStr">
         <is>
-          <t>$950</t>
+          <t>$350</t>
         </is>
       </c>
       <c r="H69" s="15" t="n">
-        <v>950</v>
-      </c>
-      <c r="I69" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
+        <v>350</v>
+      </c>
+      <c r="I69" s="13" t="inlineStr"/>
       <c r="J69" s="13" t="inlineStr"/>
       <c r="K69" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>OfferUp</t>
         </is>
       </c>
       <c r="L69" s="13" t="inlineStr">
@@ -9003,7 +8995,7 @@
       </c>
       <c r="B70" s="14" t="inlineStr">
         <is>
-          <t>Wolf Built In Microwave /Convection Oven</t>
+          <t>Wolf stove 60"" originally payed $ 18000, barely used</t>
         </is>
       </c>
       <c r="C70" s="13" t="inlineStr">
@@ -9013,12 +9005,12 @@
       </c>
       <c r="D70" s="13" t="inlineStr">
         <is>
-          <t>Brooklyn</t>
+          <t>Weehawken</t>
         </is>
       </c>
       <c r="E70" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F70" s="13" t="n">
@@ -9026,11 +9018,11 @@
       </c>
       <c r="G70" s="13" t="inlineStr">
         <is>
-          <t>$350</t>
+          <t>$11,000</t>
         </is>
       </c>
       <c r="H70" s="15" t="n">
-        <v>350</v>
+        <v>11000</v>
       </c>
       <c r="I70" s="13" t="inlineStr"/>
       <c r="J70" s="13" t="inlineStr"/>
@@ -9064,7 +9056,7 @@
       </c>
       <c r="B71" s="14" t="inlineStr">
         <is>
-          <t>Wolf stove 60"" originally payed $ 18000, barely used</t>
+          <t>48" Wolf Oven - Needs TLC But Works Great</t>
         </is>
       </c>
       <c r="C71" s="13" t="inlineStr">
@@ -9074,7 +9066,7 @@
       </c>
       <c r="D71" s="13" t="inlineStr">
         <is>
-          <t>Weehawken</t>
+          <t>Secaucus</t>
         </is>
       </c>
       <c r="E71" s="13" t="inlineStr">
@@ -9083,15 +9075,15 @@
         </is>
       </c>
       <c r="F71" s="13" t="n">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G71" s="13" t="inlineStr">
         <is>
-          <t>$11,000</t>
+          <t>$2,000</t>
         </is>
       </c>
       <c r="H71" s="15" t="n">
-        <v>11000</v>
+        <v>2000</v>
       </c>
       <c r="I71" s="13" t="inlineStr"/>
       <c r="J71" s="13" t="inlineStr"/>
@@ -9105,7 +9097,11 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M71" s="13" t="inlineStr"/>
+      <c r="M71" s="20" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
       <c r="N71" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -9113,7 +9109,7 @@
       </c>
       <c r="O71" s="14" t="inlineStr">
         <is>
-          <t>Condition: used.</t>
+          <t>Condition: used. FLIP: 48" double-oven range $2,000, needs TLC; 48" sold $3.8-3.9k; resale $3.5-5k</t>
         </is>
       </c>
     </row>
@@ -9125,7 +9121,7 @@
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>48" Wolf Oven - Needs TLC But Works Great</t>
+          <t>🔥 WOLF PROFESSIONAL APPLIANCES — COMPLETE KITCHEN SET</t>
         </is>
       </c>
       <c r="C72" s="13" t="inlineStr">
@@ -9135,7 +9131,7 @@
       </c>
       <c r="D72" s="13" t="inlineStr">
         <is>
-          <t>Secaucus</t>
+          <t>Franklin Lakes</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
@@ -9148,11 +9144,11 @@
       </c>
       <c r="G72" s="13" t="inlineStr">
         <is>
-          <t>$2,000</t>
+          <t>$5,000</t>
         </is>
       </c>
       <c r="H72" s="15" t="n">
-        <v>2000</v>
+        <v>5000</v>
       </c>
       <c r="I72" s="13" t="inlineStr"/>
       <c r="J72" s="13" t="inlineStr"/>
@@ -9166,11 +9162,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M72" s="20" t="inlineStr">
-        <is>
-          <t>FLIP</t>
-        </is>
-      </c>
+      <c r="M72" s="13" t="inlineStr"/>
       <c r="N72" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -9178,7 +9170,7 @@
       </c>
       <c r="O72" s="14" t="inlineStr">
         <is>
-          <t>Condition: used. FLIP: 48" double-oven range $2,000, needs TLC; 48" sold $3.8-3.9k; resale $3.5-5k</t>
+          <t>Condition: used.</t>
         </is>
       </c>
     </row>
@@ -9190,7 +9182,7 @@
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>🔥 WOLF PROFESSIONAL APPLIANCES — COMPLETE KITCHEN SET</t>
+          <t>Wolf Stove 36 inch used excellent condition</t>
         </is>
       </c>
       <c r="C73" s="13" t="inlineStr">
@@ -9200,7 +9192,7 @@
       </c>
       <c r="D73" s="13" t="inlineStr">
         <is>
-          <t>Franklin Lakes</t>
+          <t>Secaucus</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
@@ -9213,11 +9205,11 @@
       </c>
       <c r="G73" s="13" t="inlineStr">
         <is>
-          <t>$5,000</t>
+          <t>$4,450</t>
         </is>
       </c>
       <c r="H73" s="15" t="n">
-        <v>5000</v>
+        <v>4450</v>
       </c>
       <c r="I73" s="13" t="inlineStr"/>
       <c r="J73" s="13" t="inlineStr"/>
@@ -9251,7 +9243,7 @@
       </c>
       <c r="B74" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stove 36 inch used excellent condition</t>
+          <t>Wolf Stainless Steel 5-Burner Gas Cooktop</t>
         </is>
       </c>
       <c r="C74" s="13" t="inlineStr">
@@ -9261,7 +9253,7 @@
       </c>
       <c r="D74" s="13" t="inlineStr">
         <is>
-          <t>Secaucus</t>
+          <t>Wallington</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
@@ -9270,17 +9262,21 @@
         </is>
       </c>
       <c r="F74" s="13" t="n">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="G74" s="13" t="inlineStr">
         <is>
-          <t>$4,450</t>
+          <t>$400</t>
         </is>
       </c>
       <c r="H74" s="15" t="n">
-        <v>4450</v>
-      </c>
-      <c r="I74" s="13" t="inlineStr"/>
+        <v>400</v>
+      </c>
+      <c r="I74" s="13" t="inlineStr">
+        <is>
+          <t>posted ~1 day ago</t>
+        </is>
+      </c>
       <c r="J74" s="13" t="inlineStr"/>
       <c r="K74" s="13" t="inlineStr">
         <is>
@@ -9312,7 +9308,7 @@
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 5-Burner Gas Cooktop</t>
+          <t>Wolf 36 Dual Fuel Range DF366 Natural Gas (Beautiful USED Condition)</t>
         </is>
       </c>
       <c r="C75" s="13" t="inlineStr">
@@ -9322,7 +9318,7 @@
       </c>
       <c r="D75" s="13" t="inlineStr">
         <is>
-          <t>Wallington</t>
+          <t>Paterson</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
@@ -9335,17 +9331,13 @@
       </c>
       <c r="G75" s="13" t="inlineStr">
         <is>
-          <t>$400</t>
+          <t>$6,000</t>
         </is>
       </c>
       <c r="H75" s="15" t="n">
-        <v>400</v>
-      </c>
-      <c r="I75" s="13" t="inlineStr">
-        <is>
-          <t>posted ~1 day ago</t>
-        </is>
-      </c>
+        <v>6000</v>
+      </c>
+      <c r="I75" s="13" t="inlineStr"/>
       <c r="J75" s="13" t="inlineStr"/>
       <c r="K75" s="13" t="inlineStr">
         <is>
@@ -9377,7 +9369,7 @@
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>Wolf 36 Dual Fuel Range DF366 Natural Gas (Beautiful USED Condition)</t>
+          <t>Wolf Stainless Steel 36” Inch Wide Gas Range 4-Burners w/Grill</t>
         </is>
       </c>
       <c r="C76" s="13" t="inlineStr">
@@ -9387,7 +9379,7 @@
       </c>
       <c r="D76" s="13" t="inlineStr">
         <is>
-          <t>Paterson</t>
+          <t>Clifton</t>
         </is>
       </c>
       <c r="E76" s="13" t="inlineStr">
@@ -9396,21 +9388,25 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="G76" s="13" t="inlineStr">
         <is>
-          <t>$6,000</t>
+          <t>$3,800</t>
         </is>
       </c>
       <c r="H76" s="15" t="n">
-        <v>6000</v>
-      </c>
-      <c r="I76" s="13" t="inlineStr"/>
+        <v>3800</v>
+      </c>
+      <c r="I76" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
       <c r="J76" s="13" t="inlineStr"/>
       <c r="K76" s="13" t="inlineStr">
         <is>
-          <t>OfferUp</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L76" s="13" t="inlineStr">
@@ -9438,7 +9434,7 @@
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 36” Inch Wide Gas Range 4-Burners w/Grill</t>
+          <t>Wolf Stainless Steel 48” Inch Wide Gas Range &amp; Wolf 48” Range Hood</t>
         </is>
       </c>
       <c r="C77" s="13" t="inlineStr">
@@ -9461,11 +9457,11 @@
       </c>
       <c r="G77" s="13" t="inlineStr">
         <is>
-          <t>$3,800</t>
+          <t>$6,800</t>
         </is>
       </c>
       <c r="H77" s="15" t="n">
-        <v>3800</v>
+        <v>6800</v>
       </c>
       <c r="I77" s="13" t="inlineStr">
         <is>
@@ -9503,7 +9499,7 @@
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 48” Inch Wide Gas Range &amp; Wolf 48” Range Hood</t>
+          <t>Wolf Stainless 48” Gas Range/Wolf Hood 48”/Subzero Fridge 48” Wide</t>
         </is>
       </c>
       <c r="C78" s="13" t="inlineStr">
@@ -9526,11 +9522,11 @@
       </c>
       <c r="G78" s="13" t="inlineStr">
         <is>
-          <t>$6,800</t>
+          <t>$12,800</t>
         </is>
       </c>
       <c r="H78" s="15" t="n">
-        <v>6800</v>
+        <v>12800</v>
       </c>
       <c r="I78" s="13" t="inlineStr">
         <is>
@@ -9568,7 +9564,7 @@
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless 48” Gas Range/Wolf Hood 48”/Subzero Fridge 48” Wide</t>
+          <t>Wolf Stainless Steel 36” Wide Gas Range</t>
         </is>
       </c>
       <c r="C79" s="13" t="inlineStr">
@@ -9591,11 +9587,11 @@
       </c>
       <c r="G79" s="13" t="inlineStr">
         <is>
-          <t>$12,800</t>
+          <t>$2,800</t>
         </is>
       </c>
       <c r="H79" s="15" t="n">
-        <v>12800</v>
+        <v>2800</v>
       </c>
       <c r="I79" s="13" t="inlineStr">
         <is>
@@ -9633,7 +9629,7 @@
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 36” Wide Gas Range</t>
+          <t>Wolf Stainless Steel 48” Inch Wide Gas Range</t>
         </is>
       </c>
       <c r="C80" s="13" t="inlineStr">
@@ -9656,11 +9652,11 @@
       </c>
       <c r="G80" s="13" t="inlineStr">
         <is>
-          <t>$2,800</t>
+          <t>$3,500</t>
         </is>
       </c>
       <c r="H80" s="15" t="n">
-        <v>2800</v>
+        <v>3500</v>
       </c>
       <c r="I80" s="13" t="inlineStr">
         <is>
@@ -9698,7 +9694,7 @@
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 48” Inch Wide Gas Range</t>
+          <t>GE Monogram Stainless 48” Fridge &amp; Wolf Gas Range 48” Wide</t>
         </is>
       </c>
       <c r="C81" s="13" t="inlineStr">
@@ -9721,11 +9717,11 @@
       </c>
       <c r="G81" s="13" t="inlineStr">
         <is>
-          <t>$3,500</t>
+          <t>$8,800</t>
         </is>
       </c>
       <c r="H81" s="15" t="n">
-        <v>3500</v>
+        <v>8800</v>
       </c>
       <c r="I81" s="13" t="inlineStr">
         <is>
@@ -9763,7 +9759,7 @@
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>GE Monogram Stainless 48” Fridge &amp; Wolf Gas Range 48” Wide</t>
+          <t>Subzero Panel Ready Fridge 48” Wide/Wolf Gas Range 48” Wide</t>
         </is>
       </c>
       <c r="C82" s="13" t="inlineStr">
@@ -9786,11 +9782,11 @@
       </c>
       <c r="G82" s="13" t="inlineStr">
         <is>
-          <t>$8,800</t>
+          <t>$11,600</t>
         </is>
       </c>
       <c r="H82" s="15" t="n">
-        <v>8800</v>
+        <v>11600</v>
       </c>
       <c r="I82" s="13" t="inlineStr">
         <is>
@@ -9828,7 +9824,7 @@
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>Subzero Panel Ready Fridge 48” Wide/Wolf Gas Range 48” Wide</t>
+          <t>Wolf Stainless Steel 48” Inch Wide All Gas Range</t>
         </is>
       </c>
       <c r="C83" s="13" t="inlineStr">
@@ -9851,11 +9847,11 @@
       </c>
       <c r="G83" s="13" t="inlineStr">
         <is>
-          <t>$11,600</t>
+          <t>$4,800</t>
         </is>
       </c>
       <c r="H83" s="15" t="n">
-        <v>11600</v>
+        <v>4800</v>
       </c>
       <c r="I83" s="13" t="inlineStr">
         <is>
@@ -9893,7 +9889,7 @@
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 48” Inch Wide All Gas Range</t>
+          <t>Wolf Stainless Steel 36” Gas Range &amp; Subzero Stainless 36” Fridge</t>
         </is>
       </c>
       <c r="C84" s="13" t="inlineStr">
@@ -9916,11 +9912,11 @@
       </c>
       <c r="G84" s="13" t="inlineStr">
         <is>
-          <t>$4,800</t>
+          <t>$7,800</t>
         </is>
       </c>
       <c r="H84" s="15" t="n">
-        <v>4800</v>
+        <v>7800</v>
       </c>
       <c r="I84" s="13" t="inlineStr">
         <is>
@@ -9958,7 +9954,7 @@
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 36” Gas Range &amp; Subzero Stainless 36” Fridge</t>
+          <t>Subzero Panel Ready 3-Door Fridge/Wolf 36” Gas Range/Miele Dishwasher</t>
         </is>
       </c>
       <c r="C85" s="13" t="inlineStr">
@@ -9981,11 +9977,11 @@
       </c>
       <c r="G85" s="13" t="inlineStr">
         <is>
-          <t>$7,800</t>
+          <t>$9,800</t>
         </is>
       </c>
       <c r="H85" s="15" t="n">
-        <v>7800</v>
+        <v>9800</v>
       </c>
       <c r="I85" s="13" t="inlineStr">
         <is>
@@ -10023,7 +10019,7 @@
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>Subzero Panel Ready 3-Door Fridge/Wolf 36” Gas Range/Miele Dishwasher</t>
+          <t>Wolf Stainless Steel Gas Range 48” /Subzero 48” Fridge Panel Ready</t>
         </is>
       </c>
       <c r="C86" s="13" t="inlineStr">
@@ -10088,7 +10084,7 @@
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel Gas Range 48” /Subzero 48” Fridge Panel Ready</t>
+          <t>Wolf Stainless Steel 48” Inch Wide Gas Range (Propane Set) w/Grill</t>
         </is>
       </c>
       <c r="C87" s="13" t="inlineStr">
@@ -10111,11 +10107,11 @@
       </c>
       <c r="G87" s="13" t="inlineStr">
         <is>
-          <t>$9,800</t>
+          <t>$4,800</t>
         </is>
       </c>
       <c r="H87" s="15" t="n">
-        <v>9800</v>
+        <v>4800</v>
       </c>
       <c r="I87" s="13" t="inlineStr">
         <is>
@@ -10153,7 +10149,7 @@
       </c>
       <c r="B88" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 48” Inch Wide Gas Range (Propane Set) w/Grill</t>
+          <t>Subzero Two Panel Ready Column Fridges &amp; Wolf Gas Range 48” Wide</t>
         </is>
       </c>
       <c r="C88" s="13" t="inlineStr">
@@ -10176,11 +10172,11 @@
       </c>
       <c r="G88" s="13" t="inlineStr">
         <is>
-          <t>$4,800</t>
+          <t>$9,800</t>
         </is>
       </c>
       <c r="H88" s="15" t="n">
-        <v>4800</v>
+        <v>9800</v>
       </c>
       <c r="I88" s="13" t="inlineStr">
         <is>
@@ -10218,7 +10214,7 @@
       </c>
       <c r="B89" s="14" t="inlineStr">
         <is>
-          <t>Subzero Two Panel Ready Column Fridges &amp; Wolf Gas Range 48” Wide</t>
+          <t>Wolf Stainless Steel Gas Range 36” Wide/Subzero Fridge 48” Panel Ready</t>
         </is>
       </c>
       <c r="C89" s="13" t="inlineStr">
@@ -10241,11 +10237,11 @@
       </c>
       <c r="G89" s="13" t="inlineStr">
         <is>
-          <t>$9,800</t>
+          <t>$7,800</t>
         </is>
       </c>
       <c r="H89" s="15" t="n">
-        <v>9800</v>
+        <v>7800</v>
       </c>
       <c r="I89" s="13" t="inlineStr">
         <is>
@@ -10283,7 +10279,7 @@
       </c>
       <c r="B90" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel Gas Range 36” Wide/Subzero Fridge 48” Panel Ready</t>
+          <t>Subzero 2017 Model Fridge 48”/Wolf Gas Range 48” Wide</t>
         </is>
       </c>
       <c r="C90" s="13" t="inlineStr">
@@ -10306,11 +10302,11 @@
       </c>
       <c r="G90" s="13" t="inlineStr">
         <is>
-          <t>$7,800</t>
+          <t>$10,800</t>
         </is>
       </c>
       <c r="H90" s="15" t="n">
-        <v>7800</v>
+        <v>10800</v>
       </c>
       <c r="I90" s="13" t="inlineStr">
         <is>
@@ -10348,7 +10344,7 @@
       </c>
       <c r="B91" s="14" t="inlineStr">
         <is>
-          <t>Subzero 2017 Model Fridge 48”/Wolf Gas Range 48” Wide</t>
+          <t>Wolf Stainless Steel 36” Wide Gas Range/Kitchen Aid 42” Wide Fridge</t>
         </is>
       </c>
       <c r="C91" s="13" t="inlineStr">
@@ -10371,11 +10367,11 @@
       </c>
       <c r="G91" s="13" t="inlineStr">
         <is>
-          <t>$10,800</t>
+          <t>$9,800</t>
         </is>
       </c>
       <c r="H91" s="15" t="n">
-        <v>10800</v>
+        <v>9800</v>
       </c>
       <c r="I91" s="13" t="inlineStr">
         <is>
@@ -10413,7 +10409,7 @@
       </c>
       <c r="B92" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 36” Wide Gas Range/Kitchen Aid 42” Wide Fridge</t>
+          <t>Wolf Stainless Steel Gas Stove 36” Wide/Subzero 48” Fridge Panel Ready</t>
         </is>
       </c>
       <c r="C92" s="13" t="inlineStr">
@@ -10436,11 +10432,11 @@
       </c>
       <c r="G92" s="13" t="inlineStr">
         <is>
-          <t>$9,800</t>
+          <t>$8,800</t>
         </is>
       </c>
       <c r="H92" s="15" t="n">
-        <v>9800</v>
+        <v>8800</v>
       </c>
       <c r="I92" s="13" t="inlineStr">
         <is>
@@ -10478,7 +10474,7 @@
       </c>
       <c r="B93" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel Gas Stove 36” Wide/Subzero 48” Fridge Panel Ready</t>
+          <t>Wolf Stainless Steel 36” Wide Gas Range/Subzero 42” Built In Fridge</t>
         </is>
       </c>
       <c r="C93" s="13" t="inlineStr">
@@ -10543,7 +10539,7 @@
       </c>
       <c r="B94" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 36” Wide Gas Range/Subzero 42” Built In Fridge</t>
+          <t>Wolf Stainless 36” Wide Gas Range/Subzero 42” Wide Fridge Built In</t>
         </is>
       </c>
       <c r="C94" s="13" t="inlineStr">
@@ -10566,11 +10562,11 @@
       </c>
       <c r="G94" s="13" t="inlineStr">
         <is>
-          <t>$8,800</t>
+          <t>$7,800</t>
         </is>
       </c>
       <c r="H94" s="15" t="n">
-        <v>8800</v>
+        <v>7800</v>
       </c>
       <c r="I94" s="13" t="inlineStr">
         <is>
@@ -10608,7 +10604,7 @@
       </c>
       <c r="B95" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless 36” Wide Gas Range/Subzero 42” Wide Fridge Built In</t>
+          <t>Kitchen Aid New 42” Fridge/Wolf Stainless 36” Gas Range</t>
         </is>
       </c>
       <c r="C95" s="13" t="inlineStr">
@@ -10631,11 +10627,11 @@
       </c>
       <c r="G95" s="13" t="inlineStr">
         <is>
-          <t>$7,800</t>
+          <t>$9,800</t>
         </is>
       </c>
       <c r="H95" s="15" t="n">
-        <v>7800</v>
+        <v>9800</v>
       </c>
       <c r="I95" s="13" t="inlineStr">
         <is>
@@ -10673,7 +10669,7 @@
       </c>
       <c r="B96" s="14" t="inlineStr">
         <is>
-          <t>Kitchen Aid New 42” Fridge/Wolf Stainless 36” Gas Range</t>
+          <t>Wolf Stainless Steel 30” Gas Stove/Subzero 36” Built In Fridge</t>
         </is>
       </c>
       <c r="C96" s="13" t="inlineStr">
@@ -10696,11 +10692,11 @@
       </c>
       <c r="G96" s="13" t="inlineStr">
         <is>
-          <t>$9,800</t>
+          <t>$6,600</t>
         </is>
       </c>
       <c r="H96" s="15" t="n">
-        <v>9800</v>
+        <v>6600</v>
       </c>
       <c r="I96" s="13" t="inlineStr">
         <is>
@@ -10738,7 +10734,7 @@
       </c>
       <c r="B97" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 30” Gas Stove/Subzero 36” Built In Fridge</t>
+          <t>Subzero Panel Ready 48” Fridge/Wolf 36” Wide Gas Range</t>
         </is>
       </c>
       <c r="C97" s="13" t="inlineStr">
@@ -10761,11 +10757,11 @@
       </c>
       <c r="G97" s="13" t="inlineStr">
         <is>
-          <t>$6,600</t>
+          <t>$7,800</t>
         </is>
       </c>
       <c r="H97" s="15" t="n">
-        <v>6600</v>
+        <v>7800</v>
       </c>
       <c r="I97" s="13" t="inlineStr">
         <is>
@@ -10803,7 +10799,7 @@
       </c>
       <c r="B98" s="14" t="inlineStr">
         <is>
-          <t>Subzero Panel Ready 48” Fridge/Wolf 36” Wide Gas Range</t>
+          <t>Subzero Stainless Steel 36” Fridge/Wolf 30” Wide Gas Range Stainless</t>
         </is>
       </c>
       <c r="C98" s="13" t="inlineStr">
@@ -10826,11 +10822,11 @@
       </c>
       <c r="G98" s="13" t="inlineStr">
         <is>
-          <t>$7,800</t>
+          <t>$6,600</t>
         </is>
       </c>
       <c r="H98" s="15" t="n">
-        <v>7800</v>
+        <v>6600</v>
       </c>
       <c r="I98" s="13" t="inlineStr">
         <is>
@@ -10868,7 +10864,7 @@
       </c>
       <c r="B99" s="14" t="inlineStr">
         <is>
-          <t>Subzero Stainless Steel 36” Fridge/Wolf 30” Wide Gas Range Stainless</t>
+          <t>Wolf Stainless Steel 48” Wide Gas Range/Subzero 42” Wide Fridge</t>
         </is>
       </c>
       <c r="C99" s="13" t="inlineStr">
@@ -10891,11 +10887,11 @@
       </c>
       <c r="G99" s="13" t="inlineStr">
         <is>
-          <t>$6,600</t>
+          <t>$8,200</t>
         </is>
       </c>
       <c r="H99" s="15" t="n">
-        <v>6600</v>
+        <v>8200</v>
       </c>
       <c r="I99" s="13" t="inlineStr">
         <is>
@@ -10933,7 +10929,7 @@
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 48” Wide Gas Range/Subzero 42” Wide Fridge</t>
+          <t>Thermador Stainless 36” Wide 3-Door Fridge/Wolf 36” Gas Range</t>
         </is>
       </c>
       <c r="C100" s="13" t="inlineStr">
@@ -10956,11 +10952,11 @@
       </c>
       <c r="G100" s="13" t="inlineStr">
         <is>
-          <t>$8,200</t>
+          <t>$7,800</t>
         </is>
       </c>
       <c r="H100" s="15" t="n">
-        <v>8200</v>
+        <v>7800</v>
       </c>
       <c r="I100" s="13" t="inlineStr">
         <is>
@@ -10998,7 +10994,7 @@
       </c>
       <c r="B101" s="14" t="inlineStr">
         <is>
-          <t>Thermador Stainless 36” Wide 3-Door Fridge/Wolf 36” Gas Range</t>
+          <t>Wolf Stainless Steel 36” Inch Wide Gas Range 4-Burners w/Grill</t>
         </is>
       </c>
       <c r="C101" s="13" t="inlineStr">
@@ -11021,11 +11017,11 @@
       </c>
       <c r="G101" s="13" t="inlineStr">
         <is>
-          <t>$7,800</t>
+          <t>$3,500</t>
         </is>
       </c>
       <c r="H101" s="15" t="n">
-        <v>7800</v>
+        <v>3500</v>
       </c>
       <c r="I101" s="13" t="inlineStr">
         <is>
@@ -11063,7 +11059,7 @@
       </c>
       <c r="B102" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 36” Inch Wide Gas Range 4-Burners w/Grill</t>
+          <t>Wolf Stainless Steel 30” Inch Wide Gas Range</t>
         </is>
       </c>
       <c r="C102" s="13" t="inlineStr">
@@ -11086,11 +11082,11 @@
       </c>
       <c r="G102" s="13" t="inlineStr">
         <is>
-          <t>$3,500</t>
+          <t>$2,500</t>
         </is>
       </c>
       <c r="H102" s="15" t="n">
-        <v>3500</v>
+        <v>2500</v>
       </c>
       <c r="I102" s="13" t="inlineStr">
         <is>
@@ -11128,7 +11124,7 @@
       </c>
       <c r="B103" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 30” Inch Wide Gas Range</t>
+          <t>Wolf Stainless Steel 48” Inch Wide Gas Range 6-Burners w/Grill</t>
         </is>
       </c>
       <c r="C103" s="13" t="inlineStr">
@@ -11151,11 +11147,11 @@
       </c>
       <c r="G103" s="13" t="inlineStr">
         <is>
-          <t>$2,500</t>
+          <t>$4,500</t>
         </is>
       </c>
       <c r="H103" s="15" t="n">
-        <v>2500</v>
+        <v>4500</v>
       </c>
       <c r="I103" s="13" t="inlineStr">
         <is>
@@ -11193,7 +11189,7 @@
       </c>
       <c r="B104" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 48” Inch Wide Gas Range 6-Burners w/Grill</t>
+          <t>Kitchen Aid New Stainless 42” Fridge/Wolf 48” Gas Range</t>
         </is>
       </c>
       <c r="C104" s="13" t="inlineStr">
@@ -11216,11 +11212,11 @@
       </c>
       <c r="G104" s="13" t="inlineStr">
         <is>
-          <t>$4,500</t>
+          <t>$9,800</t>
         </is>
       </c>
       <c r="H104" s="15" t="n">
-        <v>4500</v>
+        <v>9800</v>
       </c>
       <c r="I104" s="13" t="inlineStr">
         <is>
@@ -11258,7 +11254,7 @@
       </c>
       <c r="B105" s="14" t="inlineStr">
         <is>
-          <t>Kitchen Aid New Stainless 42” Fridge/Wolf 48” Gas Range</t>
+          <t>Wolf Stainless Steel 36” Inch Wide Gas Range 6-Burners</t>
         </is>
       </c>
       <c r="C105" s="13" t="inlineStr">
@@ -11281,11 +11277,11 @@
       </c>
       <c r="G105" s="13" t="inlineStr">
         <is>
-          <t>$9,800</t>
+          <t>$3,500</t>
         </is>
       </c>
       <c r="H105" s="15" t="n">
-        <v>9800</v>
+        <v>3500</v>
       </c>
       <c r="I105" s="13" t="inlineStr">
         <is>
@@ -11323,7 +11319,7 @@
       </c>
       <c r="B106" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 36” Inch Wide Gas Range 6-Burners</t>
+          <t>Subzero Stainless 42” Wide Fridge/Wolf 36” Wide Gas Range</t>
         </is>
       </c>
       <c r="C106" s="13" t="inlineStr">
@@ -11346,11 +11342,11 @@
       </c>
       <c r="G106" s="13" t="inlineStr">
         <is>
-          <t>$3,500</t>
+          <t>$7,800</t>
         </is>
       </c>
       <c r="H106" s="15" t="n">
-        <v>3500</v>
+        <v>7800</v>
       </c>
       <c r="I106" s="13" t="inlineStr">
         <is>
@@ -11388,7 +11384,7 @@
       </c>
       <c r="B107" s="14" t="inlineStr">
         <is>
-          <t>Subzero Stainless 42” Wide Fridge/Wolf 36” Wide Gas Range</t>
+          <t>Wolf Stainless Steel 48” Wide Gas Range 6-Burner with Grill</t>
         </is>
       </c>
       <c r="C107" s="13" t="inlineStr">
@@ -11411,11 +11407,11 @@
       </c>
       <c r="G107" s="13" t="inlineStr">
         <is>
-          <t>$7,800</t>
+          <t>$4,800</t>
         </is>
       </c>
       <c r="H107" s="15" t="n">
-        <v>7800</v>
+        <v>4800</v>
       </c>
       <c r="I107" s="13" t="inlineStr">
         <is>
@@ -11453,7 +11449,7 @@
       </c>
       <c r="B108" s="14" t="inlineStr">
         <is>
-          <t>Wolf Stainless Steel 48” Wide Gas Range 6-Burner with Grill</t>
+          <t>Subzero Stainless Steel 42” Wide Built In Fridge/Wolf Gas Range 36”</t>
         </is>
       </c>
       <c r="C108" s="13" t="inlineStr">
@@ -11476,11 +11472,11 @@
       </c>
       <c r="G108" s="13" t="inlineStr">
         <is>
-          <t>$4,800</t>
+          <t>$7,800</t>
         </is>
       </c>
       <c r="H108" s="15" t="n">
-        <v>4800</v>
+        <v>7800</v>
       </c>
       <c r="I108" s="13" t="inlineStr">
         <is>
@@ -11518,7 +11514,7 @@
       </c>
       <c r="B109" s="14" t="inlineStr">
         <is>
-          <t>Subzero Stainless Steel 42” Wide Built In Fridge/Wolf Gas Range 36”</t>
+          <t>36 INCH WOLF RANGE</t>
         </is>
       </c>
       <c r="C109" s="13" t="inlineStr">
@@ -11528,7 +11524,7 @@
       </c>
       <c r="D109" s="13" t="inlineStr">
         <is>
-          <t>Clifton</t>
+          <t>Tennent</t>
         </is>
       </c>
       <c r="E109" s="13" t="inlineStr">
@@ -11537,19 +11533,19 @@
         </is>
       </c>
       <c r="F109" s="13" t="n">
-        <v>194</v>
+        <v>221</v>
       </c>
       <c r="G109" s="13" t="inlineStr">
         <is>
-          <t>$7,800</t>
+          <t>$3,500</t>
         </is>
       </c>
       <c r="H109" s="15" t="n">
-        <v>7800</v>
+        <v>3500</v>
       </c>
       <c r="I109" s="13" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-11</t>
         </is>
       </c>
       <c r="J109" s="13" t="inlineStr"/>
@@ -11583,7 +11579,7 @@
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>36 INCH WOLF RANGE</t>
+          <t>wolf 30" duel fuel range</t>
         </is>
       </c>
       <c r="C110" s="13" t="inlineStr">
@@ -11606,11 +11602,11 @@
       </c>
       <c r="G110" s="13" t="inlineStr">
         <is>
-          <t>$3,500</t>
+          <t>$4,500</t>
         </is>
       </c>
       <c r="H110" s="15" t="n">
-        <v>3500</v>
+        <v>4500</v>
       </c>
       <c r="I110" s="13" t="inlineStr">
         <is>
@@ -11648,7 +11644,7 @@
       </c>
       <c r="B111" s="14" t="inlineStr">
         <is>
-          <t>wolf 30" duel fuel range</t>
+          <t>48" WOLF RANGETOP</t>
         </is>
       </c>
       <c r="C111" s="13" t="inlineStr">
@@ -11671,11 +11667,11 @@
       </c>
       <c r="G111" s="13" t="inlineStr">
         <is>
-          <t>$4,500</t>
+          <t>$2,900</t>
         </is>
       </c>
       <c r="H111" s="15" t="n">
-        <v>4500</v>
+        <v>2900</v>
       </c>
       <c r="I111" s="13" t="inlineStr">
         <is>
@@ -11713,7 +11709,7 @@
       </c>
       <c r="B112" s="14" t="inlineStr">
         <is>
-          <t>48" WOLF RANGETOP</t>
+          <t>48” wolf range</t>
         </is>
       </c>
       <c r="C112" s="13" t="inlineStr">
@@ -11736,11 +11732,11 @@
       </c>
       <c r="G112" s="13" t="inlineStr">
         <is>
-          <t>$2,900</t>
+          <t>$5,200</t>
         </is>
       </c>
       <c r="H112" s="15" t="n">
-        <v>2900</v>
+        <v>5200</v>
       </c>
       <c r="I112" s="13" t="inlineStr">
         <is>
@@ -11778,7 +11774,7 @@
       </c>
       <c r="B113" s="14" t="inlineStr">
         <is>
-          <t>48” wolf range</t>
+          <t>48” wolf</t>
         </is>
       </c>
       <c r="C113" s="13" t="inlineStr">
@@ -11801,11 +11797,11 @@
       </c>
       <c r="G113" s="13" t="inlineStr">
         <is>
-          <t>$5,200</t>
+          <t>$5,300</t>
         </is>
       </c>
       <c r="H113" s="15" t="n">
-        <v>5200</v>
+        <v>5300</v>
       </c>
       <c r="I113" s="13" t="inlineStr">
         <is>
@@ -11843,7 +11839,7 @@
       </c>
       <c r="B114" s="14" t="inlineStr">
         <is>
-          <t>48” wolf</t>
+          <t>30” wolf duel fuel range</t>
         </is>
       </c>
       <c r="C114" s="13" t="inlineStr">
@@ -11866,11 +11862,11 @@
       </c>
       <c r="G114" s="13" t="inlineStr">
         <is>
-          <t>$5,300</t>
+          <t>$4,500</t>
         </is>
       </c>
       <c r="H114" s="15" t="n">
-        <v>5300</v>
+        <v>4500</v>
       </c>
       <c r="I114" s="13" t="inlineStr">
         <is>
@@ -11908,7 +11904,7 @@
       </c>
       <c r="B115" s="14" t="inlineStr">
         <is>
-          <t>30” wolf duel fuel range</t>
+          <t>Wolf SO36U/S L-Series 36" Electric Single Wall Oven framed Stainless S</t>
         </is>
       </c>
       <c r="C115" s="13" t="inlineStr">
@@ -11918,7 +11914,7 @@
       </c>
       <c r="D115" s="13" t="inlineStr">
         <is>
-          <t>Tennent</t>
+          <t>Brick</t>
         </is>
       </c>
       <c r="E115" s="13" t="inlineStr">
@@ -11927,19 +11923,19 @@
         </is>
       </c>
       <c r="F115" s="13" t="n">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="G115" s="13" t="inlineStr">
         <is>
-          <t>$4,500</t>
+          <t>$150</t>
         </is>
       </c>
       <c r="H115" s="15" t="n">
-        <v>4500</v>
+        <v>150</v>
       </c>
       <c r="I115" s="13" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-13</t>
         </is>
       </c>
       <c r="J115" s="13" t="inlineStr"/>
@@ -11953,7 +11949,11 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M115" s="13" t="inlineStr"/>
+      <c r="M115" s="20" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
       <c r="N115" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -11961,126 +11961,130 @@
       </c>
       <c r="O115" s="14" t="inlineStr">
         <is>
-          <t>Condition: used.</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" outlineLevel="1">
-      <c r="A116" s="13" t="inlineStr">
-        <is>
-          <t>NYC / Long Island / NJ</t>
-        </is>
-      </c>
-      <c r="B116" s="14" t="inlineStr">
-        <is>
-          <t>Wolf SO36U/S L-Series 36" Electric Single Wall Oven framed Stainless S</t>
-        </is>
-      </c>
-      <c r="C116" s="13" t="inlineStr">
-        <is>
-          <t>range/oven/rangetop</t>
-        </is>
-      </c>
-      <c r="D116" s="13" t="inlineStr">
-        <is>
-          <t>Brick</t>
-        </is>
-      </c>
-      <c r="E116" s="13" t="inlineStr">
-        <is>
-          <t>NJ</t>
-        </is>
-      </c>
-      <c r="F116" s="13" t="n">
-        <v>224</v>
-      </c>
-      <c r="G116" s="13" t="inlineStr">
-        <is>
-          <t>$150</t>
-        </is>
-      </c>
-      <c r="H116" s="15" t="n">
-        <v>150</v>
-      </c>
-      <c r="I116" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="J116" s="13" t="inlineStr"/>
-      <c r="K116" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L116" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M116" s="20" t="inlineStr">
+          <t>Condition: used. FLIP: SO36U/S $150 OBO; auction comp $350 w/ drawer; rough resale $600-1k</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="17" t="inlineStr">
+        <is>
+          <t>Subtotal — NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B116" s="17" t="inlineStr">
+        <is>
+          <t>65 item(s)</t>
+        </is>
+      </c>
+      <c r="C116" s="18" t="n"/>
+      <c r="D116" s="18" t="n"/>
+      <c r="E116" s="18" t="n"/>
+      <c r="F116" s="18" t="n"/>
+      <c r="G116" s="18" t="n"/>
+      <c r="H116" s="19" t="n">
+        <v>315351</v>
+      </c>
+      <c r="I116" s="18" t="n"/>
+      <c r="J116" s="18" t="n"/>
+      <c r="K116" s="18" t="n"/>
+      <c r="L116" s="18" t="n"/>
+      <c r="M116" s="18" t="n"/>
+      <c r="N116" s="18" t="n"/>
+      <c r="O116" s="18" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="11" t="inlineStr">
+        <is>
+          <t>▸ Eastern PA / Mid-Atlantic  (2)</t>
+        </is>
+      </c>
+      <c r="B117" s="12" t="n"/>
+      <c r="C117" s="12" t="n"/>
+      <c r="D117" s="12" t="n"/>
+      <c r="E117" s="12" t="n"/>
+      <c r="F117" s="12" t="n"/>
+      <c r="G117" s="12" t="n"/>
+      <c r="H117" s="12" t="n"/>
+      <c r="I117" s="12" t="n"/>
+      <c r="J117" s="12" t="n"/>
+      <c r="K117" s="12" t="n"/>
+      <c r="L117" s="12" t="n"/>
+      <c r="M117" s="12" t="n"/>
+      <c r="N117" s="12" t="n"/>
+      <c r="O117" s="12" t="n"/>
+    </row>
+    <row r="118" outlineLevel="1">
+      <c r="A118" s="13" t="inlineStr">
+        <is>
+          <t>Eastern PA / Mid-Atlantic</t>
+        </is>
+      </c>
+      <c r="B118" s="14" t="inlineStr">
+        <is>
+          <t>Wolf Professional stainless gas range, 4 burners, red knobs (NBM Liquidation as-is appliance auction, lot 327587466)</t>
+        </is>
+      </c>
+      <c r="C118" s="13" t="inlineStr">
+        <is>
+          <t>range</t>
+        </is>
+      </c>
+      <c r="D118" s="13" t="inlineStr">
+        <is>
+          <t>Wilkes-Barre</t>
+        </is>
+      </c>
+      <c r="E118" s="13" t="inlineStr">
+        <is>
+          <t>PA</t>
+        </is>
+      </c>
+      <c r="F118" s="13" t="n">
+        <v>268</v>
+      </c>
+      <c r="G118" s="13" t="inlineStr">
+        <is>
+          <t>$0 bid (min $10) + BP</t>
+        </is>
+      </c>
+      <c r="H118" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-22</t>
+        </is>
+      </c>
+      <c r="J118" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-27 07:11 PM ET</t>
+        </is>
+      </c>
+      <c r="K118" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (NBM Liquidation, Moosic PA)</t>
+        </is>
+      </c>
+      <c r="L118" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M118" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
       </c>
-      <c r="N116" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O116" s="14" t="inlineStr">
-        <is>
-          <t>Condition: used. FLIP: SO36U/S $150 OBO; auction comp $350 w/ drawer; rough resale $600-1k</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="17" t="inlineStr">
-        <is>
-          <t>Subtotal — NYC / Long Island / NJ</t>
-        </is>
-      </c>
-      <c r="B117" s="17" t="inlineStr">
-        <is>
-          <t>65 item(s)</t>
-        </is>
-      </c>
-      <c r="C117" s="18" t="n"/>
-      <c r="D117" s="18" t="n"/>
-      <c r="E117" s="18" t="n"/>
-      <c r="F117" s="18" t="n"/>
-      <c r="G117" s="18" t="n"/>
-      <c r="H117" s="19" t="n">
-        <v>315351</v>
-      </c>
-      <c r="I117" s="18" t="n"/>
-      <c r="J117" s="18" t="n"/>
-      <c r="K117" s="18" t="n"/>
-      <c r="L117" s="18" t="n"/>
-      <c r="M117" s="18" t="n"/>
-      <c r="N117" s="18" t="n"/>
-      <c r="O117" s="18" t="n"/>
-    </row>
-    <row r="118">
-      <c r="A118" s="11" t="inlineStr">
-        <is>
-          <t>▸ Eastern PA / Mid-Atlantic  (1)</t>
-        </is>
-      </c>
-      <c r="B118" s="12" t="n"/>
-      <c r="C118" s="12" t="n"/>
-      <c r="D118" s="12" t="n"/>
-      <c r="E118" s="12" t="n"/>
-      <c r="F118" s="12" t="n"/>
-      <c r="G118" s="12" t="n"/>
-      <c r="H118" s="12" t="n"/>
-      <c r="I118" s="12" t="n"/>
-      <c r="J118" s="12" t="n"/>
-      <c r="K118" s="12" t="n"/>
-      <c r="L118" s="12" t="n"/>
-      <c r="M118" s="12" t="n"/>
-      <c r="N118" s="12" t="n"/>
-      <c r="O118" s="12" t="n"/>
+      <c r="N118" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O118" s="14" t="inlineStr">
+        <is>
+          <t>As-is appliance liquidation auction; width/model not stated in listing, check photos. Closes Oct 27 6:11 PM EST. About 300 mi from 02339.</t>
+        </is>
+      </c>
     </row>
     <row r="119" outlineLevel="1">
       <c r="A119" s="13" t="inlineStr">
@@ -12155,7 +12159,7 @@
       </c>
       <c r="B120" s="17" t="inlineStr">
         <is>
-          <t>1 item(s)</t>
+          <t>2 item(s)</t>
         </is>
       </c>
       <c r="C120" s="18" t="n"/>
@@ -12538,9 +12542,9 @@
           <t>HiBid</t>
         </is>
       </c>
-      <c r="L129" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+      <c r="L129" s="21" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M129" s="20" t="inlineStr">
@@ -16241,7 +16245,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N46" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N47" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N48" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N49" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N51" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N52" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N53" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N54" r:id="rId40"/>
@@ -16306,7 +16310,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N113" r:id="rId99"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N114" r:id="rId100"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N115" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N116" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N118" r:id="rId102"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N119" r:id="rId103"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N122" r:id="rId104"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="N125" r:id="rId105"/>
@@ -18728,7 +18732,7 @@
     <row r="2">
       <c r="A2" s="11" t="inlineStr">
         <is>
-          <t>▸ Greater Boston / South Shore (&lt;50mi)  (5)</t>
+          <t>▸ Greater Boston / South Shore (&lt;50mi)  (6)</t>
         </is>
       </c>
       <c r="B2" s="12" t="n"/>
@@ -18880,17 +18884,17 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>Wholesale bedding lot – 525 pcs new Target overstock (comforters, duvets, quilts)</t>
+          <t>Retirement bulk tool lot – 10 tools, sold together</t>
         </is>
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>wholesale overstock lot</t>
+          <t>retirement</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
         <is>
-          <t>Natick</t>
+          <t>Waltham</t>
         </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
@@ -18899,17 +18903,17 @@
         </is>
       </c>
       <c r="F5" s="13" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G5" s="13" t="inlineStr">
         <is>
-          <t>$3,590 all 525 pcs (per-piece $4–$11)</t>
+          <t>$250 all</t>
         </is>
       </c>
       <c r="H5" s="15" t="n"/>
       <c r="I5" s="13" t="inlineStr">
         <is>
-          <t>2026-10-14</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J5" s="13" t="inlineStr"/>
@@ -18931,7 +18935,7 @@
       </c>
       <c r="O5" s="14" t="inlineStr">
         <is>
-          <t>Resale business selling bulk new bedding in original packaging: shams, duvet/sham sets, waffle comforter sets, bath runners, quilts, Casaluna pillows. Works out to about $6.84/pc; retail comps $20–$60. Local pickup Natick only, cash.</t>
+          <t>Small off-category FYI; seller says resell individually. Same $250 / 10-tool lot, reposted under new CL URLs repeatedly (latest 2026-10-21 5:36 PM).</t>
         </is>
       </c>
     </row>
@@ -18943,17 +18947,17 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>Cannabis facility contents incl. commercial kitchen / stainless</t>
+          <t>Wholesale bedding lot – 525 pcs new Target overstock (comforters, duvets, quilts)</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>facility contents</t>
+          <t>wholesale overstock lot</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
         <is>
-          <t>Milford</t>
+          <t>Natick</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -18962,23 +18966,23 @@
         </is>
       </c>
       <c r="F6" s="13" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G6" s="13" t="inlineStr">
         <is>
-          <t>Auction, 18% BP</t>
+          <t>$3,590 all 525 pcs (per-piece $4–$11)</t>
         </is>
       </c>
       <c r="H6" s="15" t="n"/>
-      <c r="I6" s="13" t="inlineStr"/>
-      <c r="J6" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-03 10:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="J6" s="13" t="inlineStr"/>
       <c r="K6" s="13" t="inlineStr">
         <is>
-          <t>Paul E. Saperstein (PESCO)</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L6" s="13" t="inlineStr">
@@ -18994,7 +18998,7 @@
       </c>
       <c r="O6" s="14" t="inlineStr">
         <is>
-          <t>Calendar page only (no event page yet). ~45 mi.</t>
+          <t>Resale business selling bulk new bedding in original packaging: shams, duvet/sham sets, waffle comforter sets, bath runners, quilts, Casaluna pillows. Works out to about $6.84/pc; retail comps $20–$60. Local pickup Natick only, cash.</t>
         </is>
       </c>
     </row>
@@ -19006,17 +19010,17 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>Donelan's Fresh Market turnkey grocery liquidation (Grafe): Hill Phoenix racks, walk-ins, display cases, rack ovens, Hobart saw/wrappers, checkouts, shelving</t>
+          <t>Cannabis facility contents incl. commercial kitchen / stainless</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>facility contents</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
-          <t>Littleton</t>
+          <t>Milford</t>
         </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
@@ -19025,156 +19029,156 @@
         </is>
       </c>
       <c r="F7" s="13" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="G7" s="13" t="inlineStr">
         <is>
-          <t>Online auction (Grafe terms)</t>
+          <t>Auction, 18% BP</t>
         </is>
       </c>
       <c r="H7" s="15" t="n"/>
       <c r="I7" s="13" t="inlineStr"/>
       <c r="J7" s="13" t="inlineStr">
         <is>
+          <t>2026-11-03 10:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K7" s="13" t="inlineStr">
+        <is>
+          <t>Paul E. Saperstein (PESCO)</t>
+        </is>
+      </c>
+      <c r="L7" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M7" s="13" t="inlineStr"/>
+      <c r="N7" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O7" s="14" t="inlineStr">
+        <is>
+          <t>Calendar page only (no event page yet). ~45 mi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" outlineLevel="1">
+      <c r="A8" s="13" t="inlineStr">
+        <is>
+          <t>Greater Boston / South Shore (&lt;50mi)</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Donelan's Fresh Market turnkey grocery liquidation (Grafe): Hill Phoenix racks, walk-ins, display cases, rack ovens, Hobart saw/wrappers, checkouts, shelving</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>store closing</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
+        <is>
+          <t>Littleton</t>
+        </is>
+      </c>
+      <c r="E8" s="13" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="F8" s="13" t="n">
+        <v>46</v>
+      </c>
+      <c r="G8" s="13" t="inlineStr">
+        <is>
+          <t>Online auction (Grafe terms)</t>
+        </is>
+      </c>
+      <c r="H8" s="15" t="n"/>
+      <c r="I8" s="13" t="inlineStr"/>
+      <c r="J8" s="13" t="inlineStr">
+        <is>
           <t>2026-11-05 10:00 AM ET</t>
         </is>
       </c>
-      <c r="K7" s="13" t="inlineStr">
+      <c r="K8" s="13" t="inlineStr">
         <is>
           <t>Grafe Auction</t>
         </is>
       </c>
-      <c r="L7" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M7" s="20" t="inlineStr">
+      <c r="L8" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M8" s="20" t="inlineStr">
         <is>
           <t>FLIP</t>
         </is>
       </c>
-      <c r="N7" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O7" s="14" t="inlineStr">
+      <c r="N8" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O8" s="14" t="inlineStr">
         <is>
           <t>Begins closing Nov 5 10 AM EST; preview Nov 4 3-6 PM. Close to home; commercial refrigeration and bakery equipment.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="17" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Greater Boston / South Shore (&lt;50mi)</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>5 item(s)</t>
-        </is>
-      </c>
-      <c r="C8" s="18" t="n"/>
-      <c r="D8" s="18" t="n"/>
-      <c r="E8" s="18" t="n"/>
-      <c r="F8" s="18" t="n"/>
-      <c r="G8" s="18" t="n"/>
-      <c r="H8" s="19" t="n">
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>6 item(s)</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="18" t="n"/>
+      <c r="G9" s="18" t="n"/>
+      <c r="H9" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="18" t="n"/>
-      <c r="J8" s="18" t="n"/>
-      <c r="K8" s="18" t="n"/>
-      <c r="L8" s="18" t="n"/>
-      <c r="M8" s="18" t="n"/>
-      <c r="N8" s="18" t="n"/>
-      <c r="O8" s="18" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
+      <c r="I9" s="18" t="n"/>
+      <c r="J9" s="18" t="n"/>
+      <c r="K9" s="18" t="n"/>
+      <c r="L9" s="18" t="n"/>
+      <c r="M9" s="18" t="n"/>
+      <c r="N9" s="18" t="n"/>
+      <c r="O9" s="18" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>▸ North Shore / Merrimack Valley / S. NH  (2)</t>
         </is>
       </c>
-      <c r="B9" s="12" t="n"/>
-      <c r="C9" s="12" t="n"/>
-      <c r="D9" s="12" t="n"/>
-      <c r="E9" s="12" t="n"/>
-      <c r="F9" s="12" t="n"/>
-      <c r="G9" s="12" t="n"/>
-      <c r="H9" s="12" t="n"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="12" t="n"/>
-      <c r="K9" s="12" t="n"/>
-      <c r="L9" s="12" t="n"/>
-      <c r="M9" s="12" t="n"/>
-      <c r="N9" s="12" t="n"/>
-      <c r="O9" s="12" t="n"/>
-    </row>
-    <row r="10" outlineLevel="1">
-      <c r="A10" s="13" t="inlineStr">
-        <is>
-          <t>North Shore / Merrimack Valley / S. NH</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>Commercial mechanical/plumbing/HVAC contractor inventory – multiple pallets of boxed stock, water heater, venting, diffusers</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>inventory</t>
-        </is>
-      </c>
-      <c r="D10" s="13" t="inlineStr">
-        <is>
-          <t>Merrimack</t>
-        </is>
-      </c>
-      <c r="E10" s="13" t="inlineStr">
-        <is>
-          <t>NH</t>
-        </is>
-      </c>
-      <c r="F10" s="13" t="n">
-        <v>62</v>
-      </c>
-      <c r="G10" s="13" t="inlineStr">
-        <is>
-          <t>$1 placeholder – make offer on everything</t>
-        </is>
-      </c>
-      <c r="H10" s="15" t="n"/>
-      <c r="I10" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="J10" s="13" t="inlineStr"/>
-      <c r="K10" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L10" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M10" s="13" t="inlineStr"/>
-      <c r="N10" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O10" s="14" t="inlineStr">
-        <is>
-          <t>Bulk buyers preferred.</t>
-        </is>
-      </c>
+      <c r="B10" s="12" t="n"/>
+      <c r="C10" s="12" t="n"/>
+      <c r="D10" s="12" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="12" t="n"/>
+      <c r="G10" s="12" t="n"/>
+      <c r="H10" s="12" t="n"/>
+      <c r="I10" s="12" t="n"/>
+      <c r="J10" s="12" t="n"/>
+      <c r="K10" s="12" t="n"/>
+      <c r="L10" s="12" t="n"/>
+      <c r="M10" s="12" t="n"/>
+      <c r="N10" s="12" t="n"/>
+      <c r="O10" s="12" t="n"/>
     </row>
     <row r="11" outlineLevel="1">
       <c r="A11" s="13" t="inlineStr">
@@ -19184,17 +19188,17 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>Plumbing &amp; heating overstock/returns online auction – 183 lots (fixtures, furnaces, heaters, A/C)</t>
+          <t>Commercial mechanical/plumbing/HVAC contractor inventory – multiple pallets of boxed stock, water heater, venting, diffusers</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="D11" s="13" t="inlineStr">
         <is>
-          <t>Concord</t>
+          <t>Merrimack</t>
         </is>
       </c>
       <c r="E11" s="13" t="inlineStr">
@@ -19203,27 +19207,23 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>84</v>
+        <v>62</v>
       </c>
       <c r="G11" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>$1 placeholder – make offer on everything</t>
         </is>
       </c>
       <c r="H11" s="15" t="n"/>
       <c r="I11" s="13" t="inlineStr">
         <is>
-          <t>2026-10-13</t>
-        </is>
-      </c>
-      <c r="J11" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-27 07:00 PM ET</t>
-        </is>
-      </c>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="J11" s="13" t="inlineStr"/>
       <c r="K11" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Atlantic Auction Co.)</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L11" s="13" t="inlineStr">
@@ -19239,120 +19239,124 @@
       </c>
       <c r="O11" s="14" t="inlineStr">
         <is>
+          <t>Bulk buyers preferred.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" outlineLevel="1">
+      <c r="A12" s="13" t="inlineStr">
+        <is>
+          <t>North Shore / Merrimack Valley / S. NH</t>
+        </is>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>Plumbing &amp; heating overstock/returns online auction – 183 lots (fixtures, furnaces, heaters, A/C)</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>auction</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
+        <is>
+          <t>Concord</t>
+        </is>
+      </c>
+      <c r="E12" s="13" t="inlineStr">
+        <is>
+          <t>NH</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="n">
+        <v>84</v>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>Online auction</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="n"/>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="J12" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-27 07:00 PM ET</t>
+        </is>
+      </c>
+      <c r="K12" s="13" t="inlineStr">
+        <is>
+          <t>HiBid (Atlantic Auction Co.)</t>
+        </is>
+      </c>
+      <c r="L12" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M12" s="13" t="inlineStr"/>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O12" s="14" t="inlineStr">
+        <is>
           <t>Overstock sale, not a closing. Pickup Oct 29–30.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="17" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Subtotal — North Shore / Merrimack Valley / S. NH</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>2 item(s)</t>
         </is>
       </c>
-      <c r="C12" s="18" t="n"/>
-      <c r="D12" s="18" t="n"/>
-      <c r="E12" s="18" t="n"/>
-      <c r="F12" s="18" t="n"/>
-      <c r="G12" s="18" t="n"/>
-      <c r="H12" s="19" t="n">
+      <c r="C13" s="18" t="n"/>
+      <c r="D13" s="18" t="n"/>
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="18" t="n"/>
+      <c r="G13" s="18" t="n"/>
+      <c r="H13" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="18" t="n"/>
-      <c r="J12" s="18" t="n"/>
-      <c r="K12" s="18" t="n"/>
-      <c r="L12" s="18" t="n"/>
-      <c r="M12" s="18" t="n"/>
-      <c r="N12" s="18" t="n"/>
-      <c r="O12" s="18" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="I13" s="18" t="n"/>
+      <c r="J13" s="18" t="n"/>
+      <c r="K13" s="18" t="n"/>
+      <c r="L13" s="18" t="n"/>
+      <c r="M13" s="18" t="n"/>
+      <c r="N13" s="18" t="n"/>
+      <c r="O13" s="18" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>▸ Central / Western MA  (3)</t>
         </is>
       </c>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
-      <c r="H13" s="12" t="n"/>
-      <c r="I13" s="12" t="n"/>
-      <c r="J13" s="12" t="n"/>
-      <c r="K13" s="12" t="n"/>
-      <c r="L13" s="12" t="n"/>
-      <c r="M13" s="12" t="n"/>
-      <c r="N13" s="12" t="n"/>
-      <c r="O13" s="12" t="n"/>
-    </row>
-    <row r="14" outlineLevel="1">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>Central / Western MA</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="inlineStr">
-        <is>
-          <t>Gift/souvenir store closing (retirement) – all new stock</t>
-        </is>
-      </c>
-      <c r="C14" s="13" t="inlineStr">
-        <is>
-          <t>store closing</t>
-        </is>
-      </c>
-      <c r="D14" s="13" t="inlineStr">
-        <is>
-          <t>Thorndike</t>
-        </is>
-      </c>
-      <c r="E14" s="13" t="inlineStr">
-        <is>
-          <t>MA</t>
-        </is>
-      </c>
-      <c r="F14" s="13" t="n">
-        <v>77</v>
-      </c>
-      <c r="G14" s="13" t="inlineStr">
-        <is>
-          <t>By appointment</t>
-        </is>
-      </c>
-      <c r="H14" s="15" t="n"/>
-      <c r="I14" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="J14" s="13" t="inlineStr"/>
-      <c r="K14" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L14" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M14" s="13" t="inlineStr"/>
-      <c r="N14" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O14" s="14" t="inlineStr">
-        <is>
-          <t>Updated Oct 8. Off-category FYI.</t>
-        </is>
-      </c>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="12" t="n"/>
+      <c r="G14" s="12" t="n"/>
+      <c r="H14" s="12" t="n"/>
+      <c r="I14" s="12" t="n"/>
+      <c r="J14" s="12" t="n"/>
+      <c r="K14" s="12" t="n"/>
+      <c r="L14" s="12" t="n"/>
+      <c r="M14" s="12" t="n"/>
+      <c r="N14" s="12" t="n"/>
+      <c r="O14" s="12" t="n"/>
     </row>
     <row r="15" outlineLevel="1">
       <c r="A15" s="13" t="inlineStr">
@@ -19362,17 +19366,17 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>UNECO Manufacturing – owners retiring, machine-shop metrology &amp; tooling</t>
+          <t>Gift/souvenir store closing (retirement) – all new stock</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>retirement</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D15" s="13" t="inlineStr">
         <is>
-          <t>Chicopee</t>
+          <t>Thorndike</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
@@ -19381,23 +19385,23 @@
         </is>
       </c>
       <c r="F15" s="13" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="G15" s="13" t="inlineStr">
         <is>
-          <t>Online auction, 18% BP</t>
+          <t>By appointment</t>
         </is>
       </c>
       <c r="H15" s="15" t="n"/>
-      <c r="I15" s="13" t="inlineStr"/>
-      <c r="J15" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-04 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I15" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="J15" s="13" t="inlineStr"/>
       <c r="K15" s="13" t="inlineStr">
         <is>
-          <t>HiBid (DeCosmo Industrial)</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L15" s="13" t="inlineStr">
@@ -19413,7 +19417,7 @@
       </c>
       <c r="O15" s="14" t="inlineStr">
         <is>
-          <t>Niche tooling only. Bidding opens Oct 19.</t>
+          <t>Updated Oct 8. Off-category FYI.</t>
         </is>
       </c>
     </row>
@@ -19425,17 +19429,17 @@
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>Restaurant closing, everything must go – kitchen equipment, stainless, smallwares</t>
+          <t>UNECO Manufacturing – owners retiring, machine-shop metrology &amp; tooling</t>
         </is>
       </c>
       <c r="C16" s="13" t="inlineStr">
         <is>
-          <t>restaurant closing</t>
+          <t>retirement</t>
         </is>
       </c>
       <c r="D16" s="13" t="inlineStr">
         <is>
-          <t>Westfield</t>
+          <t>Chicopee</t>
         </is>
       </c>
       <c r="E16" s="13" t="inlineStr">
@@ -19444,23 +19448,23 @@
         </is>
       </c>
       <c r="F16" s="13" t="n">
-        <v>99</v>
+        <v>92</v>
       </c>
       <c r="G16" s="13" t="inlineStr">
         <is>
-          <t>Make offer</t>
+          <t>Online auction, 18% BP</t>
         </is>
       </c>
       <c r="H16" s="15" t="n"/>
-      <c r="I16" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="J16" s="13" t="inlineStr"/>
+      <c r="I16" s="13" t="inlineStr"/>
+      <c r="J16" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-04 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K16" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>HiBid (DeCosmo Industrial)</t>
         </is>
       </c>
       <c r="L16" s="13" t="inlineStr">
@@ -19476,231 +19480,231 @@
       </c>
       <c r="O16" s="14" t="inlineStr">
         <is>
+          <t>Niche tooling only. Bidding opens Oct 19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" outlineLevel="1">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Central / Western MA</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Restaurant closing, everything must go – kitchen equipment, stainless, smallwares</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>restaurant closing</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Westfield</t>
+        </is>
+      </c>
+      <c r="E17" s="13" t="inlineStr">
+        <is>
+          <t>MA</t>
+        </is>
+      </c>
+      <c r="F17" s="13" t="n">
+        <v>99</v>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>Make offer</t>
+        </is>
+      </c>
+      <c r="H17" s="15" t="n"/>
+      <c r="I17" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="J17" s="13" t="inlineStr"/>
+      <c r="K17" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L17" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M17" s="13" t="inlineStr"/>
+      <c r="N17" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O17" s="14" t="inlineStr">
+        <is>
           <t>Related separate post "Complete Restaurant Equipment Package" $3,500 OBO (maybe same restaurant): https://www.craigslist.org/view/d/westfield-complete-restaurant-equipment/9Y5KCdhhgSqEBYbD3wKqVd</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="17" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Central / Western MA</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>3 item(s)</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n"/>
-      <c r="D17" s="18" t="n"/>
-      <c r="E17" s="18" t="n"/>
-      <c r="F17" s="18" t="n"/>
-      <c r="G17" s="18" t="n"/>
-      <c r="H17" s="19" t="n">
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
+      <c r="F18" s="18" t="n"/>
+      <c r="G18" s="18" t="n"/>
+      <c r="H18" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I17" s="18" t="n"/>
-      <c r="J17" s="18" t="n"/>
-      <c r="K17" s="18" t="n"/>
-      <c r="L17" s="18" t="n"/>
-      <c r="M17" s="18" t="n"/>
-      <c r="N17" s="18" t="n"/>
-      <c r="O17" s="18" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="I18" s="18" t="n"/>
+      <c r="J18" s="18" t="n"/>
+      <c r="K18" s="18" t="n"/>
+      <c r="L18" s="18" t="n"/>
+      <c r="M18" s="18" t="n"/>
+      <c r="N18" s="18" t="n"/>
+      <c r="O18" s="18" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>▸ Rhode Island  (1)</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
-      <c r="H18" s="12" t="n"/>
-      <c r="I18" s="12" t="n"/>
-      <c r="J18" s="12" t="n"/>
-      <c r="K18" s="12" t="n"/>
-      <c r="L18" s="12" t="n"/>
-      <c r="M18" s="12" t="n"/>
-      <c r="N18" s="12" t="n"/>
-      <c r="O18" s="12" t="n"/>
-    </row>
-    <row r="19" outlineLevel="1">
-      <c r="A19" s="13" t="inlineStr">
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="12" t="n"/>
+      <c r="G19" s="12" t="n"/>
+      <c r="H19" s="12" t="n"/>
+      <c r="I19" s="12" t="n"/>
+      <c r="J19" s="12" t="n"/>
+      <c r="K19" s="12" t="n"/>
+      <c r="L19" s="12" t="n"/>
+      <c r="M19" s="12" t="n"/>
+      <c r="N19" s="12" t="n"/>
+      <c r="O19" s="12" t="n"/>
+    </row>
+    <row r="20" outlineLevel="1">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Rhode Island</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>Steve's Bounce House business auction: 3 box trucks, trailer, container, 70+ bounce houses, tents, tables/chairs, pallet shelving, concession/food prep equipment</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>business auction</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>Coventry</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>RI</t>
         </is>
       </c>
-      <c r="F19" s="13" t="n">
+      <c r="F20" s="13" t="n">
         <v>53</v>
       </c>
-      <c r="G19" s="13" t="inlineStr">
+      <c r="G20" s="13" t="inlineStr">
         <is>
           <t>Online-only auction (BidSpotter)</t>
         </is>
       </c>
-      <c r="H19" s="15" t="n"/>
-      <c r="I19" s="13" t="inlineStr"/>
-      <c r="J19" s="13" t="inlineStr">
+      <c r="H20" s="15" t="n"/>
+      <c r="I20" s="13" t="inlineStr"/>
+      <c r="J20" s="13" t="inlineStr">
         <is>
           <t>2026-11-10 11:00 AM ET</t>
         </is>
       </c>
-      <c r="K19" s="13" t="inlineStr">
+      <c r="K20" s="13" t="inlineStr">
         <is>
           <t>Paul E. Saperstein (PESCO)</t>
         </is>
       </c>
-      <c r="L19" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M19" s="13" t="inlineStr"/>
-      <c r="N19" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O19" s="14" t="inlineStr">
+      <c r="L20" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M20" s="13" t="inlineStr"/>
+      <c r="N20" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O20" s="14" t="inlineStr">
         <is>
           <t>Nov 10 11 AM online only; 1372 Main St.</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="17" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Rhode Island</t>
         </is>
       </c>
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B21" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C20" s="18" t="n"/>
-      <c r="D20" s="18" t="n"/>
-      <c r="E20" s="18" t="n"/>
-      <c r="F20" s="18" t="n"/>
-      <c r="G20" s="18" t="n"/>
-      <c r="H20" s="19" t="n">
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="18" t="n"/>
+      <c r="H21" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I20" s="18" t="n"/>
-      <c r="J20" s="18" t="n"/>
-      <c r="K20" s="18" t="n"/>
-      <c r="L20" s="18" t="n"/>
-      <c r="M20" s="18" t="n"/>
-      <c r="N20" s="18" t="n"/>
-      <c r="O20" s="18" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>▸ Maine / VT / Northern NH  (4)</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="12" t="n"/>
-      <c r="H21" s="12" t="n"/>
-      <c r="I21" s="12" t="n"/>
-      <c r="J21" s="12" t="n"/>
-      <c r="K21" s="12" t="n"/>
-      <c r="L21" s="12" t="n"/>
-      <c r="M21" s="12" t="n"/>
-      <c r="N21" s="12" t="n"/>
-      <c r="O21" s="12" t="n"/>
-    </row>
-    <row r="22" outlineLevel="1">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>Maine / VT / Northern NH</t>
-        </is>
-      </c>
-      <c r="B22" s="14" t="inlineStr">
-        <is>
-          <t>Contractor appliance lot – 3 refrigerators, Bosch wall oven, gas range, washer/dryer set</t>
-        </is>
-      </c>
-      <c r="C22" s="13" t="inlineStr">
-        <is>
-          <t>contractor lot</t>
-        </is>
-      </c>
-      <c r="D22" s="13" t="inlineStr">
-        <is>
-          <t>Scarborough</t>
-        </is>
-      </c>
-      <c r="E22" s="13" t="inlineStr">
-        <is>
-          <t>ME</t>
-        </is>
-      </c>
-      <c r="F22" s="13" t="n">
-        <v>104</v>
-      </c>
-      <c r="G22" s="13" t="inlineStr">
-        <is>
-          <t>$200 OBO each, less as a bundle</t>
-        </is>
-      </c>
-      <c r="H22" s="15" t="n"/>
-      <c r="I22" s="13" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="J22" s="13" t="inlineStr"/>
-      <c r="K22" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L22" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M22" s="13" t="inlineStr"/>
-      <c r="N22" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O22" s="14" t="inlineStr">
-        <is>
-          <t>Working units pulled from jobs. Complete appliances, not parts.</t>
-        </is>
-      </c>
+      <c r="I21" s="18" t="n"/>
+      <c r="J21" s="18" t="n"/>
+      <c r="K21" s="18" t="n"/>
+      <c r="L21" s="18" t="n"/>
+      <c r="M21" s="18" t="n"/>
+      <c r="N21" s="18" t="n"/>
+      <c r="O21" s="18" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>▸ Maine / VT / Northern NH  (5)</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="12" t="n"/>
+      <c r="G22" s="12" t="n"/>
+      <c r="H22" s="12" t="n"/>
+      <c r="I22" s="12" t="n"/>
+      <c r="J22" s="12" t="n"/>
+      <c r="K22" s="12" t="n"/>
+      <c r="L22" s="12" t="n"/>
+      <c r="M22" s="12" t="n"/>
+      <c r="N22" s="12" t="n"/>
+      <c r="O22" s="12" t="n"/>
     </row>
     <row r="23" outlineLevel="1">
       <c r="A23" s="13" t="inlineStr">
@@ -19710,17 +19714,17 @@
       </c>
       <c r="B23" s="14" t="inlineStr">
         <is>
-          <t>Event-rental business closing – 300+ chairs, 40+ rounds, 1,300+ china, linens (all at once)</t>
+          <t>Contractor appliance lot – 3 refrigerators, Bosch wall oven, gas range, washer/dryer set</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
         <is>
-          <t>business closing</t>
+          <t>contractor lot</t>
         </is>
       </c>
       <c r="D23" s="13" t="inlineStr">
         <is>
-          <t>Woolwich</t>
+          <t>Scarborough</t>
         </is>
       </c>
       <c r="E23" s="13" t="inlineStr">
@@ -19729,17 +19733,17 @@
         </is>
       </c>
       <c r="F23" s="13" t="n">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="G23" s="13" t="inlineStr">
         <is>
-          <t>No price listed</t>
+          <t>$200 OBO each, less as a bundle</t>
         </is>
       </c>
       <c r="H23" s="15" t="n"/>
       <c r="I23" s="13" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="J23" s="13" t="inlineStr"/>
@@ -19761,7 +19765,7 @@
       </c>
       <c r="O23" s="14" t="inlineStr">
         <is>
-          <t>Updated Oct 7. Replacement cost &gt;$72K per post.</t>
+          <t>Working units pulled from jobs. Complete appliances, not parts.</t>
         </is>
       </c>
     </row>
@@ -19773,42 +19777,42 @@
       </c>
       <c r="B24" s="14" t="inlineStr">
         <is>
-          <t>Pellet/wood stoves, heating stock, tools &amp; heavy equipment – "business liquidation", 380 lots</t>
+          <t>Restaurant liquidation sale: 5 chafers $200, soup warmers, prep tables, wire shelving, smallwares, 3 Toast POS sets $1,250</t>
         </is>
       </c>
       <c r="C24" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>restaurant closing</t>
         </is>
       </c>
       <c r="D24" s="13" t="inlineStr">
         <is>
-          <t>Lunenburg</t>
+          <t>Plymouth</t>
         </is>
       </c>
       <c r="E24" s="13" t="inlineStr">
         <is>
-          <t>VT</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="F24" s="13" t="n">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="G24" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>$4 to $475 per item, offers considered</t>
         </is>
       </c>
       <c r="H24" s="15" t="n"/>
-      <c r="I24" s="13" t="inlineStr"/>
-      <c r="J24" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-04 10:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="J24" s="13" t="inlineStr"/>
       <c r="K24" s="13" t="inlineStr">
         <is>
-          <t>Thomas Hirchak Co.</t>
+          <t>Craigslist (by owner)</t>
         </is>
       </c>
       <c r="L24" s="13" t="inlineStr">
@@ -19824,7 +19828,7 @@
       </c>
       <c r="O24" s="14" t="inlineStr">
         <is>
-          <t>Closes Wed Nov 4 10 AM, preview Oct 28, removal Nov 9, no shipping.</t>
+          <t>Small restaurant contents, priced per item, 'much more available'. Toast POS kits resell on eBay.</t>
         </is>
       </c>
     </row>
@@ -19836,42 +19840,42 @@
       </c>
       <c r="B25" s="14" t="inlineStr">
         <is>
-          <t>Bread Loaf Corp wind-down – contractor equipment, staging, telehandler</t>
+          <t>Event-rental business closing – 300+ chairs, 40+ rounds, 1,300+ china, linens (all at once)</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>contractor liquidation</t>
+          <t>business closing</t>
         </is>
       </c>
       <c r="D25" s="13" t="inlineStr">
         <is>
-          <t>Middlebury</t>
+          <t>Woolwich</t>
         </is>
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>VT</t>
+          <t>ME</t>
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>177</v>
+        <v>135</v>
       </c>
       <c r="G25" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>No price listed</t>
         </is>
       </c>
       <c r="H25" s="15" t="n"/>
-      <c r="I25" s="13" t="inlineStr"/>
-      <c r="J25" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-28 09:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I25" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="J25" s="13" t="inlineStr"/>
       <c r="K25" s="13" t="inlineStr">
         <is>
-          <t>THC Auction</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L25" s="13" t="inlineStr">
@@ -19887,183 +19891,183 @@
       </c>
       <c r="O25" s="14" t="inlineStr">
         <is>
+          <t>Updated Oct 7. Replacement cost &gt;$72K per post.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" outlineLevel="1">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>Maine / VT / Northern NH</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="inlineStr">
+        <is>
+          <t>Pellet/wood stoves, heating stock, tools &amp; heavy equipment – "business liquidation", 380 lots</t>
+        </is>
+      </c>
+      <c r="C26" s="13" t="inlineStr">
+        <is>
+          <t>auction</t>
+        </is>
+      </c>
+      <c r="D26" s="13" t="inlineStr">
+        <is>
+          <t>Lunenburg</t>
+        </is>
+      </c>
+      <c r="E26" s="13" t="inlineStr">
+        <is>
+          <t>VT</t>
+        </is>
+      </c>
+      <c r="F26" s="13" t="n">
+        <v>168</v>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>Online auction</t>
+        </is>
+      </c>
+      <c r="H26" s="15" t="n"/>
+      <c r="I26" s="13" t="inlineStr"/>
+      <c r="J26" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-04 10:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K26" s="13" t="inlineStr">
+        <is>
+          <t>Thomas Hirchak Co.</t>
+        </is>
+      </c>
+      <c r="L26" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M26" s="13" t="inlineStr"/>
+      <c r="N26" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O26" s="14" t="inlineStr">
+        <is>
+          <t>Closes Wed Nov 4 10 AM, preview Oct 28, removal Nov 9, no shipping.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" outlineLevel="1">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Maine / VT / Northern NH</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="inlineStr">
+        <is>
+          <t>Bread Loaf Corp wind-down – contractor equipment, staging, telehandler</t>
+        </is>
+      </c>
+      <c r="C27" s="13" t="inlineStr">
+        <is>
+          <t>contractor liquidation</t>
+        </is>
+      </c>
+      <c r="D27" s="13" t="inlineStr">
+        <is>
+          <t>Middlebury</t>
+        </is>
+      </c>
+      <c r="E27" s="13" t="inlineStr">
+        <is>
+          <t>VT</t>
+        </is>
+      </c>
+      <c r="F27" s="13" t="n">
+        <v>177</v>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>Online auction</t>
+        </is>
+      </c>
+      <c r="H27" s="15" t="n"/>
+      <c r="I27" s="13" t="inlineStr"/>
+      <c r="J27" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-28 09:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K27" s="13" t="inlineStr">
+        <is>
+          <t>THC Auction</t>
+        </is>
+      </c>
+      <c r="L27" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M27" s="13" t="inlineStr"/>
+      <c r="N27" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O27" s="14" t="inlineStr">
+        <is>
           <t>Company wind-down.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="17" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Maine / VT / Northern NH</t>
         </is>
       </c>
-      <c r="B26" s="17" t="inlineStr">
-        <is>
-          <t>4 item(s)</t>
-        </is>
-      </c>
-      <c r="C26" s="18" t="n"/>
-      <c r="D26" s="18" t="n"/>
-      <c r="E26" s="18" t="n"/>
-      <c r="F26" s="18" t="n"/>
-      <c r="G26" s="18" t="n"/>
-      <c r="H26" s="19" t="n">
+      <c r="B28" s="17" t="inlineStr">
+        <is>
+          <t>5 item(s)</t>
+        </is>
+      </c>
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="18" t="n"/>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="18" t="n"/>
+      <c r="G28" s="18" t="n"/>
+      <c r="H28" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I26" s="18" t="n"/>
-      <c r="J26" s="18" t="n"/>
-      <c r="K26" s="18" t="n"/>
-      <c r="L26" s="18" t="n"/>
-      <c r="M26" s="18" t="n"/>
-      <c r="N26" s="18" t="n"/>
-      <c r="O26" s="18" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="11" t="inlineStr">
-        <is>
-          <t>▸ CT / Hudson Valley  (9)</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="12" t="n"/>
-      <c r="G27" s="12" t="n"/>
-      <c r="H27" s="12" t="n"/>
-      <c r="I27" s="12" t="n"/>
-      <c r="J27" s="12" t="n"/>
-      <c r="K27" s="12" t="n"/>
-      <c r="L27" s="12" t="n"/>
-      <c r="M27" s="12" t="n"/>
-      <c r="N27" s="12" t="n"/>
-      <c r="O27" s="12" t="n"/>
-    </row>
-    <row r="28" outlineLevel="1">
-      <c r="A28" s="13" t="inlineStr">
-        <is>
-          <t>CT / Hudson Valley</t>
-        </is>
-      </c>
-      <c r="B28" s="14" t="inlineStr">
-        <is>
-          <t>Bank-ordered electrical contractor sale – Greenlee/Hilti/Milwaukee tools, GE/Siemens breakers</t>
-        </is>
-      </c>
-      <c r="C28" s="13" t="inlineStr">
-        <is>
-          <t>contractor liquidation</t>
-        </is>
-      </c>
-      <c r="D28" s="13" t="inlineStr">
-        <is>
-          <t>Clinton</t>
-        </is>
-      </c>
-      <c r="E28" s="13" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="F28" s="13" t="n">
-        <v>106</v>
-      </c>
-      <c r="G28" s="13" t="inlineStr">
-        <is>
-          <t>Online auction</t>
-        </is>
-      </c>
-      <c r="H28" s="15" t="n"/>
-      <c r="I28" s="13" t="inlineStr"/>
-      <c r="J28" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-29 05:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K28" s="13" t="inlineStr">
-        <is>
-          <t>Hamilton Group / EstateSales.net</t>
-        </is>
-      </c>
-      <c r="L28" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M28" s="13" t="inlineStr"/>
-      <c r="N28" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O28" s="14" t="inlineStr">
-        <is>
-          <t>Listed "Oct 29 2 PM PST" (= 5 PM ET).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" outlineLevel="1">
-      <c r="A29" s="13" t="inlineStr">
-        <is>
-          <t>CT / Hudson Valley</t>
-        </is>
-      </c>
-      <c r="B29" s="14" t="inlineStr">
-        <is>
-          <t>Former Duck Donuts franchise bank-ordered sale: like-new restaurant/coffee shop equipment</t>
-        </is>
-      </c>
-      <c r="C29" s="13" t="inlineStr">
-        <is>
-          <t>restaurant equipment auction</t>
-        </is>
-      </c>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
-          <t>Madison</t>
-        </is>
-      </c>
-      <c r="E29" s="13" t="inlineStr">
-        <is>
-          <t>CT</t>
-        </is>
-      </c>
-      <c r="F29" s="13" t="n">
-        <v>109</v>
-      </c>
-      <c r="G29" s="13" t="inlineStr">
-        <is>
-          <t>Timed online auction (BidSpotter)</t>
-        </is>
-      </c>
-      <c r="H29" s="15" t="n"/>
-      <c r="I29" s="13" t="inlineStr"/>
-      <c r="J29" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-27 05:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K29" s="13" t="inlineStr">
-        <is>
-          <t>Hamilton Group via BidSpotter</t>
-        </is>
-      </c>
-      <c r="L29" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M29" s="13" t="inlineStr"/>
-      <c r="N29" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O29" s="14" t="inlineStr">
-        <is>
-          <t>Sale ends Oct 27 (listing says 12 PM; lots begin closing 2 PM PT per description).</t>
-        </is>
-      </c>
+      <c r="I28" s="18" t="n"/>
+      <c r="J28" s="18" t="n"/>
+      <c r="K28" s="18" t="n"/>
+      <c r="L28" s="18" t="n"/>
+      <c r="M28" s="18" t="n"/>
+      <c r="N28" s="18" t="n"/>
+      <c r="O28" s="18" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>▸ CT / Hudson Valley  (8)</t>
+        </is>
+      </c>
+      <c r="B29" s="12" t="n"/>
+      <c r="C29" s="12" t="n"/>
+      <c r="D29" s="12" t="n"/>
+      <c r="E29" s="12" t="n"/>
+      <c r="F29" s="12" t="n"/>
+      <c r="G29" s="12" t="n"/>
+      <c r="H29" s="12" t="n"/>
+      <c r="I29" s="12" t="n"/>
+      <c r="J29" s="12" t="n"/>
+      <c r="K29" s="12" t="n"/>
+      <c r="L29" s="12" t="n"/>
+      <c r="M29" s="12" t="n"/>
+      <c r="N29" s="12" t="n"/>
+      <c r="O29" s="12" t="n"/>
     </row>
     <row r="30" outlineLevel="1">
       <c r="A30" s="13" t="inlineStr">
@@ -20073,17 +20077,17 @@
       </c>
       <c r="B30" s="14" t="inlineStr">
         <is>
-          <t>Antique / thrift store – entire inventory (fills a 4k sq ft store, 80k+ retail)</t>
+          <t>Bank-ordered electrical contractor sale – Greenlee/Hilti/Milwaukee tools, GE/Siemens breakers</t>
         </is>
       </c>
       <c r="C30" s="13" t="inlineStr">
         <is>
-          <t>store closing – entire inventory</t>
+          <t>contractor liquidation</t>
         </is>
       </c>
       <c r="D30" s="13" t="inlineStr">
         <is>
-          <t>Waterbury</t>
+          <t>Clinton</t>
         </is>
       </c>
       <c r="E30" s="13" t="inlineStr">
@@ -20092,23 +20096,23 @@
         </is>
       </c>
       <c r="F30" s="13" t="n">
-        <v>121</v>
+        <v>106</v>
       </c>
       <c r="G30" s="13" t="inlineStr">
         <is>
-          <t>$6,500 complete inventory (open to offers)</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H30" s="15" t="n"/>
-      <c r="I30" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="J30" s="13" t="inlineStr"/>
+      <c r="I30" s="13" t="inlineStr"/>
+      <c r="J30" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-29 05:00 PM ET</t>
+        </is>
+      </c>
       <c r="K30" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>Hamilton Group / EstateSales.net</t>
         </is>
       </c>
       <c r="L30" s="13" t="inlineStr">
@@ -20124,7 +20128,7 @@
       </c>
       <c r="O30" s="14" t="inlineStr">
         <is>
-          <t>1155 Thomaston Ave. Sold only as a complete lot: antiques, furniture, tools, hardware, small appliances, electronics, display cabinets, shelving, racks, vending machine. Seller will package with their eBay inventory (jewelry, vinyl, toys, Christmas, contents of 3 box trucks, "easily 100k retail"). Mixed general merchandise, not appliance-specific.</t>
+          <t>Listed "Oct 29 2 PM PST" (= 5 PM ET).</t>
         </is>
       </c>
     </row>
@@ -20136,17 +20140,17 @@
       </c>
       <c r="B31" s="14" t="inlineStr">
         <is>
-          <t>Sausage processing &amp; packaging complete facility closure: refrigerated box trucks, Velati mixers, Vemag, packaging lines</t>
+          <t>Former Duck Donuts franchise bank-ordered sale: like-new restaurant/coffee shop equipment</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
         <is>
-          <t>facility closure auction</t>
+          <t>restaurant equipment auction</t>
         </is>
       </c>
       <c r="D31" s="13" t="inlineStr">
         <is>
-          <t>New Haven</t>
+          <t>Madison</t>
         </is>
       </c>
       <c r="E31" s="13" t="inlineStr">
@@ -20155,7 +20159,7 @@
         </is>
       </c>
       <c r="F31" s="13" t="n">
-        <v>122</v>
+        <v>109</v>
       </c>
       <c r="G31" s="13" t="inlineStr">
         <is>
@@ -20166,12 +20170,12 @@
       <c r="I31" s="13" t="inlineStr"/>
       <c r="J31" s="13" t="inlineStr">
         <is>
-          <t>2026-11-17 12:00 PM ET</t>
+          <t>2026-10-27 05:00 PM ET</t>
         </is>
       </c>
       <c r="K31" s="13" t="inlineStr">
         <is>
-          <t>M&amp;M Equipment Corp</t>
+          <t>Hamilton Group via BidSpotter</t>
         </is>
       </c>
       <c r="L31" s="13" t="inlineStr">
@@ -20187,7 +20191,7 @@
       </c>
       <c r="O31" s="14" t="inlineStr">
         <is>
-          <t>Bidding opens Nov 10 10 AM CT; lots begin closing Nov 17 11 AM CT.</t>
+          <t>Sale ends Oct 27 (listing says 12 PM; lots begin closing 2 PM PT per description).</t>
         </is>
       </c>
     </row>
@@ -20199,17 +20203,17 @@
       </c>
       <c r="B32" s="14" t="inlineStr">
         <is>
-          <t>Fabrication &amp; welding shop liquidation – everything must be sold</t>
+          <t>Antique / thrift store – entire inventory (fills a 4k sq ft store, 80k+ retail)</t>
         </is>
       </c>
       <c r="C32" s="13" t="inlineStr">
         <is>
-          <t>machine shop liquidation</t>
+          <t>store closing – entire inventory</t>
         </is>
       </c>
       <c r="D32" s="13" t="inlineStr">
         <is>
-          <t>Bridgeport</t>
+          <t>Waterbury</t>
         </is>
       </c>
       <c r="E32" s="13" t="inlineStr">
@@ -20218,17 +20222,17 @@
         </is>
       </c>
       <c r="F32" s="13" t="n">
-        <v>139</v>
+        <v>121</v>
       </c>
       <c r="G32" s="13" t="inlineStr">
         <is>
-          <t>Priced per machine (e.g. W.A. Whitney punch press $4,950; DoAll bandsaw $950)</t>
+          <t>$6,500 complete inventory (open to offers)</t>
         </is>
       </c>
       <c r="H32" s="15" t="n"/>
       <c r="I32" s="13" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="J32" s="13" t="inlineStr"/>
@@ -20250,7 +20254,7 @@
       </c>
       <c r="O32" s="14" t="inlineStr">
         <is>
-          <t>All assets/equipment/tools of a fab &amp; welding shop; machines under power, inspection by appointment, buyer removes (small forklift on site). Several big items already SOLD (Cincinnati brake/shear, plasma table, Lown roll). Remaining: Whitney + Roper Whitney punch presses, DoAll V36 bandsaw, Thompson spot welder, George Ohl 120" brake, Bridgeport mill, etc. Mostly 220V. Posted May 15, updated Oct 19.</t>
+          <t>1155 Thomaston Ave. Sold only as a complete lot: antiques, furniture, tools, hardware, small appliances, electronics, display cabinets, shelving, racks, vending machine. Seller will package with their eBay inventory (jewelry, vinyl, toys, Christmas, contents of 3 box trucks, "easily 100k retail"). Mixed general merchandise, not appliance-specific.</t>
         </is>
       </c>
     </row>
@@ -20262,17 +20266,17 @@
       </c>
       <c r="B33" s="14" t="inlineStr">
         <is>
-          <t>The Outlaw Grill Steakhouse – used restaurant equipment auction (PCI Auctions CT, e.g. Vulcan EV60 Endurance 60" range)</t>
+          <t>Sausage processing &amp; packaging complete facility closure: refrigerated box trucks, Velati mixers, Vemag, packaging lines</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>restaurant auction</t>
+          <t>facility closure auction</t>
         </is>
       </c>
       <c r="D33" s="13" t="inlineStr">
         <is>
-          <t>Stamford</t>
+          <t>New Haven</t>
         </is>
       </c>
       <c r="E33" s="13" t="inlineStr">
@@ -20281,32 +20285,28 @@
         </is>
       </c>
       <c r="F33" s="13" t="n">
-        <v>159</v>
+        <v>122</v>
       </c>
       <c r="G33" s="13" t="inlineStr">
         <is>
-          <t>Online auction, current bids</t>
+          <t>Timed online auction (BidSpotter)</t>
         </is>
       </c>
       <c r="H33" s="15" t="n"/>
-      <c r="I33" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
+      <c r="I33" s="13" t="inlineStr"/>
       <c r="J33" s="13" t="inlineStr">
         <is>
-          <t>2026-10-21 08:30 PM ET</t>
+          <t>2026-11-17 12:00 PM ET</t>
         </is>
       </c>
       <c r="K33" s="13" t="inlineStr">
         <is>
-          <t>PCI Auctions</t>
-        </is>
-      </c>
-      <c r="L33" s="21" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>M&amp;M Equipment Corp</t>
+        </is>
+      </c>
+      <c r="L33" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M33" s="13" t="inlineStr"/>
@@ -20317,7 +20317,7 @@
       </c>
       <c r="O33" s="14" t="inlineStr">
         <is>
-          <t>Ends Wed Oct 21 8:30 PM EDT. PCI warehouse, 36 Ludlow St, Stamford CT. Page lists preview Oct 28 and removal Thu Oct 29 11-3 (after close). Shipping/delivery available; payment due on pickup day. Items still being added.</t>
+          <t>Bidding opens Nov 10 10 AM CT; lots begin closing Nov 17 11 AM CT.</t>
         </is>
       </c>
     </row>
@@ -20329,42 +20329,42 @@
       </c>
       <c r="B34" s="14" t="inlineStr">
         <is>
-          <t>BJ's Wholesale closeout – racking, forklifts, Hobart</t>
+          <t>Fabrication &amp; welding shop liquidation – everything must be sold</t>
         </is>
       </c>
       <c r="C34" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>machine shop liquidation</t>
         </is>
       </c>
       <c r="D34" s="13" t="inlineStr">
         <is>
-          <t>Rotterdam</t>
+          <t>Bridgeport</t>
         </is>
       </c>
       <c r="E34" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="F34" s="13" t="n">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="G34" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Priced per machine (e.g. W.A. Whitney punch press $4,950; DoAll bandsaw $950)</t>
         </is>
       </c>
       <c r="H34" s="15" t="n"/>
-      <c r="I34" s="13" t="inlineStr"/>
-      <c r="J34" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-10 10:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I34" s="13" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="J34" s="13" t="inlineStr"/>
       <c r="K34" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L34" s="13" t="inlineStr">
@@ -20380,7 +20380,7 @@
       </c>
       <c r="O34" s="14" t="inlineStr">
         <is>
-          <t>Closes from Nov 10 10 AM.</t>
+          <t>All assets/equipment/tools of a fab &amp; welding shop; machines under power, inspection by appointment, buyer removes (small forklift on site). Several big items already SOLD (Cincinnati brake/shear, plasma table, Lown roll). Remaining: Whitney + Roper Whitney punch presses, DoAll V36 bandsaw, Thompson spot welder, George Ohl 120" brake, Bridgeport mill, etc. Mostly 220V. Posted May 15, updated Oct 19.</t>
         </is>
       </c>
     </row>
@@ -20392,17 +20392,17 @@
       </c>
       <c r="B35" s="14" t="inlineStr">
         <is>
-          <t>Body shop closing after 50 years – tools, welder, generators, plasma</t>
+          <t>BJ's Wholesale closeout – racking, forklifts, Hobart</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>tools liquidation</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D35" s="13" t="inlineStr">
         <is>
-          <t>West Nyack</t>
+          <t>Rotterdam</t>
         </is>
       </c>
       <c r="E35" s="13" t="inlineStr">
@@ -20411,23 +20411,23 @@
         </is>
       </c>
       <c r="F35" s="13" t="n">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="G35" s="13" t="inlineStr">
         <is>
-          <t>Make offer / lot</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H35" s="15" t="n"/>
-      <c r="I35" s="13" t="inlineStr">
-        <is>
-          <t>2026-08-16</t>
-        </is>
-      </c>
-      <c r="J35" s="13" t="inlineStr"/>
+      <c r="I35" s="13" t="inlineStr"/>
+      <c r="J35" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-10 10:00 AM ET</t>
+        </is>
+      </c>
       <c r="K35" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>Grafe Auction</t>
         </is>
       </c>
       <c r="L35" s="13" t="inlineStr">
@@ -20443,7 +20443,7 @@
       </c>
       <c r="O35" s="14" t="inlineStr">
         <is>
-          <t>One-man auto body shop closing/retirement (Park Ridge / West Nyack NY-NJ border). Heat lamps, Kansas jack pullers, Miller 200 welder, generators, sheet-metal brake, hydraulic press, plasma cutter, engine hoist. Posted Aug 16; still open 2026-10-19.</t>
+          <t>Closes from Nov 10 10 AM.</t>
         </is>
       </c>
     </row>
@@ -20455,17 +20455,17 @@
       </c>
       <c r="B36" s="14" t="inlineStr">
         <is>
-          <t>Woodworkers shop closing sale – shop tools &amp; hand tools</t>
+          <t>Body shop closing after 50 years – tools, welder, generators, plasma</t>
         </is>
       </c>
       <c r="C36" s="13" t="inlineStr">
         <is>
-          <t>woodworking shop closing</t>
+          <t>tools liquidation</t>
         </is>
       </c>
       <c r="D36" s="13" t="inlineStr">
         <is>
-          <t>Tappan</t>
+          <t>West Nyack</t>
         </is>
       </c>
       <c r="E36" s="13" t="inlineStr">
@@ -20474,17 +20474,17 @@
         </is>
       </c>
       <c r="F36" s="13" t="n">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G36" s="13" t="inlineStr">
         <is>
-          <t>Priced individually (some free)</t>
+          <t>Make offer / lot</t>
         </is>
       </c>
       <c r="H36" s="15" t="n"/>
       <c r="I36" s="13" t="inlineStr">
         <is>
-          <t>2026-10-10</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="J36" s="13" t="inlineStr"/>
@@ -20506,120 +20506,120 @@
       </c>
       <c r="O36" s="14" t="inlineStr">
         <is>
+          <t>One-man auto body shop closing/retirement (Park Ridge / West Nyack NY-NJ border). Heat lamps, Kansas jack pullers, Miller 200 welder, generators, sheet-metal brake, hydraulic press, plasma cutter, engine hoist. Posted Aug 16; still open 2026-10-19.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" outlineLevel="1">
+      <c r="A37" s="13" t="inlineStr">
+        <is>
+          <t>CT / Hudson Valley</t>
+        </is>
+      </c>
+      <c r="B37" s="14" t="inlineStr">
+        <is>
+          <t>Woodworkers shop closing sale – shop tools &amp; hand tools</t>
+        </is>
+      </c>
+      <c r="C37" s="13" t="inlineStr">
+        <is>
+          <t>woodworking shop closing</t>
+        </is>
+      </c>
+      <c r="D37" s="13" t="inlineStr">
+        <is>
+          <t>Tappan</t>
+        </is>
+      </c>
+      <c r="E37" s="13" t="inlineStr">
+        <is>
+          <t>NY</t>
+        </is>
+      </c>
+      <c r="F37" s="13" t="n">
+        <v>179</v>
+      </c>
+      <c r="G37" s="13" t="inlineStr">
+        <is>
+          <t>Priced individually (some free)</t>
+        </is>
+      </c>
+      <c r="H37" s="15" t="n"/>
+      <c r="I37" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="J37" s="13" t="inlineStr"/>
+      <c r="K37" s="13" t="inlineStr">
+        <is>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L37" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M37" s="13" t="inlineStr"/>
+      <c r="N37" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O37" s="14" t="inlineStr">
+        <is>
           <t>Ongoing shop-closing sale at 61 Main St, Tappan; many shop and hand tools, schedule a visit. Near the West Nyack body-shop sale (bl-054) for one trip.</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="17" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="17" t="inlineStr">
         <is>
           <t>Subtotal — CT / Hudson Valley</t>
         </is>
       </c>
-      <c r="B37" s="17" t="inlineStr">
-        <is>
-          <t>9 item(s)</t>
-        </is>
-      </c>
-      <c r="C37" s="18" t="n"/>
-      <c r="D37" s="18" t="n"/>
-      <c r="E37" s="18" t="n"/>
-      <c r="F37" s="18" t="n"/>
-      <c r="G37" s="18" t="n"/>
-      <c r="H37" s="19" t="n">
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>8 item(s)</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="n"/>
+      <c r="D38" s="18" t="n"/>
+      <c r="E38" s="18" t="n"/>
+      <c r="F38" s="18" t="n"/>
+      <c r="G38" s="18" t="n"/>
+      <c r="H38" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="18" t="n"/>
-      <c r="J37" s="18" t="n"/>
-      <c r="K37" s="18" t="n"/>
-      <c r="L37" s="18" t="n"/>
-      <c r="M37" s="18" t="n"/>
-      <c r="N37" s="18" t="n"/>
-      <c r="O37" s="18" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="I38" s="18" t="n"/>
+      <c r="J38" s="18" t="n"/>
+      <c r="K38" s="18" t="n"/>
+      <c r="L38" s="18" t="n"/>
+      <c r="M38" s="18" t="n"/>
+      <c r="N38" s="18" t="n"/>
+      <c r="O38" s="18" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>▸ NYC / Long Island / NJ  (23)</t>
         </is>
       </c>
-      <c r="B38" s="12" t="n"/>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="12" t="n"/>
-      <c r="E38" s="12" t="n"/>
-      <c r="F38" s="12" t="n"/>
-      <c r="G38" s="12" t="n"/>
-      <c r="H38" s="12" t="n"/>
-      <c r="I38" s="12" t="n"/>
-      <c r="J38" s="12" t="n"/>
-      <c r="K38" s="12" t="n"/>
-      <c r="L38" s="12" t="n"/>
-      <c r="M38" s="12" t="n"/>
-      <c r="N38" s="12" t="n"/>
-      <c r="O38" s="12" t="n"/>
-    </row>
-    <row r="39" outlineLevel="1">
-      <c r="A39" s="13" t="inlineStr">
-        <is>
-          <t>NYC / Long Island / NJ</t>
-        </is>
-      </c>
-      <c r="B39" s="14" t="inlineStr">
-        <is>
-          <t>Viva Margherita restaurant complete contents (building torn down)</t>
-        </is>
-      </c>
-      <c r="C39" s="13" t="inlineStr">
-        <is>
-          <t>restaurant closing</t>
-        </is>
-      </c>
-      <c r="D39" s="13" t="inlineStr">
-        <is>
-          <t>Edgewater</t>
-        </is>
-      </c>
-      <c r="E39" s="13" t="inlineStr">
-        <is>
-          <t>NJ</t>
-        </is>
-      </c>
-      <c r="F39" s="13" t="n">
-        <v>186</v>
-      </c>
-      <c r="G39" s="13" t="inlineStr">
-        <is>
-          <t>Complete contents / make offer</t>
-        </is>
-      </c>
-      <c r="H39" s="15" t="n"/>
-      <c r="I39" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-10</t>
-        </is>
-      </c>
-      <c r="J39" s="13" t="inlineStr"/>
-      <c r="K39" s="13" t="inlineStr">
-        <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L39" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M39" s="13" t="inlineStr"/>
-      <c r="N39" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O39" s="14" t="inlineStr">
-        <is>
-          <t>Address 163 Old River Road, Edgewater NJ. Building being torn down; complete restaurant contents for sale / make offer.</t>
-        </is>
-      </c>
+      <c r="B39" s="12" t="n"/>
+      <c r="C39" s="12" t="n"/>
+      <c r="D39" s="12" t="n"/>
+      <c r="E39" s="12" t="n"/>
+      <c r="F39" s="12" t="n"/>
+      <c r="G39" s="12" t="n"/>
+      <c r="H39" s="12" t="n"/>
+      <c r="I39" s="12" t="n"/>
+      <c r="J39" s="12" t="n"/>
+      <c r="K39" s="12" t="n"/>
+      <c r="L39" s="12" t="n"/>
+      <c r="M39" s="12" t="n"/>
+      <c r="N39" s="12" t="n"/>
+      <c r="O39" s="12" t="n"/>
     </row>
     <row r="40" outlineLevel="1">
       <c r="A40" s="13" t="inlineStr">
@@ -20629,36 +20629,36 @@
       </c>
       <c r="B40" s="14" t="inlineStr">
         <is>
-          <t>Flooring company closed – pro tool package</t>
+          <t>Viva Margherita restaurant complete contents (building torn down)</t>
         </is>
       </c>
       <c r="C40" s="13" t="inlineStr">
         <is>
-          <t>tools liquidation</t>
+          <t>restaurant closing</t>
         </is>
       </c>
       <c r="D40" s="13" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Edgewater</t>
         </is>
       </c>
       <c r="E40" s="13" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="F40" s="13" t="n">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="G40" s="13" t="inlineStr">
         <is>
-          <t>$1,000</t>
+          <t>Complete contents / make offer</t>
         </is>
       </c>
       <c r="H40" s="15" t="n"/>
       <c r="I40" s="13" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-10</t>
         </is>
       </c>
       <c r="J40" s="13" t="inlineStr"/>
@@ -20680,7 +20680,7 @@
       </c>
       <c r="O40" s="14" t="inlineStr">
         <is>
-          <t>Flooring/construction company closed; pro tool package $1,000.</t>
+          <t>Address 163 Old River Road, Edgewater NJ. Building being torn down; complete restaurant contents for sale / make offer.</t>
         </is>
       </c>
     </row>
@@ -20692,12 +20692,12 @@
       </c>
       <c r="B41" s="14" t="inlineStr">
         <is>
-          <t>New-in-box commercial refrigeration lot – 10 Beverage-Air &amp; Perlick units (bar never opened)</t>
+          <t>Flooring company closed – pro tool package</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>commercial refrigeration lot</t>
+          <t>tools liquidation</t>
         </is>
       </c>
       <c r="D41" s="13" t="inlineStr">
@@ -20715,13 +20715,13 @@
       </c>
       <c r="G41" s="13" t="inlineStr">
         <is>
-          <t>$27,500 all 10 (or per unit $2,800–$4,150)</t>
+          <t>$1,000</t>
         </is>
       </c>
       <c r="H41" s="15" t="n"/>
       <c r="I41" s="13" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="J41" s="13" t="inlineStr"/>
@@ -20743,7 +20743,7 @@
       </c>
       <c r="O41" s="14" t="inlineStr">
         <is>
-          <t>Financial District. Never installed, factory packaging: 2 Beverage-Air HBF23HC-1-HS reach-in freezers ($4,150 ea), 3 HBR23HC-1-HS reach-in fridges ($3,550 ea), 1 UCR48AHC 48" undercounter ($2,800), 3 Perlick HC24FS4 glass frosters + 1 HC24RS4 beverage fridge ($2,850 ea). Seller says full retail $47,463 (about 42% off as a bundle). Updated Oct 14.</t>
+          <t>Flooring/construction company closed; pro tool package $1,000.</t>
         </is>
       </c>
     </row>
@@ -20755,51 +20755,47 @@
       </c>
       <c r="B42" s="14" t="inlineStr">
         <is>
-          <t>Corporate caterer – Alto-Shaam, new boxed Avantco rice cookers &amp; Cadco oven, Perlick, MerryChef</t>
+          <t>New-in-box commercial refrigeration lot – 10 Beverage-Air &amp; Perlick units (bar never opened)</t>
         </is>
       </c>
       <c r="C42" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>commercial refrigeration lot</t>
         </is>
       </c>
       <c r="D42" s="13" t="inlineStr">
         <is>
-          <t>Jersey City</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="E42" s="13" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="F42" s="13" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G42" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>$27,500 all 10 (or per unit $2,800–$4,150)</t>
         </is>
       </c>
       <c r="H42" s="15" t="n"/>
       <c r="I42" s="13" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
-        </is>
-      </c>
-      <c r="J42" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-22 02:00 PM ET</t>
-        </is>
-      </c>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="J42" s="13" t="inlineStr"/>
       <c r="K42" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
-        </is>
-      </c>
-      <c r="L42" s="21" t="inlineStr">
-        <is>
-          <t>ENDING SOON</t>
+          <t>Craigslist</t>
+        </is>
+      </c>
+      <c r="L42" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="M42" s="13" t="inlineStr"/>
@@ -20810,7 +20806,7 @@
       </c>
       <c r="O42" s="14" t="inlineStr">
         <is>
-          <t>Thu Oct 22 2 PM.</t>
+          <t>Financial District. Never installed, factory packaging: 2 Beverage-Air HBF23HC-1-HS reach-in freezers ($4,150 ea), 3 HBR23HC-1-HS reach-in fridges ($3,550 ea), 1 UCR48AHC 48" undercounter ($2,800), 3 Perlick HC24FS4 glass frosters + 1 HC24RS4 beverage fridge ($2,850 ea). Seller says full retail $47,463 (about 42% off as a bundle). Updated Oct 14.</t>
         </is>
       </c>
     </row>
@@ -20822,12 +20818,12 @@
       </c>
       <c r="B43" s="14" t="inlineStr">
         <is>
-          <t>Lighting store closing – lease ended, up to 70% off showroom</t>
+          <t>Corporate caterer – Alto-Shaam, new boxed Avantco rice cookers &amp; Cadco oven, Perlick, MerryChef</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D43" s="13" t="inlineStr">
@@ -20845,24 +20841,28 @@
       </c>
       <c r="G43" s="13" t="inlineStr">
         <is>
-          <t>up to 70% off</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H43" s="15" t="n"/>
       <c r="I43" s="13" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
-        </is>
-      </c>
-      <c r="J43" s="13" t="inlineStr"/>
+          <t>2026-10-02</t>
+        </is>
+      </c>
+      <c r="J43" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-22 02:00 PM ET</t>
+        </is>
+      </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
-        </is>
-      </c>
-      <c r="L43" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
+        </is>
+      </c>
+      <c r="L43" s="21" t="inlineStr">
+        <is>
+          <t>ENDING SOON</t>
         </is>
       </c>
       <c r="M43" s="13" t="inlineStr"/>
@@ -20873,7 +20873,7 @@
       </c>
       <c r="O43" s="14" t="inlineStr">
         <is>
-          <t>Lighting store closing, lease ended. Showroom inventory up to 70% off.</t>
+          <t>Thu Oct 22 2 PM.</t>
         </is>
       </c>
     </row>
@@ -20885,12 +20885,12 @@
       </c>
       <c r="B44" s="14" t="inlineStr">
         <is>
-          <t>Baonanas LLC ABC sale: turnkey ice cream / gelato / dessert shop equipment</t>
+          <t>Lighting store closing – lease ended, up to 70% off showroom</t>
         </is>
       </c>
       <c r="C44" s="13" t="inlineStr">
         <is>
-          <t>restaurant / commercial kitchen contents</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D44" s="13" t="inlineStr">
@@ -20908,15 +20908,19 @@
       </c>
       <c r="G44" s="13" t="inlineStr">
         <is>
-          <t>Accepting offers</t>
+          <t>up to 70% off</t>
         </is>
       </c>
       <c r="H44" s="15" t="n"/>
-      <c r="I44" s="13" t="inlineStr"/>
+      <c r="I44" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
       <c r="J44" s="13" t="inlineStr"/>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>AuctionAdvisors</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L44" s="13" t="inlineStr">
@@ -20932,7 +20936,7 @@
       </c>
       <c r="O44" s="14" t="inlineStr">
         <is>
-          <t>181 Monticello Ave. Assignment for the benefit of creditors. IFI Panorama gelato display cases, refrigerated topping stations, commercial mixers, refrigerators/freezers, stainless worktables, ice machine, POS, smallwares, gelato carts, catering gear, FF&amp;E.</t>
+          <t>Lighting store closing, lease ended. Showroom inventory up to 70% off.</t>
         </is>
       </c>
     </row>
@@ -20944,17 +20948,17 @@
       </c>
       <c r="B45" s="14" t="inlineStr">
         <is>
-          <t>Tools / plumbing / MRO supply inventory – Hilti/DeWalt/Milwaukee, fittings, heat pumps</t>
+          <t>Baonanas LLC ABC sale: turnkey ice cream / gelato / dessert shop equipment</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>inventory</t>
+          <t>restaurant / commercial kitchen contents</t>
         </is>
       </c>
       <c r="D45" s="13" t="inlineStr">
         <is>
-          <t>Riverdale</t>
+          <t>Jersey City</t>
         </is>
       </c>
       <c r="E45" s="13" t="inlineStr">
@@ -20963,23 +20967,19 @@
         </is>
       </c>
       <c r="F45" s="13" t="n">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G45" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Accepting offers</t>
         </is>
       </c>
       <c r="H45" s="15" t="n"/>
       <c r="I45" s="13" t="inlineStr"/>
-      <c r="J45" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-30 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="J45" s="13" t="inlineStr"/>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>AuctionAdvisors</t>
         </is>
       </c>
       <c r="L45" s="13" t="inlineStr">
@@ -20995,7 +20995,7 @@
       </c>
       <c r="O45" s="14" t="inlineStr">
         <is>
-          <t>Bulk resale inventory.</t>
+          <t>181 Monticello Ave. Assignment for the benefit of creditors. IFI Panorama gelato display cases, refrigerated topping stations, commercial mixers, refrigerators/freezers, stainless worktables, ice machine, POS, smallwares, gelato carts, catering gear, FF&amp;E.</t>
         </is>
       </c>
     </row>
@@ -21007,12 +21007,12 @@
       </c>
       <c r="B46" s="14" t="inlineStr">
         <is>
-          <t>Ice cream + cookie franchise equipment – Taylor soft-serve, Atosa, Blodgett</t>
+          <t>Tools / plumbing / MRO supply inventory – Hilti/DeWalt/Milwaukee, fittings, heat pumps</t>
         </is>
       </c>
       <c r="C46" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>inventory</t>
         </is>
       </c>
       <c r="D46" s="13" t="inlineStr">
@@ -21037,7 +21037,7 @@
       <c r="I46" s="13" t="inlineStr"/>
       <c r="J46" s="13" t="inlineStr">
         <is>
-          <t>2026-11-05 11:00 AM ET</t>
+          <t>2026-10-30 11:00 AM ET</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
@@ -21058,7 +21058,7 @@
       </c>
       <c r="O46" s="14" t="inlineStr">
         <is>
-          <t>Resellable units.</t>
+          <t>Bulk resale inventory.</t>
         </is>
       </c>
     </row>
@@ -21070,17 +21070,17 @@
       </c>
       <c r="B47" s="14" t="inlineStr">
         <is>
-          <t>U.S. Vision court-ordered liquidation: ~70,000 designer eyeglass/sunglass frames + optical/optometry equipment at ~80 former stores + IP</t>
+          <t>Ice cream + cookie franchise equipment – Taylor soft-serve, Atosa, Blodgett</t>
         </is>
       </c>
       <c r="C47" s="13" t="inlineStr">
         <is>
-          <t>court-ordered retail chain liquidation</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D47" s="13" t="inlineStr">
         <is>
-          <t>Montclair</t>
+          <t>Riverdale</t>
         </is>
       </c>
       <c r="E47" s="13" t="inlineStr">
@@ -21089,19 +21089,23 @@
         </is>
       </c>
       <c r="F47" s="13" t="n">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G47" s="13" t="inlineStr">
         <is>
-          <t>Accepting offers (terms in offering memo, NDA required)</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H47" s="15" t="n"/>
       <c r="I47" s="13" t="inlineStr"/>
-      <c r="J47" s="13" t="inlineStr"/>
+      <c r="J47" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-05 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K47" s="13" t="inlineStr">
         <is>
-          <t>AuctionAdvisors</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L47" s="13" t="inlineStr">
@@ -21117,7 +21121,7 @@
       </c>
       <c r="O47" s="14" t="inlineStr">
         <is>
-          <t>Three-lot sale pursuant to court order; bids accepted for individual lots, combinations, or substantially all assets. Equipment is spread across ~80 former store locations. Not appliance-related; big-ticket bulk inventory play.</t>
+          <t>Resellable units.</t>
         </is>
       </c>
     </row>
@@ -21129,17 +21133,17 @@
       </c>
       <c r="B48" s="14" t="inlineStr">
         <is>
-          <t>Wascomat commercial washers liquidation (22× W105, 6× W185, dryer panels)</t>
+          <t>U.S. Vision court-ordered liquidation: ~70,000 designer eyeglass/sunglass frames + optical/optometry equipment at ~80 former stores + IP</t>
         </is>
       </c>
       <c r="C48" s="13" t="inlineStr">
         <is>
-          <t>commercial laundry</t>
+          <t>court-ordered retail chain liquidation</t>
         </is>
       </c>
       <c r="D48" s="13" t="inlineStr">
         <is>
-          <t>Newark</t>
+          <t>Montclair</t>
         </is>
       </c>
       <c r="E48" s="13" t="inlineStr">
@@ -21148,23 +21152,19 @@
         </is>
       </c>
       <c r="F48" s="13" t="n">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="G48" s="13" t="inlineStr">
         <is>
-          <t>$500–$800 each / panels $150</t>
+          <t>Accepting offers (terms in offering memo, NDA required)</t>
         </is>
       </c>
       <c r="H48" s="15" t="n"/>
-      <c r="I48" s="13" t="inlineStr">
-        <is>
-          <t>2026-07-12</t>
-        </is>
-      </c>
+      <c r="I48" s="13" t="inlineStr"/>
       <c r="J48" s="13" t="inlineStr"/>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>AuctionAdvisors</t>
         </is>
       </c>
       <c r="L48" s="13" t="inlineStr">
@@ -21180,7 +21180,7 @@
       </c>
       <c r="O48" s="14" t="inlineStr">
         <is>
-          <t>22× W105 @ $500, 6× W185 @ $800, 20 dryer panels $150. Commercial laundry liquidation.</t>
+          <t>Three-lot sale pursuant to court order; bids accepted for individual lots, combinations, or substantially all assets. Equipment is spread across ~80 former store locations. Not appliance-related; big-ticket bulk inventory play.</t>
         </is>
       </c>
     </row>
@@ -21192,17 +21192,17 @@
       </c>
       <c r="B49" s="14" t="inlineStr">
         <is>
-          <t>Major food-service caterer – new-in-box True reach-ins, Beverage-Air, TurboChef, Resfab ventless fryer</t>
+          <t>Wascomat commercial washers liquidation (22× W105, 6× W185, dryer panels)</t>
         </is>
       </c>
       <c r="C49" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>commercial laundry</t>
         </is>
       </c>
       <c r="D49" s="13" t="inlineStr">
         <is>
-          <t>Parsippany</t>
+          <t>Newark</t>
         </is>
       </c>
       <c r="E49" s="13" t="inlineStr">
@@ -21211,27 +21211,23 @@
         </is>
       </c>
       <c r="F49" s="13" t="n">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="G49" s="13" t="inlineStr">
         <is>
-          <t>Live + webcast, 18% BP + 3%</t>
+          <t>$500–$800 each / panels $150</t>
         </is>
       </c>
       <c r="H49" s="15" t="n"/>
       <c r="I49" s="13" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
-        </is>
-      </c>
-      <c r="J49" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-03 02:00 PM ET</t>
-        </is>
-      </c>
+          <t>2026-07-12</t>
+        </is>
+      </c>
+      <c r="J49" s="13" t="inlineStr"/>
       <c r="K49" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L49" s="13" t="inlineStr">
@@ -21247,7 +21243,7 @@
       </c>
       <c r="O49" s="14" t="inlineStr">
         <is>
-          <t>Tue Nov 3 2 PM, checkout Nov 4.</t>
+          <t>22× W105 @ $500, 6× W185 @ $800, 20 dryer panels $150. Commercial laundry liquidation.</t>
         </is>
       </c>
     </row>
@@ -21259,17 +21255,17 @@
       </c>
       <c r="B50" s="14" t="inlineStr">
         <is>
-          <t>Business closing – 160 new Carnes exhaust fans</t>
+          <t>Major food-service caterer – new-in-box True reach-ins, Beverage-Air, TurboChef, Resfab ventless fryer</t>
         </is>
       </c>
       <c r="C50" s="13" t="inlineStr">
         <is>
-          <t>HVAC inventory</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D50" s="13" t="inlineStr">
         <is>
-          <t>Kenilworth</t>
+          <t>Parsippany</t>
         </is>
       </c>
       <c r="E50" s="13" t="inlineStr">
@@ -21282,19 +21278,23 @@
       </c>
       <c r="G50" s="13" t="inlineStr">
         <is>
-          <t>$40 each or $5,000 all OBO</t>
+          <t>Live + webcast, 18% BP + 3%</t>
         </is>
       </c>
       <c r="H50" s="15" t="n"/>
       <c r="I50" s="13" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="J50" s="13" t="inlineStr"/>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="J50" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-03 02:00 PM ET</t>
+        </is>
+      </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>Craigslist</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
       <c r="L50" s="13" t="inlineStr">
@@ -21310,7 +21310,7 @@
       </c>
       <c r="O50" s="14" t="inlineStr">
         <is>
-          <t>160 new Carnes 80CFM 1.0 sone exhaust fans. $40 each or $5,000 for all OBO. Business closing HVAC inventory.</t>
+          <t>Tue Nov 3 2 PM, checkout Nov 4.</t>
         </is>
       </c>
     </row>
@@ -21322,12 +21322,12 @@
       </c>
       <c r="B51" s="14" t="inlineStr">
         <is>
-          <t>Air Systems Inc – sheet metal / HVAC fabrication shop liquidation</t>
+          <t>Business closing – 160 new Carnes exhaust fans</t>
         </is>
       </c>
       <c r="C51" s="13" t="inlineStr">
         <is>
-          <t>HVAC shop liquidation</t>
+          <t>HVAC inventory</t>
         </is>
       </c>
       <c r="D51" s="13" t="inlineStr">
@@ -21345,19 +21345,19 @@
       </c>
       <c r="G51" s="13" t="inlineStr">
         <is>
-          <t>Timed online (15% BP)</t>
+          <t>$40 each or $5,000 all OBO</t>
         </is>
       </c>
       <c r="H51" s="15" t="n"/>
-      <c r="I51" s="13" t="inlineStr"/>
-      <c r="J51" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-29 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="I51" s="13" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J51" s="13" t="inlineStr"/>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner Auctions</t>
+          <t>Craigslist</t>
         </is>
       </c>
       <c r="L51" s="13" t="inlineStr">
@@ -21373,7 +21373,7 @@
       </c>
       <c r="O51" s="14" t="inlineStr">
         <is>
-          <t>Vicon HVAC plasma; Flagler/Lockformer/Roto-Die/Engel fab; welders; Clark forklift; Genie Superlift; Ridgid/Milwaukee/DeWalt/Bosch/Hilti/Makita tools; AeroVent/Carnes exhaust fans; racking/scaffolding. Preview Oct 28–29 AM; pickup Oct 29 PM–Nov 4. Same town as Carnes fan CL lot.</t>
+          <t>160 new Carnes 80CFM 1.0 sone exhaust fans. $40 each or $5,000 for all OBO. Business closing HVAC inventory.</t>
         </is>
       </c>
     </row>
@@ -21385,17 +21385,17 @@
       </c>
       <c r="B52" s="14" t="inlineStr">
         <is>
-          <t>Former Rush Bowls franchise ABC sale: commercial refrigeration, Vitamix blenders, ice &amp; beverage equipment</t>
+          <t>Air Systems Inc – sheet metal / HVAC fabrication shop liquidation</t>
         </is>
       </c>
       <c r="C52" s="13" t="inlineStr">
         <is>
-          <t>restaurant / commercial kitchen contents</t>
+          <t>HVAC shop liquidation</t>
         </is>
       </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
-          <t>Westfield</t>
+          <t>Kenilworth</t>
         </is>
       </c>
       <c r="E52" s="13" t="inlineStr">
@@ -21404,19 +21404,23 @@
         </is>
       </c>
       <c r="F52" s="13" t="n">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G52" s="13" t="inlineStr">
         <is>
-          <t>Accepting offers</t>
+          <t>Timed online (15% BP)</t>
         </is>
       </c>
       <c r="H52" s="15" t="n"/>
       <c r="I52" s="13" t="inlineStr"/>
-      <c r="J52" s="13" t="inlineStr"/>
+      <c r="J52" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-29 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>AuctionAdvisors</t>
+          <t>A.J. Willner Auctions</t>
         </is>
       </c>
       <c r="L52" s="13" t="inlineStr">
@@ -21432,7 +21436,7 @@
       </c>
       <c r="O52" s="14" t="inlineStr">
         <is>
-          <t>27 East Broad St. Assignment for the benefit of creditors of 333 Star Enterprises (d/b/a Rush Bowls). Commercial refrigeration/freezers, Vitamix blenders, stainless workstations/sinks, ice and beverage equipment, POS, shelving. Inspection by contacting the auctioneer.</t>
+          <t>Vicon HVAC plasma; Flagler/Lockformer/Roto-Die/Engel fab; welders; Clark forklift; Genie Superlift; Ridgid/Milwaukee/DeWalt/Bosch/Hilti/Makita tools; AeroVent/Carnes exhaust fans; racking/scaffolding. Preview Oct 28–29 AM; pickup Oct 29 PM–Nov 4. Same town as Carnes fan CL lot.</t>
         </is>
       </c>
     </row>
@@ -21444,17 +21448,17 @@
       </c>
       <c r="B53" s="14" t="inlineStr">
         <is>
-          <t>Bimmer Clinic business liquidation (BMW repair shop): vehicle lifts, forklift, skid steer, refrigerant recovery, shop tools &amp; equipment</t>
+          <t>Former Rush Bowls franchise ABC sale: commercial refrigeration, Vitamix blenders, ice &amp; beverage equipment</t>
         </is>
       </c>
       <c r="C53" s="13" t="inlineStr">
         <is>
-          <t>business liquidation auction</t>
+          <t>restaurant / commercial kitchen contents</t>
         </is>
       </c>
       <c r="D53" s="13" t="inlineStr">
         <is>
-          <t>South Amboy</t>
+          <t>Westfield</t>
         </is>
       </c>
       <c r="E53" s="13" t="inlineStr">
@@ -21463,23 +21467,19 @@
         </is>
       </c>
       <c r="F53" s="13" t="n">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="G53" s="13" t="inlineStr">
         <is>
-          <t>Timed online auction</t>
+          <t>Accepting offers</t>
         </is>
       </c>
       <c r="H53" s="15" t="n"/>
       <c r="I53" s="13" t="inlineStr"/>
-      <c r="J53" s="13" t="inlineStr">
-        <is>
-          <t>2026-11-12 11:00 AM ET</t>
-        </is>
-      </c>
+      <c r="J53" s="13" t="inlineStr"/>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>AJ Willner Auctions</t>
+          <t>AuctionAdvisors</t>
         </is>
       </c>
       <c r="L53" s="13" t="inlineStr">
@@ -21495,7 +21495,7 @@
       </c>
       <c r="O53" s="14" t="inlineStr">
         <is>
-          <t>Ends Nov 12 11 AM EST.</t>
+          <t>27 East Broad St. Assignment for the benefit of creditors of 333 Star Enterprises (d/b/a Rush Bowls). Commercial refrigeration/freezers, Vitamix blenders, stainless workstations/sinks, ice and beverage equipment, POS, shelving. Inspection by contacting the auctioneer.</t>
         </is>
       </c>
     </row>
@@ -21507,17 +21507,17 @@
       </c>
       <c r="B54" s="14" t="inlineStr">
         <is>
-          <t>Drywall &amp; Acoustical Contractor 2: Hilti tools, material handling, supplies (Ideal Trading Corp)</t>
+          <t>Bimmer Clinic business liquidation (BMW repair shop): vehicle lifts, forklift, skid steer, refrigerant recovery, shop tools &amp; equipment</t>
         </is>
       </c>
       <c r="C54" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>business liquidation auction</t>
         </is>
       </c>
       <c r="D54" s="13" t="inlineStr">
         <is>
-          <t>Randolph</t>
+          <t>South Amboy</t>
         </is>
       </c>
       <c r="E54" s="13" t="inlineStr">
@@ -21526,23 +21526,23 @@
         </is>
       </c>
       <c r="F54" s="13" t="n">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="G54" s="13" t="inlineStr">
         <is>
-          <t>Online auction (HiBid terms)</t>
+          <t>Timed online auction</t>
         </is>
       </c>
       <c r="H54" s="15" t="n"/>
       <c r="I54" s="13" t="inlineStr"/>
       <c r="J54" s="13" t="inlineStr">
         <is>
-          <t>2026-10-28 11:00 AM ET</t>
+          <t>2026-11-12 11:00 AM ET</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Ideal Trading Corp)</t>
+          <t>AJ Willner Auctions</t>
         </is>
       </c>
       <c r="L54" s="13" t="inlineStr">
@@ -21558,7 +21558,7 @@
       </c>
       <c r="O54" s="14" t="inlineStr">
         <is>
-          <t>Contractor contents; closes Oct 28 11 AM. Hilti tools resell well on eBay.</t>
+          <t>Ends Nov 12 11 AM EST.</t>
         </is>
       </c>
     </row>
@@ -21570,17 +21570,17 @@
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
+          <t>Drywall &amp; Acoustical Contractor 2: Hilti tools, material handling, supplies (Ideal Trading Corp)</t>
         </is>
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>lien sale</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
         <is>
-          <t>Edison</t>
+          <t>Randolph</t>
         </is>
       </c>
       <c r="E55" s="13" t="inlineStr">
@@ -21589,19 +21589,23 @@
         </is>
       </c>
       <c r="F55" s="13" t="n">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G55" s="13" t="inlineStr">
         <is>
-          <t>Online auction, $2K load-out fee</t>
+          <t>Online auction (HiBid terms)</t>
         </is>
       </c>
       <c r="H55" s="15" t="n"/>
       <c r="I55" s="13" t="inlineStr"/>
-      <c r="J55" s="13" t="inlineStr"/>
+      <c r="J55" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:00 AM ET</t>
+        </is>
+      </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>HiBid (Ideal Trading Corp)</t>
         </is>
       </c>
       <c r="L55" s="13" t="inlineStr">
@@ -21617,7 +21621,7 @@
       </c>
       <c r="O55" s="14" t="inlineStr">
         <is>
-          <t>&gt;$100K new. Close date not captured.</t>
+          <t>Contractor contents; closes Oct 28 11 AM. Hilti tools resell well on eBay.</t>
         </is>
       </c>
     </row>
@@ -21629,12 +21633,12 @@
       </c>
       <c r="B56" s="14" t="inlineStr">
         <is>
-          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
+          <t>New modular concession kitchens (warehouseman's lien) – 5 units, CaptiveAire hoods, new Ovention/Turbo Air</t>
         </is>
       </c>
       <c r="C56" s="13" t="inlineStr">
         <is>
-          <t>auction</t>
+          <t>lien sale</t>
         </is>
       </c>
       <c r="D56" s="13" t="inlineStr">
@@ -21652,23 +21656,15 @@
       </c>
       <c r="G56" s="13" t="inlineStr">
         <is>
-          <t>Live + HiBid webcast, 18% BP + 3% card</t>
+          <t>Online auction, $2K load-out fee</t>
         </is>
       </c>
       <c r="H56" s="15" t="n"/>
-      <c r="I56" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-09</t>
-        </is>
-      </c>
-      <c r="J56" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-25 01:00 PM ET</t>
-        </is>
-      </c>
+      <c r="I56" s="13" t="inlineStr"/>
+      <c r="J56" s="13" t="inlineStr"/>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>HiBid (Best Buy Auctioneers)</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L56" s="13" t="inlineStr">
@@ -21676,11 +21672,7 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M56" s="20" t="inlineStr">
-        <is>
-          <t>FLIP</t>
-        </is>
-      </c>
+      <c r="M56" s="13" t="inlineStr"/>
       <c r="N56" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -21688,7 +21680,7 @@
       </c>
       <c r="O56" s="14" t="inlineStr">
         <is>
-          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
+          <t>&gt;$100K new. Close date not captured.</t>
         </is>
       </c>
     </row>
@@ -21700,17 +21692,17 @@
       </c>
       <c r="B57" s="14" t="inlineStr">
         <is>
-          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
+          <t>Brand-new &amp; scratch-and-dent kitchen/home appliances – ~185 lots (Thermador, GE Café, Miele, Wolf speed oven, Viking, Bosch…)</t>
         </is>
       </c>
       <c r="C57" s="13" t="inlineStr">
         <is>
-          <t>store closing</t>
+          <t>auction</t>
         </is>
       </c>
       <c r="D57" s="13" t="inlineStr">
         <is>
-          <t>East Brunswick</t>
+          <t>Edison</t>
         </is>
       </c>
       <c r="E57" s="13" t="inlineStr">
@@ -21719,23 +21711,27 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G57" s="13" t="inlineStr">
         <is>
-          <t>Online auction</t>
+          <t>Live + HiBid webcast, 18% BP + 3% card</t>
         </is>
       </c>
       <c r="H57" s="15" t="n"/>
-      <c r="I57" s="13" t="inlineStr"/>
+      <c r="I57" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
       <c r="J57" s="13" t="inlineStr">
         <is>
-          <t>2026-11-03 11:00 AM ET</t>
+          <t>2026-10-25 01:00 PM ET</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>A.J. Willner</t>
+          <t>HiBid (Best Buy Auctioneers)</t>
         </is>
       </c>
       <c r="L57" s="13" t="inlineStr">
@@ -21743,7 +21739,11 @@
           <t>ACTIVE</t>
         </is>
       </c>
-      <c r="M57" s="13" t="inlineStr"/>
+      <c r="M57" s="20" t="inlineStr">
+        <is>
+          <t>FLIP</t>
+        </is>
+      </c>
       <c r="N57" s="16" t="inlineStr">
         <is>
           <t>Open</t>
@@ -21751,7 +21751,7 @@
       </c>
       <c r="O57" s="14" t="inlineStr">
         <is>
-          <t>Store inventory.</t>
+          <t>Sun Oct 25 1 PM (preview 11 AM), checkout Oct 26. Many lots in box. Recurring appliance sale; the Wolf SPO24TE speed oven lot already on the map is likely from this sale.</t>
         </is>
       </c>
     </row>
@@ -21763,17 +21763,17 @@
       </c>
       <c r="B58" s="14" t="inlineStr">
         <is>
-          <t>Bakery/Cafe Somerville NJ – rack ovens, La Marzocco, food truck (~76 lots)</t>
+          <t>Party City (Ch. 11) store – fixtures + party merchandise inventory</t>
         </is>
       </c>
       <c r="C58" s="13" t="inlineStr">
         <is>
-          <t>restaurant</t>
+          <t>store closing</t>
         </is>
       </c>
       <c r="D58" s="13" t="inlineStr">
         <is>
-          <t>Somerville</t>
+          <t>East Brunswick</t>
         </is>
       </c>
       <c r="E58" s="13" t="inlineStr">
@@ -21782,27 +21782,23 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="G58" s="13" t="inlineStr">
         <is>
-          <t>Live webcast + online (18% BP online)</t>
+          <t>Online auction</t>
         </is>
       </c>
       <c r="H58" s="15" t="n"/>
-      <c r="I58" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-14</t>
-        </is>
-      </c>
+      <c r="I58" s="13" t="inlineStr"/>
       <c r="J58" s="13" t="inlineStr">
         <is>
-          <t>2026-10-26 02:00 PM ET</t>
+          <t>2026-11-03 11:00 AM ET</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
         <is>
-          <t>HiBid / Best Buy Auctioneers</t>
+          <t>A.J. Willner</t>
         </is>
       </c>
       <c r="L58" s="13" t="inlineStr">
@@ -21818,7 +21814,7 @@
       </c>
       <c r="O58" s="14" t="inlineStr">
         <is>
-          <t>Full bakery/cafe commercial kitchen: food truck w/ pizza oven, La Marzocco espresso, Mazzer, Baxter + Empire Logiudice rack ovens, dough depositor, Globe floor mixer, Artic Air / SS refrigeration, fryers, Vitamix, Robot Coupe, display cases, dining furniture. Preview 11 AM sale day; checkout Tue 10/27.</t>
+          <t>Store inventory.</t>
         </is>
       </c>
     </row>
@@ -21830,7 +21826,7 @@
       </c>
       <c r="B59" s="14" t="inlineStr">
         <is>
-          <t>Ability to Work kitchen and store – commercial kitchen + store fixtures (~135 lots)</t>
+          <t>Bakery/Cafe Somerville NJ – rack ovens, La Marzocco, food truck (~76 lots)</t>
         </is>
       </c>
       <c r="C59" s="13" t="inlineStr">
@@ -21840,7 +21836,7 @@
       </c>
       <c r="D59" s="13" t="inlineStr">
         <is>
-          <t>Flemington</t>
+          <t>Somerville</t>
         </is>
       </c>
       <c r="E59" s="13" t="inlineStr">
@@ -21849,23 +21845,27 @@
         </is>
       </c>
       <c r="F59" s="13" t="n">
-        <v>237</v>
+        <v>224</v>
       </c>
       <c r="G59" s="13" t="inlineStr">
         <is>
-          <t>Timed online (15% BP)</t>
+          <t>Live webcast + online (18% BP online)</t>
         </is>
       </c>
       <c r="H59" s="15" t="n"/>
-      <c r="I59" s="13" t="inlineStr"/>
+      <c r="I59" s="13" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
       <c r="J59" s="13" t="inlineStr">
         <is>
-          <t>2026-10-27 11:02 AM ET</t>
+          <t>2026-10-26 02:00 PM ET</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
         <is>
-          <t>HiBid</t>
+          <t>HiBid / Best Buy Auctioneers</t>
         </is>
       </c>
       <c r="L59" s="13" t="inlineStr">
@@ -21881,7 +21881,7 @@
       </c>
       <c r="O59" s="14" t="inlineStr">
         <is>
-          <t>Apprentice/hospitality training cafe-kitchen and store dispersal. Preview 9–11 AM sale day; removal Oct 27 noon–Oct 29.</t>
+          <t>Full bakery/cafe commercial kitchen: food truck w/ pizza oven, La Marzocco espresso, Mazzer, Baxter + Empire Logiudice rack ovens, dough depositor, Globe floor mixer, Artic Air / SS refrigeration, fryers, Vitamix, Robot Coupe, display cases, dining furniture. Preview 11 AM sale day; checkout Tue 10/27.</t>
         </is>
       </c>
     </row>
@@ -21893,17 +21893,17 @@
       </c>
       <c r="B60" s="14" t="inlineStr">
         <is>
-          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
+          <t>Ability to Work kitchen and store – commercial kitchen + store fixtures (~135 lots)</t>
         </is>
       </c>
       <c r="C60" s="13" t="inlineStr">
         <is>
-          <t>showroom closing</t>
+          <t>restaurant</t>
         </is>
       </c>
       <c r="D60" s="13" t="inlineStr">
         <is>
-          <t>Lawrenceville</t>
+          <t>Flemington</t>
         </is>
       </c>
       <c r="E60" s="13" t="inlineStr">
@@ -21912,23 +21912,23 @@
         </is>
       </c>
       <c r="F60" s="13" t="n">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="G60" s="13" t="inlineStr">
         <is>
-          <t>Online auction, 18% BP</t>
+          <t>Timed online (15% BP)</t>
         </is>
       </c>
       <c r="H60" s="15" t="n"/>
       <c r="I60" s="13" t="inlineStr"/>
       <c r="J60" s="13" t="inlineStr">
         <is>
-          <t>2026-10-27 09:00 AM ET</t>
+          <t>2026-10-27 11:02 AM ET</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
         <is>
-          <t>Grafe Auction</t>
+          <t>HiBid</t>
         </is>
       </c>
       <c r="L60" s="13" t="inlineStr">
@@ -21944,7 +21944,7 @@
       </c>
       <c r="O60" s="14" t="inlineStr">
         <is>
-          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
+          <t>Apprentice/hospitality training cafe-kitchen and store dispersal. Preview 9–11 AM sale day; removal Oct 27 noon–Oct 29.</t>
         </is>
       </c>
     </row>
@@ -21956,7 +21956,7 @@
       </c>
       <c r="B61" s="14" t="inlineStr">
         <is>
-          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
+          <t>Wren Kitchens showroom closing – JennAir/Café/KitchenAid/GE Profile appliances + display kitchens</t>
         </is>
       </c>
       <c r="C61" s="13" t="inlineStr">
@@ -21966,7 +21966,7 @@
       </c>
       <c r="D61" s="13" t="inlineStr">
         <is>
-          <t>Cherry Hill</t>
+          <t>Lawrenceville</t>
         </is>
       </c>
       <c r="E61" s="13" t="inlineStr">
@@ -21975,18 +21975,18 @@
         </is>
       </c>
       <c r="F61" s="13" t="n">
-        <v>266</v>
+        <v>239</v>
       </c>
       <c r="G61" s="13" t="inlineStr">
         <is>
-          <t>Online auction, openers ~$0.50</t>
+          <t>Online auction, 18% BP</t>
         </is>
       </c>
       <c r="H61" s="15" t="n"/>
       <c r="I61" s="13" t="inlineStr"/>
       <c r="J61" s="13" t="inlineStr">
         <is>
-          <t>2026-11-02 11:00 AM ET</t>
+          <t>2026-10-27 09:00 AM ET</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
@@ -22007,239 +22007,235 @@
       </c>
       <c r="O61" s="14" t="inlineStr">
         <is>
+          <t>Premium floor-model appliances; lots close from Oct 27 9 AM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" outlineLevel="1">
+      <c r="A62" s="13" t="inlineStr">
+        <is>
+          <t>NYC / Long Island / NJ</t>
+        </is>
+      </c>
+      <c r="B62" s="14" t="inlineStr">
+        <is>
+          <t>Wren Kitchens showroom closing – GE/Whirlpool/KitchenAid/Café incl. NIB Café range + 35 kitchens</t>
+        </is>
+      </c>
+      <c r="C62" s="13" t="inlineStr">
+        <is>
+          <t>showroom closing</t>
+        </is>
+      </c>
+      <c r="D62" s="13" t="inlineStr">
+        <is>
+          <t>Cherry Hill</t>
+        </is>
+      </c>
+      <c r="E62" s="13" t="inlineStr">
+        <is>
+          <t>NJ</t>
+        </is>
+      </c>
+      <c r="F62" s="13" t="n">
+        <v>266</v>
+      </c>
+      <c r="G62" s="13" t="inlineStr">
+        <is>
+          <t>Online auction, openers ~$0.50</t>
+        </is>
+      </c>
+      <c r="H62" s="15" t="n"/>
+      <c r="I62" s="13" t="inlineStr"/>
+      <c r="J62" s="13" t="inlineStr">
+        <is>
+          <t>2026-11-02 11:00 AM ET</t>
+        </is>
+      </c>
+      <c r="K62" s="13" t="inlineStr">
+        <is>
+          <t>Grafe Auction</t>
+        </is>
+      </c>
+      <c r="L62" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M62" s="13" t="inlineStr"/>
+      <c r="N62" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O62" s="14" t="inlineStr">
+        <is>
           <t>Lots close from Nov 2 11 AM.</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="17" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="17" t="inlineStr">
         <is>
           <t>Subtotal — NYC / Long Island / NJ</t>
         </is>
       </c>
-      <c r="B62" s="17" t="inlineStr">
+      <c r="B63" s="17" t="inlineStr">
         <is>
           <t>23 item(s)</t>
         </is>
       </c>
-      <c r="C62" s="18" t="n"/>
-      <c r="D62" s="18" t="n"/>
-      <c r="E62" s="18" t="n"/>
-      <c r="F62" s="18" t="n"/>
-      <c r="G62" s="18" t="n"/>
-      <c r="H62" s="19" t="n">
+      <c r="C63" s="18" t="n"/>
+      <c r="D63" s="18" t="n"/>
+      <c r="E63" s="18" t="n"/>
+      <c r="F63" s="18" t="n"/>
+      <c r="G63" s="18" t="n"/>
+      <c r="H63" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I62" s="18" t="n"/>
-      <c r="J62" s="18" t="n"/>
-      <c r="K62" s="18" t="n"/>
-      <c r="L62" s="18" t="n"/>
-      <c r="M62" s="18" t="n"/>
-      <c r="N62" s="18" t="n"/>
-      <c r="O62" s="18" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="11" t="inlineStr">
+      <c r="I63" s="18" t="n"/>
+      <c r="J63" s="18" t="n"/>
+      <c r="K63" s="18" t="n"/>
+      <c r="L63" s="18" t="n"/>
+      <c r="M63" s="18" t="n"/>
+      <c r="N63" s="18" t="n"/>
+      <c r="O63" s="18" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
         <is>
           <t>▸ Eastern PA / Mid-Atlantic  (1)</t>
         </is>
       </c>
-      <c r="B63" s="12" t="n"/>
-      <c r="C63" s="12" t="n"/>
-      <c r="D63" s="12" t="n"/>
-      <c r="E63" s="12" t="n"/>
-      <c r="F63" s="12" t="n"/>
-      <c r="G63" s="12" t="n"/>
-      <c r="H63" s="12" t="n"/>
-      <c r="I63" s="12" t="n"/>
-      <c r="J63" s="12" t="n"/>
-      <c r="K63" s="12" t="n"/>
-      <c r="L63" s="12" t="n"/>
-      <c r="M63" s="12" t="n"/>
-      <c r="N63" s="12" t="n"/>
-      <c r="O63" s="12" t="n"/>
-    </row>
-    <row r="64" outlineLevel="1">
-      <c r="A64" s="13" t="inlineStr">
+      <c r="B64" s="12" t="n"/>
+      <c r="C64" s="12" t="n"/>
+      <c r="D64" s="12" t="n"/>
+      <c r="E64" s="12" t="n"/>
+      <c r="F64" s="12" t="n"/>
+      <c r="G64" s="12" t="n"/>
+      <c r="H64" s="12" t="n"/>
+      <c r="I64" s="12" t="n"/>
+      <c r="J64" s="12" t="n"/>
+      <c r="K64" s="12" t="n"/>
+      <c r="L64" s="12" t="n"/>
+      <c r="M64" s="12" t="n"/>
+      <c r="N64" s="12" t="n"/>
+      <c r="O64" s="12" t="n"/>
+    </row>
+    <row r="65" outlineLevel="1">
+      <c r="A65" s="13" t="inlineStr">
         <is>
           <t>Eastern PA / Mid-Atlantic</t>
         </is>
       </c>
-      <c r="B64" s="14" t="inlineStr">
+      <c r="B65" s="14" t="inlineStr">
         <is>
           <t>Piscitello's Home Center closing after 68 years: storewide 20% off liquidation (hardware, lumber, doors, windows, kitchen/bath)</t>
         </is>
       </c>
-      <c r="C64" s="13" t="inlineStr">
+      <c r="C65" s="13" t="inlineStr">
         <is>
           <t>store closing</t>
         </is>
       </c>
-      <c r="D64" s="13" t="inlineStr">
+      <c r="D65" s="13" t="inlineStr">
         <is>
           <t>Wilson</t>
         </is>
       </c>
-      <c r="E64" s="13" t="inlineStr">
+      <c r="E65" s="13" t="inlineStr">
         <is>
           <t>PA</t>
         </is>
       </c>
-      <c r="F64" s="13" t="n">
+      <c r="F65" s="13" t="n">
         <v>250</v>
       </c>
-      <c r="G64" s="13" t="inlineStr">
+      <c r="G65" s="13" t="inlineStr">
         <is>
           <t>20% off storewide (all sales final)</t>
         </is>
       </c>
-      <c r="H64" s="15" t="n"/>
-      <c r="I64" s="13" t="inlineStr">
+      <c r="H65" s="15" t="n"/>
+      <c r="I65" s="13" t="inlineStr">
         <is>
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="J64" s="13" t="inlineStr">
+      <c r="J65" s="13" t="inlineStr">
         <is>
           <t>2026-10-30 06:00 PM ET</t>
         </is>
       </c>
-      <c r="K64" s="13" t="inlineStr">
+      <c r="K65" s="13" t="inlineStr">
         <is>
           <t>LehighValley.com article</t>
         </is>
       </c>
-      <c r="L64" s="13" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="M64" s="13" t="inlineStr"/>
-      <c r="N64" s="16" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="O64" s="14" t="inlineStr">
+      <c r="L65" s="13" t="inlineStr">
+        <is>
+          <t>ACTIVE</t>
+        </is>
+      </c>
+      <c r="M65" s="13" t="inlineStr"/>
+      <c r="N65" s="16" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="O65" s="14" t="inlineStr">
         <is>
           <t>2300 Wood Ave, Wilson Borough (Easton area). Final day Oct 30. Retail-floor sale, not a bulk lot; ask in person about buying remaining stock outright.</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="17" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="17" t="inlineStr">
         <is>
           <t>Subtotal — Eastern PA / Mid-Atlantic</t>
         </is>
       </c>
-      <c r="B65" s="17" t="inlineStr">
+      <c r="B66" s="17" t="inlineStr">
         <is>
           <t>1 item(s)</t>
         </is>
       </c>
-      <c r="C65" s="18" t="n"/>
-      <c r="D65" s="18" t="n"/>
-      <c r="E65" s="18" t="n"/>
-      <c r="F65" s="18" t="n"/>
-      <c r="G65" s="18" t="n"/>
-      <c r="H65" s="19" t="n">
+      <c r="C66" s="18" t="n"/>
+      <c r="D66" s="18" t="n"/>
+      <c r="E66" s="18" t="n"/>
+      <c r="F66" s="18" t="n"/>
+      <c r="G66" s="18" t="n"/>
+      <c r="H66" s="19" t="n">
         <v>0</v>
       </c>
-      <c r="I65" s="18" t="n"/>
-      <c r="J65" s="18" t="n"/>
-      <c r="K65" s="18" t="n"/>
-      <c r="L65" s="18" t="n"/>
-      <c r="M65" s="18" t="n"/>
-      <c r="N65" s="18" t="n"/>
-      <c r="O65" s="18" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="11" t="inlineStr">
-        <is>
-          <t>▸ Western PA / Ohio Valley  (3)</t>
-        </is>
-      </c>
-      <c r="B66" s="12" t="n"/>
-      <c r="C66" s="12" t="n"/>
-      <c r="D66" s="12" t="n"/>
-      <c r="E66" s="12" t="n"/>
-      <c r="F66" s="12" t="n"/>
-      <c r="G66" s="12" t="n"/>
-      <c r="H66" s="12" t="n"/>
-      <c r="I66" s="12" t="n"/>
-      <c r="J66" s="12" t="n"/>
-      <c r="K66" s="12" t="n"/>
-      <c r="L66" s="12" t="n"/>
-      <c r="M66" s="12" t="n"/>
-      <c r="N66" s="12" t="n"/>
-      <c r="O66" s="12" t="n"/>
-    </row>
-    <row r="67" outlineLevel="1">
-      <c r="A67" s="13" t="inlineStr">
-        <is>
-          <t>Western PA / Ohio Valley</t>
-        </is>
-      </c>
-      <c r="B67" s="14" t="inlineStr">
-        <is>
-          <t>Petrunak's Hardware Store liquidation Day 1 (530 lots: doors, hardware, tools, building supplies)</t>
-        </is>
-      </c>
-      <c r="C67" s="13" t="inlineStr">
-        <is>
-          <t>store closing auction</t>
-        </is>
-      </c>
-      <c r="D67" s="13" t="inlineStr">
-        <is>
-          <t>Windber</t>
-        </is>
-      </c>
-      <c r="E67" s="13" t="inlineStr">
-        <is>
-          <t>PA</t>
-        </is>
-      </c>
-      <c r="F67" s="13" t="n">
-        <v>437</v>
-      </c>
-      <c r="G67" s="13" t="inlineStr">
-        <is>
-          <t>Timed online auction (530 lots)</t>
-        </is>
-      </c>
-      <c r="H67" s="15" t="n"/>
-      <c r="I67" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="J67" s="13" t="inlineStr">
-        <is>
-          <t>2026-10-21 08:00 PM ET</t>
-        </is>
-      </c>
-      <c r="K67" s="13